--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28770" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="174">
   <si>
     <t>道具ID</t>
   </si>
@@ -706,6 +706,51 @@
   </si>
   <si>
     <t>wddc_pz_5.png</t>
+  </si>
+  <si>
+    <t>能量</t>
+  </si>
+  <si>
+    <t>SLOT游戏需求材料</t>
+  </si>
+  <si>
+    <t>知名度</t>
+  </si>
+  <si>
+    <t>建筑收益</t>
+  </si>
+  <si>
+    <t>曝光度</t>
+  </si>
+  <si>
+    <t>经营经验</t>
+  </si>
+  <si>
+    <t>研究点</t>
+  </si>
+  <si>
+    <t>升级游戏特殊词条</t>
+  </si>
+  <si>
+    <t>稀有研究点</t>
+  </si>
+  <si>
+    <t>加速卡</t>
+  </si>
+  <si>
+    <t>加速建筑升级的CD时间</t>
+  </si>
+  <si>
+    <t>雇员升级材料1</t>
+  </si>
+  <si>
+    <t>雇员升级材料2</t>
+  </si>
+  <si>
+    <t>雇员升级材料3</t>
+  </si>
+  <si>
+    <t>游客升级经验</t>
   </si>
 </sst>
 </file>
@@ -1941,7 +1986,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -2107,7 +2152,7 @@
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
     </row>
-    <row r="5" ht="21" customHeight="1" spans="1:18">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>1990000</v>
       </c>
@@ -2152,7 +2197,7 @@
         <v>1.42857142857143e-6</v>
       </c>
     </row>
-    <row r="6" ht="21" customHeight="1" spans="1:18">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>1980000</v>
       </c>
@@ -2197,7 +2242,7 @@
         <v>0.00142857142857143</v>
       </c>
     </row>
-    <row r="7" ht="21" customHeight="1" spans="1:18">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>1970000</v>
       </c>
@@ -2238,7 +2283,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" ht="21" customHeight="1" spans="1:18">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>1020001</v>
       </c>
@@ -2279,7 +2324,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:18">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>1022501</v>
       </c>
@@ -2323,7 +2368,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1" spans="1:18">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>1022502</v>
       </c>
@@ -2367,7 +2412,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1" spans="1:18">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>1022503</v>
       </c>
@@ -2411,7 +2456,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="12" s="1" customFormat="1" spans="1:18">
       <c r="A12" s="1">
         <v>1010301</v>
       </c>
@@ -2459,7 +2504,7 @@
         <v>0.099</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="13" s="1" customFormat="1" spans="1:18">
       <c r="A13" s="1">
         <v>1010302</v>
       </c>
@@ -2508,7 +2553,7 @@
         <v>0.198</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="14" s="1" customFormat="1" spans="1:18">
       <c r="A14" s="1">
         <v>1010303</v>
       </c>
@@ -2557,7 +2602,7 @@
         <v>0.594</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="15" s="1" customFormat="1" spans="1:18">
       <c r="A15" s="1">
         <v>1010304</v>
       </c>
@@ -2606,7 +2651,7 @@
         <v>0.792</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="16" s="1" customFormat="1" spans="1:18">
       <c r="A16" s="1">
         <v>1010305</v>
       </c>
@@ -2655,7 +2700,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="17" ht="23.1" customHeight="1" spans="1:15">
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>1031001</v>
       </c>
@@ -2696,7 +2741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="23.1" customHeight="1" spans="1:15">
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>1031002</v>
       </c>
@@ -2737,7 +2782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="23.1" customHeight="1" spans="1:15">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>1031201</v>
       </c>
@@ -2778,7 +2823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="23.1" customHeight="1" spans="1:15">
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>1031202</v>
       </c>
@@ -2819,7 +2864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="23.1" customHeight="1" spans="1:15">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>1031350</v>
       </c>
@@ -2860,7 +2905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="23.1" customHeight="1" spans="1:15">
+    <row r="22" spans="1:15">
       <c r="A22">
         <v>1031351</v>
       </c>
@@ -2901,7 +2946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="23.1" customHeight="1" spans="1:15">
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>1021401</v>
       </c>
@@ -2942,7 +2987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="23.1" customHeight="1" spans="1:15">
+    <row r="24" spans="1:15">
       <c r="A24">
         <v>1021402</v>
       </c>
@@ -2983,7 +3028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="23.1" customHeight="1" spans="1:15">
+    <row r="25" s="2" customFormat="1" spans="1:15">
       <c r="A25" s="2">
         <v>1031600</v>
       </c>
@@ -3024,7 +3069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="23.1" customHeight="1" spans="1:15">
+    <row r="26" spans="1:15">
       <c r="A26">
         <v>1031601</v>
       </c>
@@ -3065,7 +3110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="23.1" customHeight="1" spans="1:15">
+    <row r="27" spans="1:15">
       <c r="A27">
         <v>1031602</v>
       </c>
@@ -3106,7 +3151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="23.1" customHeight="1" spans="1:15">
+    <row r="28" spans="1:15">
       <c r="A28">
         <v>1031801</v>
       </c>
@@ -3147,7 +3192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="23.1" customHeight="1" spans="1:15">
+    <row r="29" spans="1:15">
       <c r="A29">
         <v>1031802</v>
       </c>
@@ -3188,7 +3233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="23.1" customHeight="1" spans="1:15">
+    <row r="30" spans="1:15">
       <c r="A30">
         <v>1032001</v>
       </c>
@@ -3229,7 +3274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="23.1" customHeight="1" spans="1:15">
+    <row r="31" spans="1:15">
       <c r="A31">
         <v>1032002</v>
       </c>
@@ -3270,7 +3315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="23.1" customHeight="1" spans="1:15">
+    <row r="32" spans="1:15">
       <c r="A32">
         <v>1032201</v>
       </c>
@@ -3311,7 +3356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="23.1" customHeight="1" spans="1:18">
+    <row r="33" spans="1:18">
       <c r="A33">
         <v>1032202</v>
       </c>
@@ -3352,7 +3397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1" spans="1:18">
+    <row r="34" spans="1:18">
       <c r="A34">
         <v>1022504</v>
       </c>
@@ -3393,7 +3438,7 @@
         <v>999999999</v>
       </c>
     </row>
-    <row r="35" ht="21" customHeight="1" spans="1:18">
+    <row r="35" spans="1:18">
       <c r="A35">
         <v>1023001</v>
       </c>
@@ -3435,7 +3480,7 @@
         <v>0.000544077728550903</v>
       </c>
     </row>
-    <row r="36" ht="21" customHeight="1" spans="1:18">
+    <row r="36" spans="1:18">
       <c r="A36">
         <v>1023002</v>
       </c>
@@ -3477,7 +3522,7 @@
         <v>0.0045080726079932</v>
       </c>
     </row>
-    <row r="37" ht="21" customHeight="1" spans="1:18">
+    <row r="37" spans="1:18">
       <c r="A37">
         <v>1023003</v>
       </c>
@@ -3519,7 +3564,7 @@
         <v>0.0067621089119898</v>
       </c>
     </row>
-    <row r="38" ht="21" customHeight="1" spans="1:18">
+    <row r="38" spans="1:18">
       <c r="A38">
         <v>1023004</v>
       </c>
@@ -3561,7 +3606,7 @@
         <v>0.012622603302381</v>
       </c>
     </row>
-    <row r="39" ht="21" customHeight="1" spans="1:18">
+    <row r="39" spans="1:18">
       <c r="A39">
         <v>1023005</v>
       </c>
@@ -3603,7 +3648,7 @@
         <v>0.0139155435712012</v>
       </c>
     </row>
-    <row r="40" ht="21" customHeight="1" spans="1:18">
+    <row r="40" spans="1:18">
       <c r="A40">
         <v>1023101</v>
       </c>
@@ -3645,7 +3690,7 @@
         <v>0.00174104873136289</v>
       </c>
     </row>
-    <row r="41" ht="21" customHeight="1" spans="1:18">
+    <row r="41" spans="1:18">
       <c r="A41">
         <v>1023102</v>
       </c>
@@ -3687,7 +3732,7 @@
         <v>0.0144258323455782</v>
       </c>
     </row>
-    <row r="42" ht="21" customHeight="1" spans="1:18">
+    <row r="42" spans="1:18">
       <c r="A42">
         <v>1023103</v>
       </c>
@@ -3729,7 +3774,7 @@
         <v>0.0216387485183673</v>
       </c>
     </row>
-    <row r="43" ht="21" customHeight="1" spans="1:18">
+    <row r="43" spans="1:18">
       <c r="A43">
         <v>1023104</v>
       </c>
@@ -3771,7 +3816,7 @@
         <v>0.0403923305676191</v>
       </c>
     </row>
-    <row r="44" ht="21" customHeight="1" spans="1:18">
+    <row r="44" spans="1:18">
       <c r="A44">
         <v>1023105</v>
       </c>
@@ -3813,7 +3858,7 @@
         <v>0.0445297394278439</v>
       </c>
     </row>
-    <row r="45" ht="21" customHeight="1" spans="1:18">
+    <row r="45" spans="1:18">
       <c r="A45">
         <v>1023201</v>
       </c>
@@ -3855,7 +3900,7 @@
         <v>0.00348209746272578</v>
       </c>
     </row>
-    <row r="46" ht="21" customHeight="1" spans="1:18">
+    <row r="46" spans="1:18">
       <c r="A46">
         <v>1023202</v>
       </c>
@@ -3897,7 +3942,7 @@
         <v>0.0288516646911565</v>
       </c>
     </row>
-    <row r="47" ht="21" customHeight="1" spans="1:18">
+    <row r="47" spans="1:18">
       <c r="A47">
         <v>1023203</v>
       </c>
@@ -3939,7 +3984,7 @@
         <v>0.0432774970367347</v>
       </c>
     </row>
-    <row r="48" ht="21" customHeight="1" spans="1:18">
+    <row r="48" spans="1:18">
       <c r="A48">
         <v>1023204</v>
       </c>
@@ -3981,7 +4026,7 @@
         <v>0.0807846611352381</v>
       </c>
     </row>
-    <row r="49" ht="21" customHeight="1" spans="1:18">
+    <row r="49" spans="1:18">
       <c r="A49">
         <v>1023205</v>
       </c>
@@ -4023,7 +4068,7 @@
         <v>0.0890594788556878</v>
       </c>
     </row>
-    <row r="50" ht="21" customHeight="1" spans="1:18">
+    <row r="50" spans="1:18">
       <c r="A50">
         <v>1023301</v>
       </c>
@@ -4065,7 +4110,7 @@
         <v>0.0039173596455665</v>
       </c>
     </row>
-    <row r="51" ht="21" customHeight="1" spans="1:18">
+    <row r="51" spans="1:18">
       <c r="A51">
         <v>1023302</v>
       </c>
@@ -4107,7 +4152,7 @@
         <v>0.032458122777551</v>
       </c>
     </row>
-    <row r="52" ht="21" customHeight="1" spans="1:18">
+    <row r="52" spans="1:18">
       <c r="A52">
         <v>1023303</v>
       </c>
@@ -4149,7 +4194,7 @@
         <v>0.0486871841663265</v>
       </c>
     </row>
-    <row r="53" ht="21" customHeight="1" spans="1:18">
+    <row r="53" spans="1:18">
       <c r="A53">
         <v>1023304</v>
       </c>
@@ -4191,7 +4236,7 @@
         <v>0.0908827437771429</v>
       </c>
     </row>
-    <row r="54" ht="21" customHeight="1" spans="1:18">
+    <row r="54" spans="1:18">
       <c r="A54">
         <v>1023305</v>
       </c>
@@ -4233,7 +4278,7 @@
         <v>0.100191913712649</v>
       </c>
     </row>
-    <row r="55" ht="21" customHeight="1" spans="1:18">
+    <row r="55" spans="1:18">
       <c r="A55">
         <v>1023401</v>
       </c>
@@ -4275,7 +4320,7 @@
         <v>0.00783471929113301</v>
       </c>
     </row>
-    <row r="56" ht="21" customHeight="1" spans="1:18">
+    <row r="56" spans="1:18">
       <c r="A56">
         <v>1023402</v>
       </c>
@@ -4317,7 +4362,7 @@
         <v>0.064916245555102</v>
       </c>
     </row>
-    <row r="57" ht="21" customHeight="1" spans="1:18">
+    <row r="57" spans="1:18">
       <c r="A57">
         <v>1023403</v>
       </c>
@@ -4359,7 +4404,7 @@
         <v>0.097374368332653</v>
       </c>
     </row>
-    <row r="58" ht="21" customHeight="1" spans="1:18">
+    <row r="58" spans="1:18">
       <c r="A58">
         <v>1023404</v>
       </c>
@@ -4401,7 +4446,7 @@
         <v>0.181765487554286</v>
       </c>
     </row>
-    <row r="59" ht="21" customHeight="1" spans="1:18">
+    <row r="59" spans="1:18">
       <c r="A59">
         <v>1023405</v>
       </c>
@@ -4441,6 +4486,424 @@
       </c>
       <c r="R59">
         <v>0.200383827425298</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60">
+        <v>1024001</v>
+      </c>
+      <c r="C60">
+        <v>1024001</v>
+      </c>
+      <c r="D60" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="F60" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60" t="s">
+        <v>158</v>
+      </c>
+      <c r="J60">
+        <v>2024001</v>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="s">
+        <v>160</v>
+      </c>
+      <c r="O60">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61">
+        <v>1024002</v>
+      </c>
+      <c r="C61">
+        <v>1024002</v>
+      </c>
+      <c r="D61" t="s">
+        <v>161</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61" t="s">
+        <v>43</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" t="s">
+        <v>158</v>
+      </c>
+      <c r="J61">
+        <v>2024002</v>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
+        <v>162</v>
+      </c>
+      <c r="O61">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62">
+        <v>1024003</v>
+      </c>
+      <c r="C62">
+        <v>1024003</v>
+      </c>
+      <c r="D62" t="s">
+        <v>163</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62" t="s">
+        <v>43</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62" t="s">
+        <v>158</v>
+      </c>
+      <c r="J62">
+        <v>2024003</v>
+      </c>
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="s">
+        <v>162</v>
+      </c>
+      <c r="O62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63">
+        <v>1024004</v>
+      </c>
+      <c r="C63">
+        <v>1024004</v>
+      </c>
+      <c r="D63" t="s">
+        <v>164</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63" t="s">
+        <v>43</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63" t="s">
+        <v>158</v>
+      </c>
+      <c r="J63">
+        <v>2024004</v>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="s">
+        <v>162</v>
+      </c>
+      <c r="O63">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64">
+        <v>1024005</v>
+      </c>
+      <c r="C64">
+        <v>1024005</v>
+      </c>
+      <c r="D64" t="s">
+        <v>165</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64" t="s">
+        <v>43</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="s">
+        <v>158</v>
+      </c>
+      <c r="J64">
+        <v>2024005</v>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="s">
+        <v>166</v>
+      </c>
+      <c r="O64">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65">
+        <v>1024006</v>
+      </c>
+      <c r="C65">
+        <v>1024006</v>
+      </c>
+      <c r="D65" t="s">
+        <v>167</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65" t="s">
+        <v>43</v>
+      </c>
+      <c r="G65">
+        <v>5</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="s">
+        <v>158</v>
+      </c>
+      <c r="J65">
+        <v>2024006</v>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
+        <v>166</v>
+      </c>
+      <c r="O65">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66">
+        <v>1024007</v>
+      </c>
+      <c r="C66">
+        <v>1024007</v>
+      </c>
+      <c r="D66" t="s">
+        <v>168</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>43</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>158</v>
+      </c>
+      <c r="J66">
+        <v>2024007</v>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="s">
+        <v>169</v>
+      </c>
+      <c r="O66">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67">
+        <v>1024008</v>
+      </c>
+      <c r="C67">
+        <v>1024008</v>
+      </c>
+      <c r="D67" t="s">
+        <v>170</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67" t="s">
+        <v>43</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="s">
+        <v>158</v>
+      </c>
+      <c r="J67">
+        <v>2024008</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="s">
+        <v>170</v>
+      </c>
+      <c r="O67">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68">
+        <v>1024009</v>
+      </c>
+      <c r="C68">
+        <v>1024009</v>
+      </c>
+      <c r="D68" t="s">
+        <v>171</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" t="s">
+        <v>158</v>
+      </c>
+      <c r="J68">
+        <v>2024009</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
+        <v>171</v>
+      </c>
+      <c r="O68">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69">
+        <v>1024010</v>
+      </c>
+      <c r="C69">
+        <v>1024010</v>
+      </c>
+      <c r="D69" t="s">
+        <v>172</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69" t="s">
+        <v>43</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" t="s">
+        <v>158</v>
+      </c>
+      <c r="J69">
+        <v>2024010</v>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
+        <v>172</v>
+      </c>
+      <c r="O69">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70">
+        <v>1024011</v>
+      </c>
+      <c r="C70">
+        <v>1024011</v>
+      </c>
+      <c r="D70" t="s">
+        <v>173</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70" t="s">
+        <v>43</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" t="s">
+        <v>158</v>
+      </c>
+      <c r="J70">
+        <v>2024011</v>
+      </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>173</v>
+      </c>
+      <c r="O70">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="175">
   <si>
     <t>道具ID</t>
   </si>
@@ -751,6 +751,9 @@
   </si>
   <si>
     <t>游客升级经验</t>
+  </si>
+  <si>
+    <t>服务能力</t>
   </si>
 </sst>
 </file>
@@ -1986,7 +1989,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -4508,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="s">
         <v>158</v>
@@ -4546,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="s">
         <v>158</v>
@@ -4584,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="s">
         <v>158</v>
@@ -4622,7 +4625,7 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="s">
         <v>158</v>
@@ -4660,7 +4663,7 @@
         <v>1</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="s">
         <v>158</v>
@@ -4698,7 +4701,7 @@
         <v>5</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="s">
         <v>158</v>
@@ -4774,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="s">
         <v>158</v>
@@ -4812,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="s">
         <v>158</v>
@@ -4850,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="s">
         <v>158</v>
@@ -4888,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="s">
         <v>158</v>
@@ -4903,6 +4906,44 @@
         <v>173</v>
       </c>
       <c r="O70">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71">
+        <v>1024012</v>
+      </c>
+      <c r="C71">
+        <v>1024012</v>
+      </c>
+      <c r="D71" t="s">
+        <v>174</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="F71" t="s">
+        <v>43</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71" t="s">
+        <v>158</v>
+      </c>
+      <c r="J71">
+        <v>2024012</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>174</v>
+      </c>
+      <c r="O71">
         <v>-1</v>
       </c>
     </row>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -85,7 +85,8 @@
 3：蓝
 4：紫
 5：橙
-6：红</t>
+6：红
+7：金</t>
         </r>
       </text>
     </comment>
@@ -224,12 +225,80 @@
         </r>
       </text>
     </comment>
+    <comment ref="A162" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1026代表雇员类别-导玩员（游戏区）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A172" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1027代表雇员类别-服务员员（休息区）
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A182" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1028代表雇员类别-管理员（管理区）
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="235">
   <si>
     <t>道具ID</t>
   </si>
@@ -754,6 +823,186 @@
   </si>
   <si>
     <t>服务能力</t>
+  </si>
+  <si>
+    <t>街头潮人</t>
+  </si>
+  <si>
+    <t>复古绅士</t>
+  </si>
+  <si>
+    <t>酷盖少年</t>
+  </si>
+  <si>
+    <t>潮流先锋</t>
+  </si>
+  <si>
+    <t>时尚教主</t>
+  </si>
+  <si>
+    <t>街拍达人</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
+  </si>
+  <si>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
+    <t>健身狂魔</t>
+  </si>
+  <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
+    <t>登山行者</t>
+  </si>
+  <si>
+    <t>文艺青年</t>
+  </si>
+  <si>
+    <t>书香少女</t>
+  </si>
+  <si>
+    <t>民谣歌手</t>
+  </si>
+  <si>
+    <t>马拉松客</t>
+  </si>
+  <si>
+    <t>极限玩家</t>
+  </si>
+  <si>
+    <t>科技极客</t>
+  </si>
+  <si>
+    <t>独立画家</t>
+  </si>
+  <si>
+    <t>浪漫诗人</t>
+  </si>
+  <si>
+    <t>古典乐迷</t>
+  </si>
+  <si>
+    <t>创业新贵</t>
+  </si>
+  <si>
+    <t>摸金校尉</t>
+  </si>
+  <si>
+    <t>氪金大佬</t>
+  </si>
+  <si>
+    <t>穿搭博主</t>
+  </si>
+  <si>
+    <t>美妆新秀</t>
+  </si>
+  <si>
+    <t>高定女王</t>
+  </si>
+  <si>
+    <t>威廉</t>
+  </si>
+  <si>
+    <t>艾拉</t>
+  </si>
+  <si>
+    <t>亨利</t>
+  </si>
+  <si>
+    <t>艾玛</t>
+  </si>
+  <si>
+    <t>乔治</t>
+  </si>
+  <si>
+    <t>艾娃</t>
+  </si>
+  <si>
+    <t>亚瑟</t>
+  </si>
+  <si>
+    <t>安娜</t>
+  </si>
+  <si>
+    <t>马修</t>
+  </si>
+  <si>
+    <t>哈珀</t>
+  </si>
+  <si>
+    <t>拉斐尔</t>
+  </si>
+  <si>
+    <t>伊芙琳</t>
+  </si>
+  <si>
+    <t>埃米尔</t>
+  </si>
+  <si>
+    <t>夏洛特</t>
+  </si>
+  <si>
+    <t>雷蒙德</t>
+  </si>
+  <si>
+    <t>斯嘉丽</t>
+  </si>
+  <si>
+    <t>丹尼尔</t>
+  </si>
+  <si>
+    <t>莉莉安</t>
+  </si>
+  <si>
+    <t>卢卡斯</t>
+  </si>
+  <si>
+    <t>克拉拉</t>
+  </si>
+  <si>
+    <t>尼古拉斯</t>
+  </si>
+  <si>
+    <t>奥利维亚</t>
+  </si>
+  <si>
+    <t>亚历山大</t>
+  </si>
+  <si>
+    <t>玛格丽特</t>
+  </si>
+  <si>
+    <t>奥古斯特</t>
+  </si>
+  <si>
+    <t>维奥莱特</t>
+  </si>
+  <si>
+    <t>费利克斯</t>
+  </si>
+  <si>
+    <t>维多利亚</t>
+  </si>
+  <si>
+    <t>阿尔弗雷德</t>
+  </si>
+  <si>
+    <t>伊丽莎白</t>
   </si>
 </sst>
 </file>
@@ -1989,7 +2238,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R191"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -4947,6 +5196,4686 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="72" spans="1:15">
+      <c r="A72">
+        <v>1025101</v>
+      </c>
+      <c r="C72">
+        <v>1025101</v>
+      </c>
+      <c r="D72" t="s">
+        <v>175</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>158</v>
+      </c>
+      <c r="J72">
+        <v>2025101</v>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
+        <v>175</v>
+      </c>
+      <c r="O72">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73">
+        <v>1025102</v>
+      </c>
+      <c r="C73">
+        <v>1025102</v>
+      </c>
+      <c r="D73" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73" t="s">
+        <v>43</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>158</v>
+      </c>
+      <c r="J73">
+        <v>2025102</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>176</v>
+      </c>
+      <c r="O73">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74">
+        <v>1025103</v>
+      </c>
+      <c r="C74">
+        <v>1025103</v>
+      </c>
+      <c r="D74" t="s">
+        <v>177</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
+        <v>43</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74" t="s">
+        <v>158</v>
+      </c>
+      <c r="J74">
+        <v>2025103</v>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>177</v>
+      </c>
+      <c r="O74">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75">
+        <v>1025104</v>
+      </c>
+      <c r="C75">
+        <v>1025104</v>
+      </c>
+      <c r="D75" t="s">
+        <v>178</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>43</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>158</v>
+      </c>
+      <c r="J75">
+        <v>2025104</v>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>178</v>
+      </c>
+      <c r="O75">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76">
+        <v>1025105</v>
+      </c>
+      <c r="C76">
+        <v>1025105</v>
+      </c>
+      <c r="D76" t="s">
+        <v>179</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>158</v>
+      </c>
+      <c r="J76">
+        <v>2025105</v>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>179</v>
+      </c>
+      <c r="O76">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77">
+        <v>1025106</v>
+      </c>
+      <c r="C77">
+        <v>1025106</v>
+      </c>
+      <c r="D77" t="s">
+        <v>180</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="F77" t="s">
+        <v>43</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>158</v>
+      </c>
+      <c r="J77">
+        <v>2025106</v>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>180</v>
+      </c>
+      <c r="O77">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78">
+        <v>1025201</v>
+      </c>
+      <c r="C78">
+        <v>1025201</v>
+      </c>
+      <c r="D78" t="s">
+        <v>181</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="F78" t="s">
+        <v>43</v>
+      </c>
+      <c r="G78">
+        <v>2</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78" t="s">
+        <v>158</v>
+      </c>
+      <c r="J78">
+        <v>2025201</v>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>181</v>
+      </c>
+      <c r="O78">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79">
+        <v>1025202</v>
+      </c>
+      <c r="C79">
+        <v>1025202</v>
+      </c>
+      <c r="D79" t="s">
+        <v>182</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="F79" t="s">
+        <v>43</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>158</v>
+      </c>
+      <c r="J79">
+        <v>2025202</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>182</v>
+      </c>
+      <c r="O79">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80">
+        <v>1025203</v>
+      </c>
+      <c r="C80">
+        <v>1025203</v>
+      </c>
+      <c r="D80" t="s">
+        <v>183</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="F80" t="s">
+        <v>43</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80" t="s">
+        <v>158</v>
+      </c>
+      <c r="J80">
+        <v>2025203</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>183</v>
+      </c>
+      <c r="O80">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81">
+        <v>1025204</v>
+      </c>
+      <c r="C81">
+        <v>1025204</v>
+      </c>
+      <c r="D81" t="s">
+        <v>184</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="F81" t="s">
+        <v>43</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>158</v>
+      </c>
+      <c r="J81">
+        <v>2025204</v>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>184</v>
+      </c>
+      <c r="O81">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82">
+        <v>1025205</v>
+      </c>
+      <c r="C82">
+        <v>1025205</v>
+      </c>
+      <c r="D82" t="s">
+        <v>185</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="F82" t="s">
+        <v>43</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82" t="s">
+        <v>158</v>
+      </c>
+      <c r="J82">
+        <v>2025205</v>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>185</v>
+      </c>
+      <c r="O82">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83">
+        <v>1025206</v>
+      </c>
+      <c r="C83">
+        <v>1025206</v>
+      </c>
+      <c r="D83" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="F83" t="s">
+        <v>43</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83" t="s">
+        <v>158</v>
+      </c>
+      <c r="J83">
+        <v>2025206</v>
+      </c>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>186</v>
+      </c>
+      <c r="O83">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84">
+        <v>1025301</v>
+      </c>
+      <c r="C84">
+        <v>1025301</v>
+      </c>
+      <c r="D84" t="s">
+        <v>187</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="F84" t="s">
+        <v>43</v>
+      </c>
+      <c r="G84">
+        <v>3</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84" t="s">
+        <v>158</v>
+      </c>
+      <c r="J84">
+        <v>2025301</v>
+      </c>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>187</v>
+      </c>
+      <c r="O84">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85">
+        <v>1025302</v>
+      </c>
+      <c r="C85">
+        <v>1025302</v>
+      </c>
+      <c r="D85" t="s">
+        <v>188</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="F85" t="s">
+        <v>43</v>
+      </c>
+      <c r="G85">
+        <v>3</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85" t="s">
+        <v>158</v>
+      </c>
+      <c r="J85">
+        <v>2025302</v>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>188</v>
+      </c>
+      <c r="O85">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86">
+        <v>1025303</v>
+      </c>
+      <c r="C86">
+        <v>1025303</v>
+      </c>
+      <c r="D86" t="s">
+        <v>189</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>43</v>
+      </c>
+      <c r="G86">
+        <v>3</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86" t="s">
+        <v>158</v>
+      </c>
+      <c r="J86">
+        <v>2025303</v>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>189</v>
+      </c>
+      <c r="O86">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87">
+        <v>1025304</v>
+      </c>
+      <c r="C87">
+        <v>1025304</v>
+      </c>
+      <c r="D87" t="s">
+        <v>190</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="F87" t="s">
+        <v>43</v>
+      </c>
+      <c r="G87">
+        <v>3</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87" t="s">
+        <v>158</v>
+      </c>
+      <c r="J87">
+        <v>2025304</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>190</v>
+      </c>
+      <c r="O87">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88">
+        <v>1025305</v>
+      </c>
+      <c r="C88">
+        <v>1025305</v>
+      </c>
+      <c r="D88" t="s">
+        <v>191</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88" t="s">
+        <v>43</v>
+      </c>
+      <c r="G88">
+        <v>3</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88" t="s">
+        <v>158</v>
+      </c>
+      <c r="J88">
+        <v>2025305</v>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
+        <v>191</v>
+      </c>
+      <c r="O88">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89">
+        <v>1025306</v>
+      </c>
+      <c r="C89">
+        <v>1025306</v>
+      </c>
+      <c r="D89" t="s">
+        <v>192</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89" t="s">
+        <v>43</v>
+      </c>
+      <c r="G89">
+        <v>3</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89" t="s">
+        <v>158</v>
+      </c>
+      <c r="J89">
+        <v>2025306</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" t="s">
+        <v>192</v>
+      </c>
+      <c r="O89">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90">
+        <v>1025401</v>
+      </c>
+      <c r="C90">
+        <v>1025401</v>
+      </c>
+      <c r="D90" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="F90" t="s">
+        <v>43</v>
+      </c>
+      <c r="G90">
+        <v>4</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90" t="s">
+        <v>158</v>
+      </c>
+      <c r="J90">
+        <v>2025401</v>
+      </c>
+      <c r="K90" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" t="s">
+        <v>193</v>
+      </c>
+      <c r="O90">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91">
+        <v>1025402</v>
+      </c>
+      <c r="C91">
+        <v>1025402</v>
+      </c>
+      <c r="D91" t="s">
+        <v>194</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91">
+        <v>4</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91" t="s">
+        <v>158</v>
+      </c>
+      <c r="J91">
+        <v>2025402</v>
+      </c>
+      <c r="K91" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" t="s">
+        <v>194</v>
+      </c>
+      <c r="O91">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92">
+        <v>1025403</v>
+      </c>
+      <c r="C92">
+        <v>1025403</v>
+      </c>
+      <c r="D92" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="F92" t="s">
+        <v>43</v>
+      </c>
+      <c r="G92">
+        <v>4</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92" t="s">
+        <v>158</v>
+      </c>
+      <c r="J92">
+        <v>2025403</v>
+      </c>
+      <c r="K92" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
+        <v>195</v>
+      </c>
+      <c r="O92">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93">
+        <v>1025404</v>
+      </c>
+      <c r="C93">
+        <v>1025404</v>
+      </c>
+      <c r="D93" t="s">
+        <v>196</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93">
+        <v>4</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93" t="s">
+        <v>158</v>
+      </c>
+      <c r="J93">
+        <v>2025404</v>
+      </c>
+      <c r="K93" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>196</v>
+      </c>
+      <c r="O93">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94">
+        <v>1025405</v>
+      </c>
+      <c r="C94">
+        <v>1025405</v>
+      </c>
+      <c r="D94" t="s">
+        <v>197</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="F94" t="s">
+        <v>43</v>
+      </c>
+      <c r="G94">
+        <v>4</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94" t="s">
+        <v>158</v>
+      </c>
+      <c r="J94">
+        <v>2025405</v>
+      </c>
+      <c r="K94" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
+        <v>197</v>
+      </c>
+      <c r="O94">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95">
+        <v>1025406</v>
+      </c>
+      <c r="C95">
+        <v>1025406</v>
+      </c>
+      <c r="D95" t="s">
+        <v>198</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95" t="s">
+        <v>43</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95" t="s">
+        <v>158</v>
+      </c>
+      <c r="J95">
+        <v>2025406</v>
+      </c>
+      <c r="K95" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
+        <v>198</v>
+      </c>
+      <c r="O95">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96">
+        <v>1025501</v>
+      </c>
+      <c r="C96">
+        <v>1025501</v>
+      </c>
+      <c r="D96" t="s">
+        <v>199</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="F96" t="s">
+        <v>43</v>
+      </c>
+      <c r="G96">
+        <v>7</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96" t="s">
+        <v>158</v>
+      </c>
+      <c r="J96">
+        <v>2025501</v>
+      </c>
+      <c r="K96" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" t="s">
+        <v>199</v>
+      </c>
+      <c r="O96">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97">
+        <v>1025502</v>
+      </c>
+      <c r="C97">
+        <v>1025502</v>
+      </c>
+      <c r="D97" t="s">
+        <v>200</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97" t="s">
+        <v>43</v>
+      </c>
+      <c r="G97">
+        <v>7</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97" t="s">
+        <v>158</v>
+      </c>
+      <c r="J97">
+        <v>2025502</v>
+      </c>
+      <c r="K97" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97" t="s">
+        <v>200</v>
+      </c>
+      <c r="O97">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98">
+        <v>1025503</v>
+      </c>
+      <c r="C98">
+        <v>1025503</v>
+      </c>
+      <c r="D98" t="s">
+        <v>201</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="F98" t="s">
+        <v>43</v>
+      </c>
+      <c r="G98">
+        <v>7</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98" t="s">
+        <v>158</v>
+      </c>
+      <c r="J98">
+        <v>2025503</v>
+      </c>
+      <c r="K98" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98" t="s">
+        <v>201</v>
+      </c>
+      <c r="O98">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99">
+        <v>1025504</v>
+      </c>
+      <c r="C99">
+        <v>1025504</v>
+      </c>
+      <c r="D99" t="s">
+        <v>202</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99" t="s">
+        <v>43</v>
+      </c>
+      <c r="G99">
+        <v>7</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99" t="s">
+        <v>158</v>
+      </c>
+      <c r="J99">
+        <v>2025504</v>
+      </c>
+      <c r="K99" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" t="s">
+        <v>202</v>
+      </c>
+      <c r="O99">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100">
+        <v>1025505</v>
+      </c>
+      <c r="C100">
+        <v>1025505</v>
+      </c>
+      <c r="D100" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="F100" t="s">
+        <v>43</v>
+      </c>
+      <c r="G100">
+        <v>7</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100" t="s">
+        <v>158</v>
+      </c>
+      <c r="J100">
+        <v>2025505</v>
+      </c>
+      <c r="K100" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" t="s">
+        <v>203</v>
+      </c>
+      <c r="O100">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101">
+        <v>1025506</v>
+      </c>
+      <c r="C101">
+        <v>1025506</v>
+      </c>
+      <c r="D101" t="s">
+        <v>204</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="F101" t="s">
+        <v>43</v>
+      </c>
+      <c r="G101">
+        <v>7</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101" t="s">
+        <v>158</v>
+      </c>
+      <c r="J101">
+        <v>2025506</v>
+      </c>
+      <c r="K101" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" t="s">
+        <v>204</v>
+      </c>
+      <c r="O101">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102">
+        <v>1125101</v>
+      </c>
+      <c r="C102">
+        <v>1125101</v>
+      </c>
+      <c r="D102" t="str">
+        <f>D72&amp;"碎片"</f>
+        <v>街头潮人碎片</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="F102" t="s">
+        <v>43</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102" t="s">
+        <v>158</v>
+      </c>
+      <c r="J102">
+        <v>2125101</v>
+      </c>
+      <c r="K102" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" t="str">
+        <f>D72&amp;"游客的升星道具"</f>
+        <v>街头潮人游客的升星道具</v>
+      </c>
+      <c r="O102">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103">
+        <v>1125102</v>
+      </c>
+      <c r="C103">
+        <v>1125102</v>
+      </c>
+      <c r="D103" t="str">
+        <f t="shared" ref="D103:D131" si="0">D73&amp;"碎片"</f>
+        <v>复古绅士碎片</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103" t="s">
+        <v>43</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103" t="s">
+        <v>158</v>
+      </c>
+      <c r="J103">
+        <v>2125102</v>
+      </c>
+      <c r="K103" t="b">
+        <v>0</v>
+      </c>
+      <c r="L103" t="str">
+        <f t="shared" ref="L103:L131" si="1">D73&amp;"游客的升星道具"</f>
+        <v>复古绅士游客的升星道具</v>
+      </c>
+      <c r="O103">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104">
+        <v>1125103</v>
+      </c>
+      <c r="C104">
+        <v>1125103</v>
+      </c>
+      <c r="D104" t="str">
+        <f t="shared" si="0"/>
+        <v>酷盖少年碎片</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="F104" t="s">
+        <v>43</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104" t="s">
+        <v>158</v>
+      </c>
+      <c r="J104">
+        <v>2125103</v>
+      </c>
+      <c r="K104" t="b">
+        <v>0</v>
+      </c>
+      <c r="L104" t="str">
+        <f t="shared" si="1"/>
+        <v>酷盖少年游客的升星道具</v>
+      </c>
+      <c r="O104">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105">
+        <v>1125104</v>
+      </c>
+      <c r="C105">
+        <v>1125104</v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="0"/>
+        <v>潮流先锋碎片</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105" t="s">
+        <v>158</v>
+      </c>
+      <c r="J105">
+        <v>2125104</v>
+      </c>
+      <c r="K105" t="b">
+        <v>0</v>
+      </c>
+      <c r="L105" t="str">
+        <f t="shared" si="1"/>
+        <v>潮流先锋游客的升星道具</v>
+      </c>
+      <c r="O105">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106">
+        <v>1125105</v>
+      </c>
+      <c r="C106">
+        <v>1125105</v>
+      </c>
+      <c r="D106" t="str">
+        <f t="shared" si="0"/>
+        <v>时尚教主碎片</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106" t="s">
+        <v>43</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106" t="s">
+        <v>158</v>
+      </c>
+      <c r="J106">
+        <v>2125105</v>
+      </c>
+      <c r="K106" t="b">
+        <v>0</v>
+      </c>
+      <c r="L106" t="str">
+        <f t="shared" si="1"/>
+        <v>时尚教主游客的升星道具</v>
+      </c>
+      <c r="O106">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107">
+        <v>1125106</v>
+      </c>
+      <c r="C107">
+        <v>1125106</v>
+      </c>
+      <c r="D107" t="str">
+        <f t="shared" si="0"/>
+        <v>街拍达人碎片</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107" t="s">
+        <v>43</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107" t="s">
+        <v>158</v>
+      </c>
+      <c r="J107">
+        <v>2125106</v>
+      </c>
+      <c r="K107" t="b">
+        <v>0</v>
+      </c>
+      <c r="L107" t="str">
+        <f t="shared" si="1"/>
+        <v>街拍达人游客的升星道具</v>
+      </c>
+      <c r="O107">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108">
+        <v>1125201</v>
+      </c>
+      <c r="C108">
+        <v>1125201</v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="0"/>
+        <v>运动健将碎片</v>
+      </c>
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="F108" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108">
+        <v>2</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108" t="s">
+        <v>158</v>
+      </c>
+      <c r="J108">
+        <v>2125201</v>
+      </c>
+      <c r="K108" t="b">
+        <v>0</v>
+      </c>
+      <c r="L108" t="str">
+        <f t="shared" si="1"/>
+        <v>运动健将游客的升星道具</v>
+      </c>
+      <c r="O108">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109">
+        <v>1125202</v>
+      </c>
+      <c r="C109">
+        <v>1125202</v>
+      </c>
+      <c r="D109" t="str">
+        <f t="shared" si="0"/>
+        <v>跑酷少年碎片</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="F109" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109" t="s">
+        <v>158</v>
+      </c>
+      <c r="J109">
+        <v>2125202</v>
+      </c>
+      <c r="K109" t="b">
+        <v>0</v>
+      </c>
+      <c r="L109" t="str">
+        <f t="shared" si="1"/>
+        <v>跑酷少年游客的升星道具</v>
+      </c>
+      <c r="O109">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110">
+        <v>1125203</v>
+      </c>
+      <c r="C110">
+        <v>1125203</v>
+      </c>
+      <c r="D110" t="str">
+        <f t="shared" si="0"/>
+        <v>滑板高手碎片</v>
+      </c>
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110" t="s">
+        <v>43</v>
+      </c>
+      <c r="G110">
+        <v>2</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110" t="s">
+        <v>158</v>
+      </c>
+      <c r="J110">
+        <v>2125203</v>
+      </c>
+      <c r="K110" t="b">
+        <v>0</v>
+      </c>
+      <c r="L110" t="str">
+        <f t="shared" si="1"/>
+        <v>滑板高手游客的升星道具</v>
+      </c>
+      <c r="O110">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111">
+        <v>1125204</v>
+      </c>
+      <c r="C111">
+        <v>1125204</v>
+      </c>
+      <c r="D111" t="str">
+        <f t="shared" si="0"/>
+        <v>甜心辣妹碎片</v>
+      </c>
+      <c r="E111">
+        <v>2</v>
+      </c>
+      <c r="F111" t="s">
+        <v>43</v>
+      </c>
+      <c r="G111">
+        <v>2</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111" t="s">
+        <v>158</v>
+      </c>
+      <c r="J111">
+        <v>2125204</v>
+      </c>
+      <c r="K111" t="b">
+        <v>0</v>
+      </c>
+      <c r="L111" t="str">
+        <f t="shared" si="1"/>
+        <v>甜心辣妹游客的升星道具</v>
+      </c>
+      <c r="O111">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112">
+        <v>1125205</v>
+      </c>
+      <c r="C112">
+        <v>1125205</v>
+      </c>
+      <c r="D112" t="str">
+        <f t="shared" si="0"/>
+        <v>活力少女碎片</v>
+      </c>
+      <c r="E112">
+        <v>2</v>
+      </c>
+      <c r="F112" t="s">
+        <v>43</v>
+      </c>
+      <c r="G112">
+        <v>2</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112" t="s">
+        <v>158</v>
+      </c>
+      <c r="J112">
+        <v>2125205</v>
+      </c>
+      <c r="K112" t="b">
+        <v>0</v>
+      </c>
+      <c r="L112" t="str">
+        <f t="shared" si="1"/>
+        <v>活力少女游客的升星道具</v>
+      </c>
+      <c r="O112">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113">
+        <v>1125206</v>
+      </c>
+      <c r="C113">
+        <v>1125206</v>
+      </c>
+      <c r="D113" t="str">
+        <f t="shared" si="0"/>
+        <v>优雅女神碎片</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113" t="s">
+        <v>43</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113" t="s">
+        <v>158</v>
+      </c>
+      <c r="J113">
+        <v>2125206</v>
+      </c>
+      <c r="K113" t="b">
+        <v>0</v>
+      </c>
+      <c r="L113" t="str">
+        <f t="shared" si="1"/>
+        <v>优雅女神游客的升星道具</v>
+      </c>
+      <c r="O113">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114">
+        <v>1125301</v>
+      </c>
+      <c r="C114">
+        <v>1125301</v>
+      </c>
+      <c r="D114" t="str">
+        <f t="shared" si="0"/>
+        <v>健身狂魔碎片</v>
+      </c>
+      <c r="E114">
+        <v>2</v>
+      </c>
+      <c r="F114" t="s">
+        <v>43</v>
+      </c>
+      <c r="G114">
+        <v>3</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114" t="s">
+        <v>158</v>
+      </c>
+      <c r="J114">
+        <v>2125301</v>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+      <c r="L114" t="str">
+        <f t="shared" si="1"/>
+        <v>健身狂魔游客的升星道具</v>
+      </c>
+      <c r="O114">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115">
+        <v>1125302</v>
+      </c>
+      <c r="C115">
+        <v>1125302</v>
+      </c>
+      <c r="D115" t="str">
+        <f t="shared" si="0"/>
+        <v>单车骑士碎片</v>
+      </c>
+      <c r="E115">
+        <v>2</v>
+      </c>
+      <c r="F115" t="s">
+        <v>43</v>
+      </c>
+      <c r="G115">
+        <v>3</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115" t="s">
+        <v>158</v>
+      </c>
+      <c r="J115">
+        <v>2125302</v>
+      </c>
+      <c r="K115" t="b">
+        <v>0</v>
+      </c>
+      <c r="L115" t="str">
+        <f t="shared" si="1"/>
+        <v>单车骑士游客的升星道具</v>
+      </c>
+      <c r="O115">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116">
+        <v>1125303</v>
+      </c>
+      <c r="C116">
+        <v>1125303</v>
+      </c>
+      <c r="D116" t="str">
+        <f t="shared" si="0"/>
+        <v>登山行者碎片</v>
+      </c>
+      <c r="E116">
+        <v>2</v>
+      </c>
+      <c r="F116" t="s">
+        <v>43</v>
+      </c>
+      <c r="G116">
+        <v>3</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116" t="s">
+        <v>158</v>
+      </c>
+      <c r="J116">
+        <v>2125303</v>
+      </c>
+      <c r="K116" t="b">
+        <v>0</v>
+      </c>
+      <c r="L116" t="str">
+        <f t="shared" si="1"/>
+        <v>登山行者游客的升星道具</v>
+      </c>
+      <c r="O116">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117">
+        <v>1125304</v>
+      </c>
+      <c r="C117">
+        <v>1125304</v>
+      </c>
+      <c r="D117" t="str">
+        <f t="shared" si="0"/>
+        <v>文艺青年碎片</v>
+      </c>
+      <c r="E117">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
+        <v>43</v>
+      </c>
+      <c r="G117">
+        <v>3</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117" t="s">
+        <v>158</v>
+      </c>
+      <c r="J117">
+        <v>2125304</v>
+      </c>
+      <c r="K117" t="b">
+        <v>0</v>
+      </c>
+      <c r="L117" t="str">
+        <f t="shared" si="1"/>
+        <v>文艺青年游客的升星道具</v>
+      </c>
+      <c r="O117">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118">
+        <v>1125305</v>
+      </c>
+      <c r="C118">
+        <v>1125305</v>
+      </c>
+      <c r="D118" t="str">
+        <f t="shared" si="0"/>
+        <v>书香少女碎片</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="F118" t="s">
+        <v>43</v>
+      </c>
+      <c r="G118">
+        <v>3</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118" t="s">
+        <v>158</v>
+      </c>
+      <c r="J118">
+        <v>2125305</v>
+      </c>
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
+      <c r="L118" t="str">
+        <f t="shared" si="1"/>
+        <v>书香少女游客的升星道具</v>
+      </c>
+      <c r="O118">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119">
+        <v>1125306</v>
+      </c>
+      <c r="C119">
+        <v>1125306</v>
+      </c>
+      <c r="D119" t="str">
+        <f t="shared" si="0"/>
+        <v>民谣歌手碎片</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
+      </c>
+      <c r="F119" t="s">
+        <v>43</v>
+      </c>
+      <c r="G119">
+        <v>3</v>
+      </c>
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119" t="s">
+        <v>158</v>
+      </c>
+      <c r="J119">
+        <v>2125306</v>
+      </c>
+      <c r="K119" t="b">
+        <v>0</v>
+      </c>
+      <c r="L119" t="str">
+        <f t="shared" si="1"/>
+        <v>民谣歌手游客的升星道具</v>
+      </c>
+      <c r="O119">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120">
+        <v>1125401</v>
+      </c>
+      <c r="C120">
+        <v>1125401</v>
+      </c>
+      <c r="D120" t="str">
+        <f t="shared" si="0"/>
+        <v>马拉松客碎片</v>
+      </c>
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120" t="s">
+        <v>43</v>
+      </c>
+      <c r="G120">
+        <v>4</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120" t="s">
+        <v>158</v>
+      </c>
+      <c r="J120">
+        <v>2125401</v>
+      </c>
+      <c r="K120" t="b">
+        <v>0</v>
+      </c>
+      <c r="L120" t="str">
+        <f t="shared" si="1"/>
+        <v>马拉松客游客的升星道具</v>
+      </c>
+      <c r="O120">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121">
+        <v>1125402</v>
+      </c>
+      <c r="C121">
+        <v>1125402</v>
+      </c>
+      <c r="D121" t="str">
+        <f t="shared" si="0"/>
+        <v>极限玩家碎片</v>
+      </c>
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>43</v>
+      </c>
+      <c r="G121">
+        <v>4</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121" t="s">
+        <v>158</v>
+      </c>
+      <c r="J121">
+        <v>2125402</v>
+      </c>
+      <c r="K121" t="b">
+        <v>0</v>
+      </c>
+      <c r="L121" t="str">
+        <f t="shared" si="1"/>
+        <v>极限玩家游客的升星道具</v>
+      </c>
+      <c r="O121">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
+      <c r="A122">
+        <v>1125403</v>
+      </c>
+      <c r="C122">
+        <v>1125403</v>
+      </c>
+      <c r="D122" t="str">
+        <f t="shared" si="0"/>
+        <v>科技极客碎片</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122" t="s">
+        <v>43</v>
+      </c>
+      <c r="G122">
+        <v>4</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122" t="s">
+        <v>158</v>
+      </c>
+      <c r="J122">
+        <v>2125403</v>
+      </c>
+      <c r="K122" t="b">
+        <v>0</v>
+      </c>
+      <c r="L122" t="str">
+        <f t="shared" si="1"/>
+        <v>科技极客游客的升星道具</v>
+      </c>
+      <c r="O122">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
+      <c r="A123">
+        <v>1125404</v>
+      </c>
+      <c r="C123">
+        <v>1125404</v>
+      </c>
+      <c r="D123" t="str">
+        <f t="shared" si="0"/>
+        <v>独立画家碎片</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" t="s">
+        <v>43</v>
+      </c>
+      <c r="G123">
+        <v>4</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123" t="s">
+        <v>158</v>
+      </c>
+      <c r="J123">
+        <v>2125404</v>
+      </c>
+      <c r="K123" t="b">
+        <v>0</v>
+      </c>
+      <c r="L123" t="str">
+        <f t="shared" si="1"/>
+        <v>独立画家游客的升星道具</v>
+      </c>
+      <c r="O123">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
+      <c r="A124">
+        <v>1125405</v>
+      </c>
+      <c r="C124">
+        <v>1125405</v>
+      </c>
+      <c r="D124" t="str">
+        <f t="shared" si="0"/>
+        <v>浪漫诗人碎片</v>
+      </c>
+      <c r="E124">
+        <v>2</v>
+      </c>
+      <c r="F124" t="s">
+        <v>43</v>
+      </c>
+      <c r="G124">
+        <v>4</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124" t="s">
+        <v>158</v>
+      </c>
+      <c r="J124">
+        <v>2125405</v>
+      </c>
+      <c r="K124" t="b">
+        <v>0</v>
+      </c>
+      <c r="L124" t="str">
+        <f t="shared" si="1"/>
+        <v>浪漫诗人游客的升星道具</v>
+      </c>
+      <c r="O124">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15">
+      <c r="A125">
+        <v>1125406</v>
+      </c>
+      <c r="C125">
+        <v>1125406</v>
+      </c>
+      <c r="D125" t="str">
+        <f t="shared" si="0"/>
+        <v>古典乐迷碎片</v>
+      </c>
+      <c r="E125">
+        <v>2</v>
+      </c>
+      <c r="F125" t="s">
+        <v>43</v>
+      </c>
+      <c r="G125">
+        <v>4</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125" t="s">
+        <v>158</v>
+      </c>
+      <c r="J125">
+        <v>2125406</v>
+      </c>
+      <c r="K125" t="b">
+        <v>0</v>
+      </c>
+      <c r="L125" t="str">
+        <f t="shared" si="1"/>
+        <v>古典乐迷游客的升星道具</v>
+      </c>
+      <c r="O125">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
+      <c r="A126">
+        <v>1125501</v>
+      </c>
+      <c r="C126">
+        <v>1125501</v>
+      </c>
+      <c r="D126" t="str">
+        <f t="shared" si="0"/>
+        <v>创业新贵碎片</v>
+      </c>
+      <c r="E126">
+        <v>2</v>
+      </c>
+      <c r="F126" t="s">
+        <v>43</v>
+      </c>
+      <c r="G126">
+        <v>7</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126" t="s">
+        <v>158</v>
+      </c>
+      <c r="J126">
+        <v>2125501</v>
+      </c>
+      <c r="K126" t="b">
+        <v>0</v>
+      </c>
+      <c r="L126" t="str">
+        <f t="shared" si="1"/>
+        <v>创业新贵游客的升星道具</v>
+      </c>
+      <c r="O126">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
+      <c r="A127">
+        <v>1125502</v>
+      </c>
+      <c r="C127">
+        <v>1125502</v>
+      </c>
+      <c r="D127" t="str">
+        <f t="shared" si="0"/>
+        <v>摸金校尉碎片</v>
+      </c>
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>43</v>
+      </c>
+      <c r="G127">
+        <v>7</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127" t="s">
+        <v>158</v>
+      </c>
+      <c r="J127">
+        <v>2125502</v>
+      </c>
+      <c r="K127" t="b">
+        <v>0</v>
+      </c>
+      <c r="L127" t="str">
+        <f t="shared" si="1"/>
+        <v>摸金校尉游客的升星道具</v>
+      </c>
+      <c r="O127">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
+      <c r="A128">
+        <v>1125503</v>
+      </c>
+      <c r="C128">
+        <v>1125503</v>
+      </c>
+      <c r="D128" t="str">
+        <f t="shared" si="0"/>
+        <v>氪金大佬碎片</v>
+      </c>
+      <c r="E128">
+        <v>2</v>
+      </c>
+      <c r="F128" t="s">
+        <v>43</v>
+      </c>
+      <c r="G128">
+        <v>7</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128" t="s">
+        <v>158</v>
+      </c>
+      <c r="J128">
+        <v>2125503</v>
+      </c>
+      <c r="K128" t="b">
+        <v>0</v>
+      </c>
+      <c r="L128" t="str">
+        <f t="shared" si="1"/>
+        <v>氪金大佬游客的升星道具</v>
+      </c>
+      <c r="O128">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
+      <c r="A129">
+        <v>1125504</v>
+      </c>
+      <c r="C129">
+        <v>1125504</v>
+      </c>
+      <c r="D129" t="str">
+        <f t="shared" si="0"/>
+        <v>穿搭博主碎片</v>
+      </c>
+      <c r="E129">
+        <v>2</v>
+      </c>
+      <c r="F129" t="s">
+        <v>43</v>
+      </c>
+      <c r="G129">
+        <v>7</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129" t="s">
+        <v>158</v>
+      </c>
+      <c r="J129">
+        <v>2125504</v>
+      </c>
+      <c r="K129" t="b">
+        <v>0</v>
+      </c>
+      <c r="L129" t="str">
+        <f t="shared" si="1"/>
+        <v>穿搭博主游客的升星道具</v>
+      </c>
+      <c r="O129">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
+      <c r="A130">
+        <v>1125505</v>
+      </c>
+      <c r="C130">
+        <v>1125505</v>
+      </c>
+      <c r="D130" t="str">
+        <f t="shared" si="0"/>
+        <v>美妆新秀碎片</v>
+      </c>
+      <c r="E130">
+        <v>2</v>
+      </c>
+      <c r="F130" t="s">
+        <v>43</v>
+      </c>
+      <c r="G130">
+        <v>7</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130" t="s">
+        <v>158</v>
+      </c>
+      <c r="J130">
+        <v>2125505</v>
+      </c>
+      <c r="K130" t="b">
+        <v>0</v>
+      </c>
+      <c r="L130" t="str">
+        <f t="shared" si="1"/>
+        <v>美妆新秀游客的升星道具</v>
+      </c>
+      <c r="O130">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
+      <c r="A131">
+        <v>1125506</v>
+      </c>
+      <c r="C131">
+        <v>1125506</v>
+      </c>
+      <c r="D131" t="str">
+        <f t="shared" si="0"/>
+        <v>高定女王碎片</v>
+      </c>
+      <c r="E131">
+        <v>2</v>
+      </c>
+      <c r="F131" t="s">
+        <v>43</v>
+      </c>
+      <c r="G131">
+        <v>7</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131" t="s">
+        <v>158</v>
+      </c>
+      <c r="J131">
+        <v>2125506</v>
+      </c>
+      <c r="K131" t="b">
+        <v>0</v>
+      </c>
+      <c r="L131" t="str">
+        <f t="shared" si="1"/>
+        <v>高定女王游客的升星道具</v>
+      </c>
+      <c r="O131">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
+      <c r="A132">
+        <v>1026001</v>
+      </c>
+      <c r="C132">
+        <v>1026001</v>
+      </c>
+      <c r="D132" t="s">
+        <v>205</v>
+      </c>
+      <c r="E132">
+        <v>2</v>
+      </c>
+      <c r="F132" t="s">
+        <v>43</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132" t="s">
+        <v>158</v>
+      </c>
+      <c r="J132">
+        <v>2026001</v>
+      </c>
+      <c r="K132" t="b">
+        <v>0</v>
+      </c>
+      <c r="L132" t="s">
+        <v>205</v>
+      </c>
+      <c r="O132">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="A133">
+        <v>1026002</v>
+      </c>
+      <c r="C133">
+        <v>1026002</v>
+      </c>
+      <c r="D133" t="s">
+        <v>206</v>
+      </c>
+      <c r="E133">
+        <v>2</v>
+      </c>
+      <c r="F133" t="s">
+        <v>43</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133" t="s">
+        <v>158</v>
+      </c>
+      <c r="J133">
+        <v>2026002</v>
+      </c>
+      <c r="K133" t="b">
+        <v>0</v>
+      </c>
+      <c r="L133" t="s">
+        <v>206</v>
+      </c>
+      <c r="O133">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
+      <c r="A134">
+        <v>1026101</v>
+      </c>
+      <c r="C134">
+        <v>1026101</v>
+      </c>
+      <c r="D134" t="s">
+        <v>207</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="F134" t="s">
+        <v>43</v>
+      </c>
+      <c r="G134">
+        <v>2</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134" t="s">
+        <v>158</v>
+      </c>
+      <c r="J134">
+        <v>2026101</v>
+      </c>
+      <c r="K134" t="b">
+        <v>0</v>
+      </c>
+      <c r="L134" t="s">
+        <v>207</v>
+      </c>
+      <c r="O134">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
+      <c r="A135">
+        <v>1026102</v>
+      </c>
+      <c r="C135">
+        <v>1026102</v>
+      </c>
+      <c r="D135" t="s">
+        <v>208</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+      <c r="F135" t="s">
+        <v>43</v>
+      </c>
+      <c r="G135">
+        <v>2</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135" t="s">
+        <v>158</v>
+      </c>
+      <c r="J135">
+        <v>2026102</v>
+      </c>
+      <c r="K135" t="b">
+        <v>0</v>
+      </c>
+      <c r="L135" t="s">
+        <v>208</v>
+      </c>
+      <c r="O135">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
+      <c r="A136">
+        <v>1026201</v>
+      </c>
+      <c r="C136">
+        <v>1026201</v>
+      </c>
+      <c r="D136" t="s">
+        <v>209</v>
+      </c>
+      <c r="E136">
+        <v>2</v>
+      </c>
+      <c r="F136" t="s">
+        <v>43</v>
+      </c>
+      <c r="G136">
+        <v>3</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136" t="s">
+        <v>158</v>
+      </c>
+      <c r="J136">
+        <v>2026201</v>
+      </c>
+      <c r="K136" t="b">
+        <v>0</v>
+      </c>
+      <c r="L136" t="s">
+        <v>209</v>
+      </c>
+      <c r="O136">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
+      <c r="A137">
+        <v>1026202</v>
+      </c>
+      <c r="C137">
+        <v>1026202</v>
+      </c>
+      <c r="D137" t="s">
+        <v>210</v>
+      </c>
+      <c r="E137">
+        <v>2</v>
+      </c>
+      <c r="F137" t="s">
+        <v>43</v>
+      </c>
+      <c r="G137">
+        <v>3</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137" t="s">
+        <v>158</v>
+      </c>
+      <c r="J137">
+        <v>2026202</v>
+      </c>
+      <c r="K137" t="b">
+        <v>0</v>
+      </c>
+      <c r="L137" t="s">
+        <v>210</v>
+      </c>
+      <c r="O137">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
+      <c r="A138">
+        <v>1026301</v>
+      </c>
+      <c r="C138">
+        <v>1026301</v>
+      </c>
+      <c r="D138" t="s">
+        <v>211</v>
+      </c>
+      <c r="E138">
+        <v>2</v>
+      </c>
+      <c r="F138" t="s">
+        <v>43</v>
+      </c>
+      <c r="G138">
+        <v>4</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138" t="s">
+        <v>158</v>
+      </c>
+      <c r="J138">
+        <v>2026301</v>
+      </c>
+      <c r="K138" t="b">
+        <v>0</v>
+      </c>
+      <c r="L138" t="s">
+        <v>211</v>
+      </c>
+      <c r="O138">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
+      <c r="A139">
+        <v>1026302</v>
+      </c>
+      <c r="C139">
+        <v>1026302</v>
+      </c>
+      <c r="D139" t="s">
+        <v>212</v>
+      </c>
+      <c r="E139">
+        <v>2</v>
+      </c>
+      <c r="F139" t="s">
+        <v>43</v>
+      </c>
+      <c r="G139">
+        <v>4</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139" t="s">
+        <v>158</v>
+      </c>
+      <c r="J139">
+        <v>2026302</v>
+      </c>
+      <c r="K139" t="b">
+        <v>0</v>
+      </c>
+      <c r="L139" t="s">
+        <v>212</v>
+      </c>
+      <c r="O139">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
+      <c r="A140">
+        <v>1026401</v>
+      </c>
+      <c r="C140">
+        <v>1026401</v>
+      </c>
+      <c r="D140" t="s">
+        <v>213</v>
+      </c>
+      <c r="E140">
+        <v>2</v>
+      </c>
+      <c r="F140" t="s">
+        <v>43</v>
+      </c>
+      <c r="G140">
+        <v>7</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140" t="s">
+        <v>158</v>
+      </c>
+      <c r="J140">
+        <v>2026401</v>
+      </c>
+      <c r="K140" t="b">
+        <v>0</v>
+      </c>
+      <c r="L140" t="s">
+        <v>213</v>
+      </c>
+      <c r="O140">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
+      <c r="A141">
+        <v>1026402</v>
+      </c>
+      <c r="C141">
+        <v>1026402</v>
+      </c>
+      <c r="D141" t="s">
+        <v>214</v>
+      </c>
+      <c r="E141">
+        <v>2</v>
+      </c>
+      <c r="F141" t="s">
+        <v>43</v>
+      </c>
+      <c r="G141">
+        <v>7</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141" t="s">
+        <v>158</v>
+      </c>
+      <c r="J141">
+        <v>2026402</v>
+      </c>
+      <c r="K141" t="b">
+        <v>0</v>
+      </c>
+      <c r="L141" t="s">
+        <v>214</v>
+      </c>
+      <c r="O141">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
+      <c r="A142">
+        <v>1027001</v>
+      </c>
+      <c r="C142">
+        <v>1027001</v>
+      </c>
+      <c r="D142" t="s">
+        <v>215</v>
+      </c>
+      <c r="E142">
+        <v>2</v>
+      </c>
+      <c r="F142" t="s">
+        <v>43</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142" t="s">
+        <v>158</v>
+      </c>
+      <c r="J142">
+        <v>2027001</v>
+      </c>
+      <c r="K142" t="b">
+        <v>0</v>
+      </c>
+      <c r="L142" t="s">
+        <v>215</v>
+      </c>
+      <c r="O142">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15">
+      <c r="A143">
+        <v>1027002</v>
+      </c>
+      <c r="C143">
+        <v>1027002</v>
+      </c>
+      <c r="D143" t="s">
+        <v>216</v>
+      </c>
+      <c r="E143">
+        <v>2</v>
+      </c>
+      <c r="F143" t="s">
+        <v>43</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143" t="s">
+        <v>158</v>
+      </c>
+      <c r="J143">
+        <v>2027002</v>
+      </c>
+      <c r="K143" t="b">
+        <v>0</v>
+      </c>
+      <c r="L143" t="s">
+        <v>216</v>
+      </c>
+      <c r="O143">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15">
+      <c r="A144">
+        <v>1027101</v>
+      </c>
+      <c r="C144">
+        <v>1027101</v>
+      </c>
+      <c r="D144" t="s">
+        <v>217</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144" t="s">
+        <v>43</v>
+      </c>
+      <c r="G144">
+        <v>2</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+      <c r="I144" t="s">
+        <v>158</v>
+      </c>
+      <c r="J144">
+        <v>2027101</v>
+      </c>
+      <c r="K144" t="b">
+        <v>0</v>
+      </c>
+      <c r="L144" t="s">
+        <v>217</v>
+      </c>
+      <c r="O144">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15">
+      <c r="A145">
+        <v>1027102</v>
+      </c>
+      <c r="C145">
+        <v>1027102</v>
+      </c>
+      <c r="D145" t="s">
+        <v>218</v>
+      </c>
+      <c r="E145">
+        <v>2</v>
+      </c>
+      <c r="F145" t="s">
+        <v>43</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145" t="s">
+        <v>158</v>
+      </c>
+      <c r="J145">
+        <v>2027102</v>
+      </c>
+      <c r="K145" t="b">
+        <v>0</v>
+      </c>
+      <c r="L145" t="s">
+        <v>218</v>
+      </c>
+      <c r="O145">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15">
+      <c r="A146">
+        <v>1027201</v>
+      </c>
+      <c r="C146">
+        <v>1027201</v>
+      </c>
+      <c r="D146" t="s">
+        <v>219</v>
+      </c>
+      <c r="E146">
+        <v>2</v>
+      </c>
+      <c r="F146" t="s">
+        <v>43</v>
+      </c>
+      <c r="G146">
+        <v>3</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+      <c r="I146" t="s">
+        <v>158</v>
+      </c>
+      <c r="J146">
+        <v>2027201</v>
+      </c>
+      <c r="K146" t="b">
+        <v>0</v>
+      </c>
+      <c r="L146" t="s">
+        <v>219</v>
+      </c>
+      <c r="O146">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15">
+      <c r="A147">
+        <v>1027202</v>
+      </c>
+      <c r="C147">
+        <v>1027202</v>
+      </c>
+      <c r="D147" t="s">
+        <v>220</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
+      <c r="F147" t="s">
+        <v>43</v>
+      </c>
+      <c r="G147">
+        <v>3</v>
+      </c>
+      <c r="H147">
+        <v>1</v>
+      </c>
+      <c r="I147" t="s">
+        <v>158</v>
+      </c>
+      <c r="J147">
+        <v>2027202</v>
+      </c>
+      <c r="K147" t="b">
+        <v>0</v>
+      </c>
+      <c r="L147" t="s">
+        <v>220</v>
+      </c>
+      <c r="O147">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15">
+      <c r="A148">
+        <v>1027301</v>
+      </c>
+      <c r="C148">
+        <v>1027301</v>
+      </c>
+      <c r="D148" t="s">
+        <v>221</v>
+      </c>
+      <c r="E148">
+        <v>2</v>
+      </c>
+      <c r="F148" t="s">
+        <v>43</v>
+      </c>
+      <c r="G148">
+        <v>4</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148" t="s">
+        <v>158</v>
+      </c>
+      <c r="J148">
+        <v>2027301</v>
+      </c>
+      <c r="K148" t="b">
+        <v>0</v>
+      </c>
+      <c r="L148" t="s">
+        <v>221</v>
+      </c>
+      <c r="O148">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15">
+      <c r="A149">
+        <v>1027302</v>
+      </c>
+      <c r="C149">
+        <v>1027302</v>
+      </c>
+      <c r="D149" t="s">
+        <v>222</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+      <c r="F149" t="s">
+        <v>43</v>
+      </c>
+      <c r="G149">
+        <v>4</v>
+      </c>
+      <c r="H149">
+        <v>1</v>
+      </c>
+      <c r="I149" t="s">
+        <v>158</v>
+      </c>
+      <c r="J149">
+        <v>2027302</v>
+      </c>
+      <c r="K149" t="b">
+        <v>0</v>
+      </c>
+      <c r="L149" t="s">
+        <v>222</v>
+      </c>
+      <c r="O149">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15">
+      <c r="A150">
+        <v>1027401</v>
+      </c>
+      <c r="C150">
+        <v>1027401</v>
+      </c>
+      <c r="D150" t="s">
+        <v>223</v>
+      </c>
+      <c r="E150">
+        <v>2</v>
+      </c>
+      <c r="F150" t="s">
+        <v>43</v>
+      </c>
+      <c r="G150">
+        <v>7</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150" t="s">
+        <v>158</v>
+      </c>
+      <c r="J150">
+        <v>2027401</v>
+      </c>
+      <c r="K150" t="b">
+        <v>0</v>
+      </c>
+      <c r="L150" t="s">
+        <v>223</v>
+      </c>
+      <c r="O150">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15">
+      <c r="A151">
+        <v>1027402</v>
+      </c>
+      <c r="C151">
+        <v>1027402</v>
+      </c>
+      <c r="D151" t="s">
+        <v>224</v>
+      </c>
+      <c r="E151">
+        <v>2</v>
+      </c>
+      <c r="F151" t="s">
+        <v>43</v>
+      </c>
+      <c r="G151">
+        <v>7</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151" t="s">
+        <v>158</v>
+      </c>
+      <c r="J151">
+        <v>2027402</v>
+      </c>
+      <c r="K151" t="b">
+        <v>0</v>
+      </c>
+      <c r="L151" t="s">
+        <v>224</v>
+      </c>
+      <c r="O151">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
+      <c r="A152">
+        <v>1028001</v>
+      </c>
+      <c r="C152">
+        <v>1028001</v>
+      </c>
+      <c r="D152" t="s">
+        <v>225</v>
+      </c>
+      <c r="E152">
+        <v>2</v>
+      </c>
+      <c r="F152" t="s">
+        <v>43</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152" t="s">
+        <v>158</v>
+      </c>
+      <c r="J152">
+        <v>2028001</v>
+      </c>
+      <c r="K152" t="b">
+        <v>0</v>
+      </c>
+      <c r="L152" t="s">
+        <v>225</v>
+      </c>
+      <c r="O152">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15">
+      <c r="A153">
+        <v>1028002</v>
+      </c>
+      <c r="C153">
+        <v>1028002</v>
+      </c>
+      <c r="D153" t="s">
+        <v>226</v>
+      </c>
+      <c r="E153">
+        <v>2</v>
+      </c>
+      <c r="F153" t="s">
+        <v>43</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>1</v>
+      </c>
+      <c r="I153" t="s">
+        <v>158</v>
+      </c>
+      <c r="J153">
+        <v>2028002</v>
+      </c>
+      <c r="K153" t="b">
+        <v>0</v>
+      </c>
+      <c r="L153" t="s">
+        <v>226</v>
+      </c>
+      <c r="O153">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15">
+      <c r="A154">
+        <v>1028101</v>
+      </c>
+      <c r="C154">
+        <v>1028101</v>
+      </c>
+      <c r="D154" t="s">
+        <v>227</v>
+      </c>
+      <c r="E154">
+        <v>2</v>
+      </c>
+      <c r="F154" t="s">
+        <v>43</v>
+      </c>
+      <c r="G154">
+        <v>2</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+      <c r="I154" t="s">
+        <v>158</v>
+      </c>
+      <c r="J154">
+        <v>2028101</v>
+      </c>
+      <c r="K154" t="b">
+        <v>0</v>
+      </c>
+      <c r="L154" t="s">
+        <v>227</v>
+      </c>
+      <c r="O154">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15">
+      <c r="A155">
+        <v>1028102</v>
+      </c>
+      <c r="C155">
+        <v>1028102</v>
+      </c>
+      <c r="D155" t="s">
+        <v>228</v>
+      </c>
+      <c r="E155">
+        <v>2</v>
+      </c>
+      <c r="F155" t="s">
+        <v>43</v>
+      </c>
+      <c r="G155">
+        <v>2</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="I155" t="s">
+        <v>158</v>
+      </c>
+      <c r="J155">
+        <v>2028102</v>
+      </c>
+      <c r="K155" t="b">
+        <v>0</v>
+      </c>
+      <c r="L155" t="s">
+        <v>228</v>
+      </c>
+      <c r="O155">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15">
+      <c r="A156">
+        <v>1028201</v>
+      </c>
+      <c r="C156">
+        <v>1028201</v>
+      </c>
+      <c r="D156" t="s">
+        <v>229</v>
+      </c>
+      <c r="E156">
+        <v>2</v>
+      </c>
+      <c r="F156" t="s">
+        <v>43</v>
+      </c>
+      <c r="G156">
+        <v>3</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="I156" t="s">
+        <v>158</v>
+      </c>
+      <c r="J156">
+        <v>2028201</v>
+      </c>
+      <c r="K156" t="b">
+        <v>0</v>
+      </c>
+      <c r="L156" t="s">
+        <v>229</v>
+      </c>
+      <c r="O156">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15">
+      <c r="A157">
+        <v>1028202</v>
+      </c>
+      <c r="C157">
+        <v>1028202</v>
+      </c>
+      <c r="D157" t="s">
+        <v>230</v>
+      </c>
+      <c r="E157">
+        <v>2</v>
+      </c>
+      <c r="F157" t="s">
+        <v>43</v>
+      </c>
+      <c r="G157">
+        <v>3</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="I157" t="s">
+        <v>158</v>
+      </c>
+      <c r="J157">
+        <v>2028202</v>
+      </c>
+      <c r="K157" t="b">
+        <v>0</v>
+      </c>
+      <c r="L157" t="s">
+        <v>230</v>
+      </c>
+      <c r="O157">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15">
+      <c r="A158">
+        <v>1028301</v>
+      </c>
+      <c r="C158">
+        <v>1028301</v>
+      </c>
+      <c r="D158" t="s">
+        <v>231</v>
+      </c>
+      <c r="E158">
+        <v>2</v>
+      </c>
+      <c r="F158" t="s">
+        <v>43</v>
+      </c>
+      <c r="G158">
+        <v>4</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+      <c r="I158" t="s">
+        <v>158</v>
+      </c>
+      <c r="J158">
+        <v>2028301</v>
+      </c>
+      <c r="K158" t="b">
+        <v>0</v>
+      </c>
+      <c r="L158" t="s">
+        <v>231</v>
+      </c>
+      <c r="O158">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
+      <c r="A159">
+        <v>1028302</v>
+      </c>
+      <c r="C159">
+        <v>1028302</v>
+      </c>
+      <c r="D159" t="s">
+        <v>232</v>
+      </c>
+      <c r="E159">
+        <v>2</v>
+      </c>
+      <c r="F159" t="s">
+        <v>43</v>
+      </c>
+      <c r="G159">
+        <v>4</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="I159" t="s">
+        <v>158</v>
+      </c>
+      <c r="J159">
+        <v>2028302</v>
+      </c>
+      <c r="K159" t="b">
+        <v>0</v>
+      </c>
+      <c r="L159" t="s">
+        <v>232</v>
+      </c>
+      <c r="O159">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15">
+      <c r="A160">
+        <v>1028401</v>
+      </c>
+      <c r="C160">
+        <v>1028401</v>
+      </c>
+      <c r="D160" t="s">
+        <v>233</v>
+      </c>
+      <c r="E160">
+        <v>2</v>
+      </c>
+      <c r="F160" t="s">
+        <v>43</v>
+      </c>
+      <c r="G160">
+        <v>7</v>
+      </c>
+      <c r="H160">
+        <v>1</v>
+      </c>
+      <c r="I160" t="s">
+        <v>158</v>
+      </c>
+      <c r="J160">
+        <v>2028401</v>
+      </c>
+      <c r="K160" t="b">
+        <v>0</v>
+      </c>
+      <c r="L160" t="s">
+        <v>233</v>
+      </c>
+      <c r="O160">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15">
+      <c r="A161">
+        <v>1028402</v>
+      </c>
+      <c r="C161">
+        <v>1028402</v>
+      </c>
+      <c r="D161" t="s">
+        <v>234</v>
+      </c>
+      <c r="E161">
+        <v>2</v>
+      </c>
+      <c r="F161" t="s">
+        <v>43</v>
+      </c>
+      <c r="G161">
+        <v>7</v>
+      </c>
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="I161" t="s">
+        <v>158</v>
+      </c>
+      <c r="J161">
+        <v>2028402</v>
+      </c>
+      <c r="K161" t="b">
+        <v>0</v>
+      </c>
+      <c r="L161" t="s">
+        <v>234</v>
+      </c>
+      <c r="O161">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15">
+      <c r="A162">
+        <v>1126001</v>
+      </c>
+      <c r="C162">
+        <v>1126001</v>
+      </c>
+      <c r="D162" t="str">
+        <f>D132&amp;"碎片"</f>
+        <v>威廉碎片</v>
+      </c>
+      <c r="E162">
+        <v>2</v>
+      </c>
+      <c r="F162" t="s">
+        <v>43</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+      <c r="I162" t="s">
+        <v>158</v>
+      </c>
+      <c r="J162">
+        <v>2126001</v>
+      </c>
+      <c r="K162" t="b">
+        <v>0</v>
+      </c>
+      <c r="L162" t="str">
+        <f>D132&amp;"雇员的升星道具"</f>
+        <v>威廉雇员的升星道具</v>
+      </c>
+      <c r="O162">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15">
+      <c r="A163">
+        <v>1126002</v>
+      </c>
+      <c r="C163">
+        <v>1126002</v>
+      </c>
+      <c r="D163" t="str">
+        <f t="shared" ref="D163:D191" si="2">D133&amp;"碎片"</f>
+        <v>艾拉碎片</v>
+      </c>
+      <c r="E163">
+        <v>2</v>
+      </c>
+      <c r="F163" t="s">
+        <v>43</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="I163" t="s">
+        <v>158</v>
+      </c>
+      <c r="J163">
+        <v>2126002</v>
+      </c>
+      <c r="K163" t="b">
+        <v>0</v>
+      </c>
+      <c r="L163" t="str">
+        <f t="shared" ref="L163:L191" si="3">D133&amp;"雇员的升星道具"</f>
+        <v>艾拉雇员的升星道具</v>
+      </c>
+      <c r="O163">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15">
+      <c r="A164">
+        <v>1126101</v>
+      </c>
+      <c r="C164">
+        <v>1126101</v>
+      </c>
+      <c r="D164" t="str">
+        <f t="shared" si="2"/>
+        <v>亨利碎片</v>
+      </c>
+      <c r="E164">
+        <v>2</v>
+      </c>
+      <c r="F164" t="s">
+        <v>43</v>
+      </c>
+      <c r="G164">
+        <v>2</v>
+      </c>
+      <c r="H164">
+        <v>1</v>
+      </c>
+      <c r="I164" t="s">
+        <v>158</v>
+      </c>
+      <c r="J164">
+        <v>2126101</v>
+      </c>
+      <c r="K164" t="b">
+        <v>0</v>
+      </c>
+      <c r="L164" t="str">
+        <f t="shared" si="3"/>
+        <v>亨利雇员的升星道具</v>
+      </c>
+      <c r="O164">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15">
+      <c r="A165">
+        <v>1126102</v>
+      </c>
+      <c r="C165">
+        <v>1126102</v>
+      </c>
+      <c r="D165" t="str">
+        <f t="shared" si="2"/>
+        <v>艾玛碎片</v>
+      </c>
+      <c r="E165">
+        <v>2</v>
+      </c>
+      <c r="F165" t="s">
+        <v>43</v>
+      </c>
+      <c r="G165">
+        <v>2</v>
+      </c>
+      <c r="H165">
+        <v>1</v>
+      </c>
+      <c r="I165" t="s">
+        <v>158</v>
+      </c>
+      <c r="J165">
+        <v>2126102</v>
+      </c>
+      <c r="K165" t="b">
+        <v>0</v>
+      </c>
+      <c r="L165" t="str">
+        <f t="shared" si="3"/>
+        <v>艾玛雇员的升星道具</v>
+      </c>
+      <c r="O165">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15">
+      <c r="A166">
+        <v>1126201</v>
+      </c>
+      <c r="C166">
+        <v>1126201</v>
+      </c>
+      <c r="D166" t="str">
+        <f t="shared" si="2"/>
+        <v>乔治碎片</v>
+      </c>
+      <c r="E166">
+        <v>2</v>
+      </c>
+      <c r="F166" t="s">
+        <v>43</v>
+      </c>
+      <c r="G166">
+        <v>3</v>
+      </c>
+      <c r="H166">
+        <v>1</v>
+      </c>
+      <c r="I166" t="s">
+        <v>158</v>
+      </c>
+      <c r="J166">
+        <v>2126201</v>
+      </c>
+      <c r="K166" t="b">
+        <v>0</v>
+      </c>
+      <c r="L166" t="str">
+        <f t="shared" si="3"/>
+        <v>乔治雇员的升星道具</v>
+      </c>
+      <c r="O166">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15">
+      <c r="A167">
+        <v>1126202</v>
+      </c>
+      <c r="C167">
+        <v>1126202</v>
+      </c>
+      <c r="D167" t="str">
+        <f t="shared" si="2"/>
+        <v>艾娃碎片</v>
+      </c>
+      <c r="E167">
+        <v>2</v>
+      </c>
+      <c r="F167" t="s">
+        <v>43</v>
+      </c>
+      <c r="G167">
+        <v>3</v>
+      </c>
+      <c r="H167">
+        <v>1</v>
+      </c>
+      <c r="I167" t="s">
+        <v>158</v>
+      </c>
+      <c r="J167">
+        <v>2126202</v>
+      </c>
+      <c r="K167" t="b">
+        <v>0</v>
+      </c>
+      <c r="L167" t="str">
+        <f t="shared" si="3"/>
+        <v>艾娃雇员的升星道具</v>
+      </c>
+      <c r="O167">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15">
+      <c r="A168">
+        <v>1126301</v>
+      </c>
+      <c r="C168">
+        <v>1126301</v>
+      </c>
+      <c r="D168" t="str">
+        <f t="shared" si="2"/>
+        <v>亚瑟碎片</v>
+      </c>
+      <c r="E168">
+        <v>2</v>
+      </c>
+      <c r="F168" t="s">
+        <v>43</v>
+      </c>
+      <c r="G168">
+        <v>4</v>
+      </c>
+      <c r="H168">
+        <v>1</v>
+      </c>
+      <c r="I168" t="s">
+        <v>158</v>
+      </c>
+      <c r="J168">
+        <v>2126301</v>
+      </c>
+      <c r="K168" t="b">
+        <v>0</v>
+      </c>
+      <c r="L168" t="str">
+        <f t="shared" si="3"/>
+        <v>亚瑟雇员的升星道具</v>
+      </c>
+      <c r="O168">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15">
+      <c r="A169">
+        <v>1126302</v>
+      </c>
+      <c r="C169">
+        <v>1126302</v>
+      </c>
+      <c r="D169" t="str">
+        <f t="shared" si="2"/>
+        <v>安娜碎片</v>
+      </c>
+      <c r="E169">
+        <v>2</v>
+      </c>
+      <c r="F169" t="s">
+        <v>43</v>
+      </c>
+      <c r="G169">
+        <v>4</v>
+      </c>
+      <c r="H169">
+        <v>1</v>
+      </c>
+      <c r="I169" t="s">
+        <v>158</v>
+      </c>
+      <c r="J169">
+        <v>2126302</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+      <c r="L169" t="str">
+        <f t="shared" si="3"/>
+        <v>安娜雇员的升星道具</v>
+      </c>
+      <c r="O169">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15">
+      <c r="A170">
+        <v>1126401</v>
+      </c>
+      <c r="C170">
+        <v>1126401</v>
+      </c>
+      <c r="D170" t="str">
+        <f t="shared" si="2"/>
+        <v>马修碎片</v>
+      </c>
+      <c r="E170">
+        <v>2</v>
+      </c>
+      <c r="F170" t="s">
+        <v>43</v>
+      </c>
+      <c r="G170">
+        <v>7</v>
+      </c>
+      <c r="H170">
+        <v>1</v>
+      </c>
+      <c r="I170" t="s">
+        <v>158</v>
+      </c>
+      <c r="J170">
+        <v>2126401</v>
+      </c>
+      <c r="K170" t="b">
+        <v>0</v>
+      </c>
+      <c r="L170" t="str">
+        <f t="shared" si="3"/>
+        <v>马修雇员的升星道具</v>
+      </c>
+      <c r="O170">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15">
+      <c r="A171">
+        <v>1126402</v>
+      </c>
+      <c r="C171">
+        <v>1126402</v>
+      </c>
+      <c r="D171" t="str">
+        <f t="shared" si="2"/>
+        <v>哈珀碎片</v>
+      </c>
+      <c r="E171">
+        <v>2</v>
+      </c>
+      <c r="F171" t="s">
+        <v>43</v>
+      </c>
+      <c r="G171">
+        <v>7</v>
+      </c>
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="I171" t="s">
+        <v>158</v>
+      </c>
+      <c r="J171">
+        <v>2126402</v>
+      </c>
+      <c r="K171" t="b">
+        <v>0</v>
+      </c>
+      <c r="L171" t="str">
+        <f t="shared" si="3"/>
+        <v>哈珀雇员的升星道具</v>
+      </c>
+      <c r="O171">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15">
+      <c r="A172">
+        <v>1127001</v>
+      </c>
+      <c r="C172">
+        <v>1127001</v>
+      </c>
+      <c r="D172" t="str">
+        <f t="shared" si="2"/>
+        <v>拉斐尔碎片</v>
+      </c>
+      <c r="E172">
+        <v>2</v>
+      </c>
+      <c r="F172" t="s">
+        <v>43</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+      <c r="I172" t="s">
+        <v>158</v>
+      </c>
+      <c r="J172">
+        <v>2127001</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+      <c r="L172" t="str">
+        <f t="shared" si="3"/>
+        <v>拉斐尔雇员的升星道具</v>
+      </c>
+      <c r="O172">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15">
+      <c r="A173">
+        <v>1127002</v>
+      </c>
+      <c r="C173">
+        <v>1127002</v>
+      </c>
+      <c r="D173" t="str">
+        <f t="shared" si="2"/>
+        <v>伊芙琳碎片</v>
+      </c>
+      <c r="E173">
+        <v>2</v>
+      </c>
+      <c r="F173" t="s">
+        <v>43</v>
+      </c>
+      <c r="G173">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>1</v>
+      </c>
+      <c r="I173" t="s">
+        <v>158</v>
+      </c>
+      <c r="J173">
+        <v>2127002</v>
+      </c>
+      <c r="K173" t="b">
+        <v>0</v>
+      </c>
+      <c r="L173" t="str">
+        <f t="shared" si="3"/>
+        <v>伊芙琳雇员的升星道具</v>
+      </c>
+      <c r="O173">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15">
+      <c r="A174">
+        <v>1127101</v>
+      </c>
+      <c r="C174">
+        <v>1127101</v>
+      </c>
+      <c r="D174" t="str">
+        <f t="shared" si="2"/>
+        <v>埃米尔碎片</v>
+      </c>
+      <c r="E174">
+        <v>2</v>
+      </c>
+      <c r="F174" t="s">
+        <v>43</v>
+      </c>
+      <c r="G174">
+        <v>2</v>
+      </c>
+      <c r="H174">
+        <v>1</v>
+      </c>
+      <c r="I174" t="s">
+        <v>158</v>
+      </c>
+      <c r="J174">
+        <v>2127101</v>
+      </c>
+      <c r="K174" t="b">
+        <v>0</v>
+      </c>
+      <c r="L174" t="str">
+        <f t="shared" si="3"/>
+        <v>埃米尔雇员的升星道具</v>
+      </c>
+      <c r="O174">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15">
+      <c r="A175">
+        <v>1127102</v>
+      </c>
+      <c r="C175">
+        <v>1127102</v>
+      </c>
+      <c r="D175" t="str">
+        <f t="shared" si="2"/>
+        <v>夏洛特碎片</v>
+      </c>
+      <c r="E175">
+        <v>2</v>
+      </c>
+      <c r="F175" t="s">
+        <v>43</v>
+      </c>
+      <c r="G175">
+        <v>2</v>
+      </c>
+      <c r="H175">
+        <v>1</v>
+      </c>
+      <c r="I175" t="s">
+        <v>158</v>
+      </c>
+      <c r="J175">
+        <v>2127102</v>
+      </c>
+      <c r="K175" t="b">
+        <v>0</v>
+      </c>
+      <c r="L175" t="str">
+        <f t="shared" si="3"/>
+        <v>夏洛特雇员的升星道具</v>
+      </c>
+      <c r="O175">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15">
+      <c r="A176">
+        <v>1127201</v>
+      </c>
+      <c r="C176">
+        <v>1127201</v>
+      </c>
+      <c r="D176" t="str">
+        <f t="shared" si="2"/>
+        <v>雷蒙德碎片</v>
+      </c>
+      <c r="E176">
+        <v>2</v>
+      </c>
+      <c r="F176" t="s">
+        <v>43</v>
+      </c>
+      <c r="G176">
+        <v>3</v>
+      </c>
+      <c r="H176">
+        <v>1</v>
+      </c>
+      <c r="I176" t="s">
+        <v>158</v>
+      </c>
+      <c r="J176">
+        <v>2127201</v>
+      </c>
+      <c r="K176" t="b">
+        <v>0</v>
+      </c>
+      <c r="L176" t="str">
+        <f t="shared" si="3"/>
+        <v>雷蒙德雇员的升星道具</v>
+      </c>
+      <c r="O176">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15">
+      <c r="A177">
+        <v>1127202</v>
+      </c>
+      <c r="C177">
+        <v>1127202</v>
+      </c>
+      <c r="D177" t="str">
+        <f t="shared" si="2"/>
+        <v>斯嘉丽碎片</v>
+      </c>
+      <c r="E177">
+        <v>2</v>
+      </c>
+      <c r="F177" t="s">
+        <v>43</v>
+      </c>
+      <c r="G177">
+        <v>3</v>
+      </c>
+      <c r="H177">
+        <v>1</v>
+      </c>
+      <c r="I177" t="s">
+        <v>158</v>
+      </c>
+      <c r="J177">
+        <v>2127202</v>
+      </c>
+      <c r="K177" t="b">
+        <v>0</v>
+      </c>
+      <c r="L177" t="str">
+        <f t="shared" si="3"/>
+        <v>斯嘉丽雇员的升星道具</v>
+      </c>
+      <c r="O177">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15">
+      <c r="A178">
+        <v>1127301</v>
+      </c>
+      <c r="C178">
+        <v>1127301</v>
+      </c>
+      <c r="D178" t="str">
+        <f t="shared" si="2"/>
+        <v>丹尼尔碎片</v>
+      </c>
+      <c r="E178">
+        <v>2</v>
+      </c>
+      <c r="F178" t="s">
+        <v>43</v>
+      </c>
+      <c r="G178">
+        <v>4</v>
+      </c>
+      <c r="H178">
+        <v>1</v>
+      </c>
+      <c r="I178" t="s">
+        <v>158</v>
+      </c>
+      <c r="J178">
+        <v>2127301</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+      <c r="L178" t="str">
+        <f t="shared" si="3"/>
+        <v>丹尼尔雇员的升星道具</v>
+      </c>
+      <c r="O178">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15">
+      <c r="A179">
+        <v>1127302</v>
+      </c>
+      <c r="C179">
+        <v>1127302</v>
+      </c>
+      <c r="D179" t="str">
+        <f t="shared" si="2"/>
+        <v>莉莉安碎片</v>
+      </c>
+      <c r="E179">
+        <v>2</v>
+      </c>
+      <c r="F179" t="s">
+        <v>43</v>
+      </c>
+      <c r="G179">
+        <v>4</v>
+      </c>
+      <c r="H179">
+        <v>1</v>
+      </c>
+      <c r="I179" t="s">
+        <v>158</v>
+      </c>
+      <c r="J179">
+        <v>2127302</v>
+      </c>
+      <c r="K179" t="b">
+        <v>0</v>
+      </c>
+      <c r="L179" t="str">
+        <f t="shared" si="3"/>
+        <v>莉莉安雇员的升星道具</v>
+      </c>
+      <c r="O179">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15">
+      <c r="A180">
+        <v>1127401</v>
+      </c>
+      <c r="C180">
+        <v>1127401</v>
+      </c>
+      <c r="D180" t="str">
+        <f t="shared" si="2"/>
+        <v>卢卡斯碎片</v>
+      </c>
+      <c r="E180">
+        <v>2</v>
+      </c>
+      <c r="F180" t="s">
+        <v>43</v>
+      </c>
+      <c r="G180">
+        <v>7</v>
+      </c>
+      <c r="H180">
+        <v>1</v>
+      </c>
+      <c r="I180" t="s">
+        <v>158</v>
+      </c>
+      <c r="J180">
+        <v>2127401</v>
+      </c>
+      <c r="K180" t="b">
+        <v>0</v>
+      </c>
+      <c r="L180" t="str">
+        <f t="shared" si="3"/>
+        <v>卢卡斯雇员的升星道具</v>
+      </c>
+      <c r="O180">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15">
+      <c r="A181">
+        <v>1127402</v>
+      </c>
+      <c r="C181">
+        <v>1127402</v>
+      </c>
+      <c r="D181" t="str">
+        <f t="shared" si="2"/>
+        <v>克拉拉碎片</v>
+      </c>
+      <c r="E181">
+        <v>2</v>
+      </c>
+      <c r="F181" t="s">
+        <v>43</v>
+      </c>
+      <c r="G181">
+        <v>7</v>
+      </c>
+      <c r="H181">
+        <v>1</v>
+      </c>
+      <c r="I181" t="s">
+        <v>158</v>
+      </c>
+      <c r="J181">
+        <v>2127402</v>
+      </c>
+      <c r="K181" t="b">
+        <v>0</v>
+      </c>
+      <c r="L181" t="str">
+        <f t="shared" si="3"/>
+        <v>克拉拉雇员的升星道具</v>
+      </c>
+      <c r="O181">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15">
+      <c r="A182">
+        <v>1128001</v>
+      </c>
+      <c r="C182">
+        <v>1128001</v>
+      </c>
+      <c r="D182" t="str">
+        <f t="shared" si="2"/>
+        <v>尼古拉斯碎片</v>
+      </c>
+      <c r="E182">
+        <v>2</v>
+      </c>
+      <c r="F182" t="s">
+        <v>43</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <v>1</v>
+      </c>
+      <c r="I182" t="s">
+        <v>158</v>
+      </c>
+      <c r="J182">
+        <v>2128001</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+      <c r="L182" t="str">
+        <f t="shared" si="3"/>
+        <v>尼古拉斯雇员的升星道具</v>
+      </c>
+      <c r="O182">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15">
+      <c r="A183">
+        <v>1128002</v>
+      </c>
+      <c r="C183">
+        <v>1128002</v>
+      </c>
+      <c r="D183" t="str">
+        <f t="shared" si="2"/>
+        <v>奥利维亚碎片</v>
+      </c>
+      <c r="E183">
+        <v>2</v>
+      </c>
+      <c r="F183" t="s">
+        <v>43</v>
+      </c>
+      <c r="G183">
+        <v>1</v>
+      </c>
+      <c r="H183">
+        <v>1</v>
+      </c>
+      <c r="I183" t="s">
+        <v>158</v>
+      </c>
+      <c r="J183">
+        <v>2128002</v>
+      </c>
+      <c r="K183" t="b">
+        <v>0</v>
+      </c>
+      <c r="L183" t="str">
+        <f t="shared" si="3"/>
+        <v>奥利维亚雇员的升星道具</v>
+      </c>
+      <c r="O183">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15">
+      <c r="A184">
+        <v>1128101</v>
+      </c>
+      <c r="C184">
+        <v>1128101</v>
+      </c>
+      <c r="D184" t="str">
+        <f t="shared" si="2"/>
+        <v>亚历山大碎片</v>
+      </c>
+      <c r="E184">
+        <v>2</v>
+      </c>
+      <c r="F184" t="s">
+        <v>43</v>
+      </c>
+      <c r="G184">
+        <v>2</v>
+      </c>
+      <c r="H184">
+        <v>1</v>
+      </c>
+      <c r="I184" t="s">
+        <v>158</v>
+      </c>
+      <c r="J184">
+        <v>2128101</v>
+      </c>
+      <c r="K184" t="b">
+        <v>0</v>
+      </c>
+      <c r="L184" t="str">
+        <f t="shared" si="3"/>
+        <v>亚历山大雇员的升星道具</v>
+      </c>
+      <c r="O184">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15">
+      <c r="A185">
+        <v>1128102</v>
+      </c>
+      <c r="C185">
+        <v>1128102</v>
+      </c>
+      <c r="D185" t="str">
+        <f t="shared" si="2"/>
+        <v>玛格丽特碎片</v>
+      </c>
+      <c r="E185">
+        <v>2</v>
+      </c>
+      <c r="F185" t="s">
+        <v>43</v>
+      </c>
+      <c r="G185">
+        <v>2</v>
+      </c>
+      <c r="H185">
+        <v>1</v>
+      </c>
+      <c r="I185" t="s">
+        <v>158</v>
+      </c>
+      <c r="J185">
+        <v>2128102</v>
+      </c>
+      <c r="K185" t="b">
+        <v>0</v>
+      </c>
+      <c r="L185" t="str">
+        <f t="shared" si="3"/>
+        <v>玛格丽特雇员的升星道具</v>
+      </c>
+      <c r="O185">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
+      <c r="A186">
+        <v>1128201</v>
+      </c>
+      <c r="C186">
+        <v>1128201</v>
+      </c>
+      <c r="D186" t="str">
+        <f t="shared" si="2"/>
+        <v>奥古斯特碎片</v>
+      </c>
+      <c r="E186">
+        <v>2</v>
+      </c>
+      <c r="F186" t="s">
+        <v>43</v>
+      </c>
+      <c r="G186">
+        <v>3</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186" t="s">
+        <v>158</v>
+      </c>
+      <c r="J186">
+        <v>2128201</v>
+      </c>
+      <c r="K186" t="b">
+        <v>0</v>
+      </c>
+      <c r="L186" t="str">
+        <f t="shared" si="3"/>
+        <v>奥古斯特雇员的升星道具</v>
+      </c>
+      <c r="O186">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15">
+      <c r="A187">
+        <v>1128202</v>
+      </c>
+      <c r="C187">
+        <v>1128202</v>
+      </c>
+      <c r="D187" t="str">
+        <f t="shared" si="2"/>
+        <v>维奥莱特碎片</v>
+      </c>
+      <c r="E187">
+        <v>2</v>
+      </c>
+      <c r="F187" t="s">
+        <v>43</v>
+      </c>
+      <c r="G187">
+        <v>3</v>
+      </c>
+      <c r="H187">
+        <v>1</v>
+      </c>
+      <c r="I187" t="s">
+        <v>158</v>
+      </c>
+      <c r="J187">
+        <v>2128202</v>
+      </c>
+      <c r="K187" t="b">
+        <v>0</v>
+      </c>
+      <c r="L187" t="str">
+        <f t="shared" si="3"/>
+        <v>维奥莱特雇员的升星道具</v>
+      </c>
+      <c r="O187">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15">
+      <c r="A188">
+        <v>1128301</v>
+      </c>
+      <c r="C188">
+        <v>1128301</v>
+      </c>
+      <c r="D188" t="str">
+        <f t="shared" si="2"/>
+        <v>费利克斯碎片</v>
+      </c>
+      <c r="E188">
+        <v>2</v>
+      </c>
+      <c r="F188" t="s">
+        <v>43</v>
+      </c>
+      <c r="G188">
+        <v>4</v>
+      </c>
+      <c r="H188">
+        <v>1</v>
+      </c>
+      <c r="I188" t="s">
+        <v>158</v>
+      </c>
+      <c r="J188">
+        <v>2128301</v>
+      </c>
+      <c r="K188" t="b">
+        <v>0</v>
+      </c>
+      <c r="L188" t="str">
+        <f t="shared" si="3"/>
+        <v>费利克斯雇员的升星道具</v>
+      </c>
+      <c r="O188">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15">
+      <c r="A189">
+        <v>1128302</v>
+      </c>
+      <c r="C189">
+        <v>1128302</v>
+      </c>
+      <c r="D189" t="str">
+        <f t="shared" si="2"/>
+        <v>维多利亚碎片</v>
+      </c>
+      <c r="E189">
+        <v>2</v>
+      </c>
+      <c r="F189" t="s">
+        <v>43</v>
+      </c>
+      <c r="G189">
+        <v>4</v>
+      </c>
+      <c r="H189">
+        <v>1</v>
+      </c>
+      <c r="I189" t="s">
+        <v>158</v>
+      </c>
+      <c r="J189">
+        <v>2128302</v>
+      </c>
+      <c r="K189" t="b">
+        <v>0</v>
+      </c>
+      <c r="L189" t="str">
+        <f t="shared" si="3"/>
+        <v>维多利亚雇员的升星道具</v>
+      </c>
+      <c r="O189">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15">
+      <c r="A190">
+        <v>1128401</v>
+      </c>
+      <c r="C190">
+        <v>1128401</v>
+      </c>
+      <c r="D190" t="str">
+        <f t="shared" si="2"/>
+        <v>阿尔弗雷德碎片</v>
+      </c>
+      <c r="E190">
+        <v>2</v>
+      </c>
+      <c r="F190" t="s">
+        <v>43</v>
+      </c>
+      <c r="G190">
+        <v>7</v>
+      </c>
+      <c r="H190">
+        <v>1</v>
+      </c>
+      <c r="I190" t="s">
+        <v>158</v>
+      </c>
+      <c r="J190">
+        <v>2128401</v>
+      </c>
+      <c r="K190" t="b">
+        <v>0</v>
+      </c>
+      <c r="L190" t="str">
+        <f t="shared" si="3"/>
+        <v>阿尔弗雷德雇员的升星道具</v>
+      </c>
+      <c r="O190">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15">
+      <c r="A191">
+        <v>1128402</v>
+      </c>
+      <c r="C191">
+        <v>1128402</v>
+      </c>
+      <c r="D191" t="str">
+        <f t="shared" si="2"/>
+        <v>伊丽莎白碎片</v>
+      </c>
+      <c r="E191">
+        <v>2</v>
+      </c>
+      <c r="F191" t="s">
+        <v>43</v>
+      </c>
+      <c r="G191">
+        <v>7</v>
+      </c>
+      <c r="H191">
+        <v>1</v>
+      </c>
+      <c r="I191" t="s">
+        <v>158</v>
+      </c>
+      <c r="J191">
+        <v>2128402</v>
+      </c>
+      <c r="K191" t="b">
+        <v>0</v>
+      </c>
+      <c r="L191" t="str">
+        <f t="shared" si="3"/>
+        <v>伊丽莎白雇员的升星道具</v>
+      </c>
+      <c r="O191">
+        <v>999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="254">
   <si>
     <t>道具ID</t>
   </si>
@@ -1003,6 +1003,63 @@
   </si>
   <si>
     <t>伊丽莎白</t>
+  </si>
+  <si>
+    <t>旋转次数：转轮王者</t>
+  </si>
+  <si>
+    <t>激活“转轮王者”勋章</t>
+  </si>
+  <si>
+    <t>建筑升级：建筑大师</t>
+  </si>
+  <si>
+    <t>激活“建筑大师”勋章</t>
+  </si>
+  <si>
+    <t>观看广告：娱乐大哼</t>
+  </si>
+  <si>
+    <t>激活“娱乐大哼”勋章</t>
+  </si>
+  <si>
+    <t>雇员数量：经营CEO</t>
+  </si>
+  <si>
+    <t>激活“经营CEO”勋章</t>
+  </si>
+  <si>
+    <t>雇员星级：培养能手</t>
+  </si>
+  <si>
+    <t>激活“培养能手”勋章</t>
+  </si>
+  <si>
+    <t>金币收益：亿万富豪</t>
+  </si>
+  <si>
+    <t>能量收益：收集达人</t>
+  </si>
+  <si>
+    <t>激活“收集达人”勋章</t>
+  </si>
+  <si>
+    <t>招商游客：招商干将</t>
+  </si>
+  <si>
+    <t>激活“招商干将”勋章</t>
+  </si>
+  <si>
+    <t>接待游客：人气之王</t>
+  </si>
+  <si>
+    <t>激活“人气之王”勋章</t>
+  </si>
+  <si>
+    <t>研发游戏：科研大佬</t>
+  </si>
+  <si>
+    <t>激活“科研大佬”勋章</t>
   </si>
 </sst>
 </file>
@@ -2238,7 +2295,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R191"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -9876,6 +9933,386 @@
         <v>999</v>
       </c>
     </row>
+    <row r="192" spans="1:15">
+      <c r="A192">
+        <v>1200001</v>
+      </c>
+      <c r="C192">
+        <v>1200001</v>
+      </c>
+      <c r="D192" t="s">
+        <v>235</v>
+      </c>
+      <c r="E192">
+        <v>2</v>
+      </c>
+      <c r="F192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G192">
+        <v>1</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192" t="s">
+        <v>158</v>
+      </c>
+      <c r="J192">
+        <v>2200001</v>
+      </c>
+      <c r="K192" t="b">
+        <v>0</v>
+      </c>
+      <c r="L192" t="s">
+        <v>236</v>
+      </c>
+      <c r="O192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15">
+      <c r="A193">
+        <v>1200002</v>
+      </c>
+      <c r="C193">
+        <v>1200002</v>
+      </c>
+      <c r="D193" t="s">
+        <v>237</v>
+      </c>
+      <c r="E193">
+        <v>2</v>
+      </c>
+      <c r="F193" t="s">
+        <v>43</v>
+      </c>
+      <c r="G193">
+        <v>1</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193" t="s">
+        <v>158</v>
+      </c>
+      <c r="J193">
+        <v>2200002</v>
+      </c>
+      <c r="K193" t="b">
+        <v>0</v>
+      </c>
+      <c r="L193" t="s">
+        <v>238</v>
+      </c>
+      <c r="O193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15">
+      <c r="A194">
+        <v>1200003</v>
+      </c>
+      <c r="C194">
+        <v>1200003</v>
+      </c>
+      <c r="D194" t="s">
+        <v>239</v>
+      </c>
+      <c r="E194">
+        <v>2</v>
+      </c>
+      <c r="F194" t="s">
+        <v>43</v>
+      </c>
+      <c r="G194">
+        <v>1</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194" t="s">
+        <v>158</v>
+      </c>
+      <c r="J194">
+        <v>2200003</v>
+      </c>
+      <c r="K194" t="b">
+        <v>0</v>
+      </c>
+      <c r="L194" t="s">
+        <v>240</v>
+      </c>
+      <c r="O194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15">
+      <c r="A195">
+        <v>1200004</v>
+      </c>
+      <c r="C195">
+        <v>1200004</v>
+      </c>
+      <c r="D195" t="s">
+        <v>241</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>43</v>
+      </c>
+      <c r="G195">
+        <v>1</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195" t="s">
+        <v>158</v>
+      </c>
+      <c r="J195">
+        <v>2200004</v>
+      </c>
+      <c r="K195" t="b">
+        <v>0</v>
+      </c>
+      <c r="L195" t="s">
+        <v>242</v>
+      </c>
+      <c r="O195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15">
+      <c r="A196">
+        <v>1200005</v>
+      </c>
+      <c r="C196">
+        <v>1200005</v>
+      </c>
+      <c r="D196" t="s">
+        <v>243</v>
+      </c>
+      <c r="E196">
+        <v>2</v>
+      </c>
+      <c r="F196" t="s">
+        <v>43</v>
+      </c>
+      <c r="G196">
+        <v>1</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196" t="s">
+        <v>158</v>
+      </c>
+      <c r="J196">
+        <v>2200005</v>
+      </c>
+      <c r="K196" t="b">
+        <v>0</v>
+      </c>
+      <c r="L196" t="s">
+        <v>244</v>
+      </c>
+      <c r="O196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15">
+      <c r="A197">
+        <v>1200006</v>
+      </c>
+      <c r="C197">
+        <v>1200006</v>
+      </c>
+      <c r="D197" t="s">
+        <v>245</v>
+      </c>
+      <c r="E197">
+        <v>2</v>
+      </c>
+      <c r="F197" t="s">
+        <v>43</v>
+      </c>
+      <c r="G197">
+        <v>1</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197" t="s">
+        <v>158</v>
+      </c>
+      <c r="J197">
+        <v>2200006</v>
+      </c>
+      <c r="K197" t="b">
+        <v>0</v>
+      </c>
+      <c r="L197" t="s">
+        <v>236</v>
+      </c>
+      <c r="O197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15">
+      <c r="A198">
+        <v>1200007</v>
+      </c>
+      <c r="C198">
+        <v>1200007</v>
+      </c>
+      <c r="D198" t="s">
+        <v>246</v>
+      </c>
+      <c r="E198">
+        <v>2</v>
+      </c>
+      <c r="F198" t="s">
+        <v>43</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198" t="s">
+        <v>158</v>
+      </c>
+      <c r="J198">
+        <v>2200007</v>
+      </c>
+      <c r="K198" t="b">
+        <v>0</v>
+      </c>
+      <c r="L198" t="s">
+        <v>247</v>
+      </c>
+      <c r="O198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15">
+      <c r="A199">
+        <v>1200008</v>
+      </c>
+      <c r="C199">
+        <v>1200008</v>
+      </c>
+      <c r="D199" t="s">
+        <v>248</v>
+      </c>
+      <c r="E199">
+        <v>2</v>
+      </c>
+      <c r="F199" t="s">
+        <v>43</v>
+      </c>
+      <c r="G199">
+        <v>1</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199" t="s">
+        <v>158</v>
+      </c>
+      <c r="J199">
+        <v>2200008</v>
+      </c>
+      <c r="K199" t="b">
+        <v>0</v>
+      </c>
+      <c r="L199" t="s">
+        <v>249</v>
+      </c>
+      <c r="O199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15">
+      <c r="A200">
+        <v>1200009</v>
+      </c>
+      <c r="C200">
+        <v>1200009</v>
+      </c>
+      <c r="D200" t="s">
+        <v>250</v>
+      </c>
+      <c r="E200">
+        <v>2</v>
+      </c>
+      <c r="F200" t="s">
+        <v>43</v>
+      </c>
+      <c r="G200">
+        <v>1</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200" t="s">
+        <v>158</v>
+      </c>
+      <c r="J200">
+        <v>2200009</v>
+      </c>
+      <c r="K200" t="b">
+        <v>0</v>
+      </c>
+      <c r="L200" t="s">
+        <v>251</v>
+      </c>
+      <c r="O200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15">
+      <c r="A201">
+        <v>1200010</v>
+      </c>
+      <c r="C201">
+        <v>1200010</v>
+      </c>
+      <c r="D201" t="s">
+        <v>252</v>
+      </c>
+      <c r="E201">
+        <v>2</v>
+      </c>
+      <c r="F201" t="s">
+        <v>43</v>
+      </c>
+      <c r="G201">
+        <v>1</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201" t="s">
+        <v>158</v>
+      </c>
+      <c r="J201">
+        <v>2200010</v>
+      </c>
+      <c r="K201" t="b">
+        <v>0</v>
+      </c>
+      <c r="L201" t="s">
+        <v>253</v>
+      </c>
+      <c r="O201">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -248,7 +248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A158" authorId="0">
+    <comment ref="A160" authorId="0">
       <text>
         <r>
           <rPr>
@@ -270,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A168" authorId="0">
+    <comment ref="A170" authorId="0">
       <text>
         <r>
           <rPr>
@@ -293,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A178" authorId="0">
+    <comment ref="A180" authorId="0">
       <text>
         <r>
           <rPr>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="257">
   <si>
     <t>道具ID</t>
   </si>
@@ -849,6 +849,12 @@
   </si>
   <si>
     <t>雇员升级材料3</t>
+  </si>
+  <si>
+    <t>声誉值</t>
+  </si>
+  <si>
+    <t>贡献值</t>
   </si>
   <si>
     <t>街头潮人</t>
@@ -2330,7 +2336,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S197"/>
+  <dimension ref="A1:S199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" customWidth="1"/>
@@ -5336,10 +5342,10 @@
     </row>
     <row r="68" spans="1:16">
       <c r="A68">
-        <v>1025101</v>
+        <v>1024011</v>
       </c>
       <c r="C68">
-        <v>1025101</v>
+        <v>1024011</v>
       </c>
       <c r="D68" t="s">
         <v>176</v>
@@ -5354,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68">
         <v>1</v>
@@ -5363,7 +5369,7 @@
         <v>160</v>
       </c>
       <c r="K68">
-        <v>2025101</v>
+        <v>2024011</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -5377,10 +5383,10 @@
     </row>
     <row r="69" spans="1:16">
       <c r="A69">
-        <v>1025102</v>
+        <v>1024012</v>
       </c>
       <c r="C69">
-        <v>1025102</v>
+        <v>1024012</v>
       </c>
       <c r="D69" t="s">
         <v>177</v>
@@ -5395,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69">
         <v>1</v>
@@ -5404,7 +5410,7 @@
         <v>160</v>
       </c>
       <c r="K69">
-        <v>2025102</v>
+        <v>2024012</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -5418,10 +5424,10 @@
     </row>
     <row r="70" spans="1:16">
       <c r="A70">
-        <v>1025103</v>
+        <v>1025101</v>
       </c>
       <c r="C70">
-        <v>1025103</v>
+        <v>1025101</v>
       </c>
       <c r="D70" t="s">
         <v>178</v>
@@ -5445,7 +5451,7 @@
         <v>160</v>
       </c>
       <c r="K70">
-        <v>2025103</v>
+        <v>2025101</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -5459,10 +5465,10 @@
     </row>
     <row r="71" spans="1:16">
       <c r="A71">
-        <v>1025104</v>
+        <v>1025102</v>
       </c>
       <c r="C71">
-        <v>1025104</v>
+        <v>1025102</v>
       </c>
       <c r="D71" t="s">
         <v>179</v>
@@ -5486,7 +5492,7 @@
         <v>160</v>
       </c>
       <c r="K71">
-        <v>2025104</v>
+        <v>2025102</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -5500,10 +5506,10 @@
     </row>
     <row r="72" spans="1:16">
       <c r="A72">
-        <v>1025105</v>
+        <v>1025103</v>
       </c>
       <c r="C72">
-        <v>1025105</v>
+        <v>1025103</v>
       </c>
       <c r="D72" t="s">
         <v>180</v>
@@ -5527,7 +5533,7 @@
         <v>160</v>
       </c>
       <c r="K72">
-        <v>2025105</v>
+        <v>2025103</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -5541,10 +5547,10 @@
     </row>
     <row r="73" spans="1:16">
       <c r="A73">
-        <v>1025106</v>
+        <v>1025104</v>
       </c>
       <c r="C73">
-        <v>1025106</v>
+        <v>1025104</v>
       </c>
       <c r="D73" t="s">
         <v>181</v>
@@ -5568,7 +5574,7 @@
         <v>160</v>
       </c>
       <c r="K73">
-        <v>2025106</v>
+        <v>2025104</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -5582,10 +5588,10 @@
     </row>
     <row r="74" spans="1:16">
       <c r="A74">
-        <v>1025201</v>
+        <v>1025105</v>
       </c>
       <c r="C74">
-        <v>1025201</v>
+        <v>1025105</v>
       </c>
       <c r="D74" t="s">
         <v>182</v>
@@ -5597,7 +5603,7 @@
         <v>45</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -5609,7 +5615,7 @@
         <v>160</v>
       </c>
       <c r="K74">
-        <v>2025201</v>
+        <v>2025105</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -5623,10 +5629,10 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75">
-        <v>1025202</v>
+        <v>1025106</v>
       </c>
       <c r="C75">
-        <v>1025202</v>
+        <v>1025106</v>
       </c>
       <c r="D75" t="s">
         <v>183</v>
@@ -5638,7 +5644,7 @@
         <v>45</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -5650,7 +5656,7 @@
         <v>160</v>
       </c>
       <c r="K75">
-        <v>2025202</v>
+        <v>2025106</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -5664,10 +5670,10 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76">
-        <v>1025203</v>
+        <v>1025201</v>
       </c>
       <c r="C76">
-        <v>1025203</v>
+        <v>1025201</v>
       </c>
       <c r="D76" t="s">
         <v>184</v>
@@ -5691,7 +5697,7 @@
         <v>160</v>
       </c>
       <c r="K76">
-        <v>2025203</v>
+        <v>2025201</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -5705,10 +5711,10 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77">
-        <v>1025204</v>
+        <v>1025202</v>
       </c>
       <c r="C77">
-        <v>1025204</v>
+        <v>1025202</v>
       </c>
       <c r="D77" t="s">
         <v>185</v>
@@ -5732,7 +5738,7 @@
         <v>160</v>
       </c>
       <c r="K77">
-        <v>2025204</v>
+        <v>2025202</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -5746,10 +5752,10 @@
     </row>
     <row r="78" spans="1:16">
       <c r="A78">
-        <v>1025205</v>
+        <v>1025203</v>
       </c>
       <c r="C78">
-        <v>1025205</v>
+        <v>1025203</v>
       </c>
       <c r="D78" t="s">
         <v>186</v>
@@ -5773,7 +5779,7 @@
         <v>160</v>
       </c>
       <c r="K78">
-        <v>2025205</v>
+        <v>2025203</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -5787,10 +5793,10 @@
     </row>
     <row r="79" spans="1:16">
       <c r="A79">
-        <v>1025206</v>
+        <v>1025204</v>
       </c>
       <c r="C79">
-        <v>1025206</v>
+        <v>1025204</v>
       </c>
       <c r="D79" t="s">
         <v>187</v>
@@ -5814,7 +5820,7 @@
         <v>160</v>
       </c>
       <c r="K79">
-        <v>2025206</v>
+        <v>2025204</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -5828,10 +5834,10 @@
     </row>
     <row r="80" spans="1:16">
       <c r="A80">
-        <v>1025301</v>
+        <v>1025205</v>
       </c>
       <c r="C80">
-        <v>1025301</v>
+        <v>1025205</v>
       </c>
       <c r="D80" t="s">
         <v>188</v>
@@ -5843,7 +5849,7 @@
         <v>45</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -5855,7 +5861,7 @@
         <v>160</v>
       </c>
       <c r="K80">
-        <v>2025301</v>
+        <v>2025205</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -5869,10 +5875,10 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81">
-        <v>1025302</v>
+        <v>1025206</v>
       </c>
       <c r="C81">
-        <v>1025302</v>
+        <v>1025206</v>
       </c>
       <c r="D81" t="s">
         <v>189</v>
@@ -5884,7 +5890,7 @@
         <v>45</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -5896,7 +5902,7 @@
         <v>160</v>
       </c>
       <c r="K81">
-        <v>2025302</v>
+        <v>2025206</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -5910,10 +5916,10 @@
     </row>
     <row r="82" spans="1:16">
       <c r="A82">
-        <v>1025303</v>
+        <v>1025301</v>
       </c>
       <c r="C82">
-        <v>1025303</v>
+        <v>1025301</v>
       </c>
       <c r="D82" t="s">
         <v>190</v>
@@ -5937,7 +5943,7 @@
         <v>160</v>
       </c>
       <c r="K82">
-        <v>2025303</v>
+        <v>2025301</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -5951,10 +5957,10 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83">
-        <v>1025304</v>
+        <v>1025302</v>
       </c>
       <c r="C83">
-        <v>1025304</v>
+        <v>1025302</v>
       </c>
       <c r="D83" t="s">
         <v>191</v>
@@ -5978,7 +5984,7 @@
         <v>160</v>
       </c>
       <c r="K83">
-        <v>2025304</v>
+        <v>2025302</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -5992,10 +5998,10 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84">
-        <v>1025305</v>
+        <v>1025303</v>
       </c>
       <c r="C84">
-        <v>1025305</v>
+        <v>1025303</v>
       </c>
       <c r="D84" t="s">
         <v>192</v>
@@ -6019,7 +6025,7 @@
         <v>160</v>
       </c>
       <c r="K84">
-        <v>2025305</v>
+        <v>2025303</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -6033,10 +6039,10 @@
     </row>
     <row r="85" spans="1:16">
       <c r="A85">
-        <v>1025306</v>
+        <v>1025304</v>
       </c>
       <c r="C85">
-        <v>1025306</v>
+        <v>1025304</v>
       </c>
       <c r="D85" t="s">
         <v>193</v>
@@ -6060,7 +6066,7 @@
         <v>160</v>
       </c>
       <c r="K85">
-        <v>2025306</v>
+        <v>2025304</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -6074,10 +6080,10 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86">
-        <v>1025401</v>
+        <v>1025305</v>
       </c>
       <c r="C86">
-        <v>1025401</v>
+        <v>1025305</v>
       </c>
       <c r="D86" t="s">
         <v>194</v>
@@ -6089,7 +6095,7 @@
         <v>45</v>
       </c>
       <c r="G86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -6101,7 +6107,7 @@
         <v>160</v>
       </c>
       <c r="K86">
-        <v>2025401</v>
+        <v>2025305</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -6115,10 +6121,10 @@
     </row>
     <row r="87" spans="1:16">
       <c r="A87">
-        <v>1025402</v>
+        <v>1025306</v>
       </c>
       <c r="C87">
-        <v>1025402</v>
+        <v>1025306</v>
       </c>
       <c r="D87" t="s">
         <v>195</v>
@@ -6130,7 +6136,7 @@
         <v>45</v>
       </c>
       <c r="G87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -6142,7 +6148,7 @@
         <v>160</v>
       </c>
       <c r="K87">
-        <v>2025402</v>
+        <v>2025306</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -6156,10 +6162,10 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88">
-        <v>1025403</v>
+        <v>1025401</v>
       </c>
       <c r="C88">
-        <v>1025403</v>
+        <v>1025401</v>
       </c>
       <c r="D88" t="s">
         <v>196</v>
@@ -6183,7 +6189,7 @@
         <v>160</v>
       </c>
       <c r="K88">
-        <v>2025403</v>
+        <v>2025401</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -6197,10 +6203,10 @@
     </row>
     <row r="89" spans="1:16">
       <c r="A89">
-        <v>1025404</v>
+        <v>1025402</v>
       </c>
       <c r="C89">
-        <v>1025404</v>
+        <v>1025402</v>
       </c>
       <c r="D89" t="s">
         <v>197</v>
@@ -6224,7 +6230,7 @@
         <v>160</v>
       </c>
       <c r="K89">
-        <v>2025404</v>
+        <v>2025402</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -6238,10 +6244,10 @@
     </row>
     <row r="90" spans="1:16">
       <c r="A90">
-        <v>1025405</v>
+        <v>1025403</v>
       </c>
       <c r="C90">
-        <v>1025405</v>
+        <v>1025403</v>
       </c>
       <c r="D90" t="s">
         <v>198</v>
@@ -6265,7 +6271,7 @@
         <v>160</v>
       </c>
       <c r="K90">
-        <v>2025405</v>
+        <v>2025403</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -6279,10 +6285,10 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91">
-        <v>1025406</v>
+        <v>1025404</v>
       </c>
       <c r="C91">
-        <v>1025406</v>
+        <v>1025404</v>
       </c>
       <c r="D91" t="s">
         <v>199</v>
@@ -6306,7 +6312,7 @@
         <v>160</v>
       </c>
       <c r="K91">
-        <v>2025406</v>
+        <v>2025404</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -6320,10 +6326,10 @@
     </row>
     <row r="92" spans="1:16">
       <c r="A92">
-        <v>1025501</v>
+        <v>1025405</v>
       </c>
       <c r="C92">
-        <v>1025501</v>
+        <v>1025405</v>
       </c>
       <c r="D92" t="s">
         <v>200</v>
@@ -6335,7 +6341,7 @@
         <v>45</v>
       </c>
       <c r="G92">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -6347,7 +6353,7 @@
         <v>160</v>
       </c>
       <c r="K92">
-        <v>2025501</v>
+        <v>2025405</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -6361,10 +6367,10 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93">
-        <v>1025502</v>
+        <v>1025406</v>
       </c>
       <c r="C93">
-        <v>1025502</v>
+        <v>1025406</v>
       </c>
       <c r="D93" t="s">
         <v>201</v>
@@ -6376,7 +6382,7 @@
         <v>45</v>
       </c>
       <c r="G93">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -6388,7 +6394,7 @@
         <v>160</v>
       </c>
       <c r="K93">
-        <v>2025502</v>
+        <v>2025406</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -6402,10 +6408,10 @@
     </row>
     <row r="94" spans="1:16">
       <c r="A94">
-        <v>1025503</v>
+        <v>1025501</v>
       </c>
       <c r="C94">
-        <v>1025503</v>
+        <v>1025501</v>
       </c>
       <c r="D94" t="s">
         <v>202</v>
@@ -6429,7 +6435,7 @@
         <v>160</v>
       </c>
       <c r="K94">
-        <v>2025503</v>
+        <v>2025501</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -6443,10 +6449,10 @@
     </row>
     <row r="95" spans="1:16">
       <c r="A95">
-        <v>1025504</v>
+        <v>1025502</v>
       </c>
       <c r="C95">
-        <v>1025504</v>
+        <v>1025502</v>
       </c>
       <c r="D95" t="s">
         <v>203</v>
@@ -6470,7 +6476,7 @@
         <v>160</v>
       </c>
       <c r="K95">
-        <v>2025504</v>
+        <v>2025502</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -6484,10 +6490,10 @@
     </row>
     <row r="96" spans="1:16">
       <c r="A96">
-        <v>1025505</v>
+        <v>1025503</v>
       </c>
       <c r="C96">
-        <v>1025505</v>
+        <v>1025503</v>
       </c>
       <c r="D96" t="s">
         <v>204</v>
@@ -6511,7 +6517,7 @@
         <v>160</v>
       </c>
       <c r="K96">
-        <v>2025505</v>
+        <v>2025503</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -6525,10 +6531,10 @@
     </row>
     <row r="97" spans="1:16">
       <c r="A97">
-        <v>1025506</v>
+        <v>1025504</v>
       </c>
       <c r="C97">
-        <v>1025506</v>
+        <v>1025504</v>
       </c>
       <c r="D97" t="s">
         <v>205</v>
@@ -6552,7 +6558,7 @@
         <v>160</v>
       </c>
       <c r="K97">
-        <v>2025506</v>
+        <v>2025504</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -6566,14 +6572,13 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98">
-        <v>1125101</v>
+        <v>1025505</v>
       </c>
       <c r="C98">
-        <v>1125101</v>
-      </c>
-      <c r="D98" t="str">
-        <f>D68&amp;"碎片"</f>
-        <v>街头潮人碎片</v>
+        <v>1025505</v>
+      </c>
+      <c r="D98" t="s">
+        <v>206</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -6582,7 +6587,7 @@
         <v>45</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -6594,29 +6599,27 @@
         <v>160</v>
       </c>
       <c r="K98">
-        <v>2125101</v>
+        <v>2025505</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
       </c>
-      <c r="M98" t="str">
-        <f>D68&amp;"游客的升星道具"</f>
-        <v>街头潮人游客的升星道具</v>
+      <c r="M98" t="s">
+        <v>206</v>
       </c>
       <c r="P98">
-        <v>999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="99" spans="1:16">
       <c r="A99">
-        <v>1125102</v>
+        <v>1025506</v>
       </c>
       <c r="C99">
-        <v>1125102</v>
-      </c>
-      <c r="D99" t="str">
-        <f t="shared" ref="D99:D127" si="0">D69&amp;"碎片"</f>
-        <v>复古绅士碎片</v>
+        <v>1025506</v>
+      </c>
+      <c r="D99" t="s">
+        <v>207</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -6625,7 +6628,7 @@
         <v>45</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -6637,1311 +6640,1314 @@
         <v>160</v>
       </c>
       <c r="K99">
-        <v>2125102</v>
+        <v>2025506</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
       </c>
-      <c r="M99" t="str">
-        <f t="shared" ref="M99:M127" si="1">D69&amp;"游客的升星道具"</f>
-        <v>复古绅士游客的升星道具</v>
+      <c r="M99" t="s">
+        <v>207</v>
       </c>
       <c r="P99">
-        <v>999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="100" spans="1:16">
       <c r="A100">
+        <v>1125101</v>
+      </c>
+      <c r="C100">
+        <v>1125101</v>
+      </c>
+      <c r="D100" t="str">
+        <f>D70&amp;"碎片"</f>
+        <v>街头潮人碎片</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="F100" t="s">
+        <v>45</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100" t="b">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100" t="s">
+        <v>160</v>
+      </c>
+      <c r="K100">
+        <v>2125101</v>
+      </c>
+      <c r="L100" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" t="str">
+        <f>D70&amp;"游客的升星道具"</f>
+        <v>街头潮人游客的升星道具</v>
+      </c>
+      <c r="P100">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101">
+        <v>1125102</v>
+      </c>
+      <c r="C101">
+        <v>1125102</v>
+      </c>
+      <c r="D101" t="str">
+        <f t="shared" ref="D101:D129" si="0">D71&amp;"碎片"</f>
+        <v>复古绅士碎片</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="F101" t="s">
+        <v>45</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101" t="s">
+        <v>160</v>
+      </c>
+      <c r="K101">
+        <v>2125102</v>
+      </c>
+      <c r="L101" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" t="str">
+        <f t="shared" ref="M101:M129" si="1">D71&amp;"游客的升星道具"</f>
+        <v>复古绅士游客的升星道具</v>
+      </c>
+      <c r="P101">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102">
         <v>1125103</v>
       </c>
-      <c r="C100">
+      <c r="C102">
         <v>1125103</v>
       </c>
-      <c r="D100" t="str">
+      <c r="D102" t="str">
         <f t="shared" si="0"/>
         <v>酷盖少年碎片</v>
       </c>
-      <c r="E100">
-        <v>2</v>
-      </c>
-      <c r="F100" t="s">
-        <v>45</v>
-      </c>
-      <c r="G100">
-        <v>1</v>
-      </c>
-      <c r="H100" t="b">
-        <v>1</v>
-      </c>
-      <c r="I100">
-        <v>1</v>
-      </c>
-      <c r="J100" t="s">
-        <v>160</v>
-      </c>
-      <c r="K100">
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="F102" t="s">
+        <v>45</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102" t="b">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102" t="s">
+        <v>160</v>
+      </c>
+      <c r="K102">
         <v>2125103</v>
       </c>
-      <c r="L100" t="b">
-        <v>0</v>
-      </c>
-      <c r="M100" t="str">
+      <c r="L102" t="b">
+        <v>0</v>
+      </c>
+      <c r="M102" t="str">
         <f t="shared" si="1"/>
         <v>酷盖少年游客的升星道具</v>
       </c>
-      <c r="P100">
+      <c r="P102">
         <v>999</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
-      <c r="A101">
+    <row r="103" spans="1:16">
+      <c r="A103">
         <v>1125104</v>
       </c>
-      <c r="C101">
+      <c r="C103">
         <v>1125104</v>
       </c>
-      <c r="D101" t="str">
+      <c r="D103" t="str">
         <f t="shared" si="0"/>
         <v>潮流先锋碎片</v>
       </c>
-      <c r="E101">
-        <v>2</v>
-      </c>
-      <c r="F101" t="s">
-        <v>45</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101" t="b">
-        <v>1</v>
-      </c>
-      <c r="I101">
-        <v>1</v>
-      </c>
-      <c r="J101" t="s">
-        <v>160</v>
-      </c>
-      <c r="K101">
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="F103" t="s">
+        <v>45</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103" t="b">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>1</v>
+      </c>
+      <c r="J103" t="s">
+        <v>160</v>
+      </c>
+      <c r="K103">
         <v>2125104</v>
       </c>
-      <c r="L101" t="b">
-        <v>0</v>
-      </c>
-      <c r="M101" t="str">
+      <c r="L103" t="b">
+        <v>0</v>
+      </c>
+      <c r="M103" t="str">
         <f t="shared" si="1"/>
         <v>潮流先锋游客的升星道具</v>
       </c>
-      <c r="P101">
+      <c r="P103">
         <v>999</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
-      <c r="A102">
+    <row r="104" spans="1:16">
+      <c r="A104">
         <v>1125105</v>
       </c>
-      <c r="C102">
+      <c r="C104">
         <v>1125105</v>
       </c>
-      <c r="D102" t="str">
+      <c r="D104" t="str">
         <f t="shared" si="0"/>
         <v>时尚教主碎片</v>
       </c>
-      <c r="E102">
-        <v>2</v>
-      </c>
-      <c r="F102" t="s">
-        <v>45</v>
-      </c>
-      <c r="G102">
-        <v>1</v>
-      </c>
-      <c r="H102" t="b">
-        <v>1</v>
-      </c>
-      <c r="I102">
-        <v>1</v>
-      </c>
-      <c r="J102" t="s">
-        <v>160</v>
-      </c>
-      <c r="K102">
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="F104" t="s">
+        <v>45</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104" t="b">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104" t="s">
+        <v>160</v>
+      </c>
+      <c r="K104">
         <v>2125105</v>
       </c>
-      <c r="L102" t="b">
-        <v>0</v>
-      </c>
-      <c r="M102" t="str">
+      <c r="L104" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" t="str">
         <f t="shared" si="1"/>
         <v>时尚教主游客的升星道具</v>
       </c>
-      <c r="P102">
+      <c r="P104">
         <v>999</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
-      <c r="A103">
+    <row r="105" spans="1:16">
+      <c r="A105">
         <v>1125106</v>
       </c>
-      <c r="C103">
+      <c r="C105">
         <v>1125106</v>
       </c>
-      <c r="D103" t="str">
+      <c r="D105" t="str">
         <f t="shared" si="0"/>
         <v>街拍达人碎片</v>
       </c>
-      <c r="E103">
-        <v>2</v>
-      </c>
-      <c r="F103" t="s">
-        <v>45</v>
-      </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
-      <c r="H103" t="b">
-        <v>1</v>
-      </c>
-      <c r="I103">
-        <v>1</v>
-      </c>
-      <c r="J103" t="s">
-        <v>160</v>
-      </c>
-      <c r="K103">
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="F105" t="s">
+        <v>45</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105" t="b">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105" t="s">
+        <v>160</v>
+      </c>
+      <c r="K105">
         <v>2125106</v>
       </c>
-      <c r="L103" t="b">
-        <v>0</v>
-      </c>
-      <c r="M103" t="str">
+      <c r="L105" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" t="str">
         <f t="shared" si="1"/>
         <v>街拍达人游客的升星道具</v>
       </c>
-      <c r="P103">
+      <c r="P105">
         <v>999</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
-      <c r="A104">
+    <row r="106" spans="1:16">
+      <c r="A106">
         <v>1125201</v>
       </c>
-      <c r="C104">
+      <c r="C106">
         <v>1125201</v>
       </c>
-      <c r="D104" t="str">
+      <c r="D106" t="str">
         <f t="shared" si="0"/>
         <v>运动健将碎片</v>
       </c>
-      <c r="E104">
-        <v>2</v>
-      </c>
-      <c r="F104" t="s">
-        <v>45</v>
-      </c>
-      <c r="G104">
-        <v>2</v>
-      </c>
-      <c r="H104" t="b">
-        <v>1</v>
-      </c>
-      <c r="I104">
-        <v>1</v>
-      </c>
-      <c r="J104" t="s">
-        <v>160</v>
-      </c>
-      <c r="K104">
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="F106" t="s">
+        <v>45</v>
+      </c>
+      <c r="G106">
+        <v>2</v>
+      </c>
+      <c r="H106" t="b">
+        <v>1</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106" t="s">
+        <v>160</v>
+      </c>
+      <c r="K106">
         <v>2125201</v>
       </c>
-      <c r="L104" t="b">
-        <v>0</v>
-      </c>
-      <c r="M104" t="str">
+      <c r="L106" t="b">
+        <v>0</v>
+      </c>
+      <c r="M106" t="str">
         <f t="shared" si="1"/>
         <v>运动健将游客的升星道具</v>
       </c>
-      <c r="P104">
+      <c r="P106">
         <v>999</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
-      <c r="A105">
+    <row r="107" spans="1:16">
+      <c r="A107">
         <v>1125202</v>
       </c>
-      <c r="C105">
+      <c r="C107">
         <v>1125202</v>
       </c>
-      <c r="D105" t="str">
+      <c r="D107" t="str">
         <f t="shared" si="0"/>
         <v>跑酷少年碎片</v>
       </c>
-      <c r="E105">
-        <v>2</v>
-      </c>
-      <c r="F105" t="s">
-        <v>45</v>
-      </c>
-      <c r="G105">
-        <v>2</v>
-      </c>
-      <c r="H105" t="b">
-        <v>1</v>
-      </c>
-      <c r="I105">
-        <v>1</v>
-      </c>
-      <c r="J105" t="s">
-        <v>160</v>
-      </c>
-      <c r="K105">
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="F107" t="s">
+        <v>45</v>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+      <c r="H107" t="b">
+        <v>1</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="J107" t="s">
+        <v>160</v>
+      </c>
+      <c r="K107">
         <v>2125202</v>
       </c>
-      <c r="L105" t="b">
-        <v>0</v>
-      </c>
-      <c r="M105" t="str">
+      <c r="L107" t="b">
+        <v>0</v>
+      </c>
+      <c r="M107" t="str">
         <f t="shared" si="1"/>
         <v>跑酷少年游客的升星道具</v>
       </c>
-      <c r="P105">
+      <c r="P107">
         <v>999</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
-      <c r="A106">
+    <row r="108" spans="1:16">
+      <c r="A108">
         <v>1125203</v>
       </c>
-      <c r="C106">
+      <c r="C108">
         <v>1125203</v>
       </c>
-      <c r="D106" t="str">
+      <c r="D108" t="str">
         <f t="shared" si="0"/>
         <v>滑板高手碎片</v>
       </c>
-      <c r="E106">
-        <v>2</v>
-      </c>
-      <c r="F106" t="s">
-        <v>45</v>
-      </c>
-      <c r="G106">
-        <v>2</v>
-      </c>
-      <c r="H106" t="b">
-        <v>1</v>
-      </c>
-      <c r="I106">
-        <v>1</v>
-      </c>
-      <c r="J106" t="s">
-        <v>160</v>
-      </c>
-      <c r="K106">
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="F108" t="s">
+        <v>45</v>
+      </c>
+      <c r="G108">
+        <v>2</v>
+      </c>
+      <c r="H108" t="b">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108" t="s">
+        <v>160</v>
+      </c>
+      <c r="K108">
         <v>2125203</v>
       </c>
-      <c r="L106" t="b">
-        <v>0</v>
-      </c>
-      <c r="M106" t="str">
+      <c r="L108" t="b">
+        <v>0</v>
+      </c>
+      <c r="M108" t="str">
         <f t="shared" si="1"/>
         <v>滑板高手游客的升星道具</v>
       </c>
-      <c r="P106">
+      <c r="P108">
         <v>999</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
-      <c r="A107">
+    <row r="109" spans="1:16">
+      <c r="A109">
         <v>1125204</v>
       </c>
-      <c r="C107">
+      <c r="C109">
         <v>1125204</v>
       </c>
-      <c r="D107" t="str">
+      <c r="D109" t="str">
         <f t="shared" si="0"/>
         <v>甜心辣妹碎片</v>
       </c>
-      <c r="E107">
-        <v>2</v>
-      </c>
-      <c r="F107" t="s">
-        <v>45</v>
-      </c>
-      <c r="G107">
-        <v>2</v>
-      </c>
-      <c r="H107" t="b">
-        <v>1</v>
-      </c>
-      <c r="I107">
-        <v>1</v>
-      </c>
-      <c r="J107" t="s">
-        <v>160</v>
-      </c>
-      <c r="K107">
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="F109" t="s">
+        <v>45</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+      <c r="H109" t="b">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109" t="s">
+        <v>160</v>
+      </c>
+      <c r="K109">
         <v>2125204</v>
       </c>
-      <c r="L107" t="b">
-        <v>0</v>
-      </c>
-      <c r="M107" t="str">
+      <c r="L109" t="b">
+        <v>0</v>
+      </c>
+      <c r="M109" t="str">
         <f t="shared" si="1"/>
         <v>甜心辣妹游客的升星道具</v>
       </c>
-      <c r="P107">
+      <c r="P109">
         <v>999</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
-      <c r="A108">
+    <row r="110" spans="1:16">
+      <c r="A110">
         <v>1125205</v>
       </c>
-      <c r="C108">
+      <c r="C110">
         <v>1125205</v>
       </c>
-      <c r="D108" t="str">
+      <c r="D110" t="str">
         <f t="shared" si="0"/>
         <v>活力少女碎片</v>
       </c>
-      <c r="E108">
-        <v>2</v>
-      </c>
-      <c r="F108" t="s">
-        <v>45</v>
-      </c>
-      <c r="G108">
-        <v>2</v>
-      </c>
-      <c r="H108" t="b">
-        <v>1</v>
-      </c>
-      <c r="I108">
-        <v>1</v>
-      </c>
-      <c r="J108" t="s">
-        <v>160</v>
-      </c>
-      <c r="K108">
+      <c r="E110">
+        <v>2</v>
+      </c>
+      <c r="F110" t="s">
+        <v>45</v>
+      </c>
+      <c r="G110">
+        <v>2</v>
+      </c>
+      <c r="H110" t="b">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110" t="s">
+        <v>160</v>
+      </c>
+      <c r="K110">
         <v>2125205</v>
       </c>
-      <c r="L108" t="b">
-        <v>0</v>
-      </c>
-      <c r="M108" t="str">
+      <c r="L110" t="b">
+        <v>0</v>
+      </c>
+      <c r="M110" t="str">
         <f t="shared" si="1"/>
         <v>活力少女游客的升星道具</v>
       </c>
-      <c r="P108">
+      <c r="P110">
         <v>999</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
-      <c r="A109">
+    <row r="111" spans="1:16">
+      <c r="A111">
         <v>1125206</v>
       </c>
-      <c r="C109">
+      <c r="C111">
         <v>1125206</v>
       </c>
-      <c r="D109" t="str">
+      <c r="D111" t="str">
         <f t="shared" si="0"/>
         <v>优雅女神碎片</v>
       </c>
-      <c r="E109">
-        <v>2</v>
-      </c>
-      <c r="F109" t="s">
-        <v>45</v>
-      </c>
-      <c r="G109">
-        <v>2</v>
-      </c>
-      <c r="H109" t="b">
-        <v>1</v>
-      </c>
-      <c r="I109">
-        <v>1</v>
-      </c>
-      <c r="J109" t="s">
-        <v>160</v>
-      </c>
-      <c r="K109">
+      <c r="E111">
+        <v>2</v>
+      </c>
+      <c r="F111" t="s">
+        <v>45</v>
+      </c>
+      <c r="G111">
+        <v>2</v>
+      </c>
+      <c r="H111" t="b">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111" t="s">
+        <v>160</v>
+      </c>
+      <c r="K111">
         <v>2125206</v>
       </c>
-      <c r="L109" t="b">
-        <v>0</v>
-      </c>
-      <c r="M109" t="str">
+      <c r="L111" t="b">
+        <v>0</v>
+      </c>
+      <c r="M111" t="str">
         <f t="shared" si="1"/>
         <v>优雅女神游客的升星道具</v>
       </c>
-      <c r="P109">
+      <c r="P111">
         <v>999</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
-      <c r="A110">
+    <row r="112" spans="1:16">
+      <c r="A112">
         <v>1125301</v>
       </c>
-      <c r="C110">
+      <c r="C112">
         <v>1125301</v>
       </c>
-      <c r="D110" t="str">
+      <c r="D112" t="str">
         <f t="shared" si="0"/>
         <v>健身狂魔碎片</v>
       </c>
-      <c r="E110">
-        <v>2</v>
-      </c>
-      <c r="F110" t="s">
-        <v>45</v>
-      </c>
-      <c r="G110">
+      <c r="E112">
+        <v>2</v>
+      </c>
+      <c r="F112" t="s">
+        <v>45</v>
+      </c>
+      <c r="G112">
         <v>3</v>
       </c>
-      <c r="H110" t="b">
-        <v>1</v>
-      </c>
-      <c r="I110">
-        <v>1</v>
-      </c>
-      <c r="J110" t="s">
-        <v>160</v>
-      </c>
-      <c r="K110">
+      <c r="H112" t="b">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112" t="s">
+        <v>160</v>
+      </c>
+      <c r="K112">
         <v>2125301</v>
       </c>
-      <c r="L110" t="b">
-        <v>0</v>
-      </c>
-      <c r="M110" t="str">
+      <c r="L112" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" t="str">
         <f t="shared" si="1"/>
         <v>健身狂魔游客的升星道具</v>
       </c>
-      <c r="P110">
+      <c r="P112">
         <v>999</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
-      <c r="A111">
+    <row r="113" spans="1:16">
+      <c r="A113">
         <v>1125302</v>
       </c>
-      <c r="C111">
+      <c r="C113">
         <v>1125302</v>
       </c>
-      <c r="D111" t="str">
+      <c r="D113" t="str">
         <f t="shared" si="0"/>
         <v>单车骑士碎片</v>
       </c>
-      <c r="E111">
-        <v>2</v>
-      </c>
-      <c r="F111" t="s">
-        <v>45</v>
-      </c>
-      <c r="G111">
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113" t="s">
+        <v>45</v>
+      </c>
+      <c r="G113">
         <v>3</v>
       </c>
-      <c r="H111" t="b">
-        <v>1</v>
-      </c>
-      <c r="I111">
-        <v>1</v>
-      </c>
-      <c r="J111" t="s">
-        <v>160</v>
-      </c>
-      <c r="K111">
+      <c r="H113" t="b">
+        <v>1</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113" t="s">
+        <v>160</v>
+      </c>
+      <c r="K113">
         <v>2125302</v>
       </c>
-      <c r="L111" t="b">
-        <v>0</v>
-      </c>
-      <c r="M111" t="str">
+      <c r="L113" t="b">
+        <v>0</v>
+      </c>
+      <c r="M113" t="str">
         <f t="shared" si="1"/>
         <v>单车骑士游客的升星道具</v>
       </c>
-      <c r="P111">
+      <c r="P113">
         <v>999</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
-      <c r="A112">
+    <row r="114" spans="1:16">
+      <c r="A114">
         <v>1125303</v>
       </c>
-      <c r="C112">
+      <c r="C114">
         <v>1125303</v>
       </c>
-      <c r="D112" t="str">
+      <c r="D114" t="str">
         <f t="shared" si="0"/>
         <v>登山行者碎片</v>
       </c>
-      <c r="E112">
-        <v>2</v>
-      </c>
-      <c r="F112" t="s">
-        <v>45</v>
-      </c>
-      <c r="G112">
+      <c r="E114">
+        <v>2</v>
+      </c>
+      <c r="F114" t="s">
+        <v>45</v>
+      </c>
+      <c r="G114">
         <v>3</v>
       </c>
-      <c r="H112" t="b">
-        <v>1</v>
-      </c>
-      <c r="I112">
-        <v>1</v>
-      </c>
-      <c r="J112" t="s">
-        <v>160</v>
-      </c>
-      <c r="K112">
+      <c r="H114" t="b">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="J114" t="s">
+        <v>160</v>
+      </c>
+      <c r="K114">
         <v>2125303</v>
       </c>
-      <c r="L112" t="b">
-        <v>0</v>
-      </c>
-      <c r="M112" t="str">
+      <c r="L114" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" t="str">
         <f t="shared" si="1"/>
         <v>登山行者游客的升星道具</v>
       </c>
-      <c r="P112">
+      <c r="P114">
         <v>999</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
-      <c r="A113">
+    <row r="115" spans="1:16">
+      <c r="A115">
         <v>1125304</v>
       </c>
-      <c r="C113">
+      <c r="C115">
         <v>1125304</v>
       </c>
-      <c r="D113" t="str">
+      <c r="D115" t="str">
         <f t="shared" si="0"/>
         <v>文艺青年碎片</v>
       </c>
-      <c r="E113">
-        <v>2</v>
-      </c>
-      <c r="F113" t="s">
-        <v>45</v>
-      </c>
-      <c r="G113">
+      <c r="E115">
+        <v>2</v>
+      </c>
+      <c r="F115" t="s">
+        <v>45</v>
+      </c>
+      <c r="G115">
         <v>3</v>
       </c>
-      <c r="H113" t="b">
-        <v>1</v>
-      </c>
-      <c r="I113">
-        <v>1</v>
-      </c>
-      <c r="J113" t="s">
-        <v>160</v>
-      </c>
-      <c r="K113">
+      <c r="H115" t="b">
+        <v>1</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115" t="s">
+        <v>160</v>
+      </c>
+      <c r="K115">
         <v>2125304</v>
       </c>
-      <c r="L113" t="b">
-        <v>0</v>
-      </c>
-      <c r="M113" t="str">
+      <c r="L115" t="b">
+        <v>0</v>
+      </c>
+      <c r="M115" t="str">
         <f t="shared" si="1"/>
         <v>文艺青年游客的升星道具</v>
       </c>
-      <c r="P113">
+      <c r="P115">
         <v>999</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
-      <c r="A114">
+    <row r="116" spans="1:16">
+      <c r="A116">
         <v>1125305</v>
       </c>
-      <c r="C114">
+      <c r="C116">
         <v>1125305</v>
       </c>
-      <c r="D114" t="str">
+      <c r="D116" t="str">
         <f t="shared" si="0"/>
         <v>书香少女碎片</v>
       </c>
-      <c r="E114">
-        <v>2</v>
-      </c>
-      <c r="F114" t="s">
-        <v>45</v>
-      </c>
-      <c r="G114">
+      <c r="E116">
+        <v>2</v>
+      </c>
+      <c r="F116" t="s">
+        <v>45</v>
+      </c>
+      <c r="G116">
         <v>3</v>
       </c>
-      <c r="H114" t="b">
-        <v>1</v>
-      </c>
-      <c r="I114">
-        <v>1</v>
-      </c>
-      <c r="J114" t="s">
-        <v>160</v>
-      </c>
-      <c r="K114">
+      <c r="H116" t="b">
+        <v>1</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116" t="s">
+        <v>160</v>
+      </c>
+      <c r="K116">
         <v>2125305</v>
       </c>
-      <c r="L114" t="b">
-        <v>0</v>
-      </c>
-      <c r="M114" t="str">
+      <c r="L116" t="b">
+        <v>0</v>
+      </c>
+      <c r="M116" t="str">
         <f t="shared" si="1"/>
         <v>书香少女游客的升星道具</v>
       </c>
-      <c r="P114">
+      <c r="P116">
         <v>999</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
-      <c r="A115">
+    <row r="117" spans="1:16">
+      <c r="A117">
         <v>1125306</v>
       </c>
-      <c r="C115">
+      <c r="C117">
         <v>1125306</v>
       </c>
-      <c r="D115" t="str">
+      <c r="D117" t="str">
         <f t="shared" si="0"/>
         <v>民谣歌手碎片</v>
       </c>
-      <c r="E115">
-        <v>2</v>
-      </c>
-      <c r="F115" t="s">
-        <v>45</v>
-      </c>
-      <c r="G115">
+      <c r="E117">
+        <v>2</v>
+      </c>
+      <c r="F117" t="s">
+        <v>45</v>
+      </c>
+      <c r="G117">
         <v>3</v>
       </c>
-      <c r="H115" t="b">
-        <v>1</v>
-      </c>
-      <c r="I115">
-        <v>1</v>
-      </c>
-      <c r="J115" t="s">
-        <v>160</v>
-      </c>
-      <c r="K115">
+      <c r="H117" t="b">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117" t="s">
+        <v>160</v>
+      </c>
+      <c r="K117">
         <v>2125306</v>
       </c>
-      <c r="L115" t="b">
-        <v>0</v>
-      </c>
-      <c r="M115" t="str">
+      <c r="L117" t="b">
+        <v>0</v>
+      </c>
+      <c r="M117" t="str">
         <f t="shared" si="1"/>
         <v>民谣歌手游客的升星道具</v>
       </c>
-      <c r="P115">
+      <c r="P117">
         <v>999</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
-      <c r="A116">
+    <row r="118" spans="1:16">
+      <c r="A118">
         <v>1125401</v>
       </c>
-      <c r="C116">
+      <c r="C118">
         <v>1125401</v>
       </c>
-      <c r="D116" t="str">
+      <c r="D118" t="str">
         <f t="shared" si="0"/>
         <v>马拉松客碎片</v>
       </c>
-      <c r="E116">
-        <v>2</v>
-      </c>
-      <c r="F116" t="s">
-        <v>45</v>
-      </c>
-      <c r="G116">
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="F118" t="s">
+        <v>45</v>
+      </c>
+      <c r="G118">
         <v>4</v>
       </c>
-      <c r="H116" t="b">
-        <v>1</v>
-      </c>
-      <c r="I116">
-        <v>1</v>
-      </c>
-      <c r="J116" t="s">
-        <v>160</v>
-      </c>
-      <c r="K116">
+      <c r="H118" t="b">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118" t="s">
+        <v>160</v>
+      </c>
+      <c r="K118">
         <v>2125401</v>
       </c>
-      <c r="L116" t="b">
-        <v>0</v>
-      </c>
-      <c r="M116" t="str">
+      <c r="L118" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" t="str">
         <f t="shared" si="1"/>
         <v>马拉松客游客的升星道具</v>
       </c>
-      <c r="P116">
+      <c r="P118">
         <v>999</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
-      <c r="A117">
+    <row r="119" spans="1:16">
+      <c r="A119">
         <v>1125402</v>
       </c>
-      <c r="C117">
+      <c r="C119">
         <v>1125402</v>
       </c>
-      <c r="D117" t="str">
+      <c r="D119" t="str">
         <f t="shared" si="0"/>
         <v>极限玩家碎片</v>
       </c>
-      <c r="E117">
-        <v>2</v>
-      </c>
-      <c r="F117" t="s">
-        <v>45</v>
-      </c>
-      <c r="G117">
+      <c r="E119">
+        <v>2</v>
+      </c>
+      <c r="F119" t="s">
+        <v>45</v>
+      </c>
+      <c r="G119">
         <v>4</v>
       </c>
-      <c r="H117" t="b">
-        <v>1</v>
-      </c>
-      <c r="I117">
-        <v>1</v>
-      </c>
-      <c r="J117" t="s">
-        <v>160</v>
-      </c>
-      <c r="K117">
+      <c r="H119" t="b">
+        <v>1</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119" t="s">
+        <v>160</v>
+      </c>
+      <c r="K119">
         <v>2125402</v>
       </c>
-      <c r="L117" t="b">
-        <v>0</v>
-      </c>
-      <c r="M117" t="str">
+      <c r="L119" t="b">
+        <v>0</v>
+      </c>
+      <c r="M119" t="str">
         <f t="shared" si="1"/>
         <v>极限玩家游客的升星道具</v>
       </c>
-      <c r="P117">
+      <c r="P119">
         <v>999</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
-      <c r="A118">
+    <row r="120" spans="1:16">
+      <c r="A120">
         <v>1125403</v>
       </c>
-      <c r="C118">
+      <c r="C120">
         <v>1125403</v>
       </c>
-      <c r="D118" t="str">
+      <c r="D120" t="str">
         <f t="shared" si="0"/>
         <v>科技极客碎片</v>
       </c>
-      <c r="E118">
-        <v>2</v>
-      </c>
-      <c r="F118" t="s">
-        <v>45</v>
-      </c>
-      <c r="G118">
+      <c r="E120">
+        <v>2</v>
+      </c>
+      <c r="F120" t="s">
+        <v>45</v>
+      </c>
+      <c r="G120">
         <v>4</v>
       </c>
-      <c r="H118" t="b">
-        <v>1</v>
-      </c>
-      <c r="I118">
-        <v>1</v>
-      </c>
-      <c r="J118" t="s">
-        <v>160</v>
-      </c>
-      <c r="K118">
+      <c r="H120" t="b">
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120" t="s">
+        <v>160</v>
+      </c>
+      <c r="K120">
         <v>2125403</v>
       </c>
-      <c r="L118" t="b">
-        <v>0</v>
-      </c>
-      <c r="M118" t="str">
+      <c r="L120" t="b">
+        <v>0</v>
+      </c>
+      <c r="M120" t="str">
         <f t="shared" si="1"/>
         <v>科技极客游客的升星道具</v>
       </c>
-      <c r="P118">
+      <c r="P120">
         <v>999</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
-      <c r="A119">
+    <row r="121" spans="1:16">
+      <c r="A121">
         <v>1125404</v>
       </c>
-      <c r="C119">
+      <c r="C121">
         <v>1125404</v>
       </c>
-      <c r="D119" t="str">
+      <c r="D121" t="str">
         <f t="shared" si="0"/>
         <v>独立画家碎片</v>
       </c>
-      <c r="E119">
-        <v>2</v>
-      </c>
-      <c r="F119" t="s">
-        <v>45</v>
-      </c>
-      <c r="G119">
+      <c r="E121">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>45</v>
+      </c>
+      <c r="G121">
         <v>4</v>
       </c>
-      <c r="H119" t="b">
-        <v>1</v>
-      </c>
-      <c r="I119">
-        <v>1</v>
-      </c>
-      <c r="J119" t="s">
-        <v>160</v>
-      </c>
-      <c r="K119">
+      <c r="H121" t="b">
+        <v>1</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121" t="s">
+        <v>160</v>
+      </c>
+      <c r="K121">
         <v>2125404</v>
       </c>
-      <c r="L119" t="b">
-        <v>0</v>
-      </c>
-      <c r="M119" t="str">
+      <c r="L121" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" t="str">
         <f t="shared" si="1"/>
         <v>独立画家游客的升星道具</v>
       </c>
-      <c r="P119">
+      <c r="P121">
         <v>999</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
-      <c r="A120">
+    <row r="122" spans="1:16">
+      <c r="A122">
         <v>1125405</v>
       </c>
-      <c r="C120">
+      <c r="C122">
         <v>1125405</v>
       </c>
-      <c r="D120" t="str">
+      <c r="D122" t="str">
         <f t="shared" si="0"/>
         <v>浪漫诗人碎片</v>
       </c>
-      <c r="E120">
-        <v>2</v>
-      </c>
-      <c r="F120" t="s">
-        <v>45</v>
-      </c>
-      <c r="G120">
+      <c r="E122">
+        <v>2</v>
+      </c>
+      <c r="F122" t="s">
+        <v>45</v>
+      </c>
+      <c r="G122">
         <v>4</v>
       </c>
-      <c r="H120" t="b">
-        <v>1</v>
-      </c>
-      <c r="I120">
-        <v>1</v>
-      </c>
-      <c r="J120" t="s">
-        <v>160</v>
-      </c>
-      <c r="K120">
+      <c r="H122" t="b">
+        <v>1</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122" t="s">
+        <v>160</v>
+      </c>
+      <c r="K122">
         <v>2125405</v>
       </c>
-      <c r="L120" t="b">
-        <v>0</v>
-      </c>
-      <c r="M120" t="str">
+      <c r="L122" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" t="str">
         <f t="shared" si="1"/>
         <v>浪漫诗人游客的升星道具</v>
       </c>
-      <c r="P120">
+      <c r="P122">
         <v>999</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
-      <c r="A121">
+    <row r="123" spans="1:16">
+      <c r="A123">
         <v>1125406</v>
       </c>
-      <c r="C121">
+      <c r="C123">
         <v>1125406</v>
       </c>
-      <c r="D121" t="str">
+      <c r="D123" t="str">
         <f t="shared" si="0"/>
         <v>古典乐迷碎片</v>
       </c>
-      <c r="E121">
-        <v>2</v>
-      </c>
-      <c r="F121" t="s">
-        <v>45</v>
-      </c>
-      <c r="G121">
+      <c r="E123">
+        <v>2</v>
+      </c>
+      <c r="F123" t="s">
+        <v>45</v>
+      </c>
+      <c r="G123">
         <v>4</v>
       </c>
-      <c r="H121" t="b">
-        <v>1</v>
-      </c>
-      <c r="I121">
-        <v>1</v>
-      </c>
-      <c r="J121" t="s">
-        <v>160</v>
-      </c>
-      <c r="K121">
+      <c r="H123" t="b">
+        <v>1</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123" t="s">
+        <v>160</v>
+      </c>
+      <c r="K123">
         <v>2125406</v>
       </c>
-      <c r="L121" t="b">
-        <v>0</v>
-      </c>
-      <c r="M121" t="str">
+      <c r="L123" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" t="str">
         <f t="shared" si="1"/>
         <v>古典乐迷游客的升星道具</v>
       </c>
-      <c r="P121">
+      <c r="P123">
         <v>999</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
-      <c r="A122">
+    <row r="124" spans="1:16">
+      <c r="A124">
         <v>1125501</v>
       </c>
-      <c r="C122">
+      <c r="C124">
         <v>1125501</v>
       </c>
-      <c r="D122" t="str">
+      <c r="D124" t="str">
         <f t="shared" si="0"/>
         <v>创业新贵碎片</v>
       </c>
-      <c r="E122">
-        <v>2</v>
-      </c>
-      <c r="F122" t="s">
-        <v>45</v>
-      </c>
-      <c r="G122">
+      <c r="E124">
+        <v>2</v>
+      </c>
+      <c r="F124" t="s">
+        <v>45</v>
+      </c>
+      <c r="G124">
         <v>7</v>
       </c>
-      <c r="H122" t="b">
-        <v>1</v>
-      </c>
-      <c r="I122">
-        <v>1</v>
-      </c>
-      <c r="J122" t="s">
-        <v>160</v>
-      </c>
-      <c r="K122">
+      <c r="H124" t="b">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124" t="s">
+        <v>160</v>
+      </c>
+      <c r="K124">
         <v>2125501</v>
       </c>
-      <c r="L122" t="b">
-        <v>0</v>
-      </c>
-      <c r="M122" t="str">
+      <c r="L124" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" t="str">
         <f t="shared" si="1"/>
         <v>创业新贵游客的升星道具</v>
       </c>
-      <c r="P122">
+      <c r="P124">
         <v>999</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
-      <c r="A123">
+    <row r="125" spans="1:16">
+      <c r="A125">
         <v>1125502</v>
       </c>
-      <c r="C123">
+      <c r="C125">
         <v>1125502</v>
       </c>
-      <c r="D123" t="str">
+      <c r="D125" t="str">
         <f t="shared" si="0"/>
         <v>摸金校尉碎片</v>
       </c>
-      <c r="E123">
-        <v>2</v>
-      </c>
-      <c r="F123" t="s">
-        <v>45</v>
-      </c>
-      <c r="G123">
+      <c r="E125">
+        <v>2</v>
+      </c>
+      <c r="F125" t="s">
+        <v>45</v>
+      </c>
+      <c r="G125">
         <v>7</v>
       </c>
-      <c r="H123" t="b">
-        <v>1</v>
-      </c>
-      <c r="I123">
-        <v>1</v>
-      </c>
-      <c r="J123" t="s">
-        <v>160</v>
-      </c>
-      <c r="K123">
+      <c r="H125" t="b">
+        <v>1</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125" t="s">
+        <v>160</v>
+      </c>
+      <c r="K125">
         <v>2125502</v>
       </c>
-      <c r="L123" t="b">
-        <v>0</v>
-      </c>
-      <c r="M123" t="str">
+      <c r="L125" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" t="str">
         <f t="shared" si="1"/>
         <v>摸金校尉游客的升星道具</v>
       </c>
-      <c r="P123">
+      <c r="P125">
         <v>999</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
-      <c r="A124">
+    <row r="126" spans="1:16">
+      <c r="A126">
         <v>1125503</v>
       </c>
-      <c r="C124">
+      <c r="C126">
         <v>1125503</v>
       </c>
-      <c r="D124" t="str">
+      <c r="D126" t="str">
         <f t="shared" si="0"/>
         <v>氪金大佬碎片</v>
       </c>
-      <c r="E124">
-        <v>2</v>
-      </c>
-      <c r="F124" t="s">
-        <v>45</v>
-      </c>
-      <c r="G124">
+      <c r="E126">
+        <v>2</v>
+      </c>
+      <c r="F126" t="s">
+        <v>45</v>
+      </c>
+      <c r="G126">
         <v>7</v>
       </c>
-      <c r="H124" t="b">
-        <v>1</v>
-      </c>
-      <c r="I124">
-        <v>1</v>
-      </c>
-      <c r="J124" t="s">
-        <v>160</v>
-      </c>
-      <c r="K124">
+      <c r="H126" t="b">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>1</v>
+      </c>
+      <c r="J126" t="s">
+        <v>160</v>
+      </c>
+      <c r="K126">
         <v>2125503</v>
       </c>
-      <c r="L124" t="b">
-        <v>0</v>
-      </c>
-      <c r="M124" t="str">
+      <c r="L126" t="b">
+        <v>0</v>
+      </c>
+      <c r="M126" t="str">
         <f t="shared" si="1"/>
         <v>氪金大佬游客的升星道具</v>
       </c>
-      <c r="P124">
+      <c r="P126">
         <v>999</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
-      <c r="A125">
+    <row r="127" spans="1:16">
+      <c r="A127">
         <v>1125504</v>
       </c>
-      <c r="C125">
+      <c r="C127">
         <v>1125504</v>
       </c>
-      <c r="D125" t="str">
+      <c r="D127" t="str">
         <f t="shared" si="0"/>
         <v>穿搭博主碎片</v>
       </c>
-      <c r="E125">
-        <v>2</v>
-      </c>
-      <c r="F125" t="s">
-        <v>45</v>
-      </c>
-      <c r="G125">
+      <c r="E127">
+        <v>2</v>
+      </c>
+      <c r="F127" t="s">
+        <v>45</v>
+      </c>
+      <c r="G127">
         <v>7</v>
       </c>
-      <c r="H125" t="b">
-        <v>1</v>
-      </c>
-      <c r="I125">
-        <v>1</v>
-      </c>
-      <c r="J125" t="s">
-        <v>160</v>
-      </c>
-      <c r="K125">
+      <c r="H127" t="b">
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="J127" t="s">
+        <v>160</v>
+      </c>
+      <c r="K127">
         <v>2125504</v>
       </c>
-      <c r="L125" t="b">
-        <v>0</v>
-      </c>
-      <c r="M125" t="str">
+      <c r="L127" t="b">
+        <v>0</v>
+      </c>
+      <c r="M127" t="str">
         <f t="shared" si="1"/>
         <v>穿搭博主游客的升星道具</v>
       </c>
-      <c r="P125">
+      <c r="P127">
         <v>999</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
-      <c r="A126">
+    <row r="128" spans="1:16">
+      <c r="A128">
         <v>1125505</v>
       </c>
-      <c r="C126">
+      <c r="C128">
         <v>1125505</v>
       </c>
-      <c r="D126" t="str">
+      <c r="D128" t="str">
         <f t="shared" si="0"/>
         <v>美妆新秀碎片</v>
       </c>
-      <c r="E126">
-        <v>2</v>
-      </c>
-      <c r="F126" t="s">
-        <v>45</v>
-      </c>
-      <c r="G126">
+      <c r="E128">
+        <v>2</v>
+      </c>
+      <c r="F128" t="s">
+        <v>45</v>
+      </c>
+      <c r="G128">
         <v>7</v>
       </c>
-      <c r="H126" t="b">
-        <v>1</v>
-      </c>
-      <c r="I126">
-        <v>1</v>
-      </c>
-      <c r="J126" t="s">
-        <v>160</v>
-      </c>
-      <c r="K126">
+      <c r="H128" t="b">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="J128" t="s">
+        <v>160</v>
+      </c>
+      <c r="K128">
         <v>2125505</v>
       </c>
-      <c r="L126" t="b">
-        <v>0</v>
-      </c>
-      <c r="M126" t="str">
+      <c r="L128" t="b">
+        <v>0</v>
+      </c>
+      <c r="M128" t="str">
         <f t="shared" si="1"/>
         <v>美妆新秀游客的升星道具</v>
       </c>
-      <c r="P126">
+      <c r="P128">
         <v>999</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
-      <c r="A127">
+    <row r="129" spans="1:16">
+      <c r="A129">
         <v>1125506</v>
       </c>
-      <c r="C127">
+      <c r="C129">
         <v>1125506</v>
       </c>
-      <c r="D127" t="str">
+      <c r="D129" t="str">
         <f t="shared" si="0"/>
         <v>高定女王碎片</v>
       </c>
-      <c r="E127">
-        <v>2</v>
-      </c>
-      <c r="F127" t="s">
-        <v>45</v>
-      </c>
-      <c r="G127">
+      <c r="E129">
+        <v>2</v>
+      </c>
+      <c r="F129" t="s">
+        <v>45</v>
+      </c>
+      <c r="G129">
         <v>7</v>
       </c>
-      <c r="H127" t="b">
-        <v>1</v>
-      </c>
-      <c r="I127">
-        <v>1</v>
-      </c>
-      <c r="J127" t="s">
-        <v>160</v>
-      </c>
-      <c r="K127">
+      <c r="H129" t="b">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129" t="s">
+        <v>160</v>
+      </c>
+      <c r="K129">
         <v>2125506</v>
       </c>
-      <c r="L127" t="b">
-        <v>0</v>
-      </c>
-      <c r="M127" t="str">
+      <c r="L129" t="b">
+        <v>0</v>
+      </c>
+      <c r="M129" t="str">
         <f t="shared" si="1"/>
         <v>高定女王游客的升星道具</v>
       </c>
-      <c r="P127">
+      <c r="P129">
         <v>999</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16">
-      <c r="A128">
-        <v>1026001</v>
-      </c>
-      <c r="C128">
-        <v>1026001</v>
-      </c>
-      <c r="D128" t="s">
-        <v>206</v>
-      </c>
-      <c r="E128">
-        <v>2</v>
-      </c>
-      <c r="F128" t="s">
-        <v>45</v>
-      </c>
-      <c r="G128">
-        <v>1</v>
-      </c>
-      <c r="H128" t="b">
-        <v>1</v>
-      </c>
-      <c r="I128">
-        <v>1</v>
-      </c>
-      <c r="J128" t="s">
-        <v>160</v>
-      </c>
-      <c r="K128">
-        <v>2026001</v>
-      </c>
-      <c r="L128" t="b">
-        <v>0</v>
-      </c>
-      <c r="M128" t="s">
-        <v>206</v>
-      </c>
-      <c r="P128">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16">
-      <c r="A129">
-        <v>1026002</v>
-      </c>
-      <c r="C129">
-        <v>1026002</v>
-      </c>
-      <c r="D129" t="s">
-        <v>207</v>
-      </c>
-      <c r="E129">
-        <v>2</v>
-      </c>
-      <c r="F129" t="s">
-        <v>45</v>
-      </c>
-      <c r="G129">
-        <v>1</v>
-      </c>
-      <c r="H129" t="b">
-        <v>1</v>
-      </c>
-      <c r="I129">
-        <v>1</v>
-      </c>
-      <c r="J129" t="s">
-        <v>160</v>
-      </c>
-      <c r="K129">
-        <v>2026002</v>
-      </c>
-      <c r="L129" t="b">
-        <v>0</v>
-      </c>
-      <c r="M129" t="s">
-        <v>207</v>
-      </c>
-      <c r="P129">
-        <v>-1</v>
       </c>
     </row>
     <row r="130" spans="1:16">
       <c r="A130">
-        <v>1026101</v>
+        <v>1026001</v>
       </c>
       <c r="C130">
-        <v>1026101</v>
+        <v>1026001</v>
       </c>
       <c r="D130" t="s">
         <v>208</v>
@@ -7953,7 +7959,7 @@
         <v>45</v>
       </c>
       <c r="G130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H130" t="b">
         <v>1</v>
@@ -7965,7 +7971,7 @@
         <v>160</v>
       </c>
       <c r="K130">
-        <v>2026101</v>
+        <v>2026001</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -7979,10 +7985,10 @@
     </row>
     <row r="131" spans="1:16">
       <c r="A131">
-        <v>1026102</v>
+        <v>1026002</v>
       </c>
       <c r="C131">
-        <v>1026102</v>
+        <v>1026002</v>
       </c>
       <c r="D131" t="s">
         <v>209</v>
@@ -7994,7 +8000,7 @@
         <v>45</v>
       </c>
       <c r="G131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" t="b">
         <v>1</v>
@@ -8006,7 +8012,7 @@
         <v>160</v>
       </c>
       <c r="K131">
-        <v>2026102</v>
+        <v>2026002</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -8020,10 +8026,10 @@
     </row>
     <row r="132" spans="1:16">
       <c r="A132">
-        <v>1026201</v>
+        <v>1026101</v>
       </c>
       <c r="C132">
-        <v>1026201</v>
+        <v>1026101</v>
       </c>
       <c r="D132" t="s">
         <v>210</v>
@@ -8035,7 +8041,7 @@
         <v>45</v>
       </c>
       <c r="G132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H132" t="b">
         <v>1</v>
@@ -8047,7 +8053,7 @@
         <v>160</v>
       </c>
       <c r="K132">
-        <v>2026201</v>
+        <v>2026101</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -8061,10 +8067,10 @@
     </row>
     <row r="133" spans="1:16">
       <c r="A133">
-        <v>1026202</v>
+        <v>1026102</v>
       </c>
       <c r="C133">
-        <v>1026202</v>
+        <v>1026102</v>
       </c>
       <c r="D133" t="s">
         <v>211</v>
@@ -8076,7 +8082,7 @@
         <v>45</v>
       </c>
       <c r="G133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H133" t="b">
         <v>1</v>
@@ -8088,7 +8094,7 @@
         <v>160</v>
       </c>
       <c r="K133">
-        <v>2026202</v>
+        <v>2026102</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
@@ -8102,10 +8108,10 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134">
-        <v>1026301</v>
+        <v>1026201</v>
       </c>
       <c r="C134">
-        <v>1026301</v>
+        <v>1026201</v>
       </c>
       <c r="D134" t="s">
         <v>212</v>
@@ -8117,7 +8123,7 @@
         <v>45</v>
       </c>
       <c r="G134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H134" t="b">
         <v>1</v>
@@ -8129,7 +8135,7 @@
         <v>160</v>
       </c>
       <c r="K134">
-        <v>2026301</v>
+        <v>2026201</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -8143,10 +8149,10 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135">
-        <v>1026302</v>
+        <v>1026202</v>
       </c>
       <c r="C135">
-        <v>1026302</v>
+        <v>1026202</v>
       </c>
       <c r="D135" t="s">
         <v>213</v>
@@ -8158,7 +8164,7 @@
         <v>45</v>
       </c>
       <c r="G135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H135" t="b">
         <v>1</v>
@@ -8170,7 +8176,7 @@
         <v>160</v>
       </c>
       <c r="K135">
-        <v>2026302</v>
+        <v>2026202</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
@@ -8184,10 +8190,10 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136">
-        <v>1026401</v>
+        <v>1026301</v>
       </c>
       <c r="C136">
-        <v>1026401</v>
+        <v>1026301</v>
       </c>
       <c r="D136" t="s">
         <v>214</v>
@@ -8199,7 +8205,7 @@
         <v>45</v>
       </c>
       <c r="G136">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H136" t="b">
         <v>1</v>
@@ -8211,7 +8217,7 @@
         <v>160</v>
       </c>
       <c r="K136">
-        <v>2026401</v>
+        <v>2026301</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -8225,10 +8231,10 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137">
-        <v>1026402</v>
+        <v>1026302</v>
       </c>
       <c r="C137">
-        <v>1026402</v>
+        <v>1026302</v>
       </c>
       <c r="D137" t="s">
         <v>215</v>
@@ -8240,7 +8246,7 @@
         <v>45</v>
       </c>
       <c r="G137">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H137" t="b">
         <v>1</v>
@@ -8252,7 +8258,7 @@
         <v>160</v>
       </c>
       <c r="K137">
-        <v>2026402</v>
+        <v>2026302</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
@@ -8266,10 +8272,10 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138">
-        <v>1027001</v>
+        <v>1026401</v>
       </c>
       <c r="C138">
-        <v>1027001</v>
+        <v>1026401</v>
       </c>
       <c r="D138" t="s">
         <v>216</v>
@@ -8281,7 +8287,7 @@
         <v>45</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H138" t="b">
         <v>1</v>
@@ -8293,7 +8299,7 @@
         <v>160</v>
       </c>
       <c r="K138">
-        <v>2027001</v>
+        <v>2026401</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -8307,10 +8313,10 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139">
-        <v>1027002</v>
+        <v>1026402</v>
       </c>
       <c r="C139">
-        <v>1027002</v>
+        <v>1026402</v>
       </c>
       <c r="D139" t="s">
         <v>217</v>
@@ -8322,7 +8328,7 @@
         <v>45</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H139" t="b">
         <v>1</v>
@@ -8334,7 +8340,7 @@
         <v>160</v>
       </c>
       <c r="K139">
-        <v>2027002</v>
+        <v>2026402</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -8348,10 +8354,10 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140">
-        <v>1027101</v>
+        <v>1027001</v>
       </c>
       <c r="C140">
-        <v>1027101</v>
+        <v>1027001</v>
       </c>
       <c r="D140" t="s">
         <v>218</v>
@@ -8363,7 +8369,7 @@
         <v>45</v>
       </c>
       <c r="G140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H140" t="b">
         <v>1</v>
@@ -8375,7 +8381,7 @@
         <v>160</v>
       </c>
       <c r="K140">
-        <v>2027101</v>
+        <v>2027001</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -8389,10 +8395,10 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141">
-        <v>1027102</v>
+        <v>1027002</v>
       </c>
       <c r="C141">
-        <v>1027102</v>
+        <v>1027002</v>
       </c>
       <c r="D141" t="s">
         <v>219</v>
@@ -8404,7 +8410,7 @@
         <v>45</v>
       </c>
       <c r="G141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H141" t="b">
         <v>1</v>
@@ -8416,7 +8422,7 @@
         <v>160</v>
       </c>
       <c r="K141">
-        <v>2027102</v>
+        <v>2027002</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
@@ -8430,10 +8436,10 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142">
-        <v>1027201</v>
+        <v>1027101</v>
       </c>
       <c r="C142">
-        <v>1027201</v>
+        <v>1027101</v>
       </c>
       <c r="D142" t="s">
         <v>220</v>
@@ -8445,7 +8451,7 @@
         <v>45</v>
       </c>
       <c r="G142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H142" t="b">
         <v>1</v>
@@ -8457,7 +8463,7 @@
         <v>160</v>
       </c>
       <c r="K142">
-        <v>2027201</v>
+        <v>2027101</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
@@ -8471,10 +8477,10 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143">
-        <v>1027202</v>
+        <v>1027102</v>
       </c>
       <c r="C143">
-        <v>1027202</v>
+        <v>1027102</v>
       </c>
       <c r="D143" t="s">
         <v>221</v>
@@ -8486,7 +8492,7 @@
         <v>45</v>
       </c>
       <c r="G143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H143" t="b">
         <v>1</v>
@@ -8498,7 +8504,7 @@
         <v>160</v>
       </c>
       <c r="K143">
-        <v>2027202</v>
+        <v>2027102</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
@@ -8512,10 +8518,10 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144">
-        <v>1027301</v>
+        <v>1027201</v>
       </c>
       <c r="C144">
-        <v>1027301</v>
+        <v>1027201</v>
       </c>
       <c r="D144" t="s">
         <v>222</v>
@@ -8527,7 +8533,7 @@
         <v>45</v>
       </c>
       <c r="G144">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H144" t="b">
         <v>1</v>
@@ -8539,7 +8545,7 @@
         <v>160</v>
       </c>
       <c r="K144">
-        <v>2027301</v>
+        <v>2027201</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -8553,10 +8559,10 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145">
-        <v>1027302</v>
+        <v>1027202</v>
       </c>
       <c r="C145">
-        <v>1027302</v>
+        <v>1027202</v>
       </c>
       <c r="D145" t="s">
         <v>223</v>
@@ -8568,7 +8574,7 @@
         <v>45</v>
       </c>
       <c r="G145">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H145" t="b">
         <v>1</v>
@@ -8580,7 +8586,7 @@
         <v>160</v>
       </c>
       <c r="K145">
-        <v>2027302</v>
+        <v>2027202</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -8594,10 +8600,10 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146">
-        <v>1027401</v>
+        <v>1027301</v>
       </c>
       <c r="C146">
-        <v>1027401</v>
+        <v>1027301</v>
       </c>
       <c r="D146" t="s">
         <v>224</v>
@@ -8609,7 +8615,7 @@
         <v>45</v>
       </c>
       <c r="G146">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H146" t="b">
         <v>1</v>
@@ -8621,7 +8627,7 @@
         <v>160</v>
       </c>
       <c r="K146">
-        <v>2027401</v>
+        <v>2027301</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -8635,10 +8641,10 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147">
-        <v>1027402</v>
+        <v>1027302</v>
       </c>
       <c r="C147">
-        <v>1027402</v>
+        <v>1027302</v>
       </c>
       <c r="D147" t="s">
         <v>225</v>
@@ -8650,7 +8656,7 @@
         <v>45</v>
       </c>
       <c r="G147">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H147" t="b">
         <v>1</v>
@@ -8662,7 +8668,7 @@
         <v>160</v>
       </c>
       <c r="K147">
-        <v>2027402</v>
+        <v>2027302</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -8676,10 +8682,10 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148">
-        <v>1028001</v>
+        <v>1027401</v>
       </c>
       <c r="C148">
-        <v>1028001</v>
+        <v>1027401</v>
       </c>
       <c r="D148" t="s">
         <v>226</v>
@@ -8691,7 +8697,7 @@
         <v>45</v>
       </c>
       <c r="G148">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H148" t="b">
         <v>1</v>
@@ -8703,7 +8709,7 @@
         <v>160</v>
       </c>
       <c r="K148">
-        <v>2028001</v>
+        <v>2027401</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -8717,10 +8723,10 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149">
-        <v>1028002</v>
+        <v>1027402</v>
       </c>
       <c r="C149">
-        <v>1028002</v>
+        <v>1027402</v>
       </c>
       <c r="D149" t="s">
         <v>227</v>
@@ -8732,7 +8738,7 @@
         <v>45</v>
       </c>
       <c r="G149">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H149" t="b">
         <v>1</v>
@@ -8744,7 +8750,7 @@
         <v>160</v>
       </c>
       <c r="K149">
-        <v>2028002</v>
+        <v>2027402</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
@@ -8758,10 +8764,10 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150">
-        <v>1028101</v>
+        <v>1028001</v>
       </c>
       <c r="C150">
-        <v>1028101</v>
+        <v>1028001</v>
       </c>
       <c r="D150" t="s">
         <v>228</v>
@@ -8773,7 +8779,7 @@
         <v>45</v>
       </c>
       <c r="G150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H150" t="b">
         <v>1</v>
@@ -8785,7 +8791,7 @@
         <v>160</v>
       </c>
       <c r="K150">
-        <v>2028101</v>
+        <v>2028001</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -8799,10 +8805,10 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151">
-        <v>1028102</v>
+        <v>1028002</v>
       </c>
       <c r="C151">
-        <v>1028102</v>
+        <v>1028002</v>
       </c>
       <c r="D151" t="s">
         <v>229</v>
@@ -8814,7 +8820,7 @@
         <v>45</v>
       </c>
       <c r="G151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151" t="b">
         <v>1</v>
@@ -8826,7 +8832,7 @@
         <v>160</v>
       </c>
       <c r="K151">
-        <v>2028102</v>
+        <v>2028002</v>
       </c>
       <c r="L151" t="b">
         <v>0</v>
@@ -8840,10 +8846,10 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152">
-        <v>1028201</v>
+        <v>1028101</v>
       </c>
       <c r="C152">
-        <v>1028201</v>
+        <v>1028101</v>
       </c>
       <c r="D152" t="s">
         <v>230</v>
@@ -8855,7 +8861,7 @@
         <v>45</v>
       </c>
       <c r="G152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H152" t="b">
         <v>1</v>
@@ -8867,7 +8873,7 @@
         <v>160</v>
       </c>
       <c r="K152">
-        <v>2028201</v>
+        <v>2028101</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -8881,10 +8887,10 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153">
-        <v>1028202</v>
+        <v>1028102</v>
       </c>
       <c r="C153">
-        <v>1028202</v>
+        <v>1028102</v>
       </c>
       <c r="D153" t="s">
         <v>231</v>
@@ -8896,7 +8902,7 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H153" t="b">
         <v>1</v>
@@ -8908,7 +8914,7 @@
         <v>160</v>
       </c>
       <c r="K153">
-        <v>2028202</v>
+        <v>2028102</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -8922,10 +8928,10 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154">
-        <v>1028301</v>
+        <v>1028201</v>
       </c>
       <c r="C154">
-        <v>1028301</v>
+        <v>1028201</v>
       </c>
       <c r="D154" t="s">
         <v>232</v>
@@ -8937,7 +8943,7 @@
         <v>45</v>
       </c>
       <c r="G154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H154" t="b">
         <v>1</v>
@@ -8949,7 +8955,7 @@
         <v>160</v>
       </c>
       <c r="K154">
-        <v>2028301</v>
+        <v>2028201</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -8963,10 +8969,10 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155">
-        <v>1028302</v>
+        <v>1028202</v>
       </c>
       <c r="C155">
-        <v>1028302</v>
+        <v>1028202</v>
       </c>
       <c r="D155" t="s">
         <v>233</v>
@@ -8978,7 +8984,7 @@
         <v>45</v>
       </c>
       <c r="G155">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H155" t="b">
         <v>1</v>
@@ -8990,7 +8996,7 @@
         <v>160</v>
       </c>
       <c r="K155">
-        <v>2028302</v>
+        <v>2028202</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
@@ -9004,10 +9010,10 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156">
-        <v>1028401</v>
+        <v>1028301</v>
       </c>
       <c r="C156">
-        <v>1028401</v>
+        <v>1028301</v>
       </c>
       <c r="D156" t="s">
         <v>234</v>
@@ -9019,7 +9025,7 @@
         <v>45</v>
       </c>
       <c r="G156">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H156" t="b">
         <v>1</v>
@@ -9031,7 +9037,7 @@
         <v>160</v>
       </c>
       <c r="K156">
-        <v>2028401</v>
+        <v>2028301</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -9045,10 +9051,10 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157">
-        <v>1028402</v>
+        <v>1028302</v>
       </c>
       <c r="C157">
-        <v>1028402</v>
+        <v>1028302</v>
       </c>
       <c r="D157" t="s">
         <v>235</v>
@@ -9060,7 +9066,7 @@
         <v>45</v>
       </c>
       <c r="G157">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H157" t="b">
         <v>1</v>
@@ -9072,7 +9078,7 @@
         <v>160</v>
       </c>
       <c r="K157">
-        <v>2028402</v>
+        <v>2028302</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -9086,14 +9092,13 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158">
-        <v>1126001</v>
+        <v>1028401</v>
       </c>
       <c r="C158">
-        <v>1126001</v>
-      </c>
-      <c r="D158" t="str">
-        <f>D128&amp;"碎片"</f>
-        <v>威廉碎片</v>
+        <v>1028401</v>
+      </c>
+      <c r="D158" t="s">
+        <v>236</v>
       </c>
       <c r="E158">
         <v>2</v>
@@ -9102,7 +9107,7 @@
         <v>45</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H158" t="b">
         <v>1</v>
@@ -9114,29 +9119,27 @@
         <v>160</v>
       </c>
       <c r="K158">
-        <v>2126001</v>
+        <v>2028401</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
       </c>
-      <c r="M158" t="str">
-        <f>D128&amp;"雇员的升星道具"</f>
-        <v>威廉雇员的升星道具</v>
+      <c r="M158" t="s">
+        <v>236</v>
       </c>
       <c r="P158">
-        <v>999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="159" spans="1:16">
       <c r="A159">
-        <v>1126002</v>
+        <v>1028402</v>
       </c>
       <c r="C159">
-        <v>1126002</v>
-      </c>
-      <c r="D159" t="str">
-        <f t="shared" ref="D159:D187" si="2">D129&amp;"碎片"</f>
-        <v>艾拉碎片</v>
+        <v>1028402</v>
+      </c>
+      <c r="D159" t="s">
+        <v>237</v>
       </c>
       <c r="E159">
         <v>2</v>
@@ -9145,7 +9148,7 @@
         <v>45</v>
       </c>
       <c r="G159">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H159" t="b">
         <v>1</v>
@@ -9157,1314 +9160,1317 @@
         <v>160</v>
       </c>
       <c r="K159">
-        <v>2126002</v>
+        <v>2028402</v>
       </c>
       <c r="L159" t="b">
         <v>0</v>
       </c>
-      <c r="M159" t="str">
-        <f t="shared" ref="M159:M187" si="3">D129&amp;"雇员的升星道具"</f>
-        <v>艾拉雇员的升星道具</v>
+      <c r="M159" t="s">
+        <v>237</v>
       </c>
       <c r="P159">
-        <v>999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="160" spans="1:16">
       <c r="A160">
+        <v>1126001</v>
+      </c>
+      <c r="C160">
+        <v>1126001</v>
+      </c>
+      <c r="D160" t="str">
+        <f>D130&amp;"碎片"</f>
+        <v>威廉碎片</v>
+      </c>
+      <c r="E160">
+        <v>2</v>
+      </c>
+      <c r="F160" t="s">
+        <v>45</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+      <c r="H160" t="b">
+        <v>1</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+      <c r="J160" t="s">
+        <v>160</v>
+      </c>
+      <c r="K160">
+        <v>2126001</v>
+      </c>
+      <c r="L160" t="b">
+        <v>0</v>
+      </c>
+      <c r="M160" t="str">
+        <f>D130&amp;"雇员的升星道具"</f>
+        <v>威廉雇员的升星道具</v>
+      </c>
+      <c r="P160">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16">
+      <c r="A161">
+        <v>1126002</v>
+      </c>
+      <c r="C161">
+        <v>1126002</v>
+      </c>
+      <c r="D161" t="str">
+        <f t="shared" ref="D161:D189" si="2">D131&amp;"碎片"</f>
+        <v>艾拉碎片</v>
+      </c>
+      <c r="E161">
+        <v>2</v>
+      </c>
+      <c r="F161" t="s">
+        <v>45</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161" t="b">
+        <v>1</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+      <c r="J161" t="s">
+        <v>160</v>
+      </c>
+      <c r="K161">
+        <v>2126002</v>
+      </c>
+      <c r="L161" t="b">
+        <v>0</v>
+      </c>
+      <c r="M161" t="str">
+        <f t="shared" ref="M161:M189" si="3">D131&amp;"雇员的升星道具"</f>
+        <v>艾拉雇员的升星道具</v>
+      </c>
+      <c r="P161">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16">
+      <c r="A162">
         <v>1126101</v>
       </c>
-      <c r="C160">
+      <c r="C162">
         <v>1126101</v>
       </c>
-      <c r="D160" t="str">
+      <c r="D162" t="str">
         <f t="shared" si="2"/>
         <v>亨利碎片</v>
       </c>
-      <c r="E160">
-        <v>2</v>
-      </c>
-      <c r="F160" t="s">
-        <v>45</v>
-      </c>
-      <c r="G160">
-        <v>2</v>
-      </c>
-      <c r="H160" t="b">
-        <v>1</v>
-      </c>
-      <c r="I160">
-        <v>1</v>
-      </c>
-      <c r="J160" t="s">
-        <v>160</v>
-      </c>
-      <c r="K160">
+      <c r="E162">
+        <v>2</v>
+      </c>
+      <c r="F162" t="s">
+        <v>45</v>
+      </c>
+      <c r="G162">
+        <v>2</v>
+      </c>
+      <c r="H162" t="b">
+        <v>1</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162" t="s">
+        <v>160</v>
+      </c>
+      <c r="K162">
         <v>2126101</v>
       </c>
-      <c r="L160" t="b">
-        <v>0</v>
-      </c>
-      <c r="M160" t="str">
+      <c r="L162" t="b">
+        <v>0</v>
+      </c>
+      <c r="M162" t="str">
         <f t="shared" si="3"/>
         <v>亨利雇员的升星道具</v>
       </c>
-      <c r="P160">
+      <c r="P162">
         <v>999</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
-      <c r="A161">
+    <row r="163" spans="1:16">
+      <c r="A163">
         <v>1126102</v>
       </c>
-      <c r="C161">
+      <c r="C163">
         <v>1126102</v>
       </c>
-      <c r="D161" t="str">
+      <c r="D163" t="str">
         <f t="shared" si="2"/>
         <v>艾玛碎片</v>
       </c>
-      <c r="E161">
-        <v>2</v>
-      </c>
-      <c r="F161" t="s">
-        <v>45</v>
-      </c>
-      <c r="G161">
-        <v>2</v>
-      </c>
-      <c r="H161" t="b">
-        <v>1</v>
-      </c>
-      <c r="I161">
-        <v>1</v>
-      </c>
-      <c r="J161" t="s">
-        <v>160</v>
-      </c>
-      <c r="K161">
+      <c r="E163">
+        <v>2</v>
+      </c>
+      <c r="F163" t="s">
+        <v>45</v>
+      </c>
+      <c r="G163">
+        <v>2</v>
+      </c>
+      <c r="H163" t="b">
+        <v>1</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163" t="s">
+        <v>160</v>
+      </c>
+      <c r="K163">
         <v>2126102</v>
       </c>
-      <c r="L161" t="b">
-        <v>0</v>
-      </c>
-      <c r="M161" t="str">
+      <c r="L163" t="b">
+        <v>0</v>
+      </c>
+      <c r="M163" t="str">
         <f t="shared" si="3"/>
         <v>艾玛雇员的升星道具</v>
       </c>
-      <c r="P161">
+      <c r="P163">
         <v>999</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
-      <c r="A162">
+    <row r="164" spans="1:16">
+      <c r="A164">
         <v>1126201</v>
       </c>
-      <c r="C162">
+      <c r="C164">
         <v>1126201</v>
       </c>
-      <c r="D162" t="str">
+      <c r="D164" t="str">
         <f t="shared" si="2"/>
         <v>乔治碎片</v>
       </c>
-      <c r="E162">
-        <v>2</v>
-      </c>
-      <c r="F162" t="s">
-        <v>45</v>
-      </c>
-      <c r="G162">
+      <c r="E164">
+        <v>2</v>
+      </c>
+      <c r="F164" t="s">
+        <v>45</v>
+      </c>
+      <c r="G164">
         <v>3</v>
       </c>
-      <c r="H162" t="b">
-        <v>1</v>
-      </c>
-      <c r="I162">
-        <v>1</v>
-      </c>
-      <c r="J162" t="s">
-        <v>160</v>
-      </c>
-      <c r="K162">
+      <c r="H164" t="b">
+        <v>1</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164" t="s">
+        <v>160</v>
+      </c>
+      <c r="K164">
         <v>2126201</v>
       </c>
-      <c r="L162" t="b">
-        <v>0</v>
-      </c>
-      <c r="M162" t="str">
+      <c r="L164" t="b">
+        <v>0</v>
+      </c>
+      <c r="M164" t="str">
         <f t="shared" si="3"/>
         <v>乔治雇员的升星道具</v>
       </c>
-      <c r="P162">
+      <c r="P164">
         <v>999</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
-      <c r="A163">
+    <row r="165" spans="1:16">
+      <c r="A165">
         <v>1126202</v>
       </c>
-      <c r="C163">
+      <c r="C165">
         <v>1126202</v>
       </c>
-      <c r="D163" t="str">
+      <c r="D165" t="str">
         <f t="shared" si="2"/>
         <v>艾娃碎片</v>
       </c>
-      <c r="E163">
-        <v>2</v>
-      </c>
-      <c r="F163" t="s">
-        <v>45</v>
-      </c>
-      <c r="G163">
+      <c r="E165">
+        <v>2</v>
+      </c>
+      <c r="F165" t="s">
+        <v>45</v>
+      </c>
+      <c r="G165">
         <v>3</v>
       </c>
-      <c r="H163" t="b">
-        <v>1</v>
-      </c>
-      <c r="I163">
-        <v>1</v>
-      </c>
-      <c r="J163" t="s">
-        <v>160</v>
-      </c>
-      <c r="K163">
+      <c r="H165" t="b">
+        <v>1</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="J165" t="s">
+        <v>160</v>
+      </c>
+      <c r="K165">
         <v>2126202</v>
       </c>
-      <c r="L163" t="b">
-        <v>0</v>
-      </c>
-      <c r="M163" t="str">
+      <c r="L165" t="b">
+        <v>0</v>
+      </c>
+      <c r="M165" t="str">
         <f t="shared" si="3"/>
         <v>艾娃雇员的升星道具</v>
       </c>
-      <c r="P163">
+      <c r="P165">
         <v>999</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
-      <c r="A164">
+    <row r="166" spans="1:16">
+      <c r="A166">
         <v>1126301</v>
       </c>
-      <c r="C164">
+      <c r="C166">
         <v>1126301</v>
       </c>
-      <c r="D164" t="str">
+      <c r="D166" t="str">
         <f t="shared" si="2"/>
         <v>亚瑟碎片</v>
       </c>
-      <c r="E164">
-        <v>2</v>
-      </c>
-      <c r="F164" t="s">
-        <v>45</v>
-      </c>
-      <c r="G164">
+      <c r="E166">
+        <v>2</v>
+      </c>
+      <c r="F166" t="s">
+        <v>45</v>
+      </c>
+      <c r="G166">
         <v>4</v>
       </c>
-      <c r="H164" t="b">
-        <v>1</v>
-      </c>
-      <c r="I164">
-        <v>1</v>
-      </c>
-      <c r="J164" t="s">
-        <v>160</v>
-      </c>
-      <c r="K164">
+      <c r="H166" t="b">
+        <v>1</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166" t="s">
+        <v>160</v>
+      </c>
+      <c r="K166">
         <v>2126301</v>
       </c>
-      <c r="L164" t="b">
-        <v>0</v>
-      </c>
-      <c r="M164" t="str">
+      <c r="L166" t="b">
+        <v>0</v>
+      </c>
+      <c r="M166" t="str">
         <f t="shared" si="3"/>
         <v>亚瑟雇员的升星道具</v>
       </c>
-      <c r="P164">
+      <c r="P166">
         <v>999</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
-      <c r="A165">
+    <row r="167" spans="1:16">
+      <c r="A167">
         <v>1126302</v>
       </c>
-      <c r="C165">
+      <c r="C167">
         <v>1126302</v>
       </c>
-      <c r="D165" t="str">
+      <c r="D167" t="str">
         <f t="shared" si="2"/>
         <v>安娜碎片</v>
       </c>
-      <c r="E165">
-        <v>2</v>
-      </c>
-      <c r="F165" t="s">
-        <v>45</v>
-      </c>
-      <c r="G165">
+      <c r="E167">
+        <v>2</v>
+      </c>
+      <c r="F167" t="s">
+        <v>45</v>
+      </c>
+      <c r="G167">
         <v>4</v>
       </c>
-      <c r="H165" t="b">
-        <v>1</v>
-      </c>
-      <c r="I165">
-        <v>1</v>
-      </c>
-      <c r="J165" t="s">
-        <v>160</v>
-      </c>
-      <c r="K165">
+      <c r="H167" t="b">
+        <v>1</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167" t="s">
+        <v>160</v>
+      </c>
+      <c r="K167">
         <v>2126302</v>
       </c>
-      <c r="L165" t="b">
-        <v>0</v>
-      </c>
-      <c r="M165" t="str">
+      <c r="L167" t="b">
+        <v>0</v>
+      </c>
+      <c r="M167" t="str">
         <f t="shared" si="3"/>
         <v>安娜雇员的升星道具</v>
       </c>
-      <c r="P165">
+      <c r="P167">
         <v>999</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
-      <c r="A166">
+    <row r="168" spans="1:16">
+      <c r="A168">
         <v>1126401</v>
       </c>
-      <c r="C166">
+      <c r="C168">
         <v>1126401</v>
       </c>
-      <c r="D166" t="str">
+      <c r="D168" t="str">
         <f t="shared" si="2"/>
         <v>马修碎片</v>
       </c>
-      <c r="E166">
-        <v>2</v>
-      </c>
-      <c r="F166" t="s">
-        <v>45</v>
-      </c>
-      <c r="G166">
+      <c r="E168">
+        <v>2</v>
+      </c>
+      <c r="F168" t="s">
+        <v>45</v>
+      </c>
+      <c r="G168">
         <v>7</v>
       </c>
-      <c r="H166" t="b">
-        <v>1</v>
-      </c>
-      <c r="I166">
-        <v>1</v>
-      </c>
-      <c r="J166" t="s">
-        <v>160</v>
-      </c>
-      <c r="K166">
+      <c r="H168" t="b">
+        <v>1</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168" t="s">
+        <v>160</v>
+      </c>
+      <c r="K168">
         <v>2126401</v>
       </c>
-      <c r="L166" t="b">
-        <v>0</v>
-      </c>
-      <c r="M166" t="str">
+      <c r="L168" t="b">
+        <v>0</v>
+      </c>
+      <c r="M168" t="str">
         <f t="shared" si="3"/>
         <v>马修雇员的升星道具</v>
       </c>
-      <c r="P166">
+      <c r="P168">
         <v>999</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
-      <c r="A167">
+    <row r="169" spans="1:16">
+      <c r="A169">
         <v>1126402</v>
       </c>
-      <c r="C167">
+      <c r="C169">
         <v>1126402</v>
       </c>
-      <c r="D167" t="str">
+      <c r="D169" t="str">
         <f t="shared" si="2"/>
         <v>哈珀碎片</v>
       </c>
-      <c r="E167">
-        <v>2</v>
-      </c>
-      <c r="F167" t="s">
-        <v>45</v>
-      </c>
-      <c r="G167">
+      <c r="E169">
+        <v>2</v>
+      </c>
+      <c r="F169" t="s">
+        <v>45</v>
+      </c>
+      <c r="G169">
         <v>7</v>
       </c>
-      <c r="H167" t="b">
-        <v>1</v>
-      </c>
-      <c r="I167">
-        <v>1</v>
-      </c>
-      <c r="J167" t="s">
-        <v>160</v>
-      </c>
-      <c r="K167">
+      <c r="H169" t="b">
+        <v>1</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169" t="s">
+        <v>160</v>
+      </c>
+      <c r="K169">
         <v>2126402</v>
       </c>
-      <c r="L167" t="b">
-        <v>0</v>
-      </c>
-      <c r="M167" t="str">
+      <c r="L169" t="b">
+        <v>0</v>
+      </c>
+      <c r="M169" t="str">
         <f t="shared" si="3"/>
         <v>哈珀雇员的升星道具</v>
       </c>
-      <c r="P167">
+      <c r="P169">
         <v>999</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
-      <c r="A168">
+    <row r="170" spans="1:16">
+      <c r="A170">
         <v>1127001</v>
       </c>
-      <c r="C168">
+      <c r="C170">
         <v>1127001</v>
       </c>
-      <c r="D168" t="str">
+      <c r="D170" t="str">
         <f t="shared" si="2"/>
         <v>拉斐尔碎片</v>
       </c>
-      <c r="E168">
-        <v>2</v>
-      </c>
-      <c r="F168" t="s">
-        <v>45</v>
-      </c>
-      <c r="G168">
-        <v>1</v>
-      </c>
-      <c r="H168" t="b">
-        <v>1</v>
-      </c>
-      <c r="I168">
-        <v>1</v>
-      </c>
-      <c r="J168" t="s">
-        <v>160</v>
-      </c>
-      <c r="K168">
+      <c r="E170">
+        <v>2</v>
+      </c>
+      <c r="F170" t="s">
+        <v>45</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+      <c r="H170" t="b">
+        <v>1</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170" t="s">
+        <v>160</v>
+      </c>
+      <c r="K170">
         <v>2127001</v>
       </c>
-      <c r="L168" t="b">
-        <v>0</v>
-      </c>
-      <c r="M168" t="str">
+      <c r="L170" t="b">
+        <v>0</v>
+      </c>
+      <c r="M170" t="str">
         <f t="shared" si="3"/>
         <v>拉斐尔雇员的升星道具</v>
       </c>
-      <c r="P168">
+      <c r="P170">
         <v>999</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
-      <c r="A169">
+    <row r="171" spans="1:16">
+      <c r="A171">
         <v>1127002</v>
       </c>
-      <c r="C169">
+      <c r="C171">
         <v>1127002</v>
       </c>
-      <c r="D169" t="str">
+      <c r="D171" t="str">
         <f t="shared" si="2"/>
         <v>伊芙琳碎片</v>
       </c>
-      <c r="E169">
-        <v>2</v>
-      </c>
-      <c r="F169" t="s">
-        <v>45</v>
-      </c>
-      <c r="G169">
-        <v>1</v>
-      </c>
-      <c r="H169" t="b">
-        <v>1</v>
-      </c>
-      <c r="I169">
-        <v>1</v>
-      </c>
-      <c r="J169" t="s">
-        <v>160</v>
-      </c>
-      <c r="K169">
+      <c r="E171">
+        <v>2</v>
+      </c>
+      <c r="F171" t="s">
+        <v>45</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171" t="b">
+        <v>1</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171" t="s">
+        <v>160</v>
+      </c>
+      <c r="K171">
         <v>2127002</v>
       </c>
-      <c r="L169" t="b">
-        <v>0</v>
-      </c>
-      <c r="M169" t="str">
+      <c r="L171" t="b">
+        <v>0</v>
+      </c>
+      <c r="M171" t="str">
         <f t="shared" si="3"/>
         <v>伊芙琳雇员的升星道具</v>
       </c>
-      <c r="P169">
+      <c r="P171">
         <v>999</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
-      <c r="A170">
+    <row r="172" spans="1:16">
+      <c r="A172">
         <v>1127101</v>
       </c>
-      <c r="C170">
+      <c r="C172">
         <v>1127101</v>
       </c>
-      <c r="D170" t="str">
+      <c r="D172" t="str">
         <f t="shared" si="2"/>
         <v>埃米尔碎片</v>
       </c>
-      <c r="E170">
-        <v>2</v>
-      </c>
-      <c r="F170" t="s">
-        <v>45</v>
-      </c>
-      <c r="G170">
-        <v>2</v>
-      </c>
-      <c r="H170" t="b">
-        <v>1</v>
-      </c>
-      <c r="I170">
-        <v>1</v>
-      </c>
-      <c r="J170" t="s">
-        <v>160</v>
-      </c>
-      <c r="K170">
+      <c r="E172">
+        <v>2</v>
+      </c>
+      <c r="F172" t="s">
+        <v>45</v>
+      </c>
+      <c r="G172">
+        <v>2</v>
+      </c>
+      <c r="H172" t="b">
+        <v>1</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172" t="s">
+        <v>160</v>
+      </c>
+      <c r="K172">
         <v>2127101</v>
       </c>
-      <c r="L170" t="b">
-        <v>0</v>
-      </c>
-      <c r="M170" t="str">
+      <c r="L172" t="b">
+        <v>0</v>
+      </c>
+      <c r="M172" t="str">
         <f t="shared" si="3"/>
         <v>埃米尔雇员的升星道具</v>
       </c>
-      <c r="P170">
+      <c r="P172">
         <v>999</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
-      <c r="A171">
+    <row r="173" spans="1:16">
+      <c r="A173">
         <v>1127102</v>
       </c>
-      <c r="C171">
+      <c r="C173">
         <v>1127102</v>
       </c>
-      <c r="D171" t="str">
+      <c r="D173" t="str">
         <f t="shared" si="2"/>
         <v>夏洛特碎片</v>
       </c>
-      <c r="E171">
-        <v>2</v>
-      </c>
-      <c r="F171" t="s">
-        <v>45</v>
-      </c>
-      <c r="G171">
-        <v>2</v>
-      </c>
-      <c r="H171" t="b">
-        <v>1</v>
-      </c>
-      <c r="I171">
-        <v>1</v>
-      </c>
-      <c r="J171" t="s">
-        <v>160</v>
-      </c>
-      <c r="K171">
+      <c r="E173">
+        <v>2</v>
+      </c>
+      <c r="F173" t="s">
+        <v>45</v>
+      </c>
+      <c r="G173">
+        <v>2</v>
+      </c>
+      <c r="H173" t="b">
+        <v>1</v>
+      </c>
+      <c r="I173">
+        <v>1</v>
+      </c>
+      <c r="J173" t="s">
+        <v>160</v>
+      </c>
+      <c r="K173">
         <v>2127102</v>
       </c>
-      <c r="L171" t="b">
-        <v>0</v>
-      </c>
-      <c r="M171" t="str">
+      <c r="L173" t="b">
+        <v>0</v>
+      </c>
+      <c r="M173" t="str">
         <f t="shared" si="3"/>
         <v>夏洛特雇员的升星道具</v>
       </c>
-      <c r="P171">
+      <c r="P173">
         <v>999</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
-      <c r="A172">
+    <row r="174" spans="1:16">
+      <c r="A174">
         <v>1127201</v>
       </c>
-      <c r="C172">
+      <c r="C174">
         <v>1127201</v>
       </c>
-      <c r="D172" t="str">
+      <c r="D174" t="str">
         <f t="shared" si="2"/>
         <v>雷蒙德碎片</v>
       </c>
-      <c r="E172">
-        <v>2</v>
-      </c>
-      <c r="F172" t="s">
-        <v>45</v>
-      </c>
-      <c r="G172">
+      <c r="E174">
+        <v>2</v>
+      </c>
+      <c r="F174" t="s">
+        <v>45</v>
+      </c>
+      <c r="G174">
         <v>3</v>
       </c>
-      <c r="H172" t="b">
-        <v>1</v>
-      </c>
-      <c r="I172">
-        <v>1</v>
-      </c>
-      <c r="J172" t="s">
-        <v>160</v>
-      </c>
-      <c r="K172">
+      <c r="H174" t="b">
+        <v>1</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174" t="s">
+        <v>160</v>
+      </c>
+      <c r="K174">
         <v>2127201</v>
       </c>
-      <c r="L172" t="b">
-        <v>0</v>
-      </c>
-      <c r="M172" t="str">
+      <c r="L174" t="b">
+        <v>0</v>
+      </c>
+      <c r="M174" t="str">
         <f t="shared" si="3"/>
         <v>雷蒙德雇员的升星道具</v>
       </c>
-      <c r="P172">
+      <c r="P174">
         <v>999</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
-      <c r="A173">
+    <row r="175" spans="1:16">
+      <c r="A175">
         <v>1127202</v>
       </c>
-      <c r="C173">
+      <c r="C175">
         <v>1127202</v>
       </c>
-      <c r="D173" t="str">
+      <c r="D175" t="str">
         <f t="shared" si="2"/>
         <v>斯嘉丽碎片</v>
       </c>
-      <c r="E173">
-        <v>2</v>
-      </c>
-      <c r="F173" t="s">
-        <v>45</v>
-      </c>
-      <c r="G173">
+      <c r="E175">
+        <v>2</v>
+      </c>
+      <c r="F175" t="s">
+        <v>45</v>
+      </c>
+      <c r="G175">
         <v>3</v>
       </c>
-      <c r="H173" t="b">
-        <v>1</v>
-      </c>
-      <c r="I173">
-        <v>1</v>
-      </c>
-      <c r="J173" t="s">
-        <v>160</v>
-      </c>
-      <c r="K173">
+      <c r="H175" t="b">
+        <v>1</v>
+      </c>
+      <c r="I175">
+        <v>1</v>
+      </c>
+      <c r="J175" t="s">
+        <v>160</v>
+      </c>
+      <c r="K175">
         <v>2127202</v>
       </c>
-      <c r="L173" t="b">
-        <v>0</v>
-      </c>
-      <c r="M173" t="str">
+      <c r="L175" t="b">
+        <v>0</v>
+      </c>
+      <c r="M175" t="str">
         <f t="shared" si="3"/>
         <v>斯嘉丽雇员的升星道具</v>
       </c>
-      <c r="P173">
+      <c r="P175">
         <v>999</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
-      <c r="A174">
+    <row r="176" spans="1:16">
+      <c r="A176">
         <v>1127301</v>
       </c>
-      <c r="C174">
+      <c r="C176">
         <v>1127301</v>
       </c>
-      <c r="D174" t="str">
+      <c r="D176" t="str">
         <f t="shared" si="2"/>
         <v>丹尼尔碎片</v>
       </c>
-      <c r="E174">
-        <v>2</v>
-      </c>
-      <c r="F174" t="s">
-        <v>45</v>
-      </c>
-      <c r="G174">
+      <c r="E176">
+        <v>2</v>
+      </c>
+      <c r="F176" t="s">
+        <v>45</v>
+      </c>
+      <c r="G176">
         <v>4</v>
       </c>
-      <c r="H174" t="b">
-        <v>1</v>
-      </c>
-      <c r="I174">
-        <v>1</v>
-      </c>
-      <c r="J174" t="s">
-        <v>160</v>
-      </c>
-      <c r="K174">
+      <c r="H176" t="b">
+        <v>1</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176" t="s">
+        <v>160</v>
+      </c>
+      <c r="K176">
         <v>2127301</v>
       </c>
-      <c r="L174" t="b">
-        <v>0</v>
-      </c>
-      <c r="M174" t="str">
+      <c r="L176" t="b">
+        <v>0</v>
+      </c>
+      <c r="M176" t="str">
         <f t="shared" si="3"/>
         <v>丹尼尔雇员的升星道具</v>
       </c>
-      <c r="P174">
+      <c r="P176">
         <v>999</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
-      <c r="A175">
+    <row r="177" spans="1:16">
+      <c r="A177">
         <v>1127302</v>
       </c>
-      <c r="C175">
+      <c r="C177">
         <v>1127302</v>
       </c>
-      <c r="D175" t="str">
+      <c r="D177" t="str">
         <f t="shared" si="2"/>
         <v>莉莉安碎片</v>
       </c>
-      <c r="E175">
-        <v>2</v>
-      </c>
-      <c r="F175" t="s">
-        <v>45</v>
-      </c>
-      <c r="G175">
+      <c r="E177">
+        <v>2</v>
+      </c>
+      <c r="F177" t="s">
+        <v>45</v>
+      </c>
+      <c r="G177">
         <v>4</v>
       </c>
-      <c r="H175" t="b">
-        <v>1</v>
-      </c>
-      <c r="I175">
-        <v>1</v>
-      </c>
-      <c r="J175" t="s">
-        <v>160</v>
-      </c>
-      <c r="K175">
+      <c r="H177" t="b">
+        <v>1</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177" t="s">
+        <v>160</v>
+      </c>
+      <c r="K177">
         <v>2127302</v>
       </c>
-      <c r="L175" t="b">
-        <v>0</v>
-      </c>
-      <c r="M175" t="str">
+      <c r="L177" t="b">
+        <v>0</v>
+      </c>
+      <c r="M177" t="str">
         <f t="shared" si="3"/>
         <v>莉莉安雇员的升星道具</v>
       </c>
-      <c r="P175">
+      <c r="P177">
         <v>999</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
-      <c r="A176">
+    <row r="178" spans="1:16">
+      <c r="A178">
         <v>1127401</v>
       </c>
-      <c r="C176">
+      <c r="C178">
         <v>1127401</v>
       </c>
-      <c r="D176" t="str">
+      <c r="D178" t="str">
         <f t="shared" si="2"/>
         <v>卢卡斯碎片</v>
       </c>
-      <c r="E176">
-        <v>2</v>
-      </c>
-      <c r="F176" t="s">
-        <v>45</v>
-      </c>
-      <c r="G176">
+      <c r="E178">
+        <v>2</v>
+      </c>
+      <c r="F178" t="s">
+        <v>45</v>
+      </c>
+      <c r="G178">
         <v>7</v>
       </c>
-      <c r="H176" t="b">
-        <v>1</v>
-      </c>
-      <c r="I176">
-        <v>1</v>
-      </c>
-      <c r="J176" t="s">
-        <v>160</v>
-      </c>
-      <c r="K176">
+      <c r="H178" t="b">
+        <v>1</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178" t="s">
+        <v>160</v>
+      </c>
+      <c r="K178">
         <v>2127401</v>
       </c>
-      <c r="L176" t="b">
-        <v>0</v>
-      </c>
-      <c r="M176" t="str">
+      <c r="L178" t="b">
+        <v>0</v>
+      </c>
+      <c r="M178" t="str">
         <f t="shared" si="3"/>
         <v>卢卡斯雇员的升星道具</v>
       </c>
-      <c r="P176">
+      <c r="P178">
         <v>999</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
-      <c r="A177">
+    <row r="179" spans="1:16">
+      <c r="A179">
         <v>1127402</v>
       </c>
-      <c r="C177">
+      <c r="C179">
         <v>1127402</v>
       </c>
-      <c r="D177" t="str">
+      <c r="D179" t="str">
         <f t="shared" si="2"/>
         <v>克拉拉碎片</v>
       </c>
-      <c r="E177">
-        <v>2</v>
-      </c>
-      <c r="F177" t="s">
-        <v>45</v>
-      </c>
-      <c r="G177">
+      <c r="E179">
+        <v>2</v>
+      </c>
+      <c r="F179" t="s">
+        <v>45</v>
+      </c>
+      <c r="G179">
         <v>7</v>
       </c>
-      <c r="H177" t="b">
-        <v>1</v>
-      </c>
-      <c r="I177">
-        <v>1</v>
-      </c>
-      <c r="J177" t="s">
-        <v>160</v>
-      </c>
-      <c r="K177">
+      <c r="H179" t="b">
+        <v>1</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="J179" t="s">
+        <v>160</v>
+      </c>
+      <c r="K179">
         <v>2127402</v>
       </c>
-      <c r="L177" t="b">
-        <v>0</v>
-      </c>
-      <c r="M177" t="str">
+      <c r="L179" t="b">
+        <v>0</v>
+      </c>
+      <c r="M179" t="str">
         <f t="shared" si="3"/>
         <v>克拉拉雇员的升星道具</v>
       </c>
-      <c r="P177">
+      <c r="P179">
         <v>999</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
-      <c r="A178">
+    <row r="180" spans="1:16">
+      <c r="A180">
         <v>1128001</v>
       </c>
-      <c r="C178">
+      <c r="C180">
         <v>1128001</v>
       </c>
-      <c r="D178" t="str">
+      <c r="D180" t="str">
         <f t="shared" si="2"/>
         <v>尼古拉斯碎片</v>
       </c>
-      <c r="E178">
-        <v>2</v>
-      </c>
-      <c r="F178" t="s">
-        <v>45</v>
-      </c>
-      <c r="G178">
-        <v>1</v>
-      </c>
-      <c r="H178" t="b">
-        <v>1</v>
-      </c>
-      <c r="I178">
-        <v>1</v>
-      </c>
-      <c r="J178" t="s">
-        <v>160</v>
-      </c>
-      <c r="K178">
+      <c r="E180">
+        <v>2</v>
+      </c>
+      <c r="F180" t="s">
+        <v>45</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180" t="b">
+        <v>1</v>
+      </c>
+      <c r="I180">
+        <v>1</v>
+      </c>
+      <c r="J180" t="s">
+        <v>160</v>
+      </c>
+      <c r="K180">
         <v>2128001</v>
       </c>
-      <c r="L178" t="b">
-        <v>0</v>
-      </c>
-      <c r="M178" t="str">
+      <c r="L180" t="b">
+        <v>0</v>
+      </c>
+      <c r="M180" t="str">
         <f t="shared" si="3"/>
         <v>尼古拉斯雇员的升星道具</v>
       </c>
-      <c r="P178">
+      <c r="P180">
         <v>999</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
-      <c r="A179">
+    <row r="181" spans="1:16">
+      <c r="A181">
         <v>1128002</v>
       </c>
-      <c r="C179">
+      <c r="C181">
         <v>1128002</v>
       </c>
-      <c r="D179" t="str">
+      <c r="D181" t="str">
         <f t="shared" si="2"/>
         <v>奥利维亚碎片</v>
       </c>
-      <c r="E179">
-        <v>2</v>
-      </c>
-      <c r="F179" t="s">
-        <v>45</v>
-      </c>
-      <c r="G179">
-        <v>1</v>
-      </c>
-      <c r="H179" t="b">
-        <v>1</v>
-      </c>
-      <c r="I179">
-        <v>1</v>
-      </c>
-      <c r="J179" t="s">
-        <v>160</v>
-      </c>
-      <c r="K179">
+      <c r="E181">
+        <v>2</v>
+      </c>
+      <c r="F181" t="s">
+        <v>45</v>
+      </c>
+      <c r="G181">
+        <v>1</v>
+      </c>
+      <c r="H181" t="b">
+        <v>1</v>
+      </c>
+      <c r="I181">
+        <v>1</v>
+      </c>
+      <c r="J181" t="s">
+        <v>160</v>
+      </c>
+      <c r="K181">
         <v>2128002</v>
       </c>
-      <c r="L179" t="b">
-        <v>0</v>
-      </c>
-      <c r="M179" t="str">
+      <c r="L181" t="b">
+        <v>0</v>
+      </c>
+      <c r="M181" t="str">
         <f t="shared" si="3"/>
         <v>奥利维亚雇员的升星道具</v>
       </c>
-      <c r="P179">
+      <c r="P181">
         <v>999</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
-      <c r="A180">
+    <row r="182" spans="1:16">
+      <c r="A182">
         <v>1128101</v>
       </c>
-      <c r="C180">
+      <c r="C182">
         <v>1128101</v>
       </c>
-      <c r="D180" t="str">
+      <c r="D182" t="str">
         <f t="shared" si="2"/>
         <v>亚历山大碎片</v>
       </c>
-      <c r="E180">
-        <v>2</v>
-      </c>
-      <c r="F180" t="s">
-        <v>45</v>
-      </c>
-      <c r="G180">
-        <v>2</v>
-      </c>
-      <c r="H180" t="b">
-        <v>1</v>
-      </c>
-      <c r="I180">
-        <v>1</v>
-      </c>
-      <c r="J180" t="s">
-        <v>160</v>
-      </c>
-      <c r="K180">
+      <c r="E182">
+        <v>2</v>
+      </c>
+      <c r="F182" t="s">
+        <v>45</v>
+      </c>
+      <c r="G182">
+        <v>2</v>
+      </c>
+      <c r="H182" t="b">
+        <v>1</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182" t="s">
+        <v>160</v>
+      </c>
+      <c r="K182">
         <v>2128101</v>
       </c>
-      <c r="L180" t="b">
-        <v>0</v>
-      </c>
-      <c r="M180" t="str">
+      <c r="L182" t="b">
+        <v>0</v>
+      </c>
+      <c r="M182" t="str">
         <f t="shared" si="3"/>
         <v>亚历山大雇员的升星道具</v>
       </c>
-      <c r="P180">
+      <c r="P182">
         <v>999</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
-      <c r="A181">
+    <row r="183" spans="1:16">
+      <c r="A183">
         <v>1128102</v>
       </c>
-      <c r="C181">
+      <c r="C183">
         <v>1128102</v>
       </c>
-      <c r="D181" t="str">
+      <c r="D183" t="str">
         <f t="shared" si="2"/>
         <v>玛格丽特碎片</v>
       </c>
-      <c r="E181">
-        <v>2</v>
-      </c>
-      <c r="F181" t="s">
-        <v>45</v>
-      </c>
-      <c r="G181">
-        <v>2</v>
-      </c>
-      <c r="H181" t="b">
-        <v>1</v>
-      </c>
-      <c r="I181">
-        <v>1</v>
-      </c>
-      <c r="J181" t="s">
-        <v>160</v>
-      </c>
-      <c r="K181">
+      <c r="E183">
+        <v>2</v>
+      </c>
+      <c r="F183" t="s">
+        <v>45</v>
+      </c>
+      <c r="G183">
+        <v>2</v>
+      </c>
+      <c r="H183" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183" t="s">
+        <v>160</v>
+      </c>
+      <c r="K183">
         <v>2128102</v>
       </c>
-      <c r="L181" t="b">
-        <v>0</v>
-      </c>
-      <c r="M181" t="str">
+      <c r="L183" t="b">
+        <v>0</v>
+      </c>
+      <c r="M183" t="str">
         <f t="shared" si="3"/>
         <v>玛格丽特雇员的升星道具</v>
       </c>
-      <c r="P181">
+      <c r="P183">
         <v>999</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
-      <c r="A182">
+    <row r="184" spans="1:16">
+      <c r="A184">
         <v>1128201</v>
       </c>
-      <c r="C182">
+      <c r="C184">
         <v>1128201</v>
       </c>
-      <c r="D182" t="str">
+      <c r="D184" t="str">
         <f t="shared" si="2"/>
         <v>奥古斯特碎片</v>
       </c>
-      <c r="E182">
-        <v>2</v>
-      </c>
-      <c r="F182" t="s">
-        <v>45</v>
-      </c>
-      <c r="G182">
+      <c r="E184">
+        <v>2</v>
+      </c>
+      <c r="F184" t="s">
+        <v>45</v>
+      </c>
+      <c r="G184">
         <v>3</v>
       </c>
-      <c r="H182" t="b">
-        <v>1</v>
-      </c>
-      <c r="I182">
-        <v>1</v>
-      </c>
-      <c r="J182" t="s">
-        <v>160</v>
-      </c>
-      <c r="K182">
+      <c r="H184" t="b">
+        <v>1</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="J184" t="s">
+        <v>160</v>
+      </c>
+      <c r="K184">
         <v>2128201</v>
       </c>
-      <c r="L182" t="b">
-        <v>0</v>
-      </c>
-      <c r="M182" t="str">
+      <c r="L184" t="b">
+        <v>0</v>
+      </c>
+      <c r="M184" t="str">
         <f t="shared" si="3"/>
         <v>奥古斯特雇员的升星道具</v>
       </c>
-      <c r="P182">
+      <c r="P184">
         <v>999</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
-      <c r="A183">
+    <row r="185" spans="1:16">
+      <c r="A185">
         <v>1128202</v>
       </c>
-      <c r="C183">
+      <c r="C185">
         <v>1128202</v>
       </c>
-      <c r="D183" t="str">
+      <c r="D185" t="str">
         <f t="shared" si="2"/>
         <v>维奥莱特碎片</v>
       </c>
-      <c r="E183">
-        <v>2</v>
-      </c>
-      <c r="F183" t="s">
-        <v>45</v>
-      </c>
-      <c r="G183">
+      <c r="E185">
+        <v>2</v>
+      </c>
+      <c r="F185" t="s">
+        <v>45</v>
+      </c>
+      <c r="G185">
         <v>3</v>
       </c>
-      <c r="H183" t="b">
-        <v>1</v>
-      </c>
-      <c r="I183">
-        <v>1</v>
-      </c>
-      <c r="J183" t="s">
-        <v>160</v>
-      </c>
-      <c r="K183">
+      <c r="H185" t="b">
+        <v>1</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="J185" t="s">
+        <v>160</v>
+      </c>
+      <c r="K185">
         <v>2128202</v>
       </c>
-      <c r="L183" t="b">
-        <v>0</v>
-      </c>
-      <c r="M183" t="str">
+      <c r="L185" t="b">
+        <v>0</v>
+      </c>
+      <c r="M185" t="str">
         <f t="shared" si="3"/>
         <v>维奥莱特雇员的升星道具</v>
       </c>
-      <c r="P183">
+      <c r="P185">
         <v>999</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
-      <c r="A184">
+    <row r="186" spans="1:16">
+      <c r="A186">
         <v>1128301</v>
       </c>
-      <c r="C184">
+      <c r="C186">
         <v>1128301</v>
       </c>
-      <c r="D184" t="str">
+      <c r="D186" t="str">
         <f t="shared" si="2"/>
         <v>费利克斯碎片</v>
       </c>
-      <c r="E184">
-        <v>2</v>
-      </c>
-      <c r="F184" t="s">
-        <v>45</v>
-      </c>
-      <c r="G184">
+      <c r="E186">
+        <v>2</v>
+      </c>
+      <c r="F186" t="s">
+        <v>45</v>
+      </c>
+      <c r="G186">
         <v>4</v>
       </c>
-      <c r="H184" t="b">
-        <v>1</v>
-      </c>
-      <c r="I184">
-        <v>1</v>
-      </c>
-      <c r="J184" t="s">
-        <v>160</v>
-      </c>
-      <c r="K184">
+      <c r="H186" t="b">
+        <v>1</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186" t="s">
+        <v>160</v>
+      </c>
+      <c r="K186">
         <v>2128301</v>
       </c>
-      <c r="L184" t="b">
-        <v>0</v>
-      </c>
-      <c r="M184" t="str">
+      <c r="L186" t="b">
+        <v>0</v>
+      </c>
+      <c r="M186" t="str">
         <f t="shared" si="3"/>
         <v>费利克斯雇员的升星道具</v>
       </c>
-      <c r="P184">
+      <c r="P186">
         <v>999</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
-      <c r="A185">
+    <row r="187" spans="1:16">
+      <c r="A187">
         <v>1128302</v>
       </c>
-      <c r="C185">
+      <c r="C187">
         <v>1128302</v>
       </c>
-      <c r="D185" t="str">
+      <c r="D187" t="str">
         <f t="shared" si="2"/>
         <v>维多利亚碎片</v>
       </c>
-      <c r="E185">
-        <v>2</v>
-      </c>
-      <c r="F185" t="s">
-        <v>45</v>
-      </c>
-      <c r="G185">
+      <c r="E187">
+        <v>2</v>
+      </c>
+      <c r="F187" t="s">
+        <v>45</v>
+      </c>
+      <c r="G187">
         <v>4</v>
       </c>
-      <c r="H185" t="b">
-        <v>1</v>
-      </c>
-      <c r="I185">
-        <v>1</v>
-      </c>
-      <c r="J185" t="s">
-        <v>160</v>
-      </c>
-      <c r="K185">
+      <c r="H187" t="b">
+        <v>1</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="J187" t="s">
+        <v>160</v>
+      </c>
+      <c r="K187">
         <v>2128302</v>
       </c>
-      <c r="L185" t="b">
-        <v>0</v>
-      </c>
-      <c r="M185" t="str">
+      <c r="L187" t="b">
+        <v>0</v>
+      </c>
+      <c r="M187" t="str">
         <f t="shared" si="3"/>
         <v>维多利亚雇员的升星道具</v>
       </c>
-      <c r="P185">
+      <c r="P187">
         <v>999</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
-      <c r="A186">
+    <row r="188" spans="1:16">
+      <c r="A188">
         <v>1128401</v>
       </c>
-      <c r="C186">
+      <c r="C188">
         <v>1128401</v>
       </c>
-      <c r="D186" t="str">
+      <c r="D188" t="str">
         <f t="shared" si="2"/>
         <v>阿尔弗雷德碎片</v>
       </c>
-      <c r="E186">
-        <v>2</v>
-      </c>
-      <c r="F186" t="s">
-        <v>45</v>
-      </c>
-      <c r="G186">
+      <c r="E188">
+        <v>2</v>
+      </c>
+      <c r="F188" t="s">
+        <v>45</v>
+      </c>
+      <c r="G188">
         <v>7</v>
       </c>
-      <c r="H186" t="b">
-        <v>1</v>
-      </c>
-      <c r="I186">
-        <v>1</v>
-      </c>
-      <c r="J186" t="s">
-        <v>160</v>
-      </c>
-      <c r="K186">
+      <c r="H188" t="b">
+        <v>1</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="J188" t="s">
+        <v>160</v>
+      </c>
+      <c r="K188">
         <v>2128401</v>
       </c>
-      <c r="L186" t="b">
-        <v>0</v>
-      </c>
-      <c r="M186" t="str">
+      <c r="L188" t="b">
+        <v>0</v>
+      </c>
+      <c r="M188" t="str">
         <f t="shared" si="3"/>
         <v>阿尔弗雷德雇员的升星道具</v>
       </c>
-      <c r="P186">
+      <c r="P188">
         <v>999</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
-      <c r="A187">
+    <row r="189" spans="1:16">
+      <c r="A189">
         <v>1128402</v>
       </c>
-      <c r="C187">
+      <c r="C189">
         <v>1128402</v>
       </c>
-      <c r="D187" t="str">
+      <c r="D189" t="str">
         <f t="shared" si="2"/>
         <v>伊丽莎白碎片</v>
       </c>
-      <c r="E187">
-        <v>2</v>
-      </c>
-      <c r="F187" t="s">
-        <v>45</v>
-      </c>
-      <c r="G187">
+      <c r="E189">
+        <v>2</v>
+      </c>
+      <c r="F189" t="s">
+        <v>45</v>
+      </c>
+      <c r="G189">
         <v>7</v>
       </c>
-      <c r="H187" t="b">
-        <v>1</v>
-      </c>
-      <c r="I187">
-        <v>1</v>
-      </c>
-      <c r="J187" t="s">
-        <v>160</v>
-      </c>
-      <c r="K187">
+      <c r="H189" t="b">
+        <v>1</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189" t="s">
+        <v>160</v>
+      </c>
+      <c r="K189">
         <v>2128402</v>
       </c>
-      <c r="L187" t="b">
-        <v>0</v>
-      </c>
-      <c r="M187" t="str">
+      <c r="L189" t="b">
+        <v>0</v>
+      </c>
+      <c r="M189" t="str">
         <f t="shared" si="3"/>
         <v>伊丽莎白雇员的升星道具</v>
       </c>
-      <c r="P187">
+      <c r="P189">
         <v>999</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16">
-      <c r="A188">
-        <v>1200001</v>
-      </c>
-      <c r="C188">
-        <v>1200001</v>
-      </c>
-      <c r="D188" t="s">
-        <v>236</v>
-      </c>
-      <c r="E188">
-        <v>2</v>
-      </c>
-      <c r="F188" t="s">
-        <v>45</v>
-      </c>
-      <c r="G188">
-        <v>1</v>
-      </c>
-      <c r="H188" t="b">
-        <v>0</v>
-      </c>
-      <c r="I188">
-        <v>0</v>
-      </c>
-      <c r="J188" t="s">
-        <v>160</v>
-      </c>
-      <c r="K188">
-        <v>2200001</v>
-      </c>
-      <c r="L188" t="b">
-        <v>0</v>
-      </c>
-      <c r="M188" t="s">
-        <v>237</v>
-      </c>
-      <c r="P188">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16">
-      <c r="A189">
-        <v>1200002</v>
-      </c>
-      <c r="C189">
-        <v>1200002</v>
-      </c>
-      <c r="D189" t="s">
-        <v>238</v>
-      </c>
-      <c r="E189">
-        <v>2</v>
-      </c>
-      <c r="F189" t="s">
-        <v>45</v>
-      </c>
-      <c r="G189">
-        <v>1</v>
-      </c>
-      <c r="H189" t="b">
-        <v>0</v>
-      </c>
-      <c r="I189">
-        <v>0</v>
-      </c>
-      <c r="J189" t="s">
-        <v>160</v>
-      </c>
-      <c r="K189">
-        <v>2200002</v>
-      </c>
-      <c r="L189" t="b">
-        <v>0</v>
-      </c>
-      <c r="M189" t="s">
-        <v>239</v>
-      </c>
-      <c r="P189">
-        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:16">
       <c r="A190">
-        <v>1200003</v>
+        <v>1200001</v>
       </c>
       <c r="C190">
-        <v>1200003</v>
+        <v>1200001</v>
       </c>
       <c r="D190" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E190">
         <v>2</v>
@@ -10485,13 +10491,13 @@
         <v>160</v>
       </c>
       <c r="K190">
-        <v>2200003</v>
+        <v>2200001</v>
       </c>
       <c r="L190" t="b">
         <v>0</v>
       </c>
       <c r="M190" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P190">
         <v>0</v>
@@ -10499,13 +10505,13 @@
     </row>
     <row r="191" spans="1:16">
       <c r="A191">
-        <v>1200004</v>
+        <v>1200002</v>
       </c>
       <c r="C191">
-        <v>1200004</v>
+        <v>1200002</v>
       </c>
       <c r="D191" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E191">
         <v>2</v>
@@ -10526,13 +10532,13 @@
         <v>160</v>
       </c>
       <c r="K191">
-        <v>2200004</v>
+        <v>2200002</v>
       </c>
       <c r="L191" t="b">
         <v>0</v>
       </c>
       <c r="M191" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="P191">
         <v>0</v>
@@ -10540,13 +10546,13 @@
     </row>
     <row r="192" spans="1:16">
       <c r="A192">
-        <v>1200005</v>
+        <v>1200003</v>
       </c>
       <c r="C192">
-        <v>1200005</v>
+        <v>1200003</v>
       </c>
       <c r="D192" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E192">
         <v>2</v>
@@ -10567,13 +10573,13 @@
         <v>160</v>
       </c>
       <c r="K192">
-        <v>2200005</v>
+        <v>2200003</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
       </c>
       <c r="M192" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P192">
         <v>0</v>
@@ -10581,13 +10587,13 @@
     </row>
     <row r="193" spans="1:16">
       <c r="A193">
-        <v>1200006</v>
+        <v>1200004</v>
       </c>
       <c r="C193">
-        <v>1200006</v>
+        <v>1200004</v>
       </c>
       <c r="D193" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E193">
         <v>2</v>
@@ -10608,13 +10614,13 @@
         <v>160</v>
       </c>
       <c r="K193">
-        <v>2200006</v>
+        <v>2200004</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
       </c>
       <c r="M193" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="P193">
         <v>0</v>
@@ -10622,40 +10628,40 @@
     </row>
     <row r="194" spans="1:16">
       <c r="A194">
-        <v>1200007</v>
+        <v>1200005</v>
       </c>
       <c r="C194">
-        <v>1200007</v>
+        <v>1200005</v>
       </c>
       <c r="D194" t="s">
+        <v>246</v>
+      </c>
+      <c r="E194">
+        <v>2</v>
+      </c>
+      <c r="F194" t="s">
+        <v>45</v>
+      </c>
+      <c r="G194">
+        <v>1</v>
+      </c>
+      <c r="H194" t="b">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="J194" t="s">
+        <v>160</v>
+      </c>
+      <c r="K194">
+        <v>2200005</v>
+      </c>
+      <c r="L194" t="b">
+        <v>0</v>
+      </c>
+      <c r="M194" t="s">
         <v>247</v>
-      </c>
-      <c r="E194">
-        <v>2</v>
-      </c>
-      <c r="F194" t="s">
-        <v>45</v>
-      </c>
-      <c r="G194">
-        <v>1</v>
-      </c>
-      <c r="H194" t="b">
-        <v>0</v>
-      </c>
-      <c r="I194">
-        <v>0</v>
-      </c>
-      <c r="J194" t="s">
-        <v>160</v>
-      </c>
-      <c r="K194">
-        <v>2200007</v>
-      </c>
-      <c r="L194" t="b">
-        <v>0</v>
-      </c>
-      <c r="M194" t="s">
-        <v>248</v>
       </c>
       <c r="P194">
         <v>0</v>
@@ -10663,13 +10669,13 @@
     </row>
     <row r="195" spans="1:16">
       <c r="A195">
-        <v>1200008</v>
+        <v>1200006</v>
       </c>
       <c r="C195">
-        <v>1200008</v>
+        <v>1200006</v>
       </c>
       <c r="D195" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E195">
         <v>2</v>
@@ -10690,13 +10696,13 @@
         <v>160</v>
       </c>
       <c r="K195">
-        <v>2200008</v>
+        <v>2200006</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
       </c>
       <c r="M195" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="P195">
         <v>0</v>
@@ -10704,13 +10710,13 @@
     </row>
     <row r="196" spans="1:16">
       <c r="A196">
-        <v>1200009</v>
+        <v>1200007</v>
       </c>
       <c r="C196">
-        <v>1200009</v>
+        <v>1200007</v>
       </c>
       <c r="D196" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E196">
         <v>2</v>
@@ -10731,13 +10737,13 @@
         <v>160</v>
       </c>
       <c r="K196">
-        <v>2200009</v>
+        <v>2200007</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
       </c>
       <c r="M196" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P196">
         <v>0</v>
@@ -10745,42 +10751,124 @@
     </row>
     <row r="197" spans="1:16">
       <c r="A197">
+        <v>1200008</v>
+      </c>
+      <c r="C197">
+        <v>1200008</v>
+      </c>
+      <c r="D197" t="s">
+        <v>251</v>
+      </c>
+      <c r="E197">
+        <v>2</v>
+      </c>
+      <c r="F197" t="s">
+        <v>45</v>
+      </c>
+      <c r="G197">
+        <v>1</v>
+      </c>
+      <c r="H197" t="b">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="J197" t="s">
+        <v>160</v>
+      </c>
+      <c r="K197">
+        <v>2200008</v>
+      </c>
+      <c r="L197" t="b">
+        <v>0</v>
+      </c>
+      <c r="M197" t="s">
+        <v>252</v>
+      </c>
+      <c r="P197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16">
+      <c r="A198">
+        <v>1200009</v>
+      </c>
+      <c r="C198">
+        <v>1200009</v>
+      </c>
+      <c r="D198" t="s">
+        <v>253</v>
+      </c>
+      <c r="E198">
+        <v>2</v>
+      </c>
+      <c r="F198" t="s">
+        <v>45</v>
+      </c>
+      <c r="G198">
+        <v>1</v>
+      </c>
+      <c r="H198" t="b">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198" t="s">
+        <v>160</v>
+      </c>
+      <c r="K198">
+        <v>2200009</v>
+      </c>
+      <c r="L198" t="b">
+        <v>0</v>
+      </c>
+      <c r="M198" t="s">
+        <v>254</v>
+      </c>
+      <c r="P198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16">
+      <c r="A199">
         <v>1200010</v>
       </c>
-      <c r="C197">
+      <c r="C199">
         <v>1200010</v>
       </c>
-      <c r="D197" t="s">
-        <v>253</v>
-      </c>
-      <c r="E197">
-        <v>2</v>
-      </c>
-      <c r="F197" t="s">
-        <v>45</v>
-      </c>
-      <c r="G197">
-        <v>1</v>
-      </c>
-      <c r="H197" t="b">
-        <v>0</v>
-      </c>
-      <c r="I197">
-        <v>0</v>
-      </c>
-      <c r="J197" t="s">
-        <v>160</v>
-      </c>
-      <c r="K197">
+      <c r="D199" t="s">
+        <v>255</v>
+      </c>
+      <c r="E199">
+        <v>2</v>
+      </c>
+      <c r="F199" t="s">
+        <v>45</v>
+      </c>
+      <c r="G199">
+        <v>1</v>
+      </c>
+      <c r="H199" t="b">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199" t="s">
+        <v>160</v>
+      </c>
+      <c r="K199">
         <v>2200010</v>
       </c>
-      <c r="L197" t="b">
-        <v>0</v>
-      </c>
-      <c r="M197" t="s">
-        <v>254</v>
-      </c>
-      <c r="P197">
+      <c r="L199" t="b">
+        <v>0</v>
+      </c>
+      <c r="M199" t="s">
+        <v>256</v>
+      </c>
+      <c r="P199">
         <v>0</v>
       </c>
     </row>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -1268,12 +1268,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2649,7 +2649,7 @@
         <v>47</v>
       </c>
       <c r="P8" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2693,7 +2693,7 @@
         <v>50</v>
       </c>
       <c r="P9" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S9" s="1">
         <v>0.05</v>
@@ -2740,7 +2740,7 @@
         <v>53</v>
       </c>
       <c r="P10" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S10" s="1">
         <v>0.99</v>
@@ -2787,7 +2787,7 @@
         <v>53</v>
       </c>
       <c r="P11" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S11" s="1">
         <v>0.99</v>
@@ -2834,7 +2834,7 @@
         <v>59</v>
       </c>
       <c r="P12" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="1">
@@ -2885,7 +2885,7 @@
         <v>59</v>
       </c>
       <c r="P13" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="Q13" s="6"/>
       <c r="R13" s="1">
@@ -2937,7 +2937,7 @@
         <v>64</v>
       </c>
       <c r="P14" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="1">
@@ -2989,7 +2989,7 @@
         <v>67</v>
       </c>
       <c r="P15" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="1">
@@ -3041,7 +3041,7 @@
         <v>69</v>
       </c>
       <c r="P16" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="1">
@@ -3882,7 +3882,7 @@
         <v>108</v>
       </c>
       <c r="P35" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S35" s="1">
         <v>0.000544077728550903</v>
@@ -3926,7 +3926,7 @@
         <v>108</v>
       </c>
       <c r="P36" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S36" s="1">
         <v>0.0045080726079932</v>
@@ -3970,7 +3970,7 @@
         <v>108</v>
       </c>
       <c r="P37" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S37" s="1">
         <v>0.0067621089119898</v>
@@ -4014,7 +4014,7 @@
         <v>108</v>
       </c>
       <c r="P38" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S38" s="1">
         <v>0.012622603302381</v>
@@ -4058,7 +4058,7 @@
         <v>108</v>
       </c>
       <c r="P39" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S39" s="1">
         <v>0.0139155435712012</v>
@@ -4102,7 +4102,7 @@
         <v>119</v>
       </c>
       <c r="P40" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S40" s="1">
         <v>0.00174104873136289</v>
@@ -4146,7 +4146,7 @@
         <v>119</v>
       </c>
       <c r="P41" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S41" s="1">
         <v>0.0144258323455782</v>
@@ -4190,7 +4190,7 @@
         <v>119</v>
       </c>
       <c r="P42" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S42" s="1">
         <v>0.0216387485183673</v>
@@ -4234,7 +4234,7 @@
         <v>119</v>
       </c>
       <c r="P43" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S43" s="1">
         <v>0.0403923305676191</v>
@@ -4278,7 +4278,7 @@
         <v>119</v>
       </c>
       <c r="P44" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S44" s="1">
         <v>0.0445297394278439</v>
@@ -4322,7 +4322,7 @@
         <v>130</v>
       </c>
       <c r="P45" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S45" s="1">
         <v>0.00348209746272578</v>
@@ -4366,7 +4366,7 @@
         <v>130</v>
       </c>
       <c r="P46" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S46" s="1">
         <v>0.0288516646911565</v>
@@ -4410,7 +4410,7 @@
         <v>130</v>
       </c>
       <c r="P47" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S47" s="1">
         <v>0.0432774970367347</v>
@@ -4454,7 +4454,7 @@
         <v>130</v>
       </c>
       <c r="P48" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S48" s="1">
         <v>0.0807846611352381</v>
@@ -4498,7 +4498,7 @@
         <v>130</v>
       </c>
       <c r="P49" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S49" s="1">
         <v>0.0890594788556878</v>
@@ -4542,7 +4542,7 @@
         <v>141</v>
       </c>
       <c r="P50" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S50" s="1">
         <v>0.0039173596455665</v>
@@ -4586,7 +4586,7 @@
         <v>141</v>
       </c>
       <c r="P51" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S51" s="1">
         <v>0.032458122777551</v>
@@ -4630,7 +4630,7 @@
         <v>141</v>
       </c>
       <c r="P52" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S52" s="1">
         <v>0.0486871841663265</v>
@@ -4674,7 +4674,7 @@
         <v>141</v>
       </c>
       <c r="P53" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S53" s="1">
         <v>0.0908827437771429</v>
@@ -4718,7 +4718,7 @@
         <v>141</v>
       </c>
       <c r="P54" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S54" s="1">
         <v>0.100191913712649</v>
@@ -4762,7 +4762,7 @@
         <v>152</v>
       </c>
       <c r="P55" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S55" s="1">
         <v>0.00783471929113301</v>
@@ -4806,7 +4806,7 @@
         <v>152</v>
       </c>
       <c r="P56" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S56" s="1">
         <v>0.064916245555102</v>
@@ -4850,7 +4850,7 @@
         <v>152</v>
       </c>
       <c r="P57" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S57" s="1">
         <v>0.097374368332653</v>
@@ -4894,7 +4894,7 @@
         <v>152</v>
       </c>
       <c r="P58" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S58" s="1">
         <v>0.181765487554286</v>
@@ -4938,7 +4938,7 @@
         <v>152</v>
       </c>
       <c r="P59" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
       <c r="S59" s="1">
         <v>0.200383827425298</v>
@@ -5187,7 +5187,7 @@
         <v>173</v>
       </c>
       <c r="P65" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5228,7 +5228,7 @@
         <v>174</v>
       </c>
       <c r="P66" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5269,7 +5269,7 @@
         <v>175</v>
       </c>
       <c r="P67" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -6624,7 +6624,7 @@
         <v>街头潮人游客的升星道具</v>
       </c>
       <c r="P100" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6667,7 +6667,7 @@
         <v>复古绅士游客的升星道具</v>
       </c>
       <c r="P101" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6710,7 +6710,7 @@
         <v>酷盖少年游客的升星道具</v>
       </c>
       <c r="P102" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6753,7 +6753,7 @@
         <v>潮流先锋游客的升星道具</v>
       </c>
       <c r="P103" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6796,7 +6796,7 @@
         <v>时尚教主游客的升星道具</v>
       </c>
       <c r="P104" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6839,7 +6839,7 @@
         <v>街拍达人游客的升星道具</v>
       </c>
       <c r="P105" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6882,7 +6882,7 @@
         <v>运动健将游客的升星道具</v>
       </c>
       <c r="P106" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6925,7 +6925,7 @@
         <v>跑酷少年游客的升星道具</v>
       </c>
       <c r="P107" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6968,7 +6968,7 @@
         <v>滑板高手游客的升星道具</v>
       </c>
       <c r="P108" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7011,7 +7011,7 @@
         <v>甜心辣妹游客的升星道具</v>
       </c>
       <c r="P109" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7054,7 +7054,7 @@
         <v>活力少女游客的升星道具</v>
       </c>
       <c r="P110" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7097,7 +7097,7 @@
         <v>优雅女神游客的升星道具</v>
       </c>
       <c r="P111" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7140,7 +7140,7 @@
         <v>健身狂魔游客的升星道具</v>
       </c>
       <c r="P112" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7183,7 +7183,7 @@
         <v>单车骑士游客的升星道具</v>
       </c>
       <c r="P113" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7226,7 +7226,7 @@
         <v>登山行者游客的升星道具</v>
       </c>
       <c r="P114" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7269,7 +7269,7 @@
         <v>文艺青年游客的升星道具</v>
       </c>
       <c r="P115" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7312,7 +7312,7 @@
         <v>书香少女游客的升星道具</v>
       </c>
       <c r="P116" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7355,7 +7355,7 @@
         <v>民谣歌手游客的升星道具</v>
       </c>
       <c r="P117" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7398,7 +7398,7 @@
         <v>马拉松客游客的升星道具</v>
       </c>
       <c r="P118" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7441,7 +7441,7 @@
         <v>极限玩家游客的升星道具</v>
       </c>
       <c r="P119" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7484,7 +7484,7 @@
         <v>科技极客游客的升星道具</v>
       </c>
       <c r="P120" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7527,7 +7527,7 @@
         <v>独立画家游客的升星道具</v>
       </c>
       <c r="P121" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7570,7 +7570,7 @@
         <v>浪漫诗人游客的升星道具</v>
       </c>
       <c r="P122" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7613,7 +7613,7 @@
         <v>古典乐迷游客的升星道具</v>
       </c>
       <c r="P123" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7656,7 +7656,7 @@
         <v>创业新贵游客的升星道具</v>
       </c>
       <c r="P124" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7699,7 +7699,7 @@
         <v>摸金校尉游客的升星道具</v>
       </c>
       <c r="P125" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7742,7 +7742,7 @@
         <v>氪金大佬游客的升星道具</v>
       </c>
       <c r="P126" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7785,7 +7785,7 @@
         <v>穿搭博主游客的升星道具</v>
       </c>
       <c r="P127" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7828,7 +7828,7 @@
         <v>美妆新秀游客的升星道具</v>
       </c>
       <c r="P128" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -7871,7 +7871,7 @@
         <v>高定女王游客的升星道具</v>
       </c>
       <c r="P129" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -9144,7 +9144,7 @@
         <v>威廉雇员的升星道具</v>
       </c>
       <c r="P160" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9187,7 +9187,7 @@
         <v>艾拉雇员的升星道具</v>
       </c>
       <c r="P161" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9230,7 +9230,7 @@
         <v>亨利雇员的升星道具</v>
       </c>
       <c r="P162" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9273,7 +9273,7 @@
         <v>艾玛雇员的升星道具</v>
       </c>
       <c r="P163" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9316,7 +9316,7 @@
         <v>乔治雇员的升星道具</v>
       </c>
       <c r="P164" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9359,7 +9359,7 @@
         <v>艾娃雇员的升星道具</v>
       </c>
       <c r="P165" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9402,7 +9402,7 @@
         <v>亚瑟雇员的升星道具</v>
       </c>
       <c r="P166" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9445,7 +9445,7 @@
         <v>安娜雇员的升星道具</v>
       </c>
       <c r="P167" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9488,7 +9488,7 @@
         <v>马修雇员的升星道具</v>
       </c>
       <c r="P168" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9531,7 +9531,7 @@
         <v>哈珀雇员的升星道具</v>
       </c>
       <c r="P169" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -9574,7 +9574,7 @@
         <v>拉斐尔雇员的升星道具</v>
       </c>
       <c r="P170" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -9617,7 +9617,7 @@
         <v>伊芙琳雇员的升星道具</v>
       </c>
       <c r="P171" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -9660,7 +9660,7 @@
         <v>埃米尔雇员的升星道具</v>
       </c>
       <c r="P172" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -9703,7 +9703,7 @@
         <v>夏洛特雇员的升星道具</v>
       </c>
       <c r="P173" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -9746,7 +9746,7 @@
         <v>雷蒙德雇员的升星道具</v>
       </c>
       <c r="P174" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -9789,7 +9789,7 @@
         <v>斯嘉丽雇员的升星道具</v>
       </c>
       <c r="P175" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -9832,7 +9832,7 @@
         <v>丹尼尔雇员的升星道具</v>
       </c>
       <c r="P176" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -9875,7 +9875,7 @@
         <v>莉莉安雇员的升星道具</v>
       </c>
       <c r="P177" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -9918,7 +9918,7 @@
         <v>卢卡斯雇员的升星道具</v>
       </c>
       <c r="P178" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -9961,7 +9961,7 @@
         <v>克拉拉雇员的升星道具</v>
       </c>
       <c r="P179" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10004,7 +10004,7 @@
         <v>尼古拉斯雇员的升星道具</v>
       </c>
       <c r="P180" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10047,7 +10047,7 @@
         <v>奥利维亚雇员的升星道具</v>
       </c>
       <c r="P181" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10090,7 +10090,7 @@
         <v>亚历山大雇员的升星道具</v>
       </c>
       <c r="P182" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10133,7 +10133,7 @@
         <v>玛格丽特雇员的升星道具</v>
       </c>
       <c r="P183" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10176,7 +10176,7 @@
         <v>奥古斯特雇员的升星道具</v>
       </c>
       <c r="P184" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10219,7 +10219,7 @@
         <v>维奥莱特雇员的升星道具</v>
       </c>
       <c r="P185" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10262,7 +10262,7 @@
         <v>费利克斯雇员的升星道具</v>
       </c>
       <c r="P186" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10305,7 +10305,7 @@
         <v>维多利亚雇员的升星道具</v>
       </c>
       <c r="P187" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10348,7 +10348,7 @@
         <v>阿尔弗雷德雇员的升星道具</v>
       </c>
       <c r="P188" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10391,7 +10391,7 @@
         <v>伊丽莎白雇员的升星道具</v>
       </c>
       <c r="P189" s="1">
-        <v>999</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10432,7 +10432,7 @@
         <v>239</v>
       </c>
       <c r="P190" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -10473,7 +10473,7 @@
         <v>241</v>
       </c>
       <c r="P191" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -10514,7 +10514,7 @@
         <v>243</v>
       </c>
       <c r="P192" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -10555,7 +10555,7 @@
         <v>245</v>
       </c>
       <c r="P193" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -10596,7 +10596,7 @@
         <v>247</v>
       </c>
       <c r="P194" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -10637,7 +10637,7 @@
         <v>239</v>
       </c>
       <c r="P195" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -10678,7 +10678,7 @@
         <v>250</v>
       </c>
       <c r="P196" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -10719,7 +10719,7 @@
         <v>252</v>
       </c>
       <c r="P197" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -10760,7 +10760,7 @@
         <v>254</v>
       </c>
       <c r="P198" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -10801,7 +10801,7 @@
         <v>256</v>
       </c>
       <c r="P199" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A160" authorId="0">
+    <comment ref="A162" authorId="0">
       <text>
         <r>
           <rPr>
@@ -269,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A170" authorId="0">
+    <comment ref="A172" authorId="0">
       <text>
         <r>
           <rPr>
@@ -292,7 +292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A180" authorId="0">
+    <comment ref="A182" authorId="0">
       <text>
         <r>
           <rPr>
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="263">
   <si>
     <t>道具ID</t>
   </si>
@@ -853,7 +853,25 @@
     <t>声誉值</t>
   </si>
   <si>
+    <t>联盟的升级经验</t>
+  </si>
+  <si>
     <t>贡献值</t>
+  </si>
+  <si>
+    <t>联盟商店兑换商品的道具</t>
+  </si>
+  <si>
+    <t>游客抽卡道具</t>
+  </si>
+  <si>
+    <t>用于游客卡池抽奖的道具</t>
+  </si>
+  <si>
+    <t>雇员抽卡道具</t>
+  </si>
+  <si>
+    <t>用于雇员卡池抽卡的道具</t>
   </si>
   <si>
     <t>街头潮人</t>
@@ -2291,7 +2309,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S199"/>
+  <dimension ref="A1:S201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" style="1" customWidth="1"/>
@@ -5307,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P68" s="1">
         <v>-1</v>
@@ -5321,7 +5339,7 @@
         <v>1024012</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
@@ -5348,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P69" s="1">
         <v>-1</v>
@@ -5356,13 +5374,13 @@
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <v>1025101</v>
+        <v>1024013</v>
       </c>
       <c r="C70" s="1">
-        <v>1025101</v>
+        <v>1024013</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
@@ -5374,36 +5392,36 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K70" s="1">
-        <v>2025101</v>
+        <v>2024013</v>
       </c>
       <c r="L70" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P70" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1">
-        <v>1025102</v>
+        <v>1024014</v>
       </c>
       <c r="C71" s="1">
-        <v>1025102</v>
+        <v>1024014</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
@@ -5415,36 +5433,36 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K71" s="1">
-        <v>2025102</v>
+        <v>2024014</v>
       </c>
       <c r="L71" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="P71" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>1025103</v>
+        <v>1025101</v>
       </c>
       <c r="C72" s="1">
-        <v>1025103</v>
+        <v>1025101</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
@@ -5465,13 +5483,13 @@
         <v>160</v>
       </c>
       <c r="K72" s="1">
-        <v>2025103</v>
+        <v>2025101</v>
       </c>
       <c r="L72" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="P72" s="1">
         <v>-1</v>
@@ -5479,13 +5497,13 @@
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <v>1025104</v>
+        <v>1025102</v>
       </c>
       <c r="C73" s="1">
-        <v>1025104</v>
+        <v>1025102</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -5506,13 +5524,13 @@
         <v>160</v>
       </c>
       <c r="K73" s="1">
-        <v>2025104</v>
+        <v>2025102</v>
       </c>
       <c r="L73" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="P73" s="1">
         <v>-1</v>
@@ -5520,13 +5538,13 @@
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>1025105</v>
+        <v>1025103</v>
       </c>
       <c r="C74" s="1">
-        <v>1025105</v>
+        <v>1025103</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -5547,13 +5565,13 @@
         <v>160</v>
       </c>
       <c r="K74" s="1">
-        <v>2025105</v>
+        <v>2025103</v>
       </c>
       <c r="L74" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="P74" s="1">
         <v>-1</v>
@@ -5561,13 +5579,13 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>1025106</v>
+        <v>1025104</v>
       </c>
       <c r="C75" s="1">
-        <v>1025106</v>
+        <v>1025104</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -5588,13 +5606,13 @@
         <v>160</v>
       </c>
       <c r="K75" s="1">
-        <v>2025106</v>
+        <v>2025104</v>
       </c>
       <c r="L75" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P75" s="1">
         <v>-1</v>
@@ -5602,13 +5620,13 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <v>1025201</v>
+        <v>1025105</v>
       </c>
       <c r="C76" s="1">
-        <v>1025201</v>
+        <v>1025105</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
@@ -5617,7 +5635,7 @@
         <v>45</v>
       </c>
       <c r="G76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" s="1" t="b">
         <v>0</v>
@@ -5629,13 +5647,13 @@
         <v>160</v>
       </c>
       <c r="K76" s="1">
-        <v>2025201</v>
+        <v>2025105</v>
       </c>
       <c r="L76" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P76" s="1">
         <v>-1</v>
@@ -5643,13 +5661,13 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <v>1025202</v>
+        <v>1025106</v>
       </c>
       <c r="C77" s="1">
-        <v>1025202</v>
+        <v>1025106</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -5658,7 +5676,7 @@
         <v>45</v>
       </c>
       <c r="G77" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1" t="b">
         <v>0</v>
@@ -5670,13 +5688,13 @@
         <v>160</v>
       </c>
       <c r="K77" s="1">
-        <v>2025202</v>
+        <v>2025106</v>
       </c>
       <c r="L77" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="P77" s="1">
         <v>-1</v>
@@ -5684,13 +5702,13 @@
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <v>1025203</v>
+        <v>1025201</v>
       </c>
       <c r="C78" s="1">
-        <v>1025203</v>
+        <v>1025201</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -5711,13 +5729,13 @@
         <v>160</v>
       </c>
       <c r="K78" s="1">
-        <v>2025203</v>
+        <v>2025201</v>
       </c>
       <c r="L78" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="P78" s="1">
         <v>-1</v>
@@ -5725,13 +5743,13 @@
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <v>1025204</v>
+        <v>1025202</v>
       </c>
       <c r="C79" s="1">
-        <v>1025204</v>
+        <v>1025202</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
@@ -5752,13 +5770,13 @@
         <v>160</v>
       </c>
       <c r="K79" s="1">
-        <v>2025204</v>
+        <v>2025202</v>
       </c>
       <c r="L79" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="P79" s="1">
         <v>-1</v>
@@ -5766,13 +5784,13 @@
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <v>1025205</v>
+        <v>1025203</v>
       </c>
       <c r="C80" s="1">
-        <v>1025205</v>
+        <v>1025203</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -5793,13 +5811,13 @@
         <v>160</v>
       </c>
       <c r="K80" s="1">
-        <v>2025205</v>
+        <v>2025203</v>
       </c>
       <c r="L80" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="P80" s="1">
         <v>-1</v>
@@ -5807,13 +5825,13 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <v>1025206</v>
+        <v>1025204</v>
       </c>
       <c r="C81" s="1">
-        <v>1025206</v>
+        <v>1025204</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -5834,13 +5852,13 @@
         <v>160</v>
       </c>
       <c r="K81" s="1">
-        <v>2025206</v>
+        <v>2025204</v>
       </c>
       <c r="L81" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P81" s="1">
         <v>-1</v>
@@ -5848,13 +5866,13 @@
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>1025301</v>
+        <v>1025205</v>
       </c>
       <c r="C82" s="1">
-        <v>1025301</v>
+        <v>1025205</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -5863,7 +5881,7 @@
         <v>45</v>
       </c>
       <c r="G82" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="1" t="b">
         <v>0</v>
@@ -5875,13 +5893,13 @@
         <v>160</v>
       </c>
       <c r="K82" s="1">
-        <v>2025301</v>
+        <v>2025205</v>
       </c>
       <c r="L82" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="P82" s="1">
         <v>-1</v>
@@ -5889,13 +5907,13 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <v>1025302</v>
+        <v>1025206</v>
       </c>
       <c r="C83" s="1">
-        <v>1025302</v>
+        <v>1025206</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -5904,7 +5922,7 @@
         <v>45</v>
       </c>
       <c r="G83" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H83" s="1" t="b">
         <v>0</v>
@@ -5916,13 +5934,13 @@
         <v>160</v>
       </c>
       <c r="K83" s="1">
-        <v>2025302</v>
+        <v>2025206</v>
       </c>
       <c r="L83" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="P83" s="1">
         <v>-1</v>
@@ -5930,13 +5948,13 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>1025303</v>
+        <v>1025301</v>
       </c>
       <c r="C84" s="1">
-        <v>1025303</v>
+        <v>1025301</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -5957,13 +5975,13 @@
         <v>160</v>
       </c>
       <c r="K84" s="1">
-        <v>2025303</v>
+        <v>2025301</v>
       </c>
       <c r="L84" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="P84" s="1">
         <v>-1</v>
@@ -5971,13 +5989,13 @@
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1">
-        <v>1025304</v>
+        <v>1025302</v>
       </c>
       <c r="C85" s="1">
-        <v>1025304</v>
+        <v>1025302</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -5998,13 +6016,13 @@
         <v>160</v>
       </c>
       <c r="K85" s="1">
-        <v>2025304</v>
+        <v>2025302</v>
       </c>
       <c r="L85" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P85" s="1">
         <v>-1</v>
@@ -6012,13 +6030,13 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
-        <v>1025305</v>
+        <v>1025303</v>
       </c>
       <c r="C86" s="1">
-        <v>1025305</v>
+        <v>1025303</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
@@ -6039,13 +6057,13 @@
         <v>160</v>
       </c>
       <c r="K86" s="1">
-        <v>2025305</v>
+        <v>2025303</v>
       </c>
       <c r="L86" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="P86" s="1">
         <v>-1</v>
@@ -6053,13 +6071,13 @@
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
-        <v>1025306</v>
+        <v>1025304</v>
       </c>
       <c r="C87" s="1">
-        <v>1025306</v>
+        <v>1025304</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -6080,13 +6098,13 @@
         <v>160</v>
       </c>
       <c r="K87" s="1">
-        <v>2025306</v>
+        <v>2025304</v>
       </c>
       <c r="L87" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="P87" s="1">
         <v>-1</v>
@@ -6094,13 +6112,13 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
-        <v>1025401</v>
+        <v>1025305</v>
       </c>
       <c r="C88" s="1">
-        <v>1025401</v>
+        <v>1025305</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -6109,7 +6127,7 @@
         <v>45</v>
       </c>
       <c r="G88" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H88" s="1" t="b">
         <v>0</v>
@@ -6121,13 +6139,13 @@
         <v>160</v>
       </c>
       <c r="K88" s="1">
-        <v>2025401</v>
+        <v>2025305</v>
       </c>
       <c r="L88" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P88" s="1">
         <v>-1</v>
@@ -6135,13 +6153,13 @@
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>1025402</v>
+        <v>1025306</v>
       </c>
       <c r="C89" s="1">
-        <v>1025402</v>
+        <v>1025306</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -6150,7 +6168,7 @@
         <v>45</v>
       </c>
       <c r="G89" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H89" s="1" t="b">
         <v>0</v>
@@ -6162,13 +6180,13 @@
         <v>160</v>
       </c>
       <c r="K89" s="1">
-        <v>2025402</v>
+        <v>2025306</v>
       </c>
       <c r="L89" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="P89" s="1">
         <v>-1</v>
@@ -6176,13 +6194,13 @@
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
-        <v>1025403</v>
+        <v>1025401</v>
       </c>
       <c r="C90" s="1">
-        <v>1025403</v>
+        <v>1025401</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -6203,13 +6221,13 @@
         <v>160</v>
       </c>
       <c r="K90" s="1">
-        <v>2025403</v>
+        <v>2025401</v>
       </c>
       <c r="L90" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="P90" s="1">
         <v>-1</v>
@@ -6217,13 +6235,13 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <v>1025404</v>
+        <v>1025402</v>
       </c>
       <c r="C91" s="1">
-        <v>1025404</v>
+        <v>1025402</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
@@ -6244,13 +6262,13 @@
         <v>160</v>
       </c>
       <c r="K91" s="1">
-        <v>2025404</v>
+        <v>2025402</v>
       </c>
       <c r="L91" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="P91" s="1">
         <v>-1</v>
@@ -6258,13 +6276,13 @@
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <v>1025405</v>
+        <v>1025403</v>
       </c>
       <c r="C92" s="1">
-        <v>1025405</v>
+        <v>1025403</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -6285,13 +6303,13 @@
         <v>160</v>
       </c>
       <c r="K92" s="1">
-        <v>2025405</v>
+        <v>2025403</v>
       </c>
       <c r="L92" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="P92" s="1">
         <v>-1</v>
@@ -6299,13 +6317,13 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1">
-        <v>1025406</v>
+        <v>1025404</v>
       </c>
       <c r="C93" s="1">
-        <v>1025406</v>
+        <v>1025404</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
@@ -6326,13 +6344,13 @@
         <v>160</v>
       </c>
       <c r="K93" s="1">
-        <v>2025406</v>
+        <v>2025404</v>
       </c>
       <c r="L93" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="P93" s="1">
         <v>-1</v>
@@ -6340,13 +6358,13 @@
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>1025501</v>
+        <v>1025405</v>
       </c>
       <c r="C94" s="1">
-        <v>1025501</v>
+        <v>1025405</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -6355,7 +6373,7 @@
         <v>45</v>
       </c>
       <c r="G94" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H94" s="1" t="b">
         <v>0</v>
@@ -6367,13 +6385,13 @@
         <v>160</v>
       </c>
       <c r="K94" s="1">
-        <v>2025501</v>
+        <v>2025405</v>
       </c>
       <c r="L94" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="P94" s="1">
         <v>-1</v>
@@ -6381,13 +6399,13 @@
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>1025502</v>
+        <v>1025406</v>
       </c>
       <c r="C95" s="1">
-        <v>1025502</v>
+        <v>1025406</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -6396,7 +6414,7 @@
         <v>45</v>
       </c>
       <c r="G95" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H95" s="1" t="b">
         <v>0</v>
@@ -6408,13 +6426,13 @@
         <v>160</v>
       </c>
       <c r="K95" s="1">
-        <v>2025502</v>
+        <v>2025406</v>
       </c>
       <c r="L95" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="P95" s="1">
         <v>-1</v>
@@ -6422,13 +6440,13 @@
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1">
-        <v>1025503</v>
+        <v>1025501</v>
       </c>
       <c r="C96" s="1">
-        <v>1025503</v>
+        <v>1025501</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -6449,13 +6467,13 @@
         <v>160</v>
       </c>
       <c r="K96" s="1">
-        <v>2025503</v>
+        <v>2025501</v>
       </c>
       <c r="L96" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P96" s="1">
         <v>-1</v>
@@ -6463,13 +6481,13 @@
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>1025504</v>
+        <v>1025502</v>
       </c>
       <c r="C97" s="1">
-        <v>1025504</v>
+        <v>1025502</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -6490,13 +6508,13 @@
         <v>160</v>
       </c>
       <c r="K97" s="1">
-        <v>2025504</v>
+        <v>2025502</v>
       </c>
       <c r="L97" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="P97" s="1">
         <v>-1</v>
@@ -6504,13 +6522,13 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <v>1025505</v>
+        <v>1025503</v>
       </c>
       <c r="C98" s="1">
-        <v>1025505</v>
+        <v>1025503</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -6531,13 +6549,13 @@
         <v>160</v>
       </c>
       <c r="K98" s="1">
-        <v>2025505</v>
+        <v>2025503</v>
       </c>
       <c r="L98" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="P98" s="1">
         <v>-1</v>
@@ -6545,13 +6563,13 @@
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>1025506</v>
+        <v>1025504</v>
       </c>
       <c r="C99" s="1">
-        <v>1025506</v>
+        <v>1025504</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -6572,13 +6590,13 @@
         <v>160</v>
       </c>
       <c r="K99" s="1">
-        <v>2025506</v>
+        <v>2025504</v>
       </c>
       <c r="L99" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="P99" s="1">
         <v>-1</v>
@@ -6586,14 +6604,13 @@
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <v>1125101</v>
+        <v>1025505</v>
       </c>
       <c r="C100" s="1">
-        <v>1125101</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>D70&amp;"碎片"</f>
-        <v>街头潮人碎片</v>
+        <v>1025505</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -6602,41 +6619,39 @@
         <v>45</v>
       </c>
       <c r="G100" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H100" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K100" s="1">
-        <v>2125101</v>
+        <v>2025505</v>
       </c>
       <c r="L100" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M100" s="1" t="str">
-        <f>D70&amp;"游客的升星道具"</f>
-        <v>街头潮人游客的升星道具</v>
+      <c r="M100" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="P100" s="1">
-        <v>999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>1125102</v>
+        <v>1025506</v>
       </c>
       <c r="C101" s="1">
-        <v>1125102</v>
-      </c>
-      <c r="D101" s="1" t="str">
-        <f t="shared" ref="D101:D129" si="0">D71&amp;"碎片"</f>
-        <v>复古绅士碎片</v>
+        <v>1025506</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="E101" s="1">
         <v>2</v>
@@ -6645,1326 +6660,1329 @@
         <v>45</v>
       </c>
       <c r="G101" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H101" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K101" s="1">
-        <v>2125102</v>
+        <v>2025506</v>
       </c>
       <c r="L101" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M101" s="1" t="str">
-        <f t="shared" ref="M101:M129" si="1">D71&amp;"游客的升星道具"</f>
-        <v>复古绅士游客的升星道具</v>
+      <c r="M101" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="P101" s="1">
-        <v>999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
+        <v>1125101</v>
+      </c>
+      <c r="C102" s="1">
+        <v>1125101</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>D72&amp;"碎片"</f>
+        <v>街头潮人碎片</v>
+      </c>
+      <c r="E102" s="1">
+        <v>2</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G102" s="1">
+        <v>1</v>
+      </c>
+      <c r="H102" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I102" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K102" s="1">
+        <v>2125101</v>
+      </c>
+      <c r="L102" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M102" s="1" t="str">
+        <f>D72&amp;"游客的升星道具"</f>
+        <v>街头潮人游客的升星道具</v>
+      </c>
+      <c r="P102" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" s="1">
+        <v>1125102</v>
+      </c>
+      <c r="C103" s="1">
+        <v>1125102</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f t="shared" ref="D103:D131" si="0">D73&amp;"碎片"</f>
+        <v>复古绅士碎片</v>
+      </c>
+      <c r="E103" s="1">
+        <v>2</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G103" s="1">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I103" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K103" s="1">
+        <v>2125102</v>
+      </c>
+      <c r="L103" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M103" s="1" t="str">
+        <f t="shared" ref="M103:M131" si="1">D73&amp;"游客的升星道具"</f>
+        <v>复古绅士游客的升星道具</v>
+      </c>
+      <c r="P103" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104" s="1">
         <v>1125103</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C104" s="1">
         <v>1125103</v>
       </c>
-      <c r="D102" s="1" t="str">
+      <c r="D104" s="1" t="str">
         <f t="shared" si="0"/>
         <v>酷盖少年碎片</v>
       </c>
-      <c r="E102" s="1">
-        <v>2</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G102" s="1">
-        <v>1</v>
-      </c>
-      <c r="H102" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I102" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K102" s="1">
+      <c r="E104" s="1">
+        <v>2</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G104" s="1">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K104" s="1">
         <v>2125103</v>
       </c>
-      <c r="L102" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M102" s="1" t="str">
+      <c r="L104" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" s="1" t="str">
         <f t="shared" si="1"/>
         <v>酷盖少年游客的升星道具</v>
       </c>
-      <c r="P102" s="1">
+      <c r="P104" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
-      <c r="A103" s="1">
+    <row r="105" spans="1:16">
+      <c r="A105" s="1">
         <v>1125104</v>
       </c>
-      <c r="C103" s="1">
+      <c r="C105" s="1">
         <v>1125104</v>
       </c>
-      <c r="D103" s="1" t="str">
+      <c r="D105" s="1" t="str">
         <f t="shared" si="0"/>
         <v>潮流先锋碎片</v>
       </c>
-      <c r="E103" s="1">
-        <v>2</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G103" s="1">
-        <v>1</v>
-      </c>
-      <c r="H103" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I103" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K103" s="1">
+      <c r="E105" s="1">
+        <v>2</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G105" s="1">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K105" s="1">
         <v>2125104</v>
       </c>
-      <c r="L103" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M103" s="1" t="str">
+      <c r="L105" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" s="1" t="str">
         <f t="shared" si="1"/>
         <v>潮流先锋游客的升星道具</v>
       </c>
-      <c r="P103" s="1">
+      <c r="P105" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
-      <c r="A104" s="1">
+    <row r="106" spans="1:16">
+      <c r="A106" s="1">
         <v>1125105</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C106" s="1">
         <v>1125105</v>
       </c>
-      <c r="D104" s="1" t="str">
+      <c r="D106" s="1" t="str">
         <f t="shared" si="0"/>
         <v>时尚教主碎片</v>
       </c>
-      <c r="E104" s="1">
-        <v>2</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G104" s="1">
-        <v>1</v>
-      </c>
-      <c r="H104" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I104" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K104" s="1">
+      <c r="E106" s="1">
+        <v>2</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G106" s="1">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K106" s="1">
         <v>2125105</v>
       </c>
-      <c r="L104" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M104" s="1" t="str">
+      <c r="L106" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M106" s="1" t="str">
         <f t="shared" si="1"/>
         <v>时尚教主游客的升星道具</v>
       </c>
-      <c r="P104" s="1">
+      <c r="P106" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
-      <c r="A105" s="1">
+    <row r="107" spans="1:16">
+      <c r="A107" s="1">
         <v>1125106</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C107" s="1">
         <v>1125106</v>
       </c>
-      <c r="D105" s="1" t="str">
+      <c r="D107" s="1" t="str">
         <f t="shared" si="0"/>
         <v>街拍达人碎片</v>
       </c>
-      <c r="E105" s="1">
-        <v>2</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G105" s="1">
-        <v>1</v>
-      </c>
-      <c r="H105" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I105" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K105" s="1">
+      <c r="E107" s="1">
+        <v>2</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G107" s="1">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I107" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K107" s="1">
         <v>2125106</v>
       </c>
-      <c r="L105" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M105" s="1" t="str">
+      <c r="L107" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M107" s="1" t="str">
         <f t="shared" si="1"/>
         <v>街拍达人游客的升星道具</v>
       </c>
-      <c r="P105" s="1">
+      <c r="P107" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
-      <c r="A106" s="1">
+    <row r="108" spans="1:16">
+      <c r="A108" s="1">
         <v>1125201</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C108" s="1">
         <v>1125201</v>
       </c>
-      <c r="D106" s="1" t="str">
+      <c r="D108" s="1" t="str">
         <f t="shared" si="0"/>
         <v>运动健将碎片</v>
       </c>
-      <c r="E106" s="1">
-        <v>2</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G106" s="1">
-        <v>2</v>
-      </c>
-      <c r="H106" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I106" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K106" s="1">
+      <c r="E108" s="1">
+        <v>2</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G108" s="1">
+        <v>2</v>
+      </c>
+      <c r="H108" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K108" s="1">
         <v>2125201</v>
       </c>
-      <c r="L106" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M106" s="1" t="str">
+      <c r="L108" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M108" s="1" t="str">
         <f t="shared" si="1"/>
         <v>运动健将游客的升星道具</v>
       </c>
-      <c r="P106" s="1">
+      <c r="P108" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
-      <c r="A107" s="1">
+    <row r="109" spans="1:16">
+      <c r="A109" s="1">
         <v>1125202</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C109" s="1">
         <v>1125202</v>
       </c>
-      <c r="D107" s="1" t="str">
+      <c r="D109" s="1" t="str">
         <f t="shared" si="0"/>
         <v>跑酷少年碎片</v>
       </c>
-      <c r="E107" s="1">
-        <v>2</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G107" s="1">
-        <v>2</v>
-      </c>
-      <c r="H107" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I107" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K107" s="1">
+      <c r="E109" s="1">
+        <v>2</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G109" s="1">
+        <v>2</v>
+      </c>
+      <c r="H109" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I109" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K109" s="1">
         <v>2125202</v>
       </c>
-      <c r="L107" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M107" s="1" t="str">
+      <c r="L109" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M109" s="1" t="str">
         <f t="shared" si="1"/>
         <v>跑酷少年游客的升星道具</v>
       </c>
-      <c r="P107" s="1">
+      <c r="P109" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
-      <c r="A108" s="1">
+    <row r="110" spans="1:16">
+      <c r="A110" s="1">
         <v>1125203</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C110" s="1">
         <v>1125203</v>
       </c>
-      <c r="D108" s="1" t="str">
+      <c r="D110" s="1" t="str">
         <f t="shared" si="0"/>
         <v>滑板高手碎片</v>
       </c>
-      <c r="E108" s="1">
-        <v>2</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G108" s="1">
-        <v>2</v>
-      </c>
-      <c r="H108" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I108" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K108" s="1">
+      <c r="E110" s="1">
+        <v>2</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G110" s="1">
+        <v>2</v>
+      </c>
+      <c r="H110" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I110" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K110" s="1">
         <v>2125203</v>
       </c>
-      <c r="L108" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M108" s="1" t="str">
+      <c r="L110" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M110" s="1" t="str">
         <f t="shared" si="1"/>
         <v>滑板高手游客的升星道具</v>
       </c>
-      <c r="P108" s="1">
+      <c r="P110" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
-      <c r="A109" s="1">
+    <row r="111" spans="1:16">
+      <c r="A111" s="1">
         <v>1125204</v>
       </c>
-      <c r="C109" s="1">
+      <c r="C111" s="1">
         <v>1125204</v>
       </c>
-      <c r="D109" s="1" t="str">
+      <c r="D111" s="1" t="str">
         <f t="shared" si="0"/>
         <v>甜心辣妹碎片</v>
       </c>
-      <c r="E109" s="1">
-        <v>2</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G109" s="1">
-        <v>2</v>
-      </c>
-      <c r="H109" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I109" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K109" s="1">
+      <c r="E111" s="1">
+        <v>2</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G111" s="1">
+        <v>2</v>
+      </c>
+      <c r="H111" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I111" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K111" s="1">
         <v>2125204</v>
       </c>
-      <c r="L109" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M109" s="1" t="str">
+      <c r="L111" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M111" s="1" t="str">
         <f t="shared" si="1"/>
         <v>甜心辣妹游客的升星道具</v>
       </c>
-      <c r="P109" s="1">
+      <c r="P111" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
-      <c r="A110" s="1">
+    <row r="112" spans="1:16">
+      <c r="A112" s="1">
         <v>1125205</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C112" s="1">
         <v>1125205</v>
       </c>
-      <c r="D110" s="1" t="str">
+      <c r="D112" s="1" t="str">
         <f t="shared" si="0"/>
         <v>活力少女碎片</v>
       </c>
-      <c r="E110" s="1">
-        <v>2</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G110" s="1">
-        <v>2</v>
-      </c>
-      <c r="H110" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I110" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K110" s="1">
+      <c r="E112" s="1">
+        <v>2</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2</v>
+      </c>
+      <c r="H112" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K112" s="1">
         <v>2125205</v>
       </c>
-      <c r="L110" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M110" s="1" t="str">
+      <c r="L112" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" s="1" t="str">
         <f t="shared" si="1"/>
         <v>活力少女游客的升星道具</v>
       </c>
-      <c r="P110" s="1">
+      <c r="P112" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
-      <c r="A111" s="1">
+    <row r="113" spans="1:16">
+      <c r="A113" s="1">
         <v>1125206</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C113" s="1">
         <v>1125206</v>
       </c>
-      <c r="D111" s="1" t="str">
+      <c r="D113" s="1" t="str">
         <f t="shared" si="0"/>
         <v>优雅女神碎片</v>
       </c>
-      <c r="E111" s="1">
-        <v>2</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G111" s="1">
-        <v>2</v>
-      </c>
-      <c r="H111" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I111" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K111" s="1">
+      <c r="E113" s="1">
+        <v>2</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G113" s="1">
+        <v>2</v>
+      </c>
+      <c r="H113" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K113" s="1">
         <v>2125206</v>
       </c>
-      <c r="L111" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M111" s="1" t="str">
+      <c r="L113" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M113" s="1" t="str">
         <f t="shared" si="1"/>
         <v>优雅女神游客的升星道具</v>
       </c>
-      <c r="P111" s="1">
+      <c r="P113" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
-      <c r="A112" s="1">
+    <row r="114" spans="1:16">
+      <c r="A114" s="1">
         <v>1125301</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C114" s="1">
         <v>1125301</v>
       </c>
-      <c r="D112" s="1" t="str">
+      <c r="D114" s="1" t="str">
         <f t="shared" si="0"/>
         <v>健身狂魔碎片</v>
       </c>
-      <c r="E112" s="1">
-        <v>2</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G112" s="1">
+      <c r="E114" s="1">
+        <v>2</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G114" s="1">
         <v>3</v>
       </c>
-      <c r="H112" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I112" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K112" s="1">
+      <c r="H114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K114" s="1">
         <v>2125301</v>
       </c>
-      <c r="L112" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M112" s="1" t="str">
+      <c r="L114" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" s="1" t="str">
         <f t="shared" si="1"/>
         <v>健身狂魔游客的升星道具</v>
       </c>
-      <c r="P112" s="1">
+      <c r="P114" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
-      <c r="A113" s="1">
+    <row r="115" spans="1:16">
+      <c r="A115" s="1">
         <v>1125302</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C115" s="1">
         <v>1125302</v>
       </c>
-      <c r="D113" s="1" t="str">
+      <c r="D115" s="1" t="str">
         <f t="shared" si="0"/>
         <v>单车骑士碎片</v>
       </c>
-      <c r="E113" s="1">
-        <v>2</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G113" s="1">
+      <c r="E115" s="1">
+        <v>2</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G115" s="1">
         <v>3</v>
       </c>
-      <c r="H113" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I113" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K113" s="1">
+      <c r="H115" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I115" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K115" s="1">
         <v>2125302</v>
       </c>
-      <c r="L113" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M113" s="1" t="str">
+      <c r="L115" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M115" s="1" t="str">
         <f t="shared" si="1"/>
         <v>单车骑士游客的升星道具</v>
       </c>
-      <c r="P113" s="1">
+      <c r="P115" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
-      <c r="A114" s="1">
+    <row r="116" spans="1:16">
+      <c r="A116" s="1">
         <v>1125303</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C116" s="1">
         <v>1125303</v>
       </c>
-      <c r="D114" s="1" t="str">
+      <c r="D116" s="1" t="str">
         <f t="shared" si="0"/>
         <v>登山行者碎片</v>
       </c>
-      <c r="E114" s="1">
-        <v>2</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G114" s="1">
+      <c r="E116" s="1">
+        <v>2</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G116" s="1">
         <v>3</v>
       </c>
-      <c r="H114" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I114" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K114" s="1">
+      <c r="H116" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I116" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K116" s="1">
         <v>2125303</v>
       </c>
-      <c r="L114" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M114" s="1" t="str">
+      <c r="L116" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M116" s="1" t="str">
         <f t="shared" si="1"/>
         <v>登山行者游客的升星道具</v>
       </c>
-      <c r="P114" s="1">
+      <c r="P116" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
-      <c r="A115" s="1">
+    <row r="117" spans="1:16">
+      <c r="A117" s="1">
         <v>1125304</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C117" s="1">
         <v>1125304</v>
       </c>
-      <c r="D115" s="1" t="str">
+      <c r="D117" s="1" t="str">
         <f t="shared" si="0"/>
         <v>文艺青年碎片</v>
       </c>
-      <c r="E115" s="1">
-        <v>2</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G115" s="1">
+      <c r="E117" s="1">
+        <v>2</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G117" s="1">
         <v>3</v>
       </c>
-      <c r="H115" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I115" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K115" s="1">
+      <c r="H117" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I117" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K117" s="1">
         <v>2125304</v>
       </c>
-      <c r="L115" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M115" s="1" t="str">
+      <c r="L117" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M117" s="1" t="str">
         <f t="shared" si="1"/>
         <v>文艺青年游客的升星道具</v>
       </c>
-      <c r="P115" s="1">
+      <c r="P117" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
-      <c r="A116" s="1">
+    <row r="118" spans="1:16">
+      <c r="A118" s="1">
         <v>1125305</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C118" s="1">
         <v>1125305</v>
       </c>
-      <c r="D116" s="1" t="str">
+      <c r="D118" s="1" t="str">
         <f t="shared" si="0"/>
         <v>书香少女碎片</v>
       </c>
-      <c r="E116" s="1">
-        <v>2</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G116" s="1">
+      <c r="E118" s="1">
+        <v>2</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G118" s="1">
         <v>3</v>
       </c>
-      <c r="H116" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I116" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K116" s="1">
+      <c r="H118" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I118" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K118" s="1">
         <v>2125305</v>
       </c>
-      <c r="L116" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M116" s="1" t="str">
+      <c r="L118" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" s="1" t="str">
         <f t="shared" si="1"/>
         <v>书香少女游客的升星道具</v>
       </c>
-      <c r="P116" s="1">
+      <c r="P118" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
-      <c r="A117" s="1">
+    <row r="119" spans="1:16">
+      <c r="A119" s="1">
         <v>1125306</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C119" s="1">
         <v>1125306</v>
       </c>
-      <c r="D117" s="1" t="str">
+      <c r="D119" s="1" t="str">
         <f t="shared" si="0"/>
         <v>民谣歌手碎片</v>
       </c>
-      <c r="E117" s="1">
-        <v>2</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G117" s="1">
+      <c r="E119" s="1">
+        <v>2</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G119" s="1">
         <v>3</v>
       </c>
-      <c r="H117" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I117" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K117" s="1">
+      <c r="H119" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I119" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K119" s="1">
         <v>2125306</v>
       </c>
-      <c r="L117" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M117" s="1" t="str">
+      <c r="L119" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M119" s="1" t="str">
         <f t="shared" si="1"/>
         <v>民谣歌手游客的升星道具</v>
       </c>
-      <c r="P117" s="1">
+      <c r="P119" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
-      <c r="A118" s="1">
+    <row r="120" spans="1:16">
+      <c r="A120" s="1">
         <v>1125401</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C120" s="1">
         <v>1125401</v>
       </c>
-      <c r="D118" s="1" t="str">
+      <c r="D120" s="1" t="str">
         <f t="shared" si="0"/>
         <v>马拉松客碎片</v>
       </c>
-      <c r="E118" s="1">
-        <v>2</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G118" s="1">
+      <c r="E120" s="1">
+        <v>2</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G120" s="1">
         <v>4</v>
       </c>
-      <c r="H118" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I118" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K118" s="1">
+      <c r="H120" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I120" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K120" s="1">
         <v>2125401</v>
       </c>
-      <c r="L118" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M118" s="1" t="str">
+      <c r="L120" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M120" s="1" t="str">
         <f t="shared" si="1"/>
         <v>马拉松客游客的升星道具</v>
       </c>
-      <c r="P118" s="1">
+      <c r="P120" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
-      <c r="A119" s="1">
+    <row r="121" spans="1:16">
+      <c r="A121" s="1">
         <v>1125402</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C121" s="1">
         <v>1125402</v>
       </c>
-      <c r="D119" s="1" t="str">
+      <c r="D121" s="1" t="str">
         <f t="shared" si="0"/>
         <v>极限玩家碎片</v>
       </c>
-      <c r="E119" s="1">
-        <v>2</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G119" s="1">
+      <c r="E121" s="1">
+        <v>2</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G121" s="1">
         <v>4</v>
       </c>
-      <c r="H119" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I119" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K119" s="1">
+      <c r="H121" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I121" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K121" s="1">
         <v>2125402</v>
       </c>
-      <c r="L119" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M119" s="1" t="str">
+      <c r="L121" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" s="1" t="str">
         <f t="shared" si="1"/>
         <v>极限玩家游客的升星道具</v>
       </c>
-      <c r="P119" s="1">
+      <c r="P121" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
-      <c r="A120" s="1">
+    <row r="122" spans="1:16">
+      <c r="A122" s="1">
         <v>1125403</v>
       </c>
-      <c r="C120" s="1">
+      <c r="C122" s="1">
         <v>1125403</v>
       </c>
-      <c r="D120" s="1" t="str">
+      <c r="D122" s="1" t="str">
         <f t="shared" si="0"/>
         <v>科技极客碎片</v>
       </c>
-      <c r="E120" s="1">
-        <v>2</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G120" s="1">
+      <c r="E122" s="1">
+        <v>2</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G122" s="1">
         <v>4</v>
       </c>
-      <c r="H120" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I120" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K120" s="1">
+      <c r="H122" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I122" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K122" s="1">
         <v>2125403</v>
       </c>
-      <c r="L120" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M120" s="1" t="str">
+      <c r="L122" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" s="1" t="str">
         <f t="shared" si="1"/>
         <v>科技极客游客的升星道具</v>
       </c>
-      <c r="P120" s="1">
+      <c r="P122" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
-      <c r="A121" s="1">
+    <row r="123" spans="1:16">
+      <c r="A123" s="1">
         <v>1125404</v>
       </c>
-      <c r="C121" s="1">
+      <c r="C123" s="1">
         <v>1125404</v>
       </c>
-      <c r="D121" s="1" t="str">
+      <c r="D123" s="1" t="str">
         <f t="shared" si="0"/>
         <v>独立画家碎片</v>
       </c>
-      <c r="E121" s="1">
-        <v>2</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G121" s="1">
+      <c r="E123" s="1">
+        <v>2</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G123" s="1">
         <v>4</v>
       </c>
-      <c r="H121" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I121" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K121" s="1">
+      <c r="H123" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I123" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K123" s="1">
         <v>2125404</v>
       </c>
-      <c r="L121" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M121" s="1" t="str">
+      <c r="L123" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" s="1" t="str">
         <f t="shared" si="1"/>
         <v>独立画家游客的升星道具</v>
       </c>
-      <c r="P121" s="1">
+      <c r="P123" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
-      <c r="A122" s="1">
+    <row r="124" spans="1:16">
+      <c r="A124" s="1">
         <v>1125405</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C124" s="1">
         <v>1125405</v>
       </c>
-      <c r="D122" s="1" t="str">
+      <c r="D124" s="1" t="str">
         <f t="shared" si="0"/>
         <v>浪漫诗人碎片</v>
       </c>
-      <c r="E122" s="1">
-        <v>2</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G122" s="1">
+      <c r="E124" s="1">
+        <v>2</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G124" s="1">
         <v>4</v>
       </c>
-      <c r="H122" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I122" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K122" s="1">
+      <c r="H124" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I124" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K124" s="1">
         <v>2125405</v>
       </c>
-      <c r="L122" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M122" s="1" t="str">
+      <c r="L124" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" s="1" t="str">
         <f t="shared" si="1"/>
         <v>浪漫诗人游客的升星道具</v>
       </c>
-      <c r="P122" s="1">
+      <c r="P124" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
-      <c r="A123" s="1">
+    <row r="125" spans="1:16">
+      <c r="A125" s="1">
         <v>1125406</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C125" s="1">
         <v>1125406</v>
       </c>
-      <c r="D123" s="1" t="str">
+      <c r="D125" s="1" t="str">
         <f t="shared" si="0"/>
         <v>古典乐迷碎片</v>
       </c>
-      <c r="E123" s="1">
-        <v>2</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G123" s="1">
+      <c r="E125" s="1">
+        <v>2</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G125" s="1">
         <v>4</v>
       </c>
-      <c r="H123" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I123" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K123" s="1">
+      <c r="H125" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I125" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K125" s="1">
         <v>2125406</v>
       </c>
-      <c r="L123" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M123" s="1" t="str">
+      <c r="L125" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" s="1" t="str">
         <f t="shared" si="1"/>
         <v>古典乐迷游客的升星道具</v>
       </c>
-      <c r="P123" s="1">
+      <c r="P125" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
-      <c r="A124" s="1">
+    <row r="126" spans="1:16">
+      <c r="A126" s="1">
         <v>1125501</v>
       </c>
-      <c r="C124" s="1">
+      <c r="C126" s="1">
         <v>1125501</v>
       </c>
-      <c r="D124" s="1" t="str">
+      <c r="D126" s="1" t="str">
         <f t="shared" si="0"/>
         <v>创业新贵碎片</v>
       </c>
-      <c r="E124" s="1">
-        <v>2</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G124" s="1">
+      <c r="E126" s="1">
+        <v>2</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G126" s="1">
         <v>7</v>
       </c>
-      <c r="H124" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I124" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K124" s="1">
+      <c r="H126" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I126" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K126" s="1">
         <v>2125501</v>
       </c>
-      <c r="L124" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M124" s="1" t="str">
+      <c r="L126" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M126" s="1" t="str">
         <f t="shared" si="1"/>
         <v>创业新贵游客的升星道具</v>
       </c>
-      <c r="P124" s="1">
+      <c r="P126" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
-      <c r="A125" s="1">
+    <row r="127" spans="1:16">
+      <c r="A127" s="1">
         <v>1125502</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C127" s="1">
         <v>1125502</v>
       </c>
-      <c r="D125" s="1" t="str">
+      <c r="D127" s="1" t="str">
         <f t="shared" si="0"/>
         <v>摸金校尉碎片</v>
       </c>
-      <c r="E125" s="1">
-        <v>2</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G125" s="1">
+      <c r="E127" s="1">
+        <v>2</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G127" s="1">
         <v>7</v>
       </c>
-      <c r="H125" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I125" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K125" s="1">
+      <c r="H127" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I127" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K127" s="1">
         <v>2125502</v>
       </c>
-      <c r="L125" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M125" s="1" t="str">
+      <c r="L127" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M127" s="1" t="str">
         <f t="shared" si="1"/>
         <v>摸金校尉游客的升星道具</v>
       </c>
-      <c r="P125" s="1">
+      <c r="P127" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
-      <c r="A126" s="1">
+    <row r="128" spans="1:16">
+      <c r="A128" s="1">
         <v>1125503</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C128" s="1">
         <v>1125503</v>
       </c>
-      <c r="D126" s="1" t="str">
+      <c r="D128" s="1" t="str">
         <f t="shared" si="0"/>
         <v>氪金大佬碎片</v>
       </c>
-      <c r="E126" s="1">
-        <v>2</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G126" s="1">
+      <c r="E128" s="1">
+        <v>2</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G128" s="1">
         <v>7</v>
       </c>
-      <c r="H126" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I126" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K126" s="1">
+      <c r="H128" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I128" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K128" s="1">
         <v>2125503</v>
       </c>
-      <c r="L126" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M126" s="1" t="str">
+      <c r="L128" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M128" s="1" t="str">
         <f t="shared" si="1"/>
         <v>氪金大佬游客的升星道具</v>
       </c>
-      <c r="P126" s="1">
+      <c r="P128" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
-      <c r="A127" s="1">
+    <row r="129" spans="1:16">
+      <c r="A129" s="1">
         <v>1125504</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C129" s="1">
         <v>1125504</v>
       </c>
-      <c r="D127" s="1" t="str">
+      <c r="D129" s="1" t="str">
         <f t="shared" si="0"/>
         <v>穿搭博主碎片</v>
       </c>
-      <c r="E127" s="1">
-        <v>2</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G127" s="1">
+      <c r="E129" s="1">
+        <v>2</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G129" s="1">
         <v>7</v>
       </c>
-      <c r="H127" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I127" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K127" s="1">
+      <c r="H129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K129" s="1">
         <v>2125504</v>
       </c>
-      <c r="L127" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M127" s="1" t="str">
+      <c r="L129" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M129" s="1" t="str">
         <f t="shared" si="1"/>
         <v>穿搭博主游客的升星道具</v>
       </c>
-      <c r="P127" s="1">
+      <c r="P129" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
-      <c r="A128" s="1">
+    <row r="130" spans="1:16">
+      <c r="A130" s="1">
         <v>1125505</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C130" s="1">
         <v>1125505</v>
       </c>
-      <c r="D128" s="1" t="str">
+      <c r="D130" s="1" t="str">
         <f t="shared" si="0"/>
         <v>美妆新秀碎片</v>
       </c>
-      <c r="E128" s="1">
-        <v>2</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G128" s="1">
+      <c r="E130" s="1">
+        <v>2</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G130" s="1">
         <v>7</v>
       </c>
-      <c r="H128" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I128" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K128" s="1">
+      <c r="H130" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I130" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K130" s="1">
         <v>2125505</v>
       </c>
-      <c r="L128" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M128" s="1" t="str">
+      <c r="L130" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M130" s="1" t="str">
         <f t="shared" si="1"/>
         <v>美妆新秀游客的升星道具</v>
       </c>
-      <c r="P128" s="1">
+      <c r="P130" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
-      <c r="A129" s="1">
+    <row r="131" spans="1:16">
+      <c r="A131" s="1">
         <v>1125506</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C131" s="1">
         <v>1125506</v>
       </c>
-      <c r="D129" s="1" t="str">
+      <c r="D131" s="1" t="str">
         <f t="shared" si="0"/>
         <v>高定女王碎片</v>
       </c>
-      <c r="E129" s="1">
-        <v>2</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G129" s="1">
+      <c r="E131" s="1">
+        <v>2</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G131" s="1">
         <v>7</v>
       </c>
-      <c r="H129" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I129" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K129" s="1">
+      <c r="H131" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I131" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K131" s="1">
         <v>2125506</v>
       </c>
-      <c r="L129" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M129" s="1" t="str">
+      <c r="L131" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M131" s="1" t="str">
         <f t="shared" si="1"/>
         <v>高定女王游客的升星道具</v>
       </c>
-      <c r="P129" s="1">
+      <c r="P131" s="1">
         <v>999999</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16">
-      <c r="A130" s="1">
-        <v>1026001</v>
-      </c>
-      <c r="C130" s="1">
-        <v>1026001</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E130" s="1">
-        <v>2</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G130" s="1">
-        <v>1</v>
-      </c>
-      <c r="H130" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I130" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K130" s="1">
-        <v>2026001</v>
-      </c>
-      <c r="L130" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M130" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="P130" s="1">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16">
-      <c r="A131" s="1">
-        <v>1026002</v>
-      </c>
-      <c r="C131" s="1">
-        <v>1026002</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="E131" s="1">
-        <v>2</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G131" s="1">
-        <v>1</v>
-      </c>
-      <c r="H131" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I131" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K131" s="1">
-        <v>2026002</v>
-      </c>
-      <c r="L131" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M131" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="P131" s="1">
-        <v>-1</v>
       </c>
     </row>
     <row r="132" spans="1:16">
       <c r="A132" s="1">
-        <v>1026101</v>
+        <v>1026001</v>
       </c>
       <c r="C132" s="1">
-        <v>1026101</v>
+        <v>1026001</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E132" s="1">
         <v>2</v>
@@ -7973,7 +7991,7 @@
         <v>45</v>
       </c>
       <c r="G132" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H132" s="1" t="b">
         <v>0</v>
@@ -7985,13 +8003,13 @@
         <v>160</v>
       </c>
       <c r="K132" s="1">
-        <v>2026101</v>
+        <v>2026001</v>
       </c>
       <c r="L132" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="P132" s="1">
         <v>-1</v>
@@ -7999,13 +8017,13 @@
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="1">
-        <v>1026102</v>
+        <v>1026002</v>
       </c>
       <c r="C133" s="1">
-        <v>1026102</v>
+        <v>1026002</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E133" s="1">
         <v>2</v>
@@ -8014,7 +8032,7 @@
         <v>45</v>
       </c>
       <c r="G133" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H133" s="1" t="b">
         <v>0</v>
@@ -8026,13 +8044,13 @@
         <v>160</v>
       </c>
       <c r="K133" s="1">
-        <v>2026102</v>
+        <v>2026002</v>
       </c>
       <c r="L133" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="P133" s="1">
         <v>-1</v>
@@ -8040,13 +8058,13 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="1">
-        <v>1026201</v>
+        <v>1026101</v>
       </c>
       <c r="C134" s="1">
-        <v>1026201</v>
+        <v>1026101</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E134" s="1">
         <v>2</v>
@@ -8055,7 +8073,7 @@
         <v>45</v>
       </c>
       <c r="G134" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H134" s="1" t="b">
         <v>0</v>
@@ -8067,13 +8085,13 @@
         <v>160</v>
       </c>
       <c r="K134" s="1">
-        <v>2026201</v>
+        <v>2026101</v>
       </c>
       <c r="L134" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="P134" s="1">
         <v>-1</v>
@@ -8081,13 +8099,13 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="1">
-        <v>1026202</v>
+        <v>1026102</v>
       </c>
       <c r="C135" s="1">
-        <v>1026202</v>
+        <v>1026102</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
@@ -8096,7 +8114,7 @@
         <v>45</v>
       </c>
       <c r="G135" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H135" s="1" t="b">
         <v>0</v>
@@ -8108,13 +8126,13 @@
         <v>160</v>
       </c>
       <c r="K135" s="1">
-        <v>2026202</v>
+        <v>2026102</v>
       </c>
       <c r="L135" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="P135" s="1">
         <v>-1</v>
@@ -8122,13 +8140,13 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="1">
-        <v>1026301</v>
+        <v>1026201</v>
       </c>
       <c r="C136" s="1">
-        <v>1026301</v>
+        <v>1026201</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -8137,7 +8155,7 @@
         <v>45</v>
       </c>
       <c r="G136" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H136" s="1" t="b">
         <v>0</v>
@@ -8149,13 +8167,13 @@
         <v>160</v>
       </c>
       <c r="K136" s="1">
-        <v>2026301</v>
+        <v>2026201</v>
       </c>
       <c r="L136" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="P136" s="1">
         <v>-1</v>
@@ -8163,13 +8181,13 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="1">
-        <v>1026302</v>
+        <v>1026202</v>
       </c>
       <c r="C137" s="1">
-        <v>1026302</v>
+        <v>1026202</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -8178,7 +8196,7 @@
         <v>45</v>
       </c>
       <c r="G137" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H137" s="1" t="b">
         <v>0</v>
@@ -8190,13 +8208,13 @@
         <v>160</v>
       </c>
       <c r="K137" s="1">
-        <v>2026302</v>
+        <v>2026202</v>
       </c>
       <c r="L137" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="P137" s="1">
         <v>-1</v>
@@ -8204,13 +8222,13 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="1">
-        <v>1026401</v>
+        <v>1026301</v>
       </c>
       <c r="C138" s="1">
-        <v>1026401</v>
+        <v>1026301</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -8219,7 +8237,7 @@
         <v>45</v>
       </c>
       <c r="G138" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H138" s="1" t="b">
         <v>0</v>
@@ -8231,13 +8249,13 @@
         <v>160</v>
       </c>
       <c r="K138" s="1">
-        <v>2026401</v>
+        <v>2026301</v>
       </c>
       <c r="L138" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P138" s="1">
         <v>-1</v>
@@ -8245,13 +8263,13 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="1">
-        <v>1026402</v>
+        <v>1026302</v>
       </c>
       <c r="C139" s="1">
-        <v>1026402</v>
+        <v>1026302</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -8260,7 +8278,7 @@
         <v>45</v>
       </c>
       <c r="G139" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H139" s="1" t="b">
         <v>0</v>
@@ -8272,13 +8290,13 @@
         <v>160</v>
       </c>
       <c r="K139" s="1">
-        <v>2026402</v>
+        <v>2026302</v>
       </c>
       <c r="L139" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="P139" s="1">
         <v>-1</v>
@@ -8286,13 +8304,13 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="1">
-        <v>1027001</v>
+        <v>1026401</v>
       </c>
       <c r="C140" s="1">
-        <v>1027001</v>
+        <v>1026401</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -8301,7 +8319,7 @@
         <v>45</v>
       </c>
       <c r="G140" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H140" s="1" t="b">
         <v>0</v>
@@ -8313,13 +8331,13 @@
         <v>160</v>
       </c>
       <c r="K140" s="1">
-        <v>2027001</v>
+        <v>2026401</v>
       </c>
       <c r="L140" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="P140" s="1">
         <v>-1</v>
@@ -8327,13 +8345,13 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="1">
-        <v>1027002</v>
+        <v>1026402</v>
       </c>
       <c r="C141" s="1">
-        <v>1027002</v>
+        <v>1026402</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -8342,7 +8360,7 @@
         <v>45</v>
       </c>
       <c r="G141" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H141" s="1" t="b">
         <v>0</v>
@@ -8354,13 +8372,13 @@
         <v>160</v>
       </c>
       <c r="K141" s="1">
-        <v>2027002</v>
+        <v>2026402</v>
       </c>
       <c r="L141" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P141" s="1">
         <v>-1</v>
@@ -8368,13 +8386,13 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="1">
-        <v>1027101</v>
+        <v>1027001</v>
       </c>
       <c r="C142" s="1">
-        <v>1027101</v>
+        <v>1027001</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -8383,7 +8401,7 @@
         <v>45</v>
       </c>
       <c r="G142" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142" s="1" t="b">
         <v>0</v>
@@ -8395,13 +8413,13 @@
         <v>160</v>
       </c>
       <c r="K142" s="1">
-        <v>2027101</v>
+        <v>2027001</v>
       </c>
       <c r="L142" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="P142" s="1">
         <v>-1</v>
@@ -8409,13 +8427,13 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="1">
-        <v>1027102</v>
+        <v>1027002</v>
       </c>
       <c r="C143" s="1">
-        <v>1027102</v>
+        <v>1027002</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -8424,7 +8442,7 @@
         <v>45</v>
       </c>
       <c r="G143" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H143" s="1" t="b">
         <v>0</v>
@@ -8436,13 +8454,13 @@
         <v>160</v>
       </c>
       <c r="K143" s="1">
-        <v>2027102</v>
+        <v>2027002</v>
       </c>
       <c r="L143" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P143" s="1">
         <v>-1</v>
@@ -8450,13 +8468,13 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="1">
-        <v>1027201</v>
+        <v>1027101</v>
       </c>
       <c r="C144" s="1">
-        <v>1027201</v>
+        <v>1027101</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -8465,7 +8483,7 @@
         <v>45</v>
       </c>
       <c r="G144" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H144" s="1" t="b">
         <v>0</v>
@@ -8477,13 +8495,13 @@
         <v>160</v>
       </c>
       <c r="K144" s="1">
-        <v>2027201</v>
+        <v>2027101</v>
       </c>
       <c r="L144" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="P144" s="1">
         <v>-1</v>
@@ -8491,13 +8509,13 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="1">
-        <v>1027202</v>
+        <v>1027102</v>
       </c>
       <c r="C145" s="1">
-        <v>1027202</v>
+        <v>1027102</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -8506,7 +8524,7 @@
         <v>45</v>
       </c>
       <c r="G145" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H145" s="1" t="b">
         <v>0</v>
@@ -8518,13 +8536,13 @@
         <v>160</v>
       </c>
       <c r="K145" s="1">
-        <v>2027202</v>
+        <v>2027102</v>
       </c>
       <c r="L145" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="P145" s="1">
         <v>-1</v>
@@ -8532,13 +8550,13 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="1">
-        <v>1027301</v>
+        <v>1027201</v>
       </c>
       <c r="C146" s="1">
-        <v>1027301</v>
+        <v>1027201</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -8547,7 +8565,7 @@
         <v>45</v>
       </c>
       <c r="G146" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H146" s="1" t="b">
         <v>0</v>
@@ -8559,13 +8577,13 @@
         <v>160</v>
       </c>
       <c r="K146" s="1">
-        <v>2027301</v>
+        <v>2027201</v>
       </c>
       <c r="L146" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="P146" s="1">
         <v>-1</v>
@@ -8573,13 +8591,13 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="1">
-        <v>1027302</v>
+        <v>1027202</v>
       </c>
       <c r="C147" s="1">
-        <v>1027302</v>
+        <v>1027202</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -8588,7 +8606,7 @@
         <v>45</v>
       </c>
       <c r="G147" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H147" s="1" t="b">
         <v>0</v>
@@ -8600,13 +8618,13 @@
         <v>160</v>
       </c>
       <c r="K147" s="1">
-        <v>2027302</v>
+        <v>2027202</v>
       </c>
       <c r="L147" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="P147" s="1">
         <v>-1</v>
@@ -8614,13 +8632,13 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" s="1">
-        <v>1027401</v>
+        <v>1027301</v>
       </c>
       <c r="C148" s="1">
-        <v>1027401</v>
+        <v>1027301</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -8629,7 +8647,7 @@
         <v>45</v>
       </c>
       <c r="G148" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H148" s="1" t="b">
         <v>0</v>
@@ -8641,13 +8659,13 @@
         <v>160</v>
       </c>
       <c r="K148" s="1">
-        <v>2027401</v>
+        <v>2027301</v>
       </c>
       <c r="L148" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="P148" s="1">
         <v>-1</v>
@@ -8655,13 +8673,13 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="1">
-        <v>1027402</v>
+        <v>1027302</v>
       </c>
       <c r="C149" s="1">
-        <v>1027402</v>
+        <v>1027302</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -8670,7 +8688,7 @@
         <v>45</v>
       </c>
       <c r="G149" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H149" s="1" t="b">
         <v>0</v>
@@ -8682,13 +8700,13 @@
         <v>160</v>
       </c>
       <c r="K149" s="1">
-        <v>2027402</v>
+        <v>2027302</v>
       </c>
       <c r="L149" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="P149" s="1">
         <v>-1</v>
@@ -8696,13 +8714,13 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="1">
-        <v>1028001</v>
+        <v>1027401</v>
       </c>
       <c r="C150" s="1">
-        <v>1028001</v>
+        <v>1027401</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -8711,7 +8729,7 @@
         <v>45</v>
       </c>
       <c r="G150" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H150" s="1" t="b">
         <v>0</v>
@@ -8723,13 +8741,13 @@
         <v>160</v>
       </c>
       <c r="K150" s="1">
-        <v>2028001</v>
+        <v>2027401</v>
       </c>
       <c r="L150" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P150" s="1">
         <v>-1</v>
@@ -8737,13 +8755,13 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="1">
-        <v>1028002</v>
+        <v>1027402</v>
       </c>
       <c r="C151" s="1">
-        <v>1028002</v>
+        <v>1027402</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -8752,7 +8770,7 @@
         <v>45</v>
       </c>
       <c r="G151" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H151" s="1" t="b">
         <v>0</v>
@@ -8764,13 +8782,13 @@
         <v>160</v>
       </c>
       <c r="K151" s="1">
-        <v>2028002</v>
+        <v>2027402</v>
       </c>
       <c r="L151" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="P151" s="1">
         <v>-1</v>
@@ -8778,13 +8796,13 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="1">
-        <v>1028101</v>
+        <v>1028001</v>
       </c>
       <c r="C152" s="1">
-        <v>1028101</v>
+        <v>1028001</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -8793,7 +8811,7 @@
         <v>45</v>
       </c>
       <c r="G152" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H152" s="1" t="b">
         <v>0</v>
@@ -8805,13 +8823,13 @@
         <v>160</v>
       </c>
       <c r="K152" s="1">
-        <v>2028101</v>
+        <v>2028001</v>
       </c>
       <c r="L152" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="P152" s="1">
         <v>-1</v>
@@ -8819,13 +8837,13 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="1">
-        <v>1028102</v>
+        <v>1028002</v>
       </c>
       <c r="C153" s="1">
-        <v>1028102</v>
+        <v>1028002</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -8834,7 +8852,7 @@
         <v>45</v>
       </c>
       <c r="G153" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H153" s="1" t="b">
         <v>0</v>
@@ -8846,13 +8864,13 @@
         <v>160</v>
       </c>
       <c r="K153" s="1">
-        <v>2028102</v>
+        <v>2028002</v>
       </c>
       <c r="L153" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P153" s="1">
         <v>-1</v>
@@ -8860,13 +8878,13 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="1">
-        <v>1028201</v>
+        <v>1028101</v>
       </c>
       <c r="C154" s="1">
-        <v>1028201</v>
+        <v>1028101</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -8875,7 +8893,7 @@
         <v>45</v>
       </c>
       <c r="G154" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H154" s="1" t="b">
         <v>0</v>
@@ -8887,13 +8905,13 @@
         <v>160</v>
       </c>
       <c r="K154" s="1">
-        <v>2028201</v>
+        <v>2028101</v>
       </c>
       <c r="L154" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="P154" s="1">
         <v>-1</v>
@@ -8901,13 +8919,13 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="1">
-        <v>1028202</v>
+        <v>1028102</v>
       </c>
       <c r="C155" s="1">
-        <v>1028202</v>
+        <v>1028102</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -8916,7 +8934,7 @@
         <v>45</v>
       </c>
       <c r="G155" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H155" s="1" t="b">
         <v>0</v>
@@ -8928,13 +8946,13 @@
         <v>160</v>
       </c>
       <c r="K155" s="1">
-        <v>2028202</v>
+        <v>2028102</v>
       </c>
       <c r="L155" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="P155" s="1">
         <v>-1</v>
@@ -8942,13 +8960,13 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="1">
-        <v>1028301</v>
+        <v>1028201</v>
       </c>
       <c r="C156" s="1">
-        <v>1028301</v>
+        <v>1028201</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -8957,7 +8975,7 @@
         <v>45</v>
       </c>
       <c r="G156" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H156" s="1" t="b">
         <v>0</v>
@@ -8969,13 +8987,13 @@
         <v>160</v>
       </c>
       <c r="K156" s="1">
-        <v>2028301</v>
+        <v>2028201</v>
       </c>
       <c r="L156" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="P156" s="1">
         <v>-1</v>
@@ -8983,13 +9001,13 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="1">
-        <v>1028302</v>
+        <v>1028202</v>
       </c>
       <c r="C157" s="1">
-        <v>1028302</v>
+        <v>1028202</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -8998,7 +9016,7 @@
         <v>45</v>
       </c>
       <c r="G157" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H157" s="1" t="b">
         <v>0</v>
@@ -9010,13 +9028,13 @@
         <v>160</v>
       </c>
       <c r="K157" s="1">
-        <v>2028302</v>
+        <v>2028202</v>
       </c>
       <c r="L157" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="P157" s="1">
         <v>-1</v>
@@ -9024,13 +9042,13 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="1">
-        <v>1028401</v>
+        <v>1028301</v>
       </c>
       <c r="C158" s="1">
-        <v>1028401</v>
+        <v>1028301</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -9039,7 +9057,7 @@
         <v>45</v>
       </c>
       <c r="G158" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H158" s="1" t="b">
         <v>0</v>
@@ -9051,13 +9069,13 @@
         <v>160</v>
       </c>
       <c r="K158" s="1">
-        <v>2028401</v>
+        <v>2028301</v>
       </c>
       <c r="L158" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="P158" s="1">
         <v>-1</v>
@@ -9065,13 +9083,13 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="1">
-        <v>1028402</v>
+        <v>1028302</v>
       </c>
       <c r="C159" s="1">
-        <v>1028402</v>
+        <v>1028302</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -9080,7 +9098,7 @@
         <v>45</v>
       </c>
       <c r="G159" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H159" s="1" t="b">
         <v>0</v>
@@ -9092,13 +9110,13 @@
         <v>160</v>
       </c>
       <c r="K159" s="1">
-        <v>2028402</v>
+        <v>2028302</v>
       </c>
       <c r="L159" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="P159" s="1">
         <v>-1</v>
@@ -9106,14 +9124,13 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" s="1">
-        <v>1126001</v>
+        <v>1028401</v>
       </c>
       <c r="C160" s="1">
-        <v>1126001</v>
-      </c>
-      <c r="D160" s="1" t="str">
-        <f>D130&amp;"碎片"</f>
-        <v>威廉碎片</v>
+        <v>1028401</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -9122,41 +9139,39 @@
         <v>45</v>
       </c>
       <c r="G160" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H160" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K160" s="1">
-        <v>2126001</v>
+        <v>2028401</v>
       </c>
       <c r="L160" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M160" s="1" t="str">
-        <f>D130&amp;"雇员的升星道具"</f>
-        <v>威廉雇员的升星道具</v>
+      <c r="M160" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="P160" s="1">
-        <v>999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="1">
-        <v>1126002</v>
+        <v>1028402</v>
       </c>
       <c r="C161" s="1">
-        <v>1126002</v>
-      </c>
-      <c r="D161" s="1" t="str">
-        <f t="shared" ref="D161:D189" si="2">D131&amp;"碎片"</f>
-        <v>艾拉碎片</v>
+        <v>1028402</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -9165,1326 +9180,1329 @@
         <v>45</v>
       </c>
       <c r="G161" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H161" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K161" s="1">
-        <v>2126002</v>
+        <v>2028402</v>
       </c>
       <c r="L161" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M161" s="1" t="str">
-        <f t="shared" ref="M161:M189" si="3">D131&amp;"雇员的升星道具"</f>
-        <v>艾拉雇员的升星道具</v>
+      <c r="M161" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="P161" s="1">
-        <v>999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="1">
+        <v>1126001</v>
+      </c>
+      <c r="C162" s="1">
+        <v>1126001</v>
+      </c>
+      <c r="D162" s="1" t="str">
+        <f>D132&amp;"碎片"</f>
+        <v>威廉碎片</v>
+      </c>
+      <c r="E162" s="1">
+        <v>2</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G162" s="1">
+        <v>1</v>
+      </c>
+      <c r="H162" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I162" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J162" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K162" s="1">
+        <v>2126001</v>
+      </c>
+      <c r="L162" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M162" s="1" t="str">
+        <f>D132&amp;"雇员的升星道具"</f>
+        <v>威廉雇员的升星道具</v>
+      </c>
+      <c r="P162" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16">
+      <c r="A163" s="1">
+        <v>1126002</v>
+      </c>
+      <c r="C163" s="1">
+        <v>1126002</v>
+      </c>
+      <c r="D163" s="1" t="str">
+        <f t="shared" ref="D163:D191" si="2">D133&amp;"碎片"</f>
+        <v>艾拉碎片</v>
+      </c>
+      <c r="E163" s="1">
+        <v>2</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G163" s="1">
+        <v>1</v>
+      </c>
+      <c r="H163" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I163" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K163" s="1">
+        <v>2126002</v>
+      </c>
+      <c r="L163" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M163" s="1" t="str">
+        <f t="shared" ref="M163:M191" si="3">D133&amp;"雇员的升星道具"</f>
+        <v>艾拉雇员的升星道具</v>
+      </c>
+      <c r="P163" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16">
+      <c r="A164" s="1">
         <v>1126101</v>
       </c>
-      <c r="C162" s="1">
+      <c r="C164" s="1">
         <v>1126101</v>
       </c>
-      <c r="D162" s="1" t="str">
+      <c r="D164" s="1" t="str">
         <f t="shared" si="2"/>
         <v>亨利碎片</v>
       </c>
-      <c r="E162" s="1">
-        <v>2</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G162" s="1">
-        <v>2</v>
-      </c>
-      <c r="H162" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I162" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J162" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K162" s="1">
+      <c r="E164" s="1">
+        <v>2</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G164" s="1">
+        <v>2</v>
+      </c>
+      <c r="H164" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I164" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K164" s="1">
         <v>2126101</v>
       </c>
-      <c r="L162" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M162" s="1" t="str">
+      <c r="L164" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M164" s="1" t="str">
         <f t="shared" si="3"/>
         <v>亨利雇员的升星道具</v>
       </c>
-      <c r="P162" s="1">
+      <c r="P164" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
-      <c r="A163" s="1">
+    <row r="165" spans="1:16">
+      <c r="A165" s="1">
         <v>1126102</v>
       </c>
-      <c r="C163" s="1">
+      <c r="C165" s="1">
         <v>1126102</v>
       </c>
-      <c r="D163" s="1" t="str">
+      <c r="D165" s="1" t="str">
         <f t="shared" si="2"/>
         <v>艾玛碎片</v>
       </c>
-      <c r="E163" s="1">
-        <v>2</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G163" s="1">
-        <v>2</v>
-      </c>
-      <c r="H163" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I163" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K163" s="1">
+      <c r="E165" s="1">
+        <v>2</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G165" s="1">
+        <v>2</v>
+      </c>
+      <c r="H165" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I165" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K165" s="1">
         <v>2126102</v>
       </c>
-      <c r="L163" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M163" s="1" t="str">
+      <c r="L165" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M165" s="1" t="str">
         <f t="shared" si="3"/>
         <v>艾玛雇员的升星道具</v>
       </c>
-      <c r="P163" s="1">
+      <c r="P165" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
-      <c r="A164" s="1">
+    <row r="166" spans="1:16">
+      <c r="A166" s="1">
         <v>1126201</v>
       </c>
-      <c r="C164" s="1">
+      <c r="C166" s="1">
         <v>1126201</v>
       </c>
-      <c r="D164" s="1" t="str">
+      <c r="D166" s="1" t="str">
         <f t="shared" si="2"/>
         <v>乔治碎片</v>
       </c>
-      <c r="E164" s="1">
-        <v>2</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G164" s="1">
+      <c r="E166" s="1">
+        <v>2</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G166" s="1">
         <v>3</v>
       </c>
-      <c r="H164" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I164" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K164" s="1">
+      <c r="H166" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I166" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K166" s="1">
         <v>2126201</v>
       </c>
-      <c r="L164" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M164" s="1" t="str">
+      <c r="L166" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M166" s="1" t="str">
         <f t="shared" si="3"/>
         <v>乔治雇员的升星道具</v>
       </c>
-      <c r="P164" s="1">
+      <c r="P166" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
-      <c r="A165" s="1">
+    <row r="167" spans="1:16">
+      <c r="A167" s="1">
         <v>1126202</v>
       </c>
-      <c r="C165" s="1">
+      <c r="C167" s="1">
         <v>1126202</v>
       </c>
-      <c r="D165" s="1" t="str">
+      <c r="D167" s="1" t="str">
         <f t="shared" si="2"/>
         <v>艾娃碎片</v>
       </c>
-      <c r="E165" s="1">
-        <v>2</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G165" s="1">
+      <c r="E167" s="1">
+        <v>2</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G167" s="1">
         <v>3</v>
       </c>
-      <c r="H165" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I165" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K165" s="1">
+      <c r="H167" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I167" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K167" s="1">
         <v>2126202</v>
       </c>
-      <c r="L165" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M165" s="1" t="str">
+      <c r="L167" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M167" s="1" t="str">
         <f t="shared" si="3"/>
         <v>艾娃雇员的升星道具</v>
       </c>
-      <c r="P165" s="1">
+      <c r="P167" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
-      <c r="A166" s="1">
+    <row r="168" spans="1:16">
+      <c r="A168" s="1">
         <v>1126301</v>
       </c>
-      <c r="C166" s="1">
+      <c r="C168" s="1">
         <v>1126301</v>
       </c>
-      <c r="D166" s="1" t="str">
+      <c r="D168" s="1" t="str">
         <f t="shared" si="2"/>
         <v>亚瑟碎片</v>
       </c>
-      <c r="E166" s="1">
-        <v>2</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G166" s="1">
+      <c r="E168" s="1">
+        <v>2</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G168" s="1">
         <v>4</v>
       </c>
-      <c r="H166" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I166" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K166" s="1">
+      <c r="H168" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I168" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K168" s="1">
         <v>2126301</v>
       </c>
-      <c r="L166" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M166" s="1" t="str">
+      <c r="L168" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M168" s="1" t="str">
         <f t="shared" si="3"/>
         <v>亚瑟雇员的升星道具</v>
       </c>
-      <c r="P166" s="1">
+      <c r="P168" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
-      <c r="A167" s="1">
+    <row r="169" spans="1:16">
+      <c r="A169" s="1">
         <v>1126302</v>
       </c>
-      <c r="C167" s="1">
+      <c r="C169" s="1">
         <v>1126302</v>
       </c>
-      <c r="D167" s="1" t="str">
+      <c r="D169" s="1" t="str">
         <f t="shared" si="2"/>
         <v>安娜碎片</v>
       </c>
-      <c r="E167" s="1">
-        <v>2</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G167" s="1">
+      <c r="E169" s="1">
+        <v>2</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G169" s="1">
         <v>4</v>
       </c>
-      <c r="H167" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I167" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J167" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K167" s="1">
+      <c r="H169" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I169" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K169" s="1">
         <v>2126302</v>
       </c>
-      <c r="L167" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M167" s="1" t="str">
+      <c r="L169" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M169" s="1" t="str">
         <f t="shared" si="3"/>
         <v>安娜雇员的升星道具</v>
       </c>
-      <c r="P167" s="1">
+      <c r="P169" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
-      <c r="A168" s="1">
+    <row r="170" spans="1:16">
+      <c r="A170" s="1">
         <v>1126401</v>
       </c>
-      <c r="C168" s="1">
+      <c r="C170" s="1">
         <v>1126401</v>
       </c>
-      <c r="D168" s="1" t="str">
+      <c r="D170" s="1" t="str">
         <f t="shared" si="2"/>
         <v>马修碎片</v>
       </c>
-      <c r="E168" s="1">
-        <v>2</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G168" s="1">
+      <c r="E170" s="1">
+        <v>2</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G170" s="1">
         <v>7</v>
       </c>
-      <c r="H168" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I168" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K168" s="1">
+      <c r="H170" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I170" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K170" s="1">
         <v>2126401</v>
       </c>
-      <c r="L168" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M168" s="1" t="str">
+      <c r="L170" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M170" s="1" t="str">
         <f t="shared" si="3"/>
         <v>马修雇员的升星道具</v>
       </c>
-      <c r="P168" s="1">
+      <c r="P170" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
-      <c r="A169" s="1">
+    <row r="171" spans="1:16">
+      <c r="A171" s="1">
         <v>1126402</v>
       </c>
-      <c r="C169" s="1">
+      <c r="C171" s="1">
         <v>1126402</v>
       </c>
-      <c r="D169" s="1" t="str">
+      <c r="D171" s="1" t="str">
         <f t="shared" si="2"/>
         <v>哈珀碎片</v>
       </c>
-      <c r="E169" s="1">
-        <v>2</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G169" s="1">
+      <c r="E171" s="1">
+        <v>2</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G171" s="1">
         <v>7</v>
       </c>
-      <c r="H169" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I169" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J169" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K169" s="1">
+      <c r="H171" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I171" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K171" s="1">
         <v>2126402</v>
       </c>
-      <c r="L169" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M169" s="1" t="str">
+      <c r="L171" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M171" s="1" t="str">
         <f t="shared" si="3"/>
         <v>哈珀雇员的升星道具</v>
       </c>
-      <c r="P169" s="1">
+      <c r="P171" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
-      <c r="A170" s="1">
+    <row r="172" spans="1:16">
+      <c r="A172" s="1">
         <v>1127001</v>
       </c>
-      <c r="C170" s="1">
+      <c r="C172" s="1">
         <v>1127001</v>
       </c>
-      <c r="D170" s="1" t="str">
+      <c r="D172" s="1" t="str">
         <f t="shared" si="2"/>
         <v>拉斐尔碎片</v>
       </c>
-      <c r="E170" s="1">
-        <v>2</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G170" s="1">
-        <v>1</v>
-      </c>
-      <c r="H170" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I170" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J170" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K170" s="1">
+      <c r="E172" s="1">
+        <v>2</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G172" s="1">
+        <v>1</v>
+      </c>
+      <c r="H172" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I172" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J172" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K172" s="1">
         <v>2127001</v>
       </c>
-      <c r="L170" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M170" s="1" t="str">
+      <c r="L172" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M172" s="1" t="str">
         <f t="shared" si="3"/>
         <v>拉斐尔雇员的升星道具</v>
       </c>
-      <c r="P170" s="1">
+      <c r="P172" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
-      <c r="A171" s="1">
+    <row r="173" spans="1:16">
+      <c r="A173" s="1">
         <v>1127002</v>
       </c>
-      <c r="C171" s="1">
+      <c r="C173" s="1">
         <v>1127002</v>
       </c>
-      <c r="D171" s="1" t="str">
+      <c r="D173" s="1" t="str">
         <f t="shared" si="2"/>
         <v>伊芙琳碎片</v>
       </c>
-      <c r="E171" s="1">
-        <v>2</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G171" s="1">
-        <v>1</v>
-      </c>
-      <c r="H171" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I171" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J171" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K171" s="1">
+      <c r="E173" s="1">
+        <v>2</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G173" s="1">
+        <v>1</v>
+      </c>
+      <c r="H173" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I173" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K173" s="1">
         <v>2127002</v>
       </c>
-      <c r="L171" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M171" s="1" t="str">
+      <c r="L173" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M173" s="1" t="str">
         <f t="shared" si="3"/>
         <v>伊芙琳雇员的升星道具</v>
       </c>
-      <c r="P171" s="1">
+      <c r="P173" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
-      <c r="A172" s="1">
+    <row r="174" spans="1:16">
+      <c r="A174" s="1">
         <v>1127101</v>
       </c>
-      <c r="C172" s="1">
+      <c r="C174" s="1">
         <v>1127101</v>
       </c>
-      <c r="D172" s="1" t="str">
+      <c r="D174" s="1" t="str">
         <f t="shared" si="2"/>
         <v>埃米尔碎片</v>
       </c>
-      <c r="E172" s="1">
-        <v>2</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G172" s="1">
-        <v>2</v>
-      </c>
-      <c r="H172" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I172" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K172" s="1">
+      <c r="E174" s="1">
+        <v>2</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G174" s="1">
+        <v>2</v>
+      </c>
+      <c r="H174" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I174" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K174" s="1">
         <v>2127101</v>
       </c>
-      <c r="L172" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M172" s="1" t="str">
+      <c r="L174" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M174" s="1" t="str">
         <f t="shared" si="3"/>
         <v>埃米尔雇员的升星道具</v>
       </c>
-      <c r="P172" s="1">
+      <c r="P174" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
-      <c r="A173" s="1">
+    <row r="175" spans="1:16">
+      <c r="A175" s="1">
         <v>1127102</v>
       </c>
-      <c r="C173" s="1">
+      <c r="C175" s="1">
         <v>1127102</v>
       </c>
-      <c r="D173" s="1" t="str">
+      <c r="D175" s="1" t="str">
         <f t="shared" si="2"/>
         <v>夏洛特碎片</v>
       </c>
-      <c r="E173" s="1">
-        <v>2</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G173" s="1">
-        <v>2</v>
-      </c>
-      <c r="H173" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I173" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J173" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K173" s="1">
+      <c r="E175" s="1">
+        <v>2</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G175" s="1">
+        <v>2</v>
+      </c>
+      <c r="H175" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I175" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K175" s="1">
         <v>2127102</v>
       </c>
-      <c r="L173" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M173" s="1" t="str">
+      <c r="L175" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M175" s="1" t="str">
         <f t="shared" si="3"/>
         <v>夏洛特雇员的升星道具</v>
       </c>
-      <c r="P173" s="1">
+      <c r="P175" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
-      <c r="A174" s="1">
+    <row r="176" spans="1:16">
+      <c r="A176" s="1">
         <v>1127201</v>
       </c>
-      <c r="C174" s="1">
+      <c r="C176" s="1">
         <v>1127201</v>
       </c>
-      <c r="D174" s="1" t="str">
+      <c r="D176" s="1" t="str">
         <f t="shared" si="2"/>
         <v>雷蒙德碎片</v>
       </c>
-      <c r="E174" s="1">
-        <v>2</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G174" s="1">
+      <c r="E176" s="1">
+        <v>2</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G176" s="1">
         <v>3</v>
       </c>
-      <c r="H174" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I174" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J174" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K174" s="1">
+      <c r="H176" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I176" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K176" s="1">
         <v>2127201</v>
       </c>
-      <c r="L174" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M174" s="1" t="str">
+      <c r="L176" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M176" s="1" t="str">
         <f t="shared" si="3"/>
         <v>雷蒙德雇员的升星道具</v>
       </c>
-      <c r="P174" s="1">
+      <c r="P176" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
-      <c r="A175" s="1">
+    <row r="177" spans="1:16">
+      <c r="A177" s="1">
         <v>1127202</v>
       </c>
-      <c r="C175" s="1">
+      <c r="C177" s="1">
         <v>1127202</v>
       </c>
-      <c r="D175" s="1" t="str">
+      <c r="D177" s="1" t="str">
         <f t="shared" si="2"/>
         <v>斯嘉丽碎片</v>
       </c>
-      <c r="E175" s="1">
-        <v>2</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G175" s="1">
+      <c r="E177" s="1">
+        <v>2</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G177" s="1">
         <v>3</v>
       </c>
-      <c r="H175" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I175" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J175" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K175" s="1">
+      <c r="H177" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I177" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K177" s="1">
         <v>2127202</v>
       </c>
-      <c r="L175" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M175" s="1" t="str">
+      <c r="L177" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M177" s="1" t="str">
         <f t="shared" si="3"/>
         <v>斯嘉丽雇员的升星道具</v>
       </c>
-      <c r="P175" s="1">
+      <c r="P177" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
-      <c r="A176" s="1">
+    <row r="178" spans="1:16">
+      <c r="A178" s="1">
         <v>1127301</v>
       </c>
-      <c r="C176" s="1">
+      <c r="C178" s="1">
         <v>1127301</v>
       </c>
-      <c r="D176" s="1" t="str">
+      <c r="D178" s="1" t="str">
         <f t="shared" si="2"/>
         <v>丹尼尔碎片</v>
       </c>
-      <c r="E176" s="1">
-        <v>2</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G176" s="1">
+      <c r="E178" s="1">
+        <v>2</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G178" s="1">
         <v>4</v>
       </c>
-      <c r="H176" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I176" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J176" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K176" s="1">
+      <c r="H178" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I178" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K178" s="1">
         <v>2127301</v>
       </c>
-      <c r="L176" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M176" s="1" t="str">
+      <c r="L178" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M178" s="1" t="str">
         <f t="shared" si="3"/>
         <v>丹尼尔雇员的升星道具</v>
       </c>
-      <c r="P176" s="1">
+      <c r="P178" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
-      <c r="A177" s="1">
+    <row r="179" spans="1:16">
+      <c r="A179" s="1">
         <v>1127302</v>
       </c>
-      <c r="C177" s="1">
+      <c r="C179" s="1">
         <v>1127302</v>
       </c>
-      <c r="D177" s="1" t="str">
+      <c r="D179" s="1" t="str">
         <f t="shared" si="2"/>
         <v>莉莉安碎片</v>
       </c>
-      <c r="E177" s="1">
-        <v>2</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G177" s="1">
+      <c r="E179" s="1">
+        <v>2</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G179" s="1">
         <v>4</v>
       </c>
-      <c r="H177" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I177" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K177" s="1">
+      <c r="H179" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I179" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K179" s="1">
         <v>2127302</v>
       </c>
-      <c r="L177" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M177" s="1" t="str">
+      <c r="L179" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M179" s="1" t="str">
         <f t="shared" si="3"/>
         <v>莉莉安雇员的升星道具</v>
       </c>
-      <c r="P177" s="1">
+      <c r="P179" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
-      <c r="A178" s="1">
+    <row r="180" spans="1:16">
+      <c r="A180" s="1">
         <v>1127401</v>
       </c>
-      <c r="C178" s="1">
+      <c r="C180" s="1">
         <v>1127401</v>
       </c>
-      <c r="D178" s="1" t="str">
+      <c r="D180" s="1" t="str">
         <f t="shared" si="2"/>
         <v>卢卡斯碎片</v>
       </c>
-      <c r="E178" s="1">
-        <v>2</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G178" s="1">
+      <c r="E180" s="1">
+        <v>2</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G180" s="1">
         <v>7</v>
       </c>
-      <c r="H178" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I178" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K178" s="1">
+      <c r="H180" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I180" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K180" s="1">
         <v>2127401</v>
       </c>
-      <c r="L178" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M178" s="1" t="str">
+      <c r="L180" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M180" s="1" t="str">
         <f t="shared" si="3"/>
         <v>卢卡斯雇员的升星道具</v>
       </c>
-      <c r="P178" s="1">
+      <c r="P180" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
-      <c r="A179" s="1">
+    <row r="181" spans="1:16">
+      <c r="A181" s="1">
         <v>1127402</v>
       </c>
-      <c r="C179" s="1">
+      <c r="C181" s="1">
         <v>1127402</v>
       </c>
-      <c r="D179" s="1" t="str">
+      <c r="D181" s="1" t="str">
         <f t="shared" si="2"/>
         <v>克拉拉碎片</v>
       </c>
-      <c r="E179" s="1">
-        <v>2</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G179" s="1">
+      <c r="E181" s="1">
+        <v>2</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G181" s="1">
         <v>7</v>
       </c>
-      <c r="H179" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I179" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J179" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K179" s="1">
+      <c r="H181" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I181" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K181" s="1">
         <v>2127402</v>
       </c>
-      <c r="L179" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M179" s="1" t="str">
+      <c r="L181" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M181" s="1" t="str">
         <f t="shared" si="3"/>
         <v>克拉拉雇员的升星道具</v>
       </c>
-      <c r="P179" s="1">
+      <c r="P181" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
-      <c r="A180" s="1">
+    <row r="182" spans="1:16">
+      <c r="A182" s="1">
         <v>1128001</v>
       </c>
-      <c r="C180" s="1">
+      <c r="C182" s="1">
         <v>1128001</v>
       </c>
-      <c r="D180" s="1" t="str">
+      <c r="D182" s="1" t="str">
         <f t="shared" si="2"/>
         <v>尼古拉斯碎片</v>
       </c>
-      <c r="E180" s="1">
-        <v>2</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G180" s="1">
-        <v>1</v>
-      </c>
-      <c r="H180" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I180" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J180" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K180" s="1">
+      <c r="E182" s="1">
+        <v>2</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G182" s="1">
+        <v>1</v>
+      </c>
+      <c r="H182" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I182" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K182" s="1">
         <v>2128001</v>
       </c>
-      <c r="L180" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M180" s="1" t="str">
+      <c r="L182" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M182" s="1" t="str">
         <f t="shared" si="3"/>
         <v>尼古拉斯雇员的升星道具</v>
       </c>
-      <c r="P180" s="1">
+      <c r="P182" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
-      <c r="A181" s="1">
+    <row r="183" spans="1:16">
+      <c r="A183" s="1">
         <v>1128002</v>
       </c>
-      <c r="C181" s="1">
+      <c r="C183" s="1">
         <v>1128002</v>
       </c>
-      <c r="D181" s="1" t="str">
+      <c r="D183" s="1" t="str">
         <f t="shared" si="2"/>
         <v>奥利维亚碎片</v>
       </c>
-      <c r="E181" s="1">
-        <v>2</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G181" s="1">
-        <v>1</v>
-      </c>
-      <c r="H181" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I181" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J181" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K181" s="1">
+      <c r="E183" s="1">
+        <v>2</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G183" s="1">
+        <v>1</v>
+      </c>
+      <c r="H183" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K183" s="1">
         <v>2128002</v>
       </c>
-      <c r="L181" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M181" s="1" t="str">
+      <c r="L183" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M183" s="1" t="str">
         <f t="shared" si="3"/>
         <v>奥利维亚雇员的升星道具</v>
       </c>
-      <c r="P181" s="1">
+      <c r="P183" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
-      <c r="A182" s="1">
+    <row r="184" spans="1:16">
+      <c r="A184" s="1">
         <v>1128101</v>
       </c>
-      <c r="C182" s="1">
+      <c r="C184" s="1">
         <v>1128101</v>
       </c>
-      <c r="D182" s="1" t="str">
+      <c r="D184" s="1" t="str">
         <f t="shared" si="2"/>
         <v>亚历山大碎片</v>
       </c>
-      <c r="E182" s="1">
-        <v>2</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G182" s="1">
-        <v>2</v>
-      </c>
-      <c r="H182" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I182" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J182" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K182" s="1">
+      <c r="E184" s="1">
+        <v>2</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G184" s="1">
+        <v>2</v>
+      </c>
+      <c r="H184" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I184" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K184" s="1">
         <v>2128101</v>
       </c>
-      <c r="L182" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M182" s="1" t="str">
+      <c r="L184" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M184" s="1" t="str">
         <f t="shared" si="3"/>
         <v>亚历山大雇员的升星道具</v>
       </c>
-      <c r="P182" s="1">
+      <c r="P184" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
-      <c r="A183" s="1">
+    <row r="185" spans="1:16">
+      <c r="A185" s="1">
         <v>1128102</v>
       </c>
-      <c r="C183" s="1">
+      <c r="C185" s="1">
         <v>1128102</v>
       </c>
-      <c r="D183" s="1" t="str">
+      <c r="D185" s="1" t="str">
         <f t="shared" si="2"/>
         <v>玛格丽特碎片</v>
       </c>
-      <c r="E183" s="1">
-        <v>2</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G183" s="1">
-        <v>2</v>
-      </c>
-      <c r="H183" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I183" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J183" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K183" s="1">
+      <c r="E185" s="1">
+        <v>2</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G185" s="1">
+        <v>2</v>
+      </c>
+      <c r="H185" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I185" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J185" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K185" s="1">
         <v>2128102</v>
       </c>
-      <c r="L183" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M183" s="1" t="str">
+      <c r="L185" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M185" s="1" t="str">
         <f t="shared" si="3"/>
         <v>玛格丽特雇员的升星道具</v>
       </c>
-      <c r="P183" s="1">
+      <c r="P185" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
-      <c r="A184" s="1">
+    <row r="186" spans="1:16">
+      <c r="A186" s="1">
         <v>1128201</v>
       </c>
-      <c r="C184" s="1">
+      <c r="C186" s="1">
         <v>1128201</v>
       </c>
-      <c r="D184" s="1" t="str">
+      <c r="D186" s="1" t="str">
         <f t="shared" si="2"/>
         <v>奥古斯特碎片</v>
       </c>
-      <c r="E184" s="1">
-        <v>2</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G184" s="1">
+      <c r="E186" s="1">
+        <v>2</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G186" s="1">
         <v>3</v>
       </c>
-      <c r="H184" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I184" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J184" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K184" s="1">
+      <c r="H186" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I186" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K186" s="1">
         <v>2128201</v>
       </c>
-      <c r="L184" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M184" s="1" t="str">
+      <c r="L186" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M186" s="1" t="str">
         <f t="shared" si="3"/>
         <v>奥古斯特雇员的升星道具</v>
       </c>
-      <c r="P184" s="1">
+      <c r="P186" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
-      <c r="A185" s="1">
+    <row r="187" spans="1:16">
+      <c r="A187" s="1">
         <v>1128202</v>
       </c>
-      <c r="C185" s="1">
+      <c r="C187" s="1">
         <v>1128202</v>
       </c>
-      <c r="D185" s="1" t="str">
+      <c r="D187" s="1" t="str">
         <f t="shared" si="2"/>
         <v>维奥莱特碎片</v>
       </c>
-      <c r="E185" s="1">
-        <v>2</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G185" s="1">
+      <c r="E187" s="1">
+        <v>2</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G187" s="1">
         <v>3</v>
       </c>
-      <c r="H185" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I185" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J185" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K185" s="1">
+      <c r="H187" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I187" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J187" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K187" s="1">
         <v>2128202</v>
       </c>
-      <c r="L185" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M185" s="1" t="str">
+      <c r="L187" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M187" s="1" t="str">
         <f t="shared" si="3"/>
         <v>维奥莱特雇员的升星道具</v>
       </c>
-      <c r="P185" s="1">
+      <c r="P187" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
-      <c r="A186" s="1">
+    <row r="188" spans="1:16">
+      <c r="A188" s="1">
         <v>1128301</v>
       </c>
-      <c r="C186" s="1">
+      <c r="C188" s="1">
         <v>1128301</v>
       </c>
-      <c r="D186" s="1" t="str">
+      <c r="D188" s="1" t="str">
         <f t="shared" si="2"/>
         <v>费利克斯碎片</v>
       </c>
-      <c r="E186" s="1">
-        <v>2</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G186" s="1">
+      <c r="E188" s="1">
+        <v>2</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G188" s="1">
         <v>4</v>
       </c>
-      <c r="H186" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I186" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J186" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K186" s="1">
+      <c r="H188" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I188" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K188" s="1">
         <v>2128301</v>
       </c>
-      <c r="L186" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M186" s="1" t="str">
+      <c r="L188" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M188" s="1" t="str">
         <f t="shared" si="3"/>
         <v>费利克斯雇员的升星道具</v>
       </c>
-      <c r="P186" s="1">
+      <c r="P188" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
-      <c r="A187" s="1">
+    <row r="189" spans="1:16">
+      <c r="A189" s="1">
         <v>1128302</v>
       </c>
-      <c r="C187" s="1">
+      <c r="C189" s="1">
         <v>1128302</v>
       </c>
-      <c r="D187" s="1" t="str">
+      <c r="D189" s="1" t="str">
         <f t="shared" si="2"/>
         <v>维多利亚碎片</v>
       </c>
-      <c r="E187" s="1">
-        <v>2</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G187" s="1">
+      <c r="E189" s="1">
+        <v>2</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G189" s="1">
         <v>4</v>
       </c>
-      <c r="H187" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I187" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J187" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K187" s="1">
+      <c r="H189" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I189" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J189" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K189" s="1">
         <v>2128302</v>
       </c>
-      <c r="L187" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M187" s="1" t="str">
+      <c r="L189" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M189" s="1" t="str">
         <f t="shared" si="3"/>
         <v>维多利亚雇员的升星道具</v>
       </c>
-      <c r="P187" s="1">
+      <c r="P189" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
-      <c r="A188" s="1">
+    <row r="190" spans="1:16">
+      <c r="A190" s="1">
         <v>1128401</v>
       </c>
-      <c r="C188" s="1">
+      <c r="C190" s="1">
         <v>1128401</v>
       </c>
-      <c r="D188" s="1" t="str">
+      <c r="D190" s="1" t="str">
         <f t="shared" si="2"/>
         <v>阿尔弗雷德碎片</v>
       </c>
-      <c r="E188" s="1">
-        <v>2</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G188" s="1">
+      <c r="E190" s="1">
+        <v>2</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G190" s="1">
         <v>7</v>
       </c>
-      <c r="H188" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I188" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J188" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K188" s="1">
+      <c r="H190" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I190" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J190" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K190" s="1">
         <v>2128401</v>
       </c>
-      <c r="L188" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M188" s="1" t="str">
+      <c r="L190" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M190" s="1" t="str">
         <f t="shared" si="3"/>
         <v>阿尔弗雷德雇员的升星道具</v>
       </c>
-      <c r="P188" s="1">
+      <c r="P190" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
-      <c r="A189" s="1">
+    <row r="191" spans="1:16">
+      <c r="A191" s="1">
         <v>1128402</v>
       </c>
-      <c r="C189" s="1">
+      <c r="C191" s="1">
         <v>1128402</v>
       </c>
-      <c r="D189" s="1" t="str">
+      <c r="D191" s="1" t="str">
         <f t="shared" si="2"/>
         <v>伊丽莎白碎片</v>
       </c>
-      <c r="E189" s="1">
-        <v>2</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G189" s="1">
+      <c r="E191" s="1">
+        <v>2</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G191" s="1">
         <v>7</v>
       </c>
-      <c r="H189" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I189" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J189" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K189" s="1">
+      <c r="H191" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I191" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K191" s="1">
         <v>2128402</v>
       </c>
-      <c r="L189" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M189" s="1" t="str">
+      <c r="L191" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M191" s="1" t="str">
         <f t="shared" si="3"/>
         <v>伊丽莎白雇员的升星道具</v>
       </c>
-      <c r="P189" s="1">
+      <c r="P191" s="1">
         <v>999999</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16">
-      <c r="A190" s="1">
-        <v>1200001</v>
-      </c>
-      <c r="C190" s="1">
-        <v>1200001</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E190" s="1">
-        <v>2</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G190" s="1">
-        <v>1</v>
-      </c>
-      <c r="H190" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I190" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J190" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K190" s="1">
-        <v>2200001</v>
-      </c>
-      <c r="L190" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M190" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="P190" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16">
-      <c r="A191" s="1">
-        <v>1200002</v>
-      </c>
-      <c r="C191" s="1">
-        <v>1200002</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E191" s="1">
-        <v>2</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G191" s="1">
-        <v>1</v>
-      </c>
-      <c r="H191" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I191" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J191" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K191" s="1">
-        <v>2200002</v>
-      </c>
-      <c r="L191" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M191" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="P191" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:16">
       <c r="A192" s="1">
-        <v>1200003</v>
+        <v>1200001</v>
       </c>
       <c r="C192" s="1">
-        <v>1200003</v>
+        <v>1200001</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E192" s="1">
         <v>2</v>
@@ -10505,13 +10523,13 @@
         <v>160</v>
       </c>
       <c r="K192" s="1">
-        <v>2200003</v>
+        <v>2200001</v>
       </c>
       <c r="L192" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P192" s="1">
         <v>1</v>
@@ -10519,13 +10537,13 @@
     </row>
     <row r="193" spans="1:16">
       <c r="A193" s="1">
-        <v>1200004</v>
+        <v>1200002</v>
       </c>
       <c r="C193" s="1">
-        <v>1200004</v>
+        <v>1200002</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E193" s="1">
         <v>2</v>
@@ -10546,13 +10564,13 @@
         <v>160</v>
       </c>
       <c r="K193" s="1">
-        <v>2200004</v>
+        <v>2200002</v>
       </c>
       <c r="L193" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P193" s="1">
         <v>1</v>
@@ -10560,13 +10578,13 @@
     </row>
     <row r="194" spans="1:16">
       <c r="A194" s="1">
-        <v>1200005</v>
+        <v>1200003</v>
       </c>
       <c r="C194" s="1">
-        <v>1200005</v>
+        <v>1200003</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E194" s="1">
         <v>2</v>
@@ -10587,13 +10605,13 @@
         <v>160</v>
       </c>
       <c r="K194" s="1">
-        <v>2200005</v>
+        <v>2200003</v>
       </c>
       <c r="L194" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P194" s="1">
         <v>1</v>
@@ -10601,13 +10619,13 @@
     </row>
     <row r="195" spans="1:16">
       <c r="A195" s="1">
-        <v>1200006</v>
+        <v>1200004</v>
       </c>
       <c r="C195" s="1">
-        <v>1200006</v>
+        <v>1200004</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E195" s="1">
         <v>2</v>
@@ -10628,13 +10646,13 @@
         <v>160</v>
       </c>
       <c r="K195" s="1">
-        <v>2200006</v>
+        <v>2200004</v>
       </c>
       <c r="L195" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="P195" s="1">
         <v>1</v>
@@ -10642,13 +10660,13 @@
     </row>
     <row r="196" spans="1:16">
       <c r="A196" s="1">
-        <v>1200007</v>
+        <v>1200005</v>
       </c>
       <c r="C196" s="1">
-        <v>1200007</v>
+        <v>1200005</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E196" s="1">
         <v>2</v>
@@ -10669,13 +10687,13 @@
         <v>160</v>
       </c>
       <c r="K196" s="1">
-        <v>2200007</v>
+        <v>2200005</v>
       </c>
       <c r="L196" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M196" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="P196" s="1">
         <v>1</v>
@@ -10683,13 +10701,13 @@
     </row>
     <row r="197" spans="1:16">
       <c r="A197" s="1">
-        <v>1200008</v>
+        <v>1200006</v>
       </c>
       <c r="C197" s="1">
-        <v>1200008</v>
+        <v>1200006</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E197" s="1">
         <v>2</v>
@@ -10710,13 +10728,13 @@
         <v>160</v>
       </c>
       <c r="K197" s="1">
-        <v>2200008</v>
+        <v>2200006</v>
       </c>
       <c r="L197" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="P197" s="1">
         <v>1</v>
@@ -10724,13 +10742,13 @@
     </row>
     <row r="198" spans="1:16">
       <c r="A198" s="1">
-        <v>1200009</v>
+        <v>1200007</v>
       </c>
       <c r="C198" s="1">
-        <v>1200009</v>
+        <v>1200007</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E198" s="1">
         <v>2</v>
@@ -10751,13 +10769,13 @@
         <v>160</v>
       </c>
       <c r="K198" s="1">
-        <v>2200009</v>
+        <v>2200007</v>
       </c>
       <c r="L198" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P198" s="1">
         <v>1</v>
@@ -10765,42 +10783,124 @@
     </row>
     <row r="199" spans="1:16">
       <c r="A199" s="1">
+        <v>1200008</v>
+      </c>
+      <c r="C199" s="1">
+        <v>1200008</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E199" s="1">
+        <v>2</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G199" s="1">
+        <v>1</v>
+      </c>
+      <c r="H199" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I199" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J199" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K199" s="1">
+        <v>2200008</v>
+      </c>
+      <c r="L199" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M199" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="P199" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16">
+      <c r="A200" s="1">
+        <v>1200009</v>
+      </c>
+      <c r="C200" s="1">
+        <v>1200009</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E200" s="1">
+        <v>2</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G200" s="1">
+        <v>1</v>
+      </c>
+      <c r="H200" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I200" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J200" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K200" s="1">
+        <v>2200009</v>
+      </c>
+      <c r="L200" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M200" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="P200" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16">
+      <c r="A201" s="1">
         <v>1200010</v>
       </c>
-      <c r="C199" s="1">
+      <c r="C201" s="1">
         <v>1200010</v>
       </c>
-      <c r="D199" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E199" s="1">
-        <v>2</v>
-      </c>
-      <c r="F199" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G199" s="1">
-        <v>1</v>
-      </c>
-      <c r="H199" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I199" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J199" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K199" s="1">
+      <c r="D201" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E201" s="1">
+        <v>2</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G201" s="1">
+        <v>1</v>
+      </c>
+      <c r="H201" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I201" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K201" s="1">
         <v>2200010</v>
       </c>
-      <c r="L199" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M199" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="P199" s="1">
+      <c r="L201" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M201" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="P201" s="1">
         <v>1</v>
       </c>
     </row>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -320,7 +320,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="264">
   <si>
     <t>道具ID</t>
   </si>
@@ -824,6 +824,9 @@
   </si>
   <si>
     <t>研究点</t>
+  </si>
+  <si>
+    <t>daoju_yjy.png</t>
   </si>
   <si>
     <t>升级游戏特殊词条</t>
@@ -1286,12 +1289,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5070,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="K62" s="1">
         <v>2024005</v>
@@ -5079,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P62" s="1">
         <v>-1</v>
@@ -5093,7 +5096,7 @@
         <v>1024006</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
@@ -5120,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P63" s="1">
         <v>-1</v>
@@ -5134,7 +5137,7 @@
         <v>1024007</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
@@ -5152,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K64" s="1">
         <v>2024007</v>
@@ -5161,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P64" s="1">
         <v>999999999</v>
@@ -5175,7 +5178,7 @@
         <v>1024008</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
@@ -5202,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P65" s="1">
         <v>999999</v>
@@ -5216,7 +5219,7 @@
         <v>1024009</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
@@ -5243,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P66" s="1">
         <v>999999</v>
@@ -5257,7 +5260,7 @@
         <v>1024010</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
@@ -5284,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P67" s="1">
         <v>999999</v>
@@ -5298,7 +5301,7 @@
         <v>1024011</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
@@ -5325,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P68" s="1">
         <v>-1</v>
@@ -5339,7 +5342,7 @@
         <v>1024012</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
@@ -5366,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P69" s="1">
         <v>-1</v>
@@ -5380,7 +5383,7 @@
         <v>1024013</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
@@ -5407,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P70" s="1">
         <v>999999</v>
@@ -5421,7 +5424,7 @@
         <v>1024014</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
@@ -5448,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P71" s="1">
         <v>999999</v>
@@ -5462,7 +5465,7 @@
         <v>1025101</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
@@ -5489,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P72" s="1">
         <v>-1</v>
@@ -5503,7 +5506,7 @@
         <v>1025102</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -5530,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P73" s="1">
         <v>-1</v>
@@ -5544,7 +5547,7 @@
         <v>1025103</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -5571,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P74" s="1">
         <v>-1</v>
@@ -5585,7 +5588,7 @@
         <v>1025104</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -5612,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P75" s="1">
         <v>-1</v>
@@ -5626,7 +5629,7 @@
         <v>1025105</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
@@ -5653,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P76" s="1">
         <v>-1</v>
@@ -5667,7 +5670,7 @@
         <v>1025106</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -5694,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P77" s="1">
         <v>-1</v>
@@ -5708,7 +5711,7 @@
         <v>1025201</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -5735,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P78" s="1">
         <v>-1</v>
@@ -5749,7 +5752,7 @@
         <v>1025202</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
@@ -5776,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P79" s="1">
         <v>-1</v>
@@ -5790,7 +5793,7 @@
         <v>1025203</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -5817,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P80" s="1">
         <v>-1</v>
@@ -5831,7 +5834,7 @@
         <v>1025204</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -5858,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P81" s="1">
         <v>-1</v>
@@ -5872,7 +5875,7 @@
         <v>1025205</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -5899,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P82" s="1">
         <v>-1</v>
@@ -5913,7 +5916,7 @@
         <v>1025206</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -5940,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P83" s="1">
         <v>-1</v>
@@ -5954,7 +5957,7 @@
         <v>1025301</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -5981,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P84" s="1">
         <v>-1</v>
@@ -5995,7 +5998,7 @@
         <v>1025302</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -6022,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P85" s="1">
         <v>-1</v>
@@ -6036,7 +6039,7 @@
         <v>1025303</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
@@ -6063,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P86" s="1">
         <v>-1</v>
@@ -6077,7 +6080,7 @@
         <v>1025304</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -6104,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P87" s="1">
         <v>-1</v>
@@ -6118,7 +6121,7 @@
         <v>1025305</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -6145,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P88" s="1">
         <v>-1</v>
@@ -6159,7 +6162,7 @@
         <v>1025306</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -6186,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P89" s="1">
         <v>-1</v>
@@ -6200,7 +6203,7 @@
         <v>1025401</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -6227,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P90" s="1">
         <v>-1</v>
@@ -6241,7 +6244,7 @@
         <v>1025402</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
@@ -6268,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P91" s="1">
         <v>-1</v>
@@ -6282,7 +6285,7 @@
         <v>1025403</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -6309,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P92" s="1">
         <v>-1</v>
@@ -6323,7 +6326,7 @@
         <v>1025404</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
@@ -6350,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P93" s="1">
         <v>-1</v>
@@ -6364,7 +6367,7 @@
         <v>1025405</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -6391,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P94" s="1">
         <v>-1</v>
@@ -6405,7 +6408,7 @@
         <v>1025406</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -6432,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P95" s="1">
         <v>-1</v>
@@ -6446,7 +6449,7 @@
         <v>1025501</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -6473,7 +6476,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P96" s="1">
         <v>-1</v>
@@ -6487,7 +6490,7 @@
         <v>1025502</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -6514,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P97" s="1">
         <v>-1</v>
@@ -6528,7 +6531,7 @@
         <v>1025503</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -6555,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P98" s="1">
         <v>-1</v>
@@ -6569,7 +6572,7 @@
         <v>1025504</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -6596,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P99" s="1">
         <v>-1</v>
@@ -6610,7 +6613,7 @@
         <v>1025505</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -6637,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P100" s="1">
         <v>-1</v>
@@ -6651,7 +6654,7 @@
         <v>1025506</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E101" s="1">
         <v>2</v>
@@ -6678,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P101" s="1">
         <v>-1</v>
@@ -7982,7 +7985,7 @@
         <v>1026001</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E132" s="1">
         <v>2</v>
@@ -8009,7 +8012,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P132" s="1">
         <v>-1</v>
@@ -8023,7 +8026,7 @@
         <v>1026002</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E133" s="1">
         <v>2</v>
@@ -8050,7 +8053,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P133" s="1">
         <v>-1</v>
@@ -8064,7 +8067,7 @@
         <v>1026101</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E134" s="1">
         <v>2</v>
@@ -8091,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P134" s="1">
         <v>-1</v>
@@ -8105,7 +8108,7 @@
         <v>1026102</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
@@ -8132,7 +8135,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P135" s="1">
         <v>-1</v>
@@ -8146,7 +8149,7 @@
         <v>1026201</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -8173,7 +8176,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P136" s="1">
         <v>-1</v>
@@ -8187,7 +8190,7 @@
         <v>1026202</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -8214,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P137" s="1">
         <v>-1</v>
@@ -8228,7 +8231,7 @@
         <v>1026301</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -8255,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P138" s="1">
         <v>-1</v>
@@ -8269,7 +8272,7 @@
         <v>1026302</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -8296,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P139" s="1">
         <v>-1</v>
@@ -8310,7 +8313,7 @@
         <v>1026401</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -8337,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P140" s="1">
         <v>-1</v>
@@ -8351,7 +8354,7 @@
         <v>1026402</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -8378,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P141" s="1">
         <v>-1</v>
@@ -8392,7 +8395,7 @@
         <v>1027001</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -8419,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P142" s="1">
         <v>-1</v>
@@ -8433,7 +8436,7 @@
         <v>1027002</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -8460,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P143" s="1">
         <v>-1</v>
@@ -8474,7 +8477,7 @@
         <v>1027101</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -8501,7 +8504,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P144" s="1">
         <v>-1</v>
@@ -8515,7 +8518,7 @@
         <v>1027102</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -8542,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P145" s="1">
         <v>-1</v>
@@ -8556,7 +8559,7 @@
         <v>1027201</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -8583,7 +8586,7 @@
         <v>0</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P146" s="1">
         <v>-1</v>
@@ -8597,7 +8600,7 @@
         <v>1027202</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -8624,7 +8627,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P147" s="1">
         <v>-1</v>
@@ -8638,7 +8641,7 @@
         <v>1027301</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -8665,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P148" s="1">
         <v>-1</v>
@@ -8679,7 +8682,7 @@
         <v>1027302</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -8706,7 +8709,7 @@
         <v>0</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P149" s="1">
         <v>-1</v>
@@ -8720,7 +8723,7 @@
         <v>1027401</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -8747,7 +8750,7 @@
         <v>0</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P150" s="1">
         <v>-1</v>
@@ -8761,7 +8764,7 @@
         <v>1027402</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -8788,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P151" s="1">
         <v>-1</v>
@@ -8802,7 +8805,7 @@
         <v>1028001</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -8829,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P152" s="1">
         <v>-1</v>
@@ -8843,7 +8846,7 @@
         <v>1028002</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -8870,7 +8873,7 @@
         <v>0</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P153" s="1">
         <v>-1</v>
@@ -8884,7 +8887,7 @@
         <v>1028101</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -8911,7 +8914,7 @@
         <v>0</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P154" s="1">
         <v>-1</v>
@@ -8925,7 +8928,7 @@
         <v>1028102</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -8952,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P155" s="1">
         <v>-1</v>
@@ -8966,7 +8969,7 @@
         <v>1028201</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -8993,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P156" s="1">
         <v>-1</v>
@@ -9007,7 +9010,7 @@
         <v>1028202</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -9034,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P157" s="1">
         <v>-1</v>
@@ -9048,7 +9051,7 @@
         <v>1028301</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -9075,7 +9078,7 @@
         <v>0</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P158" s="1">
         <v>-1</v>
@@ -9089,7 +9092,7 @@
         <v>1028302</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -9116,7 +9119,7 @@
         <v>0</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P159" s="1">
         <v>-1</v>
@@ -9130,7 +9133,7 @@
         <v>1028401</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -9157,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P160" s="1">
         <v>-1</v>
@@ -9171,7 +9174,7 @@
         <v>1028402</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -9198,7 +9201,7 @@
         <v>0</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P161" s="1">
         <v>-1</v>
@@ -10502,7 +10505,7 @@
         <v>1200001</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E192" s="1">
         <v>2</v>
@@ -10529,7 +10532,7 @@
         <v>0</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P192" s="1">
         <v>1</v>
@@ -10543,7 +10546,7 @@
         <v>1200002</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E193" s="1">
         <v>2</v>
@@ -10570,7 +10573,7 @@
         <v>0</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P193" s="1">
         <v>1</v>
@@ -10584,7 +10587,7 @@
         <v>1200003</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E194" s="1">
         <v>2</v>
@@ -10611,7 +10614,7 @@
         <v>0</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P194" s="1">
         <v>1</v>
@@ -10625,7 +10628,7 @@
         <v>1200004</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E195" s="1">
         <v>2</v>
@@ -10652,7 +10655,7 @@
         <v>0</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P195" s="1">
         <v>1</v>
@@ -10666,7 +10669,7 @@
         <v>1200005</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E196" s="1">
         <v>2</v>
@@ -10693,7 +10696,7 @@
         <v>0</v>
       </c>
       <c r="M196" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P196" s="1">
         <v>1</v>
@@ -10707,7 +10710,7 @@
         <v>1200006</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E197" s="1">
         <v>2</v>
@@ -10734,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P197" s="1">
         <v>1</v>
@@ -10748,7 +10751,7 @@
         <v>1200007</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E198" s="1">
         <v>2</v>
@@ -10775,7 +10778,7 @@
         <v>0</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P198" s="1">
         <v>1</v>
@@ -10789,7 +10792,7 @@
         <v>1200008</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E199" s="1">
         <v>2</v>
@@ -10816,7 +10819,7 @@
         <v>0</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P199" s="1">
         <v>1</v>
@@ -10830,7 +10833,7 @@
         <v>1200009</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E200" s="1">
         <v>2</v>
@@ -10857,7 +10860,7 @@
         <v>0</v>
       </c>
       <c r="M200" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P200" s="1">
         <v>1</v>
@@ -10871,7 +10874,7 @@
         <v>1200010</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E201" s="1">
         <v>2</v>
@@ -10898,7 +10901,7 @@
         <v>0</v>
       </c>
       <c r="M201" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P201" s="1">
         <v>1</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -198,6 +198,28 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+道具ID，道具数量；</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 填写 dropGroup.xlsx配置表中 trunkID 字中的值
 </t>
         </r>
@@ -320,7 +342,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="267">
   <si>
     <t>道具ID</t>
   </si>
@@ -361,7 +383,10 @@
     <t>最大堆叠数量</t>
   </si>
   <si>
-    <t>使用道具后获得道具</t>
+    <t>使用道具后获得固定道具</t>
+  </si>
+  <si>
+    <t>使用道具后选择获得道具</t>
   </si>
   <si>
     <t>掉落ID</t>
@@ -421,6 +446,9 @@
     <t>getItem</t>
   </si>
   <si>
+    <t>SelectGetItem</t>
+  </si>
+  <si>
     <t>dropId</t>
   </si>
   <si>
@@ -500,6 +528,9 @@
   </si>
   <si>
     <t>使用后随机获得1~2星赌场建筑升级道具</t>
+  </si>
+  <si>
+    <t>1023001_10;1023002_20;1023003_30</t>
   </si>
   <si>
     <t>赌场工具（精良）</t>
@@ -1289,12 +1320,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2312,15 +2343,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S201"/>
+  <dimension ref="A1:T201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.875" style="1" customWidth="1"/>
     <col min="8" max="9" width="21.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="26" style="1" customWidth="1"/>
@@ -2330,15 +2360,16 @@
     <col min="14" max="14" width="10.875" style="1" customWidth="1"/>
     <col min="15" max="15" width="17.25" style="1" customWidth="1"/>
     <col min="16" max="16" width="12.875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.625" style="1" customWidth="1"/>
-    <col min="20" max="21" width="9" style="1"/>
-    <col min="22" max="22" width="9.375" style="1"/>
-    <col min="23" max="16384" width="9" style="1"/>
+    <col min="17" max="17" width="21.0166666666667" style="1" customWidth="1"/>
+    <col min="18" max="18" width="36" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="12.625" style="1" customWidth="1"/>
+    <col min="21" max="22" width="9" style="1"/>
+    <col min="23" max="23" width="9.375" style="1"/>
+    <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2389,107 +2420,116 @@
       <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>20</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
+        <v>34</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:20">
       <c r="A5" s="1">
         <v>1990000</v>
       </c>
@@ -2500,13 +2540,13 @@
         <v>1990000</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1">
         <v>99</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -2518,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K5" s="1">
         <v>2990000</v>
@@ -2527,17 +2567,17 @@
         <v>0</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P5" s="1">
         <v>-1</v>
       </c>
-      <c r="S5" s="1">
+      <c r="T5" s="1">
         <f>1/700000</f>
         <v>1.42857142857143e-6</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:20">
       <c r="A6" s="1">
         <v>1980000</v>
       </c>
@@ -2548,13 +2588,13 @@
         <v>1980000</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1">
         <v>98</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -2566,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K6" s="1">
         <v>2980000</v>
@@ -2575,17 +2615,17 @@
         <v>0</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P6" s="1">
         <v>-1</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <f>1/700</f>
         <v>0.00142857142857143</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:20">
       <c r="A7" s="1">
         <v>1970000</v>
       </c>
@@ -2596,13 +2636,13 @@
         <v>1970000</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1">
         <v>97</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -2614,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K7" s="1">
         <v>2970000</v>
@@ -2623,13 +2663,13 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P7" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:20">
       <c r="A8" s="1">
         <v>1020001</v>
       </c>
@@ -2640,13 +2680,13 @@
         <v>1020001</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -2658,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K8" s="1">
         <v>2020001</v>
@@ -2667,13 +2707,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P8" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:20">
       <c r="A9" s="1">
         <v>1022501</v>
       </c>
@@ -2684,13 +2724,13 @@
         <v>1202501</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
@@ -2702,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K9" s="1">
         <v>2022501</v>
@@ -2711,16 +2751,16 @@
         <v>0</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P9" s="1">
         <v>999999</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:20">
       <c r="A10" s="1">
         <v>1022502</v>
       </c>
@@ -2731,13 +2771,13 @@
         <v>1202502</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -2749,7 +2789,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K10" s="1">
         <v>2022502</v>
@@ -2758,16 +2798,16 @@
         <v>0</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P10" s="1">
         <v>999999</v>
       </c>
-      <c r="S10" s="1">
+      <c r="T10" s="1">
         <v>0.99</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:20">
       <c r="A11" s="1">
         <v>1022503</v>
       </c>
@@ -2778,13 +2818,13 @@
         <v>1202503</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -2796,7 +2836,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K11" s="1">
         <v>2022503</v>
@@ -2805,16 +2845,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P11" s="1">
         <v>999999</v>
       </c>
-      <c r="S11" s="1">
+      <c r="T11" s="1">
         <v>0.99</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:19">
+    <row r="12" s="1" customFormat="1" spans="1:20">
       <c r="A12" s="1">
         <v>1010301</v>
       </c>
@@ -2825,13 +2865,13 @@
         <v>1100301</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12" s="1">
         <v>2</v>
@@ -2843,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K12" s="1">
         <v>2010301</v>
@@ -2852,20 +2892,23 @@
         <v>0</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P12" s="1">
         <v>999999</v>
       </c>
       <c r="Q12" s="6"/>
-      <c r="R12" s="1">
+      <c r="R12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="S12" s="1">
         <v>1010301</v>
       </c>
-      <c r="S12" s="1">
+      <c r="T12" s="1">
         <v>0.099</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:19">
+    <row r="13" s="1" customFormat="1" spans="1:20">
       <c r="A13" s="1">
         <v>1010302</v>
       </c>
@@ -2876,13 +2919,13 @@
         <v>1100302</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
@@ -2894,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K13" s="1">
         <v>2010302</v>
@@ -2903,21 +2946,24 @@
         <v>0</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P13" s="1">
         <v>999999</v>
       </c>
       <c r="Q13" s="6"/>
-      <c r="R13" s="1">
+      <c r="R13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="S13" s="1">
         <v>1010302</v>
       </c>
-      <c r="S13" s="1">
-        <f>S12*2</f>
+      <c r="T13" s="1">
+        <f>T12*2</f>
         <v>0.198</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:19">
+    <row r="14" s="1" customFormat="1" spans="1:20">
       <c r="A14" s="1">
         <v>1010303</v>
       </c>
@@ -2928,13 +2974,13 @@
         <v>1100303</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>
@@ -2946,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K14" s="1">
         <v>2010303</v>
@@ -2955,21 +3001,24 @@
         <v>0</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P14" s="1">
         <v>999999</v>
       </c>
       <c r="Q14" s="6"/>
-      <c r="R14" s="1">
+      <c r="R14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="S14" s="1">
         <v>1010303</v>
       </c>
-      <c r="S14" s="1">
-        <f>S12*6</f>
+      <c r="T14" s="1">
+        <f>T12*6</f>
         <v>0.594</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:19">
+    <row r="15" s="1" customFormat="1" spans="1:20">
       <c r="A15" s="1">
         <v>1010304</v>
       </c>
@@ -2980,13 +3029,13 @@
         <v>1100304</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G15" s="1">
         <v>5</v>
@@ -2998,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K15" s="1">
         <v>2010304</v>
@@ -3007,21 +3056,24 @@
         <v>0</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P15" s="1">
         <v>999999</v>
       </c>
       <c r="Q15" s="6"/>
-      <c r="R15" s="1">
+      <c r="R15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="S15" s="1">
         <v>1010304</v>
       </c>
-      <c r="S15" s="1">
-        <f>S12*8</f>
+      <c r="T15" s="1">
+        <f>T12*8</f>
         <v>0.792</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:19">
+    <row r="16" s="1" customFormat="1" spans="1:20">
       <c r="A16" s="1">
         <v>1010305</v>
       </c>
@@ -3032,13 +3084,13 @@
         <v>1100305</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G16" s="1">
         <v>6</v>
@@ -3050,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K16" s="1">
         <v>2010305</v>
@@ -3059,17 +3111,20 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P16" s="1">
         <v>999999</v>
       </c>
       <c r="Q16" s="6"/>
-      <c r="R16" s="1">
+      <c r="R16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="S16" s="1">
         <v>1010305</v>
       </c>
-      <c r="S16" s="1">
-        <f>S12*10</f>
+      <c r="T16" s="1">
+        <f>T12*10</f>
         <v>0.99</v>
       </c>
     </row>
@@ -3084,13 +3139,13 @@
         <v>1301001</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
@@ -3102,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K17" s="1">
         <v>2031001</v>
@@ -3128,13 +3183,13 @@
         <v>1301002</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G18" s="1">
         <v>1</v>
@@ -3146,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K18" s="1">
         <v>2031002</v>
@@ -3172,13 +3227,13 @@
         <v>1301201</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
@@ -3190,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K19" s="1">
         <v>2031201</v>
@@ -3216,13 +3271,13 @@
         <v>1301202</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G20" s="1">
         <v>1</v>
@@ -3234,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K20" s="1">
         <v>2031202</v>
@@ -3260,13 +3315,13 @@
         <v>101801</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
@@ -3278,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K21" s="1">
         <v>201801</v>
@@ -3304,13 +3359,13 @@
         <v>101802</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -3322,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K22" s="1">
         <v>201802</v>
@@ -3348,13 +3403,13 @@
         <v>1201401</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
@@ -3366,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K23" s="1">
         <v>2021401</v>
@@ -3392,13 +3447,13 @@
         <v>1201402</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -3410,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K24" s="1">
         <v>2021402</v>
@@ -3436,13 +3491,13 @@
         <v>103001</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
@@ -3454,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K25" s="1">
         <v>2031600</v>
@@ -3480,13 +3535,13 @@
         <v>103002</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G26" s="1">
         <v>1</v>
@@ -3498,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K26" s="1">
         <v>2031601</v>
@@ -3524,13 +3579,13 @@
         <v>103003</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -3542,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K27" s="1">
         <v>2031602</v>
@@ -3568,13 +3623,13 @@
         <v>104002</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
@@ -3586,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K28" s="1">
         <v>2031801</v>
@@ -3612,13 +3667,13 @@
         <v>104003</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
@@ -3630,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K29" s="1">
         <v>2031802</v>
@@ -3656,13 +3711,13 @@
         <v>105002</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
@@ -3674,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K30" s="1">
         <v>2032001</v>
@@ -3700,13 +3755,13 @@
         <v>105003</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -3718,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K31" s="1">
         <v>2032002</v>
@@ -3744,13 +3799,13 @@
         <v>106002</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
@@ -3762,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K32" s="1">
         <v>2032201</v>
@@ -3777,7 +3832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:20">
       <c r="A33" s="1">
         <v>1032202</v>
       </c>
@@ -3788,13 +3843,13 @@
         <v>106003</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
@@ -3806,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K33" s="1">
         <v>2032202</v>
@@ -3821,7 +3876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:20">
       <c r="A34" s="1">
         <v>1022504</v>
       </c>
@@ -3832,13 +3887,13 @@
         <v>1202504</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
@@ -3850,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K34" s="1">
         <v>2022504</v>
@@ -3859,13 +3914,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="P34" s="1">
         <v>999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:20">
       <c r="A35" s="1">
         <v>1023001</v>
       </c>
@@ -3873,13 +3928,13 @@
         <v>1023001</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G35" s="1">
         <v>2</v>
@@ -3891,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K35" s="1">
         <v>2023001</v>
@@ -3900,16 +3955,16 @@
         <v>0</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P35" s="1">
         <v>999999</v>
       </c>
-      <c r="S35" s="1">
+      <c r="T35" s="1">
         <v>0.000544077728550903</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:20">
       <c r="A36" s="1">
         <v>1023002</v>
       </c>
@@ -3917,13 +3972,13 @@
         <v>1023002</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G36" s="1">
         <v>3</v>
@@ -3935,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K36" s="1">
         <v>2023002</v>
@@ -3944,16 +3999,16 @@
         <v>0</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P36" s="1">
         <v>999999</v>
       </c>
-      <c r="S36" s="1">
+      <c r="T36" s="1">
         <v>0.0045080726079932</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:20">
       <c r="A37" s="1">
         <v>1023003</v>
       </c>
@@ -3961,13 +4016,13 @@
         <v>1023003</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G37" s="1">
         <v>4</v>
@@ -3979,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K37" s="1">
         <v>2023003</v>
@@ -3988,16 +4043,16 @@
         <v>0</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P37" s="1">
         <v>999999</v>
       </c>
-      <c r="S37" s="1">
+      <c r="T37" s="1">
         <v>0.0067621089119898</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:20">
       <c r="A38" s="1">
         <v>1023004</v>
       </c>
@@ -4005,13 +4060,13 @@
         <v>1023004</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G38" s="1">
         <v>5</v>
@@ -4023,7 +4078,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K38" s="1">
         <v>2023004</v>
@@ -4032,16 +4087,16 @@
         <v>0</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P38" s="1">
         <v>999999</v>
       </c>
-      <c r="S38" s="1">
+      <c r="T38" s="1">
         <v>0.012622603302381</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:20">
       <c r="A39" s="1">
         <v>1023005</v>
       </c>
@@ -4049,13 +4104,13 @@
         <v>1023005</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G39" s="1">
         <v>6</v>
@@ -4067,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K39" s="1">
         <v>2023005</v>
@@ -4076,16 +4131,16 @@
         <v>0</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P39" s="1">
         <v>999999</v>
       </c>
-      <c r="S39" s="1">
+      <c r="T39" s="1">
         <v>0.0139155435712012</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:20">
       <c r="A40" s="1">
         <v>1023101</v>
       </c>
@@ -4093,13 +4148,13 @@
         <v>1023101</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -4111,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K40" s="1">
         <v>2023101</v>
@@ -4120,16 +4175,16 @@
         <v>0</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P40" s="1">
         <v>999999</v>
       </c>
-      <c r="S40" s="1">
+      <c r="T40" s="1">
         <v>0.00174104873136289</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:20">
       <c r="A41" s="1">
         <v>1023102</v>
       </c>
@@ -4137,13 +4192,13 @@
         <v>1023102</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G41" s="1">
         <v>3</v>
@@ -4155,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K41" s="1">
         <v>2023102</v>
@@ -4164,16 +4219,16 @@
         <v>0</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P41" s="1">
         <v>999999</v>
       </c>
-      <c r="S41" s="1">
+      <c r="T41" s="1">
         <v>0.0144258323455782</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:20">
       <c r="A42" s="1">
         <v>1023103</v>
       </c>
@@ -4181,13 +4236,13 @@
         <v>1023103</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G42" s="1">
         <v>4</v>
@@ -4199,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K42" s="1">
         <v>2023103</v>
@@ -4208,16 +4263,16 @@
         <v>0</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P42" s="1">
         <v>999999</v>
       </c>
-      <c r="S42" s="1">
+      <c r="T42" s="1">
         <v>0.0216387485183673</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:20">
       <c r="A43" s="1">
         <v>1023104</v>
       </c>
@@ -4225,13 +4280,13 @@
         <v>1023104</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -4243,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K43" s="1">
         <v>2023104</v>
@@ -4252,16 +4307,16 @@
         <v>0</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P43" s="1">
         <v>999999</v>
       </c>
-      <c r="S43" s="1">
+      <c r="T43" s="1">
         <v>0.0403923305676191</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:20">
       <c r="A44" s="1">
         <v>1023105</v>
       </c>
@@ -4269,13 +4324,13 @@
         <v>1023105</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G44" s="1">
         <v>6</v>
@@ -4287,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K44" s="1">
         <v>2023105</v>
@@ -4296,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P44" s="1">
         <v>999999</v>
       </c>
-      <c r="S44" s="1">
+      <c r="T44" s="1">
         <v>0.0445297394278439</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:20">
       <c r="A45" s="1">
         <v>1023201</v>
       </c>
@@ -4313,13 +4368,13 @@
         <v>1023201</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G45" s="1">
         <v>2</v>
@@ -4331,7 +4386,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K45" s="1">
         <v>2023201</v>
@@ -4340,16 +4395,16 @@
         <v>0</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P45" s="1">
         <v>999999</v>
       </c>
-      <c r="S45" s="1">
+      <c r="T45" s="1">
         <v>0.00348209746272578</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:20">
       <c r="A46" s="1">
         <v>1023202</v>
       </c>
@@ -4357,13 +4412,13 @@
         <v>1023202</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G46" s="1">
         <v>3</v>
@@ -4375,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K46" s="1">
         <v>2023202</v>
@@ -4384,16 +4439,16 @@
         <v>0</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P46" s="1">
         <v>999999</v>
       </c>
-      <c r="S46" s="1">
+      <c r="T46" s="1">
         <v>0.0288516646911565</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:20">
       <c r="A47" s="1">
         <v>1023203</v>
       </c>
@@ -4401,13 +4456,13 @@
         <v>1023203</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G47" s="1">
         <v>4</v>
@@ -4419,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K47" s="1">
         <v>2023203</v>
@@ -4428,16 +4483,16 @@
         <v>0</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P47" s="1">
         <v>999999</v>
       </c>
-      <c r="S47" s="1">
+      <c r="T47" s="1">
         <v>0.0432774970367347</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:20">
       <c r="A48" s="1">
         <v>1023204</v>
       </c>
@@ -4445,13 +4500,13 @@
         <v>1023204</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G48" s="1">
         <v>5</v>
@@ -4463,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K48" s="1">
         <v>2023204</v>
@@ -4472,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P48" s="1">
         <v>999999</v>
       </c>
-      <c r="S48" s="1">
+      <c r="T48" s="1">
         <v>0.0807846611352381</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:20">
       <c r="A49" s="1">
         <v>1023205</v>
       </c>
@@ -4489,13 +4544,13 @@
         <v>1023205</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G49" s="1">
         <v>6</v>
@@ -4507,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K49" s="1">
         <v>2023205</v>
@@ -4516,16 +4571,16 @@
         <v>0</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P49" s="1">
         <v>999999</v>
       </c>
-      <c r="S49" s="1">
+      <c r="T49" s="1">
         <v>0.0890594788556878</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:20">
       <c r="A50" s="1">
         <v>1023301</v>
       </c>
@@ -4533,13 +4588,13 @@
         <v>1023301</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G50" s="1">
         <v>2</v>
@@ -4551,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K50" s="1">
         <v>2023301</v>
@@ -4560,16 +4615,16 @@
         <v>0</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P50" s="1">
         <v>999999</v>
       </c>
-      <c r="S50" s="1">
+      <c r="T50" s="1">
         <v>0.0039173596455665</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:20">
       <c r="A51" s="1">
         <v>1023302</v>
       </c>
@@ -4577,13 +4632,13 @@
         <v>1023302</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G51" s="1">
         <v>3</v>
@@ -4595,7 +4650,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K51" s="1">
         <v>2023302</v>
@@ -4604,16 +4659,16 @@
         <v>0</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P51" s="1">
         <v>999999</v>
       </c>
-      <c r="S51" s="1">
+      <c r="T51" s="1">
         <v>0.032458122777551</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:20">
       <c r="A52" s="1">
         <v>1023303</v>
       </c>
@@ -4621,13 +4676,13 @@
         <v>1023303</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G52" s="1">
         <v>4</v>
@@ -4639,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K52" s="1">
         <v>2023303</v>
@@ -4648,16 +4703,16 @@
         <v>0</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P52" s="1">
         <v>999999</v>
       </c>
-      <c r="S52" s="1">
+      <c r="T52" s="1">
         <v>0.0486871841663265</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:20">
       <c r="A53" s="1">
         <v>1023304</v>
       </c>
@@ -4665,13 +4720,13 @@
         <v>1023304</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G53" s="1">
         <v>5</v>
@@ -4683,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K53" s="1">
         <v>2023304</v>
@@ -4692,16 +4747,16 @@
         <v>0</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P53" s="1">
         <v>999999</v>
       </c>
-      <c r="S53" s="1">
+      <c r="T53" s="1">
         <v>0.0908827437771429</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:20">
       <c r="A54" s="1">
         <v>1023305</v>
       </c>
@@ -4709,13 +4764,13 @@
         <v>1023305</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G54" s="1">
         <v>6</v>
@@ -4727,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K54" s="1">
         <v>2023305</v>
@@ -4736,16 +4791,16 @@
         <v>0</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="P54" s="1">
         <v>999999</v>
       </c>
-      <c r="S54" s="1">
+      <c r="T54" s="1">
         <v>0.100191913712649</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:20">
       <c r="A55" s="1">
         <v>1023401</v>
       </c>
@@ -4753,13 +4808,13 @@
         <v>1023401</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G55" s="1">
         <v>2</v>
@@ -4771,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K55" s="1">
         <v>2023401</v>
@@ -4780,16 +4835,16 @@
         <v>0</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P55" s="1">
         <v>999999</v>
       </c>
-      <c r="S55" s="1">
+      <c r="T55" s="1">
         <v>0.00783471929113301</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:20">
       <c r="A56" s="1">
         <v>1023402</v>
       </c>
@@ -4797,13 +4852,13 @@
         <v>1023402</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G56" s="1">
         <v>3</v>
@@ -4815,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K56" s="1">
         <v>2023402</v>
@@ -4824,16 +4879,16 @@
         <v>0</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P56" s="1">
         <v>999999</v>
       </c>
-      <c r="S56" s="1">
+      <c r="T56" s="1">
         <v>0.064916245555102</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:20">
       <c r="A57" s="1">
         <v>1023403</v>
       </c>
@@ -4841,13 +4896,13 @@
         <v>1023403</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G57" s="1">
         <v>4</v>
@@ -4859,7 +4914,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K57" s="1">
         <v>2023403</v>
@@ -4868,16 +4923,16 @@
         <v>0</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P57" s="1">
         <v>999999</v>
       </c>
-      <c r="S57" s="1">
+      <c r="T57" s="1">
         <v>0.097374368332653</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:20">
       <c r="A58" s="1">
         <v>1023404</v>
       </c>
@@ -4885,13 +4940,13 @@
         <v>1023404</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G58" s="1">
         <v>5</v>
@@ -4903,7 +4958,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K58" s="1">
         <v>2023404</v>
@@ -4912,16 +4967,16 @@
         <v>0</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P58" s="1">
         <v>999999</v>
       </c>
-      <c r="S58" s="1">
+      <c r="T58" s="1">
         <v>0.181765487554286</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:20">
       <c r="A59" s="1">
         <v>1023405</v>
       </c>
@@ -4929,13 +4984,13 @@
         <v>1023405</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G59" s="1">
         <v>6</v>
@@ -4947,7 +5002,7 @@
         <v>1</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K59" s="1">
         <v>2023405</v>
@@ -4956,16 +5011,16 @@
         <v>0</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="P59" s="1">
         <v>999999</v>
       </c>
-      <c r="S59" s="1">
+      <c r="T59" s="1">
         <v>0.200383827425298</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="1:19">
+    <row r="60" s="1" customFormat="1" spans="1:20">
       <c r="A60" s="1">
         <v>1024001</v>
       </c>
@@ -4973,13 +5028,13 @@
         <v>1024001</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -4991,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K60" s="1">
         <v>2024001</v>
@@ -5000,13 +5055,13 @@
         <v>0</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="P60" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="1:19">
+    <row r="61" s="1" customFormat="1" spans="1:20">
       <c r="A61" s="1">
         <v>1024003</v>
       </c>
@@ -5014,13 +5069,13 @@
         <v>1024003</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
@@ -5032,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K61" s="1">
         <v>2024003</v>
@@ -5041,13 +5096,13 @@
         <v>0</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="P61" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:20">
       <c r="A62" s="1">
         <v>1024005</v>
       </c>
@@ -5055,13 +5110,13 @@
         <v>1024005</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G62" s="1">
         <v>1</v>
@@ -5073,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K62" s="1">
         <v>2024005</v>
@@ -5082,13 +5137,13 @@
         <v>0</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="P62" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:20">
       <c r="A63" s="1">
         <v>1024006</v>
       </c>
@@ -5096,13 +5151,13 @@
         <v>1024006</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G63" s="1">
         <v>5</v>
@@ -5114,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K63" s="1">
         <v>2024006</v>
@@ -5123,13 +5178,13 @@
         <v>0</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="P63" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" spans="1:19">
+    <row r="64" s="1" customFormat="1" spans="1:20">
       <c r="A64" s="1">
         <v>1024007</v>
       </c>
@@ -5137,13 +5192,13 @@
         <v>1024007</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G64" s="1">
         <v>1</v>
@@ -5155,7 +5210,7 @@
         <v>1</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K64" s="1">
         <v>2024007</v>
@@ -5164,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="P64" s="1">
         <v>999999999</v>
@@ -5178,13 +5233,13 @@
         <v>1024008</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G65" s="1">
         <v>1</v>
@@ -5196,7 +5251,7 @@
         <v>1</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K65" s="1">
         <v>2024008</v>
@@ -5205,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="P65" s="1">
         <v>999999</v>
@@ -5219,13 +5274,13 @@
         <v>1024009</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -5237,7 +5292,7 @@
         <v>1</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K66" s="1">
         <v>2024009</v>
@@ -5246,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="P66" s="1">
         <v>999999</v>
@@ -5260,13 +5315,13 @@
         <v>1024010</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G67" s="1">
         <v>1</v>
@@ -5278,7 +5333,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K67" s="1">
         <v>2024010</v>
@@ -5287,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="P67" s="1">
         <v>999999</v>
@@ -5301,13 +5356,13 @@
         <v>1024011</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G68" s="1">
         <v>1</v>
@@ -5319,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K68" s="1">
         <v>2024011</v>
@@ -5328,7 +5383,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="P68" s="1">
         <v>-1</v>
@@ -5342,13 +5397,13 @@
         <v>1024012</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
@@ -5360,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K69" s="1">
         <v>2024012</v>
@@ -5369,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P69" s="1">
         <v>-1</v>
@@ -5383,13 +5438,13 @@
         <v>1024013</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G70" s="1">
         <v>1</v>
@@ -5401,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K70" s="1">
         <v>2024013</v>
@@ -5410,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="P70" s="1">
         <v>999999</v>
@@ -5424,13 +5479,13 @@
         <v>1024014</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -5442,7 +5497,7 @@
         <v>1</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K71" s="1">
         <v>2024014</v>
@@ -5451,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="P71" s="1">
         <v>999999</v>
@@ -5465,13 +5520,13 @@
         <v>1025101</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -5483,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K72" s="1">
         <v>2025101</v>
@@ -5492,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P72" s="1">
         <v>-1</v>
@@ -5506,13 +5561,13 @@
         <v>1025102</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -5524,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K73" s="1">
         <v>2025102</v>
@@ -5533,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P73" s="1">
         <v>-1</v>
@@ -5547,13 +5602,13 @@
         <v>1025103</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G74" s="1">
         <v>1</v>
@@ -5565,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K74" s="1">
         <v>2025103</v>
@@ -5574,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="P74" s="1">
         <v>-1</v>
@@ -5588,13 +5643,13 @@
         <v>1025104</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G75" s="1">
         <v>1</v>
@@ -5606,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K75" s="1">
         <v>2025104</v>
@@ -5615,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P75" s="1">
         <v>-1</v>
@@ -5629,13 +5684,13 @@
         <v>1025105</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G76" s="1">
         <v>1</v>
@@ -5647,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K76" s="1">
         <v>2025105</v>
@@ -5656,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P76" s="1">
         <v>-1</v>
@@ -5670,13 +5725,13 @@
         <v>1025106</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G77" s="1">
         <v>1</v>
@@ -5688,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K77" s="1">
         <v>2025106</v>
@@ -5697,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="P77" s="1">
         <v>-1</v>
@@ -5711,13 +5766,13 @@
         <v>1025201</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G78" s="1">
         <v>2</v>
@@ -5729,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K78" s="1">
         <v>2025201</v>
@@ -5738,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P78" s="1">
         <v>-1</v>
@@ -5752,13 +5807,13 @@
         <v>1025202</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G79" s="1">
         <v>2</v>
@@ -5770,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K79" s="1">
         <v>2025202</v>
@@ -5779,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="P79" s="1">
         <v>-1</v>
@@ -5793,13 +5848,13 @@
         <v>1025203</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G80" s="1">
         <v>2</v>
@@ -5811,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K80" s="1">
         <v>2025203</v>
@@ -5820,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="P80" s="1">
         <v>-1</v>
@@ -5834,13 +5889,13 @@
         <v>1025204</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G81" s="1">
         <v>2</v>
@@ -5852,7 +5907,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K81" s="1">
         <v>2025204</v>
@@ -5861,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P81" s="1">
         <v>-1</v>
@@ -5875,13 +5930,13 @@
         <v>1025205</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G82" s="1">
         <v>2</v>
@@ -5893,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K82" s="1">
         <v>2025205</v>
@@ -5902,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="P82" s="1">
         <v>-1</v>
@@ -5916,13 +5971,13 @@
         <v>1025206</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G83" s="1">
         <v>2</v>
@@ -5934,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K83" s="1">
         <v>2025206</v>
@@ -5943,7 +5998,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P83" s="1">
         <v>-1</v>
@@ -5957,13 +6012,13 @@
         <v>1025301</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G84" s="1">
         <v>3</v>
@@ -5975,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K84" s="1">
         <v>2025301</v>
@@ -5984,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="P84" s="1">
         <v>-1</v>
@@ -5998,13 +6053,13 @@
         <v>1025302</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G85" s="1">
         <v>3</v>
@@ -6016,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K85" s="1">
         <v>2025302</v>
@@ -6025,7 +6080,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="P85" s="1">
         <v>-1</v>
@@ -6039,13 +6094,13 @@
         <v>1025303</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G86" s="1">
         <v>3</v>
@@ -6057,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K86" s="1">
         <v>2025303</v>
@@ -6066,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="P86" s="1">
         <v>-1</v>
@@ -6080,13 +6135,13 @@
         <v>1025304</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G87" s="1">
         <v>3</v>
@@ -6098,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K87" s="1">
         <v>2025304</v>
@@ -6107,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="P87" s="1">
         <v>-1</v>
@@ -6121,13 +6176,13 @@
         <v>1025305</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G88" s="1">
         <v>3</v>
@@ -6139,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K88" s="1">
         <v>2025305</v>
@@ -6148,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P88" s="1">
         <v>-1</v>
@@ -6162,13 +6217,13 @@
         <v>1025306</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G89" s="1">
         <v>3</v>
@@ -6180,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K89" s="1">
         <v>2025306</v>
@@ -6189,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P89" s="1">
         <v>-1</v>
@@ -6203,13 +6258,13 @@
         <v>1025401</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G90" s="1">
         <v>4</v>
@@ -6221,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K90" s="1">
         <v>2025401</v>
@@ -6230,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="P90" s="1">
         <v>-1</v>
@@ -6244,13 +6299,13 @@
         <v>1025402</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G91" s="1">
         <v>4</v>
@@ -6262,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K91" s="1">
         <v>2025402</v>
@@ -6271,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P91" s="1">
         <v>-1</v>
@@ -6285,13 +6340,13 @@
         <v>1025403</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G92" s="1">
         <v>4</v>
@@ -6303,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K92" s="1">
         <v>2025403</v>
@@ -6312,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="P92" s="1">
         <v>-1</v>
@@ -6326,13 +6381,13 @@
         <v>1025404</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G93" s="1">
         <v>4</v>
@@ -6344,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K93" s="1">
         <v>2025404</v>
@@ -6353,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P93" s="1">
         <v>-1</v>
@@ -6367,13 +6422,13 @@
         <v>1025405</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G94" s="1">
         <v>4</v>
@@ -6385,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K94" s="1">
         <v>2025405</v>
@@ -6394,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="P94" s="1">
         <v>-1</v>
@@ -6408,13 +6463,13 @@
         <v>1025406</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G95" s="1">
         <v>4</v>
@@ -6426,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K95" s="1">
         <v>2025406</v>
@@ -6435,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P95" s="1">
         <v>-1</v>
@@ -6449,13 +6504,13 @@
         <v>1025501</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G96" s="1">
         <v>7</v>
@@ -6467,7 +6522,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K96" s="1">
         <v>2025501</v>
@@ -6476,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="P96" s="1">
         <v>-1</v>
@@ -6490,13 +6545,13 @@
         <v>1025502</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G97" s="1">
         <v>7</v>
@@ -6508,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K97" s="1">
         <v>2025502</v>
@@ -6517,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="P97" s="1">
         <v>-1</v>
@@ -6531,13 +6586,13 @@
         <v>1025503</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G98" s="1">
         <v>7</v>
@@ -6549,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K98" s="1">
         <v>2025503</v>
@@ -6558,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P98" s="1">
         <v>-1</v>
@@ -6572,13 +6627,13 @@
         <v>1025504</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G99" s="1">
         <v>7</v>
@@ -6590,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K99" s="1">
         <v>2025504</v>
@@ -6599,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P99" s="1">
         <v>-1</v>
@@ -6613,13 +6668,13 @@
         <v>1025505</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G100" s="1">
         <v>7</v>
@@ -6631,7 +6686,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K100" s="1">
         <v>2025505</v>
@@ -6640,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="P100" s="1">
         <v>-1</v>
@@ -6654,13 +6709,13 @@
         <v>1025506</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E101" s="1">
         <v>2</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G101" s="1">
         <v>7</v>
@@ -6672,7 +6727,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K101" s="1">
         <v>2025506</v>
@@ -6681,7 +6736,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="P101" s="1">
         <v>-1</v>
@@ -6702,7 +6757,7 @@
         <v>2</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G102" s="1">
         <v>1</v>
@@ -6714,7 +6769,7 @@
         <v>1</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K102" s="1">
         <v>2125101</v>
@@ -6745,7 +6800,7 @@
         <v>2</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -6757,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K103" s="1">
         <v>2125102</v>
@@ -6788,7 +6843,7 @@
         <v>2</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -6800,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K104" s="1">
         <v>2125103</v>
@@ -6831,7 +6886,7 @@
         <v>2</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -6843,7 +6898,7 @@
         <v>1</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K105" s="1">
         <v>2125104</v>
@@ -6874,7 +6929,7 @@
         <v>2</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G106" s="1">
         <v>1</v>
@@ -6886,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K106" s="1">
         <v>2125105</v>
@@ -6917,7 +6972,7 @@
         <v>2</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G107" s="1">
         <v>1</v>
@@ -6929,7 +6984,7 @@
         <v>1</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K107" s="1">
         <v>2125106</v>
@@ -6960,7 +7015,7 @@
         <v>2</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G108" s="1">
         <v>2</v>
@@ -6972,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K108" s="1">
         <v>2125201</v>
@@ -7003,7 +7058,7 @@
         <v>2</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G109" s="1">
         <v>2</v>
@@ -7015,7 +7070,7 @@
         <v>1</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K109" s="1">
         <v>2125202</v>
@@ -7046,7 +7101,7 @@
         <v>2</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G110" s="1">
         <v>2</v>
@@ -7058,7 +7113,7 @@
         <v>1</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K110" s="1">
         <v>2125203</v>
@@ -7089,7 +7144,7 @@
         <v>2</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G111" s="1">
         <v>2</v>
@@ -7101,7 +7156,7 @@
         <v>1</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K111" s="1">
         <v>2125204</v>
@@ -7132,7 +7187,7 @@
         <v>2</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G112" s="1">
         <v>2</v>
@@ -7144,7 +7199,7 @@
         <v>1</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K112" s="1">
         <v>2125205</v>
@@ -7175,7 +7230,7 @@
         <v>2</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G113" s="1">
         <v>2</v>
@@ -7187,7 +7242,7 @@
         <v>1</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K113" s="1">
         <v>2125206</v>
@@ -7218,7 +7273,7 @@
         <v>2</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G114" s="1">
         <v>3</v>
@@ -7230,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K114" s="1">
         <v>2125301</v>
@@ -7261,7 +7316,7 @@
         <v>2</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G115" s="1">
         <v>3</v>
@@ -7273,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K115" s="1">
         <v>2125302</v>
@@ -7304,7 +7359,7 @@
         <v>2</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G116" s="1">
         <v>3</v>
@@ -7316,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K116" s="1">
         <v>2125303</v>
@@ -7347,7 +7402,7 @@
         <v>2</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G117" s="1">
         <v>3</v>
@@ -7359,7 +7414,7 @@
         <v>1</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K117" s="1">
         <v>2125304</v>
@@ -7390,7 +7445,7 @@
         <v>2</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G118" s="1">
         <v>3</v>
@@ -7402,7 +7457,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K118" s="1">
         <v>2125305</v>
@@ -7433,7 +7488,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G119" s="1">
         <v>3</v>
@@ -7445,7 +7500,7 @@
         <v>1</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K119" s="1">
         <v>2125306</v>
@@ -7476,7 +7531,7 @@
         <v>2</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G120" s="1">
         <v>4</v>
@@ -7488,7 +7543,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K120" s="1">
         <v>2125401</v>
@@ -7519,7 +7574,7 @@
         <v>2</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G121" s="1">
         <v>4</v>
@@ -7531,7 +7586,7 @@
         <v>1</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K121" s="1">
         <v>2125402</v>
@@ -7562,7 +7617,7 @@
         <v>2</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G122" s="1">
         <v>4</v>
@@ -7574,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K122" s="1">
         <v>2125403</v>
@@ -7605,7 +7660,7 @@
         <v>2</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G123" s="1">
         <v>4</v>
@@ -7617,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K123" s="1">
         <v>2125404</v>
@@ -7648,7 +7703,7 @@
         <v>2</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G124" s="1">
         <v>4</v>
@@ -7660,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K124" s="1">
         <v>2125405</v>
@@ -7691,7 +7746,7 @@
         <v>2</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G125" s="1">
         <v>4</v>
@@ -7703,7 +7758,7 @@
         <v>1</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K125" s="1">
         <v>2125406</v>
@@ -7734,7 +7789,7 @@
         <v>2</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G126" s="1">
         <v>7</v>
@@ -7746,7 +7801,7 @@
         <v>1</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K126" s="1">
         <v>2125501</v>
@@ -7777,7 +7832,7 @@
         <v>2</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G127" s="1">
         <v>7</v>
@@ -7789,7 +7844,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K127" s="1">
         <v>2125502</v>
@@ -7820,7 +7875,7 @@
         <v>2</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G128" s="1">
         <v>7</v>
@@ -7832,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K128" s="1">
         <v>2125503</v>
@@ -7863,7 +7918,7 @@
         <v>2</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G129" s="1">
         <v>7</v>
@@ -7875,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K129" s="1">
         <v>2125504</v>
@@ -7906,7 +7961,7 @@
         <v>2</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G130" s="1">
         <v>7</v>
@@ -7918,7 +7973,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K130" s="1">
         <v>2125505</v>
@@ -7949,7 +8004,7 @@
         <v>2</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G131" s="1">
         <v>7</v>
@@ -7961,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K131" s="1">
         <v>2125506</v>
@@ -7985,13 +8040,13 @@
         <v>1026001</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E132" s="1">
         <v>2</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G132" s="1">
         <v>1</v>
@@ -8003,7 +8058,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K132" s="1">
         <v>2026001</v>
@@ -8012,7 +8067,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P132" s="1">
         <v>-1</v>
@@ -8026,13 +8081,13 @@
         <v>1026002</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E133" s="1">
         <v>2</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G133" s="1">
         <v>1</v>
@@ -8044,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K133" s="1">
         <v>2026002</v>
@@ -8053,7 +8108,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="P133" s="1">
         <v>-1</v>
@@ -8067,13 +8122,13 @@
         <v>1026101</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E134" s="1">
         <v>2</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G134" s="1">
         <v>2</v>
@@ -8085,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K134" s="1">
         <v>2026101</v>
@@ -8094,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P134" s="1">
         <v>-1</v>
@@ -8108,13 +8163,13 @@
         <v>1026102</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G135" s="1">
         <v>2</v>
@@ -8126,7 +8181,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K135" s="1">
         <v>2026102</v>
@@ -8135,7 +8190,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="P135" s="1">
         <v>-1</v>
@@ -8149,13 +8204,13 @@
         <v>1026201</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G136" s="1">
         <v>3</v>
@@ -8167,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K136" s="1">
         <v>2026201</v>
@@ -8176,7 +8231,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P136" s="1">
         <v>-1</v>
@@ -8190,13 +8245,13 @@
         <v>1026202</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G137" s="1">
         <v>3</v>
@@ -8208,7 +8263,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K137" s="1">
         <v>2026202</v>
@@ -8217,7 +8272,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="P137" s="1">
         <v>-1</v>
@@ -8231,13 +8286,13 @@
         <v>1026301</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G138" s="1">
         <v>4</v>
@@ -8249,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K138" s="1">
         <v>2026301</v>
@@ -8258,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P138" s="1">
         <v>-1</v>
@@ -8272,13 +8327,13 @@
         <v>1026302</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G139" s="1">
         <v>4</v>
@@ -8290,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K139" s="1">
         <v>2026302</v>
@@ -8299,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P139" s="1">
         <v>-1</v>
@@ -8313,13 +8368,13 @@
         <v>1026401</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G140" s="1">
         <v>7</v>
@@ -8331,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K140" s="1">
         <v>2026401</v>
@@ -8340,7 +8395,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="P140" s="1">
         <v>-1</v>
@@ -8354,13 +8409,13 @@
         <v>1026402</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G141" s="1">
         <v>7</v>
@@ -8372,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K141" s="1">
         <v>2026402</v>
@@ -8381,7 +8436,7 @@
         <v>0</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P141" s="1">
         <v>-1</v>
@@ -8395,13 +8450,13 @@
         <v>1027001</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G142" s="1">
         <v>1</v>
@@ -8413,7 +8468,7 @@
         <v>0</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K142" s="1">
         <v>2027001</v>
@@ -8422,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P142" s="1">
         <v>-1</v>
@@ -8436,13 +8491,13 @@
         <v>1027002</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G143" s="1">
         <v>1</v>
@@ -8454,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K143" s="1">
         <v>2027002</v>
@@ -8463,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P143" s="1">
         <v>-1</v>
@@ -8477,13 +8532,13 @@
         <v>1027101</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G144" s="1">
         <v>2</v>
@@ -8495,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K144" s="1">
         <v>2027101</v>
@@ -8504,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="P144" s="1">
         <v>-1</v>
@@ -8518,13 +8573,13 @@
         <v>1027102</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G145" s="1">
         <v>2</v>
@@ -8536,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K145" s="1">
         <v>2027102</v>
@@ -8545,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P145" s="1">
         <v>-1</v>
@@ -8559,13 +8614,13 @@
         <v>1027201</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G146" s="1">
         <v>3</v>
@@ -8577,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K146" s="1">
         <v>2027201</v>
@@ -8586,7 +8641,7 @@
         <v>0</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="P146" s="1">
         <v>-1</v>
@@ -8600,13 +8655,13 @@
         <v>1027202</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G147" s="1">
         <v>3</v>
@@ -8618,7 +8673,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K147" s="1">
         <v>2027202</v>
@@ -8627,7 +8682,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P147" s="1">
         <v>-1</v>
@@ -8641,13 +8696,13 @@
         <v>1027301</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G148" s="1">
         <v>4</v>
@@ -8659,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K148" s="1">
         <v>2027301</v>
@@ -8668,7 +8723,7 @@
         <v>0</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="P148" s="1">
         <v>-1</v>
@@ -8682,13 +8737,13 @@
         <v>1027302</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G149" s="1">
         <v>4</v>
@@ -8700,7 +8755,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K149" s="1">
         <v>2027302</v>
@@ -8709,7 +8764,7 @@
         <v>0</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P149" s="1">
         <v>-1</v>
@@ -8723,13 +8778,13 @@
         <v>1027401</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G150" s="1">
         <v>7</v>
@@ -8741,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K150" s="1">
         <v>2027401</v>
@@ -8750,7 +8805,7 @@
         <v>0</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="P150" s="1">
         <v>-1</v>
@@ -8764,13 +8819,13 @@
         <v>1027402</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G151" s="1">
         <v>7</v>
@@ -8782,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K151" s="1">
         <v>2027402</v>
@@ -8791,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="P151" s="1">
         <v>-1</v>
@@ -8805,13 +8860,13 @@
         <v>1028001</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G152" s="1">
         <v>1</v>
@@ -8823,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K152" s="1">
         <v>2028001</v>
@@ -8832,7 +8887,7 @@
         <v>0</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P152" s="1">
         <v>-1</v>
@@ -8846,13 +8901,13 @@
         <v>1028002</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G153" s="1">
         <v>1</v>
@@ -8864,7 +8919,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K153" s="1">
         <v>2028002</v>
@@ -8873,7 +8928,7 @@
         <v>0</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="P153" s="1">
         <v>-1</v>
@@ -8887,13 +8942,13 @@
         <v>1028101</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G154" s="1">
         <v>2</v>
@@ -8905,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K154" s="1">
         <v>2028101</v>
@@ -8914,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="P154" s="1">
         <v>-1</v>
@@ -8928,13 +8983,13 @@
         <v>1028102</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G155" s="1">
         <v>2</v>
@@ -8946,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K155" s="1">
         <v>2028102</v>
@@ -8955,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P155" s="1">
         <v>-1</v>
@@ -8969,13 +9024,13 @@
         <v>1028201</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G156" s="1">
         <v>3</v>
@@ -8987,7 +9042,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K156" s="1">
         <v>2028201</v>
@@ -8996,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P156" s="1">
         <v>-1</v>
@@ -9010,13 +9065,13 @@
         <v>1028202</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G157" s="1">
         <v>3</v>
@@ -9028,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K157" s="1">
         <v>2028202</v>
@@ -9037,7 +9092,7 @@
         <v>0</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P157" s="1">
         <v>-1</v>
@@ -9051,13 +9106,13 @@
         <v>1028301</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G158" s="1">
         <v>4</v>
@@ -9069,7 +9124,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K158" s="1">
         <v>2028301</v>
@@ -9078,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="P158" s="1">
         <v>-1</v>
@@ -9092,13 +9147,13 @@
         <v>1028302</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G159" s="1">
         <v>4</v>
@@ -9110,7 +9165,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K159" s="1">
         <v>2028302</v>
@@ -9119,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="P159" s="1">
         <v>-1</v>
@@ -9133,13 +9188,13 @@
         <v>1028401</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G160" s="1">
         <v>7</v>
@@ -9151,7 +9206,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K160" s="1">
         <v>2028401</v>
@@ -9160,7 +9215,7 @@
         <v>0</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="P160" s="1">
         <v>-1</v>
@@ -9174,13 +9229,13 @@
         <v>1028402</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G161" s="1">
         <v>7</v>
@@ -9192,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K161" s="1">
         <v>2028402</v>
@@ -9201,7 +9256,7 @@
         <v>0</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="P161" s="1">
         <v>-1</v>
@@ -9222,7 +9277,7 @@
         <v>2</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G162" s="1">
         <v>1</v>
@@ -9234,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K162" s="1">
         <v>2126001</v>
@@ -9265,7 +9320,7 @@
         <v>2</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G163" s="1">
         <v>1</v>
@@ -9277,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K163" s="1">
         <v>2126002</v>
@@ -9308,7 +9363,7 @@
         <v>2</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G164" s="1">
         <v>2</v>
@@ -9320,7 +9375,7 @@
         <v>1</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K164" s="1">
         <v>2126101</v>
@@ -9351,7 +9406,7 @@
         <v>2</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G165" s="1">
         <v>2</v>
@@ -9363,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K165" s="1">
         <v>2126102</v>
@@ -9394,7 +9449,7 @@
         <v>2</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G166" s="1">
         <v>3</v>
@@ -9406,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K166" s="1">
         <v>2126201</v>
@@ -9437,7 +9492,7 @@
         <v>2</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G167" s="1">
         <v>3</v>
@@ -9449,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K167" s="1">
         <v>2126202</v>
@@ -9480,7 +9535,7 @@
         <v>2</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G168" s="1">
         <v>4</v>
@@ -9492,7 +9547,7 @@
         <v>1</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K168" s="1">
         <v>2126301</v>
@@ -9523,7 +9578,7 @@
         <v>2</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G169" s="1">
         <v>4</v>
@@ -9535,7 +9590,7 @@
         <v>1</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K169" s="1">
         <v>2126302</v>
@@ -9566,7 +9621,7 @@
         <v>2</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G170" s="1">
         <v>7</v>
@@ -9578,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K170" s="1">
         <v>2126401</v>
@@ -9609,7 +9664,7 @@
         <v>2</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G171" s="1">
         <v>7</v>
@@ -9621,7 +9676,7 @@
         <v>1</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K171" s="1">
         <v>2126402</v>
@@ -9652,7 +9707,7 @@
         <v>2</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G172" s="1">
         <v>1</v>
@@ -9664,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K172" s="1">
         <v>2127001</v>
@@ -9695,7 +9750,7 @@
         <v>2</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G173" s="1">
         <v>1</v>
@@ -9707,7 +9762,7 @@
         <v>1</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K173" s="1">
         <v>2127002</v>
@@ -9738,7 +9793,7 @@
         <v>2</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G174" s="1">
         <v>2</v>
@@ -9750,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K174" s="1">
         <v>2127101</v>
@@ -9781,7 +9836,7 @@
         <v>2</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G175" s="1">
         <v>2</v>
@@ -9793,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K175" s="1">
         <v>2127102</v>
@@ -9824,7 +9879,7 @@
         <v>2</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G176" s="1">
         <v>3</v>
@@ -9836,7 +9891,7 @@
         <v>1</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K176" s="1">
         <v>2127201</v>
@@ -9867,7 +9922,7 @@
         <v>2</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G177" s="1">
         <v>3</v>
@@ -9879,7 +9934,7 @@
         <v>1</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K177" s="1">
         <v>2127202</v>
@@ -9910,7 +9965,7 @@
         <v>2</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G178" s="1">
         <v>4</v>
@@ -9922,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K178" s="1">
         <v>2127301</v>
@@ -9953,7 +10008,7 @@
         <v>2</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G179" s="1">
         <v>4</v>
@@ -9965,7 +10020,7 @@
         <v>1</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K179" s="1">
         <v>2127302</v>
@@ -9996,7 +10051,7 @@
         <v>2</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G180" s="1">
         <v>7</v>
@@ -10008,7 +10063,7 @@
         <v>1</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K180" s="1">
         <v>2127401</v>
@@ -10039,7 +10094,7 @@
         <v>2</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G181" s="1">
         <v>7</v>
@@ -10051,7 +10106,7 @@
         <v>1</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K181" s="1">
         <v>2127402</v>
@@ -10082,7 +10137,7 @@
         <v>2</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G182" s="1">
         <v>1</v>
@@ -10094,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K182" s="1">
         <v>2128001</v>
@@ -10125,7 +10180,7 @@
         <v>2</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G183" s="1">
         <v>1</v>
@@ -10137,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K183" s="1">
         <v>2128002</v>
@@ -10168,7 +10223,7 @@
         <v>2</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G184" s="1">
         <v>2</v>
@@ -10180,7 +10235,7 @@
         <v>1</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K184" s="1">
         <v>2128101</v>
@@ -10211,7 +10266,7 @@
         <v>2</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G185" s="1">
         <v>2</v>
@@ -10223,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K185" s="1">
         <v>2128102</v>
@@ -10254,7 +10309,7 @@
         <v>2</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G186" s="1">
         <v>3</v>
@@ -10266,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K186" s="1">
         <v>2128201</v>
@@ -10297,7 +10352,7 @@
         <v>2</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G187" s="1">
         <v>3</v>
@@ -10309,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K187" s="1">
         <v>2128202</v>
@@ -10340,7 +10395,7 @@
         <v>2</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G188" s="1">
         <v>4</v>
@@ -10352,7 +10407,7 @@
         <v>1</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K188" s="1">
         <v>2128301</v>
@@ -10383,7 +10438,7 @@
         <v>2</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G189" s="1">
         <v>4</v>
@@ -10395,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K189" s="1">
         <v>2128302</v>
@@ -10426,7 +10481,7 @@
         <v>2</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G190" s="1">
         <v>7</v>
@@ -10438,7 +10493,7 @@
         <v>1</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K190" s="1">
         <v>2128401</v>
@@ -10469,7 +10524,7 @@
         <v>2</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G191" s="1">
         <v>7</v>
@@ -10481,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K191" s="1">
         <v>2128402</v>
@@ -10505,13 +10560,13 @@
         <v>1200001</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E192" s="1">
         <v>2</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G192" s="1">
         <v>1</v>
@@ -10523,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K192" s="1">
         <v>2200001</v>
@@ -10532,7 +10587,7 @@
         <v>0</v>
       </c>
       <c r="M192" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P192" s="1">
         <v>1</v>
@@ -10546,13 +10601,13 @@
         <v>1200002</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E193" s="1">
         <v>2</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G193" s="1">
         <v>1</v>
@@ -10564,7 +10619,7 @@
         <v>0</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K193" s="1">
         <v>2200002</v>
@@ -10573,7 +10628,7 @@
         <v>0</v>
       </c>
       <c r="M193" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="P193" s="1">
         <v>1</v>
@@ -10587,13 +10642,13 @@
         <v>1200003</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E194" s="1">
         <v>2</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G194" s="1">
         <v>1</v>
@@ -10605,7 +10660,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K194" s="1">
         <v>2200003</v>
@@ -10614,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="M194" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="P194" s="1">
         <v>1</v>
@@ -10628,13 +10683,13 @@
         <v>1200004</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E195" s="1">
         <v>2</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G195" s="1">
         <v>1</v>
@@ -10646,7 +10701,7 @@
         <v>0</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K195" s="1">
         <v>2200004</v>
@@ -10655,7 +10710,7 @@
         <v>0</v>
       </c>
       <c r="M195" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P195" s="1">
         <v>1</v>
@@ -10669,13 +10724,13 @@
         <v>1200005</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E196" s="1">
         <v>2</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G196" s="1">
         <v>1</v>
@@ -10687,7 +10742,7 @@
         <v>0</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K196" s="1">
         <v>2200005</v>
@@ -10696,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="M196" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P196" s="1">
         <v>1</v>
@@ -10710,13 +10765,13 @@
         <v>1200006</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E197" s="1">
         <v>2</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G197" s="1">
         <v>1</v>
@@ -10728,7 +10783,7 @@
         <v>0</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K197" s="1">
         <v>2200006</v>
@@ -10737,7 +10792,7 @@
         <v>0</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P197" s="1">
         <v>1</v>
@@ -10751,13 +10806,13 @@
         <v>1200007</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E198" s="1">
         <v>2</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G198" s="1">
         <v>1</v>
@@ -10769,7 +10824,7 @@
         <v>0</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K198" s="1">
         <v>2200007</v>
@@ -10778,7 +10833,7 @@
         <v>0</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="P198" s="1">
         <v>1</v>
@@ -10792,13 +10847,13 @@
         <v>1200008</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E199" s="1">
         <v>2</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G199" s="1">
         <v>1</v>
@@ -10810,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K199" s="1">
         <v>2200008</v>
@@ -10819,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="M199" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P199" s="1">
         <v>1</v>
@@ -10833,13 +10888,13 @@
         <v>1200009</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E200" s="1">
         <v>2</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G200" s="1">
         <v>1</v>
@@ -10851,7 +10906,7 @@
         <v>0</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K200" s="1">
         <v>2200009</v>
@@ -10860,7 +10915,7 @@
         <v>0</v>
       </c>
       <c r="M200" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P200" s="1">
         <v>1</v>
@@ -10874,13 +10929,13 @@
         <v>1200010</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E201" s="1">
         <v>2</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G201" s="1">
         <v>1</v>
@@ -10892,7 +10947,7 @@
         <v>0</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K201" s="1">
         <v>2200010</v>
@@ -10901,7 +10956,7 @@
         <v>0</v>
       </c>
       <c r="M201" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="P201" s="1">
         <v>1</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -269,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A162" authorId="0">
+    <comment ref="A163" authorId="0">
       <text>
         <r>
           <rPr>
@@ -291,7 +291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A172" authorId="0">
+    <comment ref="A173" authorId="0">
       <text>
         <r>
           <rPr>
@@ -314,7 +314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A182" authorId="0">
+    <comment ref="A183" authorId="0">
       <text>
         <r>
           <rPr>
@@ -342,7 +342,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="269">
   <si>
     <t>道具ID</t>
   </si>
@@ -906,6 +906,12 @@
   </si>
   <si>
     <t>用于雇员卡池抽卡的道具</t>
+  </si>
+  <si>
+    <t>游客邀请函</t>
+  </si>
+  <si>
+    <t>用于指定生成游客的道具</t>
   </si>
   <si>
     <t>街头潮人</t>
@@ -1320,12 +1326,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2343,7 +2349,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T201"/>
+  <dimension ref="A1:T202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" style="1" customWidth="1"/>
@@ -5514,10 +5520,10 @@
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <v>1025101</v>
+        <v>1024015</v>
       </c>
       <c r="C72" s="1">
-        <v>1025101</v>
+        <v>1024015</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>188</v>
@@ -5532,36 +5538,36 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>163</v>
       </c>
       <c r="K72" s="1">
-        <v>2025101</v>
+        <v>2024015</v>
       </c>
       <c r="L72" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P72" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <v>1025102</v>
+        <v>1025101</v>
       </c>
       <c r="C73" s="1">
-        <v>1025102</v>
+        <v>1025101</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -5582,13 +5588,13 @@
         <v>163</v>
       </c>
       <c r="K73" s="1">
-        <v>2025102</v>
+        <v>2025101</v>
       </c>
       <c r="L73" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P73" s="1">
         <v>-1</v>
@@ -5596,13 +5602,13 @@
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <v>1025103</v>
+        <v>1025102</v>
       </c>
       <c r="C74" s="1">
-        <v>1025103</v>
+        <v>1025102</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -5623,13 +5629,13 @@
         <v>163</v>
       </c>
       <c r="K74" s="1">
-        <v>2025103</v>
+        <v>2025102</v>
       </c>
       <c r="L74" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P74" s="1">
         <v>-1</v>
@@ -5637,13 +5643,13 @@
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <v>1025104</v>
+        <v>1025103</v>
       </c>
       <c r="C75" s="1">
-        <v>1025104</v>
+        <v>1025103</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -5664,13 +5670,13 @@
         <v>163</v>
       </c>
       <c r="K75" s="1">
-        <v>2025104</v>
+        <v>2025103</v>
       </c>
       <c r="L75" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P75" s="1">
         <v>-1</v>
@@ -5678,13 +5684,13 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <v>1025105</v>
+        <v>1025104</v>
       </c>
       <c r="C76" s="1">
-        <v>1025105</v>
+        <v>1025104</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
@@ -5705,13 +5711,13 @@
         <v>163</v>
       </c>
       <c r="K76" s="1">
-        <v>2025105</v>
+        <v>2025104</v>
       </c>
       <c r="L76" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P76" s="1">
         <v>-1</v>
@@ -5719,13 +5725,13 @@
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <v>1025106</v>
+        <v>1025105</v>
       </c>
       <c r="C77" s="1">
-        <v>1025106</v>
+        <v>1025105</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -5746,13 +5752,13 @@
         <v>163</v>
       </c>
       <c r="K77" s="1">
-        <v>2025106</v>
+        <v>2025105</v>
       </c>
       <c r="L77" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P77" s="1">
         <v>-1</v>
@@ -5760,13 +5766,13 @@
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <v>1025201</v>
+        <v>1025106</v>
       </c>
       <c r="C78" s="1">
-        <v>1025201</v>
+        <v>1025106</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -5775,7 +5781,7 @@
         <v>47</v>
       </c>
       <c r="G78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1" t="b">
         <v>0</v>
@@ -5787,13 +5793,13 @@
         <v>163</v>
       </c>
       <c r="K78" s="1">
-        <v>2025201</v>
+        <v>2025106</v>
       </c>
       <c r="L78" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P78" s="1">
         <v>-1</v>
@@ -5801,13 +5807,13 @@
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <v>1025202</v>
+        <v>1025201</v>
       </c>
       <c r="C79" s="1">
-        <v>1025202</v>
+        <v>1025201</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
@@ -5828,13 +5834,13 @@
         <v>163</v>
       </c>
       <c r="K79" s="1">
-        <v>2025202</v>
+        <v>2025201</v>
       </c>
       <c r="L79" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P79" s="1">
         <v>-1</v>
@@ -5842,13 +5848,13 @@
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <v>1025203</v>
+        <v>1025202</v>
       </c>
       <c r="C80" s="1">
-        <v>1025203</v>
+        <v>1025202</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -5869,13 +5875,13 @@
         <v>163</v>
       </c>
       <c r="K80" s="1">
-        <v>2025203</v>
+        <v>2025202</v>
       </c>
       <c r="L80" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P80" s="1">
         <v>-1</v>
@@ -5883,13 +5889,13 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <v>1025204</v>
+        <v>1025203</v>
       </c>
       <c r="C81" s="1">
-        <v>1025204</v>
+        <v>1025203</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -5910,13 +5916,13 @@
         <v>163</v>
       </c>
       <c r="K81" s="1">
-        <v>2025204</v>
+        <v>2025203</v>
       </c>
       <c r="L81" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P81" s="1">
         <v>-1</v>
@@ -5924,13 +5930,13 @@
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <v>1025205</v>
+        <v>1025204</v>
       </c>
       <c r="C82" s="1">
-        <v>1025205</v>
+        <v>1025204</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -5951,13 +5957,13 @@
         <v>163</v>
       </c>
       <c r="K82" s="1">
-        <v>2025205</v>
+        <v>2025204</v>
       </c>
       <c r="L82" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P82" s="1">
         <v>-1</v>
@@ -5965,13 +5971,13 @@
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <v>1025206</v>
+        <v>1025205</v>
       </c>
       <c r="C83" s="1">
-        <v>1025206</v>
+        <v>1025205</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -5992,13 +5998,13 @@
         <v>163</v>
       </c>
       <c r="K83" s="1">
-        <v>2025206</v>
+        <v>2025205</v>
       </c>
       <c r="L83" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P83" s="1">
         <v>-1</v>
@@ -6006,13 +6012,13 @@
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <v>1025301</v>
+        <v>1025206</v>
       </c>
       <c r="C84" s="1">
-        <v>1025301</v>
+        <v>1025206</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -6021,7 +6027,7 @@
         <v>47</v>
       </c>
       <c r="G84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H84" s="1" t="b">
         <v>0</v>
@@ -6033,13 +6039,13 @@
         <v>163</v>
       </c>
       <c r="K84" s="1">
-        <v>2025301</v>
+        <v>2025206</v>
       </c>
       <c r="L84" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P84" s="1">
         <v>-1</v>
@@ -6047,13 +6053,13 @@
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1">
-        <v>1025302</v>
+        <v>1025301</v>
       </c>
       <c r="C85" s="1">
-        <v>1025302</v>
+        <v>1025301</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -6074,13 +6080,13 @@
         <v>163</v>
       </c>
       <c r="K85" s="1">
-        <v>2025302</v>
+        <v>2025301</v>
       </c>
       <c r="L85" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P85" s="1">
         <v>-1</v>
@@ -6088,13 +6094,13 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
-        <v>1025303</v>
+        <v>1025302</v>
       </c>
       <c r="C86" s="1">
-        <v>1025303</v>
+        <v>1025302</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
@@ -6115,13 +6121,13 @@
         <v>163</v>
       </c>
       <c r="K86" s="1">
-        <v>2025303</v>
+        <v>2025302</v>
       </c>
       <c r="L86" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P86" s="1">
         <v>-1</v>
@@ -6129,13 +6135,13 @@
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
-        <v>1025304</v>
+        <v>1025303</v>
       </c>
       <c r="C87" s="1">
-        <v>1025304</v>
+        <v>1025303</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -6156,13 +6162,13 @@
         <v>163</v>
       </c>
       <c r="K87" s="1">
-        <v>2025304</v>
+        <v>2025303</v>
       </c>
       <c r="L87" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P87" s="1">
         <v>-1</v>
@@ -6170,13 +6176,13 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
-        <v>1025305</v>
+        <v>1025304</v>
       </c>
       <c r="C88" s="1">
-        <v>1025305</v>
+        <v>1025304</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -6197,13 +6203,13 @@
         <v>163</v>
       </c>
       <c r="K88" s="1">
-        <v>2025305</v>
+        <v>2025304</v>
       </c>
       <c r="L88" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P88" s="1">
         <v>-1</v>
@@ -6211,13 +6217,13 @@
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
-        <v>1025306</v>
+        <v>1025305</v>
       </c>
       <c r="C89" s="1">
-        <v>1025306</v>
+        <v>1025305</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -6238,13 +6244,13 @@
         <v>163</v>
       </c>
       <c r="K89" s="1">
-        <v>2025306</v>
+        <v>2025305</v>
       </c>
       <c r="L89" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P89" s="1">
         <v>-1</v>
@@ -6252,13 +6258,13 @@
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
-        <v>1025401</v>
+        <v>1025306</v>
       </c>
       <c r="C90" s="1">
-        <v>1025401</v>
+        <v>1025306</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -6267,7 +6273,7 @@
         <v>47</v>
       </c>
       <c r="G90" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H90" s="1" t="b">
         <v>0</v>
@@ -6279,13 +6285,13 @@
         <v>163</v>
       </c>
       <c r="K90" s="1">
-        <v>2025401</v>
+        <v>2025306</v>
       </c>
       <c r="L90" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P90" s="1">
         <v>-1</v>
@@ -6293,13 +6299,13 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <v>1025402</v>
+        <v>1025401</v>
       </c>
       <c r="C91" s="1">
-        <v>1025402</v>
+        <v>1025401</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
@@ -6320,13 +6326,13 @@
         <v>163</v>
       </c>
       <c r="K91" s="1">
-        <v>2025402</v>
+        <v>2025401</v>
       </c>
       <c r="L91" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P91" s="1">
         <v>-1</v>
@@ -6334,13 +6340,13 @@
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <v>1025403</v>
+        <v>1025402</v>
       </c>
       <c r="C92" s="1">
-        <v>1025403</v>
+        <v>1025402</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -6361,13 +6367,13 @@
         <v>163</v>
       </c>
       <c r="K92" s="1">
-        <v>2025403</v>
+        <v>2025402</v>
       </c>
       <c r="L92" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P92" s="1">
         <v>-1</v>
@@ -6375,13 +6381,13 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1">
-        <v>1025404</v>
+        <v>1025403</v>
       </c>
       <c r="C93" s="1">
-        <v>1025404</v>
+        <v>1025403</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
@@ -6402,13 +6408,13 @@
         <v>163</v>
       </c>
       <c r="K93" s="1">
-        <v>2025404</v>
+        <v>2025403</v>
       </c>
       <c r="L93" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P93" s="1">
         <v>-1</v>
@@ -6416,13 +6422,13 @@
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <v>1025405</v>
+        <v>1025404</v>
       </c>
       <c r="C94" s="1">
-        <v>1025405</v>
+        <v>1025404</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -6443,13 +6449,13 @@
         <v>163</v>
       </c>
       <c r="K94" s="1">
-        <v>2025405</v>
+        <v>2025404</v>
       </c>
       <c r="L94" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P94" s="1">
         <v>-1</v>
@@ -6457,13 +6463,13 @@
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <v>1025406</v>
+        <v>1025405</v>
       </c>
       <c r="C95" s="1">
-        <v>1025406</v>
+        <v>1025405</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -6484,13 +6490,13 @@
         <v>163</v>
       </c>
       <c r="K95" s="1">
-        <v>2025406</v>
+        <v>2025405</v>
       </c>
       <c r="L95" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P95" s="1">
         <v>-1</v>
@@ -6498,13 +6504,13 @@
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1">
-        <v>1025501</v>
+        <v>1025406</v>
       </c>
       <c r="C96" s="1">
-        <v>1025501</v>
+        <v>1025406</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -6513,7 +6519,7 @@
         <v>47</v>
       </c>
       <c r="G96" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H96" s="1" t="b">
         <v>0</v>
@@ -6525,13 +6531,13 @@
         <v>163</v>
       </c>
       <c r="K96" s="1">
-        <v>2025501</v>
+        <v>2025406</v>
       </c>
       <c r="L96" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P96" s="1">
         <v>-1</v>
@@ -6539,13 +6545,13 @@
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <v>1025502</v>
+        <v>1025501</v>
       </c>
       <c r="C97" s="1">
-        <v>1025502</v>
+        <v>1025501</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -6566,13 +6572,13 @@
         <v>163</v>
       </c>
       <c r="K97" s="1">
-        <v>2025502</v>
+        <v>2025501</v>
       </c>
       <c r="L97" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P97" s="1">
         <v>-1</v>
@@ -6580,13 +6586,13 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <v>1025503</v>
+        <v>1025502</v>
       </c>
       <c r="C98" s="1">
-        <v>1025503</v>
+        <v>1025502</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -6607,13 +6613,13 @@
         <v>163</v>
       </c>
       <c r="K98" s="1">
-        <v>2025503</v>
+        <v>2025502</v>
       </c>
       <c r="L98" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P98" s="1">
         <v>-1</v>
@@ -6621,13 +6627,13 @@
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <v>1025504</v>
+        <v>1025503</v>
       </c>
       <c r="C99" s="1">
-        <v>1025504</v>
+        <v>1025503</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -6648,13 +6654,13 @@
         <v>163</v>
       </c>
       <c r="K99" s="1">
-        <v>2025504</v>
+        <v>2025503</v>
       </c>
       <c r="L99" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P99" s="1">
         <v>-1</v>
@@ -6662,13 +6668,13 @@
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <v>1025505</v>
+        <v>1025504</v>
       </c>
       <c r="C100" s="1">
-        <v>1025505</v>
+        <v>1025504</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -6689,13 +6695,13 @@
         <v>163</v>
       </c>
       <c r="K100" s="1">
-        <v>2025505</v>
+        <v>2025504</v>
       </c>
       <c r="L100" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P100" s="1">
         <v>-1</v>
@@ -6703,13 +6709,13 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <v>1025506</v>
+        <v>1025505</v>
       </c>
       <c r="C101" s="1">
-        <v>1025506</v>
+        <v>1025505</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E101" s="1">
         <v>2</v>
@@ -6730,13 +6736,13 @@
         <v>163</v>
       </c>
       <c r="K101" s="1">
-        <v>2025506</v>
+        <v>2025505</v>
       </c>
       <c r="L101" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P101" s="1">
         <v>-1</v>
@@ -6744,14 +6750,13 @@
     </row>
     <row r="102" spans="1:16">
       <c r="A102" s="1">
-        <v>1125101</v>
+        <v>1025506</v>
       </c>
       <c r="C102" s="1">
-        <v>1125101</v>
-      </c>
-      <c r="D102" s="1" t="str">
-        <f>D72&amp;"碎片"</f>
-        <v>街头潮人碎片</v>
+        <v>1025506</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="E102" s="1">
         <v>2</v>
@@ -6760,41 +6765,40 @@
         <v>47</v>
       </c>
       <c r="G102" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H102" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>163</v>
       </c>
       <c r="K102" s="1">
-        <v>2125101</v>
+        <v>2025506</v>
       </c>
       <c r="L102" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M102" s="1" t="str">
-        <f>D72&amp;"游客的升星道具"</f>
-        <v>街头潮人游客的升星道具</v>
+      <c r="M102" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="P102" s="1">
-        <v>999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="103" spans="1:16">
       <c r="A103" s="1">
-        <v>1125102</v>
+        <v>1125101</v>
       </c>
       <c r="C103" s="1">
-        <v>1125102</v>
+        <v>1125101</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f t="shared" ref="D103:D131" si="0">D73&amp;"碎片"</f>
-        <v>复古绅士碎片</v>
+        <f>D73&amp;"碎片"</f>
+        <v>街头潮人碎片</v>
       </c>
       <c r="E103" s="1">
         <v>2</v>
@@ -6815,14 +6819,14 @@
         <v>163</v>
       </c>
       <c r="K103" s="1">
-        <v>2125102</v>
+        <v>2125101</v>
       </c>
       <c r="L103" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M103" s="1" t="str">
-        <f t="shared" ref="M103:M131" si="1">D73&amp;"游客的升星道具"</f>
-        <v>复古绅士游客的升星道具</v>
+        <f>D73&amp;"游客的升星道具"</f>
+        <v>街头潮人游客的升星道具</v>
       </c>
       <c r="P103" s="1">
         <v>999999</v>
@@ -6830,1258 +6834,1260 @@
     </row>
     <row r="104" spans="1:16">
       <c r="A104" s="1">
+        <v>1125102</v>
+      </c>
+      <c r="C104" s="1">
+        <v>1125102</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f t="shared" ref="D104:D132" si="0">D74&amp;"碎片"</f>
+        <v>复古绅士碎片</v>
+      </c>
+      <c r="E104" s="1">
+        <v>2</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G104" s="1">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K104" s="1">
+        <v>2125102</v>
+      </c>
+      <c r="L104" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" s="1" t="str">
+        <f t="shared" ref="M104:M132" si="1">D74&amp;"游客的升星道具"</f>
+        <v>复古绅士游客的升星道具</v>
+      </c>
+      <c r="P104" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105" s="1">
         <v>1125103</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C105" s="1">
         <v>1125103</v>
       </c>
-      <c r="D104" s="1" t="str">
+      <c r="D105" s="1" t="str">
         <f t="shared" si="0"/>
         <v>酷盖少年碎片</v>
       </c>
-      <c r="E104" s="1">
-        <v>2</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G104" s="1">
-        <v>1</v>
-      </c>
-      <c r="H104" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I104" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K104" s="1">
+      <c r="E105" s="1">
+        <v>2</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G105" s="1">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K105" s="1">
         <v>2125103</v>
       </c>
-      <c r="L104" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M104" s="1" t="str">
+      <c r="L105" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" s="1" t="str">
         <f t="shared" si="1"/>
         <v>酷盖少年游客的升星道具</v>
       </c>
-      <c r="P104" s="1">
+      <c r="P105" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
-      <c r="A105" s="1">
+    <row r="106" spans="1:16">
+      <c r="A106" s="1">
         <v>1125104</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C106" s="1">
         <v>1125104</v>
       </c>
-      <c r="D105" s="1" t="str">
+      <c r="D106" s="1" t="str">
         <f t="shared" si="0"/>
         <v>潮流先锋碎片</v>
       </c>
-      <c r="E105" s="1">
-        <v>2</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G105" s="1">
-        <v>1</v>
-      </c>
-      <c r="H105" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I105" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K105" s="1">
+      <c r="E106" s="1">
+        <v>2</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G106" s="1">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K106" s="1">
         <v>2125104</v>
       </c>
-      <c r="L105" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M105" s="1" t="str">
+      <c r="L106" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M106" s="1" t="str">
         <f t="shared" si="1"/>
         <v>潮流先锋游客的升星道具</v>
       </c>
-      <c r="P105" s="1">
+      <c r="P106" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
-      <c r="A106" s="1">
+    <row r="107" spans="1:16">
+      <c r="A107" s="1">
         <v>1125105</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C107" s="1">
         <v>1125105</v>
       </c>
-      <c r="D106" s="1" t="str">
+      <c r="D107" s="1" t="str">
         <f t="shared" si="0"/>
         <v>时尚教主碎片</v>
       </c>
-      <c r="E106" s="1">
-        <v>2</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G106" s="1">
-        <v>1</v>
-      </c>
-      <c r="H106" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I106" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J106" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K106" s="1">
+      <c r="E107" s="1">
+        <v>2</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G107" s="1">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I107" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K107" s="1">
         <v>2125105</v>
       </c>
-      <c r="L106" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M106" s="1" t="str">
+      <c r="L107" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M107" s="1" t="str">
         <f t="shared" si="1"/>
         <v>时尚教主游客的升星道具</v>
       </c>
-      <c r="P106" s="1">
+      <c r="P107" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
-      <c r="A107" s="1">
+    <row r="108" spans="1:16">
+      <c r="A108" s="1">
         <v>1125106</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C108" s="1">
         <v>1125106</v>
       </c>
-      <c r="D107" s="1" t="str">
+      <c r="D108" s="1" t="str">
         <f t="shared" si="0"/>
         <v>街拍达人碎片</v>
       </c>
-      <c r="E107" s="1">
-        <v>2</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G107" s="1">
-        <v>1</v>
-      </c>
-      <c r="H107" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I107" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K107" s="1">
+      <c r="E108" s="1">
+        <v>2</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G108" s="1">
+        <v>1</v>
+      </c>
+      <c r="H108" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K108" s="1">
         <v>2125106</v>
       </c>
-      <c r="L107" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M107" s="1" t="str">
+      <c r="L108" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M108" s="1" t="str">
         <f t="shared" si="1"/>
         <v>街拍达人游客的升星道具</v>
       </c>
-      <c r="P107" s="1">
+      <c r="P108" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
-      <c r="A108" s="1">
+    <row r="109" spans="1:16">
+      <c r="A109" s="1">
         <v>1125201</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C109" s="1">
         <v>1125201</v>
       </c>
-      <c r="D108" s="1" t="str">
+      <c r="D109" s="1" t="str">
         <f t="shared" si="0"/>
         <v>运动健将碎片</v>
       </c>
-      <c r="E108" s="1">
-        <v>2</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G108" s="1">
-        <v>2</v>
-      </c>
-      <c r="H108" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I108" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K108" s="1">
+      <c r="E109" s="1">
+        <v>2</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G109" s="1">
+        <v>2</v>
+      </c>
+      <c r="H109" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I109" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K109" s="1">
         <v>2125201</v>
       </c>
-      <c r="L108" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M108" s="1" t="str">
+      <c r="L109" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M109" s="1" t="str">
         <f t="shared" si="1"/>
         <v>运动健将游客的升星道具</v>
       </c>
-      <c r="P108" s="1">
+      <c r="P109" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
-      <c r="A109" s="1">
+    <row r="110" spans="1:16">
+      <c r="A110" s="1">
         <v>1125202</v>
       </c>
-      <c r="C109" s="1">
+      <c r="C110" s="1">
         <v>1125202</v>
       </c>
-      <c r="D109" s="1" t="str">
+      <c r="D110" s="1" t="str">
         <f t="shared" si="0"/>
         <v>跑酷少年碎片</v>
       </c>
-      <c r="E109" s="1">
-        <v>2</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G109" s="1">
-        <v>2</v>
-      </c>
-      <c r="H109" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I109" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K109" s="1">
+      <c r="E110" s="1">
+        <v>2</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G110" s="1">
+        <v>2</v>
+      </c>
+      <c r="H110" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I110" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K110" s="1">
         <v>2125202</v>
       </c>
-      <c r="L109" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M109" s="1" t="str">
+      <c r="L110" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M110" s="1" t="str">
         <f t="shared" si="1"/>
         <v>跑酷少年游客的升星道具</v>
       </c>
-      <c r="P109" s="1">
+      <c r="P110" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
-      <c r="A110" s="1">
+    <row r="111" spans="1:16">
+      <c r="A111" s="1">
         <v>1125203</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C111" s="1">
         <v>1125203</v>
       </c>
-      <c r="D110" s="1" t="str">
+      <c r="D111" s="1" t="str">
         <f t="shared" si="0"/>
         <v>滑板高手碎片</v>
       </c>
-      <c r="E110" s="1">
-        <v>2</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G110" s="1">
-        <v>2</v>
-      </c>
-      <c r="H110" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I110" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J110" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K110" s="1">
+      <c r="E111" s="1">
+        <v>2</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G111" s="1">
+        <v>2</v>
+      </c>
+      <c r="H111" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I111" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K111" s="1">
         <v>2125203</v>
       </c>
-      <c r="L110" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M110" s="1" t="str">
+      <c r="L111" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M111" s="1" t="str">
         <f t="shared" si="1"/>
         <v>滑板高手游客的升星道具</v>
       </c>
-      <c r="P110" s="1">
+      <c r="P111" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
-      <c r="A111" s="1">
+    <row r="112" spans="1:16">
+      <c r="A112" s="1">
         <v>1125204</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C112" s="1">
         <v>1125204</v>
       </c>
-      <c r="D111" s="1" t="str">
+      <c r="D112" s="1" t="str">
         <f t="shared" si="0"/>
         <v>甜心辣妹碎片</v>
       </c>
-      <c r="E111" s="1">
-        <v>2</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G111" s="1">
-        <v>2</v>
-      </c>
-      <c r="H111" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I111" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J111" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K111" s="1">
+      <c r="E112" s="1">
+        <v>2</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G112" s="1">
+        <v>2</v>
+      </c>
+      <c r="H112" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K112" s="1">
         <v>2125204</v>
       </c>
-      <c r="L111" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M111" s="1" t="str">
+      <c r="L112" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" s="1" t="str">
         <f t="shared" si="1"/>
         <v>甜心辣妹游客的升星道具</v>
       </c>
-      <c r="P111" s="1">
+      <c r="P112" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
-      <c r="A112" s="1">
+    <row r="113" spans="1:16">
+      <c r="A113" s="1">
         <v>1125205</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C113" s="1">
         <v>1125205</v>
       </c>
-      <c r="D112" s="1" t="str">
+      <c r="D113" s="1" t="str">
         <f t="shared" si="0"/>
         <v>活力少女碎片</v>
       </c>
-      <c r="E112" s="1">
-        <v>2</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G112" s="1">
-        <v>2</v>
-      </c>
-      <c r="H112" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I112" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K112" s="1">
+      <c r="E113" s="1">
+        <v>2</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G113" s="1">
+        <v>2</v>
+      </c>
+      <c r="H113" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K113" s="1">
         <v>2125205</v>
       </c>
-      <c r="L112" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M112" s="1" t="str">
+      <c r="L113" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M113" s="1" t="str">
         <f t="shared" si="1"/>
         <v>活力少女游客的升星道具</v>
       </c>
-      <c r="P112" s="1">
+      <c r="P113" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
-      <c r="A113" s="1">
+    <row r="114" spans="1:16">
+      <c r="A114" s="1">
         <v>1125206</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C114" s="1">
         <v>1125206</v>
       </c>
-      <c r="D113" s="1" t="str">
+      <c r="D114" s="1" t="str">
         <f t="shared" si="0"/>
         <v>优雅女神碎片</v>
       </c>
-      <c r="E113" s="1">
-        <v>2</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G113" s="1">
-        <v>2</v>
-      </c>
-      <c r="H113" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I113" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J113" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K113" s="1">
+      <c r="E114" s="1">
+        <v>2</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G114" s="1">
+        <v>2</v>
+      </c>
+      <c r="H114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K114" s="1">
         <v>2125206</v>
       </c>
-      <c r="L113" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M113" s="1" t="str">
+      <c r="L114" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" s="1" t="str">
         <f t="shared" si="1"/>
         <v>优雅女神游客的升星道具</v>
       </c>
-      <c r="P113" s="1">
+      <c r="P114" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
-      <c r="A114" s="1">
+    <row r="115" spans="1:16">
+      <c r="A115" s="1">
         <v>1125301</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C115" s="1">
         <v>1125301</v>
       </c>
-      <c r="D114" s="1" t="str">
+      <c r="D115" s="1" t="str">
         <f t="shared" si="0"/>
         <v>健身狂魔碎片</v>
       </c>
-      <c r="E114" s="1">
-        <v>2</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G114" s="1">
+      <c r="E115" s="1">
+        <v>2</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G115" s="1">
         <v>3</v>
       </c>
-      <c r="H114" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I114" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K114" s="1">
+      <c r="H115" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I115" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K115" s="1">
         <v>2125301</v>
       </c>
-      <c r="L114" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M114" s="1" t="str">
+      <c r="L115" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M115" s="1" t="str">
         <f t="shared" si="1"/>
         <v>健身狂魔游客的升星道具</v>
       </c>
-      <c r="P114" s="1">
+      <c r="P115" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
-      <c r="A115" s="1">
+    <row r="116" spans="1:16">
+      <c r="A116" s="1">
         <v>1125302</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C116" s="1">
         <v>1125302</v>
       </c>
-      <c r="D115" s="1" t="str">
+      <c r="D116" s="1" t="str">
         <f t="shared" si="0"/>
         <v>单车骑士碎片</v>
       </c>
-      <c r="E115" s="1">
-        <v>2</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G115" s="1">
+      <c r="E116" s="1">
+        <v>2</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G116" s="1">
         <v>3</v>
       </c>
-      <c r="H115" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I115" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K115" s="1">
+      <c r="H116" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I116" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K116" s="1">
         <v>2125302</v>
       </c>
-      <c r="L115" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M115" s="1" t="str">
+      <c r="L116" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M116" s="1" t="str">
         <f t="shared" si="1"/>
         <v>单车骑士游客的升星道具</v>
       </c>
-      <c r="P115" s="1">
+      <c r="P116" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
-      <c r="A116" s="1">
+    <row r="117" spans="1:16">
+      <c r="A117" s="1">
         <v>1125303</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C117" s="1">
         <v>1125303</v>
       </c>
-      <c r="D116" s="1" t="str">
+      <c r="D117" s="1" t="str">
         <f t="shared" si="0"/>
         <v>登山行者碎片</v>
       </c>
-      <c r="E116" s="1">
-        <v>2</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G116" s="1">
+      <c r="E117" s="1">
+        <v>2</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G117" s="1">
         <v>3</v>
       </c>
-      <c r="H116" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I116" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K116" s="1">
+      <c r="H117" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I117" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K117" s="1">
         <v>2125303</v>
       </c>
-      <c r="L116" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M116" s="1" t="str">
+      <c r="L117" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M117" s="1" t="str">
         <f t="shared" si="1"/>
         <v>登山行者游客的升星道具</v>
       </c>
-      <c r="P116" s="1">
+      <c r="P117" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
-      <c r="A117" s="1">
+    <row r="118" spans="1:16">
+      <c r="A118" s="1">
         <v>1125304</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C118" s="1">
         <v>1125304</v>
       </c>
-      <c r="D117" s="1" t="str">
+      <c r="D118" s="1" t="str">
         <f t="shared" si="0"/>
         <v>文艺青年碎片</v>
       </c>
-      <c r="E117" s="1">
-        <v>2</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G117" s="1">
+      <c r="E118" s="1">
+        <v>2</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G118" s="1">
         <v>3</v>
       </c>
-      <c r="H117" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I117" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K117" s="1">
+      <c r="H118" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I118" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K118" s="1">
         <v>2125304</v>
       </c>
-      <c r="L117" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M117" s="1" t="str">
+      <c r="L118" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" s="1" t="str">
         <f t="shared" si="1"/>
         <v>文艺青年游客的升星道具</v>
       </c>
-      <c r="P117" s="1">
+      <c r="P118" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
-      <c r="A118" s="1">
+    <row r="119" spans="1:16">
+      <c r="A119" s="1">
         <v>1125305</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C119" s="1">
         <v>1125305</v>
       </c>
-      <c r="D118" s="1" t="str">
+      <c r="D119" s="1" t="str">
         <f t="shared" si="0"/>
         <v>书香少女碎片</v>
       </c>
-      <c r="E118" s="1">
-        <v>2</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G118" s="1">
+      <c r="E119" s="1">
+        <v>2</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G119" s="1">
         <v>3</v>
       </c>
-      <c r="H118" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I118" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K118" s="1">
+      <c r="H119" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I119" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K119" s="1">
         <v>2125305</v>
       </c>
-      <c r="L118" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M118" s="1" t="str">
+      <c r="L119" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M119" s="1" t="str">
         <f t="shared" si="1"/>
         <v>书香少女游客的升星道具</v>
       </c>
-      <c r="P118" s="1">
+      <c r="P119" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
-      <c r="A119" s="1">
+    <row r="120" spans="1:16">
+      <c r="A120" s="1">
         <v>1125306</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C120" s="1">
         <v>1125306</v>
       </c>
-      <c r="D119" s="1" t="str">
+      <c r="D120" s="1" t="str">
         <f t="shared" si="0"/>
         <v>民谣歌手碎片</v>
       </c>
-      <c r="E119" s="1">
-        <v>2</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G119" s="1">
+      <c r="E120" s="1">
+        <v>2</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G120" s="1">
         <v>3</v>
       </c>
-      <c r="H119" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I119" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K119" s="1">
+      <c r="H120" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I120" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K120" s="1">
         <v>2125306</v>
       </c>
-      <c r="L119" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M119" s="1" t="str">
+      <c r="L120" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M120" s="1" t="str">
         <f t="shared" si="1"/>
         <v>民谣歌手游客的升星道具</v>
       </c>
-      <c r="P119" s="1">
+      <c r="P120" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
-      <c r="A120" s="1">
+    <row r="121" spans="1:16">
+      <c r="A121" s="1">
         <v>1125401</v>
       </c>
-      <c r="C120" s="1">
+      <c r="C121" s="1">
         <v>1125401</v>
       </c>
-      <c r="D120" s="1" t="str">
+      <c r="D121" s="1" t="str">
         <f t="shared" si="0"/>
         <v>马拉松客碎片</v>
       </c>
-      <c r="E120" s="1">
-        <v>2</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G120" s="1">
+      <c r="E121" s="1">
+        <v>2</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G121" s="1">
         <v>4</v>
       </c>
-      <c r="H120" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I120" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K120" s="1">
+      <c r="H121" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I121" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K121" s="1">
         <v>2125401</v>
       </c>
-      <c r="L120" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M120" s="1" t="str">
+      <c r="L121" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" s="1" t="str">
         <f t="shared" si="1"/>
         <v>马拉松客游客的升星道具</v>
       </c>
-      <c r="P120" s="1">
+      <c r="P121" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
-      <c r="A121" s="1">
+    <row r="122" spans="1:16">
+      <c r="A122" s="1">
         <v>1125402</v>
       </c>
-      <c r="C121" s="1">
+      <c r="C122" s="1">
         <v>1125402</v>
       </c>
-      <c r="D121" s="1" t="str">
+      <c r="D122" s="1" t="str">
         <f t="shared" si="0"/>
         <v>极限玩家碎片</v>
       </c>
-      <c r="E121" s="1">
-        <v>2</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G121" s="1">
+      <c r="E122" s="1">
+        <v>2</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G122" s="1">
         <v>4</v>
       </c>
-      <c r="H121" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I121" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K121" s="1">
+      <c r="H122" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I122" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K122" s="1">
         <v>2125402</v>
       </c>
-      <c r="L121" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M121" s="1" t="str">
+      <c r="L122" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" s="1" t="str">
         <f t="shared" si="1"/>
         <v>极限玩家游客的升星道具</v>
       </c>
-      <c r="P121" s="1">
+      <c r="P122" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
-      <c r="A122" s="1">
+    <row r="123" spans="1:16">
+      <c r="A123" s="1">
         <v>1125403</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C123" s="1">
         <v>1125403</v>
       </c>
-      <c r="D122" s="1" t="str">
+      <c r="D123" s="1" t="str">
         <f t="shared" si="0"/>
         <v>科技极客碎片</v>
       </c>
-      <c r="E122" s="1">
-        <v>2</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G122" s="1">
+      <c r="E123" s="1">
+        <v>2</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G123" s="1">
         <v>4</v>
       </c>
-      <c r="H122" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I122" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K122" s="1">
+      <c r="H123" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I123" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K123" s="1">
         <v>2125403</v>
       </c>
-      <c r="L122" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M122" s="1" t="str">
+      <c r="L123" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" s="1" t="str">
         <f t="shared" si="1"/>
         <v>科技极客游客的升星道具</v>
       </c>
-      <c r="P122" s="1">
+      <c r="P123" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
-      <c r="A123" s="1">
+    <row r="124" spans="1:16">
+      <c r="A124" s="1">
         <v>1125404</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C124" s="1">
         <v>1125404</v>
       </c>
-      <c r="D123" s="1" t="str">
+      <c r="D124" s="1" t="str">
         <f t="shared" si="0"/>
         <v>独立画家碎片</v>
       </c>
-      <c r="E123" s="1">
-        <v>2</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G123" s="1">
+      <c r="E124" s="1">
+        <v>2</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G124" s="1">
         <v>4</v>
       </c>
-      <c r="H123" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I123" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K123" s="1">
+      <c r="H124" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I124" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K124" s="1">
         <v>2125404</v>
       </c>
-      <c r="L123" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M123" s="1" t="str">
+      <c r="L124" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" s="1" t="str">
         <f t="shared" si="1"/>
         <v>独立画家游客的升星道具</v>
       </c>
-      <c r="P123" s="1">
+      <c r="P124" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
-      <c r="A124" s="1">
+    <row r="125" spans="1:16">
+      <c r="A125" s="1">
         <v>1125405</v>
       </c>
-      <c r="C124" s="1">
+      <c r="C125" s="1">
         <v>1125405</v>
       </c>
-      <c r="D124" s="1" t="str">
+      <c r="D125" s="1" t="str">
         <f t="shared" si="0"/>
         <v>浪漫诗人碎片</v>
       </c>
-      <c r="E124" s="1">
-        <v>2</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G124" s="1">
+      <c r="E125" s="1">
+        <v>2</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G125" s="1">
         <v>4</v>
       </c>
-      <c r="H124" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I124" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K124" s="1">
+      <c r="H125" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I125" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K125" s="1">
         <v>2125405</v>
       </c>
-      <c r="L124" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M124" s="1" t="str">
+      <c r="L125" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" s="1" t="str">
         <f t="shared" si="1"/>
         <v>浪漫诗人游客的升星道具</v>
       </c>
-      <c r="P124" s="1">
+      <c r="P125" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
-      <c r="A125" s="1">
+    <row r="126" spans="1:16">
+      <c r="A126" s="1">
         <v>1125406</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C126" s="1">
         <v>1125406</v>
       </c>
-      <c r="D125" s="1" t="str">
+      <c r="D126" s="1" t="str">
         <f t="shared" si="0"/>
         <v>古典乐迷碎片</v>
       </c>
-      <c r="E125" s="1">
-        <v>2</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G125" s="1">
+      <c r="E126" s="1">
+        <v>2</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G126" s="1">
         <v>4</v>
       </c>
-      <c r="H125" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I125" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K125" s="1">
+      <c r="H126" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I126" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K126" s="1">
         <v>2125406</v>
       </c>
-      <c r="L125" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M125" s="1" t="str">
+      <c r="L126" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M126" s="1" t="str">
         <f t="shared" si="1"/>
         <v>古典乐迷游客的升星道具</v>
       </c>
-      <c r="P125" s="1">
+      <c r="P126" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
-      <c r="A126" s="1">
+    <row r="127" spans="1:16">
+      <c r="A127" s="1">
         <v>1125501</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C127" s="1">
         <v>1125501</v>
       </c>
-      <c r="D126" s="1" t="str">
+      <c r="D127" s="1" t="str">
         <f t="shared" si="0"/>
         <v>创业新贵碎片</v>
       </c>
-      <c r="E126" s="1">
-        <v>2</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G126" s="1">
+      <c r="E127" s="1">
+        <v>2</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G127" s="1">
         <v>7</v>
       </c>
-      <c r="H126" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I126" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K126" s="1">
+      <c r="H127" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I127" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K127" s="1">
         <v>2125501</v>
       </c>
-      <c r="L126" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M126" s="1" t="str">
+      <c r="L127" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M127" s="1" t="str">
         <f t="shared" si="1"/>
         <v>创业新贵游客的升星道具</v>
       </c>
-      <c r="P126" s="1">
+      <c r="P127" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
-      <c r="A127" s="1">
+    <row r="128" spans="1:16">
+      <c r="A128" s="1">
         <v>1125502</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C128" s="1">
         <v>1125502</v>
       </c>
-      <c r="D127" s="1" t="str">
+      <c r="D128" s="1" t="str">
         <f t="shared" si="0"/>
         <v>摸金校尉碎片</v>
       </c>
-      <c r="E127" s="1">
-        <v>2</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G127" s="1">
+      <c r="E128" s="1">
+        <v>2</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G128" s="1">
         <v>7</v>
       </c>
-      <c r="H127" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I127" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K127" s="1">
+      <c r="H128" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I128" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K128" s="1">
         <v>2125502</v>
       </c>
-      <c r="L127" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M127" s="1" t="str">
+      <c r="L128" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M128" s="1" t="str">
         <f t="shared" si="1"/>
         <v>摸金校尉游客的升星道具</v>
       </c>
-      <c r="P127" s="1">
+      <c r="P128" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
-      <c r="A128" s="1">
+    <row r="129" spans="1:16">
+      <c r="A129" s="1">
         <v>1125503</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C129" s="1">
         <v>1125503</v>
       </c>
-      <c r="D128" s="1" t="str">
+      <c r="D129" s="1" t="str">
         <f t="shared" si="0"/>
         <v>氪金大佬碎片</v>
       </c>
-      <c r="E128" s="1">
-        <v>2</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G128" s="1">
+      <c r="E129" s="1">
+        <v>2</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G129" s="1">
         <v>7</v>
       </c>
-      <c r="H128" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I128" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K128" s="1">
+      <c r="H129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K129" s="1">
         <v>2125503</v>
       </c>
-      <c r="L128" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M128" s="1" t="str">
+      <c r="L129" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M129" s="1" t="str">
         <f t="shared" si="1"/>
         <v>氪金大佬游客的升星道具</v>
       </c>
-      <c r="P128" s="1">
+      <c r="P129" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
-      <c r="A129" s="1">
+    <row r="130" spans="1:16">
+      <c r="A130" s="1">
         <v>1125504</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C130" s="1">
         <v>1125504</v>
       </c>
-      <c r="D129" s="1" t="str">
+      <c r="D130" s="1" t="str">
         <f t="shared" si="0"/>
         <v>穿搭博主碎片</v>
       </c>
-      <c r="E129" s="1">
-        <v>2</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G129" s="1">
+      <c r="E130" s="1">
+        <v>2</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G130" s="1">
         <v>7</v>
       </c>
-      <c r="H129" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I129" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K129" s="1">
+      <c r="H130" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I130" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K130" s="1">
         <v>2125504</v>
       </c>
-      <c r="L129" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M129" s="1" t="str">
+      <c r="L130" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M130" s="1" t="str">
         <f t="shared" si="1"/>
         <v>穿搭博主游客的升星道具</v>
       </c>
-      <c r="P129" s="1">
+      <c r="P130" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
-      <c r="A130" s="1">
+    <row r="131" spans="1:16">
+      <c r="A131" s="1">
         <v>1125505</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C131" s="1">
         <v>1125505</v>
       </c>
-      <c r="D130" s="1" t="str">
+      <c r="D131" s="1" t="str">
         <f t="shared" si="0"/>
         <v>美妆新秀碎片</v>
       </c>
-      <c r="E130" s="1">
-        <v>2</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G130" s="1">
+      <c r="E131" s="1">
+        <v>2</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G131" s="1">
         <v>7</v>
       </c>
-      <c r="H130" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I130" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J130" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K130" s="1">
+      <c r="H131" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I131" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K131" s="1">
         <v>2125505</v>
       </c>
-      <c r="L130" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M130" s="1" t="str">
+      <c r="L131" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M131" s="1" t="str">
         <f t="shared" si="1"/>
         <v>美妆新秀游客的升星道具</v>
       </c>
-      <c r="P130" s="1">
+      <c r="P131" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
-      <c r="A131" s="1">
+    <row r="132" spans="1:16">
+      <c r="A132" s="1">
         <v>1125506</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C132" s="1">
         <v>1125506</v>
       </c>
-      <c r="D131" s="1" t="str">
+      <c r="D132" s="1" t="str">
         <f t="shared" si="0"/>
         <v>高定女王碎片</v>
       </c>
-      <c r="E131" s="1">
-        <v>2</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G131" s="1">
+      <c r="E132" s="1">
+        <v>2</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G132" s="1">
         <v>7</v>
       </c>
-      <c r="H131" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I131" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K131" s="1">
+      <c r="H132" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I132" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K132" s="1">
         <v>2125506</v>
       </c>
-      <c r="L131" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M131" s="1" t="str">
+      <c r="L132" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M132" s="1" t="str">
         <f t="shared" si="1"/>
         <v>高定女王游客的升星道具</v>
       </c>
-      <c r="P131" s="1">
+      <c r="P132" s="1">
         <v>999999</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16">
-      <c r="A132" s="1">
-        <v>1026001</v>
-      </c>
-      <c r="C132" s="1">
-        <v>1026001</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E132" s="1">
-        <v>2</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G132" s="1">
-        <v>1</v>
-      </c>
-      <c r="H132" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I132" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K132" s="1">
-        <v>2026001</v>
-      </c>
-      <c r="L132" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M132" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="P132" s="1">
-        <v>-1</v>
       </c>
     </row>
     <row r="133" spans="1:16">
       <c r="A133" s="1">
-        <v>1026002</v>
+        <v>1026001</v>
       </c>
       <c r="C133" s="1">
-        <v>1026002</v>
+        <v>1026001</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E133" s="1">
         <v>2</v>
@@ -8102,13 +8108,13 @@
         <v>163</v>
       </c>
       <c r="K133" s="1">
-        <v>2026002</v>
+        <v>2026001</v>
       </c>
       <c r="L133" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M133" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P133" s="1">
         <v>-1</v>
@@ -8116,13 +8122,13 @@
     </row>
     <row r="134" spans="1:16">
       <c r="A134" s="1">
-        <v>1026101</v>
+        <v>1026002</v>
       </c>
       <c r="C134" s="1">
-        <v>1026101</v>
+        <v>1026002</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E134" s="1">
         <v>2</v>
@@ -8131,7 +8137,7 @@
         <v>47</v>
       </c>
       <c r="G134" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" s="1" t="b">
         <v>0</v>
@@ -8143,13 +8149,13 @@
         <v>163</v>
       </c>
       <c r="K134" s="1">
-        <v>2026101</v>
+        <v>2026002</v>
       </c>
       <c r="L134" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M134" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P134" s="1">
         <v>-1</v>
@@ -8157,13 +8163,13 @@
     </row>
     <row r="135" spans="1:16">
       <c r="A135" s="1">
-        <v>1026102</v>
+        <v>1026101</v>
       </c>
       <c r="C135" s="1">
-        <v>1026102</v>
+        <v>1026101</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
@@ -8184,13 +8190,13 @@
         <v>163</v>
       </c>
       <c r="K135" s="1">
-        <v>2026102</v>
+        <v>2026101</v>
       </c>
       <c r="L135" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P135" s="1">
         <v>-1</v>
@@ -8198,13 +8204,13 @@
     </row>
     <row r="136" spans="1:16">
       <c r="A136" s="1">
-        <v>1026201</v>
+        <v>1026102</v>
       </c>
       <c r="C136" s="1">
-        <v>1026201</v>
+        <v>1026102</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -8213,7 +8219,7 @@
         <v>47</v>
       </c>
       <c r="G136" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H136" s="1" t="b">
         <v>0</v>
@@ -8225,13 +8231,13 @@
         <v>163</v>
       </c>
       <c r="K136" s="1">
-        <v>2026201</v>
+        <v>2026102</v>
       </c>
       <c r="L136" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M136" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P136" s="1">
         <v>-1</v>
@@ -8239,13 +8245,13 @@
     </row>
     <row r="137" spans="1:16">
       <c r="A137" s="1">
-        <v>1026202</v>
+        <v>1026201</v>
       </c>
       <c r="C137" s="1">
-        <v>1026202</v>
+        <v>1026201</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -8266,13 +8272,13 @@
         <v>163</v>
       </c>
       <c r="K137" s="1">
-        <v>2026202</v>
+        <v>2026201</v>
       </c>
       <c r="L137" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M137" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P137" s="1">
         <v>-1</v>
@@ -8280,13 +8286,13 @@
     </row>
     <row r="138" spans="1:16">
       <c r="A138" s="1">
-        <v>1026301</v>
+        <v>1026202</v>
       </c>
       <c r="C138" s="1">
-        <v>1026301</v>
+        <v>1026202</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -8295,7 +8301,7 @@
         <v>47</v>
       </c>
       <c r="G138" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H138" s="1" t="b">
         <v>0</v>
@@ -8307,13 +8313,13 @@
         <v>163</v>
       </c>
       <c r="K138" s="1">
-        <v>2026301</v>
+        <v>2026202</v>
       </c>
       <c r="L138" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M138" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P138" s="1">
         <v>-1</v>
@@ -8321,13 +8327,13 @@
     </row>
     <row r="139" spans="1:16">
       <c r="A139" s="1">
-        <v>1026302</v>
+        <v>1026301</v>
       </c>
       <c r="C139" s="1">
-        <v>1026302</v>
+        <v>1026301</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -8348,13 +8354,13 @@
         <v>163</v>
       </c>
       <c r="K139" s="1">
-        <v>2026302</v>
+        <v>2026301</v>
       </c>
       <c r="L139" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M139" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P139" s="1">
         <v>-1</v>
@@ -8362,13 +8368,13 @@
     </row>
     <row r="140" spans="1:16">
       <c r="A140" s="1">
-        <v>1026401</v>
+        <v>1026302</v>
       </c>
       <c r="C140" s="1">
-        <v>1026401</v>
+        <v>1026302</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -8377,7 +8383,7 @@
         <v>47</v>
       </c>
       <c r="G140" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H140" s="1" t="b">
         <v>0</v>
@@ -8389,13 +8395,13 @@
         <v>163</v>
       </c>
       <c r="K140" s="1">
-        <v>2026401</v>
+        <v>2026302</v>
       </c>
       <c r="L140" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M140" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P140" s="1">
         <v>-1</v>
@@ -8403,13 +8409,13 @@
     </row>
     <row r="141" spans="1:16">
       <c r="A141" s="1">
-        <v>1026402</v>
+        <v>1026401</v>
       </c>
       <c r="C141" s="1">
-        <v>1026402</v>
+        <v>1026401</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -8430,13 +8436,13 @@
         <v>163</v>
       </c>
       <c r="K141" s="1">
-        <v>2026402</v>
+        <v>2026401</v>
       </c>
       <c r="L141" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M141" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P141" s="1">
         <v>-1</v>
@@ -8444,13 +8450,13 @@
     </row>
     <row r="142" spans="1:16">
       <c r="A142" s="1">
-        <v>1027001</v>
+        <v>1026402</v>
       </c>
       <c r="C142" s="1">
-        <v>1027001</v>
+        <v>1026402</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -8459,7 +8465,7 @@
         <v>47</v>
       </c>
       <c r="G142" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H142" s="1" t="b">
         <v>0</v>
@@ -8471,13 +8477,13 @@
         <v>163</v>
       </c>
       <c r="K142" s="1">
-        <v>2027001</v>
+        <v>2026402</v>
       </c>
       <c r="L142" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P142" s="1">
         <v>-1</v>
@@ -8485,13 +8491,13 @@
     </row>
     <row r="143" spans="1:16">
       <c r="A143" s="1">
-        <v>1027002</v>
+        <v>1027001</v>
       </c>
       <c r="C143" s="1">
-        <v>1027002</v>
+        <v>1027001</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -8512,13 +8518,13 @@
         <v>163</v>
       </c>
       <c r="K143" s="1">
-        <v>2027002</v>
+        <v>2027001</v>
       </c>
       <c r="L143" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P143" s="1">
         <v>-1</v>
@@ -8526,13 +8532,13 @@
     </row>
     <row r="144" spans="1:16">
       <c r="A144" s="1">
-        <v>1027101</v>
+        <v>1027002</v>
       </c>
       <c r="C144" s="1">
-        <v>1027101</v>
+        <v>1027002</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -8541,7 +8547,7 @@
         <v>47</v>
       </c>
       <c r="G144" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144" s="1" t="b">
         <v>0</v>
@@ -8553,13 +8559,13 @@
         <v>163</v>
       </c>
       <c r="K144" s="1">
-        <v>2027101</v>
+        <v>2027002</v>
       </c>
       <c r="L144" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P144" s="1">
         <v>-1</v>
@@ -8567,13 +8573,13 @@
     </row>
     <row r="145" spans="1:16">
       <c r="A145" s="1">
-        <v>1027102</v>
+        <v>1027101</v>
       </c>
       <c r="C145" s="1">
-        <v>1027102</v>
+        <v>1027101</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -8594,13 +8600,13 @@
         <v>163</v>
       </c>
       <c r="K145" s="1">
-        <v>2027102</v>
+        <v>2027101</v>
       </c>
       <c r="L145" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M145" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P145" s="1">
         <v>-1</v>
@@ -8608,13 +8614,13 @@
     </row>
     <row r="146" spans="1:16">
       <c r="A146" s="1">
-        <v>1027201</v>
+        <v>1027102</v>
       </c>
       <c r="C146" s="1">
-        <v>1027201</v>
+        <v>1027102</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -8623,7 +8629,7 @@
         <v>47</v>
       </c>
       <c r="G146" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H146" s="1" t="b">
         <v>0</v>
@@ -8635,13 +8641,13 @@
         <v>163</v>
       </c>
       <c r="K146" s="1">
-        <v>2027201</v>
+        <v>2027102</v>
       </c>
       <c r="L146" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P146" s="1">
         <v>-1</v>
@@ -8649,13 +8655,13 @@
     </row>
     <row r="147" spans="1:16">
       <c r="A147" s="1">
-        <v>1027202</v>
+        <v>1027201</v>
       </c>
       <c r="C147" s="1">
-        <v>1027202</v>
+        <v>1027201</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -8676,13 +8682,13 @@
         <v>163</v>
       </c>
       <c r="K147" s="1">
-        <v>2027202</v>
+        <v>2027201</v>
       </c>
       <c r="L147" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P147" s="1">
         <v>-1</v>
@@ -8690,13 +8696,13 @@
     </row>
     <row r="148" spans="1:16">
       <c r="A148" s="1">
-        <v>1027301</v>
+        <v>1027202</v>
       </c>
       <c r="C148" s="1">
-        <v>1027301</v>
+        <v>1027202</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -8705,7 +8711,7 @@
         <v>47</v>
       </c>
       <c r="G148" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H148" s="1" t="b">
         <v>0</v>
@@ -8717,13 +8723,13 @@
         <v>163</v>
       </c>
       <c r="K148" s="1">
-        <v>2027301</v>
+        <v>2027202</v>
       </c>
       <c r="L148" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M148" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P148" s="1">
         <v>-1</v>
@@ -8731,13 +8737,13 @@
     </row>
     <row r="149" spans="1:16">
       <c r="A149" s="1">
-        <v>1027302</v>
+        <v>1027301</v>
       </c>
       <c r="C149" s="1">
-        <v>1027302</v>
+        <v>1027301</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -8758,13 +8764,13 @@
         <v>163</v>
       </c>
       <c r="K149" s="1">
-        <v>2027302</v>
+        <v>2027301</v>
       </c>
       <c r="L149" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M149" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P149" s="1">
         <v>-1</v>
@@ -8772,13 +8778,13 @@
     </row>
     <row r="150" spans="1:16">
       <c r="A150" s="1">
-        <v>1027401</v>
+        <v>1027302</v>
       </c>
       <c r="C150" s="1">
-        <v>1027401</v>
+        <v>1027302</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -8787,7 +8793,7 @@
         <v>47</v>
       </c>
       <c r="G150" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H150" s="1" t="b">
         <v>0</v>
@@ -8799,13 +8805,13 @@
         <v>163</v>
       </c>
       <c r="K150" s="1">
-        <v>2027401</v>
+        <v>2027302</v>
       </c>
       <c r="L150" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M150" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P150" s="1">
         <v>-1</v>
@@ -8813,13 +8819,13 @@
     </row>
     <row r="151" spans="1:16">
       <c r="A151" s="1">
-        <v>1027402</v>
+        <v>1027401</v>
       </c>
       <c r="C151" s="1">
-        <v>1027402</v>
+        <v>1027401</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -8840,13 +8846,13 @@
         <v>163</v>
       </c>
       <c r="K151" s="1">
-        <v>2027402</v>
+        <v>2027401</v>
       </c>
       <c r="L151" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M151" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P151" s="1">
         <v>-1</v>
@@ -8854,13 +8860,13 @@
     </row>
     <row r="152" spans="1:16">
       <c r="A152" s="1">
-        <v>1028001</v>
+        <v>1027402</v>
       </c>
       <c r="C152" s="1">
-        <v>1028001</v>
+        <v>1027402</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -8869,7 +8875,7 @@
         <v>47</v>
       </c>
       <c r="G152" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H152" s="1" t="b">
         <v>0</v>
@@ -8881,13 +8887,13 @@
         <v>163</v>
       </c>
       <c r="K152" s="1">
-        <v>2028001</v>
+        <v>2027402</v>
       </c>
       <c r="L152" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P152" s="1">
         <v>-1</v>
@@ -8895,13 +8901,13 @@
     </row>
     <row r="153" spans="1:16">
       <c r="A153" s="1">
-        <v>1028002</v>
+        <v>1028001</v>
       </c>
       <c r="C153" s="1">
-        <v>1028002</v>
+        <v>1028001</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -8922,13 +8928,13 @@
         <v>163</v>
       </c>
       <c r="K153" s="1">
-        <v>2028002</v>
+        <v>2028001</v>
       </c>
       <c r="L153" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P153" s="1">
         <v>-1</v>
@@ -8936,13 +8942,13 @@
     </row>
     <row r="154" spans="1:16">
       <c r="A154" s="1">
-        <v>1028101</v>
+        <v>1028002</v>
       </c>
       <c r="C154" s="1">
-        <v>1028101</v>
+        <v>1028002</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -8951,7 +8957,7 @@
         <v>47</v>
       </c>
       <c r="G154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H154" s="1" t="b">
         <v>0</v>
@@ -8963,13 +8969,13 @@
         <v>163</v>
       </c>
       <c r="K154" s="1">
-        <v>2028101</v>
+        <v>2028002</v>
       </c>
       <c r="L154" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P154" s="1">
         <v>-1</v>
@@ -8977,13 +8983,13 @@
     </row>
     <row r="155" spans="1:16">
       <c r="A155" s="1">
-        <v>1028102</v>
+        <v>1028101</v>
       </c>
       <c r="C155" s="1">
-        <v>1028102</v>
+        <v>1028101</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -9004,13 +9010,13 @@
         <v>163</v>
       </c>
       <c r="K155" s="1">
-        <v>2028102</v>
+        <v>2028101</v>
       </c>
       <c r="L155" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M155" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P155" s="1">
         <v>-1</v>
@@ -9018,13 +9024,13 @@
     </row>
     <row r="156" spans="1:16">
       <c r="A156" s="1">
-        <v>1028201</v>
+        <v>1028102</v>
       </c>
       <c r="C156" s="1">
-        <v>1028201</v>
+        <v>1028102</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -9033,7 +9039,7 @@
         <v>47</v>
       </c>
       <c r="G156" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H156" s="1" t="b">
         <v>0</v>
@@ -9045,13 +9051,13 @@
         <v>163</v>
       </c>
       <c r="K156" s="1">
-        <v>2028201</v>
+        <v>2028102</v>
       </c>
       <c r="L156" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M156" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P156" s="1">
         <v>-1</v>
@@ -9059,13 +9065,13 @@
     </row>
     <row r="157" spans="1:16">
       <c r="A157" s="1">
-        <v>1028202</v>
+        <v>1028201</v>
       </c>
       <c r="C157" s="1">
-        <v>1028202</v>
+        <v>1028201</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -9086,13 +9092,13 @@
         <v>163</v>
       </c>
       <c r="K157" s="1">
-        <v>2028202</v>
+        <v>2028201</v>
       </c>
       <c r="L157" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M157" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P157" s="1">
         <v>-1</v>
@@ -9100,13 +9106,13 @@
     </row>
     <row r="158" spans="1:16">
       <c r="A158" s="1">
-        <v>1028301</v>
+        <v>1028202</v>
       </c>
       <c r="C158" s="1">
-        <v>1028301</v>
+        <v>1028202</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -9115,7 +9121,7 @@
         <v>47</v>
       </c>
       <c r="G158" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H158" s="1" t="b">
         <v>0</v>
@@ -9127,13 +9133,13 @@
         <v>163</v>
       </c>
       <c r="K158" s="1">
-        <v>2028301</v>
+        <v>2028202</v>
       </c>
       <c r="L158" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P158" s="1">
         <v>-1</v>
@@ -9141,13 +9147,13 @@
     </row>
     <row r="159" spans="1:16">
       <c r="A159" s="1">
-        <v>1028302</v>
+        <v>1028301</v>
       </c>
       <c r="C159" s="1">
-        <v>1028302</v>
+        <v>1028301</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -9168,13 +9174,13 @@
         <v>163</v>
       </c>
       <c r="K159" s="1">
-        <v>2028302</v>
+        <v>2028301</v>
       </c>
       <c r="L159" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P159" s="1">
         <v>-1</v>
@@ -9182,13 +9188,13 @@
     </row>
     <row r="160" spans="1:16">
       <c r="A160" s="1">
-        <v>1028401</v>
+        <v>1028302</v>
       </c>
       <c r="C160" s="1">
-        <v>1028401</v>
+        <v>1028302</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -9197,7 +9203,7 @@
         <v>47</v>
       </c>
       <c r="G160" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H160" s="1" t="b">
         <v>0</v>
@@ -9209,13 +9215,13 @@
         <v>163</v>
       </c>
       <c r="K160" s="1">
-        <v>2028401</v>
+        <v>2028302</v>
       </c>
       <c r="L160" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P160" s="1">
         <v>-1</v>
@@ -9223,13 +9229,13 @@
     </row>
     <row r="161" spans="1:16">
       <c r="A161" s="1">
-        <v>1028402</v>
+        <v>1028401</v>
       </c>
       <c r="C161" s="1">
-        <v>1028402</v>
+        <v>1028401</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -9250,13 +9256,13 @@
         <v>163</v>
       </c>
       <c r="K161" s="1">
-        <v>2028402</v>
+        <v>2028401</v>
       </c>
       <c r="L161" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P161" s="1">
         <v>-1</v>
@@ -9264,14 +9270,13 @@
     </row>
     <row r="162" spans="1:16">
       <c r="A162" s="1">
-        <v>1126001</v>
+        <v>1028402</v>
       </c>
       <c r="C162" s="1">
-        <v>1126001</v>
-      </c>
-      <c r="D162" s="1" t="str">
-        <f>D132&amp;"碎片"</f>
-        <v>威廉碎片</v>
+        <v>1028402</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -9280,41 +9285,40 @@
         <v>47</v>
       </c>
       <c r="G162" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H162" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>163</v>
       </c>
       <c r="K162" s="1">
-        <v>2126001</v>
+        <v>2028402</v>
       </c>
       <c r="L162" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M162" s="1" t="str">
-        <f>D132&amp;"雇员的升星道具"</f>
-        <v>威廉雇员的升星道具</v>
+      <c r="M162" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="P162" s="1">
-        <v>999999</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="163" spans="1:16">
       <c r="A163" s="1">
-        <v>1126002</v>
+        <v>1126001</v>
       </c>
       <c r="C163" s="1">
-        <v>1126002</v>
+        <v>1126001</v>
       </c>
       <c r="D163" s="1" t="str">
-        <f t="shared" ref="D163:D191" si="2">D133&amp;"碎片"</f>
-        <v>艾拉碎片</v>
+        <f>D133&amp;"碎片"</f>
+        <v>威廉碎片</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -9335,14 +9339,14 @@
         <v>163</v>
       </c>
       <c r="K163" s="1">
-        <v>2126002</v>
+        <v>2126001</v>
       </c>
       <c r="L163" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M163" s="1" t="str">
-        <f t="shared" ref="M163:M191" si="3">D133&amp;"雇员的升星道具"</f>
-        <v>艾拉雇员的升星道具</v>
+        <f>D133&amp;"雇员的升星道具"</f>
+        <v>威廉雇员的升星道具</v>
       </c>
       <c r="P163" s="1">
         <v>999999</v>
@@ -9350,1255 +9354,1257 @@
     </row>
     <row r="164" spans="1:16">
       <c r="A164" s="1">
+        <v>1126002</v>
+      </c>
+      <c r="C164" s="1">
+        <v>1126002</v>
+      </c>
+      <c r="D164" s="1" t="str">
+        <f t="shared" ref="D164:D192" si="2">D134&amp;"碎片"</f>
+        <v>艾拉碎片</v>
+      </c>
+      <c r="E164" s="1">
+        <v>2</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G164" s="1">
+        <v>1</v>
+      </c>
+      <c r="H164" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I164" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K164" s="1">
+        <v>2126002</v>
+      </c>
+      <c r="L164" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M164" s="1" t="str">
+        <f t="shared" ref="M164:M192" si="3">D134&amp;"雇员的升星道具"</f>
+        <v>艾拉雇员的升星道具</v>
+      </c>
+      <c r="P164" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16">
+      <c r="A165" s="1">
         <v>1126101</v>
       </c>
-      <c r="C164" s="1">
+      <c r="C165" s="1">
         <v>1126101</v>
       </c>
-      <c r="D164" s="1" t="str">
+      <c r="D165" s="1" t="str">
         <f t="shared" si="2"/>
         <v>亨利碎片</v>
       </c>
-      <c r="E164" s="1">
-        <v>2</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G164" s="1">
-        <v>2</v>
-      </c>
-      <c r="H164" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I164" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K164" s="1">
+      <c r="E165" s="1">
+        <v>2</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G165" s="1">
+        <v>2</v>
+      </c>
+      <c r="H165" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I165" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J165" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K165" s="1">
         <v>2126101</v>
       </c>
-      <c r="L164" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M164" s="1" t="str">
+      <c r="L165" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M165" s="1" t="str">
         <f t="shared" si="3"/>
         <v>亨利雇员的升星道具</v>
       </c>
-      <c r="P164" s="1">
+      <c r="P165" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
-      <c r="A165" s="1">
+    <row r="166" spans="1:16">
+      <c r="A166" s="1">
         <v>1126102</v>
       </c>
-      <c r="C165" s="1">
+      <c r="C166" s="1">
         <v>1126102</v>
       </c>
-      <c r="D165" s="1" t="str">
+      <c r="D166" s="1" t="str">
         <f t="shared" si="2"/>
         <v>艾玛碎片</v>
       </c>
-      <c r="E165" s="1">
-        <v>2</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G165" s="1">
-        <v>2</v>
-      </c>
-      <c r="H165" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I165" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J165" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K165" s="1">
+      <c r="E166" s="1">
+        <v>2</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G166" s="1">
+        <v>2</v>
+      </c>
+      <c r="H166" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I166" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J166" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K166" s="1">
         <v>2126102</v>
       </c>
-      <c r="L165" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M165" s="1" t="str">
+      <c r="L166" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M166" s="1" t="str">
         <f t="shared" si="3"/>
         <v>艾玛雇员的升星道具</v>
       </c>
-      <c r="P165" s="1">
+      <c r="P166" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
-      <c r="A166" s="1">
+    <row r="167" spans="1:16">
+      <c r="A167" s="1">
         <v>1126201</v>
       </c>
-      <c r="C166" s="1">
+      <c r="C167" s="1">
         <v>1126201</v>
       </c>
-      <c r="D166" s="1" t="str">
+      <c r="D167" s="1" t="str">
         <f t="shared" si="2"/>
         <v>乔治碎片</v>
       </c>
-      <c r="E166" s="1">
-        <v>2</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G166" s="1">
+      <c r="E167" s="1">
+        <v>2</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G167" s="1">
         <v>3</v>
       </c>
-      <c r="H166" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I166" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J166" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K166" s="1">
+      <c r="H167" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I167" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K167" s="1">
         <v>2126201</v>
       </c>
-      <c r="L166" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M166" s="1" t="str">
+      <c r="L167" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M167" s="1" t="str">
         <f t="shared" si="3"/>
         <v>乔治雇员的升星道具</v>
       </c>
-      <c r="P166" s="1">
+      <c r="P167" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
-      <c r="A167" s="1">
+    <row r="168" spans="1:16">
+      <c r="A168" s="1">
         <v>1126202</v>
       </c>
-      <c r="C167" s="1">
+      <c r="C168" s="1">
         <v>1126202</v>
       </c>
-      <c r="D167" s="1" t="str">
+      <c r="D168" s="1" t="str">
         <f t="shared" si="2"/>
         <v>艾娃碎片</v>
       </c>
-      <c r="E167" s="1">
-        <v>2</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G167" s="1">
+      <c r="E168" s="1">
+        <v>2</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G168" s="1">
         <v>3</v>
       </c>
-      <c r="H167" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I167" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J167" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K167" s="1">
+      <c r="H168" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I168" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K168" s="1">
         <v>2126202</v>
       </c>
-      <c r="L167" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M167" s="1" t="str">
+      <c r="L168" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M168" s="1" t="str">
         <f t="shared" si="3"/>
         <v>艾娃雇员的升星道具</v>
       </c>
-      <c r="P167" s="1">
+      <c r="P168" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
-      <c r="A168" s="1">
+    <row r="169" spans="1:16">
+      <c r="A169" s="1">
         <v>1126301</v>
       </c>
-      <c r="C168" s="1">
+      <c r="C169" s="1">
         <v>1126301</v>
       </c>
-      <c r="D168" s="1" t="str">
+      <c r="D169" s="1" t="str">
         <f t="shared" si="2"/>
         <v>亚瑟碎片</v>
       </c>
-      <c r="E168" s="1">
-        <v>2</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G168" s="1">
+      <c r="E169" s="1">
+        <v>2</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G169" s="1">
         <v>4</v>
       </c>
-      <c r="H168" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I168" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K168" s="1">
+      <c r="H169" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I169" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J169" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K169" s="1">
         <v>2126301</v>
       </c>
-      <c r="L168" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M168" s="1" t="str">
+      <c r="L169" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M169" s="1" t="str">
         <f t="shared" si="3"/>
         <v>亚瑟雇员的升星道具</v>
       </c>
-      <c r="P168" s="1">
+      <c r="P169" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
-      <c r="A169" s="1">
+    <row r="170" spans="1:16">
+      <c r="A170" s="1">
         <v>1126302</v>
       </c>
-      <c r="C169" s="1">
+      <c r="C170" s="1">
         <v>1126302</v>
       </c>
-      <c r="D169" s="1" t="str">
+      <c r="D170" s="1" t="str">
         <f t="shared" si="2"/>
         <v>安娜碎片</v>
       </c>
-      <c r="E169" s="1">
-        <v>2</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G169" s="1">
+      <c r="E170" s="1">
+        <v>2</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G170" s="1">
         <v>4</v>
       </c>
-      <c r="H169" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I169" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J169" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K169" s="1">
+      <c r="H170" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I170" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J170" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K170" s="1">
         <v>2126302</v>
       </c>
-      <c r="L169" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M169" s="1" t="str">
+      <c r="L170" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M170" s="1" t="str">
         <f t="shared" si="3"/>
         <v>安娜雇员的升星道具</v>
       </c>
-      <c r="P169" s="1">
+      <c r="P170" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
-      <c r="A170" s="1">
+    <row r="171" spans="1:16">
+      <c r="A171" s="1">
         <v>1126401</v>
       </c>
-      <c r="C170" s="1">
+      <c r="C171" s="1">
         <v>1126401</v>
       </c>
-      <c r="D170" s="1" t="str">
+      <c r="D171" s="1" t="str">
         <f t="shared" si="2"/>
         <v>马修碎片</v>
       </c>
-      <c r="E170" s="1">
-        <v>2</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G170" s="1">
+      <c r="E171" s="1">
+        <v>2</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G171" s="1">
         <v>7</v>
       </c>
-      <c r="H170" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I170" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J170" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K170" s="1">
+      <c r="H171" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I171" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K171" s="1">
         <v>2126401</v>
       </c>
-      <c r="L170" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M170" s="1" t="str">
+      <c r="L171" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M171" s="1" t="str">
         <f t="shared" si="3"/>
         <v>马修雇员的升星道具</v>
       </c>
-      <c r="P170" s="1">
+      <c r="P171" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
-      <c r="A171" s="1">
+    <row r="172" spans="1:16">
+      <c r="A172" s="1">
         <v>1126402</v>
       </c>
-      <c r="C171" s="1">
+      <c r="C172" s="1">
         <v>1126402</v>
       </c>
-      <c r="D171" s="1" t="str">
+      <c r="D172" s="1" t="str">
         <f t="shared" si="2"/>
         <v>哈珀碎片</v>
       </c>
-      <c r="E171" s="1">
-        <v>2</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G171" s="1">
+      <c r="E172" s="1">
+        <v>2</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G172" s="1">
         <v>7</v>
       </c>
-      <c r="H171" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I171" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J171" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K171" s="1">
+      <c r="H172" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I172" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J172" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K172" s="1">
         <v>2126402</v>
       </c>
-      <c r="L171" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M171" s="1" t="str">
+      <c r="L172" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M172" s="1" t="str">
         <f t="shared" si="3"/>
         <v>哈珀雇员的升星道具</v>
       </c>
-      <c r="P171" s="1">
+      <c r="P172" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
-      <c r="A172" s="1">
+    <row r="173" spans="1:16">
+      <c r="A173" s="1">
         <v>1127001</v>
       </c>
-      <c r="C172" s="1">
+      <c r="C173" s="1">
         <v>1127001</v>
       </c>
-      <c r="D172" s="1" t="str">
+      <c r="D173" s="1" t="str">
         <f t="shared" si="2"/>
         <v>拉斐尔碎片</v>
       </c>
-      <c r="E172" s="1">
-        <v>2</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G172" s="1">
-        <v>1</v>
-      </c>
-      <c r="H172" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I172" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J172" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K172" s="1">
+      <c r="E173" s="1">
+        <v>2</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G173" s="1">
+        <v>1</v>
+      </c>
+      <c r="H173" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I173" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K173" s="1">
         <v>2127001</v>
       </c>
-      <c r="L172" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M172" s="1" t="str">
+      <c r="L173" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M173" s="1" t="str">
         <f t="shared" si="3"/>
         <v>拉斐尔雇员的升星道具</v>
       </c>
-      <c r="P172" s="1">
+      <c r="P173" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
-      <c r="A173" s="1">
+    <row r="174" spans="1:16">
+      <c r="A174" s="1">
         <v>1127002</v>
       </c>
-      <c r="C173" s="1">
+      <c r="C174" s="1">
         <v>1127002</v>
       </c>
-      <c r="D173" s="1" t="str">
+      <c r="D174" s="1" t="str">
         <f t="shared" si="2"/>
         <v>伊芙琳碎片</v>
       </c>
-      <c r="E173" s="1">
-        <v>2</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G173" s="1">
-        <v>1</v>
-      </c>
-      <c r="H173" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I173" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J173" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K173" s="1">
+      <c r="E174" s="1">
+        <v>2</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G174" s="1">
+        <v>1</v>
+      </c>
+      <c r="H174" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I174" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J174" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K174" s="1">
         <v>2127002</v>
       </c>
-      <c r="L173" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M173" s="1" t="str">
+      <c r="L174" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M174" s="1" t="str">
         <f t="shared" si="3"/>
         <v>伊芙琳雇员的升星道具</v>
       </c>
-      <c r="P173" s="1">
+      <c r="P174" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
-      <c r="A174" s="1">
+    <row r="175" spans="1:16">
+      <c r="A175" s="1">
         <v>1127101</v>
       </c>
-      <c r="C174" s="1">
+      <c r="C175" s="1">
         <v>1127101</v>
       </c>
-      <c r="D174" s="1" t="str">
+      <c r="D175" s="1" t="str">
         <f t="shared" si="2"/>
         <v>埃米尔碎片</v>
       </c>
-      <c r="E174" s="1">
-        <v>2</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G174" s="1">
-        <v>2</v>
-      </c>
-      <c r="H174" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I174" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J174" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K174" s="1">
+      <c r="E175" s="1">
+        <v>2</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G175" s="1">
+        <v>2</v>
+      </c>
+      <c r="H175" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I175" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K175" s="1">
         <v>2127101</v>
       </c>
-      <c r="L174" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M174" s="1" t="str">
+      <c r="L175" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M175" s="1" t="str">
         <f t="shared" si="3"/>
         <v>埃米尔雇员的升星道具</v>
       </c>
-      <c r="P174" s="1">
+      <c r="P175" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
-      <c r="A175" s="1">
+    <row r="176" spans="1:16">
+      <c r="A176" s="1">
         <v>1127102</v>
       </c>
-      <c r="C175" s="1">
+      <c r="C176" s="1">
         <v>1127102</v>
       </c>
-      <c r="D175" s="1" t="str">
+      <c r="D176" s="1" t="str">
         <f t="shared" si="2"/>
         <v>夏洛特碎片</v>
       </c>
-      <c r="E175" s="1">
-        <v>2</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G175" s="1">
-        <v>2</v>
-      </c>
-      <c r="H175" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I175" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J175" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K175" s="1">
+      <c r="E176" s="1">
+        <v>2</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G176" s="1">
+        <v>2</v>
+      </c>
+      <c r="H176" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I176" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J176" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K176" s="1">
         <v>2127102</v>
       </c>
-      <c r="L175" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M175" s="1" t="str">
+      <c r="L176" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M176" s="1" t="str">
         <f t="shared" si="3"/>
         <v>夏洛特雇员的升星道具</v>
       </c>
-      <c r="P175" s="1">
+      <c r="P176" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
-      <c r="A176" s="1">
+    <row r="177" spans="1:16">
+      <c r="A177" s="1">
         <v>1127201</v>
       </c>
-      <c r="C176" s="1">
+      <c r="C177" s="1">
         <v>1127201</v>
       </c>
-      <c r="D176" s="1" t="str">
+      <c r="D177" s="1" t="str">
         <f t="shared" si="2"/>
         <v>雷蒙德碎片</v>
       </c>
-      <c r="E176" s="1">
-        <v>2</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G176" s="1">
+      <c r="E177" s="1">
+        <v>2</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G177" s="1">
         <v>3</v>
       </c>
-      <c r="H176" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I176" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J176" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K176" s="1">
+      <c r="H177" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I177" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J177" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K177" s="1">
         <v>2127201</v>
       </c>
-      <c r="L176" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M176" s="1" t="str">
+      <c r="L177" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M177" s="1" t="str">
         <f t="shared" si="3"/>
         <v>雷蒙德雇员的升星道具</v>
       </c>
-      <c r="P176" s="1">
+      <c r="P177" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
-      <c r="A177" s="1">
+    <row r="178" spans="1:16">
+      <c r="A178" s="1">
         <v>1127202</v>
       </c>
-      <c r="C177" s="1">
+      <c r="C178" s="1">
         <v>1127202</v>
       </c>
-      <c r="D177" s="1" t="str">
+      <c r="D178" s="1" t="str">
         <f t="shared" si="2"/>
         <v>斯嘉丽碎片</v>
       </c>
-      <c r="E177" s="1">
-        <v>2</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G177" s="1">
+      <c r="E178" s="1">
+        <v>2</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G178" s="1">
         <v>3</v>
       </c>
-      <c r="H177" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I177" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K177" s="1">
+      <c r="H178" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I178" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J178" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K178" s="1">
         <v>2127202</v>
       </c>
-      <c r="L177" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M177" s="1" t="str">
+      <c r="L178" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M178" s="1" t="str">
         <f t="shared" si="3"/>
         <v>斯嘉丽雇员的升星道具</v>
       </c>
-      <c r="P177" s="1">
+      <c r="P178" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
-      <c r="A178" s="1">
+    <row r="179" spans="1:16">
+      <c r="A179" s="1">
         <v>1127301</v>
       </c>
-      <c r="C178" s="1">
+      <c r="C179" s="1">
         <v>1127301</v>
       </c>
-      <c r="D178" s="1" t="str">
+      <c r="D179" s="1" t="str">
         <f t="shared" si="2"/>
         <v>丹尼尔碎片</v>
       </c>
-      <c r="E178" s="1">
-        <v>2</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G178" s="1">
+      <c r="E179" s="1">
+        <v>2</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G179" s="1">
         <v>4</v>
       </c>
-      <c r="H178" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I178" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J178" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K178" s="1">
+      <c r="H179" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I179" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K179" s="1">
         <v>2127301</v>
       </c>
-      <c r="L178" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M178" s="1" t="str">
+      <c r="L179" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M179" s="1" t="str">
         <f t="shared" si="3"/>
         <v>丹尼尔雇员的升星道具</v>
       </c>
-      <c r="P178" s="1">
+      <c r="P179" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
-      <c r="A179" s="1">
+    <row r="180" spans="1:16">
+      <c r="A180" s="1">
         <v>1127302</v>
       </c>
-      <c r="C179" s="1">
+      <c r="C180" s="1">
         <v>1127302</v>
       </c>
-      <c r="D179" s="1" t="str">
+      <c r="D180" s="1" t="str">
         <f t="shared" si="2"/>
         <v>莉莉安碎片</v>
       </c>
-      <c r="E179" s="1">
-        <v>2</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G179" s="1">
+      <c r="E180" s="1">
+        <v>2</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G180" s="1">
         <v>4</v>
       </c>
-      <c r="H179" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I179" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J179" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K179" s="1">
+      <c r="H180" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I180" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K180" s="1">
         <v>2127302</v>
       </c>
-      <c r="L179" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M179" s="1" t="str">
+      <c r="L180" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M180" s="1" t="str">
         <f t="shared" si="3"/>
         <v>莉莉安雇员的升星道具</v>
       </c>
-      <c r="P179" s="1">
+      <c r="P180" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
-      <c r="A180" s="1">
+    <row r="181" spans="1:16">
+      <c r="A181" s="1">
         <v>1127401</v>
       </c>
-      <c r="C180" s="1">
+      <c r="C181" s="1">
         <v>1127401</v>
       </c>
-      <c r="D180" s="1" t="str">
+      <c r="D181" s="1" t="str">
         <f t="shared" si="2"/>
         <v>卢卡斯碎片</v>
       </c>
-      <c r="E180" s="1">
-        <v>2</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G180" s="1">
+      <c r="E181" s="1">
+        <v>2</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G181" s="1">
         <v>7</v>
       </c>
-      <c r="H180" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I180" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J180" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K180" s="1">
+      <c r="H181" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I181" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J181" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K181" s="1">
         <v>2127401</v>
       </c>
-      <c r="L180" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M180" s="1" t="str">
+      <c r="L181" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M181" s="1" t="str">
         <f t="shared" si="3"/>
         <v>卢卡斯雇员的升星道具</v>
       </c>
-      <c r="P180" s="1">
+      <c r="P181" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
-      <c r="A181" s="1">
+    <row r="182" spans="1:16">
+      <c r="A182" s="1">
         <v>1127402</v>
       </c>
-      <c r="C181" s="1">
+      <c r="C182" s="1">
         <v>1127402</v>
       </c>
-      <c r="D181" s="1" t="str">
+      <c r="D182" s="1" t="str">
         <f t="shared" si="2"/>
         <v>克拉拉碎片</v>
       </c>
-      <c r="E181" s="1">
-        <v>2</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G181" s="1">
+      <c r="E182" s="1">
+        <v>2</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G182" s="1">
         <v>7</v>
       </c>
-      <c r="H181" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I181" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J181" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K181" s="1">
+      <c r="H182" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I182" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K182" s="1">
         <v>2127402</v>
       </c>
-      <c r="L181" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M181" s="1" t="str">
+      <c r="L182" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M182" s="1" t="str">
         <f t="shared" si="3"/>
         <v>克拉拉雇员的升星道具</v>
       </c>
-      <c r="P181" s="1">
+      <c r="P182" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
-      <c r="A182" s="1">
+    <row r="183" spans="1:16">
+      <c r="A183" s="1">
         <v>1128001</v>
       </c>
-      <c r="C182" s="1">
+      <c r="C183" s="1">
         <v>1128001</v>
       </c>
-      <c r="D182" s="1" t="str">
+      <c r="D183" s="1" t="str">
         <f t="shared" si="2"/>
         <v>尼古拉斯碎片</v>
       </c>
-      <c r="E182" s="1">
-        <v>2</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G182" s="1">
-        <v>1</v>
-      </c>
-      <c r="H182" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I182" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J182" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K182" s="1">
+      <c r="E183" s="1">
+        <v>2</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G183" s="1">
+        <v>1</v>
+      </c>
+      <c r="H183" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K183" s="1">
         <v>2128001</v>
       </c>
-      <c r="L182" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M182" s="1" t="str">
+      <c r="L183" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M183" s="1" t="str">
         <f t="shared" si="3"/>
         <v>尼古拉斯雇员的升星道具</v>
       </c>
-      <c r="P182" s="1">
+      <c r="P183" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
-      <c r="A183" s="1">
+    <row r="184" spans="1:16">
+      <c r="A184" s="1">
         <v>1128002</v>
       </c>
-      <c r="C183" s="1">
+      <c r="C184" s="1">
         <v>1128002</v>
       </c>
-      <c r="D183" s="1" t="str">
+      <c r="D184" s="1" t="str">
         <f t="shared" si="2"/>
         <v>奥利维亚碎片</v>
       </c>
-      <c r="E183" s="1">
-        <v>2</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G183" s="1">
-        <v>1</v>
-      </c>
-      <c r="H183" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I183" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J183" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K183" s="1">
+      <c r="E184" s="1">
+        <v>2</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G184" s="1">
+        <v>1</v>
+      </c>
+      <c r="H184" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I184" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J184" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K184" s="1">
         <v>2128002</v>
       </c>
-      <c r="L183" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M183" s="1" t="str">
+      <c r="L184" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M184" s="1" t="str">
         <f t="shared" si="3"/>
         <v>奥利维亚雇员的升星道具</v>
       </c>
-      <c r="P183" s="1">
+      <c r="P184" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
-      <c r="A184" s="1">
+    <row r="185" spans="1:16">
+      <c r="A185" s="1">
         <v>1128101</v>
       </c>
-      <c r="C184" s="1">
+      <c r="C185" s="1">
         <v>1128101</v>
       </c>
-      <c r="D184" s="1" t="str">
+      <c r="D185" s="1" t="str">
         <f t="shared" si="2"/>
         <v>亚历山大碎片</v>
       </c>
-      <c r="E184" s="1">
-        <v>2</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G184" s="1">
-        <v>2</v>
-      </c>
-      <c r="H184" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I184" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J184" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K184" s="1">
+      <c r="E185" s="1">
+        <v>2</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G185" s="1">
+        <v>2</v>
+      </c>
+      <c r="H185" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I185" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J185" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K185" s="1">
         <v>2128101</v>
       </c>
-      <c r="L184" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M184" s="1" t="str">
+      <c r="L185" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M185" s="1" t="str">
         <f t="shared" si="3"/>
         <v>亚历山大雇员的升星道具</v>
       </c>
-      <c r="P184" s="1">
+      <c r="P185" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
-      <c r="A185" s="1">
+    <row r="186" spans="1:16">
+      <c r="A186" s="1">
         <v>1128102</v>
       </c>
-      <c r="C185" s="1">
+      <c r="C186" s="1">
         <v>1128102</v>
       </c>
-      <c r="D185" s="1" t="str">
+      <c r="D186" s="1" t="str">
         <f t="shared" si="2"/>
         <v>玛格丽特碎片</v>
       </c>
-      <c r="E185" s="1">
-        <v>2</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G185" s="1">
-        <v>2</v>
-      </c>
-      <c r="H185" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I185" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J185" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K185" s="1">
+      <c r="E186" s="1">
+        <v>2</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G186" s="1">
+        <v>2</v>
+      </c>
+      <c r="H186" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I186" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J186" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K186" s="1">
         <v>2128102</v>
       </c>
-      <c r="L185" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M185" s="1" t="str">
+      <c r="L186" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M186" s="1" t="str">
         <f t="shared" si="3"/>
         <v>玛格丽特雇员的升星道具</v>
       </c>
-      <c r="P185" s="1">
+      <c r="P186" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
-      <c r="A186" s="1">
+    <row r="187" spans="1:16">
+      <c r="A187" s="1">
         <v>1128201</v>
       </c>
-      <c r="C186" s="1">
+      <c r="C187" s="1">
         <v>1128201</v>
       </c>
-      <c r="D186" s="1" t="str">
+      <c r="D187" s="1" t="str">
         <f t="shared" si="2"/>
         <v>奥古斯特碎片</v>
       </c>
-      <c r="E186" s="1">
-        <v>2</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G186" s="1">
+      <c r="E187" s="1">
+        <v>2</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G187" s="1">
         <v>3</v>
       </c>
-      <c r="H186" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I186" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J186" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K186" s="1">
+      <c r="H187" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I187" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J187" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K187" s="1">
         <v>2128201</v>
       </c>
-      <c r="L186" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M186" s="1" t="str">
+      <c r="L187" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M187" s="1" t="str">
         <f t="shared" si="3"/>
         <v>奥古斯特雇员的升星道具</v>
       </c>
-      <c r="P186" s="1">
+      <c r="P187" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
-      <c r="A187" s="1">
+    <row r="188" spans="1:16">
+      <c r="A188" s="1">
         <v>1128202</v>
       </c>
-      <c r="C187" s="1">
+      <c r="C188" s="1">
         <v>1128202</v>
       </c>
-      <c r="D187" s="1" t="str">
+      <c r="D188" s="1" t="str">
         <f t="shared" si="2"/>
         <v>维奥莱特碎片</v>
       </c>
-      <c r="E187" s="1">
-        <v>2</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G187" s="1">
+      <c r="E188" s="1">
+        <v>2</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G188" s="1">
         <v>3</v>
       </c>
-      <c r="H187" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I187" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J187" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K187" s="1">
+      <c r="H188" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I188" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J188" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K188" s="1">
         <v>2128202</v>
       </c>
-      <c r="L187" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M187" s="1" t="str">
+      <c r="L188" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M188" s="1" t="str">
         <f t="shared" si="3"/>
         <v>维奥莱特雇员的升星道具</v>
       </c>
-      <c r="P187" s="1">
+      <c r="P188" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
-      <c r="A188" s="1">
+    <row r="189" spans="1:16">
+      <c r="A189" s="1">
         <v>1128301</v>
       </c>
-      <c r="C188" s="1">
+      <c r="C189" s="1">
         <v>1128301</v>
       </c>
-      <c r="D188" s="1" t="str">
+      <c r="D189" s="1" t="str">
         <f t="shared" si="2"/>
         <v>费利克斯碎片</v>
       </c>
-      <c r="E188" s="1">
-        <v>2</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G188" s="1">
+      <c r="E189" s="1">
+        <v>2</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G189" s="1">
         <v>4</v>
       </c>
-      <c r="H188" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I188" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J188" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K188" s="1">
+      <c r="H189" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I189" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J189" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K189" s="1">
         <v>2128301</v>
       </c>
-      <c r="L188" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M188" s="1" t="str">
+      <c r="L189" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M189" s="1" t="str">
         <f t="shared" si="3"/>
         <v>费利克斯雇员的升星道具</v>
       </c>
-      <c r="P188" s="1">
+      <c r="P189" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
-      <c r="A189" s="1">
+    <row r="190" spans="1:16">
+      <c r="A190" s="1">
         <v>1128302</v>
       </c>
-      <c r="C189" s="1">
+      <c r="C190" s="1">
         <v>1128302</v>
       </c>
-      <c r="D189" s="1" t="str">
+      <c r="D190" s="1" t="str">
         <f t="shared" si="2"/>
         <v>维多利亚碎片</v>
       </c>
-      <c r="E189" s="1">
-        <v>2</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G189" s="1">
+      <c r="E190" s="1">
+        <v>2</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G190" s="1">
         <v>4</v>
       </c>
-      <c r="H189" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I189" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J189" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K189" s="1">
+      <c r="H190" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I190" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J190" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K190" s="1">
         <v>2128302</v>
       </c>
-      <c r="L189" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M189" s="1" t="str">
+      <c r="L190" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M190" s="1" t="str">
         <f t="shared" si="3"/>
         <v>维多利亚雇员的升星道具</v>
       </c>
-      <c r="P189" s="1">
+      <c r="P190" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="190" spans="1:16">
-      <c r="A190" s="1">
+    <row r="191" spans="1:16">
+      <c r="A191" s="1">
         <v>1128401</v>
       </c>
-      <c r="C190" s="1">
+      <c r="C191" s="1">
         <v>1128401</v>
       </c>
-      <c r="D190" s="1" t="str">
+      <c r="D191" s="1" t="str">
         <f t="shared" si="2"/>
         <v>阿尔弗雷德碎片</v>
       </c>
-      <c r="E190" s="1">
-        <v>2</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G190" s="1">
+      <c r="E191" s="1">
+        <v>2</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G191" s="1">
         <v>7</v>
       </c>
-      <c r="H190" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I190" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J190" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K190" s="1">
+      <c r="H191" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I191" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K191" s="1">
         <v>2128401</v>
       </c>
-      <c r="L190" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M190" s="1" t="str">
+      <c r="L191" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M191" s="1" t="str">
         <f t="shared" si="3"/>
         <v>阿尔弗雷德雇员的升星道具</v>
       </c>
-      <c r="P190" s="1">
+      <c r="P191" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="191" spans="1:16">
-      <c r="A191" s="1">
+    <row r="192" spans="1:16">
+      <c r="A192" s="1">
         <v>1128402</v>
       </c>
-      <c r="C191" s="1">
+      <c r="C192" s="1">
         <v>1128402</v>
       </c>
-      <c r="D191" s="1" t="str">
+      <c r="D192" s="1" t="str">
         <f t="shared" si="2"/>
         <v>伊丽莎白碎片</v>
       </c>
-      <c r="E191" s="1">
-        <v>2</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G191" s="1">
+      <c r="E192" s="1">
+        <v>2</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G192" s="1">
         <v>7</v>
       </c>
-      <c r="H191" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I191" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J191" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K191" s="1">
+      <c r="H192" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I192" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J192" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K192" s="1">
         <v>2128402</v>
       </c>
-      <c r="L191" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M191" s="1" t="str">
+      <c r="L192" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M192" s="1" t="str">
         <f t="shared" si="3"/>
         <v>伊丽莎白雇员的升星道具</v>
       </c>
-      <c r="P191" s="1">
+      <c r="P192" s="1">
         <v>999999</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16">
-      <c r="A192" s="1">
-        <v>1200001</v>
-      </c>
-      <c r="C192" s="1">
-        <v>1200001</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E192" s="1">
-        <v>2</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G192" s="1">
-        <v>1</v>
-      </c>
-      <c r="H192" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I192" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J192" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="K192" s="1">
-        <v>2200001</v>
-      </c>
-      <c r="L192" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M192" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="P192" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:16">
       <c r="A193" s="1">
-        <v>1200002</v>
+        <v>1200001</v>
       </c>
       <c r="C193" s="1">
-        <v>1200002</v>
+        <v>1200001</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>250</v>
@@ -10622,7 +10628,7 @@
         <v>163</v>
       </c>
       <c r="K193" s="1">
-        <v>2200002</v>
+        <v>2200001</v>
       </c>
       <c r="L193" s="1" t="b">
         <v>0</v>
@@ -10636,10 +10642,10 @@
     </row>
     <row r="194" spans="1:16">
       <c r="A194" s="1">
-        <v>1200003</v>
+        <v>1200002</v>
       </c>
       <c r="C194" s="1">
-        <v>1200003</v>
+        <v>1200002</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>252</v>
@@ -10663,7 +10669,7 @@
         <v>163</v>
       </c>
       <c r="K194" s="1">
-        <v>2200003</v>
+        <v>2200002</v>
       </c>
       <c r="L194" s="1" t="b">
         <v>0</v>
@@ -10677,10 +10683,10 @@
     </row>
     <row r="195" spans="1:16">
       <c r="A195" s="1">
-        <v>1200004</v>
+        <v>1200003</v>
       </c>
       <c r="C195" s="1">
-        <v>1200004</v>
+        <v>1200003</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>254</v>
@@ -10704,7 +10710,7 @@
         <v>163</v>
       </c>
       <c r="K195" s="1">
-        <v>2200004</v>
+        <v>2200003</v>
       </c>
       <c r="L195" s="1" t="b">
         <v>0</v>
@@ -10718,10 +10724,10 @@
     </row>
     <row r="196" spans="1:16">
       <c r="A196" s="1">
-        <v>1200005</v>
+        <v>1200004</v>
       </c>
       <c r="C196" s="1">
-        <v>1200005</v>
+        <v>1200004</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>256</v>
@@ -10745,7 +10751,7 @@
         <v>163</v>
       </c>
       <c r="K196" s="1">
-        <v>2200005</v>
+        <v>2200004</v>
       </c>
       <c r="L196" s="1" t="b">
         <v>0</v>
@@ -10759,10 +10765,10 @@
     </row>
     <row r="197" spans="1:16">
       <c r="A197" s="1">
-        <v>1200006</v>
+        <v>1200005</v>
       </c>
       <c r="C197" s="1">
-        <v>1200006</v>
+        <v>1200005</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>258</v>
@@ -10786,13 +10792,13 @@
         <v>163</v>
       </c>
       <c r="K197" s="1">
-        <v>2200006</v>
+        <v>2200005</v>
       </c>
       <c r="L197" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M197" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="P197" s="1">
         <v>1</v>
@@ -10800,13 +10806,13 @@
     </row>
     <row r="198" spans="1:16">
       <c r="A198" s="1">
-        <v>1200007</v>
+        <v>1200006</v>
       </c>
       <c r="C198" s="1">
-        <v>1200007</v>
+        <v>1200006</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E198" s="1">
         <v>2</v>
@@ -10827,13 +10833,13 @@
         <v>163</v>
       </c>
       <c r="K198" s="1">
-        <v>2200007</v>
+        <v>2200006</v>
       </c>
       <c r="L198" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M198" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P198" s="1">
         <v>1</v>
@@ -10841,10 +10847,10 @@
     </row>
     <row r="199" spans="1:16">
       <c r="A199" s="1">
-        <v>1200008</v>
+        <v>1200007</v>
       </c>
       <c r="C199" s="1">
-        <v>1200008</v>
+        <v>1200007</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>261</v>
@@ -10868,7 +10874,7 @@
         <v>163</v>
       </c>
       <c r="K199" s="1">
-        <v>2200008</v>
+        <v>2200007</v>
       </c>
       <c r="L199" s="1" t="b">
         <v>0</v>
@@ -10882,10 +10888,10 @@
     </row>
     <row r="200" spans="1:16">
       <c r="A200" s="1">
-        <v>1200009</v>
+        <v>1200008</v>
       </c>
       <c r="C200" s="1">
-        <v>1200009</v>
+        <v>1200008</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>263</v>
@@ -10909,7 +10915,7 @@
         <v>163</v>
       </c>
       <c r="K200" s="1">
-        <v>2200009</v>
+        <v>2200008</v>
       </c>
       <c r="L200" s="1" t="b">
         <v>0</v>
@@ -10923,10 +10929,10 @@
     </row>
     <row r="201" spans="1:16">
       <c r="A201" s="1">
-        <v>1200010</v>
+        <v>1200009</v>
       </c>
       <c r="C201" s="1">
-        <v>1200010</v>
+        <v>1200009</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>265</v>
@@ -10950,7 +10956,7 @@
         <v>163</v>
       </c>
       <c r="K201" s="1">
-        <v>2200010</v>
+        <v>2200009</v>
       </c>
       <c r="L201" s="1" t="b">
         <v>0</v>
@@ -10959,6 +10965,47 @@
         <v>266</v>
       </c>
       <c r="P201" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16">
+      <c r="A202" s="1">
+        <v>1200010</v>
+      </c>
+      <c r="C202" s="1">
+        <v>1200010</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E202" s="1">
+        <v>2</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G202" s="1">
+        <v>1</v>
+      </c>
+      <c r="H202" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I202" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J202" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="K202" s="1">
+        <v>2200010</v>
+      </c>
+      <c r="L202" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M202" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="P202" s="1">
         <v>1</v>
       </c>
     </row>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -3139,9 +3139,6 @@
       <c r="Q12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="S12" s="1">
-        <v>1010301</v>
-      </c>
       <c r="T12" s="1">
         <v>0.099</v>
       </c>
@@ -3192,9 +3189,6 @@
       <c r="Q13" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="S13" s="1">
-        <v>1010302</v>
-      </c>
       <c r="T13" s="1">
         <f>T12*2</f>
         <v>0.198</v>
@@ -3246,9 +3240,6 @@
       <c r="Q14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="S14" s="1">
-        <v>1010303</v>
-      </c>
       <c r="T14" s="1">
         <f>T12*6</f>
         <v>0.594</v>
@@ -3300,9 +3291,6 @@
       <c r="Q15" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="S15" s="1">
-        <v>1010304</v>
-      </c>
       <c r="T15" s="1">
         <f>T12*8</f>
         <v>0.792</v>
@@ -3353,9 +3341,6 @@
       </c>
       <c r="Q16" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="S16" s="1">
-        <v>1010305</v>
       </c>
       <c r="T16" s="1">
         <f>T12*10</f>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -342,7 +342,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="354">
   <si>
     <t>道具ID</t>
   </si>
@@ -1190,6 +1190,9 @@
     <t>打卡卫士</t>
   </si>
   <si>
+    <t>1001.png</t>
+  </si>
+  <si>
     <t>成长之路</t>
   </si>
   <si>
@@ -1235,9 +1238,15 @@
     <t>建筑大师</t>
   </si>
   <si>
+    <t>2001.png</t>
+  </si>
+  <si>
     <t>人气之王</t>
   </si>
   <si>
+    <t>2002.png</t>
+  </si>
+  <si>
     <t>团队高管</t>
   </si>
   <si>
@@ -1256,6 +1265,9 @@
     <t>小有成就</t>
   </si>
   <si>
+    <t>2008.png</t>
+  </si>
+  <si>
     <t>中奖能手</t>
   </si>
   <si>
@@ -1265,12 +1277,21 @@
     <t>财富自由</t>
   </si>
   <si>
+    <t>2011.png</t>
+  </si>
+  <si>
     <t>超级赢家</t>
   </si>
   <si>
+    <t>2012.png</t>
+  </si>
+  <si>
     <t>VIP专享</t>
   </si>
   <si>
+    <t>3001.png</t>
+  </si>
+  <si>
     <t>研发院士</t>
   </si>
   <si>
@@ -1283,6 +1304,9 @@
     <t>游戏大亨</t>
   </si>
   <si>
+    <t>3005.png</t>
+  </si>
+  <si>
     <t>营销高手</t>
   </si>
   <si>
@@ -1304,6 +1328,9 @@
     <t>幸运之神</t>
   </si>
   <si>
+    <t>3012.png</t>
+  </si>
+  <si>
     <t>大奖得主</t>
   </si>
   <si>
@@ -1313,6 +1340,9 @@
     <t>财富神话</t>
   </si>
   <si>
+    <t>4001.png</t>
+  </si>
+  <si>
     <t>财运亨通</t>
   </si>
   <si>
@@ -1331,6 +1361,9 @@
     <t>产业巨头</t>
   </si>
   <si>
+    <t>4007.png</t>
+  </si>
+  <si>
     <t>管理大师</t>
   </si>
   <si>
@@ -1347,6 +1380,9 @@
   </si>
   <si>
     <t>转轮之王</t>
+  </si>
+  <si>
+    <t>4013.png</t>
   </si>
   <si>
     <t>赌场之王</t>
@@ -11301,7 +11337,7 @@
         <v>0</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>103</v>
+        <v>282</v>
       </c>
       <c r="K204" s="1">
         <v>2150001</v>
@@ -11325,7 +11361,7 @@
         <v>1150002</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E205" s="1">
         <v>2</v>
@@ -11367,7 +11403,7 @@
         <v>1150003</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -11409,7 +11445,7 @@
         <v>1150004</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -11451,7 +11487,7 @@
         <v>1150005</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -11493,7 +11529,7 @@
         <v>1150006</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -11535,7 +11571,7 @@
         <v>1150007</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -11577,7 +11613,7 @@
         <v>1150008</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -11619,7 +11655,7 @@
         <v>1150009</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -11661,7 +11697,7 @@
         <v>1150010</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -11703,7 +11739,7 @@
         <v>1150011</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -11745,7 +11781,7 @@
         <v>1150012</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -11787,7 +11823,7 @@
         <v>1150013</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -11829,7 +11865,7 @@
         <v>1150014</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -11871,7 +11907,7 @@
         <v>1150015</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -11913,7 +11949,7 @@
         <v>1150016</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -11931,7 +11967,7 @@
         <v>0</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>103</v>
+        <v>298</v>
       </c>
       <c r="K219" s="1">
         <v>2150016</v>
@@ -11955,7 +11991,7 @@
         <v>1150017</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -11973,7 +12009,7 @@
         <v>0</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="K220" s="1">
         <v>2150017</v>
@@ -11997,7 +12033,7 @@
         <v>1150018</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -12039,7 +12075,7 @@
         <v>1150019</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -12081,7 +12117,7 @@
         <v>1150020</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -12123,7 +12159,7 @@
         <v>1150021</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -12165,7 +12201,7 @@
         <v>1150022</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -12207,7 +12243,7 @@
         <v>1150023</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E226" s="1">
         <v>2</v>
@@ -12225,7 +12261,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>103</v>
+        <v>307</v>
       </c>
       <c r="K226" s="1">
         <v>2150023</v>
@@ -12249,7 +12285,7 @@
         <v>1150024</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
@@ -12291,7 +12327,7 @@
         <v>1150025</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
@@ -12333,7 +12369,7 @@
         <v>1150026</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
@@ -12351,7 +12387,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>103</v>
+        <v>311</v>
       </c>
       <c r="K229" s="1">
         <v>2150026</v>
@@ -12375,7 +12411,7 @@
         <v>1150027</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
@@ -12393,7 +12429,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>103</v>
+        <v>313</v>
       </c>
       <c r="K230" s="1">
         <v>2150027</v>
@@ -12417,7 +12453,7 @@
         <v>1150028</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
@@ -12435,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>103</v>
+        <v>315</v>
       </c>
       <c r="K231" s="1">
         <v>2150028</v>
@@ -12459,7 +12495,7 @@
         <v>1150029</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
@@ -12501,7 +12537,7 @@
         <v>1150030</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E233" s="1">
         <v>2</v>
@@ -12519,7 +12555,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K233" s="1">
         <v>2150030</v>
@@ -12543,7 +12579,7 @@
         <v>1150031</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E234" s="1">
         <v>2</v>
@@ -12561,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K234" s="1">
         <v>2150031</v>
@@ -12585,7 +12621,7 @@
         <v>1150032</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E235" s="1">
         <v>2</v>
@@ -12603,7 +12639,7 @@
         <v>0</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>99</v>
+        <v>320</v>
       </c>
       <c r="K235" s="1">
         <v>2150032</v>
@@ -12627,7 +12663,7 @@
         <v>1150033</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E236" s="1">
         <v>2</v>
@@ -12645,7 +12681,7 @@
         <v>0</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K236" s="1">
         <v>2150033</v>
@@ -12669,7 +12705,7 @@
         <v>1150034</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E237" s="1">
         <v>2</v>
@@ -12687,7 +12723,7 @@
         <v>0</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K237" s="1">
         <v>2150034</v>
@@ -12711,7 +12747,7 @@
         <v>1150035</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E238" s="1">
         <v>2</v>
@@ -12729,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K238" s="1">
         <v>2150035</v>
@@ -12753,7 +12789,7 @@
         <v>1150036</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="E239" s="1">
         <v>2</v>
@@ -12771,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K239" s="1">
         <v>2150036</v>
@@ -12795,7 +12831,7 @@
         <v>1150037</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E240" s="1">
         <v>2</v>
@@ -12813,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K240" s="1">
         <v>2150037</v>
@@ -12837,7 +12873,7 @@
         <v>1150038</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="E241" s="1">
         <v>2</v>
@@ -12855,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K241" s="1">
         <v>2150038</v>
@@ -12879,7 +12915,7 @@
         <v>1150039</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E242" s="1">
         <v>2</v>
@@ -12897,7 +12933,7 @@
         <v>0</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>99</v>
+        <v>328</v>
       </c>
       <c r="K242" s="1">
         <v>2150039</v>
@@ -12921,7 +12957,7 @@
         <v>1150040</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E243" s="1">
         <v>2</v>
@@ -12939,7 +12975,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K243" s="1">
         <v>2150040</v>
@@ -12963,7 +12999,7 @@
         <v>1150041</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="E244" s="1">
         <v>2</v>
@@ -12981,7 +13017,7 @@
         <v>0</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K244" s="1">
         <v>2150041</v>
@@ -13005,7 +13041,7 @@
         <v>1150042</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="E245" s="1">
         <v>2</v>
@@ -13023,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>99</v>
+        <v>332</v>
       </c>
       <c r="K245" s="1">
         <v>2150042</v>
@@ -13047,7 +13083,7 @@
         <v>1150043</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="E246" s="1">
         <v>2</v>
@@ -13065,7 +13101,7 @@
         <v>0</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K246" s="1">
         <v>2150043</v>
@@ -13089,7 +13125,7 @@
         <v>1150044</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="E247" s="1">
         <v>2</v>
@@ -13107,7 +13143,7 @@
         <v>0</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K247" s="1">
         <v>2150044</v>
@@ -13131,7 +13167,7 @@
         <v>1150045</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="E248" s="1">
         <v>2</v>
@@ -13149,7 +13185,7 @@
         <v>0</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K248" s="1">
         <v>2150045</v>
@@ -13173,7 +13209,7 @@
         <v>1150046</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E249" s="1">
         <v>2</v>
@@ -13191,7 +13227,7 @@
         <v>0</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K249" s="1">
         <v>2150046</v>
@@ -13215,7 +13251,7 @@
         <v>1150047</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="E250" s="1">
         <v>2</v>
@@ -13233,7 +13269,7 @@
         <v>0</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K250" s="1">
         <v>2150047</v>
@@ -13257,7 +13293,7 @@
         <v>1150048</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="E251" s="1">
         <v>2</v>
@@ -13275,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>99</v>
+        <v>339</v>
       </c>
       <c r="K251" s="1">
         <v>2150048</v>
@@ -13299,7 +13335,7 @@
         <v>1150049</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="E252" s="1">
         <v>2</v>
@@ -13317,7 +13353,7 @@
         <v>0</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K252" s="1">
         <v>2150049</v>
@@ -13341,7 +13377,7 @@
         <v>1150050</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E253" s="1">
         <v>2</v>
@@ -13359,7 +13395,7 @@
         <v>0</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K253" s="1">
         <v>2150050</v>
@@ -13383,7 +13419,7 @@
         <v>1150051</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="E254" s="1">
         <v>2</v>
@@ -13401,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K254" s="1">
         <v>2150051</v>
@@ -13425,7 +13461,7 @@
         <v>1150052</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="E255" s="1">
         <v>2</v>
@@ -13443,7 +13479,7 @@
         <v>0</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K255" s="1">
         <v>2150052</v>
@@ -13467,7 +13503,7 @@
         <v>1150053</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="E256" s="1">
         <v>2</v>
@@ -13485,7 +13521,7 @@
         <v>0</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K256" s="1">
         <v>2150053</v>
@@ -13509,7 +13545,7 @@
         <v>1150054</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="E257" s="1">
         <v>2</v>
@@ -13527,7 +13563,7 @@
         <v>0</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>99</v>
+        <v>346</v>
       </c>
       <c r="K257" s="1">
         <v>2150054</v>
@@ -13551,7 +13587,7 @@
         <v>1150055</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="E258" s="1">
         <v>2</v>
@@ -13569,7 +13605,7 @@
         <v>0</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K258" s="1">
         <v>2150055</v>
@@ -13593,7 +13629,7 @@
         <v>1150056</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="E259" s="1">
         <v>2</v>
@@ -13611,7 +13647,7 @@
         <v>0</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K259" s="1">
         <v>2150056</v>
@@ -13635,7 +13671,7 @@
         <v>1150057</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="E260" s="1">
         <v>2</v>
@@ -13653,7 +13689,7 @@
         <v>0</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K260" s="1">
         <v>2150057</v>
@@ -13677,7 +13713,7 @@
         <v>1150058</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="E261" s="1">
         <v>2</v>
@@ -13695,7 +13731,7 @@
         <v>0</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K261" s="1">
         <v>2150058</v>
@@ -13719,7 +13755,7 @@
         <v>1150059</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="E262" s="1">
         <v>2</v>
@@ -13737,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K262" s="1">
         <v>2150059</v>
@@ -13761,7 +13797,7 @@
         <v>1150060</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -13779,7 +13815,7 @@
         <v>0</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K263" s="1">
         <v>2150060</v>
@@ -13803,7 +13839,7 @@
         <v>1150061</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="E264" s="1">
         <v>2</v>
@@ -13821,7 +13857,7 @@
         <v>0</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K264" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -342,7 +342,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="403">
   <si>
     <t>道具ID</t>
   </si>
@@ -1190,220 +1190,367 @@
     <t>打卡卫士</t>
   </si>
   <si>
-    <t>1001.png</t>
+    <t>1150001.png</t>
   </si>
   <si>
     <t>成长之路</t>
   </si>
   <si>
+    <t>1150002.png</t>
+  </si>
+  <si>
     <t>转轮高手</t>
   </si>
   <si>
+    <t>1150003.png</t>
+  </si>
+  <si>
     <t>大赢家</t>
   </si>
   <si>
+    <t>1150004.png</t>
+  </si>
+  <si>
     <t>转轮精英</t>
   </si>
   <si>
+    <t>1150005.png</t>
+  </si>
+  <si>
     <t>幸运之星</t>
   </si>
   <si>
+    <t>1150006.png</t>
+  </si>
+  <si>
     <t>游戏收集者</t>
   </si>
   <si>
+    <t>1150007.png</t>
+  </si>
+  <si>
     <t>建筑能手</t>
   </si>
   <si>
+    <t>1150008.png</t>
+  </si>
+  <si>
     <t>百万富豪</t>
   </si>
   <si>
+    <t>1150009.png</t>
+  </si>
+  <si>
     <t>能量收集者</t>
   </si>
   <si>
+    <t>1150010.png</t>
+  </si>
+  <si>
     <t>金币大师</t>
   </si>
   <si>
+    <t>1150011.png</t>
+  </si>
+  <si>
     <t>钻石富豪</t>
   </si>
   <si>
+    <t>1150012.png</t>
+  </si>
+  <si>
     <t>招商能手</t>
   </si>
   <si>
+    <t>1150013.png</t>
+  </si>
+  <si>
     <t>娱乐CEO</t>
   </si>
   <si>
+    <t>1150014.png</t>
+  </si>
+  <si>
     <t>人气爆棚</t>
   </si>
   <si>
+    <t>1150015.png</t>
+  </si>
+  <si>
     <t>建筑大师</t>
   </si>
   <si>
-    <t>2001.png</t>
+    <t>1150016.png</t>
   </si>
   <si>
     <t>人气之王</t>
   </si>
   <si>
-    <t>2002.png</t>
+    <t>1150017.png</t>
   </si>
   <si>
     <t>团队高管</t>
   </si>
   <si>
+    <t>1150018.png</t>
+  </si>
+  <si>
     <t>培养能手</t>
   </si>
   <si>
+    <t>1150019.png</t>
+  </si>
+  <si>
     <t>培养大师</t>
   </si>
   <si>
+    <t>1150020.png</t>
+  </si>
+  <si>
     <t>培养专家</t>
   </si>
   <si>
+    <t>1150021.png</t>
+  </si>
+  <si>
     <t>有点小钱</t>
   </si>
   <si>
+    <t>1150022.png</t>
+  </si>
+  <si>
     <t>小有成就</t>
   </si>
   <si>
-    <t>2008.png</t>
+    <t>1150023.png</t>
   </si>
   <si>
     <t>中奖能手</t>
   </si>
   <si>
+    <t>1150024.png</t>
+  </si>
+  <si>
     <t>招财进宝</t>
   </si>
   <si>
+    <t>1150025.png</t>
+  </si>
+  <si>
     <t>财富自由</t>
   </si>
   <si>
-    <t>2011.png</t>
+    <t>1150026.png</t>
   </si>
   <si>
     <t>超级赢家</t>
   </si>
   <si>
-    <t>2012.png</t>
+    <t>1150027.png</t>
   </si>
   <si>
     <t>VIP专享</t>
   </si>
   <si>
-    <t>3001.png</t>
+    <t>1150028.png</t>
   </si>
   <si>
     <t>研发院士</t>
   </si>
   <si>
+    <t>1150029.png</t>
+  </si>
+  <si>
     <t>社交精英</t>
   </si>
   <si>
+    <t>1150030.png</t>
+  </si>
+  <si>
     <t>精英团队</t>
   </si>
   <si>
+    <t>1150031.png</t>
+  </si>
+  <si>
     <t>游戏大亨</t>
   </si>
   <si>
-    <t>3005.png</t>
+    <t>1150032.png</t>
   </si>
   <si>
     <t>营销高手</t>
   </si>
   <si>
+    <t>1150033.png</t>
+  </si>
+  <si>
     <t>招商经理</t>
   </si>
   <si>
+    <t>1150034.png</t>
+  </si>
+  <si>
     <t>广告精英</t>
   </si>
   <si>
+    <t>1150035.png</t>
+  </si>
+  <si>
     <t>招募精英</t>
   </si>
   <si>
+    <t>1150036.png</t>
+  </si>
+  <si>
     <t>商界精英</t>
   </si>
   <si>
+    <t>1150037.png</t>
+  </si>
+  <si>
     <t>策略大师</t>
   </si>
   <si>
+    <t>1150038.png</t>
+  </si>
+  <si>
     <t>幸运之神</t>
   </si>
   <si>
-    <t>3012.png</t>
+    <t>1150039.png</t>
   </si>
   <si>
     <t>大奖得主</t>
   </si>
   <si>
+    <t>1150040.png</t>
+  </si>
+  <si>
     <t>最佳经理人</t>
   </si>
   <si>
+    <t>1150041.png</t>
+  </si>
+  <si>
     <t>财富神话</t>
   </si>
   <si>
-    <t>4001.png</t>
+    <t>1150042.png</t>
   </si>
   <si>
     <t>财运亨通</t>
   </si>
   <si>
+    <t>1150043.png</t>
+  </si>
+  <si>
     <t>亿万富豪</t>
   </si>
   <si>
+    <t>1150044.png</t>
+  </si>
+  <si>
     <t>巨富大亨</t>
   </si>
   <si>
+    <t>1150045.png</t>
+  </si>
+  <si>
     <t>传奇赢家</t>
   </si>
   <si>
+    <t>1150046.png</t>
+  </si>
+  <si>
     <t>营销冠军</t>
   </si>
   <si>
+    <t>1150047.png</t>
+  </si>
+  <si>
     <t>产业巨头</t>
   </si>
   <si>
-    <t>4007.png</t>
+    <t>1150048.png</t>
   </si>
   <si>
     <t>管理大师</t>
   </si>
   <si>
+    <t>1150049.png</t>
+  </si>
+  <si>
     <t>娱乐大亨</t>
   </si>
   <si>
+    <t>1150050.png</t>
+  </si>
+  <si>
     <t>商界奇才</t>
   </si>
   <si>
+    <t>1150051.png</t>
+  </si>
+  <si>
     <t>商界传奇</t>
   </si>
   <si>
+    <t>1150052.png</t>
+  </si>
+  <si>
     <t>科研之王</t>
   </si>
   <si>
+    <t>1150053.png</t>
+  </si>
+  <si>
     <t>转轮之王</t>
   </si>
   <si>
-    <t>4013.png</t>
+    <t>1150054.png</t>
   </si>
   <si>
     <t>赌场之王</t>
   </si>
   <si>
+    <t>1150055.png</t>
+  </si>
+  <si>
     <t>全服名人</t>
   </si>
   <si>
+    <t>1150056.png</t>
+  </si>
+  <si>
     <t>富贵逼人</t>
   </si>
   <si>
+    <t>1150057.png</t>
+  </si>
+  <si>
     <t>辉煌人生</t>
   </si>
   <si>
+    <t>1150058.png</t>
+  </si>
+  <si>
     <t>风云人物</t>
   </si>
   <si>
+    <t>1150059.png</t>
+  </si>
+  <si>
     <t>名震世界</t>
   </si>
   <si>
+    <t>1150060.png</t>
+  </si>
+  <si>
     <t>时代传说</t>
+  </si>
+  <si>
+    <t>1150061.png</t>
   </si>
 </sst>
 </file>
@@ -11379,7 +11526,7 @@
         <v>0</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>103</v>
+        <v>284</v>
       </c>
       <c r="K205" s="1">
         <v>2150002</v>
@@ -11403,7 +11550,7 @@
         <v>1150003</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -11421,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="K206" s="1">
         <v>2150003</v>
@@ -11445,7 +11592,7 @@
         <v>1150004</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -11463,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="K207" s="1">
         <v>2150004</v>
@@ -11487,7 +11634,7 @@
         <v>1150005</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -11505,7 +11652,7 @@
         <v>0</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>103</v>
+        <v>290</v>
       </c>
       <c r="K208" s="1">
         <v>2150005</v>
@@ -11529,7 +11676,7 @@
         <v>1150006</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -11547,7 +11694,7 @@
         <v>0</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>103</v>
+        <v>292</v>
       </c>
       <c r="K209" s="1">
         <v>2150006</v>
@@ -11571,7 +11718,7 @@
         <v>1150007</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -11589,7 +11736,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>103</v>
+        <v>294</v>
       </c>
       <c r="K210" s="1">
         <v>2150007</v>
@@ -11613,7 +11760,7 @@
         <v>1150008</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -11631,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>103</v>
+        <v>296</v>
       </c>
       <c r="K211" s="1">
         <v>2150008</v>
@@ -11655,7 +11802,7 @@
         <v>1150009</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -11673,7 +11820,7 @@
         <v>0</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>103</v>
+        <v>298</v>
       </c>
       <c r="K212" s="1">
         <v>2150009</v>
@@ -11697,7 +11844,7 @@
         <v>1150010</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -11715,7 +11862,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="K213" s="1">
         <v>2150010</v>
@@ -11739,7 +11886,7 @@
         <v>1150011</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -11757,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>103</v>
+        <v>302</v>
       </c>
       <c r="K214" s="1">
         <v>2150011</v>
@@ -11781,7 +11928,7 @@
         <v>1150012</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -11799,7 +11946,7 @@
         <v>0</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>103</v>
+        <v>304</v>
       </c>
       <c r="K215" s="1">
         <v>2150012</v>
@@ -11823,7 +11970,7 @@
         <v>1150013</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -11841,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>103</v>
+        <v>306</v>
       </c>
       <c r="K216" s="1">
         <v>2150013</v>
@@ -11865,7 +12012,7 @@
         <v>1150014</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -11883,7 +12030,7 @@
         <v>0</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>103</v>
+        <v>308</v>
       </c>
       <c r="K217" s="1">
         <v>2150014</v>
@@ -11907,7 +12054,7 @@
         <v>1150015</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -11925,7 +12072,7 @@
         <v>0</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>103</v>
+        <v>310</v>
       </c>
       <c r="K218" s="1">
         <v>2150015</v>
@@ -11949,7 +12096,7 @@
         <v>1150016</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -11967,7 +12114,7 @@
         <v>0</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="K219" s="1">
         <v>2150016</v>
@@ -11991,7 +12138,7 @@
         <v>1150017</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -12009,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="K220" s="1">
         <v>2150017</v>
@@ -12033,7 +12180,7 @@
         <v>1150018</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -12051,7 +12198,7 @@
         <v>0</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>103</v>
+        <v>316</v>
       </c>
       <c r="K221" s="1">
         <v>2150018</v>
@@ -12075,7 +12222,7 @@
         <v>1150019</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -12093,7 +12240,7 @@
         <v>0</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>103</v>
+        <v>318</v>
       </c>
       <c r="K222" s="1">
         <v>2150019</v>
@@ -12117,7 +12264,7 @@
         <v>1150020</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -12135,7 +12282,7 @@
         <v>0</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="K223" s="1">
         <v>2150020</v>
@@ -12159,7 +12306,7 @@
         <v>1150021</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -12177,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>103</v>
+        <v>322</v>
       </c>
       <c r="K224" s="1">
         <v>2150021</v>
@@ -12201,7 +12348,7 @@
         <v>1150022</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -12219,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>103</v>
+        <v>324</v>
       </c>
       <c r="K225" s="1">
         <v>2150022</v>
@@ -12243,7 +12390,7 @@
         <v>1150023</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="E226" s="1">
         <v>2</v>
@@ -12261,7 +12408,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="K226" s="1">
         <v>2150023</v>
@@ -12285,7 +12432,7 @@
         <v>1150024</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
@@ -12303,7 +12450,7 @@
         <v>0</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>103</v>
+        <v>328</v>
       </c>
       <c r="K227" s="1">
         <v>2150024</v>
@@ -12327,7 +12474,7 @@
         <v>1150025</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
@@ -12345,7 +12492,7 @@
         <v>0</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>103</v>
+        <v>330</v>
       </c>
       <c r="K228" s="1">
         <v>2150025</v>
@@ -12369,7 +12516,7 @@
         <v>1150026</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
@@ -12387,7 +12534,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="K229" s="1">
         <v>2150026</v>
@@ -12411,7 +12558,7 @@
         <v>1150027</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
@@ -12429,7 +12576,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="K230" s="1">
         <v>2150027</v>
@@ -12453,7 +12600,7 @@
         <v>1150028</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
@@ -12471,7 +12618,7 @@
         <v>0</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="K231" s="1">
         <v>2150028</v>
@@ -12495,7 +12642,7 @@
         <v>1150029</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
@@ -12513,7 +12660,7 @@
         <v>0</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>103</v>
+        <v>338</v>
       </c>
       <c r="K232" s="1">
         <v>2150029</v>
@@ -12537,7 +12684,7 @@
         <v>1150030</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="E233" s="1">
         <v>2</v>
@@ -12555,7 +12702,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>103</v>
+        <v>340</v>
       </c>
       <c r="K233" s="1">
         <v>2150030</v>
@@ -12579,7 +12726,7 @@
         <v>1150031</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="E234" s="1">
         <v>2</v>
@@ -12597,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>103</v>
+        <v>342</v>
       </c>
       <c r="K234" s="1">
         <v>2150031</v>
@@ -12621,7 +12768,7 @@
         <v>1150032</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="E235" s="1">
         <v>2</v>
@@ -12639,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="K235" s="1">
         <v>2150032</v>
@@ -12663,7 +12810,7 @@
         <v>1150033</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="E236" s="1">
         <v>2</v>
@@ -12681,7 +12828,7 @@
         <v>0</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>103</v>
+        <v>346</v>
       </c>
       <c r="K236" s="1">
         <v>2150033</v>
@@ -12705,7 +12852,7 @@
         <v>1150034</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="E237" s="1">
         <v>2</v>
@@ -12723,7 +12870,7 @@
         <v>0</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>103</v>
+        <v>348</v>
       </c>
       <c r="K237" s="1">
         <v>2150034</v>
@@ -12747,7 +12894,7 @@
         <v>1150035</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="E238" s="1">
         <v>2</v>
@@ -12765,7 +12912,7 @@
         <v>0</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>103</v>
+        <v>350</v>
       </c>
       <c r="K238" s="1">
         <v>2150035</v>
@@ -12789,7 +12936,7 @@
         <v>1150036</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="E239" s="1">
         <v>2</v>
@@ -12807,7 +12954,7 @@
         <v>0</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>103</v>
+        <v>352</v>
       </c>
       <c r="K239" s="1">
         <v>2150036</v>
@@ -12831,7 +12978,7 @@
         <v>1150037</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="E240" s="1">
         <v>2</v>
@@ -12849,7 +12996,7 @@
         <v>0</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>103</v>
+        <v>354</v>
       </c>
       <c r="K240" s="1">
         <v>2150037</v>
@@ -12873,7 +13020,7 @@
         <v>1150038</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="E241" s="1">
         <v>2</v>
@@ -12891,7 +13038,7 @@
         <v>0</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>103</v>
+        <v>356</v>
       </c>
       <c r="K241" s="1">
         <v>2150038</v>
@@ -12915,7 +13062,7 @@
         <v>1150039</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="E242" s="1">
         <v>2</v>
@@ -12933,7 +13080,7 @@
         <v>0</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="K242" s="1">
         <v>2150039</v>
@@ -12957,7 +13104,7 @@
         <v>1150040</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="E243" s="1">
         <v>2</v>
@@ -12975,7 +13122,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>103</v>
+        <v>360</v>
       </c>
       <c r="K243" s="1">
         <v>2150040</v>
@@ -12999,7 +13146,7 @@
         <v>1150041</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="E244" s="1">
         <v>2</v>
@@ -13017,7 +13164,7 @@
         <v>0</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>103</v>
+        <v>362</v>
       </c>
       <c r="K244" s="1">
         <v>2150041</v>
@@ -13041,7 +13188,7 @@
         <v>1150042</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="E245" s="1">
         <v>2</v>
@@ -13059,7 +13206,7 @@
         <v>0</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="K245" s="1">
         <v>2150042</v>
@@ -13083,7 +13230,7 @@
         <v>1150043</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="E246" s="1">
         <v>2</v>
@@ -13101,7 +13248,7 @@
         <v>0</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>103</v>
+        <v>366</v>
       </c>
       <c r="K246" s="1">
         <v>2150043</v>
@@ -13125,7 +13272,7 @@
         <v>1150044</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="E247" s="1">
         <v>2</v>
@@ -13143,7 +13290,7 @@
         <v>0</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>103</v>
+        <v>368</v>
       </c>
       <c r="K247" s="1">
         <v>2150044</v>
@@ -13167,7 +13314,7 @@
         <v>1150045</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>335</v>
+        <v>369</v>
       </c>
       <c r="E248" s="1">
         <v>2</v>
@@ -13185,7 +13332,7 @@
         <v>0</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>103</v>
+        <v>370</v>
       </c>
       <c r="K248" s="1">
         <v>2150045</v>
@@ -13209,7 +13356,7 @@
         <v>1150046</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="E249" s="1">
         <v>2</v>
@@ -13227,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>103</v>
+        <v>372</v>
       </c>
       <c r="K249" s="1">
         <v>2150046</v>
@@ -13251,7 +13398,7 @@
         <v>1150047</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="E250" s="1">
         <v>2</v>
@@ -13269,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>103</v>
+        <v>374</v>
       </c>
       <c r="K250" s="1">
         <v>2150047</v>
@@ -13293,7 +13440,7 @@
         <v>1150048</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="E251" s="1">
         <v>2</v>
@@ -13311,7 +13458,7 @@
         <v>0</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="K251" s="1">
         <v>2150048</v>
@@ -13335,7 +13482,7 @@
         <v>1150049</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="E252" s="1">
         <v>2</v>
@@ -13353,7 +13500,7 @@
         <v>0</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>103</v>
+        <v>378</v>
       </c>
       <c r="K252" s="1">
         <v>2150049</v>
@@ -13377,7 +13524,7 @@
         <v>1150050</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="E253" s="1">
         <v>2</v>
@@ -13395,7 +13542,7 @@
         <v>0</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>103</v>
+        <v>380</v>
       </c>
       <c r="K253" s="1">
         <v>2150050</v>
@@ -13419,7 +13566,7 @@
         <v>1150051</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="E254" s="1">
         <v>2</v>
@@ -13437,7 +13584,7 @@
         <v>0</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>103</v>
+        <v>382</v>
       </c>
       <c r="K254" s="1">
         <v>2150051</v>
@@ -13461,7 +13608,7 @@
         <v>1150052</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>343</v>
+        <v>383</v>
       </c>
       <c r="E255" s="1">
         <v>2</v>
@@ -13479,7 +13626,7 @@
         <v>0</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>103</v>
+        <v>384</v>
       </c>
       <c r="K255" s="1">
         <v>2150052</v>
@@ -13503,7 +13650,7 @@
         <v>1150053</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="E256" s="1">
         <v>2</v>
@@ -13521,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>103</v>
+        <v>386</v>
       </c>
       <c r="K256" s="1">
         <v>2150053</v>
@@ -13545,7 +13692,7 @@
         <v>1150054</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="E257" s="1">
         <v>2</v>
@@ -13563,7 +13710,7 @@
         <v>0</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>346</v>
+        <v>388</v>
       </c>
       <c r="K257" s="1">
         <v>2150054</v>
@@ -13587,7 +13734,7 @@
         <v>1150055</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="E258" s="1">
         <v>2</v>
@@ -13605,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>103</v>
+        <v>390</v>
       </c>
       <c r="K258" s="1">
         <v>2150055</v>
@@ -13629,7 +13776,7 @@
         <v>1150056</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="E259" s="1">
         <v>2</v>
@@ -13647,7 +13794,7 @@
         <v>0</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>103</v>
+        <v>392</v>
       </c>
       <c r="K259" s="1">
         <v>2150056</v>
@@ -13671,7 +13818,7 @@
         <v>1150057</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="E260" s="1">
         <v>2</v>
@@ -13689,7 +13836,7 @@
         <v>0</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>103</v>
+        <v>394</v>
       </c>
       <c r="K260" s="1">
         <v>2150057</v>
@@ -13713,7 +13860,7 @@
         <v>1150058</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>350</v>
+        <v>395</v>
       </c>
       <c r="E261" s="1">
         <v>2</v>
@@ -13731,7 +13878,7 @@
         <v>0</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>103</v>
+        <v>396</v>
       </c>
       <c r="K261" s="1">
         <v>2150058</v>
@@ -13755,7 +13902,7 @@
         <v>1150059</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>351</v>
+        <v>397</v>
       </c>
       <c r="E262" s="1">
         <v>2</v>
@@ -13773,7 +13920,7 @@
         <v>0</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>103</v>
+        <v>398</v>
       </c>
       <c r="K262" s="1">
         <v>2150059</v>
@@ -13797,7 +13944,7 @@
         <v>1150060</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -13815,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>103</v>
+        <v>400</v>
       </c>
       <c r="K263" s="1">
         <v>2150060</v>
@@ -13839,7 +13986,7 @@
         <v>1150061</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>353</v>
+        <v>401</v>
       </c>
       <c r="E264" s="1">
         <v>2</v>
@@ -13857,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>103</v>
+        <v>402</v>
       </c>
       <c r="K264" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -2092,12 +2092,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6860,7 +6860,7 @@
         <v>223</v>
       </c>
       <c r="P85" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6901,7 +6901,7 @@
         <v>225</v>
       </c>
       <c r="P86" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6942,7 +6942,7 @@
         <v>227</v>
       </c>
       <c r="P87" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6983,7 +6983,7 @@
         <v>229</v>
       </c>
       <c r="P88" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -7024,7 +7024,7 @@
         <v>231</v>
       </c>
       <c r="P89" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -7065,7 +7065,7 @@
         <v>233</v>
       </c>
       <c r="P90" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -7106,7 +7106,7 @@
         <v>235</v>
       </c>
       <c r="P91" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7147,7 +7147,7 @@
         <v>237</v>
       </c>
       <c r="P92" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -7188,7 +7188,7 @@
         <v>239</v>
       </c>
       <c r="P93" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -7229,7 +7229,7 @@
         <v>241</v>
       </c>
       <c r="P94" s="1">
-        <v>-1</v>
+        <v>999999</v>
       </c>
     </row>
     <row r="95" spans="1:16">

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -342,7 +342,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="518">
   <si>
     <t>道具ID</t>
   </si>
@@ -536,7 +536,7 @@
     <t>wdcc_ccb_1.png</t>
   </si>
   <si>
-    <t>使用后随机获得1~2星赌场建筑升级道具</t>
+    <t>使用后获得礼包内全部道具</t>
   </si>
   <si>
     <t>1023001_10;1023002_20;1023003_30</t>
@@ -554,22 +554,13 @@
     <t>wdcc_ccb_3.png</t>
   </si>
   <si>
-    <t>使用后随机获得1~3星赌场建筑升级道具</t>
-  </si>
-  <si>
     <t>赌场工具（绝佳）</t>
   </si>
   <si>
     <t>itemicon_1010101.png</t>
   </si>
   <si>
-    <t>使用后随机获得1~4星赌场建筑升级道具</t>
-  </si>
-  <si>
     <t>赌场工具（传奇）</t>
-  </si>
-  <si>
-    <t>使用后随机获得1~5星赌场建筑升级道具</t>
   </si>
   <si>
     <t>管理雇员碎片(普通)</t>
@@ -3819,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="P15" s="1">
         <v>999999</v>
@@ -3843,7 +3834,7 @@
         <v>1100304</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -3861,7 +3852,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K16" s="1">
         <v>2010304</v>
@@ -3870,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="P16" s="1">
         <v>999999</v>
@@ -3894,7 +3885,7 @@
         <v>1100305</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -3912,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K17" s="1">
         <v>2010305</v>
@@ -3921,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="P17" s="1">
         <v>999999</v>
@@ -3945,7 +3936,7 @@
         <v>1100401</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -3972,14 +3963,14 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P18" s="2">
         <v>999999</v>
       </c>
       <c r="Q18" s="8"/>
       <c r="R18" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:20">
@@ -3993,7 +3984,7 @@
         <v>1100501</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -4020,14 +4011,14 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P19" s="2">
         <v>999999</v>
       </c>
       <c r="Q19" s="8"/>
       <c r="R19" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:20">
@@ -4041,7 +4032,7 @@
         <v>1100601</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -4068,14 +4059,14 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P20" s="2">
         <v>999999</v>
       </c>
       <c r="Q20" s="8"/>
       <c r="R20" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -4089,7 +4080,7 @@
         <v>1301001</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -4107,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K21" s="1">
         <v>2031001</v>
@@ -4133,7 +4124,7 @@
         <v>1301002</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -4151,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K22" s="1">
         <v>2031002</v>
@@ -4177,7 +4168,7 @@
         <v>1301201</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -4195,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K23" s="1">
         <v>2031201</v>
@@ -4221,7 +4212,7 @@
         <v>1301202</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -4239,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K24" s="1">
         <v>2031202</v>
@@ -4265,7 +4256,7 @@
         <v>101801</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -4283,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K25" s="1">
         <v>201801</v>
@@ -4309,7 +4300,7 @@
         <v>101802</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -4327,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K26" s="1">
         <v>201802</v>
@@ -4353,7 +4344,7 @@
         <v>1201401</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -4371,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K27" s="1">
         <v>2021401</v>
@@ -4397,7 +4388,7 @@
         <v>1201402</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -4415,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K28" s="1">
         <v>2021402</v>
@@ -4441,7 +4432,7 @@
         <v>103001</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -4459,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K29" s="1">
         <v>2031600</v>
@@ -4485,7 +4476,7 @@
         <v>103002</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -4503,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K30" s="1">
         <v>2031601</v>
@@ -4529,7 +4520,7 @@
         <v>103003</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
@@ -4547,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K31" s="1">
         <v>2031602</v>
@@ -4573,7 +4564,7 @@
         <v>104002</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -4591,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K32" s="1">
         <v>2031801</v>
@@ -4617,7 +4608,7 @@
         <v>104003</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -4635,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K33" s="1">
         <v>2031802</v>
@@ -4661,7 +4652,7 @@
         <v>105002</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -4679,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K34" s="1">
         <v>2032001</v>
@@ -4705,7 +4696,7 @@
         <v>105003</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -4723,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K35" s="1">
         <v>2032002</v>
@@ -4749,7 +4740,7 @@
         <v>106002</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E36" s="1">
         <v>3</v>
@@ -4767,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K36" s="1">
         <v>2032201</v>
@@ -4793,7 +4784,7 @@
         <v>106003</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -4811,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="K37" s="1">
         <v>2032202</v>
@@ -4837,7 +4828,7 @@
         <v>1202504</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -4855,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K38" s="1">
         <v>2022504</v>
@@ -4864,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P38" s="1">
         <v>999999999</v>
@@ -4878,7 +4869,7 @@
         <v>1023001</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -4896,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K39" s="1">
         <v>2023001</v>
@@ -4905,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P39" s="1">
         <v>999999</v>
@@ -4922,7 +4913,7 @@
         <v>1023002</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -4940,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K40" s="1">
         <v>2023002</v>
@@ -4949,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P40" s="1">
         <v>999999</v>
@@ -4966,7 +4957,7 @@
         <v>1023003</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
@@ -4984,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K41" s="1">
         <v>2023003</v>
@@ -4993,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P41" s="1">
         <v>999999</v>
@@ -5010,7 +5001,7 @@
         <v>1023004</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -5028,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K42" s="1">
         <v>2023004</v>
@@ -5037,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P42" s="1">
         <v>999999</v>
@@ -5054,7 +5045,7 @@
         <v>1023005</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -5072,7 +5063,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K43" s="1">
         <v>2023005</v>
@@ -5081,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P43" s="1">
         <v>999999</v>
@@ -5098,7 +5089,7 @@
         <v>1023101</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
@@ -5116,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K44" s="1">
         <v>2023101</v>
@@ -5125,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P44" s="1">
         <v>999999</v>
@@ -5142,7 +5133,7 @@
         <v>1023102</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
@@ -5160,7 +5151,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K45" s="1">
         <v>2023102</v>
@@ -5169,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P45" s="1">
         <v>999999</v>
@@ -5186,7 +5177,7 @@
         <v>1023103</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
@@ -5204,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K46" s="1">
         <v>2023103</v>
@@ -5213,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P46" s="1">
         <v>999999</v>
@@ -5230,7 +5221,7 @@
         <v>1023104</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
@@ -5248,7 +5239,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K47" s="1">
         <v>2023104</v>
@@ -5257,7 +5248,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P47" s="1">
         <v>999999</v>
@@ -5274,7 +5265,7 @@
         <v>1023105</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
@@ -5292,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K48" s="1">
         <v>2023105</v>
@@ -5301,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P48" s="1">
         <v>999999</v>
@@ -5318,7 +5309,7 @@
         <v>1023201</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
@@ -5336,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K49" s="1">
         <v>2023201</v>
@@ -5345,7 +5336,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P49" s="1">
         <v>999999</v>
@@ -5362,7 +5353,7 @@
         <v>1023202</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
@@ -5380,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K50" s="1">
         <v>2023202</v>
@@ -5389,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P50" s="1">
         <v>999999</v>
@@ -5406,7 +5397,7 @@
         <v>1023203</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
@@ -5424,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K51" s="1">
         <v>2023203</v>
@@ -5433,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P51" s="1">
         <v>999999</v>
@@ -5450,7 +5441,7 @@
         <v>1023204</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
@@ -5468,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K52" s="1">
         <v>2023204</v>
@@ -5477,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P52" s="1">
         <v>999999</v>
@@ -5494,7 +5485,7 @@
         <v>1023205</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
@@ -5512,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K53" s="1">
         <v>2023205</v>
@@ -5521,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P53" s="1">
         <v>999999</v>
@@ -5538,7 +5529,7 @@
         <v>1023301</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
@@ -5556,7 +5547,7 @@
         <v>1</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K54" s="1">
         <v>2023301</v>
@@ -5565,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P54" s="1">
         <v>999999</v>
@@ -5582,7 +5573,7 @@
         <v>1023302</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
@@ -5600,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K55" s="1">
         <v>2023302</v>
@@ -5609,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P55" s="1">
         <v>999999</v>
@@ -5626,7 +5617,7 @@
         <v>1023303</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
@@ -5644,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K56" s="1">
         <v>2023303</v>
@@ -5653,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P56" s="1">
         <v>999999</v>
@@ -5670,7 +5661,7 @@
         <v>1023304</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
@@ -5688,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K57" s="1">
         <v>2023304</v>
@@ -5697,7 +5688,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P57" s="1">
         <v>999999</v>
@@ -5714,7 +5705,7 @@
         <v>1023305</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
@@ -5732,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K58" s="1">
         <v>2023305</v>
@@ -5741,7 +5732,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P58" s="1">
         <v>999999</v>
@@ -5758,7 +5749,7 @@
         <v>1023401</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
@@ -5776,7 +5767,7 @@
         <v>1</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K59" s="1">
         <v>2023401</v>
@@ -5785,7 +5776,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P59" s="1">
         <v>999999</v>
@@ -5802,7 +5793,7 @@
         <v>1023402</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
@@ -5820,7 +5811,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K60" s="1">
         <v>2023402</v>
@@ -5829,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P60" s="1">
         <v>999999</v>
@@ -5846,7 +5837,7 @@
         <v>1023403</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
@@ -5864,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="K61" s="1">
         <v>2023403</v>
@@ -5873,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P61" s="1">
         <v>999999</v>
@@ -5890,7 +5881,7 @@
         <v>1023404</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
@@ -5908,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K62" s="1">
         <v>2023404</v>
@@ -5917,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P62" s="1">
         <v>999999</v>
@@ -5934,7 +5925,7 @@
         <v>1023405</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
@@ -5952,7 +5943,7 @@
         <v>1</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K63" s="1">
         <v>2023405</v>
@@ -5961,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P63" s="1">
         <v>999999</v>
@@ -5978,7 +5969,7 @@
         <v>1024001</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
@@ -5996,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K64" s="1">
         <v>2024001</v>
@@ -6005,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P64" s="1">
         <v>-1</v>
@@ -6019,7 +6010,7 @@
         <v>1024003</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
@@ -6037,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K65" s="1">
         <v>2024003</v>
@@ -6046,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P65" s="1">
         <v>-1</v>
@@ -6060,7 +6051,7 @@
         <v>1024005</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
@@ -6078,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K66" s="1">
         <v>2024005</v>
@@ -6087,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P66" s="1">
         <v>-1</v>
@@ -6101,7 +6092,7 @@
         <v>1024006</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
@@ -6119,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K67" s="1">
         <v>2024006</v>
@@ -6128,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P67" s="1">
         <v>-1</v>
@@ -6142,7 +6133,7 @@
         <v>1024007</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
@@ -6160,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K68" s="1">
         <v>2024007</v>
@@ -6169,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P68" s="1">
         <v>999999999</v>
@@ -6183,7 +6174,7 @@
         <v>1024008</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
@@ -6201,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K69" s="1">
         <v>2024008</v>
@@ -6210,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P69" s="1">
         <v>999999</v>
@@ -6224,7 +6215,7 @@
         <v>1024009</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
@@ -6242,7 +6233,7 @@
         <v>1</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K70" s="1">
         <v>2024009</v>
@@ -6251,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P70" s="1">
         <v>999999</v>
@@ -6265,7 +6256,7 @@
         <v>1024010</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
@@ -6283,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K71" s="1">
         <v>2024010</v>
@@ -6292,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P71" s="1">
         <v>999999</v>
@@ -6306,7 +6297,7 @@
         <v>1024011</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
@@ -6324,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K72" s="1">
         <v>2024011</v>
@@ -6333,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P72" s="1">
         <v>-1</v>
@@ -6347,7 +6338,7 @@
         <v>1024012</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -6374,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P73" s="1">
         <v>-1</v>
@@ -6388,7 +6379,7 @@
         <v>1024013</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -6415,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P74" s="1">
         <v>999999</v>
@@ -6429,7 +6420,7 @@
         <v>1024014</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -6456,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P75" s="1">
         <v>999999</v>
@@ -6470,7 +6461,7 @@
         <v>1024015</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
@@ -6488,7 +6479,7 @@
         <v>1</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K76" s="1">
         <v>2024015</v>
@@ -6497,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P76" s="1">
         <v>999999</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -6514,7 +6505,7 @@
         <v>1024016</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -6532,7 +6523,7 @@
         <v>1</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K77" s="1">
         <v>2024016</v>
@@ -6541,13 +6532,13 @@
         <v>0</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P77" s="1">
         <v>999999</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -6558,7 +6549,7 @@
         <v>1024017</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -6576,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K78" s="1">
         <v>2024017</v>
@@ -6585,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P78" s="1">
         <v>999999</v>
@@ -6599,7 +6590,7 @@
         <v>1024018</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
@@ -6617,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K79" s="1">
         <v>2024018</v>
@@ -6626,7 +6617,7 @@
         <v>0</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P79" s="1">
         <v>-1</v>
@@ -6640,7 +6631,7 @@
         <v>1024019</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -6658,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K80" s="1">
         <v>2024019</v>
@@ -6667,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6678,7 +6669,7 @@
         <v>1024020</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -6696,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K81" s="1">
         <v>2024020</v>
@@ -6705,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6716,7 +6707,7 @@
         <v>1024021</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -6734,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K82" s="1">
         <v>2024021</v>
@@ -6743,7 +6734,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6754,7 +6745,7 @@
         <v>1024022</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -6772,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K83" s="1">
         <v>2024022</v>
@@ -6781,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6792,7 +6783,7 @@
         <v>1024023</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -6810,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K84" s="1">
         <v>2024023</v>
@@ -6819,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6830,7 +6821,7 @@
         <v>1024024</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -6848,7 +6839,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K85" s="1">
         <v>2024024</v>
@@ -6857,7 +6848,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P85" s="1">
         <v>999999</v>
@@ -6871,25 +6862,25 @@
         <v>1024024</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E86" s="1">
+        <v>2</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G86" s="1">
+        <v>1</v>
+      </c>
+      <c r="H86" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="E86" s="1">
-        <v>2</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G86" s="1">
-        <v>1</v>
-      </c>
-      <c r="H86" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="I86" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="K86" s="1">
         <v>2024025</v>
@@ -6898,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P86" s="1">
         <v>999999</v>
@@ -6912,7 +6903,7 @@
         <v>1024024</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -6930,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K87" s="1">
         <v>2024026</v>
@@ -6939,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P87" s="1">
         <v>999999</v>
@@ -6953,7 +6944,7 @@
         <v>1024024</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -6971,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K88" s="1">
         <v>2024027</v>
@@ -6980,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P88" s="1">
         <v>999999</v>
@@ -6994,7 +6985,7 @@
         <v>1024024</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -7012,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K89" s="1">
         <v>2024028</v>
@@ -7021,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P89" s="1">
         <v>999999</v>
@@ -7035,7 +7026,7 @@
         <v>1024024</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -7053,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K90" s="1">
         <v>2024029</v>
@@ -7062,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P90" s="1">
         <v>999999</v>
@@ -7076,7 +7067,7 @@
         <v>1024024</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
@@ -7094,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K91" s="1">
         <v>2024030</v>
@@ -7103,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P91" s="1">
         <v>999999</v>
@@ -7117,7 +7108,7 @@
         <v>1024024</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -7135,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K92" s="1">
         <v>2024031</v>
@@ -7144,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P92" s="1">
         <v>999999</v>
@@ -7158,7 +7149,7 @@
         <v>1024024</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
@@ -7176,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K93" s="1">
         <v>2024032</v>
@@ -7185,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P93" s="1">
         <v>999999</v>
@@ -7199,7 +7190,7 @@
         <v>1024024</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -7217,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K94" s="1">
         <v>2024033</v>
@@ -7226,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P94" s="1">
         <v>999999</v>
@@ -7240,7 +7231,7 @@
         <v>1024025</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -7264,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P95" s="1">
         <v>999999</v>
@@ -7278,7 +7269,7 @@
         <v>1024026</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -7302,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P96" s="1">
         <v>999999</v>
@@ -7316,7 +7307,7 @@
         <v>1024027</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -7340,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P97" s="1">
         <v>999999</v>
@@ -7354,7 +7345,7 @@
         <v>1024028</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -7378,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P98" s="1">
         <v>999999</v>
@@ -7392,7 +7383,7 @@
         <v>1024029</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -7416,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P99" s="1">
         <v>999999</v>
@@ -7430,7 +7421,7 @@
         <v>1024030</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -7454,7 +7445,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="P100" s="1">
         <v>999999</v>
@@ -7468,7 +7459,7 @@
         <v>1025101</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E101" s="1">
         <v>2</v>
@@ -7486,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="K101" s="1">
         <v>2025101</v>
@@ -7495,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P101" s="1">
         <v>-1</v>
@@ -7509,7 +7500,7 @@
         <v>1025102</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E102" s="1">
         <v>2</v>
@@ -7527,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K102" s="1">
         <v>2025102</v>
@@ -7536,7 +7527,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="P102" s="1">
         <v>-1</v>
@@ -7550,7 +7541,7 @@
         <v>1025103</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E103" s="1">
         <v>2</v>
@@ -7568,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="K103" s="1">
         <v>2025103</v>
@@ -7577,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P103" s="1">
         <v>-1</v>
@@ -7591,7 +7582,7 @@
         <v>1025104</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E104" s="1">
         <v>2</v>
@@ -7609,7 +7600,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K104" s="1">
         <v>2025104</v>
@@ -7618,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P104" s="1">
         <v>-1</v>
@@ -7632,7 +7623,7 @@
         <v>1025105</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E105" s="1">
         <v>2</v>
@@ -7650,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K105" s="1">
         <v>2025105</v>
@@ -7659,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P105" s="1">
         <v>-1</v>
@@ -7673,7 +7664,7 @@
         <v>1025106</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E106" s="1">
         <v>2</v>
@@ -7691,7 +7682,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K106" s="1">
         <v>2025106</v>
@@ -7700,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P106" s="1">
         <v>-1</v>
@@ -7714,7 +7705,7 @@
         <v>1025201</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E107" s="1">
         <v>2</v>
@@ -7732,7 +7723,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="K107" s="1">
         <v>2025201</v>
@@ -7741,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P107" s="1">
         <v>-1</v>
@@ -7755,7 +7746,7 @@
         <v>1025202</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E108" s="1">
         <v>2</v>
@@ -7773,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="K108" s="1">
         <v>2025202</v>
@@ -7782,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P108" s="1">
         <v>-1</v>
@@ -7796,7 +7787,7 @@
         <v>1025203</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E109" s="1">
         <v>2</v>
@@ -7814,7 +7805,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K109" s="1">
         <v>2025203</v>
@@ -7823,7 +7814,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P109" s="1">
         <v>-1</v>
@@ -7837,7 +7828,7 @@
         <v>1025204</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E110" s="1">
         <v>2</v>
@@ -7855,7 +7846,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K110" s="1">
         <v>2025204</v>
@@ -7864,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="P110" s="1">
         <v>-1</v>
@@ -7878,7 +7869,7 @@
         <v>1025205</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E111" s="1">
         <v>2</v>
@@ -7896,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="K111" s="1">
         <v>2025205</v>
@@ -7905,7 +7896,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P111" s="1">
         <v>-1</v>
@@ -7919,7 +7910,7 @@
         <v>1025206</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E112" s="1">
         <v>2</v>
@@ -7937,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K112" s="1">
         <v>2025206</v>
@@ -7946,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P112" s="1">
         <v>-1</v>
@@ -7960,7 +7951,7 @@
         <v>1025301</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E113" s="1">
         <v>2</v>
@@ -7978,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K113" s="1">
         <v>2025301</v>
@@ -7987,7 +7978,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P113" s="1">
         <v>-1</v>
@@ -8001,7 +7992,7 @@
         <v>1025302</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E114" s="1">
         <v>2</v>
@@ -8019,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="K114" s="1">
         <v>2025302</v>
@@ -8028,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="P114" s="1">
         <v>-1</v>
@@ -8042,7 +8033,7 @@
         <v>1025303</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E115" s="1">
         <v>2</v>
@@ -8060,7 +8051,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K115" s="1">
         <v>2025303</v>
@@ -8069,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P115" s="1">
         <v>-1</v>
@@ -8083,7 +8074,7 @@
         <v>1025304</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E116" s="1">
         <v>2</v>
@@ -8101,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K116" s="1">
         <v>2025304</v>
@@ -8110,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="P116" s="1">
         <v>-1</v>
@@ -8124,7 +8115,7 @@
         <v>1025305</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E117" s="1">
         <v>2</v>
@@ -8142,7 +8133,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K117" s="1">
         <v>2025305</v>
@@ -8151,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P117" s="1">
         <v>-1</v>
@@ -8165,7 +8156,7 @@
         <v>1025306</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E118" s="1">
         <v>2</v>
@@ -8183,7 +8174,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="K118" s="1">
         <v>2025306</v>
@@ -8192,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P118" s="1">
         <v>-1</v>
@@ -8206,7 +8197,7 @@
         <v>1025401</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E119" s="1">
         <v>2</v>
@@ -8224,7 +8215,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K119" s="1">
         <v>2025401</v>
@@ -8233,7 +8224,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P119" s="1">
         <v>-1</v>
@@ -8247,7 +8238,7 @@
         <v>1025402</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E120" s="1">
         <v>2</v>
@@ -8265,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="K120" s="1">
         <v>2025402</v>
@@ -8274,7 +8265,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P120" s="1">
         <v>-1</v>
@@ -8288,7 +8279,7 @@
         <v>1025403</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E121" s="1">
         <v>2</v>
@@ -8306,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="K121" s="1">
         <v>2025403</v>
@@ -8315,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P121" s="1">
         <v>-1</v>
@@ -8329,7 +8320,7 @@
         <v>1025404</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E122" s="1">
         <v>2</v>
@@ -8347,7 +8338,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="K122" s="1">
         <v>2025404</v>
@@ -8356,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="P122" s="1">
         <v>-1</v>
@@ -8370,7 +8361,7 @@
         <v>1025405</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E123" s="1">
         <v>2</v>
@@ -8388,7 +8379,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K123" s="1">
         <v>2025405</v>
@@ -8397,7 +8388,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="P123" s="1">
         <v>-1</v>
@@ -8411,7 +8402,7 @@
         <v>1025406</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E124" s="1">
         <v>2</v>
@@ -8429,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="K124" s="1">
         <v>2025406</v>
@@ -8438,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="P124" s="1">
         <v>-1</v>
@@ -8452,7 +8443,7 @@
         <v>1025501</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E125" s="1">
         <v>2</v>
@@ -8470,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="K125" s="1">
         <v>2025501</v>
@@ -8479,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="P125" s="1">
         <v>-1</v>
@@ -8493,7 +8484,7 @@
         <v>1025502</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E126" s="1">
         <v>2</v>
@@ -8511,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K126" s="1">
         <v>2025502</v>
@@ -8520,7 +8511,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="P126" s="1">
         <v>-1</v>
@@ -8534,7 +8525,7 @@
         <v>1025503</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E127" s="1">
         <v>2</v>
@@ -8552,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K127" s="1">
         <v>2025503</v>
@@ -8561,7 +8552,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="P127" s="1">
         <v>-1</v>
@@ -8575,7 +8566,7 @@
         <v>1025504</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E128" s="1">
         <v>2</v>
@@ -8593,7 +8584,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K128" s="1">
         <v>2025504</v>
@@ -8602,7 +8593,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="P128" s="1">
         <v>-1</v>
@@ -8616,7 +8607,7 @@
         <v>1025505</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E129" s="1">
         <v>2</v>
@@ -8634,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K129" s="1">
         <v>2025505</v>
@@ -8643,7 +8634,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="P129" s="1">
         <v>-1</v>
@@ -8657,7 +8648,7 @@
         <v>1025506</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E130" s="1">
         <v>2</v>
@@ -8675,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K130" s="1">
         <v>2025506</v>
@@ -8684,7 +8675,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="P130" s="1">
         <v>-1</v>
@@ -8717,7 +8708,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K131" s="1">
         <v>2125101</v>
@@ -8760,7 +8751,7 @@
         <v>1</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K132" s="1">
         <v>2125102</v>
@@ -8803,7 +8794,7 @@
         <v>1</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K133" s="1">
         <v>2125103</v>
@@ -8846,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K134" s="1">
         <v>2125104</v>
@@ -8889,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K135" s="1">
         <v>2125105</v>
@@ -8932,7 +8923,7 @@
         <v>1</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K136" s="1">
         <v>2125106</v>
@@ -8975,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K137" s="1">
         <v>2125201</v>
@@ -9018,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K138" s="1">
         <v>2125202</v>
@@ -9061,7 +9052,7 @@
         <v>1</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K139" s="1">
         <v>2125203</v>
@@ -9104,7 +9095,7 @@
         <v>1</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K140" s="1">
         <v>2125204</v>
@@ -9147,7 +9138,7 @@
         <v>1</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K141" s="1">
         <v>2125205</v>
@@ -9190,7 +9181,7 @@
         <v>1</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K142" s="1">
         <v>2125206</v>
@@ -9233,7 +9224,7 @@
         <v>1</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K143" s="1">
         <v>2125301</v>
@@ -9276,7 +9267,7 @@
         <v>1</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K144" s="1">
         <v>2125302</v>
@@ -9319,7 +9310,7 @@
         <v>1</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K145" s="1">
         <v>2125303</v>
@@ -9362,7 +9353,7 @@
         <v>1</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K146" s="1">
         <v>2125304</v>
@@ -9405,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K147" s="1">
         <v>2125305</v>
@@ -9448,7 +9439,7 @@
         <v>1</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K148" s="1">
         <v>2125306</v>
@@ -9491,7 +9482,7 @@
         <v>1</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K149" s="1">
         <v>2125401</v>
@@ -9534,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K150" s="1">
         <v>2125402</v>
@@ -9577,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K151" s="1">
         <v>2125403</v>
@@ -9620,7 +9611,7 @@
         <v>1</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K152" s="1">
         <v>2125404</v>
@@ -9663,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K153" s="1">
         <v>2125405</v>
@@ -9706,7 +9697,7 @@
         <v>1</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K154" s="1">
         <v>2125406</v>
@@ -9749,7 +9740,7 @@
         <v>1</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K155" s="1">
         <v>2125501</v>
@@ -9792,7 +9783,7 @@
         <v>1</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K156" s="1">
         <v>2125502</v>
@@ -9835,7 +9826,7 @@
         <v>1</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K157" s="1">
         <v>2125503</v>
@@ -9878,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K158" s="1">
         <v>2125504</v>
@@ -9921,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K159" s="1">
         <v>2125505</v>
@@ -9964,7 +9955,7 @@
         <v>1</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K160" s="1">
         <v>2125506</v>
@@ -9988,7 +9979,7 @@
         <v>1026001</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -10006,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K161" s="1">
         <v>2026001</v>
@@ -10015,7 +10006,7 @@
         <v>0</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P161" s="1">
         <v>-1</v>
@@ -10029,7 +10020,7 @@
         <v>1026002</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -10047,7 +10038,7 @@
         <v>0</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="K162" s="1">
         <v>2026002</v>
@@ -10056,7 +10047,7 @@
         <v>0</v>
       </c>
       <c r="M162" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="P162" s="1">
         <v>-1</v>
@@ -10070,7 +10061,7 @@
         <v>1026101</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -10088,7 +10079,7 @@
         <v>0</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K163" s="1">
         <v>2026101</v>
@@ -10097,7 +10088,7 @@
         <v>0</v>
       </c>
       <c r="M163" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="P163" s="1">
         <v>-1</v>
@@ -10111,7 +10102,7 @@
         <v>1026102</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
@@ -10129,7 +10120,7 @@
         <v>0</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K164" s="1">
         <v>2026102</v>
@@ -10138,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="M164" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="P164" s="1">
         <v>-1</v>
@@ -10152,7 +10143,7 @@
         <v>1026201</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
@@ -10170,7 +10161,7 @@
         <v>0</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K165" s="1">
         <v>2026201</v>
@@ -10179,7 +10170,7 @@
         <v>0</v>
       </c>
       <c r="M165" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="P165" s="1">
         <v>-1</v>
@@ -10193,7 +10184,7 @@
         <v>1026202</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E166" s="1">
         <v>2</v>
@@ -10211,7 +10202,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K166" s="1">
         <v>2026202</v>
@@ -10220,7 +10211,7 @@
         <v>0</v>
       </c>
       <c r="M166" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="P166" s="1">
         <v>-1</v>
@@ -10234,7 +10225,7 @@
         <v>1026301</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E167" s="1">
         <v>2</v>
@@ -10252,7 +10243,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K167" s="1">
         <v>2026301</v>
@@ -10261,7 +10252,7 @@
         <v>0</v>
       </c>
       <c r="M167" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="P167" s="1">
         <v>-1</v>
@@ -10275,7 +10266,7 @@
         <v>1026302</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E168" s="1">
         <v>2</v>
@@ -10293,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K168" s="1">
         <v>2026302</v>
@@ -10302,7 +10293,7 @@
         <v>0</v>
       </c>
       <c r="M168" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P168" s="1">
         <v>-1</v>
@@ -10316,7 +10307,7 @@
         <v>1026401</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E169" s="1">
         <v>2</v>
@@ -10334,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K169" s="1">
         <v>2026401</v>
@@ -10343,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="M169" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P169" s="1">
         <v>-1</v>
@@ -10357,7 +10348,7 @@
         <v>1026402</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E170" s="1">
         <v>2</v>
@@ -10375,7 +10366,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K170" s="1">
         <v>2026402</v>
@@ -10384,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="M170" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="P170" s="1">
         <v>-1</v>
@@ -10398,7 +10389,7 @@
         <v>1027001</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E171" s="1">
         <v>2</v>
@@ -10416,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="J171" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K171" s="1">
         <v>2027001</v>
@@ -10425,7 +10416,7 @@
         <v>0</v>
       </c>
       <c r="M171" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="P171" s="1">
         <v>-1</v>
@@ -10439,7 +10430,7 @@
         <v>1027002</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E172" s="1">
         <v>2</v>
@@ -10457,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K172" s="1">
         <v>2027002</v>
@@ -10466,7 +10457,7 @@
         <v>0</v>
       </c>
       <c r="M172" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P172" s="1">
         <v>-1</v>
@@ -10480,7 +10471,7 @@
         <v>1027101</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E173" s="1">
         <v>2</v>
@@ -10498,7 +10489,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K173" s="1">
         <v>2027101</v>
@@ -10507,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="M173" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="P173" s="1">
         <v>-1</v>
@@ -10521,7 +10512,7 @@
         <v>1027102</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E174" s="1">
         <v>2</v>
@@ -10539,7 +10530,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K174" s="1">
         <v>2027102</v>
@@ -10548,7 +10539,7 @@
         <v>0</v>
       </c>
       <c r="M174" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="P174" s="1">
         <v>-1</v>
@@ -10562,7 +10553,7 @@
         <v>1027201</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E175" s="1">
         <v>2</v>
@@ -10580,7 +10571,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K175" s="1">
         <v>2027201</v>
@@ -10589,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="M175" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="P175" s="1">
         <v>-1</v>
@@ -10603,7 +10594,7 @@
         <v>1027202</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E176" s="1">
         <v>2</v>
@@ -10621,7 +10612,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K176" s="1">
         <v>2027202</v>
@@ -10630,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="M176" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="P176" s="1">
         <v>-1</v>
@@ -10644,7 +10635,7 @@
         <v>1027301</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E177" s="1">
         <v>2</v>
@@ -10662,7 +10653,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K177" s="1">
         <v>2027301</v>
@@ -10671,7 +10662,7 @@
         <v>0</v>
       </c>
       <c r="M177" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="P177" s="1">
         <v>-1</v>
@@ -10685,7 +10676,7 @@
         <v>1027302</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E178" s="1">
         <v>2</v>
@@ -10703,7 +10694,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="K178" s="1">
         <v>2027302</v>
@@ -10712,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="M178" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P178" s="1">
         <v>-1</v>
@@ -10726,7 +10717,7 @@
         <v>1027401</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E179" s="1">
         <v>2</v>
@@ -10744,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K179" s="1">
         <v>2027401</v>
@@ -10753,7 +10744,7 @@
         <v>0</v>
       </c>
       <c r="M179" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="P179" s="1">
         <v>-1</v>
@@ -10767,7 +10758,7 @@
         <v>1027402</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E180" s="1">
         <v>2</v>
@@ -10785,7 +10776,7 @@
         <v>0</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K180" s="1">
         <v>2027402</v>
@@ -10794,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="M180" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="P180" s="1">
         <v>-1</v>
@@ -10808,7 +10799,7 @@
         <v>1028001</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E181" s="1">
         <v>2</v>
@@ -10826,7 +10817,7 @@
         <v>0</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K181" s="1">
         <v>2028001</v>
@@ -10835,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="M181" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="P181" s="1">
         <v>-1</v>
@@ -10849,7 +10840,7 @@
         <v>1028002</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E182" s="1">
         <v>2</v>
@@ -10867,7 +10858,7 @@
         <v>0</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K182" s="1">
         <v>2028002</v>
@@ -10876,7 +10867,7 @@
         <v>0</v>
       </c>
       <c r="M182" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="P182" s="1">
         <v>-1</v>
@@ -10890,7 +10881,7 @@
         <v>1028101</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E183" s="1">
         <v>2</v>
@@ -10908,7 +10899,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K183" s="1">
         <v>2028101</v>
@@ -10917,7 +10908,7 @@
         <v>0</v>
       </c>
       <c r="M183" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="P183" s="1">
         <v>-1</v>
@@ -10931,7 +10922,7 @@
         <v>1028102</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E184" s="1">
         <v>2</v>
@@ -10949,7 +10940,7 @@
         <v>0</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K184" s="1">
         <v>2028102</v>
@@ -10958,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="M184" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="P184" s="1">
         <v>-1</v>
@@ -10972,7 +10963,7 @@
         <v>1028201</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E185" s="1">
         <v>2</v>
@@ -10990,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K185" s="1">
         <v>2028201</v>
@@ -10999,7 +10990,7 @@
         <v>0</v>
       </c>
       <c r="M185" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="P185" s="1">
         <v>-1</v>
@@ -11013,7 +11004,7 @@
         <v>1028202</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E186" s="1">
         <v>2</v>
@@ -11031,7 +11022,7 @@
         <v>0</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K186" s="1">
         <v>2028202</v>
@@ -11040,7 +11031,7 @@
         <v>0</v>
       </c>
       <c r="M186" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="P186" s="1">
         <v>-1</v>
@@ -11054,7 +11045,7 @@
         <v>1028301</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E187" s="1">
         <v>2</v>
@@ -11072,7 +11063,7 @@
         <v>0</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K187" s="1">
         <v>2028301</v>
@@ -11081,7 +11072,7 @@
         <v>0</v>
       </c>
       <c r="M187" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="P187" s="1">
         <v>-1</v>
@@ -11095,7 +11086,7 @@
         <v>1028302</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E188" s="1">
         <v>2</v>
@@ -11113,7 +11104,7 @@
         <v>0</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K188" s="1">
         <v>2028302</v>
@@ -11122,7 +11113,7 @@
         <v>0</v>
       </c>
       <c r="M188" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="P188" s="1">
         <v>-1</v>
@@ -11136,7 +11127,7 @@
         <v>1028401</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E189" s="1">
         <v>2</v>
@@ -11154,7 +11145,7 @@
         <v>0</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K189" s="1">
         <v>2028401</v>
@@ -11163,7 +11154,7 @@
         <v>0</v>
       </c>
       <c r="M189" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="P189" s="1">
         <v>-1</v>
@@ -11177,7 +11168,7 @@
         <v>1028402</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E190" s="1">
         <v>2</v>
@@ -11195,7 +11186,7 @@
         <v>0</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K190" s="1">
         <v>2028402</v>
@@ -11204,7 +11195,7 @@
         <v>0</v>
       </c>
       <c r="M190" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="P190" s="1">
         <v>-1</v>
@@ -11237,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="K191" s="1">
         <v>2126001</v>
@@ -11280,7 +11271,7 @@
         <v>1</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K192" s="1">
         <v>2126002</v>
@@ -11323,7 +11314,7 @@
         <v>1</v>
       </c>
       <c r="J193" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K193" s="1">
         <v>2126101</v>
@@ -11366,7 +11357,7 @@
         <v>1</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K194" s="1">
         <v>2126102</v>
@@ -11409,7 +11400,7 @@
         <v>1</v>
       </c>
       <c r="J195" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K195" s="1">
         <v>2126201</v>
@@ -11452,7 +11443,7 @@
         <v>1</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K196" s="1">
         <v>2126202</v>
@@ -11495,7 +11486,7 @@
         <v>1</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K197" s="1">
         <v>2126301</v>
@@ -11538,7 +11529,7 @@
         <v>1</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K198" s="1">
         <v>2126302</v>
@@ -11581,7 +11572,7 @@
         <v>1</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K199" s="1">
         <v>2126401</v>
@@ -11624,7 +11615,7 @@
         <v>1</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K200" s="1">
         <v>2126402</v>
@@ -11667,7 +11658,7 @@
         <v>1</v>
       </c>
       <c r="J201" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K201" s="1">
         <v>2127001</v>
@@ -11710,7 +11701,7 @@
         <v>1</v>
       </c>
       <c r="J202" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K202" s="1">
         <v>2127002</v>
@@ -11753,7 +11744,7 @@
         <v>1</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K203" s="1">
         <v>2127101</v>
@@ -11796,7 +11787,7 @@
         <v>1</v>
       </c>
       <c r="J204" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K204" s="1">
         <v>2127102</v>
@@ -11839,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="J205" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K205" s="1">
         <v>2127201</v>
@@ -11882,7 +11873,7 @@
         <v>1</v>
       </c>
       <c r="J206" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K206" s="1">
         <v>2127202</v>
@@ -11925,7 +11916,7 @@
         <v>1</v>
       </c>
       <c r="J207" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K207" s="1">
         <v>2127301</v>
@@ -11968,7 +11959,7 @@
         <v>1</v>
       </c>
       <c r="J208" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K208" s="1">
         <v>2127302</v>
@@ -12011,7 +12002,7 @@
         <v>1</v>
       </c>
       <c r="J209" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K209" s="1">
         <v>2127401</v>
@@ -12054,7 +12045,7 @@
         <v>1</v>
       </c>
       <c r="J210" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K210" s="1">
         <v>2127402</v>
@@ -12097,7 +12088,7 @@
         <v>1</v>
       </c>
       <c r="J211" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K211" s="1">
         <v>2128001</v>
@@ -12140,7 +12131,7 @@
         <v>1</v>
       </c>
       <c r="J212" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K212" s="1">
         <v>2128002</v>
@@ -12183,7 +12174,7 @@
         <v>1</v>
       </c>
       <c r="J213" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K213" s="1">
         <v>2128101</v>
@@ -12226,7 +12217,7 @@
         <v>1</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K214" s="1">
         <v>2128102</v>
@@ -12269,7 +12260,7 @@
         <v>1</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K215" s="1">
         <v>2128201</v>
@@ -12312,7 +12303,7 @@
         <v>1</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K216" s="1">
         <v>2128202</v>
@@ -12355,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K217" s="1">
         <v>2128301</v>
@@ -12398,7 +12389,7 @@
         <v>1</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K218" s="1">
         <v>2128302</v>
@@ -12441,7 +12432,7 @@
         <v>1</v>
       </c>
       <c r="J219" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K219" s="1">
         <v>2128401</v>
@@ -12484,7 +12475,7 @@
         <v>1</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="K220" s="1">
         <v>2128402</v>
@@ -12508,7 +12499,7 @@
         <v>1130001</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -12532,7 +12523,7 @@
         <v>0</v>
       </c>
       <c r="M221" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="P221" s="1">
         <v>999999</v>
@@ -12546,7 +12537,7 @@
         <v>1130002</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E222" s="1">
         <v>1</v>
@@ -12570,7 +12561,7 @@
         <v>0</v>
       </c>
       <c r="M222" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="P222" s="1">
         <v>999999</v>
@@ -12584,7 +12575,7 @@
         <v>1130003</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E223" s="1">
         <v>1</v>
@@ -12608,7 +12599,7 @@
         <v>0</v>
       </c>
       <c r="M223" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P223" s="1">
         <v>999999</v>
@@ -12622,7 +12613,7 @@
         <v>1130004</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E224" s="1">
         <v>1</v>
@@ -12646,7 +12637,7 @@
         <v>0</v>
       </c>
       <c r="M224" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="P224" s="1">
         <v>999999</v>
@@ -12660,7 +12651,7 @@
         <v>1130005</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E225" s="1">
         <v>1</v>
@@ -12684,7 +12675,7 @@
         <v>0</v>
       </c>
       <c r="M225" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P225" s="1">
         <v>999999</v>
@@ -12698,7 +12689,7 @@
         <v>1130006</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E226" s="1">
         <v>1</v>
@@ -12722,7 +12713,7 @@
         <v>0</v>
       </c>
       <c r="M226" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="P226" s="1">
         <v>999999</v>
@@ -12736,7 +12727,7 @@
         <v>1131001</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
@@ -12760,7 +12751,7 @@
         <v>0</v>
       </c>
       <c r="M227" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12771,7 +12762,7 @@
         <v>1131002</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
@@ -12795,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="M228" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12806,7 +12797,7 @@
         <v>1131003</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
@@ -12830,7 +12821,7 @@
         <v>0</v>
       </c>
       <c r="M229" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12841,7 +12832,7 @@
         <v>1131004</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
@@ -12865,7 +12856,7 @@
         <v>0</v>
       </c>
       <c r="M230" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -12876,7 +12867,7 @@
         <v>1131005</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
@@ -12900,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="M231" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -12911,7 +12902,7 @@
         <v>1131006</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
@@ -12935,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="M232" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -12946,7 +12937,7 @@
         <v>1131101</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E233" s="1">
         <v>2</v>
@@ -12970,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="M233" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -12981,7 +12972,7 @@
         <v>1131102</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E234" s="1">
         <v>2</v>
@@ -13005,7 +12996,7 @@
         <v>0</v>
       </c>
       <c r="M234" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13016,7 +13007,7 @@
         <v>1131103</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E235" s="1">
         <v>2</v>
@@ -13040,7 +13031,7 @@
         <v>0</v>
       </c>
       <c r="M235" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13051,7 +13042,7 @@
         <v>1131104</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E236" s="1">
         <v>2</v>
@@ -13075,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="M236" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13086,7 +13077,7 @@
         <v>1131105</v>
       </c>
       <c r="D237" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E237" s="1">
         <v>2</v>
@@ -13110,7 +13101,7 @@
         <v>0</v>
       </c>
       <c r="M237" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13121,7 +13112,7 @@
         <v>1131106</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E238" s="1">
         <v>2</v>
@@ -13145,7 +13136,7 @@
         <v>0</v>
       </c>
       <c r="M238" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13156,7 +13147,7 @@
         <v>1131201</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E239" s="1">
         <v>2</v>
@@ -13180,7 +13171,7 @@
         <v>0</v>
       </c>
       <c r="M239" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13191,7 +13182,7 @@
         <v>1131202</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E240" s="1">
         <v>2</v>
@@ -13215,7 +13206,7 @@
         <v>0</v>
       </c>
       <c r="M240" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="241" spans="1:13">
@@ -13226,7 +13217,7 @@
         <v>1131203</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E241" s="1">
         <v>2</v>
@@ -13250,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="M241" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="242" spans="1:13">
@@ -13261,7 +13252,7 @@
         <v>1131204</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E242" s="1">
         <v>2</v>
@@ -13285,7 +13276,7 @@
         <v>0</v>
       </c>
       <c r="M242" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="243" spans="1:13">
@@ -13296,7 +13287,7 @@
         <v>1131205</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E243" s="1">
         <v>2</v>
@@ -13320,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="M243" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="244" spans="1:13">
@@ -13331,7 +13322,7 @@
         <v>1131206</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E244" s="1">
         <v>2</v>
@@ -13355,7 +13346,7 @@
         <v>0</v>
       </c>
       <c r="M244" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="245" spans="1:13">
@@ -13366,7 +13357,7 @@
         <v>1131301</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E245" s="1">
         <v>2</v>
@@ -13390,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="M245" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="246" spans="1:13">
@@ -13401,7 +13392,7 @@
         <v>1131302</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E246" s="1">
         <v>2</v>
@@ -13425,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="M246" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="247" spans="1:13">
@@ -13436,7 +13427,7 @@
         <v>1131303</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E247" s="1">
         <v>2</v>
@@ -13460,7 +13451,7 @@
         <v>0</v>
       </c>
       <c r="M247" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="248" spans="1:13">
@@ -13471,7 +13462,7 @@
         <v>1131304</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E248" s="1">
         <v>2</v>
@@ -13495,7 +13486,7 @@
         <v>0</v>
       </c>
       <c r="M248" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="249" spans="1:13">
@@ -13506,7 +13497,7 @@
         <v>1131305</v>
       </c>
       <c r="D249" s="9" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E249" s="1">
         <v>2</v>
@@ -13530,7 +13521,7 @@
         <v>0</v>
       </c>
       <c r="M249" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="250" spans="1:13">
@@ -13541,7 +13532,7 @@
         <v>1131306</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E250" s="1">
         <v>2</v>
@@ -13565,7 +13556,7 @@
         <v>0</v>
       </c>
       <c r="M250" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="251" spans="1:13">
@@ -13576,7 +13567,7 @@
         <v>1131401</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E251" s="1">
         <v>2</v>
@@ -13600,7 +13591,7 @@
         <v>0</v>
       </c>
       <c r="M251" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="252" spans="1:13">
@@ -13611,7 +13602,7 @@
         <v>1131402</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E252" s="1">
         <v>2</v>
@@ -13635,7 +13626,7 @@
         <v>0</v>
       </c>
       <c r="M252" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="253" spans="1:13">
@@ -13646,7 +13637,7 @@
         <v>1131403</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E253" s="1">
         <v>2</v>
@@ -13670,7 +13661,7 @@
         <v>0</v>
       </c>
       <c r="M253" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="254" spans="1:13">
@@ -13681,7 +13672,7 @@
         <v>1131404</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E254" s="1">
         <v>2</v>
@@ -13705,7 +13696,7 @@
         <v>0</v>
       </c>
       <c r="M254" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="255" spans="1:13">
@@ -13716,7 +13707,7 @@
         <v>1131405</v>
       </c>
       <c r="D255" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E255" s="1">
         <v>2</v>
@@ -13740,7 +13731,7 @@
         <v>0</v>
       </c>
       <c r="M255" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="256" spans="1:13">
@@ -13751,7 +13742,7 @@
         <v>1131406</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E256" s="1">
         <v>2</v>
@@ -13775,7 +13766,7 @@
         <v>0</v>
       </c>
       <c r="M256" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -13786,7 +13777,7 @@
         <v>1150001</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E257" s="1">
         <v>2</v>
@@ -13804,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="K257" s="1">
         <v>2150001</v>
@@ -13828,7 +13819,7 @@
         <v>1150002</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E258" s="1">
         <v>2</v>
@@ -13846,7 +13837,7 @@
         <v>0</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="K258" s="1">
         <v>2150002</v>
@@ -13870,7 +13861,7 @@
         <v>1150003</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E259" s="1">
         <v>2</v>
@@ -13888,7 +13879,7 @@
         <v>0</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="K259" s="1">
         <v>2150003</v>
@@ -13912,7 +13903,7 @@
         <v>1150004</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E260" s="1">
         <v>2</v>
@@ -13930,7 +13921,7 @@
         <v>0</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="K260" s="1">
         <v>2150004</v>
@@ -13954,7 +13945,7 @@
         <v>1150005</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E261" s="1">
         <v>2</v>
@@ -13972,7 +13963,7 @@
         <v>0</v>
       </c>
       <c r="J261" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="K261" s="1">
         <v>2150005</v>
@@ -13996,7 +13987,7 @@
         <v>1150006</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E262" s="1">
         <v>2</v>
@@ -14014,7 +14005,7 @@
         <v>0</v>
       </c>
       <c r="J262" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="K262" s="1">
         <v>2150006</v>
@@ -14038,7 +14029,7 @@
         <v>1150007</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -14056,7 +14047,7 @@
         <v>0</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K263" s="1">
         <v>2150007</v>
@@ -14080,7 +14071,7 @@
         <v>1150008</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E264" s="1">
         <v>2</v>
@@ -14098,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="J264" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="K264" s="1">
         <v>2150008</v>
@@ -14122,7 +14113,7 @@
         <v>1150009</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E265" s="1">
         <v>2</v>
@@ -14140,7 +14131,7 @@
         <v>0</v>
       </c>
       <c r="J265" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="K265" s="1">
         <v>2150009</v>
@@ -14164,7 +14155,7 @@
         <v>1150010</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E266" s="1">
         <v>2</v>
@@ -14182,7 +14173,7 @@
         <v>0</v>
       </c>
       <c r="J266" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="K266" s="1">
         <v>2150010</v>
@@ -14206,7 +14197,7 @@
         <v>1150011</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E267" s="1">
         <v>2</v>
@@ -14224,7 +14215,7 @@
         <v>0</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="K267" s="1">
         <v>2150011</v>
@@ -14248,7 +14239,7 @@
         <v>1150012</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E268" s="1">
         <v>2</v>
@@ -14266,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K268" s="1">
         <v>2150012</v>
@@ -14290,7 +14281,7 @@
         <v>1150013</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -14308,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="K269" s="1">
         <v>2150013</v>
@@ -14332,7 +14323,7 @@
         <v>1150014</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -14350,7 +14341,7 @@
         <v>0</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="K270" s="1">
         <v>2150014</v>
@@ -14374,7 +14365,7 @@
         <v>1150015</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -14392,7 +14383,7 @@
         <v>0</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K271" s="1">
         <v>2150015</v>
@@ -14416,7 +14407,7 @@
         <v>1150016</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -14434,7 +14425,7 @@
         <v>0</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="K272" s="1">
         <v>2150016</v>
@@ -14458,7 +14449,7 @@
         <v>1150017</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -14476,7 +14467,7 @@
         <v>0</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="K273" s="1">
         <v>2150017</v>
@@ -14500,7 +14491,7 @@
         <v>1150018</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -14518,7 +14509,7 @@
         <v>0</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="K274" s="1">
         <v>2150018</v>
@@ -14542,7 +14533,7 @@
         <v>1150019</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -14560,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="K275" s="1">
         <v>2150019</v>
@@ -14584,7 +14575,7 @@
         <v>1150020</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -14602,7 +14593,7 @@
         <v>0</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="K276" s="1">
         <v>2150020</v>
@@ -14626,7 +14617,7 @@
         <v>1150021</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -14644,7 +14635,7 @@
         <v>0</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="K277" s="1">
         <v>2150021</v>
@@ -14668,7 +14659,7 @@
         <v>1150022</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -14686,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="K278" s="1">
         <v>2150022</v>
@@ -14710,7 +14701,7 @@
         <v>1150023</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -14728,7 +14719,7 @@
         <v>0</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="K279" s="1">
         <v>2150023</v>
@@ -14752,7 +14743,7 @@
         <v>1150024</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -14770,7 +14761,7 @@
         <v>0</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="K280" s="1">
         <v>2150024</v>
@@ -14794,7 +14785,7 @@
         <v>1150025</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -14812,7 +14803,7 @@
         <v>0</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="K281" s="1">
         <v>2150025</v>
@@ -14836,7 +14827,7 @@
         <v>1150026</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -14854,7 +14845,7 @@
         <v>0</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="K282" s="1">
         <v>2150026</v>
@@ -14878,7 +14869,7 @@
         <v>1150027</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -14896,7 +14887,7 @@
         <v>0</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K283" s="1">
         <v>2150027</v>
@@ -14920,7 +14911,7 @@
         <v>1150028</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -14938,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K284" s="1">
         <v>2150028</v>
@@ -14962,7 +14953,7 @@
         <v>1150029</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -14980,7 +14971,7 @@
         <v>0</v>
       </c>
       <c r="J285" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="K285" s="1">
         <v>2150029</v>
@@ -15004,7 +14995,7 @@
         <v>1150030</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15022,7 +15013,7 @@
         <v>0</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K286" s="1">
         <v>2150030</v>
@@ -15046,7 +15037,7 @@
         <v>1150031</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -15064,7 +15055,7 @@
         <v>0</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="K287" s="1">
         <v>2150031</v>
@@ -15088,7 +15079,7 @@
         <v>1150032</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -15106,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="J288" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="K288" s="1">
         <v>2150032</v>
@@ -15130,7 +15121,7 @@
         <v>1150033</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -15148,7 +15139,7 @@
         <v>0</v>
       </c>
       <c r="J289" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="K289" s="1">
         <v>2150033</v>
@@ -15172,7 +15163,7 @@
         <v>1150034</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -15190,7 +15181,7 @@
         <v>0</v>
       </c>
       <c r="J290" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="K290" s="1">
         <v>2150034</v>
@@ -15214,7 +15205,7 @@
         <v>1150035</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -15232,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="J291" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K291" s="1">
         <v>2150035</v>
@@ -15256,7 +15247,7 @@
         <v>1150036</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -15274,7 +15265,7 @@
         <v>0</v>
       </c>
       <c r="J292" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K292" s="1">
         <v>2150036</v>
@@ -15298,7 +15289,7 @@
         <v>1150037</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -15316,7 +15307,7 @@
         <v>0</v>
       </c>
       <c r="J293" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="K293" s="1">
         <v>2150037</v>
@@ -15340,7 +15331,7 @@
         <v>1150038</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -15358,7 +15349,7 @@
         <v>0</v>
       </c>
       <c r="J294" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="K294" s="1">
         <v>2150038</v>
@@ -15382,7 +15373,7 @@
         <v>1150039</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -15400,7 +15391,7 @@
         <v>0</v>
       </c>
       <c r="J295" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="K295" s="1">
         <v>2150039</v>
@@ -15424,7 +15415,7 @@
         <v>1150040</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -15442,7 +15433,7 @@
         <v>0</v>
       </c>
       <c r="J296" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="K296" s="1">
         <v>2150040</v>
@@ -15466,7 +15457,7 @@
         <v>1150041</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -15484,7 +15475,7 @@
         <v>0</v>
       </c>
       <c r="J297" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="K297" s="1">
         <v>2150041</v>
@@ -15508,7 +15499,7 @@
         <v>1150042</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -15526,7 +15517,7 @@
         <v>0</v>
       </c>
       <c r="J298" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="K298" s="1">
         <v>2150042</v>
@@ -15550,7 +15541,7 @@
         <v>1150043</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -15568,7 +15559,7 @@
         <v>0</v>
       </c>
       <c r="J299" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="K299" s="1">
         <v>2150043</v>
@@ -15592,7 +15583,7 @@
         <v>1150044</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -15610,7 +15601,7 @@
         <v>0</v>
       </c>
       <c r="J300" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="K300" s="1">
         <v>2150044</v>
@@ -15634,7 +15625,7 @@
         <v>1150045</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -15652,7 +15643,7 @@
         <v>0</v>
       </c>
       <c r="J301" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="K301" s="1">
         <v>2150045</v>
@@ -15676,7 +15667,7 @@
         <v>1150046</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -15694,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="J302" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="K302" s="1">
         <v>2150046</v>
@@ -15718,7 +15709,7 @@
         <v>1150047</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -15736,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="J303" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="K303" s="1">
         <v>2150047</v>
@@ -15760,7 +15751,7 @@
         <v>1150048</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -15778,7 +15769,7 @@
         <v>0</v>
       </c>
       <c r="J304" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="K304" s="1">
         <v>2150048</v>
@@ -15802,7 +15793,7 @@
         <v>1150049</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -15820,7 +15811,7 @@
         <v>0</v>
       </c>
       <c r="J305" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="K305" s="1">
         <v>2150049</v>
@@ -15844,7 +15835,7 @@
         <v>1150050</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -15862,7 +15853,7 @@
         <v>0</v>
       </c>
       <c r="J306" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="K306" s="1">
         <v>2150050</v>
@@ -15886,7 +15877,7 @@
         <v>1150051</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -15904,7 +15895,7 @@
         <v>0</v>
       </c>
       <c r="J307" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K307" s="1">
         <v>2150051</v>
@@ -15928,7 +15919,7 @@
         <v>1150052</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -15946,7 +15937,7 @@
         <v>0</v>
       </c>
       <c r="J308" s="1" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="K308" s="1">
         <v>2150052</v>
@@ -15970,7 +15961,7 @@
         <v>1150053</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -15988,7 +15979,7 @@
         <v>0</v>
       </c>
       <c r="J309" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K309" s="1">
         <v>2150053</v>
@@ -16012,7 +16003,7 @@
         <v>1150054</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16030,7 +16021,7 @@
         <v>0</v>
       </c>
       <c r="J310" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="K310" s="1">
         <v>2150054</v>
@@ -16054,7 +16045,7 @@
         <v>1150055</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -16072,7 +16063,7 @@
         <v>0</v>
       </c>
       <c r="J311" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K311" s="1">
         <v>2150055</v>
@@ -16096,7 +16087,7 @@
         <v>1150056</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -16114,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="J312" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="K312" s="1">
         <v>2150056</v>
@@ -16138,7 +16129,7 @@
         <v>1150057</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -16156,7 +16147,7 @@
         <v>0</v>
       </c>
       <c r="J313" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="K313" s="1">
         <v>2150057</v>
@@ -16180,7 +16171,7 @@
         <v>1150058</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -16198,7 +16189,7 @@
         <v>0</v>
       </c>
       <c r="J314" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K314" s="1">
         <v>2150058</v>
@@ -16222,7 +16213,7 @@
         <v>1150059</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -16240,7 +16231,7 @@
         <v>0</v>
       </c>
       <c r="J315" s="1" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="K315" s="1">
         <v>2150059</v>
@@ -16264,7 +16255,7 @@
         <v>1150060</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -16282,7 +16273,7 @@
         <v>0</v>
       </c>
       <c r="J316" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="K316" s="1">
         <v>2150060</v>
@@ -16306,7 +16297,7 @@
         <v>1150061</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -16324,7 +16315,7 @@
         <v>0</v>
       </c>
       <c r="J317" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K317" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="524">
   <si>
     <t>道具ID</t>
   </si>
@@ -544,6 +544,9 @@
     <t>赛季币</t>
   </si>
   <si>
+    <t>daoju_sjb.png</t>
+  </si>
+  <si>
     <t>在赛季玩法中使用的货币</t>
   </si>
   <si>
@@ -940,6 +943,9 @@
     <t>研究点</t>
   </si>
   <si>
+    <t>daoju_yjy.png</t>
+  </si>
+  <si>
     <t>升级游戏特殊词条</t>
   </si>
   <si>
@@ -1051,61 +1057,61 @@
     <t>专属研究点</t>
   </si>
   <si>
-    <t>yjy_tb_cjmx.png</t>
+    <t>daoju_cjmx.png</t>
   </si>
   <si>
     <t>升级超级明星游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_smfy.png</t>
+    <t>daoju_smfy.png</t>
   </si>
   <si>
     <t>升级神马飞扬游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_hhsc.png</t>
+    <t>daoju_hhsc.png</t>
   </si>
   <si>
     <t>升级虎虎生财游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_ajyh.png</t>
+    <t>daoju_ajyh.png</t>
   </si>
   <si>
     <t>升级埃及延后游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_jszc.png</t>
+    <t>daoju_jszc.png</t>
   </si>
   <si>
     <t>升级金蛇招财游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_jqt.png</t>
+    <t>daoju_jqt.png</t>
   </si>
   <si>
     <t>升级金钱兔游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_mjhl.png</t>
+    <t>daoju_mjhl.png</t>
   </si>
   <si>
     <t>升级麻将胡了游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_nqct.png</t>
+    <t>daoju_nqct.png</t>
   </si>
   <si>
     <t>升级牛气冲天游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_sshh.png</t>
+    <t>daoju_ssff.png</t>
   </si>
   <si>
     <t>升级鼠鼠福福游戏特殊词条</t>
   </si>
   <si>
-    <t>yjy_tb_sdkhy.png</t>
+    <t>daoju_sdkhy.png</t>
   </si>
   <si>
     <t>升级圣诞狂欢夜游戏特殊词条</t>
@@ -2151,12 +2157,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3576,6 +3582,9 @@
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L8" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="M8" s="1">
         <v>2960000</v>
       </c>
@@ -3583,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R8" s="1">
         <v>-1</v>
@@ -3600,13 +3609,13 @@
         <v>1020001</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
@@ -3618,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M9" s="1">
         <v>2020001</v>
@@ -3627,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R9" s="1">
         <v>999999</v>
@@ -3644,13 +3653,13 @@
         <v>1202501</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
@@ -3662,7 +3671,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M10" s="1">
         <v>2022501</v>
@@ -3671,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R10" s="1">
         <v>999999</v>
@@ -3691,13 +3700,13 @@
         <v>1202502</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
@@ -3709,7 +3718,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M11" s="1">
         <v>2022502</v>
@@ -3718,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R11" s="1">
         <v>999999</v>
@@ -3738,13 +3747,13 @@
         <v>1202503</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
@@ -3756,7 +3765,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M12" s="1">
         <v>2022503</v>
@@ -3765,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R12" s="1">
         <v>999999</v>
@@ -3785,13 +3794,13 @@
         <v>1100301</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="1">
@@ -3804,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M13" s="1">
         <v>2010301</v>
@@ -3813,13 +3822,13 @@
         <v>0</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R13" s="1">
         <v>999999</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V13" s="1">
         <v>0.099</v>
@@ -3836,13 +3845,13 @@
         <v>1100302</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="1">
@@ -3855,7 +3864,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M14" s="1">
         <v>2010302</v>
@@ -3864,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R14" s="1">
         <v>999999</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V14" s="1">
         <f>V13*2</f>
@@ -3888,13 +3897,13 @@
         <v>1100303</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="1">
@@ -3907,7 +3916,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M15" s="1">
         <v>2010303</v>
@@ -3916,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R15" s="1">
         <v>999999</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V15" s="1">
         <f>V13*6</f>
@@ -3940,13 +3949,13 @@
         <v>1100304</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="1">
@@ -3959,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M16" s="1">
         <v>2010304</v>
@@ -3968,13 +3977,13 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R16" s="1">
         <v>999999</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V16" s="1">
         <f>V13*8</f>
@@ -3992,13 +4001,13 @@
         <v>1100305</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="1">
@@ -4011,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M17" s="1">
         <v>2010305</v>
@@ -4020,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R17" s="1">
         <v>999999</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V17" s="1">
         <f>V13*10</f>
@@ -4044,13 +4053,13 @@
         <v>1100401</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="2">
@@ -4063,7 +4072,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M18" s="2">
         <v>2010401</v>
@@ -4072,14 +4081,14 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R18" s="2">
         <v>999999</v>
       </c>
       <c r="S18" s="11"/>
       <c r="T18" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" spans="1:22">
@@ -4093,13 +4102,13 @@
         <v>1100501</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="2">
@@ -4112,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M19" s="2">
         <v>2010501</v>
@@ -4121,14 +4130,14 @@
         <v>0</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R19" s="2">
         <v>999999</v>
       </c>
       <c r="S19" s="11"/>
       <c r="T19" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" spans="1:22">
@@ -4142,13 +4151,13 @@
         <v>1100601</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="2">
@@ -4161,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M20" s="2">
         <v>2010601</v>
@@ -4170,14 +4179,14 @@
         <v>0</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R20" s="2">
         <v>999999</v>
       </c>
       <c r="S20" s="11"/>
       <c r="T20" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4191,13 +4200,13 @@
         <v>1301001</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I21" s="1">
         <v>1</v>
@@ -4209,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M21" s="1">
         <v>2031001</v>
@@ -4235,13 +4244,13 @@
         <v>1301002</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
@@ -4253,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M22" s="1">
         <v>2031002</v>
@@ -4279,13 +4288,13 @@
         <v>1301201</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I23" s="1">
         <v>1</v>
@@ -4297,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M23" s="1">
         <v>2031201</v>
@@ -4323,13 +4332,13 @@
         <v>1301202</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
@@ -4341,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M24" s="1">
         <v>2031202</v>
@@ -4367,13 +4376,13 @@
         <v>101801</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I25" s="1">
         <v>1</v>
@@ -4385,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M25" s="1">
         <v>201801</v>
@@ -4411,13 +4420,13 @@
         <v>101802</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
@@ -4429,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M26" s="1">
         <v>201802</v>
@@ -4455,13 +4464,13 @@
         <v>1201401</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I27" s="1">
         <v>1</v>
@@ -4473,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M27" s="1">
         <v>2021401</v>
@@ -4499,25 +4508,25 @@
         <v>1201402</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1</v>
-      </c>
-      <c r="J28" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="M28" s="1">
         <v>2021402</v>
@@ -4543,13 +4552,13 @@
         <v>103001</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="1">
@@ -4562,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M29" s="1">
         <v>2031600</v>
@@ -4588,13 +4597,13 @@
         <v>103002</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I30" s="1">
         <v>1</v>
@@ -4606,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M30" s="1">
         <v>2031601</v>
@@ -4632,13 +4641,13 @@
         <v>103003</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I31" s="1">
         <v>1</v>
@@ -4650,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M31" s="1">
         <v>2031602</v>
@@ -4676,13 +4685,13 @@
         <v>104002</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -4694,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M32" s="1">
         <v>2031801</v>
@@ -4720,13 +4729,13 @@
         <v>104003</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I33" s="1">
         <v>1</v>
@@ -4738,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M33" s="1">
         <v>2031802</v>
@@ -4764,13 +4773,13 @@
         <v>105002</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
@@ -4782,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M34" s="1">
         <v>2032001</v>
@@ -4808,13 +4817,13 @@
         <v>105003</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I35" s="1">
         <v>1</v>
@@ -4826,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M35" s="1">
         <v>2032002</v>
@@ -4852,13 +4861,13 @@
         <v>106002</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E36" s="1">
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
@@ -4870,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M36" s="1">
         <v>2032201</v>
@@ -4896,13 +4905,13 @@
         <v>106003</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
@@ -4914,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M37" s="1">
         <v>2032202</v>
@@ -4940,13 +4949,13 @@
         <v>1202504</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I38" s="1">
         <v>1</v>
@@ -4958,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M38" s="1">
         <v>2022504</v>
@@ -4967,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R38" s="1">
         <v>999999999</v>
@@ -4981,13 +4990,13 @@
         <v>1023001</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I39" s="1">
         <v>2</v>
@@ -4999,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M39" s="1">
         <v>2023001</v>
@@ -5008,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R39" s="1">
         <v>999999</v>
@@ -5025,13 +5034,13 @@
         <v>1023002</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I40" s="1">
         <v>3</v>
@@ -5043,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M40" s="1">
         <v>2023002</v>
@@ -5052,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R40" s="1">
         <v>999999</v>
@@ -5069,13 +5078,13 @@
         <v>1023003</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I41" s="1">
         <v>4</v>
@@ -5087,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M41" s="1">
         <v>2023003</v>
@@ -5096,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R41" s="1">
         <v>999999</v>
@@ -5113,13 +5122,13 @@
         <v>1023004</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I42" s="1">
         <v>5</v>
@@ -5131,7 +5140,7 @@
         <v>1</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M42" s="1">
         <v>2023004</v>
@@ -5140,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R42" s="1">
         <v>999999</v>
@@ -5157,13 +5166,13 @@
         <v>1023005</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I43" s="1">
         <v>6</v>
@@ -5175,7 +5184,7 @@
         <v>1</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M43" s="1">
         <v>2023005</v>
@@ -5184,7 +5193,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R43" s="1">
         <v>999999</v>
@@ -5201,13 +5210,13 @@
         <v>1023101</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I44" s="1">
         <v>2</v>
@@ -5219,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M44" s="1">
         <v>2023101</v>
@@ -5228,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R44" s="1">
         <v>999999</v>
@@ -5245,13 +5254,13 @@
         <v>1023102</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I45" s="1">
         <v>3</v>
@@ -5263,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M45" s="1">
         <v>2023102</v>
@@ -5272,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R45" s="1">
         <v>999999</v>
@@ -5289,13 +5298,13 @@
         <v>1023103</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I46" s="1">
         <v>4</v>
@@ -5307,7 +5316,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M46" s="1">
         <v>2023103</v>
@@ -5316,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R46" s="1">
         <v>999999</v>
@@ -5333,13 +5342,13 @@
         <v>1023104</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I47" s="1">
         <v>5</v>
@@ -5351,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M47" s="1">
         <v>2023104</v>
@@ -5360,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R47" s="1">
         <v>999999</v>
@@ -5377,13 +5386,13 @@
         <v>1023105</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I48" s="1">
         <v>6</v>
@@ -5395,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M48" s="1">
         <v>2023105</v>
@@ -5404,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R48" s="1">
         <v>999999</v>
@@ -5421,13 +5430,13 @@
         <v>1023201</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I49" s="1">
         <v>2</v>
@@ -5439,7 +5448,7 @@
         <v>1</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M49" s="1">
         <v>2023201</v>
@@ -5448,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R49" s="1">
         <v>999999</v>
@@ -5465,13 +5474,13 @@
         <v>1023202</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I50" s="1">
         <v>3</v>
@@ -5483,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M50" s="1">
         <v>2023202</v>
@@ -5492,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R50" s="1">
         <v>999999</v>
@@ -5509,13 +5518,13 @@
         <v>1023203</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I51" s="1">
         <v>4</v>
@@ -5527,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M51" s="1">
         <v>2023203</v>
@@ -5536,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R51" s="1">
         <v>999999</v>
@@ -5553,13 +5562,13 @@
         <v>1023204</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I52" s="1">
         <v>5</v>
@@ -5571,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M52" s="1">
         <v>2023204</v>
@@ -5580,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R52" s="1">
         <v>999999</v>
@@ -5597,13 +5606,13 @@
         <v>1023205</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I53" s="1">
         <v>6</v>
@@ -5615,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M53" s="1">
         <v>2023205</v>
@@ -5624,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R53" s="1">
         <v>999999</v>
@@ -5641,13 +5650,13 @@
         <v>1023301</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I54" s="1">
         <v>2</v>
@@ -5659,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M54" s="1">
         <v>2023301</v>
@@ -5668,7 +5677,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R54" s="1">
         <v>999999</v>
@@ -5685,13 +5694,13 @@
         <v>1023302</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I55" s="1">
         <v>3</v>
@@ -5703,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M55" s="1">
         <v>2023302</v>
@@ -5712,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R55" s="1">
         <v>999999</v>
@@ -5729,13 +5738,13 @@
         <v>1023303</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I56" s="1">
         <v>4</v>
@@ -5747,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M56" s="1">
         <v>2023303</v>
@@ -5756,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R56" s="1">
         <v>999999</v>
@@ -5773,13 +5782,13 @@
         <v>1023304</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I57" s="1">
         <v>5</v>
@@ -5791,7 +5800,7 @@
         <v>1</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M57" s="1">
         <v>2023304</v>
@@ -5800,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R57" s="1">
         <v>999999</v>
@@ -5817,13 +5826,13 @@
         <v>1023305</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I58" s="1">
         <v>6</v>
@@ -5835,7 +5844,7 @@
         <v>1</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M58" s="1">
         <v>2023305</v>
@@ -5844,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R58" s="1">
         <v>999999</v>
@@ -5861,13 +5870,13 @@
         <v>1023401</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I59" s="1">
         <v>2</v>
@@ -5879,7 +5888,7 @@
         <v>1</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M59" s="1">
         <v>2023401</v>
@@ -5888,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R59" s="1">
         <v>999999</v>
@@ -5905,13 +5914,13 @@
         <v>1023402</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I60" s="1">
         <v>3</v>
@@ -5923,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M60" s="1">
         <v>2023402</v>
@@ -5932,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R60" s="1">
         <v>999999</v>
@@ -5949,13 +5958,13 @@
         <v>1023403</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I61" s="1">
         <v>4</v>
@@ -5967,7 +5976,7 @@
         <v>1</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M61" s="1">
         <v>2023403</v>
@@ -5976,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R61" s="1">
         <v>999999</v>
@@ -5993,13 +6002,13 @@
         <v>1023404</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I62" s="1">
         <v>5</v>
@@ -6011,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M62" s="1">
         <v>2023404</v>
@@ -6020,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R62" s="1">
         <v>999999</v>
@@ -6037,13 +6046,13 @@
         <v>1023405</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I63" s="1">
         <v>6</v>
@@ -6055,7 +6064,7 @@
         <v>1</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M63" s="1">
         <v>2023405</v>
@@ -6064,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="R63" s="1">
         <v>999999</v>
@@ -6081,13 +6090,13 @@
         <v>1024001</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="1">
@@ -6100,7 +6109,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M64" s="1">
         <v>2024001</v>
@@ -6109,7 +6118,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R64" s="1">
         <v>-1</v>
@@ -6123,13 +6132,13 @@
         <v>1024003</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="1">
@@ -6142,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M65" s="1">
         <v>2024003</v>
@@ -6151,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="R65" s="1">
         <v>-1</v>
@@ -6165,13 +6174,13 @@
         <v>1024005</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -6186,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="M66" s="1">
         <v>2024005</v>
@@ -6195,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R66" s="1">
         <v>-1</v>
@@ -6209,13 +6218,13 @@
         <v>1024007</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="1">
@@ -6228,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M67" s="1">
         <v>2024007</v>
@@ -6237,7 +6246,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="R67" s="1">
         <v>999999999</v>
@@ -6251,13 +6260,13 @@
         <v>1024008</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I68" s="1">
         <v>1</v>
@@ -6269,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M68" s="1">
         <v>2024008</v>
@@ -6278,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R68" s="1">
         <v>999999</v>
@@ -6292,13 +6301,13 @@
         <v>1024009</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I69" s="1">
         <v>1</v>
@@ -6310,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M69" s="1">
         <v>2024009</v>
@@ -6319,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R69" s="1">
         <v>999999</v>
@@ -6333,13 +6342,13 @@
         <v>1024010</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I70" s="1">
         <v>1</v>
@@ -6351,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M70" s="1">
         <v>2024010</v>
@@ -6360,7 +6369,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="R70" s="1">
         <v>999999</v>
@@ -6374,13 +6383,13 @@
         <v>1024011</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I71" s="1">
         <v>1</v>
@@ -6392,7 +6401,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M71" s="1">
         <v>2024011</v>
@@ -6401,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="R71" s="1">
         <v>-1</v>
@@ -6415,13 +6424,13 @@
         <v>1024012</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I72" s="1">
         <v>1</v>
@@ -6442,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="R72" s="1">
         <v>-1</v>
@@ -6456,13 +6465,13 @@
         <v>1024013</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I73" s="1">
         <v>1</v>
@@ -6474,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M73" s="1">
         <v>2024013</v>
@@ -6483,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="R73" s="1">
         <v>999999</v>
@@ -6497,13 +6506,13 @@
         <v>1024014</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I74" s="1">
         <v>1</v>
@@ -6515,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M74" s="1">
         <v>2024014</v>
@@ -6524,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R74" s="1">
         <v>999999</v>
@@ -6538,13 +6547,13 @@
         <v>1024015</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I75" s="1">
         <v>1</v>
@@ -6556,7 +6565,7 @@
         <v>1</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M75" s="1">
         <v>2024015</v>
@@ -6565,13 +6574,13 @@
         <v>0</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="R75" s="1">
         <v>999999</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -6582,13 +6591,13 @@
         <v>1024016</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I76" s="1">
         <v>1</v>
@@ -6600,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M76" s="1">
         <v>2024016</v>
@@ -6609,13 +6618,13 @@
         <v>0</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="R76" s="1">
         <v>999999</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -6626,13 +6635,13 @@
         <v>1024017</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I77" s="1">
         <v>1</v>
@@ -6644,7 +6653,7 @@
         <v>1</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M77" s="1">
         <v>2024017</v>
@@ -6653,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="R77" s="1">
         <v>999999</v>
@@ -6667,13 +6676,13 @@
         <v>1024018</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I78" s="1">
         <v>1</v>
@@ -6685,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M78" s="1">
         <v>2024018</v>
@@ -6694,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="R78" s="1">
         <v>-1</v>
@@ -6708,25 +6717,25 @@
         <v>1024019</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E79" s="1">
+        <v>2</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1</v>
+      </c>
+      <c r="J79" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="E79" s="1">
-        <v>2</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I79" s="1">
-        <v>1</v>
-      </c>
-      <c r="J79" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="M79" s="1">
         <v>2024019</v>
@@ -6735,7 +6744,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -6746,13 +6755,13 @@
         <v>1024020</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I80" s="1">
         <v>1</v>
@@ -6764,7 +6773,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M80" s="1">
         <v>2024020</v>
@@ -6773,7 +6782,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -6784,13 +6793,13 @@
         <v>1024021</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I81" s="1">
         <v>1</v>
@@ -6802,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M81" s="1">
         <v>2024021</v>
@@ -6811,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -6822,13 +6831,13 @@
         <v>1024022</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I82" s="1">
         <v>1</v>
@@ -6840,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M82" s="1">
         <v>2024022</v>
@@ -6849,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -6860,13 +6869,13 @@
         <v>1024023</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I83" s="1">
         <v>1</v>
@@ -6878,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M83" s="1">
         <v>2024023</v>
@@ -6887,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" ht="17.25" spans="1:18">
@@ -6898,13 +6907,13 @@
         <v>1024024</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G84" s="1">
         <v>1</v>
@@ -6922,7 +6931,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M84" s="1">
         <v>2024024</v>
@@ -6931,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="R84" s="1">
         <v>999999</v>
@@ -6945,13 +6954,13 @@
         <v>1024024</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G85" s="1">
         <v>1</v>
@@ -6969,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M85" s="1">
         <v>2024025</v>
@@ -6978,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R85" s="1">
         <v>999999</v>
@@ -6992,13 +7001,13 @@
         <v>1024024</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G86" s="1">
         <v>1</v>
@@ -7016,7 +7025,7 @@
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M86" s="1">
         <v>2024026</v>
@@ -7025,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="R86" s="1">
         <v>999999</v>
@@ -7039,13 +7048,13 @@
         <v>1024024</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G87" s="1">
         <v>1</v>
@@ -7063,7 +7072,7 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M87" s="1">
         <v>2024027</v>
@@ -7072,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="R87" s="1">
         <v>999999</v>
@@ -7086,13 +7095,13 @@
         <v>1024024</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G88" s="1">
         <v>1</v>
@@ -7110,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M88" s="1">
         <v>2024028</v>
@@ -7119,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="R88" s="1">
         <v>999999</v>
@@ -7133,13 +7142,13 @@
         <v>1024024</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G89" s="1">
         <v>1</v>
@@ -7157,7 +7166,7 @@
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M89" s="1">
         <v>2024029</v>
@@ -7166,7 +7175,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="R89" s="1">
         <v>999999</v>
@@ -7180,13 +7189,13 @@
         <v>1024024</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G90" s="1">
         <v>1</v>
@@ -7204,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M90" s="1">
         <v>2024030</v>
@@ -7213,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R90" s="1">
         <v>999999</v>
@@ -7227,13 +7236,13 @@
         <v>1024024</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G91" s="1">
         <v>1</v>
@@ -7251,7 +7260,7 @@
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M91" s="1">
         <v>2024031</v>
@@ -7260,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R91" s="1">
         <v>999999</v>
@@ -7274,13 +7283,13 @@
         <v>1024024</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G92" s="1">
         <v>1</v>
@@ -7298,7 +7307,7 @@
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M92" s="1">
         <v>2024032</v>
@@ -7307,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="R92" s="1">
         <v>999999</v>
@@ -7321,13 +7330,13 @@
         <v>1024024</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G93" s="1">
         <v>1</v>
@@ -7345,7 +7354,7 @@
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M93" s="1">
         <v>2024033</v>
@@ -7354,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="R93" s="1">
         <v>999999</v>
@@ -7368,13 +7377,13 @@
         <v>1024025</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I94" s="1">
         <v>1</v>
@@ -7392,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="R94" s="1">
         <v>999999</v>
@@ -7406,13 +7415,13 @@
         <v>1024026</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I95" s="1">
         <v>1</v>
@@ -7430,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="R95" s="1">
         <v>999999</v>
@@ -7444,13 +7453,13 @@
         <v>1024027</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I96" s="1">
         <v>1</v>
@@ -7468,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="R96" s="1">
         <v>999999</v>
@@ -7482,13 +7491,13 @@
         <v>1024028</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I97" s="1">
         <v>1</v>
@@ -7506,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R97" s="1">
         <v>999999</v>
@@ -7520,13 +7529,13 @@
         <v>1024029</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I98" s="1">
         <v>1</v>
@@ -7544,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="R98" s="1">
         <v>999999</v>
@@ -7558,13 +7567,13 @@
         <v>1024030</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I99" s="1">
         <v>1</v>
@@ -7582,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="R99" s="1">
         <v>999999</v>
@@ -7596,13 +7605,13 @@
         <v>1024024</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G100" s="1">
         <v>1</v>
@@ -7620,7 +7629,7 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M100" s="1">
         <v>2024040</v>
@@ -7629,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="R100" s="1">
         <v>999999</v>
@@ -7643,13 +7652,13 @@
         <v>1025101</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E101" s="1">
         <v>2</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I101" s="1">
         <v>1</v>
@@ -7661,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M101" s="1">
         <v>2025101</v>
@@ -7670,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="R101" s="1">
         <v>-1</v>
@@ -7684,13 +7693,13 @@
         <v>1025102</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E102" s="1">
         <v>2</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I102" s="1">
         <v>1</v>
@@ -7702,7 +7711,7 @@
         <v>0</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M102" s="1">
         <v>2025102</v>
@@ -7711,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R102" s="1">
         <v>-1</v>
@@ -7725,13 +7734,13 @@
         <v>1025103</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E103" s="1">
         <v>2</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I103" s="1">
         <v>1</v>
@@ -7743,7 +7752,7 @@
         <v>0</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M103" s="1">
         <v>2025103</v>
@@ -7752,7 +7761,7 @@
         <v>0</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="R103" s="1">
         <v>-1</v>
@@ -7766,13 +7775,13 @@
         <v>1025104</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E104" s="1">
         <v>2</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I104" s="1">
         <v>1</v>
@@ -7784,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M104" s="1">
         <v>2025104</v>
@@ -7793,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="R104" s="1">
         <v>-1</v>
@@ -7807,13 +7816,13 @@
         <v>1025105</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E105" s="1">
         <v>2</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I105" s="1">
         <v>1</v>
@@ -7825,7 +7834,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M105" s="1">
         <v>2025105</v>
@@ -7834,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="R105" s="1">
         <v>-1</v>
@@ -7848,13 +7857,13 @@
         <v>1025106</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E106" s="1">
         <v>2</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I106" s="1">
         <v>1</v>
@@ -7866,7 +7875,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M106" s="1">
         <v>2025106</v>
@@ -7875,7 +7884,7 @@
         <v>0</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="R106" s="1">
         <v>-1</v>
@@ -7889,13 +7898,13 @@
         <v>1025201</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E107" s="1">
         <v>2</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I107" s="1">
         <v>2</v>
@@ -7907,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M107" s="1">
         <v>2025201</v>
@@ -7916,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="R107" s="1">
         <v>-1</v>
@@ -7930,13 +7939,13 @@
         <v>1025202</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E108" s="1">
         <v>2</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I108" s="1">
         <v>2</v>
@@ -7948,7 +7957,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M108" s="1">
         <v>2025202</v>
@@ -7957,7 +7966,7 @@
         <v>0</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="R108" s="1">
         <v>-1</v>
@@ -7971,13 +7980,13 @@
         <v>1025203</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E109" s="1">
         <v>2</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I109" s="1">
         <v>2</v>
@@ -7989,7 +7998,7 @@
         <v>0</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M109" s="1">
         <v>2025203</v>
@@ -7998,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R109" s="1">
         <v>-1</v>
@@ -8012,13 +8021,13 @@
         <v>1025204</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E110" s="1">
         <v>2</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I110" s="1">
         <v>2</v>
@@ -8030,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M110" s="1">
         <v>2025204</v>
@@ -8039,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="R110" s="1">
         <v>-1</v>
@@ -8053,13 +8062,13 @@
         <v>1025205</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E111" s="1">
         <v>2</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I111" s="1">
         <v>2</v>
@@ -8071,7 +8080,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M111" s="1">
         <v>2025205</v>
@@ -8080,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="R111" s="1">
         <v>-1</v>
@@ -8094,13 +8103,13 @@
         <v>1025206</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E112" s="1">
         <v>2</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I112" s="1">
         <v>2</v>
@@ -8112,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M112" s="1">
         <v>2025206</v>
@@ -8121,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="R112" s="1">
         <v>-1</v>
@@ -8135,13 +8144,13 @@
         <v>1025301</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E113" s="1">
         <v>2</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I113" s="1">
         <v>3</v>
@@ -8153,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M113" s="1">
         <v>2025301</v>
@@ -8162,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="O113" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="R113" s="1">
         <v>-1</v>
@@ -8176,13 +8185,13 @@
         <v>1025302</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E114" s="1">
         <v>2</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I114" s="1">
         <v>3</v>
@@ -8194,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M114" s="1">
         <v>2025302</v>
@@ -8203,7 +8212,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="R114" s="1">
         <v>-1</v>
@@ -8217,13 +8226,13 @@
         <v>1025303</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E115" s="1">
         <v>2</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I115" s="1">
         <v>3</v>
@@ -8235,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M115" s="1">
         <v>2025303</v>
@@ -8244,7 +8253,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="R115" s="1">
         <v>-1</v>
@@ -8258,13 +8267,13 @@
         <v>1025304</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E116" s="1">
         <v>2</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I116" s="1">
         <v>3</v>
@@ -8276,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M116" s="1">
         <v>2025304</v>
@@ -8285,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="O116" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="R116" s="1">
         <v>-1</v>
@@ -8299,13 +8308,13 @@
         <v>1025305</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E117" s="1">
         <v>2</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I117" s="1">
         <v>3</v>
@@ -8317,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M117" s="1">
         <v>2025305</v>
@@ -8326,7 +8335,7 @@
         <v>0</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="R117" s="1">
         <v>-1</v>
@@ -8340,13 +8349,13 @@
         <v>1025306</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E118" s="1">
         <v>2</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I118" s="1">
         <v>3</v>
@@ -8358,7 +8367,7 @@
         <v>0</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M118" s="1">
         <v>2025306</v>
@@ -8367,7 +8376,7 @@
         <v>0</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="R118" s="1">
         <v>-1</v>
@@ -8381,13 +8390,13 @@
         <v>1025401</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E119" s="1">
         <v>2</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I119" s="1">
         <v>4</v>
@@ -8399,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M119" s="1">
         <v>2025401</v>
@@ -8408,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="O119" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="R119" s="1">
         <v>-1</v>
@@ -8422,13 +8431,13 @@
         <v>1025402</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E120" s="1">
         <v>2</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I120" s="1">
         <v>4</v>
@@ -8440,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M120" s="1">
         <v>2025402</v>
@@ -8449,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="R120" s="1">
         <v>-1</v>
@@ -8463,13 +8472,13 @@
         <v>1025403</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E121" s="1">
         <v>2</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I121" s="1">
         <v>4</v>
@@ -8481,7 +8490,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M121" s="1">
         <v>2025403</v>
@@ -8490,7 +8499,7 @@
         <v>0</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="R121" s="1">
         <v>-1</v>
@@ -8504,13 +8513,13 @@
         <v>1025404</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E122" s="1">
         <v>2</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I122" s="1">
         <v>4</v>
@@ -8522,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M122" s="1">
         <v>2025404</v>
@@ -8531,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="R122" s="1">
         <v>-1</v>
@@ -8545,13 +8554,13 @@
         <v>1025405</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E123" s="1">
         <v>2</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I123" s="1">
         <v>4</v>
@@ -8563,7 +8572,7 @@
         <v>0</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M123" s="1">
         <v>2025405</v>
@@ -8572,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R123" s="1">
         <v>-1</v>
@@ -8586,13 +8595,13 @@
         <v>1025406</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E124" s="1">
         <v>2</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I124" s="1">
         <v>4</v>
@@ -8604,7 +8613,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M124" s="1">
         <v>2025406</v>
@@ -8613,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R124" s="1">
         <v>-1</v>
@@ -8627,13 +8636,13 @@
         <v>1025501</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E125" s="1">
         <v>2</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I125" s="1">
         <v>5</v>
@@ -8645,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M125" s="1">
         <v>2025501</v>
@@ -8654,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="O125" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="R125" s="1">
         <v>-1</v>
@@ -8668,13 +8677,13 @@
         <v>1025502</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E126" s="1">
         <v>2</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I126" s="1">
         <v>5</v>
@@ -8686,7 +8695,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M126" s="1">
         <v>2025502</v>
@@ -8695,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="O126" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="R126" s="1">
         <v>-1</v>
@@ -8709,13 +8718,13 @@
         <v>1025503</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E127" s="1">
         <v>2</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I127" s="1">
         <v>5</v>
@@ -8727,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M127" s="1">
         <v>2025503</v>
@@ -8736,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="O127" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="R127" s="1">
         <v>-1</v>
@@ -8750,13 +8759,13 @@
         <v>1025504</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E128" s="1">
         <v>2</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I128" s="1">
         <v>5</v>
@@ -8768,7 +8777,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M128" s="1">
         <v>2025504</v>
@@ -8777,7 +8786,7 @@
         <v>0</v>
       </c>
       <c r="O128" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="R128" s="1">
         <v>-1</v>
@@ -8791,13 +8800,13 @@
         <v>1025505</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E129" s="1">
         <v>2</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I129" s="1">
         <v>5</v>
@@ -8809,7 +8818,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M129" s="1">
         <v>2025505</v>
@@ -8818,7 +8827,7 @@
         <v>0</v>
       </c>
       <c r="O129" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="R129" s="1">
         <v>-1</v>
@@ -8832,13 +8841,13 @@
         <v>1025506</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E130" s="1">
         <v>2</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I130" s="1">
         <v>5</v>
@@ -8850,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M130" s="1">
         <v>2025506</v>
@@ -8859,7 +8868,7 @@
         <v>0</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="R130" s="1">
         <v>-1</v>
@@ -8880,7 +8889,7 @@
         <v>2</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I131" s="1">
         <v>1</v>
@@ -8892,7 +8901,7 @@
         <v>1</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M131" s="1">
         <v>2125101</v>
@@ -8923,7 +8932,7 @@
         <v>2</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I132" s="1">
         <v>1</v>
@@ -8935,7 +8944,7 @@
         <v>1</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M132" s="1">
         <v>2125102</v>
@@ -8966,7 +8975,7 @@
         <v>2</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I133" s="1">
         <v>1</v>
@@ -8978,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M133" s="1">
         <v>2125103</v>
@@ -9009,7 +9018,7 @@
         <v>2</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I134" s="1">
         <v>1</v>
@@ -9021,7 +9030,7 @@
         <v>1</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M134" s="1">
         <v>2125104</v>
@@ -9052,7 +9061,7 @@
         <v>2</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I135" s="1">
         <v>1</v>
@@ -9064,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M135" s="1">
         <v>2125105</v>
@@ -9095,7 +9104,7 @@
         <v>2</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I136" s="1">
         <v>1</v>
@@ -9107,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M136" s="1">
         <v>2125106</v>
@@ -9138,7 +9147,7 @@
         <v>2</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I137" s="1">
         <v>2</v>
@@ -9150,7 +9159,7 @@
         <v>1</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M137" s="1">
         <v>2125201</v>
@@ -9181,7 +9190,7 @@
         <v>2</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I138" s="1">
         <v>2</v>
@@ -9193,7 +9202,7 @@
         <v>1</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M138" s="1">
         <v>2125202</v>
@@ -9224,7 +9233,7 @@
         <v>2</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I139" s="1">
         <v>2</v>
@@ -9236,7 +9245,7 @@
         <v>1</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M139" s="1">
         <v>2125203</v>
@@ -9267,7 +9276,7 @@
         <v>2</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I140" s="1">
         <v>2</v>
@@ -9279,7 +9288,7 @@
         <v>1</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M140" s="1">
         <v>2125204</v>
@@ -9310,7 +9319,7 @@
         <v>2</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I141" s="1">
         <v>2</v>
@@ -9322,7 +9331,7 @@
         <v>1</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M141" s="1">
         <v>2125205</v>
@@ -9353,7 +9362,7 @@
         <v>2</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I142" s="1">
         <v>2</v>
@@ -9365,7 +9374,7 @@
         <v>1</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M142" s="1">
         <v>2125206</v>
@@ -9396,7 +9405,7 @@
         <v>2</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I143" s="1">
         <v>3</v>
@@ -9408,7 +9417,7 @@
         <v>1</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M143" s="1">
         <v>2125301</v>
@@ -9439,7 +9448,7 @@
         <v>2</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I144" s="1">
         <v>3</v>
@@ -9451,7 +9460,7 @@
         <v>1</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M144" s="1">
         <v>2125302</v>
@@ -9482,7 +9491,7 @@
         <v>2</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I145" s="1">
         <v>3</v>
@@ -9494,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M145" s="1">
         <v>2125303</v>
@@ -9525,7 +9534,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I146" s="1">
         <v>3</v>
@@ -9537,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M146" s="1">
         <v>2125304</v>
@@ -9568,7 +9577,7 @@
         <v>2</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I147" s="1">
         <v>3</v>
@@ -9580,7 +9589,7 @@
         <v>1</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M147" s="1">
         <v>2125305</v>
@@ -9611,7 +9620,7 @@
         <v>2</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I148" s="1">
         <v>3</v>
@@ -9623,7 +9632,7 @@
         <v>1</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M148" s="1">
         <v>2125306</v>
@@ -9654,7 +9663,7 @@
         <v>2</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I149" s="1">
         <v>4</v>
@@ -9666,7 +9675,7 @@
         <v>1</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M149" s="1">
         <v>2125401</v>
@@ -9697,7 +9706,7 @@
         <v>2</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I150" s="1">
         <v>4</v>
@@ -9709,7 +9718,7 @@
         <v>1</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M150" s="1">
         <v>2125402</v>
@@ -9740,7 +9749,7 @@
         <v>2</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I151" s="1">
         <v>4</v>
@@ -9752,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M151" s="1">
         <v>2125403</v>
@@ -9783,7 +9792,7 @@
         <v>2</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I152" s="1">
         <v>4</v>
@@ -9795,7 +9804,7 @@
         <v>1</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M152" s="1">
         <v>2125404</v>
@@ -9826,7 +9835,7 @@
         <v>2</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I153" s="1">
         <v>4</v>
@@ -9838,7 +9847,7 @@
         <v>1</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M153" s="1">
         <v>2125405</v>
@@ -9869,7 +9878,7 @@
         <v>2</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I154" s="1">
         <v>4</v>
@@ -9881,7 +9890,7 @@
         <v>1</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M154" s="1">
         <v>2125406</v>
@@ -9912,7 +9921,7 @@
         <v>2</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I155" s="1">
         <v>5</v>
@@ -9924,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M155" s="1">
         <v>2125501</v>
@@ -9955,7 +9964,7 @@
         <v>2</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I156" s="1">
         <v>5</v>
@@ -9967,7 +9976,7 @@
         <v>1</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M156" s="1">
         <v>2125502</v>
@@ -9998,7 +10007,7 @@
         <v>2</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I157" s="1">
         <v>5</v>
@@ -10010,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M157" s="1">
         <v>2125503</v>
@@ -10041,7 +10050,7 @@
         <v>2</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I158" s="1">
         <v>5</v>
@@ -10053,7 +10062,7 @@
         <v>1</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M158" s="1">
         <v>2125504</v>
@@ -10084,7 +10093,7 @@
         <v>2</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I159" s="1">
         <v>5</v>
@@ -10096,7 +10105,7 @@
         <v>1</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M159" s="1">
         <v>2125505</v>
@@ -10127,7 +10136,7 @@
         <v>2</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I160" s="1">
         <v>5</v>
@@ -10139,7 +10148,7 @@
         <v>1</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M160" s="1">
         <v>2125506</v>
@@ -10163,13 +10172,13 @@
         <v>1026001</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I161" s="1">
         <v>1</v>
@@ -10181,7 +10190,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M161" s="1">
         <v>2026001</v>
@@ -10190,7 +10199,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R161" s="1">
         <v>-1</v>
@@ -10204,13 +10213,13 @@
         <v>1026002</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I162" s="1">
         <v>1</v>
@@ -10222,7 +10231,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M162" s="1">
         <v>2026002</v>
@@ -10231,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="R162" s="1">
         <v>-1</v>
@@ -10245,13 +10254,13 @@
         <v>1026101</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I163" s="1">
         <v>2</v>
@@ -10263,7 +10272,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M163" s="1">
         <v>2026101</v>
@@ -10272,7 +10281,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="R163" s="1">
         <v>-1</v>
@@ -10286,13 +10295,13 @@
         <v>1026102</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I164" s="1">
         <v>2</v>
@@ -10304,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M164" s="1">
         <v>2026102</v>
@@ -10313,7 +10322,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R164" s="1">
         <v>-1</v>
@@ -10327,13 +10336,13 @@
         <v>1026201</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I165" s="1">
         <v>3</v>
@@ -10345,7 +10354,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M165" s="1">
         <v>2026201</v>
@@ -10354,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="R165" s="1">
         <v>-1</v>
@@ -10368,13 +10377,13 @@
         <v>1026202</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E166" s="1">
         <v>2</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I166" s="1">
         <v>3</v>
@@ -10386,7 +10395,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M166" s="1">
         <v>2026202</v>
@@ -10395,7 +10404,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R166" s="1">
         <v>-1</v>
@@ -10409,13 +10418,13 @@
         <v>1026301</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E167" s="1">
         <v>2</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I167" s="1">
         <v>4</v>
@@ -10427,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M167" s="1">
         <v>2026301</v>
@@ -10436,7 +10445,7 @@
         <v>0</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="R167" s="1">
         <v>-1</v>
@@ -10450,13 +10459,13 @@
         <v>1026302</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E168" s="1">
         <v>2</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I168" s="1">
         <v>4</v>
@@ -10468,7 +10477,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M168" s="1">
         <v>2026302</v>
@@ -10477,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="R168" s="1">
         <v>-1</v>
@@ -10491,13 +10500,13 @@
         <v>1026401</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E169" s="1">
         <v>2</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I169" s="1">
         <v>5</v>
@@ -10509,7 +10518,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M169" s="1">
         <v>2026401</v>
@@ -10518,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="R169" s="1">
         <v>-1</v>
@@ -10532,13 +10541,13 @@
         <v>1026402</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E170" s="1">
         <v>2</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I170" s="1">
         <v>5</v>
@@ -10550,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M170" s="1">
         <v>2026402</v>
@@ -10559,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="R170" s="1">
         <v>-1</v>
@@ -10573,13 +10582,13 @@
         <v>1027001</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E171" s="1">
         <v>2</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I171" s="1">
         <v>1</v>
@@ -10591,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M171" s="1">
         <v>2027001</v>
@@ -10600,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="R171" s="1">
         <v>-1</v>
@@ -10614,13 +10623,13 @@
         <v>1027002</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E172" s="1">
         <v>2</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I172" s="1">
         <v>1</v>
@@ -10632,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M172" s="1">
         <v>2027002</v>
@@ -10641,7 +10650,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="R172" s="1">
         <v>-1</v>
@@ -10655,13 +10664,13 @@
         <v>1027101</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E173" s="1">
         <v>2</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I173" s="1">
         <v>2</v>
@@ -10673,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M173" s="1">
         <v>2027101</v>
@@ -10682,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="O173" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R173" s="1">
         <v>-1</v>
@@ -10696,13 +10705,13 @@
         <v>1027102</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E174" s="1">
         <v>2</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I174" s="1">
         <v>2</v>
@@ -10714,7 +10723,7 @@
         <v>0</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M174" s="1">
         <v>2027102</v>
@@ -10723,7 +10732,7 @@
         <v>0</v>
       </c>
       <c r="O174" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="R174" s="1">
         <v>-1</v>
@@ -10737,13 +10746,13 @@
         <v>1027201</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E175" s="1">
         <v>2</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I175" s="1">
         <v>3</v>
@@ -10755,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M175" s="1">
         <v>2027201</v>
@@ -10764,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="O175" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="R175" s="1">
         <v>-1</v>
@@ -10778,13 +10787,13 @@
         <v>1027202</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E176" s="1">
         <v>2</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I176" s="1">
         <v>3</v>
@@ -10796,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M176" s="1">
         <v>2027202</v>
@@ -10805,7 +10814,7 @@
         <v>0</v>
       </c>
       <c r="O176" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="R176" s="1">
         <v>-1</v>
@@ -10819,13 +10828,13 @@
         <v>1027301</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E177" s="1">
         <v>2</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I177" s="1">
         <v>4</v>
@@ -10837,7 +10846,7 @@
         <v>0</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M177" s="1">
         <v>2027301</v>
@@ -10846,7 +10855,7 @@
         <v>0</v>
       </c>
       <c r="O177" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="R177" s="1">
         <v>-1</v>
@@ -10860,13 +10869,13 @@
         <v>1027302</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E178" s="1">
         <v>2</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I178" s="1">
         <v>4</v>
@@ -10878,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M178" s="1">
         <v>2027302</v>
@@ -10887,7 +10896,7 @@
         <v>0</v>
       </c>
       <c r="O178" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R178" s="1">
         <v>-1</v>
@@ -10901,13 +10910,13 @@
         <v>1027401</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E179" s="1">
         <v>2</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I179" s="1">
         <v>5</v>
@@ -10919,7 +10928,7 @@
         <v>0</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M179" s="1">
         <v>2027401</v>
@@ -10928,7 +10937,7 @@
         <v>0</v>
       </c>
       <c r="O179" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="R179" s="1">
         <v>-1</v>
@@ -10942,13 +10951,13 @@
         <v>1027402</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E180" s="1">
         <v>2</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I180" s="1">
         <v>5</v>
@@ -10960,7 +10969,7 @@
         <v>0</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M180" s="1">
         <v>2027402</v>
@@ -10969,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="O180" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="R180" s="1">
         <v>-1</v>
@@ -10983,13 +10992,13 @@
         <v>1028001</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E181" s="1">
         <v>2</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I181" s="1">
         <v>1</v>
@@ -11001,7 +11010,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M181" s="1">
         <v>2028001</v>
@@ -11010,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="O181" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="R181" s="1">
         <v>-1</v>
@@ -11024,13 +11033,13 @@
         <v>1028002</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E182" s="1">
         <v>2</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I182" s="1">
         <v>1</v>
@@ -11042,7 +11051,7 @@
         <v>0</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M182" s="1">
         <v>2028002</v>
@@ -11051,7 +11060,7 @@
         <v>0</v>
       </c>
       <c r="O182" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="R182" s="1">
         <v>-1</v>
@@ -11065,13 +11074,13 @@
         <v>1028101</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E183" s="1">
         <v>2</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I183" s="1">
         <v>2</v>
@@ -11083,7 +11092,7 @@
         <v>0</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M183" s="1">
         <v>2028101</v>
@@ -11092,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="O183" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="R183" s="1">
         <v>-1</v>
@@ -11106,13 +11115,13 @@
         <v>1028102</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E184" s="1">
         <v>2</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I184" s="1">
         <v>2</v>
@@ -11124,7 +11133,7 @@
         <v>0</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M184" s="1">
         <v>2028102</v>
@@ -11133,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="O184" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="R184" s="1">
         <v>-1</v>
@@ -11147,13 +11156,13 @@
         <v>1028201</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E185" s="1">
         <v>2</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I185" s="1">
         <v>3</v>
@@ -11165,7 +11174,7 @@
         <v>0</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M185" s="1">
         <v>2028201</v>
@@ -11174,7 +11183,7 @@
         <v>0</v>
       </c>
       <c r="O185" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="R185" s="1">
         <v>-1</v>
@@ -11188,13 +11197,13 @@
         <v>1028202</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E186" s="1">
         <v>2</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I186" s="1">
         <v>3</v>
@@ -11206,7 +11215,7 @@
         <v>0</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M186" s="1">
         <v>2028202</v>
@@ -11215,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="O186" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="R186" s="1">
         <v>-1</v>
@@ -11229,13 +11238,13 @@
         <v>1028301</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E187" s="1">
         <v>2</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I187" s="1">
         <v>4</v>
@@ -11247,7 +11256,7 @@
         <v>0</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M187" s="1">
         <v>2028301</v>
@@ -11256,7 +11265,7 @@
         <v>0</v>
       </c>
       <c r="O187" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="R187" s="1">
         <v>-1</v>
@@ -11270,13 +11279,13 @@
         <v>1028302</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E188" s="1">
         <v>2</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I188" s="1">
         <v>4</v>
@@ -11288,7 +11297,7 @@
         <v>0</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M188" s="1">
         <v>2028302</v>
@@ -11297,7 +11306,7 @@
         <v>0</v>
       </c>
       <c r="O188" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="R188" s="1">
         <v>-1</v>
@@ -11311,13 +11320,13 @@
         <v>1028401</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E189" s="1">
         <v>2</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I189" s="1">
         <v>5</v>
@@ -11329,7 +11338,7 @@
         <v>0</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M189" s="1">
         <v>2028401</v>
@@ -11338,7 +11347,7 @@
         <v>0</v>
       </c>
       <c r="O189" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="R189" s="1">
         <v>-1</v>
@@ -11352,13 +11361,13 @@
         <v>1028402</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E190" s="1">
         <v>2</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I190" s="1">
         <v>5</v>
@@ -11370,7 +11379,7 @@
         <v>0</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M190" s="1">
         <v>2028402</v>
@@ -11379,7 +11388,7 @@
         <v>0</v>
       </c>
       <c r="O190" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="R190" s="1">
         <v>-1</v>
@@ -11400,7 +11409,7 @@
         <v>2</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I191" s="1">
         <v>1</v>
@@ -11412,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M191" s="1">
         <v>2126001</v>
@@ -11443,7 +11452,7 @@
         <v>2</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I192" s="1">
         <v>1</v>
@@ -11455,7 +11464,7 @@
         <v>1</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M192" s="1">
         <v>2126002</v>
@@ -11486,7 +11495,7 @@
         <v>2</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I193" s="1">
         <v>2</v>
@@ -11498,7 +11507,7 @@
         <v>1</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M193" s="1">
         <v>2126101</v>
@@ -11529,7 +11538,7 @@
         <v>2</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I194" s="1">
         <v>2</v>
@@ -11541,7 +11550,7 @@
         <v>1</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M194" s="1">
         <v>2126102</v>
@@ -11572,7 +11581,7 @@
         <v>2</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I195" s="1">
         <v>3</v>
@@ -11584,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M195" s="1">
         <v>2126201</v>
@@ -11615,7 +11624,7 @@
         <v>2</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I196" s="1">
         <v>3</v>
@@ -11627,7 +11636,7 @@
         <v>1</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M196" s="1">
         <v>2126202</v>
@@ -11658,7 +11667,7 @@
         <v>2</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I197" s="1">
         <v>4</v>
@@ -11670,7 +11679,7 @@
         <v>1</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M197" s="1">
         <v>2126301</v>
@@ -11701,7 +11710,7 @@
         <v>2</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I198" s="1">
         <v>4</v>
@@ -11713,7 +11722,7 @@
         <v>1</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M198" s="1">
         <v>2126302</v>
@@ -11744,7 +11753,7 @@
         <v>2</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I199" s="1">
         <v>5</v>
@@ -11756,7 +11765,7 @@
         <v>1</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M199" s="1">
         <v>2126401</v>
@@ -11787,7 +11796,7 @@
         <v>2</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I200" s="1">
         <v>5</v>
@@ -11799,7 +11808,7 @@
         <v>1</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M200" s="1">
         <v>2126402</v>
@@ -11830,7 +11839,7 @@
         <v>2</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I201" s="1">
         <v>1</v>
@@ -11842,7 +11851,7 @@
         <v>1</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M201" s="1">
         <v>2127001</v>
@@ -11873,7 +11882,7 @@
         <v>2</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I202" s="1">
         <v>1</v>
@@ -11885,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M202" s="1">
         <v>2127002</v>
@@ -11916,7 +11925,7 @@
         <v>2</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I203" s="1">
         <v>2</v>
@@ -11928,7 +11937,7 @@
         <v>1</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M203" s="1">
         <v>2127101</v>
@@ -11959,7 +11968,7 @@
         <v>2</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I204" s="1">
         <v>2</v>
@@ -11971,7 +11980,7 @@
         <v>1</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M204" s="1">
         <v>2127102</v>
@@ -12002,7 +12011,7 @@
         <v>2</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I205" s="1">
         <v>3</v>
@@ -12014,7 +12023,7 @@
         <v>1</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M205" s="1">
         <v>2127201</v>
@@ -12045,7 +12054,7 @@
         <v>2</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I206" s="1">
         <v>3</v>
@@ -12057,7 +12066,7 @@
         <v>1</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M206" s="1">
         <v>2127202</v>
@@ -12088,7 +12097,7 @@
         <v>2</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I207" s="1">
         <v>4</v>
@@ -12100,7 +12109,7 @@
         <v>1</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M207" s="1">
         <v>2127301</v>
@@ -12131,7 +12140,7 @@
         <v>2</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I208" s="1">
         <v>4</v>
@@ -12143,7 +12152,7 @@
         <v>1</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M208" s="1">
         <v>2127302</v>
@@ -12174,7 +12183,7 @@
         <v>2</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I209" s="1">
         <v>5</v>
@@ -12186,7 +12195,7 @@
         <v>1</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M209" s="1">
         <v>2127401</v>
@@ -12217,7 +12226,7 @@
         <v>2</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I210" s="1">
         <v>5</v>
@@ -12229,7 +12238,7 @@
         <v>1</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M210" s="1">
         <v>2127402</v>
@@ -12260,7 +12269,7 @@
         <v>2</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I211" s="1">
         <v>1</v>
@@ -12272,7 +12281,7 @@
         <v>1</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M211" s="1">
         <v>2128001</v>
@@ -12303,7 +12312,7 @@
         <v>2</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I212" s="1">
         <v>1</v>
@@ -12315,7 +12324,7 @@
         <v>1</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M212" s="1">
         <v>2128002</v>
@@ -12346,7 +12355,7 @@
         <v>2</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I213" s="1">
         <v>2</v>
@@ -12358,7 +12367,7 @@
         <v>1</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M213" s="1">
         <v>2128101</v>
@@ -12389,7 +12398,7 @@
         <v>2</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I214" s="1">
         <v>2</v>
@@ -12401,7 +12410,7 @@
         <v>1</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M214" s="1">
         <v>2128102</v>
@@ -12432,7 +12441,7 @@
         <v>2</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I215" s="1">
         <v>3</v>
@@ -12444,7 +12453,7 @@
         <v>1</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M215" s="1">
         <v>2128201</v>
@@ -12475,7 +12484,7 @@
         <v>2</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I216" s="1">
         <v>3</v>
@@ -12487,7 +12496,7 @@
         <v>1</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M216" s="1">
         <v>2128202</v>
@@ -12518,7 +12527,7 @@
         <v>2</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I217" s="1">
         <v>4</v>
@@ -12530,7 +12539,7 @@
         <v>1</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M217" s="1">
         <v>2128301</v>
@@ -12561,7 +12570,7 @@
         <v>2</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I218" s="1">
         <v>4</v>
@@ -12573,7 +12582,7 @@
         <v>1</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M218" s="1">
         <v>2128302</v>
@@ -12604,7 +12613,7 @@
         <v>2</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I219" s="1">
         <v>5</v>
@@ -12616,7 +12625,7 @@
         <v>1</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M219" s="1">
         <v>2128401</v>
@@ -12647,7 +12656,7 @@
         <v>2</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I220" s="1">
         <v>5</v>
@@ -12659,7 +12668,7 @@
         <v>1</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M220" s="1">
         <v>2128402</v>
@@ -12683,13 +12692,13 @@
         <v>1130001</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I221" s="1">
         <v>1</v>
@@ -12707,7 +12716,7 @@
         <v>0</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="R221" s="1">
         <v>999999</v>
@@ -12721,13 +12730,13 @@
         <v>1130002</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E222" s="1">
         <v>1</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I222" s="1">
         <v>1</v>
@@ -12745,7 +12754,7 @@
         <v>0</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="R222" s="1">
         <v>999999</v>
@@ -12759,13 +12768,13 @@
         <v>1130003</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E223" s="1">
         <v>1</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I223" s="1">
         <v>2</v>
@@ -12783,7 +12792,7 @@
         <v>0</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="R223" s="1">
         <v>999999</v>
@@ -12797,13 +12806,13 @@
         <v>1130004</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E224" s="1">
         <v>1</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I224" s="1">
         <v>3</v>
@@ -12821,7 +12830,7 @@
         <v>0</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="R224" s="1">
         <v>999999</v>
@@ -12835,13 +12844,13 @@
         <v>1130005</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E225" s="1">
         <v>1</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I225" s="1">
         <v>4</v>
@@ -12859,7 +12868,7 @@
         <v>0</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="R225" s="1">
         <v>999999</v>
@@ -12873,13 +12882,13 @@
         <v>1130006</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E226" s="1">
         <v>1</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I226" s="1">
         <v>5</v>
@@ -12897,7 +12906,7 @@
         <v>0</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R226" s="1">
         <v>999999</v>
@@ -12911,13 +12920,13 @@
         <v>1131001</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I227" s="1">
         <v>1</v>
@@ -12935,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="O227" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="228" spans="1:18">
@@ -12946,13 +12955,13 @@
         <v>1131002</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I228" s="1">
         <v>1</v>
@@ -12970,7 +12979,7 @@
         <v>0</v>
       </c>
       <c r="O228" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="229" spans="1:18">
@@ -12981,13 +12990,13 @@
         <v>1131003</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I229" s="1">
         <v>1</v>
@@ -13005,7 +13014,7 @@
         <v>0</v>
       </c>
       <c r="O229" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="230" spans="1:18">
@@ -13016,13 +13025,13 @@
         <v>1131004</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I230" s="1">
         <v>1</v>
@@ -13040,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="231" spans="1:18">
@@ -13051,13 +13060,13 @@
         <v>1131005</v>
       </c>
       <c r="D231" s="14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I231" s="1">
         <v>1</v>
@@ -13075,7 +13084,7 @@
         <v>0</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="232" spans="1:18">
@@ -13086,13 +13095,13 @@
         <v>1131006</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I232" s="1">
         <v>1</v>
@@ -13110,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="233" spans="1:18">
@@ -13121,13 +13130,13 @@
         <v>1131101</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E233" s="1">
         <v>2</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I233" s="1">
         <v>2</v>
@@ -13145,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="O233" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="234" spans="1:18">
@@ -13156,13 +13165,13 @@
         <v>1131102</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E234" s="1">
         <v>2</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I234" s="1">
         <v>2</v>
@@ -13180,7 +13189,7 @@
         <v>0</v>
       </c>
       <c r="O234" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="235" spans="1:18">
@@ -13191,13 +13200,13 @@
         <v>1131103</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E235" s="1">
         <v>2</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I235" s="1">
         <v>2</v>
@@ -13215,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="O235" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="236" spans="1:18">
@@ -13226,13 +13235,13 @@
         <v>1131104</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E236" s="1">
         <v>2</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I236" s="1">
         <v>2</v>
@@ -13250,7 +13259,7 @@
         <v>0</v>
       </c>
       <c r="O236" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="237" spans="1:18">
@@ -13261,13 +13270,13 @@
         <v>1131105</v>
       </c>
       <c r="D237" s="14" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E237" s="1">
         <v>2</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I237" s="1">
         <v>2</v>
@@ -13285,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="O237" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="238" spans="1:18">
@@ -13296,13 +13305,13 @@
         <v>1131106</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E238" s="1">
         <v>2</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I238" s="1">
         <v>2</v>
@@ -13320,7 +13329,7 @@
         <v>0</v>
       </c>
       <c r="O238" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="239" spans="1:18">
@@ -13331,13 +13340,13 @@
         <v>1131201</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E239" s="1">
         <v>2</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I239" s="1">
         <v>3</v>
@@ -13355,7 +13364,7 @@
         <v>0</v>
       </c>
       <c r="O239" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="240" spans="1:18">
@@ -13366,13 +13375,13 @@
         <v>1131202</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E240" s="1">
         <v>2</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I240" s="1">
         <v>3</v>
@@ -13390,7 +13399,7 @@
         <v>0</v>
       </c>
       <c r="O240" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="241" spans="1:15">
@@ -13401,13 +13410,13 @@
         <v>1131203</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E241" s="1">
         <v>2</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I241" s="1">
         <v>3</v>
@@ -13425,7 +13434,7 @@
         <v>0</v>
       </c>
       <c r="O241" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="242" spans="1:15">
@@ -13436,13 +13445,13 @@
         <v>1131204</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E242" s="1">
         <v>2</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I242" s="1">
         <v>3</v>
@@ -13460,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="O242" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="243" spans="1:15">
@@ -13471,13 +13480,13 @@
         <v>1131205</v>
       </c>
       <c r="D243" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E243" s="1">
         <v>2</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I243" s="1">
         <v>3</v>
@@ -13495,7 +13504,7 @@
         <v>0</v>
       </c>
       <c r="O243" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="244" spans="1:15">
@@ -13506,13 +13515,13 @@
         <v>1131206</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E244" s="1">
         <v>2</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I244" s="1">
         <v>3</v>
@@ -13530,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="O244" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="245" spans="1:15">
@@ -13541,13 +13550,13 @@
         <v>1131301</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E245" s="1">
         <v>2</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I245" s="1">
         <v>4</v>
@@ -13565,7 +13574,7 @@
         <v>0</v>
       </c>
       <c r="O245" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="246" spans="1:15">
@@ -13576,13 +13585,13 @@
         <v>1131302</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E246" s="1">
         <v>2</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I246" s="1">
         <v>4</v>
@@ -13600,7 +13609,7 @@
         <v>0</v>
       </c>
       <c r="O246" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="247" spans="1:15">
@@ -13611,13 +13620,13 @@
         <v>1131303</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E247" s="1">
         <v>2</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I247" s="1">
         <v>4</v>
@@ -13635,7 +13644,7 @@
         <v>0</v>
       </c>
       <c r="O247" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="248" spans="1:15">
@@ -13646,13 +13655,13 @@
         <v>1131304</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E248" s="1">
         <v>2</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I248" s="1">
         <v>4</v>
@@ -13670,7 +13679,7 @@
         <v>0</v>
       </c>
       <c r="O248" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="249" spans="1:15">
@@ -13681,13 +13690,13 @@
         <v>1131305</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E249" s="1">
         <v>2</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I249" s="1">
         <v>4</v>
@@ -13705,7 +13714,7 @@
         <v>0</v>
       </c>
       <c r="O249" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="250" spans="1:15">
@@ -13716,13 +13725,13 @@
         <v>1131306</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E250" s="1">
         <v>2</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I250" s="1">
         <v>4</v>
@@ -13740,7 +13749,7 @@
         <v>0</v>
       </c>
       <c r="O250" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="251" spans="1:15">
@@ -13751,13 +13760,13 @@
         <v>1131401</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E251" s="1">
         <v>2</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I251" s="1">
         <v>5</v>
@@ -13775,7 +13784,7 @@
         <v>0</v>
       </c>
       <c r="O251" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="252" spans="1:15">
@@ -13786,13 +13795,13 @@
         <v>1131402</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E252" s="1">
         <v>2</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I252" s="1">
         <v>5</v>
@@ -13810,7 +13819,7 @@
         <v>0</v>
       </c>
       <c r="O252" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="253" spans="1:15">
@@ -13821,13 +13830,13 @@
         <v>1131403</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E253" s="1">
         <v>2</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I253" s="1">
         <v>5</v>
@@ -13845,7 +13854,7 @@
         <v>0</v>
       </c>
       <c r="O253" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="254" spans="1:15">
@@ -13856,13 +13865,13 @@
         <v>1131404</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E254" s="1">
         <v>2</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I254" s="1">
         <v>5</v>
@@ -13880,7 +13889,7 @@
         <v>0</v>
       </c>
       <c r="O254" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="255" spans="1:15">
@@ -13891,13 +13900,13 @@
         <v>1131405</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E255" s="1">
         <v>2</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I255" s="1">
         <v>5</v>
@@ -13915,7 +13924,7 @@
         <v>0</v>
       </c>
       <c r="O255" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="256" spans="1:15">
@@ -13926,13 +13935,13 @@
         <v>1131406</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E256" s="1">
         <v>2</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I256" s="1">
         <v>5</v>
@@ -13950,7 +13959,7 @@
         <v>0</v>
       </c>
       <c r="O256" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="257" spans="1:18">
@@ -13961,13 +13970,13 @@
         <v>1150001</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E257" s="1">
         <v>2</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I257" s="1">
         <v>2</v>
@@ -13979,7 +13988,7 @@
         <v>0</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M257" s="1">
         <v>2150001</v>
@@ -14003,13 +14012,13 @@
         <v>1150002</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E258" s="1">
         <v>2</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I258" s="1">
         <v>2</v>
@@ -14021,7 +14030,7 @@
         <v>0</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M258" s="1">
         <v>2150002</v>
@@ -14045,13 +14054,13 @@
         <v>1150003</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E259" s="1">
         <v>2</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I259" s="1">
         <v>2</v>
@@ -14063,7 +14072,7 @@
         <v>0</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M259" s="1">
         <v>2150003</v>
@@ -14087,13 +14096,13 @@
         <v>1150004</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E260" s="1">
         <v>2</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I260" s="1">
         <v>2</v>
@@ -14105,7 +14114,7 @@
         <v>0</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M260" s="1">
         <v>2150004</v>
@@ -14129,13 +14138,13 @@
         <v>1150005</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E261" s="1">
         <v>2</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I261" s="1">
         <v>2</v>
@@ -14147,7 +14156,7 @@
         <v>0</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M261" s="1">
         <v>2150005</v>
@@ -14171,13 +14180,13 @@
         <v>1150006</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E262" s="1">
         <v>2</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I262" s="1">
         <v>2</v>
@@ -14189,7 +14198,7 @@
         <v>0</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M262" s="1">
         <v>2150006</v>
@@ -14213,13 +14222,13 @@
         <v>1150007</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I263" s="1">
         <v>2</v>
@@ -14231,7 +14240,7 @@
         <v>0</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M263" s="1">
         <v>2150007</v>
@@ -14255,13 +14264,13 @@
         <v>1150008</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E264" s="1">
         <v>2</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I264" s="1">
         <v>2</v>
@@ -14273,7 +14282,7 @@
         <v>0</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M264" s="1">
         <v>2150008</v>
@@ -14297,13 +14306,13 @@
         <v>1150009</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E265" s="1">
         <v>2</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I265" s="1">
         <v>2</v>
@@ -14315,7 +14324,7 @@
         <v>0</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="M265" s="1">
         <v>2150009</v>
@@ -14339,13 +14348,13 @@
         <v>1150010</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E266" s="1">
         <v>2</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I266" s="1">
         <v>2</v>
@@ -14357,7 +14366,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M266" s="1">
         <v>2150010</v>
@@ -14381,13 +14390,13 @@
         <v>1150011</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E267" s="1">
         <v>2</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I267" s="1">
         <v>2</v>
@@ -14399,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M267" s="1">
         <v>2150011</v>
@@ -14423,13 +14432,13 @@
         <v>1150012</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E268" s="1">
         <v>2</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I268" s="1">
         <v>2</v>
@@ -14441,7 +14450,7 @@
         <v>0</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M268" s="1">
         <v>2150012</v>
@@ -14465,13 +14474,13 @@
         <v>1150013</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I269" s="1">
         <v>2</v>
@@ -14483,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M269" s="1">
         <v>2150013</v>
@@ -14507,13 +14516,13 @@
         <v>1150014</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I270" s="1">
         <v>2</v>
@@ -14525,7 +14534,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M270" s="1">
         <v>2150014</v>
@@ -14549,13 +14558,13 @@
         <v>1150015</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I271" s="1">
         <v>2</v>
@@ -14567,7 +14576,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M271" s="1">
         <v>2150015</v>
@@ -14591,13 +14600,13 @@
         <v>1150016</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I272" s="1">
         <v>3</v>
@@ -14609,7 +14618,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M272" s="1">
         <v>2150016</v>
@@ -14633,13 +14642,13 @@
         <v>1150017</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I273" s="1">
         <v>3</v>
@@ -14651,7 +14660,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M273" s="1">
         <v>2150017</v>
@@ -14675,13 +14684,13 @@
         <v>1150018</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I274" s="1">
         <v>3</v>
@@ -14693,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M274" s="1">
         <v>2150018</v>
@@ -14717,13 +14726,13 @@
         <v>1150019</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I275" s="1">
         <v>3</v>
@@ -14735,7 +14744,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M275" s="1">
         <v>2150019</v>
@@ -14759,13 +14768,13 @@
         <v>1150020</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I276" s="1">
         <v>3</v>
@@ -14777,7 +14786,7 @@
         <v>0</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M276" s="1">
         <v>2150020</v>
@@ -14801,13 +14810,13 @@
         <v>1150021</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I277" s="1">
         <v>3</v>
@@ -14819,7 +14828,7 @@
         <v>0</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M277" s="1">
         <v>2150021</v>
@@ -14843,13 +14852,13 @@
         <v>1150022</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I278" s="1">
         <v>3</v>
@@ -14861,7 +14870,7 @@
         <v>0</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M278" s="1">
         <v>2150022</v>
@@ -14885,13 +14894,13 @@
         <v>1150023</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I279" s="1">
         <v>3</v>
@@ -14903,7 +14912,7 @@
         <v>0</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M279" s="1">
         <v>2150023</v>
@@ -14927,13 +14936,13 @@
         <v>1150024</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I280" s="1">
         <v>3</v>
@@ -14945,7 +14954,7 @@
         <v>0</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M280" s="1">
         <v>2150024</v>
@@ -14969,13 +14978,13 @@
         <v>1150025</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I281" s="1">
         <v>3</v>
@@ -14987,7 +14996,7 @@
         <v>0</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M281" s="1">
         <v>2150025</v>
@@ -15011,13 +15020,13 @@
         <v>1150026</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I282" s="1">
         <v>3</v>
@@ -15029,7 +15038,7 @@
         <v>0</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M282" s="1">
         <v>2150026</v>
@@ -15053,13 +15062,13 @@
         <v>1150027</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I283" s="1">
         <v>3</v>
@@ -15071,7 +15080,7 @@
         <v>0</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M283" s="1">
         <v>2150027</v>
@@ -15095,13 +15104,13 @@
         <v>1150028</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I284" s="1">
         <v>4</v>
@@ -15113,7 +15122,7 @@
         <v>0</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M284" s="1">
         <v>2150028</v>
@@ -15137,13 +15146,13 @@
         <v>1150029</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I285" s="1">
         <v>4</v>
@@ -15155,7 +15164,7 @@
         <v>0</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M285" s="1">
         <v>2150029</v>
@@ -15179,13 +15188,13 @@
         <v>1150030</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I286" s="1">
         <v>4</v>
@@ -15197,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M286" s="1">
         <v>2150030</v>
@@ -15221,13 +15230,13 @@
         <v>1150031</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I287" s="1">
         <v>4</v>
@@ -15239,7 +15248,7 @@
         <v>0</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M287" s="1">
         <v>2150031</v>
@@ -15263,13 +15272,13 @@
         <v>1150032</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I288" s="1">
         <v>4</v>
@@ -15281,7 +15290,7 @@
         <v>0</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M288" s="1">
         <v>2150032</v>
@@ -15305,13 +15314,13 @@
         <v>1150033</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I289" s="1">
         <v>4</v>
@@ -15323,7 +15332,7 @@
         <v>0</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M289" s="1">
         <v>2150033</v>
@@ -15347,13 +15356,13 @@
         <v>1150034</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I290" s="1">
         <v>4</v>
@@ -15365,7 +15374,7 @@
         <v>0</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M290" s="1">
         <v>2150034</v>
@@ -15389,13 +15398,13 @@
         <v>1150035</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I291" s="1">
         <v>4</v>
@@ -15407,7 +15416,7 @@
         <v>0</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M291" s="1">
         <v>2150035</v>
@@ -15431,13 +15440,13 @@
         <v>1150036</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I292" s="1">
         <v>4</v>
@@ -15449,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M292" s="1">
         <v>2150036</v>
@@ -15473,13 +15482,13 @@
         <v>1150037</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I293" s="1">
         <v>4</v>
@@ -15491,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M293" s="1">
         <v>2150037</v>
@@ -15515,13 +15524,13 @@
         <v>1150038</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I294" s="1">
         <v>4</v>
@@ -15533,7 +15542,7 @@
         <v>0</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M294" s="1">
         <v>2150038</v>
@@ -15557,13 +15566,13 @@
         <v>1150039</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I295" s="1">
         <v>4</v>
@@ -15575,7 +15584,7 @@
         <v>0</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M295" s="1">
         <v>2150039</v>
@@ -15599,13 +15608,13 @@
         <v>1150040</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I296" s="1">
         <v>4</v>
@@ -15617,7 +15626,7 @@
         <v>0</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M296" s="1">
         <v>2150040</v>
@@ -15641,13 +15650,13 @@
         <v>1150041</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I297" s="1">
         <v>4</v>
@@ -15659,7 +15668,7 @@
         <v>0</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M297" s="1">
         <v>2150041</v>
@@ -15683,13 +15692,13 @@
         <v>1150042</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I298" s="1">
         <v>5</v>
@@ -15701,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M298" s="1">
         <v>2150042</v>
@@ -15725,13 +15734,13 @@
         <v>1150043</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I299" s="1">
         <v>5</v>
@@ -15743,7 +15752,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M299" s="1">
         <v>2150043</v>
@@ -15767,13 +15776,13 @@
         <v>1150044</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I300" s="1">
         <v>5</v>
@@ -15785,7 +15794,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M300" s="1">
         <v>2150044</v>
@@ -15809,13 +15818,13 @@
         <v>1150045</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I301" s="1">
         <v>5</v>
@@ -15827,7 +15836,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M301" s="1">
         <v>2150045</v>
@@ -15851,13 +15860,13 @@
         <v>1150046</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I302" s="1">
         <v>5</v>
@@ -15869,7 +15878,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M302" s="1">
         <v>2150046</v>
@@ -15893,13 +15902,13 @@
         <v>1150047</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I303" s="1">
         <v>5</v>
@@ -15911,7 +15920,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M303" s="1">
         <v>2150047</v>
@@ -15935,13 +15944,13 @@
         <v>1150048</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I304" s="1">
         <v>5</v>
@@ -15953,7 +15962,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M304" s="1">
         <v>2150048</v>
@@ -15977,13 +15986,13 @@
         <v>1150049</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I305" s="1">
         <v>5</v>
@@ -15995,7 +16004,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="M305" s="1">
         <v>2150049</v>
@@ -16019,13 +16028,13 @@
         <v>1150050</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I306" s="1">
         <v>5</v>
@@ -16037,7 +16046,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M306" s="1">
         <v>2150050</v>
@@ -16061,13 +16070,13 @@
         <v>1150051</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I307" s="1">
         <v>5</v>
@@ -16079,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M307" s="1">
         <v>2150051</v>
@@ -16103,13 +16112,13 @@
         <v>1150052</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I308" s="1">
         <v>5</v>
@@ -16121,7 +16130,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M308" s="1">
         <v>2150052</v>
@@ -16145,13 +16154,13 @@
         <v>1150053</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I309" s="1">
         <v>5</v>
@@ -16163,7 +16172,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M309" s="1">
         <v>2150053</v>
@@ -16187,13 +16196,13 @@
         <v>1150054</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I310" s="1">
         <v>5</v>
@@ -16205,7 +16214,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M310" s="1">
         <v>2150054</v>
@@ -16229,13 +16238,13 @@
         <v>1150055</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I311" s="1">
         <v>5</v>
@@ -16247,7 +16256,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M311" s="1">
         <v>2150055</v>
@@ -16271,13 +16280,13 @@
         <v>1150056</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I312" s="1">
         <v>5</v>
@@ -16289,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M312" s="1">
         <v>2150056</v>
@@ -16313,13 +16322,13 @@
         <v>1150057</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I313" s="1">
         <v>5</v>
@@ -16331,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M313" s="1">
         <v>2150057</v>
@@ -16355,13 +16364,13 @@
         <v>1150058</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I314" s="1">
         <v>5</v>
@@ -16373,7 +16382,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M314" s="1">
         <v>2150058</v>
@@ -16397,13 +16406,13 @@
         <v>1150059</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I315" s="1">
         <v>5</v>
@@ -16415,7 +16424,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M315" s="1">
         <v>2150059</v>
@@ -16439,13 +16448,13 @@
         <v>1150060</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I316" s="1">
         <v>5</v>
@@ -16457,7 +16466,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M316" s="1">
         <v>2150060</v>
@@ -16481,13 +16490,13 @@
         <v>1150061</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I317" s="1">
         <v>5</v>
@@ -16499,7 +16508,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="M317" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -1153,7 +1153,7 @@
     <t>挖矿小游戏中的高价值矿石，可在兑换商店中兑换道具</t>
   </si>
   <si>
-    <t>yjy_tb_cs.png</t>
+    <t>daoju_cs.png</t>
   </si>
   <si>
     <t>升级财神游戏特殊词条</t>
@@ -2157,12 +2157,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="588">
   <si>
     <t>道具ID</t>
   </si>
@@ -1157,6 +1157,96 @@
   </si>
   <si>
     <t>升级财神游戏特殊词条</t>
+  </si>
+  <si>
+    <t>1025101_1</t>
+  </si>
+  <si>
+    <t>1025102_1</t>
+  </si>
+  <si>
+    <t>1025103_1</t>
+  </si>
+  <si>
+    <t>1025104_1</t>
+  </si>
+  <si>
+    <t>1025105_1</t>
+  </si>
+  <si>
+    <t>1025106_1</t>
+  </si>
+  <si>
+    <t>1025201_1</t>
+  </si>
+  <si>
+    <t>1025202_1</t>
+  </si>
+  <si>
+    <t>1025203_1</t>
+  </si>
+  <si>
+    <t>1025204_1</t>
+  </si>
+  <si>
+    <t>1025205_1</t>
+  </si>
+  <si>
+    <t>1025206_1</t>
+  </si>
+  <si>
+    <t>1025301_1</t>
+  </si>
+  <si>
+    <t>1025302_1</t>
+  </si>
+  <si>
+    <t>1025303_1</t>
+  </si>
+  <si>
+    <t>1025304_1</t>
+  </si>
+  <si>
+    <t>1025305_1</t>
+  </si>
+  <si>
+    <t>1025306_1</t>
+  </si>
+  <si>
+    <t>1025401_1</t>
+  </si>
+  <si>
+    <t>1025402_1</t>
+  </si>
+  <si>
+    <t>1025403_1</t>
+  </si>
+  <si>
+    <t>1025404_1</t>
+  </si>
+  <si>
+    <t>1025405_1</t>
+  </si>
+  <si>
+    <t>1025406_1</t>
+  </si>
+  <si>
+    <t>1025501_1</t>
+  </si>
+  <si>
+    <t>1025502_1</t>
+  </si>
+  <si>
+    <t>1025503_1</t>
+  </si>
+  <si>
+    <t>1025504_1</t>
+  </si>
+  <si>
+    <t>1025505_1</t>
+  </si>
+  <si>
+    <t>1025506_1</t>
   </si>
   <si>
     <t>白色品质游客邀请函</t>
@@ -7585,7 +7675,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:19">
       <c r="A97" s="1">
         <v>1024037</v>
       </c>
@@ -7623,7 +7713,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:19">
       <c r="A98" s="1">
         <v>1024038</v>
       </c>
@@ -7661,7 +7751,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="99" spans="1:18">
+    <row r="99" spans="1:19">
       <c r="A99" s="1">
         <v>1024039</v>
       </c>
@@ -7699,7 +7789,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:19">
       <c r="A100" s="1">
         <v>1024040</v>
       </c>
@@ -7746,7 +7836,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:19">
       <c r="A101" s="1">
         <v>1024041</v>
       </c>
@@ -7782,8 +7872,11 @@
         <f>"使用该道具后可以指定生成游客"&amp;O136</f>
         <v>使用该道具后可以指定生成游客街头潮人</v>
       </c>
-    </row>
-    <row r="102" spans="1:18">
+      <c r="S101" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
       <c r="A102" s="1">
         <v>1024042</v>
       </c>
@@ -7819,8 +7912,11 @@
         <f t="shared" ref="O102:O130" si="1">"使用该道具后可以指定生成游客"&amp;O137</f>
         <v>使用该道具后可以指定生成游客复古绅士</v>
       </c>
-    </row>
-    <row r="103" spans="1:18">
+      <c r="S102" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
       <c r="A103" s="1">
         <v>1024043</v>
       </c>
@@ -7856,8 +7952,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客酷盖少年</v>
       </c>
-    </row>
-    <row r="104" spans="1:18">
+      <c r="S103" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19">
       <c r="A104" s="1">
         <v>1024044</v>
       </c>
@@ -7893,8 +7992,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客潮流先锋</v>
       </c>
-    </row>
-    <row r="105" spans="1:18">
+      <c r="S104" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
       <c r="A105" s="1">
         <v>1024045</v>
       </c>
@@ -7930,8 +8032,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客时尚教主</v>
       </c>
-    </row>
-    <row r="106" spans="1:18">
+      <c r="S105" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
       <c r="A106" s="1">
         <v>1024046</v>
       </c>
@@ -7967,8 +8072,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客街拍达人</v>
       </c>
-    </row>
-    <row r="107" spans="1:18">
+      <c r="S106" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
       <c r="A107" s="1">
         <v>1024047</v>
       </c>
@@ -7986,7 +8094,7 @@
         <v>55</v>
       </c>
       <c r="I107" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J107" s="1" t="b">
         <v>1</v>
@@ -8004,8 +8112,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客运动健将</v>
       </c>
-    </row>
-    <row r="108" spans="1:18">
+      <c r="S107" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
       <c r="A108" s="1">
         <v>1024048</v>
       </c>
@@ -8023,7 +8134,7 @@
         <v>55</v>
       </c>
       <c r="I108" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" s="1" t="b">
         <v>1</v>
@@ -8041,8 +8152,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客跑酷少年</v>
       </c>
-    </row>
-    <row r="109" spans="1:18">
+      <c r="S108" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
       <c r="A109" s="1">
         <v>1024049</v>
       </c>
@@ -8060,7 +8174,7 @@
         <v>55</v>
       </c>
       <c r="I109" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J109" s="1" t="b">
         <v>1</v>
@@ -8078,8 +8192,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客滑板高手</v>
       </c>
-    </row>
-    <row r="110" spans="1:18">
+      <c r="S109" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
       <c r="A110" s="1">
         <v>1024050</v>
       </c>
@@ -8097,7 +8214,7 @@
         <v>55</v>
       </c>
       <c r="I110" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J110" s="1" t="b">
         <v>1</v>
@@ -8115,8 +8232,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客甜心辣妹</v>
       </c>
-    </row>
-    <row r="111" spans="1:18">
+      <c r="S110" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
       <c r="A111" s="1">
         <v>1024051</v>
       </c>
@@ -8134,7 +8254,7 @@
         <v>55</v>
       </c>
       <c r="I111" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J111" s="1" t="b">
         <v>1</v>
@@ -8152,8 +8272,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客活力少女</v>
       </c>
-    </row>
-    <row r="112" spans="1:18">
+      <c r="S111" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
       <c r="A112" s="1">
         <v>1024052</v>
       </c>
@@ -8171,7 +8294,7 @@
         <v>55</v>
       </c>
       <c r="I112" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J112" s="1" t="b">
         <v>1</v>
@@ -8189,8 +8312,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客优雅女神</v>
       </c>
-    </row>
-    <row r="113" spans="1:15">
+      <c r="S112" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19">
       <c r="A113" s="1">
         <v>1024053</v>
       </c>
@@ -8208,7 +8334,7 @@
         <v>55</v>
       </c>
       <c r="I113" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J113" s="1" t="b">
         <v>1</v>
@@ -8226,8 +8352,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客健身狂魔</v>
       </c>
-    </row>
-    <row r="114" spans="1:15">
+      <c r="S113" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19">
       <c r="A114" s="1">
         <v>1024054</v>
       </c>
@@ -8245,7 +8374,7 @@
         <v>55</v>
       </c>
       <c r="I114" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J114" s="1" t="b">
         <v>1</v>
@@ -8263,8 +8392,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客单车骑士</v>
       </c>
-    </row>
-    <row r="115" spans="1:15">
+      <c r="S114" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19">
       <c r="A115" s="1">
         <v>1024055</v>
       </c>
@@ -8282,7 +8414,7 @@
         <v>55</v>
       </c>
       <c r="I115" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J115" s="1" t="b">
         <v>1</v>
@@ -8300,8 +8432,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客登山行者</v>
       </c>
-    </row>
-    <row r="116" spans="1:15">
+      <c r="S115" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19">
       <c r="A116" s="1">
         <v>1024056</v>
       </c>
@@ -8319,7 +8454,7 @@
         <v>55</v>
       </c>
       <c r="I116" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J116" s="1" t="b">
         <v>1</v>
@@ -8337,8 +8472,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客文艺青年</v>
       </c>
-    </row>
-    <row r="117" spans="1:15">
+      <c r="S116" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19">
       <c r="A117" s="1">
         <v>1024057</v>
       </c>
@@ -8356,7 +8494,7 @@
         <v>55</v>
       </c>
       <c r="I117" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J117" s="1" t="b">
         <v>1</v>
@@ -8374,8 +8512,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客书香少女</v>
       </c>
-    </row>
-    <row r="118" spans="1:15">
+      <c r="S117" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19">
       <c r="A118" s="1">
         <v>1024058</v>
       </c>
@@ -8393,7 +8534,7 @@
         <v>55</v>
       </c>
       <c r="I118" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J118" s="1" t="b">
         <v>1</v>
@@ -8411,8 +8552,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客民谣歌手</v>
       </c>
-    </row>
-    <row r="119" spans="1:15">
+      <c r="S118" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19">
       <c r="A119" s="1">
         <v>1024059</v>
       </c>
@@ -8430,7 +8574,7 @@
         <v>55</v>
       </c>
       <c r="I119" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J119" s="1" t="b">
         <v>1</v>
@@ -8448,8 +8592,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客马拉松客</v>
       </c>
-    </row>
-    <row r="120" spans="1:15">
+      <c r="S119" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19">
       <c r="A120" s="1">
         <v>1024060</v>
       </c>
@@ -8467,7 +8614,7 @@
         <v>55</v>
       </c>
       <c r="I120" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J120" s="1" t="b">
         <v>1</v>
@@ -8485,8 +8632,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客极限玩家</v>
       </c>
-    </row>
-    <row r="121" spans="1:15">
+      <c r="S120" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19">
       <c r="A121" s="1">
         <v>1024061</v>
       </c>
@@ -8504,7 +8654,7 @@
         <v>55</v>
       </c>
       <c r="I121" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J121" s="1" t="b">
         <v>1</v>
@@ -8522,8 +8672,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客科技极客</v>
       </c>
-    </row>
-    <row r="122" spans="1:15">
+      <c r="S121" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19">
       <c r="A122" s="1">
         <v>1024062</v>
       </c>
@@ -8541,7 +8694,7 @@
         <v>55</v>
       </c>
       <c r="I122" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J122" s="1" t="b">
         <v>1</v>
@@ -8559,8 +8712,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客独立画家</v>
       </c>
-    </row>
-    <row r="123" spans="1:15">
+      <c r="S122" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19">
       <c r="A123" s="1">
         <v>1024063</v>
       </c>
@@ -8578,7 +8734,7 @@
         <v>55</v>
       </c>
       <c r="I123" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J123" s="1" t="b">
         <v>1</v>
@@ -8596,8 +8752,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客浪漫诗人</v>
       </c>
-    </row>
-    <row r="124" spans="1:15">
+      <c r="S123" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19">
       <c r="A124" s="1">
         <v>1024064</v>
       </c>
@@ -8615,7 +8774,7 @@
         <v>55</v>
       </c>
       <c r="I124" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J124" s="1" t="b">
         <v>1</v>
@@ -8633,8 +8792,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客古典乐迷</v>
       </c>
-    </row>
-    <row r="125" spans="1:15">
+      <c r="S124" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19">
       <c r="A125" s="1">
         <v>1024065</v>
       </c>
@@ -8652,7 +8814,7 @@
         <v>55</v>
       </c>
       <c r="I125" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J125" s="1" t="b">
         <v>1</v>
@@ -8670,8 +8832,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客创业新贵</v>
       </c>
-    </row>
-    <row r="126" spans="1:15">
+      <c r="S125" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19">
       <c r="A126" s="1">
         <v>1024066</v>
       </c>
@@ -8689,7 +8854,7 @@
         <v>55</v>
       </c>
       <c r="I126" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J126" s="1" t="b">
         <v>1</v>
@@ -8707,8 +8872,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客摸金校尉</v>
       </c>
-    </row>
-    <row r="127" spans="1:15">
+      <c r="S126" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19">
       <c r="A127" s="1">
         <v>1024067</v>
       </c>
@@ -8726,7 +8894,7 @@
         <v>55</v>
       </c>
       <c r="I127" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J127" s="1" t="b">
         <v>1</v>
@@ -8744,8 +8912,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客氪金大佬</v>
       </c>
-    </row>
-    <row r="128" spans="1:15">
+      <c r="S127" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19">
       <c r="A128" s="1">
         <v>1024068</v>
       </c>
@@ -8763,7 +8934,7 @@
         <v>55</v>
       </c>
       <c r="I128" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J128" s="1" t="b">
         <v>1</v>
@@ -8781,8 +8952,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客穿搭博主</v>
       </c>
-    </row>
-    <row r="129" spans="1:18">
+      <c r="S128" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19">
       <c r="A129" s="1">
         <v>1024069</v>
       </c>
@@ -8800,7 +8974,7 @@
         <v>55</v>
       </c>
       <c r="I129" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J129" s="1" t="b">
         <v>1</v>
@@ -8818,8 +8992,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客美妆新秀</v>
       </c>
-    </row>
-    <row r="130" spans="1:18">
+      <c r="S129" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19">
       <c r="A130" s="1">
         <v>1024070</v>
       </c>
@@ -8837,7 +9014,7 @@
         <v>55</v>
       </c>
       <c r="I130" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J130" s="1" t="b">
         <v>1</v>
@@ -8855,8 +9032,11 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客高定女王</v>
       </c>
-    </row>
-    <row r="131" spans="1:18">
+      <c r="S130" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19">
       <c r="A131" s="1">
         <v>1024071</v>
       </c>
@@ -8864,7 +9044,7 @@
         <v>1024061</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
@@ -8888,10 +9068,10 @@
         <v>0</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="132" spans="1:18">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19">
       <c r="A132" s="1">
         <v>1024072</v>
       </c>
@@ -8899,7 +9079,7 @@
         <v>1024062</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -8923,10 +9103,10 @@
         <v>0</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="133" spans="1:18">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19">
       <c r="A133" s="1">
         <v>1024073</v>
       </c>
@@ -8934,7 +9114,7 @@
         <v>1024063</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -8958,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="134" spans="1:18">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19">
       <c r="A134" s="1">
         <v>1024074</v>
       </c>
@@ -8969,7 +9149,7 @@
         <v>1024064</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -8993,10 +9173,10 @@
         <v>0</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="135" spans="1:18">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19">
       <c r="A135" s="1">
         <v>1024075</v>
       </c>
@@ -9004,7 +9184,7 @@
         <v>1024065</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -9028,10 +9208,10 @@
         <v>0</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="136" spans="1:18">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19">
       <c r="A136" s="1">
         <v>1025101</v>
       </c>
@@ -9039,7 +9219,7 @@
         <v>1025101</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -9057,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="M136" s="1">
         <v>2025101</v>
@@ -9066,13 +9246,13 @@
         <v>0</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="R136" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="137" spans="1:18">
+    <row r="137" spans="1:19">
       <c r="A137" s="1">
         <v>1025102</v>
       </c>
@@ -9080,7 +9260,7 @@
         <v>1025102</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -9098,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="M137" s="1">
         <v>2025102</v>
@@ -9107,13 +9287,13 @@
         <v>0</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="R137" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="138" spans="1:18">
+    <row r="138" spans="1:19">
       <c r="A138" s="1">
         <v>1025103</v>
       </c>
@@ -9121,7 +9301,7 @@
         <v>1025103</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -9139,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="M138" s="1">
         <v>2025103</v>
@@ -9148,13 +9328,13 @@
         <v>0</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="R138" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="139" spans="1:18">
+    <row r="139" spans="1:19">
       <c r="A139" s="1">
         <v>1025104</v>
       </c>
@@ -9162,7 +9342,7 @@
         <v>1025104</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -9180,7 +9360,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="M139" s="1">
         <v>2025104</v>
@@ -9189,13 +9369,13 @@
         <v>0</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="R139" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="140" spans="1:18">
+    <row r="140" spans="1:19">
       <c r="A140" s="1">
         <v>1025105</v>
       </c>
@@ -9203,7 +9383,7 @@
         <v>1025105</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -9221,7 +9401,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="M140" s="1">
         <v>2025105</v>
@@ -9230,13 +9410,13 @@
         <v>0</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="R140" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="141" spans="1:18">
+    <row r="141" spans="1:19">
       <c r="A141" s="1">
         <v>1025106</v>
       </c>
@@ -9244,7 +9424,7 @@
         <v>1025106</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -9262,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="M141" s="1">
         <v>2025106</v>
@@ -9271,13 +9451,13 @@
         <v>0</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="R141" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="142" spans="1:18">
+    <row r="142" spans="1:19">
       <c r="A142" s="1">
         <v>1025201</v>
       </c>
@@ -9285,7 +9465,7 @@
         <v>1025201</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -9303,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="M142" s="1">
         <v>2025201</v>
@@ -9312,13 +9492,13 @@
         <v>0</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="R142" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="143" spans="1:18">
+    <row r="143" spans="1:19">
       <c r="A143" s="1">
         <v>1025202</v>
       </c>
@@ -9326,7 +9506,7 @@
         <v>1025202</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -9344,7 +9524,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="M143" s="1">
         <v>2025202</v>
@@ -9353,13 +9533,13 @@
         <v>0</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="R143" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="144" spans="1:18">
+    <row r="144" spans="1:19">
       <c r="A144" s="1">
         <v>1025203</v>
       </c>
@@ -9367,7 +9547,7 @@
         <v>1025203</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -9385,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="M144" s="1">
         <v>2025203</v>
@@ -9394,7 +9574,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="R144" s="1">
         <v>-1</v>
@@ -9408,7 +9588,7 @@
         <v>1025204</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -9426,7 +9606,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="M145" s="1">
         <v>2025204</v>
@@ -9435,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="R145" s="1">
         <v>-1</v>
@@ -9449,7 +9629,7 @@
         <v>1025205</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -9467,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="M146" s="1">
         <v>2025205</v>
@@ -9476,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="R146" s="1">
         <v>-1</v>
@@ -9490,7 +9670,7 @@
         <v>1025206</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -9508,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="M147" s="1">
         <v>2025206</v>
@@ -9517,7 +9697,7 @@
         <v>0</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="R147" s="1">
         <v>-1</v>
@@ -9531,7 +9711,7 @@
         <v>1025301</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -9549,7 +9729,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="M148" s="1">
         <v>2025301</v>
@@ -9558,7 +9738,7 @@
         <v>0</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="R148" s="1">
         <v>-1</v>
@@ -9572,7 +9752,7 @@
         <v>1025302</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -9590,7 +9770,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="M149" s="1">
         <v>2025302</v>
@@ -9599,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="R149" s="1">
         <v>-1</v>
@@ -9613,7 +9793,7 @@
         <v>1025303</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -9631,7 +9811,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="M150" s="1">
         <v>2025303</v>
@@ -9640,7 +9820,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="R150" s="1">
         <v>-1</v>
@@ -9654,7 +9834,7 @@
         <v>1025304</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -9672,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="M151" s="1">
         <v>2025304</v>
@@ -9681,7 +9861,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="R151" s="1">
         <v>-1</v>
@@ -9695,7 +9875,7 @@
         <v>1025305</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -9713,7 +9893,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="M152" s="1">
         <v>2025305</v>
@@ -9722,7 +9902,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="R152" s="1">
         <v>-1</v>
@@ -9736,7 +9916,7 @@
         <v>1025306</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -9754,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="M153" s="1">
         <v>2025306</v>
@@ -9763,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="R153" s="1">
         <v>-1</v>
@@ -9777,7 +9957,7 @@
         <v>1025401</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -9795,7 +9975,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="M154" s="1">
         <v>2025401</v>
@@ -9804,7 +9984,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="R154" s="1">
         <v>-1</v>
@@ -9818,7 +9998,7 @@
         <v>1025402</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -9836,7 +10016,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="M155" s="1">
         <v>2025402</v>
@@ -9845,7 +10025,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="R155" s="1">
         <v>-1</v>
@@ -9859,7 +10039,7 @@
         <v>1025403</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -9877,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="M156" s="1">
         <v>2025403</v>
@@ -9886,7 +10066,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="R156" s="1">
         <v>-1</v>
@@ -9900,7 +10080,7 @@
         <v>1025404</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -9918,7 +10098,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="M157" s="1">
         <v>2025404</v>
@@ -9927,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="R157" s="1">
         <v>-1</v>
@@ -9941,7 +10121,7 @@
         <v>1025405</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -9959,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="M158" s="1">
         <v>2025405</v>
@@ -9968,7 +10148,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="R158" s="1">
         <v>-1</v>
@@ -9982,7 +10162,7 @@
         <v>1025406</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -10000,7 +10180,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="M159" s="1">
         <v>2025406</v>
@@ -10009,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="R159" s="1">
         <v>-1</v>
@@ -10023,7 +10203,7 @@
         <v>1025501</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -10041,7 +10221,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="M160" s="1">
         <v>2025501</v>
@@ -10050,7 +10230,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="R160" s="1">
         <v>-1</v>
@@ -10064,7 +10244,7 @@
         <v>1025502</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -10082,7 +10262,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="M161" s="1">
         <v>2025502</v>
@@ -10091,7 +10271,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="R161" s="1">
         <v>-1</v>
@@ -10105,7 +10285,7 @@
         <v>1025503</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -10123,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="M162" s="1">
         <v>2025503</v>
@@ -10132,7 +10312,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="R162" s="1">
         <v>-1</v>
@@ -10146,7 +10326,7 @@
         <v>1025504</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -10164,7 +10344,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="M163" s="1">
         <v>2025504</v>
@@ -10173,7 +10353,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="R163" s="1">
         <v>-1</v>
@@ -10187,7 +10367,7 @@
         <v>1025505</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
@@ -10205,7 +10385,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="M164" s="1">
         <v>2025505</v>
@@ -10214,7 +10394,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="R164" s="1">
         <v>-1</v>
@@ -10228,7 +10408,7 @@
         <v>1025506</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
@@ -10246,7 +10426,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="M165" s="1">
         <v>2025506</v>
@@ -10255,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="R165" s="1">
         <v>-1</v>
@@ -10288,7 +10468,7 @@
         <v>1</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M166" s="1">
         <v>2125101</v>
@@ -10331,7 +10511,7 @@
         <v>1</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M167" s="1">
         <v>2125102</v>
@@ -10374,7 +10554,7 @@
         <v>1</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M168" s="1">
         <v>2125103</v>
@@ -10417,7 +10597,7 @@
         <v>1</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M169" s="1">
         <v>2125104</v>
@@ -10460,7 +10640,7 @@
         <v>1</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M170" s="1">
         <v>2125105</v>
@@ -10503,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M171" s="1">
         <v>2125106</v>
@@ -10546,7 +10726,7 @@
         <v>1</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M172" s="1">
         <v>2125201</v>
@@ -10589,7 +10769,7 @@
         <v>1</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M173" s="1">
         <v>2125202</v>
@@ -10632,7 +10812,7 @@
         <v>1</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M174" s="1">
         <v>2125203</v>
@@ -10675,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M175" s="1">
         <v>2125204</v>
@@ -10718,7 +10898,7 @@
         <v>1</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M176" s="1">
         <v>2125205</v>
@@ -10761,7 +10941,7 @@
         <v>1</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M177" s="1">
         <v>2125206</v>
@@ -10804,7 +10984,7 @@
         <v>1</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M178" s="1">
         <v>2125301</v>
@@ -10847,7 +11027,7 @@
         <v>1</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M179" s="1">
         <v>2125302</v>
@@ -10890,7 +11070,7 @@
         <v>1</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M180" s="1">
         <v>2125303</v>
@@ -10933,7 +11113,7 @@
         <v>1</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M181" s="1">
         <v>2125304</v>
@@ -10976,7 +11156,7 @@
         <v>1</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M182" s="1">
         <v>2125305</v>
@@ -11019,7 +11199,7 @@
         <v>1</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M183" s="1">
         <v>2125306</v>
@@ -11062,7 +11242,7 @@
         <v>1</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M184" s="1">
         <v>2125401</v>
@@ -11105,7 +11285,7 @@
         <v>1</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M185" s="1">
         <v>2125402</v>
@@ -11148,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M186" s="1">
         <v>2125403</v>
@@ -11191,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M187" s="1">
         <v>2125404</v>
@@ -11234,7 +11414,7 @@
         <v>1</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M188" s="1">
         <v>2125405</v>
@@ -11277,7 +11457,7 @@
         <v>1</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M189" s="1">
         <v>2125406</v>
@@ -11320,7 +11500,7 @@
         <v>1</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M190" s="1">
         <v>2125501</v>
@@ -11363,7 +11543,7 @@
         <v>1</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M191" s="1">
         <v>2125502</v>
@@ -11406,7 +11586,7 @@
         <v>1</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M192" s="1">
         <v>2125503</v>
@@ -11449,7 +11629,7 @@
         <v>1</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M193" s="1">
         <v>2125504</v>
@@ -11492,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M194" s="1">
         <v>2125505</v>
@@ -11535,7 +11715,7 @@
         <v>1</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="M195" s="1">
         <v>2125506</v>
@@ -11559,7 +11739,7 @@
         <v>1026001</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="E196" s="1">
         <v>2</v>
@@ -11577,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="M196" s="1">
         <v>2026001</v>
@@ -11586,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="O196" s="1" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="R196" s="1">
         <v>-1</v>
@@ -11600,7 +11780,7 @@
         <v>1026002</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="E197" s="1">
         <v>2</v>
@@ -11618,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="M197" s="1">
         <v>2026002</v>
@@ -11627,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="O197" s="1" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="R197" s="1">
         <v>-1</v>
@@ -11641,7 +11821,7 @@
         <v>1026101</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="E198" s="1">
         <v>2</v>
@@ -11668,7 +11848,7 @@
         <v>0</v>
       </c>
       <c r="O198" s="1" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="R198" s="1">
         <v>-1</v>
@@ -11682,7 +11862,7 @@
         <v>1026102</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="E199" s="1">
         <v>2</v>
@@ -11709,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="O199" s="1" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="R199" s="1">
         <v>-1</v>
@@ -11723,7 +11903,7 @@
         <v>1026201</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="E200" s="1">
         <v>2</v>
@@ -11750,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="O200" s="1" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="R200" s="1">
         <v>-1</v>
@@ -11764,7 +11944,7 @@
         <v>1026202</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="E201" s="1">
         <v>2</v>
@@ -11791,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="O201" s="1" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="R201" s="1">
         <v>-1</v>
@@ -11805,7 +11985,7 @@
         <v>1026301</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="E202" s="1">
         <v>2</v>
@@ -11832,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="O202" s="1" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="R202" s="1">
         <v>-1</v>
@@ -11846,7 +12026,7 @@
         <v>1026302</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="E203" s="1">
         <v>2</v>
@@ -11873,7 +12053,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="R203" s="1">
         <v>-1</v>
@@ -11887,7 +12067,7 @@
         <v>1026401</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="E204" s="1">
         <v>2</v>
@@ -11914,7 +12094,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="R204" s="1">
         <v>-1</v>
@@ -11928,7 +12108,7 @@
         <v>1026402</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="E205" s="1">
         <v>2</v>
@@ -11955,7 +12135,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="R205" s="1">
         <v>-1</v>
@@ -11969,7 +12149,7 @@
         <v>1027001</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -11987,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="M206" s="1">
         <v>2027001</v>
@@ -11996,7 +12176,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="R206" s="1">
         <v>-1</v>
@@ -12010,7 +12190,7 @@
         <v>1027002</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -12037,7 +12217,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="R207" s="1">
         <v>-1</v>
@@ -12051,7 +12231,7 @@
         <v>1027101</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -12078,7 +12258,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="R208" s="1">
         <v>-1</v>
@@ -12092,7 +12272,7 @@
         <v>1027102</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -12119,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>344</v>
+        <v>374</v>
       </c>
       <c r="R209" s="1">
         <v>-1</v>
@@ -12133,7 +12313,7 @@
         <v>1027201</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -12160,7 +12340,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="R210" s="1">
         <v>-1</v>
@@ -12174,7 +12354,7 @@
         <v>1027202</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -12201,7 +12381,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="R211" s="1">
         <v>-1</v>
@@ -12215,7 +12395,7 @@
         <v>1027301</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -12242,7 +12422,7 @@
         <v>0</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
       <c r="R212" s="1">
         <v>-1</v>
@@ -12256,7 +12436,7 @@
         <v>1027302</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -12274,7 +12454,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>349</v>
+        <v>379</v>
       </c>
       <c r="M213" s="1">
         <v>2027302</v>
@@ -12283,7 +12463,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="R213" s="1">
         <v>-1</v>
@@ -12297,7 +12477,7 @@
         <v>1027401</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -12324,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="R214" s="1">
         <v>-1</v>
@@ -12338,7 +12518,7 @@
         <v>1027402</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -12356,7 +12536,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="M215" s="1">
         <v>2027402</v>
@@ -12365,7 +12545,7 @@
         <v>0</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="R215" s="1">
         <v>-1</v>
@@ -12379,7 +12559,7 @@
         <v>1028001</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -12406,7 +12586,7 @@
         <v>0</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="R216" s="1">
         <v>-1</v>
@@ -12420,7 +12600,7 @@
         <v>1028002</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -12447,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
       <c r="R217" s="1">
         <v>-1</v>
@@ -12461,7 +12641,7 @@
         <v>1028101</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -12488,7 +12668,7 @@
         <v>0</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="R218" s="1">
         <v>-1</v>
@@ -12502,7 +12682,7 @@
         <v>1028102</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -12529,7 +12709,7 @@
         <v>0</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="R219" s="1">
         <v>-1</v>
@@ -12543,7 +12723,7 @@
         <v>1028201</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -12570,7 +12750,7 @@
         <v>0</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="R220" s="1">
         <v>-1</v>
@@ -12584,7 +12764,7 @@
         <v>1028202</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -12611,7 +12791,7 @@
         <v>0</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="R221" s="1">
         <v>-1</v>
@@ -12625,7 +12805,7 @@
         <v>1028301</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -12652,7 +12832,7 @@
         <v>0</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="R222" s="1">
         <v>-1</v>
@@ -12666,7 +12846,7 @@
         <v>1028302</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -12693,7 +12873,7 @@
         <v>0</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="R223" s="1">
         <v>-1</v>
@@ -12707,7 +12887,7 @@
         <v>1028401</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -12734,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="R224" s="1">
         <v>-1</v>
@@ -12748,7 +12928,7 @@
         <v>1028402</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -12775,7 +12955,7 @@
         <v>0</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="R225" s="1">
         <v>-1</v>
@@ -12851,7 +13031,7 @@
         <v>1</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M227" s="1">
         <v>2126002</v>
@@ -12894,7 +13074,7 @@
         <v>1</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M228" s="1">
         <v>2126101</v>
@@ -12937,7 +13117,7 @@
         <v>1</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M229" s="1">
         <v>2126102</v>
@@ -12980,7 +13160,7 @@
         <v>1</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M230" s="1">
         <v>2126201</v>
@@ -13023,7 +13203,7 @@
         <v>1</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M231" s="1">
         <v>2126202</v>
@@ -13066,7 +13246,7 @@
         <v>1</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M232" s="1">
         <v>2126301</v>
@@ -13109,7 +13289,7 @@
         <v>1</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M233" s="1">
         <v>2126302</v>
@@ -13152,7 +13332,7 @@
         <v>1</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M234" s="1">
         <v>2126401</v>
@@ -13195,7 +13375,7 @@
         <v>1</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M235" s="1">
         <v>2126402</v>
@@ -13238,7 +13418,7 @@
         <v>1</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M236" s="1">
         <v>2127001</v>
@@ -13281,7 +13461,7 @@
         <v>1</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M237" s="1">
         <v>2127002</v>
@@ -13324,7 +13504,7 @@
         <v>1</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M238" s="1">
         <v>2127101</v>
@@ -13367,7 +13547,7 @@
         <v>1</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M239" s="1">
         <v>2127102</v>
@@ -13410,7 +13590,7 @@
         <v>1</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M240" s="1">
         <v>2127201</v>
@@ -13453,7 +13633,7 @@
         <v>1</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M241" s="1">
         <v>2127202</v>
@@ -13496,7 +13676,7 @@
         <v>1</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M242" s="1">
         <v>2127301</v>
@@ -13539,7 +13719,7 @@
         <v>1</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M243" s="1">
         <v>2127302</v>
@@ -13582,7 +13762,7 @@
         <v>1</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M244" s="1">
         <v>2127401</v>
@@ -13625,7 +13805,7 @@
         <v>1</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M245" s="1">
         <v>2127402</v>
@@ -13668,7 +13848,7 @@
         <v>1</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M246" s="1">
         <v>2128001</v>
@@ -13711,7 +13891,7 @@
         <v>1</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M247" s="1">
         <v>2128002</v>
@@ -13754,7 +13934,7 @@
         <v>1</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M248" s="1">
         <v>2128101</v>
@@ -13797,7 +13977,7 @@
         <v>1</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M249" s="1">
         <v>2128102</v>
@@ -13840,7 +14020,7 @@
         <v>1</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M250" s="1">
         <v>2128201</v>
@@ -13883,7 +14063,7 @@
         <v>1</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M251" s="1">
         <v>2128202</v>
@@ -13926,7 +14106,7 @@
         <v>1</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M252" s="1">
         <v>2128301</v>
@@ -13969,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M253" s="1">
         <v>2128302</v>
@@ -14012,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M254" s="1">
         <v>2128401</v>
@@ -14055,7 +14235,7 @@
         <v>1</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="M255" s="1">
         <v>2128402</v>
@@ -14079,7 +14259,7 @@
         <v>1130001</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="E256" s="1">
         <v>2</v>
@@ -14097,7 +14277,7 @@
         <v>1</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>365</v>
+        <v>395</v>
       </c>
       <c r="M256" s="1">
         <v>2130001</v>
@@ -14106,7 +14286,7 @@
         <v>0</v>
       </c>
       <c r="O256" s="1" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="R256" s="1">
         <v>999999</v>
@@ -14120,7 +14300,7 @@
         <v>1130002</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>367</v>
+        <v>397</v>
       </c>
       <c r="E257" s="1">
         <v>1</v>
@@ -14138,7 +14318,7 @@
         <v>1</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="M257" s="1">
         <v>2130002</v>
@@ -14147,7 +14327,7 @@
         <v>0</v>
       </c>
       <c r="O257" s="1" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="R257" s="1">
         <v>999999</v>
@@ -14161,7 +14341,7 @@
         <v>1130003</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="E258" s="1">
         <v>1</v>
@@ -14179,7 +14359,7 @@
         <v>1</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="M258" s="1">
         <v>2130003</v>
@@ -14188,7 +14368,7 @@
         <v>0</v>
       </c>
       <c r="O258" s="1" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="R258" s="1">
         <v>999999</v>
@@ -14202,7 +14382,7 @@
         <v>1130004</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="E259" s="1">
         <v>1</v>
@@ -14220,7 +14400,7 @@
         <v>1</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="M259" s="1">
         <v>2130004</v>
@@ -14229,7 +14409,7 @@
         <v>0</v>
       </c>
       <c r="O259" s="1" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="R259" s="1">
         <v>999999</v>
@@ -14243,7 +14423,7 @@
         <v>1130005</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
       <c r="E260" s="1">
         <v>1</v>
@@ -14261,7 +14441,7 @@
         <v>1</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>377</v>
+        <v>407</v>
       </c>
       <c r="M260" s="1">
         <v>2130005</v>
@@ -14270,7 +14450,7 @@
         <v>0</v>
       </c>
       <c r="O260" s="1" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="R260" s="1">
         <v>999999</v>
@@ -14284,7 +14464,7 @@
         <v>1130006</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="E261" s="1">
         <v>1</v>
@@ -14302,7 +14482,7 @@
         <v>1</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="M261" s="1">
         <v>2130006</v>
@@ -14311,7 +14491,7 @@
         <v>0</v>
       </c>
       <c r="O261" s="1" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="R261" s="1">
         <v>999999</v>
@@ -14325,7 +14505,7 @@
         <v>1131001</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="E262" s="1">
         <v>2</v>
@@ -14349,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="O262" s="1" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
     </row>
     <row r="263" spans="1:18">
@@ -14360,7 +14540,7 @@
         <v>1131002</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>384</v>
+        <v>414</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -14384,7 +14564,7 @@
         <v>0</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
     </row>
     <row r="264" spans="1:18">
@@ -14395,7 +14575,7 @@
         <v>1131003</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="E264" s="1">
         <v>2</v>
@@ -14419,7 +14599,7 @@
         <v>0</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
     </row>
     <row r="265" spans="1:18">
@@ -14430,7 +14610,7 @@
         <v>1131004</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>388</v>
+        <v>418</v>
       </c>
       <c r="E265" s="1">
         <v>2</v>
@@ -14454,7 +14634,7 @@
         <v>0</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
     </row>
     <row r="266" spans="1:18">
@@ -14465,7 +14645,7 @@
         <v>1131005</v>
       </c>
       <c r="D266" s="14" t="s">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="E266" s="1">
         <v>2</v>
@@ -14489,7 +14669,7 @@
         <v>0</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
     </row>
     <row r="267" spans="1:18">
@@ -14500,7 +14680,7 @@
         <v>1131006</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="E267" s="1">
         <v>2</v>
@@ -14524,7 +14704,7 @@
         <v>0</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
     </row>
     <row r="268" spans="1:18">
@@ -14535,7 +14715,7 @@
         <v>1131101</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="E268" s="1">
         <v>2</v>
@@ -14559,7 +14739,7 @@
         <v>0</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
     </row>
     <row r="269" spans="1:18">
@@ -14570,7 +14750,7 @@
         <v>1131102</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -14594,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
     </row>
     <row r="270" spans="1:18">
@@ -14605,7 +14785,7 @@
         <v>1131103</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>396</v>
+        <v>426</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -14629,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
     </row>
     <row r="271" spans="1:18">
@@ -14640,7 +14820,7 @@
         <v>1131104</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -14664,7 +14844,7 @@
         <v>0</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
     </row>
     <row r="272" spans="1:18">
@@ -14675,7 +14855,7 @@
         <v>1131105</v>
       </c>
       <c r="D272" s="14" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -14699,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
     </row>
     <row r="273" spans="1:15">
@@ -14710,7 +14890,7 @@
         <v>1131106</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -14734,7 +14914,7 @@
         <v>0</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
     </row>
     <row r="274" spans="1:15">
@@ -14745,7 +14925,7 @@
         <v>1131201</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -14769,7 +14949,7 @@
         <v>0</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
     </row>
     <row r="275" spans="1:15">
@@ -14780,7 +14960,7 @@
         <v>1131202</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>401</v>
+        <v>431</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -14804,7 +14984,7 @@
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
     </row>
     <row r="276" spans="1:15">
@@ -14815,7 +14995,7 @@
         <v>1131203</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -14839,7 +15019,7 @@
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
     </row>
     <row r="277" spans="1:15">
@@ -14850,7 +15030,7 @@
         <v>1131204</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>403</v>
+        <v>433</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -14874,7 +15054,7 @@
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
     </row>
     <row r="278" spans="1:15">
@@ -14885,7 +15065,7 @@
         <v>1131205</v>
       </c>
       <c r="D278" s="14" t="s">
-        <v>404</v>
+        <v>434</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -14909,7 +15089,7 @@
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
     </row>
     <row r="279" spans="1:15">
@@ -14920,7 +15100,7 @@
         <v>1131206</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -14944,7 +15124,7 @@
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
     </row>
     <row r="280" spans="1:15">
@@ -14955,7 +15135,7 @@
         <v>1131301</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -14979,7 +15159,7 @@
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
     </row>
     <row r="281" spans="1:15">
@@ -14990,7 +15170,7 @@
         <v>1131302</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15014,7 +15194,7 @@
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
     </row>
     <row r="282" spans="1:15">
@@ -15025,7 +15205,7 @@
         <v>1131303</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15049,7 +15229,7 @@
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
     </row>
     <row r="283" spans="1:15">
@@ -15060,7 +15240,7 @@
         <v>1131304</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15084,7 +15264,7 @@
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
     </row>
     <row r="284" spans="1:15">
@@ -15095,7 +15275,7 @@
         <v>1131305</v>
       </c>
       <c r="D284" s="14" t="s">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15119,7 +15299,7 @@
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
     </row>
     <row r="285" spans="1:15">
@@ -15130,7 +15310,7 @@
         <v>1131306</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15154,7 +15334,7 @@
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
     </row>
     <row r="286" spans="1:15">
@@ -15165,7 +15345,7 @@
         <v>1131401</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15189,7 +15369,7 @@
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
     </row>
     <row r="287" spans="1:15">
@@ -15200,7 +15380,7 @@
         <v>1131402</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -15224,7 +15404,7 @@
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
     </row>
     <row r="288" spans="1:15">
@@ -15235,7 +15415,7 @@
         <v>1131403</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>414</v>
+        <v>444</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -15259,7 +15439,7 @@
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>387</v>
+        <v>417</v>
       </c>
     </row>
     <row r="289" spans="1:18">
@@ -15270,7 +15450,7 @@
         <v>1131404</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -15294,7 +15474,7 @@
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>389</v>
+        <v>419</v>
       </c>
     </row>
     <row r="290" spans="1:18">
@@ -15305,7 +15485,7 @@
         <v>1131405</v>
       </c>
       <c r="D290" s="14" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -15329,7 +15509,7 @@
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>391</v>
+        <v>421</v>
       </c>
     </row>
     <row r="291" spans="1:18">
@@ -15340,7 +15520,7 @@
         <v>1131406</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -15364,7 +15544,7 @@
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>393</v>
+        <v>423</v>
       </c>
     </row>
     <row r="292" spans="1:18">
@@ -15375,7 +15555,7 @@
         <v>1140001</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -15393,7 +15573,7 @@
         <v>0</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>419</v>
+        <v>449</v>
       </c>
       <c r="M292" s="1">
         <v>2140001</v>
@@ -15402,7 +15582,7 @@
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row r="293" spans="1:18">
@@ -15413,7 +15593,7 @@
         <v>1140002</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -15431,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="M293" s="1">
         <v>2140002</v>
@@ -15440,7 +15620,7 @@
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>423</v>
+        <v>453</v>
       </c>
     </row>
     <row r="294" spans="1:18">
@@ -15451,7 +15631,7 @@
         <v>1140003</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -15469,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="M294" s="1">
         <v>2140003</v>
@@ -15478,7 +15658,7 @@
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>426</v>
+        <v>456</v>
       </c>
     </row>
     <row r="295" spans="1:18">
@@ -15489,7 +15669,7 @@
         <v>1140004</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -15507,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="M295" s="1">
         <v>2140004</v>
@@ -15516,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>429</v>
+        <v>459</v>
       </c>
     </row>
     <row r="296" spans="1:18">
@@ -15527,7 +15707,7 @@
         <v>1140005</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -15545,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="M296" s="1">
         <v>2140005</v>
@@ -15554,7 +15734,7 @@
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
     </row>
     <row r="297" spans="1:18">
@@ -15565,7 +15745,7 @@
         <v>1140006</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -15583,7 +15763,7 @@
         <v>0</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="M297" s="1">
         <v>2140006</v>
@@ -15592,7 +15772,7 @@
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
     </row>
     <row r="298" spans="1:18">
@@ -15603,7 +15783,7 @@
         <v>1150001</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -15621,7 +15801,7 @@
         <v>0</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="M298" s="1">
         <v>2150001</v>
@@ -15645,7 +15825,7 @@
         <v>1150002</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -15663,7 +15843,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="M299" s="1">
         <v>2150002</v>
@@ -15687,7 +15867,7 @@
         <v>1150003</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -15705,7 +15885,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="M300" s="1">
         <v>2150003</v>
@@ -15729,7 +15909,7 @@
         <v>1150004</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -15747,7 +15927,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="M301" s="1">
         <v>2150004</v>
@@ -15771,7 +15951,7 @@
         <v>1150005</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -15789,7 +15969,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="M302" s="1">
         <v>2150005</v>
@@ -15813,7 +15993,7 @@
         <v>1150006</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -15831,7 +16011,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="M303" s="1">
         <v>2150006</v>
@@ -15855,7 +16035,7 @@
         <v>1150007</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -15873,7 +16053,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="M304" s="1">
         <v>2150007</v>
@@ -15897,7 +16077,7 @@
         <v>1150008</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -15915,7 +16095,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="M305" s="1">
         <v>2150008</v>
@@ -15939,7 +16119,7 @@
         <v>1150009</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -15957,7 +16137,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="M306" s="1">
         <v>2150009</v>
@@ -15981,7 +16161,7 @@
         <v>1150010</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -15999,7 +16179,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="M307" s="1">
         <v>2150010</v>
@@ -16023,7 +16203,7 @@
         <v>1150011</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16041,7 +16221,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="M308" s="1">
         <v>2150011</v>
@@ -16065,7 +16245,7 @@
         <v>1150012</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16083,7 +16263,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="M309" s="1">
         <v>2150012</v>
@@ -16107,7 +16287,7 @@
         <v>1150013</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16125,7 +16305,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="M310" s="1">
         <v>2150013</v>
@@ -16149,7 +16329,7 @@
         <v>1150014</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -16167,7 +16347,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="M311" s="1">
         <v>2150014</v>
@@ -16191,7 +16371,7 @@
         <v>1150015</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -16209,7 +16389,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="M312" s="1">
         <v>2150015</v>
@@ -16233,7 +16413,7 @@
         <v>1150016</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -16251,7 +16431,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="M313" s="1">
         <v>2150016</v>
@@ -16275,7 +16455,7 @@
         <v>1150017</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -16293,7 +16473,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="M314" s="1">
         <v>2150017</v>
@@ -16317,7 +16497,7 @@
         <v>1150018</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -16335,7 +16515,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="M315" s="1">
         <v>2150018</v>
@@ -16359,7 +16539,7 @@
         <v>1150019</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -16377,7 +16557,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="M316" s="1">
         <v>2150019</v>
@@ -16401,7 +16581,7 @@
         <v>1150020</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -16419,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="M317" s="1">
         <v>2150020</v>
@@ -16443,7 +16623,7 @@
         <v>1150021</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -16461,7 +16641,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
       <c r="M318" s="1">
         <v>2150021</v>
@@ -16485,7 +16665,7 @@
         <v>1150022</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -16503,7 +16683,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="M319" s="1">
         <v>2150022</v>
@@ -16527,7 +16707,7 @@
         <v>1150023</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -16545,7 +16725,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="M320" s="1">
         <v>2150023</v>
@@ -16569,7 +16749,7 @@
         <v>1150024</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -16587,7 +16767,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="M321" s="1">
         <v>2150024</v>
@@ -16611,7 +16791,7 @@
         <v>1150025</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -16629,7 +16809,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="M322" s="1">
         <v>2150025</v>
@@ -16653,7 +16833,7 @@
         <v>1150026</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -16671,7 +16851,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="M323" s="1">
         <v>2150026</v>
@@ -16695,7 +16875,7 @@
         <v>1150027</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -16713,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="M324" s="1">
         <v>2150027</v>
@@ -16737,7 +16917,7 @@
         <v>1150028</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -16755,7 +16935,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="M325" s="1">
         <v>2150028</v>
@@ -16779,7 +16959,7 @@
         <v>1150029</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -16797,7 +16977,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="M326" s="1">
         <v>2150029</v>
@@ -16821,7 +17001,7 @@
         <v>1150030</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -16839,7 +17019,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="M327" s="1">
         <v>2150030</v>
@@ -16863,7 +17043,7 @@
         <v>1150031</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -16881,7 +17061,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="M328" s="1">
         <v>2150031</v>
@@ -16905,7 +17085,7 @@
         <v>1150032</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -16923,7 +17103,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>499</v>
+        <v>529</v>
       </c>
       <c r="M329" s="1">
         <v>2150032</v>
@@ -16947,7 +17127,7 @@
         <v>1150033</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -16965,7 +17145,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="M330" s="1">
         <v>2150033</v>
@@ -16989,7 +17169,7 @@
         <v>1150034</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17007,7 +17187,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="M331" s="1">
         <v>2150034</v>
@@ -17031,7 +17211,7 @@
         <v>1150035</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17049,7 +17229,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="M332" s="1">
         <v>2150035</v>
@@ -17073,7 +17253,7 @@
         <v>1150036</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17091,7 +17271,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="M333" s="1">
         <v>2150036</v>
@@ -17115,7 +17295,7 @@
         <v>1150037</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -17133,7 +17313,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="M334" s="1">
         <v>2150037</v>
@@ -17157,7 +17337,7 @@
         <v>1150038</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -17175,7 +17355,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>511</v>
+        <v>541</v>
       </c>
       <c r="M335" s="1">
         <v>2150038</v>
@@ -17199,7 +17379,7 @@
         <v>1150039</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -17217,7 +17397,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>513</v>
+        <v>543</v>
       </c>
       <c r="M336" s="1">
         <v>2150039</v>
@@ -17241,7 +17421,7 @@
         <v>1150040</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -17259,7 +17439,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="M337" s="1">
         <v>2150040</v>
@@ -17283,7 +17463,7 @@
         <v>1150041</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -17301,7 +17481,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
       <c r="M338" s="1">
         <v>2150041</v>
@@ -17325,7 +17505,7 @@
         <v>1150042</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -17343,7 +17523,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="M339" s="1">
         <v>2150042</v>
@@ -17367,7 +17547,7 @@
         <v>1150043</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -17385,7 +17565,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="M340" s="1">
         <v>2150043</v>
@@ -17409,7 +17589,7 @@
         <v>1150044</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -17427,7 +17607,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="M341" s="1">
         <v>2150044</v>
@@ -17451,7 +17631,7 @@
         <v>1150045</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -17469,7 +17649,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="M342" s="1">
         <v>2150045</v>
@@ -17493,7 +17673,7 @@
         <v>1150046</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -17511,7 +17691,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="M343" s="1">
         <v>2150046</v>
@@ -17535,7 +17715,7 @@
         <v>1150047</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -17553,7 +17733,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="M344" s="1">
         <v>2150047</v>
@@ -17577,7 +17757,7 @@
         <v>1150048</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -17595,7 +17775,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="M345" s="1">
         <v>2150048</v>
@@ -17619,7 +17799,7 @@
         <v>1150049</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -17637,7 +17817,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="M346" s="1">
         <v>2150049</v>
@@ -17661,7 +17841,7 @@
         <v>1150050</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>534</v>
+        <v>564</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -17679,7 +17859,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>535</v>
+        <v>565</v>
       </c>
       <c r="M347" s="1">
         <v>2150050</v>
@@ -17703,7 +17883,7 @@
         <v>1150051</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -17721,7 +17901,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>537</v>
+        <v>567</v>
       </c>
       <c r="M348" s="1">
         <v>2150051</v>
@@ -17745,7 +17925,7 @@
         <v>1150052</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -17763,7 +17943,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="M349" s="1">
         <v>2150052</v>
@@ -17787,7 +17967,7 @@
         <v>1150053</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -17805,7 +17985,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="M350" s="1">
         <v>2150053</v>
@@ -17829,7 +18009,7 @@
         <v>1150054</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -17847,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="M351" s="1">
         <v>2150054</v>
@@ -17871,7 +18051,7 @@
         <v>1150055</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -17889,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="M352" s="1">
         <v>2150055</v>
@@ -17913,7 +18093,7 @@
         <v>1150056</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -17931,7 +18111,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="M353" s="1">
         <v>2150056</v>
@@ -17955,7 +18135,7 @@
         <v>1150057</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -17973,7 +18153,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="M354" s="1">
         <v>2150057</v>
@@ -17997,7 +18177,7 @@
         <v>1150058</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18015,7 +18195,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="M355" s="1">
         <v>2150058</v>
@@ -18039,7 +18219,7 @@
         <v>1150059</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18057,7 +18237,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
       <c r="M356" s="1">
         <v>2150059</v>
@@ -18081,7 +18261,7 @@
         <v>1150060</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18099,7 +18279,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="M357" s="1">
         <v>2150060</v>
@@ -18123,7 +18303,7 @@
         <v>1150061</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -18141,7 +18321,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="M358" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -6742,7 +6742,7 @@
         <v>201</v>
       </c>
       <c r="E75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>55</v>
@@ -6786,7 +6786,7 @@
         <v>204</v>
       </c>
       <c r="E76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>55</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="589">
   <si>
     <t>道具ID</t>
   </si>
@@ -974,6 +974,9 @@
   </si>
   <si>
     <t>贡献值</t>
+  </si>
+  <si>
+    <t>lm_sc_gxz.png</t>
   </si>
   <si>
     <t>联盟商店兑换商品的道具</t>
@@ -2349,12 +2352,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -6634,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>49</v>
+        <v>196</v>
       </c>
       <c r="M72" s="1">
         <v>2024012</v>
@@ -6643,7 +6646,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R72" s="1">
         <v>-1</v>
@@ -6657,7 +6660,7 @@
         <v>1024013</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -6684,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R73" s="1">
         <v>999999</v>
@@ -6698,7 +6701,7 @@
         <v>1024014</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -6725,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R74" s="1">
         <v>999999</v>
@@ -6739,7 +6742,7 @@
         <v>1024015</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -6766,13 +6769,13 @@
         <v>0</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R75" s="1">
         <v>999999</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -6783,7 +6786,7 @@
         <v>1024016</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -6810,13 +6813,13 @@
         <v>0</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R76" s="1">
         <v>999999</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -6827,7 +6830,7 @@
         <v>1024017</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -6854,7 +6857,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R77" s="1">
         <v>999999</v>
@@ -6868,7 +6871,7 @@
         <v>1024018</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -6886,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M78" s="1">
         <v>2024018</v>
@@ -6895,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="R78" s="1">
         <v>-1</v>
@@ -6909,7 +6912,7 @@
         <v>1024019</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
@@ -6927,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M79" s="1">
         <v>2024019</v>
@@ -6936,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -6947,7 +6950,7 @@
         <v>1024020</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -6965,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M80" s="1">
         <v>2024020</v>
@@ -6974,7 +6977,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -6985,7 +6988,7 @@
         <v>1024021</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -7003,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M81" s="1">
         <v>2024021</v>
@@ -7012,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -7023,7 +7026,7 @@
         <v>1024022</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -7041,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M82" s="1">
         <v>2024022</v>
@@ -7050,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -7061,7 +7064,7 @@
         <v>1024023</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -7079,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M83" s="1">
         <v>2024023</v>
@@ -7088,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" ht="17.25" spans="1:18">
@@ -7099,7 +7102,7 @@
         <v>1024024</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -7123,7 +7126,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M84" s="1">
         <v>2024024</v>
@@ -7132,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="R84" s="1">
         <v>999999</v>
@@ -7146,7 +7149,7 @@
         <v>1024024</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -7170,7 +7173,7 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M85" s="1">
         <v>2024025</v>
@@ -7179,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R85" s="1">
         <v>999999</v>
@@ -7193,7 +7196,7 @@
         <v>1024024</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
@@ -7217,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M86" s="1">
         <v>2024026</v>
@@ -7226,7 +7229,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R86" s="1">
         <v>999999</v>
@@ -7240,7 +7243,7 @@
         <v>1024024</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -7264,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M87" s="1">
         <v>2024027</v>
@@ -7273,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="R87" s="1">
         <v>999999</v>
@@ -7287,7 +7290,7 @@
         <v>1024024</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -7311,7 +7314,7 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M88" s="1">
         <v>2024028</v>
@@ -7320,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="R88" s="1">
         <v>999999</v>
@@ -7334,7 +7337,7 @@
         <v>1024024</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -7358,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M89" s="1">
         <v>2024029</v>
@@ -7367,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R89" s="1">
         <v>999999</v>
@@ -7381,7 +7384,7 @@
         <v>1024024</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -7405,7 +7408,7 @@
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M90" s="1">
         <v>2024030</v>
@@ -7414,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R90" s="1">
         <v>999999</v>
@@ -7428,7 +7431,7 @@
         <v>1024024</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
@@ -7452,7 +7455,7 @@
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M91" s="1">
         <v>2024031</v>
@@ -7461,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="R91" s="1">
         <v>999999</v>
@@ -7475,7 +7478,7 @@
         <v>1024024</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -7499,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M92" s="1">
         <v>2024032</v>
@@ -7508,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="R92" s="1">
         <v>999999</v>
@@ -7522,7 +7525,7 @@
         <v>1024024</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
@@ -7546,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M93" s="1">
         <v>2024033</v>
@@ -7555,7 +7558,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R93" s="1">
         <v>999999</v>
@@ -7569,7 +7572,7 @@
         <v>1024025</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -7593,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="R94" s="1">
         <v>999999</v>
@@ -7607,7 +7610,7 @@
         <v>1024026</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -7631,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R95" s="1">
         <v>999999</v>
@@ -7645,7 +7648,7 @@
         <v>1024027</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -7669,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R96" s="1">
         <v>999999</v>
@@ -7683,7 +7686,7 @@
         <v>1024028</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -7707,7 +7710,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R97" s="1">
         <v>999999</v>
@@ -7721,7 +7724,7 @@
         <v>1024029</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -7745,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="R98" s="1">
         <v>999999</v>
@@ -7759,7 +7762,7 @@
         <v>1024030</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -7783,7 +7786,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R99" s="1">
         <v>999999</v>
@@ -7797,7 +7800,7 @@
         <v>1024024</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -7821,7 +7824,7 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M100" s="1">
         <v>2024040</v>
@@ -7830,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R100" s="1">
         <v>999999</v>
@@ -7873,7 +7876,7 @@
         <v>使用该道具后可以指定生成游客街头潮人</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -7913,7 +7916,7 @@
         <v>使用该道具后可以指定生成游客复古绅士</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -7953,7 +7956,7 @@
         <v>使用该道具后可以指定生成游客酷盖少年</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -7993,7 +7996,7 @@
         <v>使用该道具后可以指定生成游客潮流先锋</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -8033,7 +8036,7 @@
         <v>使用该道具后可以指定生成游客时尚教主</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -8073,7 +8076,7 @@
         <v>使用该道具后可以指定生成游客街拍达人</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -8113,7 +8116,7 @@
         <v>使用该道具后可以指定生成游客运动健将</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -8153,7 +8156,7 @@
         <v>使用该道具后可以指定生成游客跑酷少年</v>
       </c>
       <c r="S108" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -8193,7 +8196,7 @@
         <v>使用该道具后可以指定生成游客滑板高手</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -8233,7 +8236,7 @@
         <v>使用该道具后可以指定生成游客甜心辣妹</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -8273,7 +8276,7 @@
         <v>使用该道具后可以指定生成游客活力少女</v>
       </c>
       <c r="S111" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -8313,7 +8316,7 @@
         <v>使用该道具后可以指定生成游客优雅女神</v>
       </c>
       <c r="S112" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -8353,7 +8356,7 @@
         <v>使用该道具后可以指定生成游客健身狂魔</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -8393,7 +8396,7 @@
         <v>使用该道具后可以指定生成游客单车骑士</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -8433,7 +8436,7 @@
         <v>使用该道具后可以指定生成游客登山行者</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -8473,7 +8476,7 @@
         <v>使用该道具后可以指定生成游客文艺青年</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -8513,7 +8516,7 @@
         <v>使用该道具后可以指定生成游客书香少女</v>
       </c>
       <c r="S117" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -8553,7 +8556,7 @@
         <v>使用该道具后可以指定生成游客民谣歌手</v>
       </c>
       <c r="S118" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -8593,7 +8596,7 @@
         <v>使用该道具后可以指定生成游客马拉松客</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -8633,7 +8636,7 @@
         <v>使用该道具后可以指定生成游客极限玩家</v>
       </c>
       <c r="S120" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -8673,7 +8676,7 @@
         <v>使用该道具后可以指定生成游客科技极客</v>
       </c>
       <c r="S121" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -8713,7 +8716,7 @@
         <v>使用该道具后可以指定生成游客独立画家</v>
       </c>
       <c r="S122" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -8753,7 +8756,7 @@
         <v>使用该道具后可以指定生成游客浪漫诗人</v>
       </c>
       <c r="S123" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -8793,7 +8796,7 @@
         <v>使用该道具后可以指定生成游客古典乐迷</v>
       </c>
       <c r="S124" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -8833,7 +8836,7 @@
         <v>使用该道具后可以指定生成游客创业新贵</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -8873,7 +8876,7 @@
         <v>使用该道具后可以指定生成游客摸金校尉</v>
       </c>
       <c r="S126" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -8913,7 +8916,7 @@
         <v>使用该道具后可以指定生成游客氪金大佬</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -8953,7 +8956,7 @@
         <v>使用该道具后可以指定生成游客穿搭博主</v>
       </c>
       <c r="S128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -8993,7 +8996,7 @@
         <v>使用该道具后可以指定生成游客美妆新秀</v>
       </c>
       <c r="S129" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -9033,7 +9036,7 @@
         <v>使用该道具后可以指定生成游客高定女王</v>
       </c>
       <c r="S130" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -9044,7 +9047,7 @@
         <v>1024061</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
@@ -9068,7 +9071,7 @@
         <v>0</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -9079,7 +9082,7 @@
         <v>1024062</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -9103,7 +9106,7 @@
         <v>0</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -9114,7 +9117,7 @@
         <v>1024063</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -9138,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -9149,7 +9152,7 @@
         <v>1024064</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -9173,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -9184,7 +9187,7 @@
         <v>1024065</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -9208,7 +9211,7 @@
         <v>0</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -9219,7 +9222,7 @@
         <v>1025101</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -9237,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M136" s="1">
         <v>2025101</v>
@@ -9246,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="R136" s="1">
         <v>-1</v>
@@ -9260,7 +9263,7 @@
         <v>1025102</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -9278,7 +9281,7 @@
         <v>0</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M137" s="1">
         <v>2025102</v>
@@ -9287,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R137" s="1">
         <v>-1</v>
@@ -9301,7 +9304,7 @@
         <v>1025103</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -9319,7 +9322,7 @@
         <v>0</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M138" s="1">
         <v>2025103</v>
@@ -9328,7 +9331,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R138" s="1">
         <v>-1</v>
@@ -9342,7 +9345,7 @@
         <v>1025104</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -9360,7 +9363,7 @@
         <v>0</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M139" s="1">
         <v>2025104</v>
@@ -9369,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R139" s="1">
         <v>-1</v>
@@ -9383,7 +9386,7 @@
         <v>1025105</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -9401,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M140" s="1">
         <v>2025105</v>
@@ -9410,7 +9413,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R140" s="1">
         <v>-1</v>
@@ -9424,7 +9427,7 @@
         <v>1025106</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -9442,7 +9445,7 @@
         <v>0</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M141" s="1">
         <v>2025106</v>
@@ -9451,7 +9454,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R141" s="1">
         <v>-1</v>
@@ -9465,7 +9468,7 @@
         <v>1025201</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -9483,7 +9486,7 @@
         <v>0</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M142" s="1">
         <v>2025201</v>
@@ -9492,7 +9495,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R142" s="1">
         <v>-1</v>
@@ -9506,7 +9509,7 @@
         <v>1025202</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -9524,7 +9527,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M143" s="1">
         <v>2025202</v>
@@ -9533,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R143" s="1">
         <v>-1</v>
@@ -9547,7 +9550,7 @@
         <v>1025203</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -9565,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M144" s="1">
         <v>2025203</v>
@@ -9574,7 +9577,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R144" s="1">
         <v>-1</v>
@@ -9588,7 +9591,7 @@
         <v>1025204</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -9606,7 +9609,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M145" s="1">
         <v>2025204</v>
@@ -9615,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="R145" s="1">
         <v>-1</v>
@@ -9629,7 +9632,7 @@
         <v>1025205</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -9647,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M146" s="1">
         <v>2025205</v>
@@ -9656,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="R146" s="1">
         <v>-1</v>
@@ -9670,7 +9673,7 @@
         <v>1025206</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -9688,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M147" s="1">
         <v>2025206</v>
@@ -9697,7 +9700,7 @@
         <v>0</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R147" s="1">
         <v>-1</v>
@@ -9711,7 +9714,7 @@
         <v>1025301</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -9729,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M148" s="1">
         <v>2025301</v>
@@ -9738,7 +9741,7 @@
         <v>0</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="R148" s="1">
         <v>-1</v>
@@ -9752,7 +9755,7 @@
         <v>1025302</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -9770,7 +9773,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M149" s="1">
         <v>2025302</v>
@@ -9779,7 +9782,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="R149" s="1">
         <v>-1</v>
@@ -9793,7 +9796,7 @@
         <v>1025303</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -9811,7 +9814,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M150" s="1">
         <v>2025303</v>
@@ -9820,7 +9823,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R150" s="1">
         <v>-1</v>
@@ -9834,7 +9837,7 @@
         <v>1025304</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -9852,7 +9855,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M151" s="1">
         <v>2025304</v>
@@ -9861,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R151" s="1">
         <v>-1</v>
@@ -9875,7 +9878,7 @@
         <v>1025305</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -9893,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M152" s="1">
         <v>2025305</v>
@@ -9902,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R152" s="1">
         <v>-1</v>
@@ -9916,7 +9919,7 @@
         <v>1025306</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -9934,7 +9937,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M153" s="1">
         <v>2025306</v>
@@ -9943,7 +9946,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="R153" s="1">
         <v>-1</v>
@@ -9957,7 +9960,7 @@
         <v>1025401</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -9975,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M154" s="1">
         <v>2025401</v>
@@ -9984,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R154" s="1">
         <v>-1</v>
@@ -9998,7 +10001,7 @@
         <v>1025402</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -10016,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M155" s="1">
         <v>2025402</v>
@@ -10025,7 +10028,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R155" s="1">
         <v>-1</v>
@@ -10039,7 +10042,7 @@
         <v>1025403</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -10057,7 +10060,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M156" s="1">
         <v>2025403</v>
@@ -10066,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="R156" s="1">
         <v>-1</v>
@@ -10080,7 +10083,7 @@
         <v>1025404</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -10098,7 +10101,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M157" s="1">
         <v>2025404</v>
@@ -10107,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R157" s="1">
         <v>-1</v>
@@ -10121,7 +10124,7 @@
         <v>1025405</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -10139,7 +10142,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M158" s="1">
         <v>2025405</v>
@@ -10148,7 +10151,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R158" s="1">
         <v>-1</v>
@@ -10162,7 +10165,7 @@
         <v>1025406</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -10180,7 +10183,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M159" s="1">
         <v>2025406</v>
@@ -10189,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R159" s="1">
         <v>-1</v>
@@ -10203,7 +10206,7 @@
         <v>1025501</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -10221,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M160" s="1">
         <v>2025501</v>
@@ -10230,7 +10233,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R160" s="1">
         <v>-1</v>
@@ -10244,7 +10247,7 @@
         <v>1025502</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -10262,7 +10265,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M161" s="1">
         <v>2025502</v>
@@ -10271,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="R161" s="1">
         <v>-1</v>
@@ -10285,7 +10288,7 @@
         <v>1025503</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -10303,7 +10306,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M162" s="1">
         <v>2025503</v>
@@ -10312,7 +10315,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R162" s="1">
         <v>-1</v>
@@ -10326,7 +10329,7 @@
         <v>1025504</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -10344,7 +10347,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M163" s="1">
         <v>2025504</v>
@@ -10353,7 +10356,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R163" s="1">
         <v>-1</v>
@@ -10367,7 +10370,7 @@
         <v>1025505</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
@@ -10385,7 +10388,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M164" s="1">
         <v>2025505</v>
@@ -10394,7 +10397,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R164" s="1">
         <v>-1</v>
@@ -10408,7 +10411,7 @@
         <v>1025506</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
@@ -10426,7 +10429,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M165" s="1">
         <v>2025506</v>
@@ -10435,7 +10438,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R165" s="1">
         <v>-1</v>
@@ -10468,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M166" s="1">
         <v>2125101</v>
@@ -10511,7 +10514,7 @@
         <v>1</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M167" s="1">
         <v>2125102</v>
@@ -10554,7 +10557,7 @@
         <v>1</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M168" s="1">
         <v>2125103</v>
@@ -10597,7 +10600,7 @@
         <v>1</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M169" s="1">
         <v>2125104</v>
@@ -10640,7 +10643,7 @@
         <v>1</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M170" s="1">
         <v>2125105</v>
@@ -10683,7 +10686,7 @@
         <v>1</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M171" s="1">
         <v>2125106</v>
@@ -10726,7 +10729,7 @@
         <v>1</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M172" s="1">
         <v>2125201</v>
@@ -10769,7 +10772,7 @@
         <v>1</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M173" s="1">
         <v>2125202</v>
@@ -10812,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M174" s="1">
         <v>2125203</v>
@@ -10855,7 +10858,7 @@
         <v>1</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M175" s="1">
         <v>2125204</v>
@@ -10898,7 +10901,7 @@
         <v>1</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M176" s="1">
         <v>2125205</v>
@@ -10941,7 +10944,7 @@
         <v>1</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M177" s="1">
         <v>2125206</v>
@@ -10984,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M178" s="1">
         <v>2125301</v>
@@ -11027,7 +11030,7 @@
         <v>1</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M179" s="1">
         <v>2125302</v>
@@ -11070,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M180" s="1">
         <v>2125303</v>
@@ -11113,7 +11116,7 @@
         <v>1</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M181" s="1">
         <v>2125304</v>
@@ -11156,7 +11159,7 @@
         <v>1</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M182" s="1">
         <v>2125305</v>
@@ -11199,7 +11202,7 @@
         <v>1</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M183" s="1">
         <v>2125306</v>
@@ -11242,7 +11245,7 @@
         <v>1</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M184" s="1">
         <v>2125401</v>
@@ -11285,7 +11288,7 @@
         <v>1</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M185" s="1">
         <v>2125402</v>
@@ -11328,7 +11331,7 @@
         <v>1</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M186" s="1">
         <v>2125403</v>
@@ -11371,7 +11374,7 @@
         <v>1</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M187" s="1">
         <v>2125404</v>
@@ -11414,7 +11417,7 @@
         <v>1</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M188" s="1">
         <v>2125405</v>
@@ -11457,7 +11460,7 @@
         <v>1</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M189" s="1">
         <v>2125406</v>
@@ -11500,7 +11503,7 @@
         <v>1</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M190" s="1">
         <v>2125501</v>
@@ -11543,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M191" s="1">
         <v>2125502</v>
@@ -11586,7 +11589,7 @@
         <v>1</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M192" s="1">
         <v>2125503</v>
@@ -11629,7 +11632,7 @@
         <v>1</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M193" s="1">
         <v>2125504</v>
@@ -11672,7 +11675,7 @@
         <v>1</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M194" s="1">
         <v>2125505</v>
@@ -11715,7 +11718,7 @@
         <v>1</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M195" s="1">
         <v>2125506</v>
@@ -11739,7 +11742,7 @@
         <v>1026001</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E196" s="1">
         <v>2</v>
@@ -11757,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M196" s="1">
         <v>2026001</v>
@@ -11766,7 +11769,7 @@
         <v>0</v>
       </c>
       <c r="O196" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R196" s="1">
         <v>-1</v>
@@ -11780,7 +11783,7 @@
         <v>1026002</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E197" s="1">
         <v>2</v>
@@ -11798,7 +11801,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M197" s="1">
         <v>2026002</v>
@@ -11807,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="O197" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="R197" s="1">
         <v>-1</v>
@@ -11821,7 +11824,7 @@
         <v>1026101</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E198" s="1">
         <v>2</v>
@@ -11839,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M198" s="1">
         <v>2026101</v>
@@ -11848,7 +11851,7 @@
         <v>0</v>
       </c>
       <c r="O198" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="R198" s="1">
         <v>-1</v>
@@ -11862,7 +11865,7 @@
         <v>1026102</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E199" s="1">
         <v>2</v>
@@ -11880,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M199" s="1">
         <v>2026102</v>
@@ -11889,7 +11892,7 @@
         <v>0</v>
       </c>
       <c r="O199" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="R199" s="1">
         <v>-1</v>
@@ -11903,7 +11906,7 @@
         <v>1026201</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E200" s="1">
         <v>2</v>
@@ -11921,7 +11924,7 @@
         <v>0</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M200" s="1">
         <v>2026201</v>
@@ -11930,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="O200" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="R200" s="1">
         <v>-1</v>
@@ -11944,7 +11947,7 @@
         <v>1026202</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E201" s="1">
         <v>2</v>
@@ -11962,7 +11965,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M201" s="1">
         <v>2026202</v>
@@ -11971,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="O201" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="R201" s="1">
         <v>-1</v>
@@ -11985,7 +11988,7 @@
         <v>1026301</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E202" s="1">
         <v>2</v>
@@ -12003,7 +12006,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M202" s="1">
         <v>2026301</v>
@@ -12012,7 +12015,7 @@
         <v>0</v>
       </c>
       <c r="O202" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="R202" s="1">
         <v>-1</v>
@@ -12026,7 +12029,7 @@
         <v>1026302</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E203" s="1">
         <v>2</v>
@@ -12044,7 +12047,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M203" s="1">
         <v>2026302</v>
@@ -12053,7 +12056,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R203" s="1">
         <v>-1</v>
@@ -12067,7 +12070,7 @@
         <v>1026401</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E204" s="1">
         <v>2</v>
@@ -12085,7 +12088,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M204" s="1">
         <v>2026401</v>
@@ -12094,7 +12097,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R204" s="1">
         <v>-1</v>
@@ -12108,7 +12111,7 @@
         <v>1026402</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E205" s="1">
         <v>2</v>
@@ -12126,7 +12129,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M205" s="1">
         <v>2026402</v>
@@ -12135,7 +12138,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="R205" s="1">
         <v>-1</v>
@@ -12149,7 +12152,7 @@
         <v>1027001</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -12167,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M206" s="1">
         <v>2027001</v>
@@ -12176,7 +12179,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="R206" s="1">
         <v>-1</v>
@@ -12190,7 +12193,7 @@
         <v>1027002</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -12208,7 +12211,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M207" s="1">
         <v>2027002</v>
@@ -12217,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R207" s="1">
         <v>-1</v>
@@ -12231,7 +12234,7 @@
         <v>1027101</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -12249,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M208" s="1">
         <v>2027101</v>
@@ -12258,7 +12261,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="R208" s="1">
         <v>-1</v>
@@ -12272,7 +12275,7 @@
         <v>1027102</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -12290,7 +12293,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M209" s="1">
         <v>2027102</v>
@@ -12299,7 +12302,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R209" s="1">
         <v>-1</v>
@@ -12313,7 +12316,7 @@
         <v>1027201</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -12331,7 +12334,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M210" s="1">
         <v>2027201</v>
@@ -12340,7 +12343,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="R210" s="1">
         <v>-1</v>
@@ -12354,7 +12357,7 @@
         <v>1027202</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -12372,7 +12375,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M211" s="1">
         <v>2027202</v>
@@ -12381,7 +12384,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="R211" s="1">
         <v>-1</v>
@@ -12395,7 +12398,7 @@
         <v>1027301</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -12413,7 +12416,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M212" s="1">
         <v>2027301</v>
@@ -12422,7 +12425,7 @@
         <v>0</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="R212" s="1">
         <v>-1</v>
@@ -12436,7 +12439,7 @@
         <v>1027302</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -12454,7 +12457,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M213" s="1">
         <v>2027302</v>
@@ -12463,7 +12466,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="R213" s="1">
         <v>-1</v>
@@ -12477,7 +12480,7 @@
         <v>1027401</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -12495,7 +12498,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M214" s="1">
         <v>2027401</v>
@@ -12504,7 +12507,7 @@
         <v>0</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R214" s="1">
         <v>-1</v>
@@ -12518,7 +12521,7 @@
         <v>1027402</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -12536,7 +12539,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M215" s="1">
         <v>2027402</v>
@@ -12545,7 +12548,7 @@
         <v>0</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="R215" s="1">
         <v>-1</v>
@@ -12559,7 +12562,7 @@
         <v>1028001</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -12577,7 +12580,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M216" s="1">
         <v>2028001</v>
@@ -12586,7 +12589,7 @@
         <v>0</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R216" s="1">
         <v>-1</v>
@@ -12600,7 +12603,7 @@
         <v>1028002</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -12618,7 +12621,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M217" s="1">
         <v>2028002</v>
@@ -12627,7 +12630,7 @@
         <v>0</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="R217" s="1">
         <v>-1</v>
@@ -12641,7 +12644,7 @@
         <v>1028101</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -12659,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M218" s="1">
         <v>2028101</v>
@@ -12668,7 +12671,7 @@
         <v>0</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R218" s="1">
         <v>-1</v>
@@ -12682,7 +12685,7 @@
         <v>1028102</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -12700,7 +12703,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M219" s="1">
         <v>2028102</v>
@@ -12709,7 +12712,7 @@
         <v>0</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R219" s="1">
         <v>-1</v>
@@ -12723,7 +12726,7 @@
         <v>1028201</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -12741,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M220" s="1">
         <v>2028201</v>
@@ -12750,7 +12753,7 @@
         <v>0</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R220" s="1">
         <v>-1</v>
@@ -12764,7 +12767,7 @@
         <v>1028202</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -12782,7 +12785,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M221" s="1">
         <v>2028202</v>
@@ -12791,7 +12794,7 @@
         <v>0</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="R221" s="1">
         <v>-1</v>
@@ -12805,7 +12808,7 @@
         <v>1028301</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -12823,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M222" s="1">
         <v>2028301</v>
@@ -12832,7 +12835,7 @@
         <v>0</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="R222" s="1">
         <v>-1</v>
@@ -12846,7 +12849,7 @@
         <v>1028302</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -12864,7 +12867,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M223" s="1">
         <v>2028302</v>
@@ -12873,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="R223" s="1">
         <v>-1</v>
@@ -12887,7 +12890,7 @@
         <v>1028401</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -12905,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M224" s="1">
         <v>2028401</v>
@@ -12914,7 +12917,7 @@
         <v>0</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="R224" s="1">
         <v>-1</v>
@@ -12928,7 +12931,7 @@
         <v>1028402</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -12946,7 +12949,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M225" s="1">
         <v>2028402</v>
@@ -12955,7 +12958,7 @@
         <v>0</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R225" s="1">
         <v>-1</v>
@@ -12988,7 +12991,7 @@
         <v>1</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M226" s="1">
         <v>2126001</v>
@@ -13031,7 +13034,7 @@
         <v>1</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M227" s="1">
         <v>2126002</v>
@@ -13074,7 +13077,7 @@
         <v>1</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M228" s="1">
         <v>2126101</v>
@@ -13117,7 +13120,7 @@
         <v>1</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M229" s="1">
         <v>2126102</v>
@@ -13160,7 +13163,7 @@
         <v>1</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M230" s="1">
         <v>2126201</v>
@@ -13203,7 +13206,7 @@
         <v>1</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M231" s="1">
         <v>2126202</v>
@@ -13246,7 +13249,7 @@
         <v>1</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M232" s="1">
         <v>2126301</v>
@@ -13289,7 +13292,7 @@
         <v>1</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M233" s="1">
         <v>2126302</v>
@@ -13332,7 +13335,7 @@
         <v>1</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M234" s="1">
         <v>2126401</v>
@@ -13375,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M235" s="1">
         <v>2126402</v>
@@ -13418,7 +13421,7 @@
         <v>1</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M236" s="1">
         <v>2127001</v>
@@ -13461,7 +13464,7 @@
         <v>1</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M237" s="1">
         <v>2127002</v>
@@ -13504,7 +13507,7 @@
         <v>1</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M238" s="1">
         <v>2127101</v>
@@ -13547,7 +13550,7 @@
         <v>1</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M239" s="1">
         <v>2127102</v>
@@ -13590,7 +13593,7 @@
         <v>1</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M240" s="1">
         <v>2127201</v>
@@ -13633,7 +13636,7 @@
         <v>1</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M241" s="1">
         <v>2127202</v>
@@ -13676,7 +13679,7 @@
         <v>1</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M242" s="1">
         <v>2127301</v>
@@ -13719,7 +13722,7 @@
         <v>1</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M243" s="1">
         <v>2127302</v>
@@ -13762,7 +13765,7 @@
         <v>1</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M244" s="1">
         <v>2127401</v>
@@ -13805,7 +13808,7 @@
         <v>1</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M245" s="1">
         <v>2127402</v>
@@ -13848,7 +13851,7 @@
         <v>1</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M246" s="1">
         <v>2128001</v>
@@ -13891,7 +13894,7 @@
         <v>1</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M247" s="1">
         <v>2128002</v>
@@ -13934,7 +13937,7 @@
         <v>1</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M248" s="1">
         <v>2128101</v>
@@ -13977,7 +13980,7 @@
         <v>1</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M249" s="1">
         <v>2128102</v>
@@ -14020,7 +14023,7 @@
         <v>1</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M250" s="1">
         <v>2128201</v>
@@ -14063,7 +14066,7 @@
         <v>1</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M251" s="1">
         <v>2128202</v>
@@ -14106,7 +14109,7 @@
         <v>1</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M252" s="1">
         <v>2128301</v>
@@ -14149,7 +14152,7 @@
         <v>1</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M253" s="1">
         <v>2128302</v>
@@ -14192,7 +14195,7 @@
         <v>1</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M254" s="1">
         <v>2128401</v>
@@ -14235,7 +14238,7 @@
         <v>1</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M255" s="1">
         <v>2128402</v>
@@ -14259,7 +14262,7 @@
         <v>1130001</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E256" s="1">
         <v>2</v>
@@ -14277,7 +14280,7 @@
         <v>1</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M256" s="1">
         <v>2130001</v>
@@ -14286,7 +14289,7 @@
         <v>0</v>
       </c>
       <c r="O256" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R256" s="1">
         <v>999999</v>
@@ -14300,7 +14303,7 @@
         <v>1130002</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E257" s="1">
         <v>1</v>
@@ -14318,7 +14321,7 @@
         <v>1</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M257" s="1">
         <v>2130002</v>
@@ -14327,7 +14330,7 @@
         <v>0</v>
       </c>
       <c r="O257" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="R257" s="1">
         <v>999999</v>
@@ -14341,7 +14344,7 @@
         <v>1130003</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E258" s="1">
         <v>1</v>
@@ -14359,7 +14362,7 @@
         <v>1</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M258" s="1">
         <v>2130003</v>
@@ -14368,7 +14371,7 @@
         <v>0</v>
       </c>
       <c r="O258" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="R258" s="1">
         <v>999999</v>
@@ -14382,7 +14385,7 @@
         <v>1130004</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E259" s="1">
         <v>1</v>
@@ -14400,7 +14403,7 @@
         <v>1</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M259" s="1">
         <v>2130004</v>
@@ -14409,7 +14412,7 @@
         <v>0</v>
       </c>
       <c r="O259" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="R259" s="1">
         <v>999999</v>
@@ -14423,7 +14426,7 @@
         <v>1130005</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E260" s="1">
         <v>1</v>
@@ -14441,7 +14444,7 @@
         <v>1</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M260" s="1">
         <v>2130005</v>
@@ -14450,7 +14453,7 @@
         <v>0</v>
       </c>
       <c r="O260" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R260" s="1">
         <v>999999</v>
@@ -14464,7 +14467,7 @@
         <v>1130006</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E261" s="1">
         <v>1</v>
@@ -14482,7 +14485,7 @@
         <v>1</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M261" s="1">
         <v>2130006</v>
@@ -14491,7 +14494,7 @@
         <v>0</v>
       </c>
       <c r="O261" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="R261" s="1">
         <v>999999</v>
@@ -14505,7 +14508,7 @@
         <v>1131001</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E262" s="1">
         <v>2</v>
@@ -14529,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="O262" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="263" spans="1:18">
@@ -14540,7 +14543,7 @@
         <v>1131002</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -14564,7 +14567,7 @@
         <v>0</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="264" spans="1:18">
@@ -14575,7 +14578,7 @@
         <v>1131003</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E264" s="1">
         <v>2</v>
@@ -14599,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="265" spans="1:18">
@@ -14610,7 +14613,7 @@
         <v>1131004</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E265" s="1">
         <v>2</v>
@@ -14634,7 +14637,7 @@
         <v>0</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="266" spans="1:18">
@@ -14645,7 +14648,7 @@
         <v>1131005</v>
       </c>
       <c r="D266" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E266" s="1">
         <v>2</v>
@@ -14669,7 +14672,7 @@
         <v>0</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="267" spans="1:18">
@@ -14680,7 +14683,7 @@
         <v>1131006</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E267" s="1">
         <v>2</v>
@@ -14704,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="268" spans="1:18">
@@ -14715,7 +14718,7 @@
         <v>1131101</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E268" s="1">
         <v>2</v>
@@ -14739,7 +14742,7 @@
         <v>0</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="269" spans="1:18">
@@ -14750,7 +14753,7 @@
         <v>1131102</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -14774,7 +14777,7 @@
         <v>0</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="270" spans="1:18">
@@ -14785,7 +14788,7 @@
         <v>1131103</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -14809,7 +14812,7 @@
         <v>0</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="271" spans="1:18">
@@ -14820,7 +14823,7 @@
         <v>1131104</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -14844,7 +14847,7 @@
         <v>0</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="272" spans="1:18">
@@ -14855,7 +14858,7 @@
         <v>1131105</v>
       </c>
       <c r="D272" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -14879,7 +14882,7 @@
         <v>0</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="273" spans="1:15">
@@ -14890,7 +14893,7 @@
         <v>1131106</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -14914,7 +14917,7 @@
         <v>0</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="274" spans="1:15">
@@ -14925,7 +14928,7 @@
         <v>1131201</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -14949,7 +14952,7 @@
         <v>0</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="275" spans="1:15">
@@ -14960,7 +14963,7 @@
         <v>1131202</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -14984,7 +14987,7 @@
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="276" spans="1:15">
@@ -14995,7 +14998,7 @@
         <v>1131203</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -15019,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="277" spans="1:15">
@@ -15030,7 +15033,7 @@
         <v>1131204</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -15054,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="278" spans="1:15">
@@ -15065,7 +15068,7 @@
         <v>1131205</v>
       </c>
       <c r="D278" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -15089,7 +15092,7 @@
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="279" spans="1:15">
@@ -15100,7 +15103,7 @@
         <v>1131206</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -15124,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="280" spans="1:15">
@@ -15135,7 +15138,7 @@
         <v>1131301</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -15159,7 +15162,7 @@
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="281" spans="1:15">
@@ -15170,7 +15173,7 @@
         <v>1131302</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15194,7 +15197,7 @@
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="282" spans="1:15">
@@ -15205,7 +15208,7 @@
         <v>1131303</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15229,7 +15232,7 @@
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="283" spans="1:15">
@@ -15240,7 +15243,7 @@
         <v>1131304</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15264,7 +15267,7 @@
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="284" spans="1:15">
@@ -15275,7 +15278,7 @@
         <v>1131305</v>
       </c>
       <c r="D284" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15299,7 +15302,7 @@
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="285" spans="1:15">
@@ -15310,7 +15313,7 @@
         <v>1131306</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15334,7 +15337,7 @@
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="286" spans="1:15">
@@ -15345,7 +15348,7 @@
         <v>1131401</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15369,7 +15372,7 @@
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="287" spans="1:15">
@@ -15380,7 +15383,7 @@
         <v>1131402</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -15404,7 +15407,7 @@
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="288" spans="1:15">
@@ -15415,7 +15418,7 @@
         <v>1131403</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -15439,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="289" spans="1:18">
@@ -15450,7 +15453,7 @@
         <v>1131404</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -15474,7 +15477,7 @@
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="290" spans="1:18">
@@ -15485,7 +15488,7 @@
         <v>1131405</v>
       </c>
       <c r="D290" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -15509,7 +15512,7 @@
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="291" spans="1:18">
@@ -15520,7 +15523,7 @@
         <v>1131406</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -15544,7 +15547,7 @@
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="292" spans="1:18">
@@ -15555,7 +15558,7 @@
         <v>1140001</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -15573,7 +15576,7 @@
         <v>0</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M292" s="1">
         <v>2140001</v>
@@ -15582,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="293" spans="1:18">
@@ -15593,7 +15596,7 @@
         <v>1140002</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -15611,7 +15614,7 @@
         <v>0</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M293" s="1">
         <v>2140002</v>
@@ -15620,7 +15623,7 @@
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="294" spans="1:18">
@@ -15631,7 +15634,7 @@
         <v>1140003</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -15649,7 +15652,7 @@
         <v>0</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M294" s="1">
         <v>2140003</v>
@@ -15658,7 +15661,7 @@
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="295" spans="1:18">
@@ -15669,7 +15672,7 @@
         <v>1140004</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -15687,7 +15690,7 @@
         <v>0</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M295" s="1">
         <v>2140004</v>
@@ -15696,7 +15699,7 @@
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="296" spans="1:18">
@@ -15707,7 +15710,7 @@
         <v>1140005</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -15725,7 +15728,7 @@
         <v>0</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M296" s="1">
         <v>2140005</v>
@@ -15734,7 +15737,7 @@
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="297" spans="1:18">
@@ -15745,7 +15748,7 @@
         <v>1140006</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -15763,7 +15766,7 @@
         <v>0</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M297" s="1">
         <v>2140006</v>
@@ -15772,7 +15775,7 @@
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="298" spans="1:18">
@@ -15783,7 +15786,7 @@
         <v>1150001</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -15801,7 +15804,7 @@
         <v>0</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M298" s="1">
         <v>2150001</v>
@@ -15825,7 +15828,7 @@
         <v>1150002</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -15843,7 +15846,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M299" s="1">
         <v>2150002</v>
@@ -15867,7 +15870,7 @@
         <v>1150003</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -15885,7 +15888,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M300" s="1">
         <v>2150003</v>
@@ -15909,7 +15912,7 @@
         <v>1150004</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -15927,7 +15930,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M301" s="1">
         <v>2150004</v>
@@ -15951,7 +15954,7 @@
         <v>1150005</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -15969,7 +15972,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M302" s="1">
         <v>2150005</v>
@@ -15993,7 +15996,7 @@
         <v>1150006</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -16011,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M303" s="1">
         <v>2150006</v>
@@ -16035,7 +16038,7 @@
         <v>1150007</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -16053,7 +16056,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M304" s="1">
         <v>2150007</v>
@@ -16077,7 +16080,7 @@
         <v>1150008</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -16095,7 +16098,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M305" s="1">
         <v>2150008</v>
@@ -16119,7 +16122,7 @@
         <v>1150009</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -16137,7 +16140,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M306" s="1">
         <v>2150009</v>
@@ -16161,7 +16164,7 @@
         <v>1150010</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -16179,7 +16182,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M307" s="1">
         <v>2150010</v>
@@ -16203,7 +16206,7 @@
         <v>1150011</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16221,7 +16224,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M308" s="1">
         <v>2150011</v>
@@ -16245,7 +16248,7 @@
         <v>1150012</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16263,7 +16266,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M309" s="1">
         <v>2150012</v>
@@ -16287,7 +16290,7 @@
         <v>1150013</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16305,7 +16308,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M310" s="1">
         <v>2150013</v>
@@ -16329,7 +16332,7 @@
         <v>1150014</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -16347,7 +16350,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M311" s="1">
         <v>2150014</v>
@@ -16371,7 +16374,7 @@
         <v>1150015</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -16389,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M312" s="1">
         <v>2150015</v>
@@ -16413,7 +16416,7 @@
         <v>1150016</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -16431,7 +16434,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M313" s="1">
         <v>2150016</v>
@@ -16455,7 +16458,7 @@
         <v>1150017</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -16473,7 +16476,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M314" s="1">
         <v>2150017</v>
@@ -16497,7 +16500,7 @@
         <v>1150018</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -16515,7 +16518,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M315" s="1">
         <v>2150018</v>
@@ -16539,7 +16542,7 @@
         <v>1150019</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -16557,7 +16560,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M316" s="1">
         <v>2150019</v>
@@ -16581,7 +16584,7 @@
         <v>1150020</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -16599,7 +16602,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M317" s="1">
         <v>2150020</v>
@@ -16623,7 +16626,7 @@
         <v>1150021</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -16641,7 +16644,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M318" s="1">
         <v>2150021</v>
@@ -16665,7 +16668,7 @@
         <v>1150022</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -16683,7 +16686,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M319" s="1">
         <v>2150022</v>
@@ -16707,7 +16710,7 @@
         <v>1150023</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -16725,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M320" s="1">
         <v>2150023</v>
@@ -16749,7 +16752,7 @@
         <v>1150024</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -16767,7 +16770,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M321" s="1">
         <v>2150024</v>
@@ -16791,7 +16794,7 @@
         <v>1150025</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -16809,7 +16812,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M322" s="1">
         <v>2150025</v>
@@ -16833,7 +16836,7 @@
         <v>1150026</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -16851,7 +16854,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M323" s="1">
         <v>2150026</v>
@@ -16875,7 +16878,7 @@
         <v>1150027</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -16893,7 +16896,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M324" s="1">
         <v>2150027</v>
@@ -16917,7 +16920,7 @@
         <v>1150028</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -16935,7 +16938,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M325" s="1">
         <v>2150028</v>
@@ -16959,7 +16962,7 @@
         <v>1150029</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -16977,7 +16980,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M326" s="1">
         <v>2150029</v>
@@ -17001,7 +17004,7 @@
         <v>1150030</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -17019,7 +17022,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M327" s="1">
         <v>2150030</v>
@@ -17043,7 +17046,7 @@
         <v>1150031</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -17061,7 +17064,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M328" s="1">
         <v>2150031</v>
@@ -17085,7 +17088,7 @@
         <v>1150032</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -17103,7 +17106,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M329" s="1">
         <v>2150032</v>
@@ -17127,7 +17130,7 @@
         <v>1150033</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -17145,7 +17148,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M330" s="1">
         <v>2150033</v>
@@ -17169,7 +17172,7 @@
         <v>1150034</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17187,7 +17190,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M331" s="1">
         <v>2150034</v>
@@ -17211,7 +17214,7 @@
         <v>1150035</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17229,7 +17232,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M332" s="1">
         <v>2150035</v>
@@ -17253,7 +17256,7 @@
         <v>1150036</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17271,7 +17274,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M333" s="1">
         <v>2150036</v>
@@ -17295,7 +17298,7 @@
         <v>1150037</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -17313,7 +17316,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M334" s="1">
         <v>2150037</v>
@@ -17337,7 +17340,7 @@
         <v>1150038</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -17355,7 +17358,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M335" s="1">
         <v>2150038</v>
@@ -17379,7 +17382,7 @@
         <v>1150039</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -17397,7 +17400,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M336" s="1">
         <v>2150039</v>
@@ -17421,7 +17424,7 @@
         <v>1150040</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -17439,7 +17442,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M337" s="1">
         <v>2150040</v>
@@ -17463,7 +17466,7 @@
         <v>1150041</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -17481,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M338" s="1">
         <v>2150041</v>
@@ -17505,7 +17508,7 @@
         <v>1150042</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -17523,7 +17526,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M339" s="1">
         <v>2150042</v>
@@ -17547,7 +17550,7 @@
         <v>1150043</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -17565,7 +17568,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M340" s="1">
         <v>2150043</v>
@@ -17589,7 +17592,7 @@
         <v>1150044</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -17607,7 +17610,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M341" s="1">
         <v>2150044</v>
@@ -17631,7 +17634,7 @@
         <v>1150045</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -17649,7 +17652,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M342" s="1">
         <v>2150045</v>
@@ -17673,7 +17676,7 @@
         <v>1150046</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -17691,7 +17694,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M343" s="1">
         <v>2150046</v>
@@ -17715,7 +17718,7 @@
         <v>1150047</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -17733,7 +17736,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M344" s="1">
         <v>2150047</v>
@@ -17757,7 +17760,7 @@
         <v>1150048</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -17775,7 +17778,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M345" s="1">
         <v>2150048</v>
@@ -17799,7 +17802,7 @@
         <v>1150049</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -17817,7 +17820,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M346" s="1">
         <v>2150049</v>
@@ -17841,7 +17844,7 @@
         <v>1150050</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -17859,7 +17862,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M347" s="1">
         <v>2150050</v>
@@ -17883,7 +17886,7 @@
         <v>1150051</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -17901,7 +17904,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M348" s="1">
         <v>2150051</v>
@@ -17925,7 +17928,7 @@
         <v>1150052</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -17943,7 +17946,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M349" s="1">
         <v>2150052</v>
@@ -17967,7 +17970,7 @@
         <v>1150053</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -17985,7 +17988,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M350" s="1">
         <v>2150053</v>
@@ -18009,7 +18012,7 @@
         <v>1150054</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -18027,7 +18030,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M351" s="1">
         <v>2150054</v>
@@ -18051,7 +18054,7 @@
         <v>1150055</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -18069,7 +18072,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M352" s="1">
         <v>2150055</v>
@@ -18093,7 +18096,7 @@
         <v>1150056</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -18111,7 +18114,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M353" s="1">
         <v>2150056</v>
@@ -18135,7 +18138,7 @@
         <v>1150057</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -18153,7 +18156,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M354" s="1">
         <v>2150057</v>
@@ -18177,7 +18180,7 @@
         <v>1150058</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18195,7 +18198,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M355" s="1">
         <v>2150058</v>
@@ -18219,7 +18222,7 @@
         <v>1150059</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18237,7 +18240,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M356" s="1">
         <v>2150059</v>
@@ -18261,7 +18264,7 @@
         <v>1150060</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18279,7 +18282,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M357" s="1">
         <v>2150060</v>
@@ -18303,7 +18306,7 @@
         <v>1150061</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -18321,7 +18324,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M358" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="644">
   <si>
     <t>道具ID</t>
   </si>
@@ -1285,42 +1285,63 @@
     <t>101800</t>
   </si>
   <si>
+    <t>daoju_lqjx.png</t>
+  </si>
+  <si>
     <t>升级篮球巨星游戏特殊词条</t>
   </si>
   <si>
     <t>102500</t>
   </si>
   <si>
+    <t>daoju_hbwz.png</t>
+  </si>
+  <si>
     <t>升级寒冰王座游戏特殊词条</t>
   </si>
   <si>
     <t>103100</t>
   </si>
   <si>
+    <t>daoju_ljr.png</t>
+  </si>
+  <si>
     <t>升级绿巨人游戏特殊词条</t>
   </si>
   <si>
     <t>102200</t>
   </si>
   <si>
+    <t>daoju_ls.png</t>
+  </si>
+  <si>
     <t>升级雷神游戏特殊词条</t>
   </si>
   <si>
     <t>102100</t>
   </si>
   <si>
+    <t>daoju_jkcz.png</t>
+  </si>
+  <si>
     <t>升级杰克船长游戏特殊词条</t>
   </si>
   <si>
     <t>103900</t>
   </si>
   <si>
+    <t>daoju_fndxn.png</t>
+  </si>
+  <si>
     <t>升级愤怒的小鸟游戏特殊词条</t>
   </si>
   <si>
     <t>102000</t>
   </si>
   <si>
+    <t>daoju_zsvshds.png</t>
+  </si>
+  <si>
     <t>升级宙斯VS哈迪斯游戏特殊词条</t>
   </si>
   <si>
@@ -1504,7 +1525,94 @@
     <t>yk_gdnw.png</t>
   </si>
   <si>
-    <t>itemicon_1020002.png</t>
+    <t>daoju_yk_jtcr.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_fgss.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_kgsn.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_clxf.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_ssjz.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_jpdr.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_ydjj.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_pksn.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_hbgs.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_txlm.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_hlsn.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_yyns.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_jskm.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_dcqs.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_dsxz.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_wyqn.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_sxsn.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_mygs.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_mlsk.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_jxwj.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_kjjk.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_dlhj.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_lmsr.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_gdlm.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_cyxg.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_mjxw.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_kjdl.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_cdbz.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_mzxx.png</t>
+  </si>
+  <si>
+    <t>daoju_yk_gdnw.png</t>
   </si>
   <si>
     <t>威廉</t>
@@ -1612,7 +1720,22 @@
     <t>伊丽莎白</t>
   </si>
   <si>
+    <t>daoju_gy_nan_wl.png</t>
+  </si>
+  <si>
+    <t>daoju_gy_nv_al.png</t>
+  </si>
+  <si>
     <t>itemicon_1020006.png</t>
+  </si>
+  <si>
+    <t>daoju_gy_nan_lfe.png</t>
+  </si>
+  <si>
+    <t>daoju_gy_nv_lla.png</t>
+  </si>
+  <si>
+    <t>daoju_gy_nv_kll.png</t>
   </si>
   <si>
     <t>挑战券</t>
@@ -2870,7 +2993,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2911,6 +3034,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -9287,6 +9413,9 @@
       <c r="K136" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L136" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="M136" s="1">
         <v>2024076</v>
       </c>
@@ -9294,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="137" ht="17.25" spans="1:19">
@@ -9317,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I137" s="1">
         <v>1</v>
@@ -9327,6 +9456,9 @@
       </c>
       <c r="K137" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="M137" s="1">
         <v>2024077</v>
@@ -9335,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -9358,7 +9490,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I138" s="1">
         <v>1</v>
@@ -9368,6 +9500,9 @@
       </c>
       <c r="K138" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="M138" s="1">
         <v>2024078</v>
@@ -9376,7 +9511,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -9399,7 +9534,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I139" s="1">
         <v>1</v>
@@ -9409,6 +9544,9 @@
       </c>
       <c r="K139" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="M139" s="1">
         <v>2024079</v>
@@ -9417,7 +9555,7 @@
         <v>0</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -9440,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I140" s="1">
         <v>1</v>
@@ -9450,6 +9588,9 @@
       </c>
       <c r="K140" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="M140" s="1">
         <v>2024080</v>
@@ -9458,7 +9599,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="141" spans="1:19">
@@ -9481,7 +9622,7 @@
         <v>1</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="I141" s="1">
         <v>1</v>
@@ -9491,6 +9632,9 @@
       </c>
       <c r="K141" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="M141" s="1">
         <v>2024081</v>
@@ -9499,7 +9643,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -9522,7 +9666,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I142" s="1">
         <v>1</v>
@@ -9532,6 +9676,9 @@
       </c>
       <c r="K142" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="M142" s="1">
         <v>2024082</v>
@@ -9540,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -9551,7 +9698,7 @@
         <v>1025101</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -9569,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M143" s="1">
         <v>2025101</v>
@@ -9578,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="R143" s="1">
         <v>-1</v>
@@ -9592,7 +9739,7 @@
         <v>1025102</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -9610,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M144" s="1">
         <v>2025102</v>
@@ -9619,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="R144" s="1">
         <v>-1</v>
@@ -9633,7 +9780,7 @@
         <v>1025103</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -9651,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="M145" s="1">
         <v>2025103</v>
@@ -9660,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="R145" s="1">
         <v>-1</v>
@@ -9674,7 +9821,7 @@
         <v>1025104</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -9692,7 +9839,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="M146" s="1">
         <v>2025104</v>
@@ -9701,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="R146" s="1">
         <v>-1</v>
@@ -9715,7 +9862,7 @@
         <v>1025105</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -9733,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="M147" s="1">
         <v>2025105</v>
@@ -9742,7 +9889,7 @@
         <v>0</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="R147" s="1">
         <v>-1</v>
@@ -9756,7 +9903,7 @@
         <v>1025106</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -9774,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="M148" s="1">
         <v>2025106</v>
@@ -9783,7 +9930,7 @@
         <v>0</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="R148" s="1">
         <v>-1</v>
@@ -9797,7 +9944,7 @@
         <v>1025201</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -9815,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="M149" s="1">
         <v>2025201</v>
@@ -9824,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="R149" s="1">
         <v>-1</v>
@@ -9838,7 +9985,7 @@
         <v>1025202</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -9856,7 +10003,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M150" s="1">
         <v>2025202</v>
@@ -9865,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="R150" s="1">
         <v>-1</v>
@@ -9879,7 +10026,7 @@
         <v>1025203</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -9897,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="M151" s="1">
         <v>2025203</v>
@@ -9906,7 +10053,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="R151" s="1">
         <v>-1</v>
@@ -9920,7 +10067,7 @@
         <v>1025204</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -9938,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M152" s="1">
         <v>2025204</v>
@@ -9947,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="R152" s="1">
         <v>-1</v>
@@ -9961,7 +10108,7 @@
         <v>1025205</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -9979,7 +10126,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="M153" s="1">
         <v>2025205</v>
@@ -9988,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="R153" s="1">
         <v>-1</v>
@@ -10002,7 +10149,7 @@
         <v>1025206</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -10020,7 +10167,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="M154" s="1">
         <v>2025206</v>
@@ -10029,7 +10176,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="R154" s="1">
         <v>-1</v>
@@ -10043,7 +10190,7 @@
         <v>1025301</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -10061,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="M155" s="1">
         <v>2025301</v>
@@ -10070,7 +10217,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="R155" s="1">
         <v>-1</v>
@@ -10084,7 +10231,7 @@
         <v>1025302</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -10102,7 +10249,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="M156" s="1">
         <v>2025302</v>
@@ -10111,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="R156" s="1">
         <v>-1</v>
@@ -10125,7 +10272,7 @@
         <v>1025303</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -10143,7 +10290,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="M157" s="1">
         <v>2025303</v>
@@ -10152,7 +10299,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="R157" s="1">
         <v>-1</v>
@@ -10166,7 +10313,7 @@
         <v>1025304</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -10184,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="M158" s="1">
         <v>2025304</v>
@@ -10193,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="R158" s="1">
         <v>-1</v>
@@ -10207,7 +10354,7 @@
         <v>1025305</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -10225,7 +10372,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="M159" s="1">
         <v>2025305</v>
@@ -10234,7 +10381,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="R159" s="1">
         <v>-1</v>
@@ -10248,7 +10395,7 @@
         <v>1025306</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -10266,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="M160" s="1">
         <v>2025306</v>
@@ -10275,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="R160" s="1">
         <v>-1</v>
@@ -10289,7 +10436,7 @@
         <v>1025401</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -10307,7 +10454,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="M161" s="1">
         <v>2025401</v>
@@ -10316,7 +10463,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="R161" s="1">
         <v>-1</v>
@@ -10330,7 +10477,7 @@
         <v>1025402</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -10348,7 +10495,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M162" s="1">
         <v>2025402</v>
@@ -10357,7 +10504,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="R162" s="1">
         <v>-1</v>
@@ -10371,7 +10518,7 @@
         <v>1025403</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -10389,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="M163" s="1">
         <v>2025403</v>
@@ -10398,7 +10545,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="R163" s="1">
         <v>-1</v>
@@ -10412,7 +10559,7 @@
         <v>1025404</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
@@ -10430,7 +10577,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="M164" s="1">
         <v>2025404</v>
@@ -10439,7 +10586,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="R164" s="1">
         <v>-1</v>
@@ -10453,7 +10600,7 @@
         <v>1025405</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
@@ -10471,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="M165" s="1">
         <v>2025405</v>
@@ -10480,7 +10627,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="R165" s="1">
         <v>-1</v>
@@ -10494,7 +10641,7 @@
         <v>1025406</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E166" s="1">
         <v>2</v>
@@ -10512,7 +10659,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="M166" s="1">
         <v>2025406</v>
@@ -10521,7 +10668,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="R166" s="1">
         <v>-1</v>
@@ -10535,7 +10682,7 @@
         <v>1025501</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="E167" s="1">
         <v>2</v>
@@ -10553,7 +10700,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="M167" s="1">
         <v>2025501</v>
@@ -10562,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="R167" s="1">
         <v>-1</v>
@@ -10576,7 +10723,7 @@
         <v>1025502</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E168" s="1">
         <v>2</v>
@@ -10594,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="M168" s="1">
         <v>2025502</v>
@@ -10603,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="R168" s="1">
         <v>-1</v>
@@ -10617,7 +10764,7 @@
         <v>1025503</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E169" s="1">
         <v>2</v>
@@ -10635,7 +10782,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="M169" s="1">
         <v>2025503</v>
@@ -10644,7 +10791,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="R169" s="1">
         <v>-1</v>
@@ -10658,7 +10805,7 @@
         <v>1025504</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E170" s="1">
         <v>2</v>
@@ -10676,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="M170" s="1">
         <v>2025504</v>
@@ -10685,7 +10832,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="R170" s="1">
         <v>-1</v>
@@ -10699,7 +10846,7 @@
         <v>1025505</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E171" s="1">
         <v>2</v>
@@ -10717,7 +10864,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="M171" s="1">
         <v>2025505</v>
@@ -10726,7 +10873,7 @@
         <v>0</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="R171" s="1">
         <v>-1</v>
@@ -10740,7 +10887,7 @@
         <v>1025506</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="E172" s="1">
         <v>2</v>
@@ -10758,7 +10905,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="M172" s="1">
         <v>2025506</v>
@@ -10767,7 +10914,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="R172" s="1">
         <v>-1</v>
@@ -10799,8 +10946,8 @@
       <c r="K173" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L173" s="1" t="s">
-        <v>372</v>
+      <c r="L173" s="14" t="s">
+        <v>379</v>
       </c>
       <c r="M173" s="1">
         <v>2125101</v>
@@ -10842,8 +10989,8 @@
       <c r="K174" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L174" s="1" t="s">
-        <v>372</v>
+      <c r="L174" s="14" t="s">
+        <v>380</v>
       </c>
       <c r="M174" s="1">
         <v>2125102</v>
@@ -10885,8 +11032,8 @@
       <c r="K175" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L175" s="1" t="s">
-        <v>372</v>
+      <c r="L175" s="14" t="s">
+        <v>381</v>
       </c>
       <c r="M175" s="1">
         <v>2125103</v>
@@ -10928,8 +11075,8 @@
       <c r="K176" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L176" s="1" t="s">
-        <v>372</v>
+      <c r="L176" s="14" t="s">
+        <v>382</v>
       </c>
       <c r="M176" s="1">
         <v>2125104</v>
@@ -10971,8 +11118,8 @@
       <c r="K177" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L177" s="1" t="s">
-        <v>372</v>
+      <c r="L177" s="14" t="s">
+        <v>383</v>
       </c>
       <c r="M177" s="1">
         <v>2125105</v>
@@ -11014,8 +11161,8 @@
       <c r="K178" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L178" s="1" t="s">
-        <v>372</v>
+      <c r="L178" s="14" t="s">
+        <v>384</v>
       </c>
       <c r="M178" s="1">
         <v>2125106</v>
@@ -11057,8 +11204,8 @@
       <c r="K179" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L179" s="1" t="s">
-        <v>372</v>
+      <c r="L179" s="14" t="s">
+        <v>385</v>
       </c>
       <c r="M179" s="1">
         <v>2125201</v>
@@ -11100,8 +11247,8 @@
       <c r="K180" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L180" s="1" t="s">
-        <v>372</v>
+      <c r="L180" s="14" t="s">
+        <v>386</v>
       </c>
       <c r="M180" s="1">
         <v>2125202</v>
@@ -11143,8 +11290,8 @@
       <c r="K181" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L181" s="1" t="s">
-        <v>372</v>
+      <c r="L181" s="14" t="s">
+        <v>387</v>
       </c>
       <c r="M181" s="1">
         <v>2125203</v>
@@ -11186,8 +11333,8 @@
       <c r="K182" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L182" s="1" t="s">
-        <v>372</v>
+      <c r="L182" s="14" t="s">
+        <v>388</v>
       </c>
       <c r="M182" s="1">
         <v>2125204</v>
@@ -11229,8 +11376,8 @@
       <c r="K183" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L183" s="1" t="s">
-        <v>372</v>
+      <c r="L183" s="14" t="s">
+        <v>389</v>
       </c>
       <c r="M183" s="1">
         <v>2125205</v>
@@ -11272,8 +11419,8 @@
       <c r="K184" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L184" s="1" t="s">
-        <v>372</v>
+      <c r="L184" s="14" t="s">
+        <v>390</v>
       </c>
       <c r="M184" s="1">
         <v>2125206</v>
@@ -11315,8 +11462,8 @@
       <c r="K185" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L185" s="1" t="s">
-        <v>372</v>
+      <c r="L185" s="14" t="s">
+        <v>391</v>
       </c>
       <c r="M185" s="1">
         <v>2125301</v>
@@ -11358,8 +11505,8 @@
       <c r="K186" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L186" s="1" t="s">
-        <v>372</v>
+      <c r="L186" s="14" t="s">
+        <v>392</v>
       </c>
       <c r="M186" s="1">
         <v>2125302</v>
@@ -11401,8 +11548,8 @@
       <c r="K187" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L187" s="1" t="s">
-        <v>372</v>
+      <c r="L187" s="14" t="s">
+        <v>393</v>
       </c>
       <c r="M187" s="1">
         <v>2125303</v>
@@ -11444,8 +11591,8 @@
       <c r="K188" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L188" s="1" t="s">
-        <v>372</v>
+      <c r="L188" s="14" t="s">
+        <v>394</v>
       </c>
       <c r="M188" s="1">
         <v>2125304</v>
@@ -11487,8 +11634,8 @@
       <c r="K189" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L189" s="1" t="s">
-        <v>372</v>
+      <c r="L189" s="14" t="s">
+        <v>395</v>
       </c>
       <c r="M189" s="1">
         <v>2125305</v>
@@ -11530,8 +11677,8 @@
       <c r="K190" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L190" s="1" t="s">
-        <v>372</v>
+      <c r="L190" s="14" t="s">
+        <v>396</v>
       </c>
       <c r="M190" s="1">
         <v>2125306</v>
@@ -11573,8 +11720,8 @@
       <c r="K191" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L191" s="1" t="s">
-        <v>372</v>
+      <c r="L191" s="14" t="s">
+        <v>397</v>
       </c>
       <c r="M191" s="1">
         <v>2125401</v>
@@ -11616,8 +11763,8 @@
       <c r="K192" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L192" s="1" t="s">
-        <v>372</v>
+      <c r="L192" s="14" t="s">
+        <v>398</v>
       </c>
       <c r="M192" s="1">
         <v>2125402</v>
@@ -11659,8 +11806,8 @@
       <c r="K193" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L193" s="1" t="s">
-        <v>372</v>
+      <c r="L193" s="14" t="s">
+        <v>399</v>
       </c>
       <c r="M193" s="1">
         <v>2125403</v>
@@ -11702,8 +11849,8 @@
       <c r="K194" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L194" s="1" t="s">
-        <v>372</v>
+      <c r="L194" s="14" t="s">
+        <v>400</v>
       </c>
       <c r="M194" s="1">
         <v>2125404</v>
@@ -11745,8 +11892,8 @@
       <c r="K195" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L195" s="1" t="s">
-        <v>372</v>
+      <c r="L195" s="14" t="s">
+        <v>401</v>
       </c>
       <c r="M195" s="1">
         <v>2125405</v>
@@ -11788,8 +11935,8 @@
       <c r="K196" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L196" s="1" t="s">
-        <v>372</v>
+      <c r="L196" s="14" t="s">
+        <v>402</v>
       </c>
       <c r="M196" s="1">
         <v>2125406</v>
@@ -11831,8 +11978,8 @@
       <c r="K197" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L197" s="1" t="s">
-        <v>372</v>
+      <c r="L197" s="14" t="s">
+        <v>403</v>
       </c>
       <c r="M197" s="1">
         <v>2125501</v>
@@ -11874,8 +12021,8 @@
       <c r="K198" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L198" s="1" t="s">
-        <v>372</v>
+      <c r="L198" s="14" t="s">
+        <v>404</v>
       </c>
       <c r="M198" s="1">
         <v>2125502</v>
@@ -11917,8 +12064,8 @@
       <c r="K199" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L199" s="1" t="s">
-        <v>372</v>
+      <c r="L199" s="14" t="s">
+        <v>405</v>
       </c>
       <c r="M199" s="1">
         <v>2125503</v>
@@ -11960,8 +12107,8 @@
       <c r="K200" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L200" s="1" t="s">
-        <v>372</v>
+      <c r="L200" s="14" t="s">
+        <v>406</v>
       </c>
       <c r="M200" s="1">
         <v>2125504</v>
@@ -12003,8 +12150,8 @@
       <c r="K201" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L201" s="1" t="s">
-        <v>372</v>
+      <c r="L201" s="14" t="s">
+        <v>407</v>
       </c>
       <c r="M201" s="1">
         <v>2125505</v>
@@ -12046,8 +12193,8 @@
       <c r="K202" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L202" s="1" t="s">
-        <v>372</v>
+      <c r="L202" s="14" t="s">
+        <v>408</v>
       </c>
       <c r="M202" s="1">
         <v>2125506</v>
@@ -12071,7 +12218,7 @@
         <v>1026001</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="E203" s="1">
         <v>2</v>
@@ -12089,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="M203" s="1">
         <v>2026001</v>
@@ -12098,7 +12245,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="R203" s="1">
         <v>-1</v>
@@ -12112,7 +12259,7 @@
         <v>1026002</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="E204" s="1">
         <v>2</v>
@@ -12130,7 +12277,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="M204" s="1">
         <v>2026002</v>
@@ -12139,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="R204" s="1">
         <v>-1</v>
@@ -12153,7 +12300,7 @@
         <v>1026101</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="E205" s="1">
         <v>2</v>
@@ -12180,7 +12327,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="R205" s="1">
         <v>-1</v>
@@ -12194,7 +12341,7 @@
         <v>1026102</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -12221,7 +12368,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="R206" s="1">
         <v>-1</v>
@@ -12235,7 +12382,7 @@
         <v>1026201</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -12262,7 +12409,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
       <c r="R207" s="1">
         <v>-1</v>
@@ -12276,7 +12423,7 @@
         <v>1026202</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -12303,7 +12450,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>380</v>
+        <v>416</v>
       </c>
       <c r="R208" s="1">
         <v>-1</v>
@@ -12317,7 +12464,7 @@
         <v>1026301</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -12344,7 +12491,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="R209" s="1">
         <v>-1</v>
@@ -12358,7 +12505,7 @@
         <v>1026302</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -12385,7 +12532,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="R210" s="1">
         <v>-1</v>
@@ -12399,7 +12546,7 @@
         <v>1026401</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -12426,7 +12573,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="R211" s="1">
         <v>-1</v>
@@ -12440,7 +12587,7 @@
         <v>1026402</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -12467,7 +12614,7 @@
         <v>0</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="R212" s="1">
         <v>-1</v>
@@ -12481,7 +12628,7 @@
         <v>1027001</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -12499,7 +12646,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="M213" s="1">
         <v>2027001</v>
@@ -12508,7 +12655,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="R213" s="1">
         <v>-1</v>
@@ -12522,7 +12669,7 @@
         <v>1027002</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -12549,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="R214" s="1">
         <v>-1</v>
@@ -12563,7 +12710,7 @@
         <v>1027101</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -12590,7 +12737,7 @@
         <v>0</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="R215" s="1">
         <v>-1</v>
@@ -12604,7 +12751,7 @@
         <v>1027102</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -12631,7 +12778,7 @@
         <v>0</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="R216" s="1">
         <v>-1</v>
@@ -12645,7 +12792,7 @@
         <v>1027201</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -12672,7 +12819,7 @@
         <v>0</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="R217" s="1">
         <v>-1</v>
@@ -12686,7 +12833,7 @@
         <v>1027202</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -12713,7 +12860,7 @@
         <v>0</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="R218" s="1">
         <v>-1</v>
@@ -12727,7 +12874,7 @@
         <v>1027301</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -12754,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="R219" s="1">
         <v>-1</v>
@@ -12768,7 +12915,7 @@
         <v>1027302</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -12786,7 +12933,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="M220" s="1">
         <v>2027302</v>
@@ -12795,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="R220" s="1">
         <v>-1</v>
@@ -12809,7 +12956,7 @@
         <v>1027401</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -12836,7 +12983,7 @@
         <v>0</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="R221" s="1">
         <v>-1</v>
@@ -12850,7 +12997,7 @@
         <v>1027402</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -12868,7 +13015,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="M222" s="1">
         <v>2027402</v>
@@ -12877,7 +13024,7 @@
         <v>0</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="R222" s="1">
         <v>-1</v>
@@ -12891,7 +13038,7 @@
         <v>1028001</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -12918,7 +13065,7 @@
         <v>0</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>398</v>
+        <v>434</v>
       </c>
       <c r="R223" s="1">
         <v>-1</v>
@@ -12932,7 +13079,7 @@
         <v>1028002</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -12959,7 +13106,7 @@
         <v>0</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="R224" s="1">
         <v>-1</v>
@@ -12973,7 +13120,7 @@
         <v>1028101</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -13000,7 +13147,7 @@
         <v>0</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="R225" s="1">
         <v>-1</v>
@@ -13014,7 +13161,7 @@
         <v>1028102</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="E226" s="1">
         <v>2</v>
@@ -13041,7 +13188,7 @@
         <v>0</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="R226" s="1">
         <v>-1</v>
@@ -13055,7 +13202,7 @@
         <v>1028201</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
@@ -13082,7 +13229,7 @@
         <v>0</v>
       </c>
       <c r="O227" s="1" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
       <c r="R227" s="1">
         <v>-1</v>
@@ -13096,7 +13243,7 @@
         <v>1028202</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
@@ -13123,7 +13270,7 @@
         <v>0</v>
       </c>
       <c r="O228" s="1" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
       <c r="R228" s="1">
         <v>-1</v>
@@ -13137,7 +13284,7 @@
         <v>1028301</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
@@ -13164,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="O229" s="1" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="R229" s="1">
         <v>-1</v>
@@ -13178,7 +13325,7 @@
         <v>1028302</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
@@ -13205,7 +13352,7 @@
         <v>0</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="R230" s="1">
         <v>-1</v>
@@ -13219,7 +13366,7 @@
         <v>1028401</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
@@ -13246,7 +13393,7 @@
         <v>0</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="R231" s="1">
         <v>-1</v>
@@ -13260,7 +13407,7 @@
         <v>1028402</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
@@ -13287,7 +13434,7 @@
         <v>0</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="R232" s="1">
         <v>-1</v>
@@ -13320,7 +13467,7 @@
         <v>1</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>211</v>
+        <v>444</v>
       </c>
       <c r="M233" s="1">
         <v>2126001</v>
@@ -13363,7 +13510,7 @@
         <v>1</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="M234" s="1">
         <v>2126002</v>
@@ -13406,7 +13553,7 @@
         <v>1</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M235" s="1">
         <v>2126101</v>
@@ -13449,7 +13596,7 @@
         <v>1</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M236" s="1">
         <v>2126102</v>
@@ -13492,7 +13639,7 @@
         <v>1</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M237" s="1">
         <v>2126201</v>
@@ -13535,7 +13682,7 @@
         <v>1</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M238" s="1">
         <v>2126202</v>
@@ -13578,7 +13725,7 @@
         <v>1</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M239" s="1">
         <v>2126301</v>
@@ -13621,7 +13768,7 @@
         <v>1</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M240" s="1">
         <v>2126302</v>
@@ -13664,7 +13811,7 @@
         <v>1</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M241" s="1">
         <v>2126401</v>
@@ -13707,7 +13854,7 @@
         <v>1</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M242" s="1">
         <v>2126402</v>
@@ -13750,7 +13897,7 @@
         <v>1</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="M243" s="1">
         <v>2127001</v>
@@ -13793,7 +13940,7 @@
         <v>1</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M244" s="1">
         <v>2127002</v>
@@ -13836,7 +13983,7 @@
         <v>1</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M245" s="1">
         <v>2127101</v>
@@ -13879,7 +14026,7 @@
         <v>1</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M246" s="1">
         <v>2127102</v>
@@ -13922,7 +14069,7 @@
         <v>1</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M247" s="1">
         <v>2127201</v>
@@ -13965,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M248" s="1">
         <v>2127202</v>
@@ -14008,7 +14155,7 @@
         <v>1</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M249" s="1">
         <v>2127301</v>
@@ -14051,7 +14198,7 @@
         <v>1</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="M250" s="1">
         <v>2127302</v>
@@ -14094,7 +14241,7 @@
         <v>1</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M251" s="1">
         <v>2127401</v>
@@ -14137,7 +14284,7 @@
         <v>1</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>408</v>
+        <v>449</v>
       </c>
       <c r="M252" s="1">
         <v>2127402</v>
@@ -14180,7 +14327,7 @@
         <v>1</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M253" s="1">
         <v>2128001</v>
@@ -14223,7 +14370,7 @@
         <v>1</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M254" s="1">
         <v>2128002</v>
@@ -14266,7 +14413,7 @@
         <v>1</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M255" s="1">
         <v>2128101</v>
@@ -14309,7 +14456,7 @@
         <v>1</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M256" s="1">
         <v>2128102</v>
@@ -14352,7 +14499,7 @@
         <v>1</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M257" s="1">
         <v>2128201</v>
@@ -14395,7 +14542,7 @@
         <v>1</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M258" s="1">
         <v>2128202</v>
@@ -14438,7 +14585,7 @@
         <v>1</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M259" s="1">
         <v>2128301</v>
@@ -14481,7 +14628,7 @@
         <v>1</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M260" s="1">
         <v>2128302</v>
@@ -14524,7 +14671,7 @@
         <v>1</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M261" s="1">
         <v>2128401</v>
@@ -14567,7 +14714,7 @@
         <v>1</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="M262" s="1">
         <v>2128402</v>
@@ -14591,7 +14738,7 @@
         <v>1130001</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -14609,7 +14756,7 @@
         <v>1</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="M263" s="1">
         <v>2130001</v>
@@ -14618,7 +14765,7 @@
         <v>0</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="R263" s="1">
         <v>999999</v>
@@ -14632,7 +14779,7 @@
         <v>1130002</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>412</v>
+        <v>453</v>
       </c>
       <c r="E264" s="1">
         <v>1</v>
@@ -14650,7 +14797,7 @@
         <v>1</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="M264" s="1">
         <v>2130002</v>
@@ -14659,7 +14806,7 @@
         <v>0</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="R264" s="1">
         <v>999999</v>
@@ -14673,7 +14820,7 @@
         <v>1130003</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>415</v>
+        <v>456</v>
       </c>
       <c r="E265" s="1">
         <v>1</v>
@@ -14691,7 +14838,7 @@
         <v>1</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="M265" s="1">
         <v>2130003</v>
@@ -14700,7 +14847,7 @@
         <v>0</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="R265" s="1">
         <v>999999</v>
@@ -14714,7 +14861,7 @@
         <v>1130004</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="E266" s="1">
         <v>1</v>
@@ -14732,7 +14879,7 @@
         <v>1</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="M266" s="1">
         <v>2130004</v>
@@ -14741,7 +14888,7 @@
         <v>0</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="R266" s="1">
         <v>999999</v>
@@ -14755,7 +14902,7 @@
         <v>1130005</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="E267" s="1">
         <v>1</v>
@@ -14773,7 +14920,7 @@
         <v>1</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="M267" s="1">
         <v>2130005</v>
@@ -14782,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>423</v>
+        <v>464</v>
       </c>
       <c r="R267" s="1">
         <v>999999</v>
@@ -14796,7 +14943,7 @@
         <v>1130006</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>424</v>
+        <v>465</v>
       </c>
       <c r="E268" s="1">
         <v>1</v>
@@ -14814,7 +14961,7 @@
         <v>1</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>425</v>
+        <v>466</v>
       </c>
       <c r="M268" s="1">
         <v>2130006</v>
@@ -14823,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="R268" s="1">
         <v>999999</v>
@@ -14837,7 +14984,7 @@
         <v>1131001</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>427</v>
+        <v>468</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -14861,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
     </row>
     <row r="270" spans="1:18">
@@ -14872,7 +15019,7 @@
         <v>1131002</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>429</v>
+        <v>470</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -14896,7 +15043,7 @@
         <v>0</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
     </row>
     <row r="271" spans="1:18">
@@ -14907,7 +15054,7 @@
         <v>1131003</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -14931,7 +15078,7 @@
         <v>0</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
     </row>
     <row r="272" spans="1:18">
@@ -14942,7 +15089,7 @@
         <v>1131004</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -14966,7 +15113,7 @@
         <v>0</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
     </row>
     <row r="273" spans="1:15">
@@ -14976,8 +15123,8 @@
       <c r="C273" s="1">
         <v>1131005</v>
       </c>
-      <c r="D273" s="14" t="s">
-        <v>435</v>
+      <c r="D273" s="15" t="s">
+        <v>476</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -15001,7 +15148,7 @@
         <v>0</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
     </row>
     <row r="274" spans="1:15">
@@ -15012,7 +15159,7 @@
         <v>1131006</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -15036,7 +15183,7 @@
         <v>0</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
     </row>
     <row r="275" spans="1:15">
@@ -15047,7 +15194,7 @@
         <v>1131101</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -15071,7 +15218,7 @@
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
     </row>
     <row r="276" spans="1:15">
@@ -15082,7 +15229,7 @@
         <v>1131102</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -15106,7 +15253,7 @@
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
     </row>
     <row r="277" spans="1:15">
@@ -15117,7 +15264,7 @@
         <v>1131103</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>441</v>
+        <v>482</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -15141,7 +15288,7 @@
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
     </row>
     <row r="278" spans="1:15">
@@ -15152,7 +15299,7 @@
         <v>1131104</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -15176,7 +15323,7 @@
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
     </row>
     <row r="279" spans="1:15">
@@ -15186,8 +15333,8 @@
       <c r="C279" s="1">
         <v>1131105</v>
       </c>
-      <c r="D279" s="14" t="s">
-        <v>443</v>
+      <c r="D279" s="15" t="s">
+        <v>484</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -15211,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
     </row>
     <row r="280" spans="1:15">
@@ -15222,7 +15369,7 @@
         <v>1131106</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -15246,7 +15393,7 @@
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
     </row>
     <row r="281" spans="1:15">
@@ -15257,7 +15404,7 @@
         <v>1131201</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>445</v>
+        <v>486</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15281,7 +15428,7 @@
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
     </row>
     <row r="282" spans="1:15">
@@ -15292,7 +15439,7 @@
         <v>1131202</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15316,7 +15463,7 @@
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
     </row>
     <row r="283" spans="1:15">
@@ -15327,7 +15474,7 @@
         <v>1131203</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15351,7 +15498,7 @@
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
     </row>
     <row r="284" spans="1:15">
@@ -15362,7 +15509,7 @@
         <v>1131204</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15386,7 +15533,7 @@
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
     </row>
     <row r="285" spans="1:15">
@@ -15396,8 +15543,8 @@
       <c r="C285" s="1">
         <v>1131205</v>
       </c>
-      <c r="D285" s="14" t="s">
-        <v>449</v>
+      <c r="D285" s="15" t="s">
+        <v>490</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15421,7 +15568,7 @@
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
     </row>
     <row r="286" spans="1:15">
@@ -15432,7 +15579,7 @@
         <v>1131206</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>450</v>
+        <v>491</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15456,7 +15603,7 @@
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
     </row>
     <row r="287" spans="1:15">
@@ -15467,7 +15614,7 @@
         <v>1131301</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -15491,7 +15638,7 @@
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
     </row>
     <row r="288" spans="1:15">
@@ -15502,7 +15649,7 @@
         <v>1131302</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -15526,7 +15673,7 @@
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
     </row>
     <row r="289" spans="1:15">
@@ -15537,7 +15684,7 @@
         <v>1131303</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -15561,7 +15708,7 @@
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
     </row>
     <row r="290" spans="1:15">
@@ -15572,7 +15719,7 @@
         <v>1131304</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -15596,7 +15743,7 @@
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:15">
@@ -15606,8 +15753,8 @@
       <c r="C291" s="1">
         <v>1131305</v>
       </c>
-      <c r="D291" s="14" t="s">
-        <v>455</v>
+      <c r="D291" s="15" t="s">
+        <v>496</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -15631,7 +15778,7 @@
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
     </row>
     <row r="292" spans="1:15">
@@ -15642,7 +15789,7 @@
         <v>1131306</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -15666,7 +15813,7 @@
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
     </row>
     <row r="293" spans="1:15">
@@ -15677,7 +15824,7 @@
         <v>1131401</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>457</v>
+        <v>498</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -15701,7 +15848,7 @@
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
     </row>
     <row r="294" spans="1:15">
@@ -15712,7 +15859,7 @@
         <v>1131402</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -15736,7 +15883,7 @@
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
     </row>
     <row r="295" spans="1:15">
@@ -15747,7 +15894,7 @@
         <v>1131403</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -15771,7 +15918,7 @@
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
     </row>
     <row r="296" spans="1:15">
@@ -15782,7 +15929,7 @@
         <v>1131404</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -15806,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
     </row>
     <row r="297" spans="1:15">
@@ -15816,8 +15963,8 @@
       <c r="C297" s="1">
         <v>1131405</v>
       </c>
-      <c r="D297" s="14" t="s">
-        <v>461</v>
+      <c r="D297" s="15" t="s">
+        <v>502</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -15841,7 +15988,7 @@
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
     </row>
     <row r="298" spans="1:15">
@@ -15852,7 +15999,7 @@
         <v>1131406</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>462</v>
+        <v>503</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -15876,7 +16023,7 @@
         <v>0</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
     </row>
     <row r="299" spans="1:15">
@@ -15887,7 +16034,7 @@
         <v>1140001</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>463</v>
+        <v>504</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -15905,7 +16052,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="M299" s="1">
         <v>2140001</v>
@@ -15914,7 +16061,7 @@
         <v>0</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>465</v>
+        <v>506</v>
       </c>
     </row>
     <row r="300" spans="1:15">
@@ -15925,7 +16072,7 @@
         <v>1140002</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -15943,7 +16090,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="M300" s="1">
         <v>2140002</v>
@@ -15952,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>468</v>
+        <v>509</v>
       </c>
     </row>
     <row r="301" spans="1:15">
@@ -15963,7 +16110,7 @@
         <v>1140003</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>469</v>
+        <v>510</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -15981,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="M301" s="1">
         <v>2140003</v>
@@ -15990,7 +16137,7 @@
         <v>0</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
     </row>
     <row r="302" spans="1:15">
@@ -16001,7 +16148,7 @@
         <v>1140004</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -16019,7 +16166,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="M302" s="1">
         <v>2140004</v>
@@ -16028,7 +16175,7 @@
         <v>0</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
     </row>
     <row r="303" spans="1:15">
@@ -16039,7 +16186,7 @@
         <v>1140005</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -16057,7 +16204,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="M303" s="1">
         <v>2140005</v>
@@ -16066,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>477</v>
+        <v>518</v>
       </c>
     </row>
     <row r="304" spans="1:15">
@@ -16077,7 +16224,7 @@
         <v>1140006</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>478</v>
+        <v>519</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -16095,7 +16242,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="M304" s="1">
         <v>2140006</v>
@@ -16104,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
     </row>
     <row r="305" spans="1:18">
@@ -16115,7 +16262,7 @@
         <v>1150001</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>481</v>
+        <v>522</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -16133,7 +16280,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>482</v>
+        <v>523</v>
       </c>
       <c r="M305" s="1">
         <v>2150001</v>
@@ -16157,7 +16304,7 @@
         <v>1150002</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>483</v>
+        <v>524</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -16175,7 +16322,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>484</v>
+        <v>525</v>
       </c>
       <c r="M306" s="1">
         <v>2150002</v>
@@ -16199,7 +16346,7 @@
         <v>1150003</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>485</v>
+        <v>526</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -16217,7 +16364,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="M307" s="1">
         <v>2150003</v>
@@ -16241,7 +16388,7 @@
         <v>1150004</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16259,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>488</v>
+        <v>529</v>
       </c>
       <c r="M308" s="1">
         <v>2150004</v>
@@ -16283,7 +16430,7 @@
         <v>1150005</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16301,7 +16448,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>490</v>
+        <v>531</v>
       </c>
       <c r="M309" s="1">
         <v>2150005</v>
@@ -16325,7 +16472,7 @@
         <v>1150006</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16343,7 +16490,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="M310" s="1">
         <v>2150006</v>
@@ -16367,7 +16514,7 @@
         <v>1150007</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>493</v>
+        <v>534</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -16385,7 +16532,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="M311" s="1">
         <v>2150007</v>
@@ -16409,7 +16556,7 @@
         <v>1150008</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -16427,7 +16574,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="M312" s="1">
         <v>2150008</v>
@@ -16451,7 +16598,7 @@
         <v>1150009</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -16469,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="M313" s="1">
         <v>2150009</v>
@@ -16493,7 +16640,7 @@
         <v>1150010</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -16511,7 +16658,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>500</v>
+        <v>541</v>
       </c>
       <c r="M314" s="1">
         <v>2150010</v>
@@ -16535,7 +16682,7 @@
         <v>1150011</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -16553,7 +16700,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="M315" s="1">
         <v>2150011</v>
@@ -16577,7 +16724,7 @@
         <v>1150012</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -16595,7 +16742,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="M316" s="1">
         <v>2150012</v>
@@ -16619,7 +16766,7 @@
         <v>1150013</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -16637,7 +16784,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="M317" s="1">
         <v>2150013</v>
@@ -16661,7 +16808,7 @@
         <v>1150014</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>507</v>
+        <v>548</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -16679,7 +16826,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="M318" s="1">
         <v>2150014</v>
@@ -16703,7 +16850,7 @@
         <v>1150015</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -16721,7 +16868,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>510</v>
+        <v>551</v>
       </c>
       <c r="M319" s="1">
         <v>2150015</v>
@@ -16745,7 +16892,7 @@
         <v>1150016</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -16763,7 +16910,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>512</v>
+        <v>553</v>
       </c>
       <c r="M320" s="1">
         <v>2150016</v>
@@ -16787,7 +16934,7 @@
         <v>1150017</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -16805,7 +16952,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>514</v>
+        <v>555</v>
       </c>
       <c r="M321" s="1">
         <v>2150017</v>
@@ -16829,7 +16976,7 @@
         <v>1150018</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -16847,7 +16994,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="M322" s="1">
         <v>2150018</v>
@@ -16871,7 +17018,7 @@
         <v>1150019</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -16889,7 +17036,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="M323" s="1">
         <v>2150019</v>
@@ -16913,7 +17060,7 @@
         <v>1150020</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -16931,7 +17078,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>520</v>
+        <v>561</v>
       </c>
       <c r="M324" s="1">
         <v>2150020</v>
@@ -16955,7 +17102,7 @@
         <v>1150021</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -16973,7 +17120,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="M325" s="1">
         <v>2150021</v>
@@ -16997,7 +17144,7 @@
         <v>1150022</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>523</v>
+        <v>564</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -17015,7 +17162,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="M326" s="1">
         <v>2150022</v>
@@ -17039,7 +17186,7 @@
         <v>1150023</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>525</v>
+        <v>566</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -17057,7 +17204,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>526</v>
+        <v>567</v>
       </c>
       <c r="M327" s="1">
         <v>2150023</v>
@@ -17081,7 +17228,7 @@
         <v>1150024</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>527</v>
+        <v>568</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -17099,7 +17246,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>528</v>
+        <v>569</v>
       </c>
       <c r="M328" s="1">
         <v>2150024</v>
@@ -17123,7 +17270,7 @@
         <v>1150025</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>529</v>
+        <v>570</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -17141,7 +17288,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>530</v>
+        <v>571</v>
       </c>
       <c r="M329" s="1">
         <v>2150025</v>
@@ -17165,7 +17312,7 @@
         <v>1150026</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>531</v>
+        <v>572</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -17183,7 +17330,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>532</v>
+        <v>573</v>
       </c>
       <c r="M330" s="1">
         <v>2150026</v>
@@ -17207,7 +17354,7 @@
         <v>1150027</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>533</v>
+        <v>574</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17225,7 +17372,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>534</v>
+        <v>575</v>
       </c>
       <c r="M331" s="1">
         <v>2150027</v>
@@ -17249,7 +17396,7 @@
         <v>1150028</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17267,7 +17414,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="M332" s="1">
         <v>2150028</v>
@@ -17291,7 +17438,7 @@
         <v>1150029</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17309,7 +17456,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>538</v>
+        <v>579</v>
       </c>
       <c r="M333" s="1">
         <v>2150029</v>
@@ -17333,7 +17480,7 @@
         <v>1150030</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>539</v>
+        <v>580</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -17351,7 +17498,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>540</v>
+        <v>581</v>
       </c>
       <c r="M334" s="1">
         <v>2150030</v>
@@ -17375,7 +17522,7 @@
         <v>1150031</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>541</v>
+        <v>582</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -17393,7 +17540,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="M335" s="1">
         <v>2150031</v>
@@ -17417,7 +17564,7 @@
         <v>1150032</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>543</v>
+        <v>584</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -17435,7 +17582,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>544</v>
+        <v>585</v>
       </c>
       <c r="M336" s="1">
         <v>2150032</v>
@@ -17459,7 +17606,7 @@
         <v>1150033</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>545</v>
+        <v>586</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -17477,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>546</v>
+        <v>587</v>
       </c>
       <c r="M337" s="1">
         <v>2150033</v>
@@ -17501,7 +17648,7 @@
         <v>1150034</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>547</v>
+        <v>588</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -17519,7 +17666,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>548</v>
+        <v>589</v>
       </c>
       <c r="M338" s="1">
         <v>2150034</v>
@@ -17543,7 +17690,7 @@
         <v>1150035</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>549</v>
+        <v>590</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -17561,7 +17708,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>550</v>
+        <v>591</v>
       </c>
       <c r="M339" s="1">
         <v>2150035</v>
@@ -17585,7 +17732,7 @@
         <v>1150036</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>551</v>
+        <v>592</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -17603,7 +17750,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>552</v>
+        <v>593</v>
       </c>
       <c r="M340" s="1">
         <v>2150036</v>
@@ -17627,7 +17774,7 @@
         <v>1150037</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>553</v>
+        <v>594</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -17645,7 +17792,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>554</v>
+        <v>595</v>
       </c>
       <c r="M341" s="1">
         <v>2150037</v>
@@ -17669,7 +17816,7 @@
         <v>1150038</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>555</v>
+        <v>596</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -17687,7 +17834,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="M342" s="1">
         <v>2150038</v>
@@ -17711,7 +17858,7 @@
         <v>1150039</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -17729,7 +17876,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="M343" s="1">
         <v>2150039</v>
@@ -17753,7 +17900,7 @@
         <v>1150040</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>559</v>
+        <v>600</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -17771,7 +17918,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>560</v>
+        <v>601</v>
       </c>
       <c r="M344" s="1">
         <v>2150040</v>
@@ -17795,7 +17942,7 @@
         <v>1150041</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>561</v>
+        <v>602</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -17813,7 +17960,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>562</v>
+        <v>603</v>
       </c>
       <c r="M345" s="1">
         <v>2150041</v>
@@ -17837,7 +17984,7 @@
         <v>1150042</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -17855,7 +18002,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="M346" s="1">
         <v>2150042</v>
@@ -17879,7 +18026,7 @@
         <v>1150043</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -17897,7 +18044,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
       <c r="M347" s="1">
         <v>2150043</v>
@@ -17921,7 +18068,7 @@
         <v>1150044</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>567</v>
+        <v>608</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -17939,7 +18086,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>568</v>
+        <v>609</v>
       </c>
       <c r="M348" s="1">
         <v>2150044</v>
@@ -17963,7 +18110,7 @@
         <v>1150045</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>569</v>
+        <v>610</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -17981,7 +18128,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>570</v>
+        <v>611</v>
       </c>
       <c r="M349" s="1">
         <v>2150045</v>
@@ -18005,7 +18152,7 @@
         <v>1150046</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>571</v>
+        <v>612</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -18023,7 +18170,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="M350" s="1">
         <v>2150046</v>
@@ -18047,7 +18194,7 @@
         <v>1150047</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -18065,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="M351" s="1">
         <v>2150047</v>
@@ -18089,7 +18236,7 @@
         <v>1150048</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>575</v>
+        <v>616</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -18107,7 +18254,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>576</v>
+        <v>617</v>
       </c>
       <c r="M352" s="1">
         <v>2150048</v>
@@ -18131,7 +18278,7 @@
         <v>1150049</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>577</v>
+        <v>618</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -18149,7 +18296,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>578</v>
+        <v>619</v>
       </c>
       <c r="M353" s="1">
         <v>2150049</v>
@@ -18173,7 +18320,7 @@
         <v>1150050</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>579</v>
+        <v>620</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -18191,7 +18338,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>580</v>
+        <v>621</v>
       </c>
       <c r="M354" s="1">
         <v>2150050</v>
@@ -18215,7 +18362,7 @@
         <v>1150051</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>581</v>
+        <v>622</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18233,7 +18380,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>582</v>
+        <v>623</v>
       </c>
       <c r="M355" s="1">
         <v>2150051</v>
@@ -18257,7 +18404,7 @@
         <v>1150052</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>583</v>
+        <v>624</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18275,7 +18422,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>584</v>
+        <v>625</v>
       </c>
       <c r="M356" s="1">
         <v>2150052</v>
@@ -18299,7 +18446,7 @@
         <v>1150053</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>585</v>
+        <v>626</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18317,7 +18464,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>586</v>
+        <v>627</v>
       </c>
       <c r="M357" s="1">
         <v>2150053</v>
@@ -18341,7 +18488,7 @@
         <v>1150054</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>587</v>
+        <v>628</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -18359,7 +18506,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>588</v>
+        <v>629</v>
       </c>
       <c r="M358" s="1">
         <v>2150054</v>
@@ -18383,7 +18530,7 @@
         <v>1150055</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>589</v>
+        <v>630</v>
       </c>
       <c r="E359" s="1">
         <v>2</v>
@@ -18401,7 +18548,7 @@
         <v>0</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>590</v>
+        <v>631</v>
       </c>
       <c r="M359" s="1">
         <v>2150055</v>
@@ -18425,7 +18572,7 @@
         <v>1150056</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>591</v>
+        <v>632</v>
       </c>
       <c r="E360" s="1">
         <v>2</v>
@@ -18443,7 +18590,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>592</v>
+        <v>633</v>
       </c>
       <c r="M360" s="1">
         <v>2150056</v>
@@ -18467,7 +18614,7 @@
         <v>1150057</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>593</v>
+        <v>634</v>
       </c>
       <c r="E361" s="1">
         <v>2</v>
@@ -18485,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="M361" s="1">
         <v>2150057</v>
@@ -18509,7 +18656,7 @@
         <v>1150058</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>595</v>
+        <v>636</v>
       </c>
       <c r="E362" s="1">
         <v>2</v>
@@ -18527,7 +18674,7 @@
         <v>0</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>596</v>
+        <v>637</v>
       </c>
       <c r="M362" s="1">
         <v>2150058</v>
@@ -18551,7 +18698,7 @@
         <v>1150059</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>597</v>
+        <v>638</v>
       </c>
       <c r="E363" s="1">
         <v>2</v>
@@ -18569,7 +18716,7 @@
         <v>0</v>
       </c>
       <c r="L363" s="1" t="s">
-        <v>598</v>
+        <v>639</v>
       </c>
       <c r="M363" s="1">
         <v>2150059</v>
@@ -18593,7 +18740,7 @@
         <v>1150060</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>599</v>
+        <v>640</v>
       </c>
       <c r="E364" s="1">
         <v>2</v>
@@ -18611,7 +18758,7 @@
         <v>0</v>
       </c>
       <c r="L364" s="1" t="s">
-        <v>600</v>
+        <v>641</v>
       </c>
       <c r="M364" s="1">
         <v>2150060</v>
@@ -18635,7 +18782,7 @@
         <v>1150061</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>601</v>
+        <v>642</v>
       </c>
       <c r="E365" s="1">
         <v>2</v>
@@ -18653,7 +18800,7 @@
         <v>0</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="M365" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="668">
   <si>
     <t>道具ID</t>
   </si>
@@ -1795,109 +1795,181 @@
     <t>基础命中.白</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+%s</t>
+    <t>普通模式Spin基础中奖概率+3%</t>
   </si>
   <si>
     <t>免费命中.白</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内中奖概率+%s</t>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+1%</t>
   </si>
   <si>
     <t>基础收益.白</t>
   </si>
   <si>
-    <t>10-20倍区间的中奖概率+%s</t>
+    <t>5-10倍区间的中奖概率+2%</t>
   </si>
   <si>
     <t>大奖冲刺.白</t>
   </si>
   <si>
-    <t>50-100倍区间的触发概率+%s</t>
+    <t>20-50倍区间的触发概率+2%</t>
   </si>
   <si>
     <t>下注提升.白</t>
   </si>
   <si>
-    <t>下注的金额提升到%s</t>
+    <t>下注的金额提升到200%</t>
   </si>
   <si>
     <t>免费模式.白</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+%s</t>
+    <t>进入免费旋转模式的概率+2%</t>
   </si>
   <si>
     <t>基础命中.绿</t>
   </si>
   <si>
+    <t>普通模式Spin基础中奖概率+6%</t>
+  </si>
+  <si>
     <t>免费命中.绿</t>
   </si>
   <si>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+2%</t>
+  </si>
+  <si>
     <t>基础收益.绿</t>
   </si>
   <si>
+    <t>5-10倍区间的中奖概率+4%</t>
+  </si>
+  <si>
     <t>大奖冲刺.绿</t>
   </si>
   <si>
+    <t>20-50倍区间的触发概率+4%</t>
+  </si>
+  <si>
     <t>下注提升.绿</t>
   </si>
   <si>
+    <t>下注的金额提升到400%</t>
+  </si>
+  <si>
     <t>免费模式.绿</t>
   </si>
   <si>
+    <t>进入免费旋转模式的概率+4%</t>
+  </si>
+  <si>
     <t>基础命中.蓝</t>
   </si>
   <si>
+    <t>普通模式Spin基础中奖概率+10%</t>
+  </si>
+  <si>
     <t>免费命中.蓝</t>
   </si>
   <si>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+3%</t>
+  </si>
+  <si>
     <t>基础收益.蓝</t>
   </si>
   <si>
+    <t>5-10倍区间的中奖概率+6%</t>
+  </si>
+  <si>
     <t>大奖冲刺.蓝</t>
   </si>
   <si>
+    <t>20-50倍区间的触发概率+6%</t>
+  </si>
+  <si>
     <t>下注提升.蓝</t>
   </si>
   <si>
+    <t>下注的金额提升到600%</t>
+  </si>
+  <si>
     <t>免费模式.蓝</t>
   </si>
   <si>
+    <t>进入免费旋转模式的概率+6%</t>
+  </si>
+  <si>
     <t>基础命中.紫</t>
   </si>
   <si>
+    <t>普通模式Spin基础中奖概率+15%</t>
+  </si>
+  <si>
     <t>免费命中.紫</t>
   </si>
   <si>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+4%</t>
+  </si>
+  <si>
     <t>基础收益.紫</t>
   </si>
   <si>
+    <t>5-10倍区间的中奖概率+8%</t>
+  </si>
+  <si>
     <t>大奖冲刺.紫</t>
   </si>
   <si>
+    <t>20-50倍区间的触发概率+8%</t>
+  </si>
+  <si>
     <t>下注提升.紫</t>
   </si>
   <si>
+    <t>下注的金额提升到800%</t>
+  </si>
+  <si>
     <t>免费模式.紫</t>
   </si>
   <si>
+    <t>进入免费旋转模式的概率+8%</t>
+  </si>
+  <si>
     <t>基础命中.橙</t>
   </si>
   <si>
+    <t>普通模式Spin基础中奖概率+20%</t>
+  </si>
+  <si>
     <t>免费命中.橙</t>
   </si>
   <si>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+5%</t>
+  </si>
+  <si>
     <t>基础收益.橙</t>
   </si>
   <si>
+    <t>5-10倍区间的中奖概率+10%</t>
+  </si>
+  <si>
     <t>大奖冲刺.橙</t>
   </si>
   <si>
+    <t>20-50倍区间的触发概率+10%</t>
+  </si>
+  <si>
     <t>下注提升.橙</t>
   </si>
   <si>
+    <t>下注的金额提升到1000%</t>
+  </si>
+  <si>
     <t>免费模式.橙</t>
+  </si>
+  <si>
+    <t>进入免费旋转模式的概率+10%</t>
   </si>
   <si>
     <t>倔强青铜</t>
@@ -15218,7 +15290,7 @@
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
     </row>
     <row r="276" spans="1:15">
@@ -15229,7 +15301,7 @@
         <v>1131102</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -15253,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
     </row>
     <row r="277" spans="1:15">
@@ -15264,7 +15336,7 @@
         <v>1131103</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -15288,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
     </row>
     <row r="278" spans="1:15">
@@ -15299,7 +15371,7 @@
         <v>1131104</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -15323,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
     </row>
     <row r="279" spans="1:15">
@@ -15334,7 +15406,7 @@
         <v>1131105</v>
       </c>
       <c r="D279" s="15" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -15358,7 +15430,7 @@
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
     </row>
     <row r="280" spans="1:15">
@@ -15369,7 +15441,7 @@
         <v>1131106</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -15393,7 +15465,7 @@
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="281" spans="1:15">
@@ -15404,7 +15476,7 @@
         <v>1131201</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15428,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
     </row>
     <row r="282" spans="1:15">
@@ -15439,7 +15511,7 @@
         <v>1131202</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15463,7 +15535,7 @@
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
     </row>
     <row r="283" spans="1:15">
@@ -15474,7 +15546,7 @@
         <v>1131203</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15498,7 +15570,7 @@
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
     </row>
     <row r="284" spans="1:15">
@@ -15509,7 +15581,7 @@
         <v>1131204</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15533,7 +15605,7 @@
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
     </row>
     <row r="285" spans="1:15">
@@ -15544,7 +15616,7 @@
         <v>1131205</v>
       </c>
       <c r="D285" s="15" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15568,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
     </row>
     <row r="286" spans="1:15">
@@ -15579,7 +15651,7 @@
         <v>1131206</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15603,7 +15675,7 @@
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
     </row>
     <row r="287" spans="1:15">
@@ -15614,7 +15686,7 @@
         <v>1131301</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -15638,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>469</v>
+        <v>505</v>
       </c>
     </row>
     <row r="288" spans="1:15">
@@ -15649,7 +15721,7 @@
         <v>1131302</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -15673,7 +15745,7 @@
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>471</v>
+        <v>507</v>
       </c>
     </row>
     <row r="289" spans="1:15">
@@ -15684,7 +15756,7 @@
         <v>1131303</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -15708,7 +15780,7 @@
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>473</v>
+        <v>509</v>
       </c>
     </row>
     <row r="290" spans="1:15">
@@ -15719,7 +15791,7 @@
         <v>1131304</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -15743,7 +15815,7 @@
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>475</v>
+        <v>511</v>
       </c>
     </row>
     <row r="291" spans="1:15">
@@ -15754,7 +15826,7 @@
         <v>1131305</v>
       </c>
       <c r="D291" s="15" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -15778,7 +15850,7 @@
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>477</v>
+        <v>513</v>
       </c>
     </row>
     <row r="292" spans="1:15">
@@ -15789,7 +15861,7 @@
         <v>1131306</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -15813,7 +15885,7 @@
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>479</v>
+        <v>515</v>
       </c>
     </row>
     <row r="293" spans="1:15">
@@ -15824,7 +15896,7 @@
         <v>1131401</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -15848,7 +15920,7 @@
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>469</v>
+        <v>517</v>
       </c>
     </row>
     <row r="294" spans="1:15">
@@ -15859,7 +15931,7 @@
         <v>1131402</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -15883,7 +15955,7 @@
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>471</v>
+        <v>519</v>
       </c>
     </row>
     <row r="295" spans="1:15">
@@ -15894,7 +15966,7 @@
         <v>1131403</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -15918,7 +15990,7 @@
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
     </row>
     <row r="296" spans="1:15">
@@ -15929,7 +16001,7 @@
         <v>1131404</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -15953,7 +16025,7 @@
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>475</v>
+        <v>523</v>
       </c>
     </row>
     <row r="297" spans="1:15">
@@ -15964,7 +16036,7 @@
         <v>1131405</v>
       </c>
       <c r="D297" s="15" t="s">
-        <v>502</v>
+        <v>524</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -15988,7 +16060,7 @@
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>477</v>
+        <v>525</v>
       </c>
     </row>
     <row r="298" spans="1:15">
@@ -15999,7 +16071,7 @@
         <v>1131406</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -16023,7 +16095,7 @@
         <v>0</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>479</v>
+        <v>527</v>
       </c>
     </row>
     <row r="299" spans="1:15">
@@ -16034,7 +16106,7 @@
         <v>1140001</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -16052,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="M299" s="1">
         <v>2140001</v>
@@ -16061,7 +16133,7 @@
         <v>0</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
     </row>
     <row r="300" spans="1:15">
@@ -16072,7 +16144,7 @@
         <v>1140002</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -16090,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="M300" s="1">
         <v>2140002</v>
@@ -16099,7 +16171,7 @@
         <v>0</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
     </row>
     <row r="301" spans="1:15">
@@ -16110,7 +16182,7 @@
         <v>1140003</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -16128,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="M301" s="1">
         <v>2140003</v>
@@ -16137,7 +16209,7 @@
         <v>0</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
     </row>
     <row r="302" spans="1:15">
@@ -16148,7 +16220,7 @@
         <v>1140004</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -16166,7 +16238,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="M302" s="1">
         <v>2140004</v>
@@ -16175,7 +16247,7 @@
         <v>0</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
     </row>
     <row r="303" spans="1:15">
@@ -16186,7 +16258,7 @@
         <v>1140005</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -16204,7 +16276,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="M303" s="1">
         <v>2140005</v>
@@ -16213,7 +16285,7 @@
         <v>0</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
     </row>
     <row r="304" spans="1:15">
@@ -16224,7 +16296,7 @@
         <v>1140006</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -16242,7 +16314,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
       <c r="M304" s="1">
         <v>2140006</v>
@@ -16251,7 +16323,7 @@
         <v>0</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>521</v>
+        <v>545</v>
       </c>
     </row>
     <row r="305" spans="1:18">
@@ -16262,7 +16334,7 @@
         <v>1150001</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -16280,7 +16352,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="M305" s="1">
         <v>2150001</v>
@@ -16304,7 +16376,7 @@
         <v>1150002</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -16322,7 +16394,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="M306" s="1">
         <v>2150002</v>
@@ -16346,7 +16418,7 @@
         <v>1150003</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -16364,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="M307" s="1">
         <v>2150003</v>
@@ -16388,7 +16460,7 @@
         <v>1150004</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16406,7 +16478,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="M308" s="1">
         <v>2150004</v>
@@ -16430,7 +16502,7 @@
         <v>1150005</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16448,7 +16520,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="M309" s="1">
         <v>2150005</v>
@@ -16472,7 +16544,7 @@
         <v>1150006</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16490,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="M310" s="1">
         <v>2150006</v>
@@ -16514,7 +16586,7 @@
         <v>1150007</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -16532,7 +16604,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="M311" s="1">
         <v>2150007</v>
@@ -16556,7 +16628,7 @@
         <v>1150008</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -16574,7 +16646,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="M312" s="1">
         <v>2150008</v>
@@ -16598,7 +16670,7 @@
         <v>1150009</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -16616,7 +16688,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="M313" s="1">
         <v>2150009</v>
@@ -16640,7 +16712,7 @@
         <v>1150010</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -16658,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="M314" s="1">
         <v>2150010</v>
@@ -16682,7 +16754,7 @@
         <v>1150011</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>542</v>
+        <v>566</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -16700,7 +16772,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="M315" s="1">
         <v>2150011</v>
@@ -16724,7 +16796,7 @@
         <v>1150012</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>544</v>
+        <v>568</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -16742,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="M316" s="1">
         <v>2150012</v>
@@ -16766,7 +16838,7 @@
         <v>1150013</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -16784,7 +16856,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="M317" s="1">
         <v>2150013</v>
@@ -16808,7 +16880,7 @@
         <v>1150014</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -16826,7 +16898,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="M318" s="1">
         <v>2150014</v>
@@ -16850,7 +16922,7 @@
         <v>1150015</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>550</v>
+        <v>574</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -16868,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="M319" s="1">
         <v>2150015</v>
@@ -16892,7 +16964,7 @@
         <v>1150016</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -16910,7 +16982,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="M320" s="1">
         <v>2150016</v>
@@ -16934,7 +17006,7 @@
         <v>1150017</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -16952,7 +17024,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="M321" s="1">
         <v>2150017</v>
@@ -16976,7 +17048,7 @@
         <v>1150018</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>556</v>
+        <v>580</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -16994,7 +17066,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="M322" s="1">
         <v>2150018</v>
@@ -17018,7 +17090,7 @@
         <v>1150019</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -17036,7 +17108,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>559</v>
+        <v>583</v>
       </c>
       <c r="M323" s="1">
         <v>2150019</v>
@@ -17060,7 +17132,7 @@
         <v>1150020</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -17078,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>561</v>
+        <v>585</v>
       </c>
       <c r="M324" s="1">
         <v>2150020</v>
@@ -17102,7 +17174,7 @@
         <v>1150021</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -17120,7 +17192,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>563</v>
+        <v>587</v>
       </c>
       <c r="M325" s="1">
         <v>2150021</v>
@@ -17144,7 +17216,7 @@
         <v>1150022</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>564</v>
+        <v>588</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -17162,7 +17234,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="M326" s="1">
         <v>2150022</v>
@@ -17186,7 +17258,7 @@
         <v>1150023</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>566</v>
+        <v>590</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -17204,7 +17276,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="M327" s="1">
         <v>2150023</v>
@@ -17228,7 +17300,7 @@
         <v>1150024</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -17246,7 +17318,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="M328" s="1">
         <v>2150024</v>
@@ -17270,7 +17342,7 @@
         <v>1150025</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -17288,7 +17360,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="M329" s="1">
         <v>2150025</v>
@@ -17312,7 +17384,7 @@
         <v>1150026</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -17330,7 +17402,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="M330" s="1">
         <v>2150026</v>
@@ -17354,7 +17426,7 @@
         <v>1150027</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17372,7 +17444,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="M331" s="1">
         <v>2150027</v>
@@ -17396,7 +17468,7 @@
         <v>1150028</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17414,7 +17486,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="M332" s="1">
         <v>2150028</v>
@@ -17438,7 +17510,7 @@
         <v>1150029</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17456,7 +17528,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="M333" s="1">
         <v>2150029</v>
@@ -17480,7 +17552,7 @@
         <v>1150030</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -17498,7 +17570,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="M334" s="1">
         <v>2150030</v>
@@ -17522,7 +17594,7 @@
         <v>1150031</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -17540,7 +17612,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="M335" s="1">
         <v>2150031</v>
@@ -17564,7 +17636,7 @@
         <v>1150032</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -17582,7 +17654,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="M336" s="1">
         <v>2150032</v>
@@ -17606,7 +17678,7 @@
         <v>1150033</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -17624,7 +17696,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="M337" s="1">
         <v>2150033</v>
@@ -17648,7 +17720,7 @@
         <v>1150034</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -17666,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="M338" s="1">
         <v>2150034</v>
@@ -17690,7 +17762,7 @@
         <v>1150035</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -17708,7 +17780,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="M339" s="1">
         <v>2150035</v>
@@ -17732,7 +17804,7 @@
         <v>1150036</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -17750,7 +17822,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="M340" s="1">
         <v>2150036</v>
@@ -17774,7 +17846,7 @@
         <v>1150037</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -17792,7 +17864,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="M341" s="1">
         <v>2150037</v>
@@ -17816,7 +17888,7 @@
         <v>1150038</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>596</v>
+        <v>620</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -17834,7 +17906,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="M342" s="1">
         <v>2150038</v>
@@ -17858,7 +17930,7 @@
         <v>1150039</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -17876,7 +17948,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="M343" s="1">
         <v>2150039</v>
@@ -17900,7 +17972,7 @@
         <v>1150040</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -17918,7 +17990,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="M344" s="1">
         <v>2150040</v>
@@ -17942,7 +18014,7 @@
         <v>1150041</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -17960,7 +18032,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="M345" s="1">
         <v>2150041</v>
@@ -17984,7 +18056,7 @@
         <v>1150042</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -18002,7 +18074,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="M346" s="1">
         <v>2150042</v>
@@ -18026,7 +18098,7 @@
         <v>1150043</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>606</v>
+        <v>630</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -18044,7 +18116,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="M347" s="1">
         <v>2150043</v>
@@ -18068,7 +18140,7 @@
         <v>1150044</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -18086,7 +18158,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="M348" s="1">
         <v>2150044</v>
@@ -18110,7 +18182,7 @@
         <v>1150045</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>610</v>
+        <v>634</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -18128,7 +18200,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>611</v>
+        <v>635</v>
       </c>
       <c r="M349" s="1">
         <v>2150045</v>
@@ -18152,7 +18224,7 @@
         <v>1150046</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -18170,7 +18242,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>613</v>
+        <v>637</v>
       </c>
       <c r="M350" s="1">
         <v>2150046</v>
@@ -18194,7 +18266,7 @@
         <v>1150047</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -18212,7 +18284,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="M351" s="1">
         <v>2150047</v>
@@ -18236,7 +18308,7 @@
         <v>1150048</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -18254,7 +18326,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="M352" s="1">
         <v>2150048</v>
@@ -18278,7 +18350,7 @@
         <v>1150049</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -18296,7 +18368,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="M353" s="1">
         <v>2150049</v>
@@ -18320,7 +18392,7 @@
         <v>1150050</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -18338,7 +18410,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="M354" s="1">
         <v>2150050</v>
@@ -18362,7 +18434,7 @@
         <v>1150051</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18380,7 +18452,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="M355" s="1">
         <v>2150051</v>
@@ -18404,7 +18476,7 @@
         <v>1150052</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18422,7 +18494,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>625</v>
+        <v>649</v>
       </c>
       <c r="M356" s="1">
         <v>2150052</v>
@@ -18446,7 +18518,7 @@
         <v>1150053</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18464,7 +18536,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="M357" s="1">
         <v>2150053</v>
@@ -18488,7 +18560,7 @@
         <v>1150054</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>628</v>
+        <v>652</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -18506,7 +18578,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>629</v>
+        <v>653</v>
       </c>
       <c r="M358" s="1">
         <v>2150054</v>
@@ -18530,7 +18602,7 @@
         <v>1150055</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="E359" s="1">
         <v>2</v>
@@ -18548,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>631</v>
+        <v>655</v>
       </c>
       <c r="M359" s="1">
         <v>2150055</v>
@@ -18572,7 +18644,7 @@
         <v>1150056</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>632</v>
+        <v>656</v>
       </c>
       <c r="E360" s="1">
         <v>2</v>
@@ -18590,7 +18662,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>633</v>
+        <v>657</v>
       </c>
       <c r="M360" s="1">
         <v>2150056</v>
@@ -18614,7 +18686,7 @@
         <v>1150057</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="E361" s="1">
         <v>2</v>
@@ -18632,7 +18704,7 @@
         <v>0</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>635</v>
+        <v>659</v>
       </c>
       <c r="M361" s="1">
         <v>2150057</v>
@@ -18656,7 +18728,7 @@
         <v>1150058</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>636</v>
+        <v>660</v>
       </c>
       <c r="E362" s="1">
         <v>2</v>
@@ -18674,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>637</v>
+        <v>661</v>
       </c>
       <c r="M362" s="1">
         <v>2150058</v>
@@ -18698,7 +18770,7 @@
         <v>1150059</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>638</v>
+        <v>662</v>
       </c>
       <c r="E363" s="1">
         <v>2</v>
@@ -18716,7 +18788,7 @@
         <v>0</v>
       </c>
       <c r="L363" s="1" t="s">
-        <v>639</v>
+        <v>663</v>
       </c>
       <c r="M363" s="1">
         <v>2150059</v>
@@ -18740,7 +18812,7 @@
         <v>1150060</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>640</v>
+        <v>664</v>
       </c>
       <c r="E364" s="1">
         <v>2</v>
@@ -18758,7 +18830,7 @@
         <v>0</v>
       </c>
       <c r="L364" s="1" t="s">
-        <v>641</v>
+        <v>665</v>
       </c>
       <c r="M364" s="1">
         <v>2150060</v>
@@ -18782,7 +18854,7 @@
         <v>1150061</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>642</v>
+        <v>666</v>
       </c>
       <c r="E365" s="1">
         <v>2</v>
@@ -18800,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>643</v>
+        <v>667</v>
       </c>
       <c r="M365" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="679">
   <si>
     <t>道具ID</t>
   </si>
@@ -961,15 +961,27 @@
     <t>雇员升级材料1</t>
   </si>
   <si>
+    <t>daoju_cailiao_1.png</t>
+  </si>
+  <si>
     <t>雇员升级材料2</t>
   </si>
   <si>
+    <t>daoju_cailiao_2.png</t>
+  </si>
+  <si>
     <t>雇员升级材料3</t>
   </si>
   <si>
+    <t>daoju_cailiao_3.png</t>
+  </si>
+  <si>
     <t>声誉值</t>
   </si>
   <si>
+    <t>daoju_syz.png</t>
+  </si>
+  <si>
     <t>联盟的升级经验</t>
   </si>
   <si>
@@ -1795,187 +1807,208 @@
     <t>基础命中.白</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+3%</t>
+    <t>sj_bs_tb_sj_b.png</t>
+  </si>
+  <si>
+    <t>普通模式Spin基础中奖概率+%s</t>
   </si>
   <si>
     <t>免费命中.白</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+1%</t>
+    <t>sj_bs_tb_sj_b_1.png</t>
+  </si>
+  <si>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+%s</t>
   </si>
   <si>
     <t>基础收益.白</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+2%</t>
+    <t>sj_bs_tb_f_b.png</t>
+  </si>
+  <si>
+    <t>5-10倍区间的中奖概率+%s</t>
   </si>
   <si>
     <t>大奖冲刺.白</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+2%</t>
+    <t>sj_bs_tb_f_b_1.png</t>
+  </si>
+  <si>
+    <t>20-50倍区间的触发概率+%s</t>
   </si>
   <si>
     <t>下注提升.白</t>
   </si>
   <si>
-    <t>下注的金额提升到200%</t>
+    <t>sj_bs_tb_sj_b-1.png</t>
+  </si>
+  <si>
+    <t>下注的金额提升到%s</t>
   </si>
   <si>
     <t>免费模式.白</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+2%</t>
+    <t>sj_bs_tb_sj_b_1_1.png</t>
+  </si>
+  <si>
+    <t>进入免费旋转模式的概率+%s</t>
   </si>
   <si>
     <t>基础命中.绿</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+6%</t>
+    <t>sj_bs_tb_sj_lv.png</t>
   </si>
   <si>
     <t>免费命中.绿</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+2%</t>
+    <t>sj_bs_tb_sj_lv_1.png</t>
   </si>
   <si>
     <t>基础收益.绿</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+4%</t>
+    <t>sj_bs_tb_f_lv.png</t>
   </si>
   <si>
     <t>大奖冲刺.绿</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+4%</t>
+    <t>sj_bs_tb_f_lv_1.png</t>
   </si>
   <si>
     <t>下注提升.绿</t>
   </si>
   <si>
-    <t>下注的金额提升到400%</t>
+    <t>sj_bs_tb_sj_lv-1.png</t>
   </si>
   <si>
     <t>免费模式.绿</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+4%</t>
+    <t>sj_bs_tb_sj_lv_1_1.png</t>
   </si>
   <si>
     <t>基础命中.蓝</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+10%</t>
+    <t>sj_bs_tb_sj_lan.png</t>
   </si>
   <si>
     <t>免费命中.蓝</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+3%</t>
+    <t>sj_bs_tb_sj_lan_1.png</t>
   </si>
   <si>
     <t>基础收益.蓝</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+6%</t>
+    <t>sj_bs_tb_f_lan.png</t>
   </si>
   <si>
     <t>大奖冲刺.蓝</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+6%</t>
+    <t>sj_bs_tb_f_lan_1.png</t>
   </si>
   <si>
     <t>下注提升.蓝</t>
   </si>
   <si>
-    <t>下注的金额提升到600%</t>
+    <t>sj_bs_tb_sj_lan-1.png</t>
   </si>
   <si>
     <t>免费模式.蓝</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+6%</t>
+    <t>sj_bs_tb_sj_lan_1_1.png</t>
   </si>
   <si>
     <t>基础命中.紫</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+15%</t>
+    <t>sj_bs_tb_sj_zi.png</t>
+  </si>
+  <si>
+    <t>普通模式Spin基础中奖概率+%ss</t>
   </si>
   <si>
     <t>免费命中.紫</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+4%</t>
+    <t>sj_bs_tb_sj_zi_1.png</t>
   </si>
   <si>
     <t>基础收益.紫</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+8%</t>
+    <t>sj_bs_tb_f_zi.png</t>
   </si>
   <si>
     <t>大奖冲刺.紫</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+8%</t>
+    <t>sj_bs_tb_f_zi_1.png</t>
   </si>
   <si>
     <t>下注提升.紫</t>
   </si>
   <si>
-    <t>下注的金额提升到800%</t>
+    <t>sj_bs_tb_sj_zi-1.png</t>
   </si>
   <si>
     <t>免费模式.紫</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+8%</t>
+    <t>sj_bs_tb_sj_zi_1_1.png</t>
   </si>
   <si>
     <t>基础命中.橙</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+20%</t>
+    <t>sj_bs_tb_sj_c.png</t>
   </si>
   <si>
     <t>免费命中.橙</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+5%</t>
+    <t>sj_bs_tb_sj_c_1.png</t>
   </si>
   <si>
     <t>基础收益.橙</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+10%</t>
+    <t>sj_bs_tb_f_c.png</t>
   </si>
   <si>
     <t>大奖冲刺.橙</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+10%</t>
+    <t>sj_bs_tb_f_c_1.png</t>
   </si>
   <si>
     <t>下注提升.橙</t>
   </si>
   <si>
-    <t>下注的金额提升到1000%</t>
+    <t>sj_bs_tb_sj_c-1.png</t>
   </si>
   <si>
     <t>免费模式.橙</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+10%</t>
+    <t>sj_bs_tb_sj_c_1_1.png</t>
   </si>
   <si>
     <t>倔强青铜</t>
   </si>
   <si>
-    <t>1140001.png</t>
+    <t>daoju_sjdwhz_1.png</t>
   </si>
   <si>
     <t>赛季段位玩法中，达到青铜段位可获得此徽章成就；</t>
@@ -1984,7 +2017,7 @@
     <t>不屈白银</t>
   </si>
   <si>
-    <t>1140002.png</t>
+    <t>daoju_sjdwhz_2.png</t>
   </si>
   <si>
     <t>赛季段位玩法中，达到白银段位可获得此徽章成就；</t>
@@ -1993,7 +2026,7 @@
     <t>荣耀黄金</t>
   </si>
   <si>
-    <t>1140003.png</t>
+    <t>daoju_sjdwhz_3.png</t>
   </si>
   <si>
     <t>赛季段位玩法中，达到黄金段位可获得此徽章成就；</t>
@@ -2002,7 +2035,7 @@
     <t>华贵铂金</t>
   </si>
   <si>
-    <t>1140004.png</t>
+    <t>daoju_sjdwhz_4.png</t>
   </si>
   <si>
     <t>赛季段位玩法中，达到铂金段位可获得此徽章成就；</t>
@@ -2011,7 +2044,7 @@
     <t>璀璨钻石</t>
   </si>
   <si>
-    <t>1140005.png</t>
+    <t>daoju_sjdwhz_5.png</t>
   </si>
   <si>
     <t>赛季段位玩法中，达到钻石段位可获得此徽章成就；</t>
@@ -2020,7 +2053,7 @@
     <t>最强王者</t>
   </si>
   <si>
-    <t>1140006.png</t>
+    <t>daoju_sjdwhz_6.png</t>
   </si>
   <si>
     <t>赛季段位玩法中，达到王者段位可获得此徽章成就；</t>
@@ -6713,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="M68" s="1">
         <v>2024008</v>
@@ -6736,7 +6769,7 @@
         <v>1024009</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
@@ -6754,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="M69" s="1">
         <v>2024009</v>
@@ -6763,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="R69" s="1">
         <v>999999</v>
@@ -6777,7 +6810,7 @@
         <v>1024010</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
@@ -6795,7 +6828,7 @@
         <v>1</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="M70" s="1">
         <v>2024010</v>
@@ -6804,7 +6837,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="R70" s="1">
         <v>999999</v>
@@ -6818,7 +6851,7 @@
         <v>1024011</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
@@ -6836,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="M71" s="1">
         <v>2024011</v>
@@ -6845,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="R71" s="1">
         <v>-1</v>
@@ -6859,7 +6892,7 @@
         <v>1024012</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
@@ -6877,7 +6910,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="M72" s="1">
         <v>2024012</v>
@@ -6886,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="R72" s="1">
         <v>-1</v>
@@ -6900,7 +6933,7 @@
         <v>1024013</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -6927,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="R73" s="1">
         <v>999999</v>
@@ -6941,7 +6974,7 @@
         <v>1024014</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -6968,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="R74" s="1">
         <v>999999</v>
@@ -6982,7 +7015,7 @@
         <v>1024015</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7009,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="R75" s="1">
         <v>999999</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -7026,7 +7059,7 @@
         <v>1024016</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7053,13 +7086,13 @@
         <v>0</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="R76" s="1">
         <v>999999</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -7070,7 +7103,7 @@
         <v>1024017</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -7097,7 +7130,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="R77" s="1">
         <v>999999</v>
@@ -7111,7 +7144,7 @@
         <v>1024018</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -7129,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M78" s="1">
         <v>2024018</v>
@@ -7138,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="R78" s="1">
         <v>-1</v>
@@ -7152,7 +7185,7 @@
         <v>1024019</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
@@ -7170,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M79" s="1">
         <v>2024019</v>
@@ -7179,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -7190,25 +7223,25 @@
         <v>1024020</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I80" s="1">
+        <v>1</v>
+      </c>
+      <c r="J80" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="E80" s="1">
-        <v>2</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I80" s="1">
-        <v>1</v>
-      </c>
-      <c r="J80" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L80" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="M80" s="1">
         <v>2024020</v>
@@ -7217,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -7228,7 +7261,7 @@
         <v>1024021</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -7246,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M81" s="1">
         <v>2024021</v>
@@ -7255,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -7266,7 +7299,7 @@
         <v>1024022</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -7284,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M82" s="1">
         <v>2024022</v>
@@ -7293,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -7304,7 +7337,7 @@
         <v>1024023</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -7322,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M83" s="1">
         <v>2024023</v>
@@ -7331,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" ht="17.25" spans="1:18">
@@ -7342,7 +7375,7 @@
         <v>1024024</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -7366,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M84" s="1">
         <v>2024024</v>
@@ -7375,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="R84" s="1">
         <v>999999</v>
@@ -7389,7 +7422,7 @@
         <v>1024024</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -7413,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M85" s="1">
         <v>2024025</v>
@@ -7422,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="R85" s="1">
         <v>999999</v>
@@ -7436,7 +7469,7 @@
         <v>1024024</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
@@ -7460,7 +7493,7 @@
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M86" s="1">
         <v>2024026</v>
@@ -7469,7 +7502,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="R86" s="1">
         <v>999999</v>
@@ -7483,7 +7516,7 @@
         <v>1024024</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -7507,7 +7540,7 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M87" s="1">
         <v>2024027</v>
@@ -7516,7 +7549,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="R87" s="1">
         <v>999999</v>
@@ -7530,7 +7563,7 @@
         <v>1024024</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -7554,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="M88" s="1">
         <v>2024028</v>
@@ -7563,7 +7596,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="R88" s="1">
         <v>999999</v>
@@ -7577,7 +7610,7 @@
         <v>1024024</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -7601,7 +7634,7 @@
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M89" s="1">
         <v>2024029</v>
@@ -7610,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="R89" s="1">
         <v>999999</v>
@@ -7624,7 +7657,7 @@
         <v>1024024</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -7648,7 +7681,7 @@
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="M90" s="1">
         <v>2024030</v>
@@ -7657,7 +7690,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="R90" s="1">
         <v>999999</v>
@@ -7671,7 +7704,7 @@
         <v>1024024</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
@@ -7695,7 +7728,7 @@
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="M91" s="1">
         <v>2024031</v>
@@ -7704,7 +7737,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="R91" s="1">
         <v>999999</v>
@@ -7718,7 +7751,7 @@
         <v>1024024</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -7742,7 +7775,7 @@
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="M92" s="1">
         <v>2024032</v>
@@ -7751,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="R92" s="1">
         <v>999999</v>
@@ -7765,7 +7798,7 @@
         <v>1024024</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
@@ -7789,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="M93" s="1">
         <v>2024033</v>
@@ -7798,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="R93" s="1">
         <v>999999</v>
@@ -7812,7 +7845,7 @@
         <v>1024025</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -7836,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="R94" s="1">
         <v>999999</v>
@@ -7850,7 +7883,7 @@
         <v>1024026</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -7874,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="R95" s="1">
         <v>999999</v>
@@ -7888,7 +7921,7 @@
         <v>1024027</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -7912,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="R96" s="1">
         <v>999999</v>
@@ -7926,7 +7959,7 @@
         <v>1024028</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -7950,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="R97" s="1">
         <v>999999</v>
@@ -7964,7 +7997,7 @@
         <v>1024029</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -7988,7 +8021,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="R98" s="1">
         <v>999999</v>
@@ -8002,7 +8035,7 @@
         <v>1024030</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -8026,7 +8059,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="R99" s="1">
         <v>999999</v>
@@ -8040,7 +8073,7 @@
         <v>1024024</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -8064,7 +8097,7 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="M100" s="1">
         <v>2024040</v>
@@ -8073,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="R100" s="1">
         <v>999999</v>
@@ -8116,7 +8149,7 @@
         <v>使用该道具后可以指定生成游客街头潮人</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -8156,7 +8189,7 @@
         <v>使用该道具后可以指定生成游客复古绅士</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -8196,7 +8229,7 @@
         <v>使用该道具后可以指定生成游客酷盖少年</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -8236,7 +8269,7 @@
         <v>使用该道具后可以指定生成游客潮流先锋</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -8276,7 +8309,7 @@
         <v>使用该道具后可以指定生成游客时尚教主</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -8316,7 +8349,7 @@
         <v>使用该道具后可以指定生成游客街拍达人</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -8356,7 +8389,7 @@
         <v>使用该道具后可以指定生成游客运动健将</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -8396,7 +8429,7 @@
         <v>使用该道具后可以指定生成游客跑酷少年</v>
       </c>
       <c r="S108" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -8436,7 +8469,7 @@
         <v>使用该道具后可以指定生成游客滑板高手</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -8476,7 +8509,7 @@
         <v>使用该道具后可以指定生成游客甜心辣妹</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -8516,7 +8549,7 @@
         <v>使用该道具后可以指定生成游客活力少女</v>
       </c>
       <c r="S111" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -8556,7 +8589,7 @@
         <v>使用该道具后可以指定生成游客优雅女神</v>
       </c>
       <c r="S112" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -8596,7 +8629,7 @@
         <v>使用该道具后可以指定生成游客健身狂魔</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -8636,7 +8669,7 @@
         <v>使用该道具后可以指定生成游客单车骑士</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -8676,7 +8709,7 @@
         <v>使用该道具后可以指定生成游客登山行者</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -8716,7 +8749,7 @@
         <v>使用该道具后可以指定生成游客文艺青年</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -8756,7 +8789,7 @@
         <v>使用该道具后可以指定生成游客书香少女</v>
       </c>
       <c r="S117" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -8796,7 +8829,7 @@
         <v>使用该道具后可以指定生成游客民谣歌手</v>
       </c>
       <c r="S118" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -8836,7 +8869,7 @@
         <v>使用该道具后可以指定生成游客马拉松客</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -8876,7 +8909,7 @@
         <v>使用该道具后可以指定生成游客极限玩家</v>
       </c>
       <c r="S120" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -8916,7 +8949,7 @@
         <v>使用该道具后可以指定生成游客科技极客</v>
       </c>
       <c r="S121" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -8956,7 +8989,7 @@
         <v>使用该道具后可以指定生成游客独立画家</v>
       </c>
       <c r="S122" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -8996,7 +9029,7 @@
         <v>使用该道具后可以指定生成游客浪漫诗人</v>
       </c>
       <c r="S123" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -9036,7 +9069,7 @@
         <v>使用该道具后可以指定生成游客古典乐迷</v>
       </c>
       <c r="S124" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -9076,7 +9109,7 @@
         <v>使用该道具后可以指定生成游客创业新贵</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -9116,7 +9149,7 @@
         <v>使用该道具后可以指定生成游客摸金校尉</v>
       </c>
       <c r="S126" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -9156,7 +9189,7 @@
         <v>使用该道具后可以指定生成游客氪金大佬</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -9196,7 +9229,7 @@
         <v>使用该道具后可以指定生成游客穿搭博主</v>
       </c>
       <c r="S128" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -9236,7 +9269,7 @@
         <v>使用该道具后可以指定生成游客美妆新秀</v>
       </c>
       <c r="S129" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -9276,7 +9309,7 @@
         <v>使用该道具后可以指定生成游客高定女王</v>
       </c>
       <c r="S130" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -9287,7 +9320,7 @@
         <v>1024061</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
@@ -9311,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -9322,7 +9355,7 @@
         <v>1024062</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -9346,7 +9379,7 @@
         <v>0</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -9357,7 +9390,7 @@
         <v>1024063</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -9381,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -9392,7 +9425,7 @@
         <v>1024064</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -9416,7 +9449,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -9427,7 +9460,7 @@
         <v>1024065</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -9451,7 +9484,7 @@
         <v>0</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="136" ht="17.25" spans="1:19">
@@ -9462,7 +9495,7 @@
         <v>1024024</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -9474,7 +9507,7 @@
         <v>1</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="I136" s="1">
         <v>1</v>
@@ -9486,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="M136" s="1">
         <v>2024076</v>
@@ -9495,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="137" ht="17.25" spans="1:19">
@@ -9506,7 +9539,7 @@
         <v>1024024</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -9518,7 +9551,7 @@
         <v>1</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I137" s="1">
         <v>1</v>
@@ -9530,7 +9563,7 @@
         <v>1</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="M137" s="1">
         <v>2024077</v>
@@ -9539,7 +9572,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -9550,7 +9583,7 @@
         <v>1024024</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -9562,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I138" s="1">
         <v>1</v>
@@ -9574,7 +9607,7 @@
         <v>1</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M138" s="1">
         <v>2024078</v>
@@ -9583,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -9594,7 +9627,7 @@
         <v>1024024</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -9606,7 +9639,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="I139" s="1">
         <v>1</v>
@@ -9618,7 +9651,7 @@
         <v>1</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="M139" s="1">
         <v>2024079</v>
@@ -9627,7 +9660,7 @@
         <v>0</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -9638,7 +9671,7 @@
         <v>1024024</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -9650,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="I140" s="1">
         <v>1</v>
@@ -9662,7 +9695,7 @@
         <v>1</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="M140" s="1">
         <v>2024080</v>
@@ -9671,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="141" spans="1:19">
@@ -9682,7 +9715,7 @@
         <v>1024024</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -9694,7 +9727,7 @@
         <v>1</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I141" s="1">
         <v>1</v>
@@ -9706,7 +9739,7 @@
         <v>1</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="M141" s="1">
         <v>2024081</v>
@@ -9715,7 +9748,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -9726,7 +9759,7 @@
         <v>1024024</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -9738,7 +9771,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="I142" s="1">
         <v>1</v>
@@ -9750,7 +9783,7 @@
         <v>1</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M142" s="1">
         <v>2024082</v>
@@ -9759,7 +9792,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -9770,7 +9803,7 @@
         <v>1025101</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -9788,7 +9821,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="M143" s="1">
         <v>2025101</v>
@@ -9797,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="R143" s="1">
         <v>-1</v>
@@ -9811,7 +9844,7 @@
         <v>1025102</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -9829,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="M144" s="1">
         <v>2025102</v>
@@ -9838,7 +9871,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="R144" s="1">
         <v>-1</v>
@@ -9852,7 +9885,7 @@
         <v>1025103</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -9870,7 +9903,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M145" s="1">
         <v>2025103</v>
@@ -9879,7 +9912,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="R145" s="1">
         <v>-1</v>
@@ -9893,7 +9926,7 @@
         <v>1025104</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -9911,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="M146" s="1">
         <v>2025104</v>
@@ -9920,7 +9953,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="R146" s="1">
         <v>-1</v>
@@ -9934,7 +9967,7 @@
         <v>1025105</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -9952,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M147" s="1">
         <v>2025105</v>
@@ -9961,7 +9994,7 @@
         <v>0</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="R147" s="1">
         <v>-1</v>
@@ -9975,7 +10008,7 @@
         <v>1025106</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -9993,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="M148" s="1">
         <v>2025106</v>
@@ -10002,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="R148" s="1">
         <v>-1</v>
@@ -10016,7 +10049,7 @@
         <v>1025201</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -10034,7 +10067,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="M149" s="1">
         <v>2025201</v>
@@ -10043,7 +10076,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="R149" s="1">
         <v>-1</v>
@@ -10057,7 +10090,7 @@
         <v>1025202</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -10075,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M150" s="1">
         <v>2025202</v>
@@ -10084,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="R150" s="1">
         <v>-1</v>
@@ -10098,7 +10131,7 @@
         <v>1025203</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -10116,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="M151" s="1">
         <v>2025203</v>
@@ -10125,7 +10158,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="R151" s="1">
         <v>-1</v>
@@ -10139,7 +10172,7 @@
         <v>1025204</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -10157,7 +10190,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="M152" s="1">
         <v>2025204</v>
@@ -10166,7 +10199,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="R152" s="1">
         <v>-1</v>
@@ -10180,7 +10213,7 @@
         <v>1025205</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -10198,7 +10231,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="M153" s="1">
         <v>2025205</v>
@@ -10207,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="R153" s="1">
         <v>-1</v>
@@ -10221,7 +10254,7 @@
         <v>1025206</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -10239,7 +10272,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="M154" s="1">
         <v>2025206</v>
@@ -10248,7 +10281,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="R154" s="1">
         <v>-1</v>
@@ -10262,7 +10295,7 @@
         <v>1025301</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -10280,7 +10313,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M155" s="1">
         <v>2025301</v>
@@ -10289,7 +10322,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="R155" s="1">
         <v>-1</v>
@@ -10303,7 +10336,7 @@
         <v>1025302</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -10321,7 +10354,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M156" s="1">
         <v>2025302</v>
@@ -10330,7 +10363,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="R156" s="1">
         <v>-1</v>
@@ -10344,7 +10377,7 @@
         <v>1025303</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -10362,7 +10395,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="M157" s="1">
         <v>2025303</v>
@@ -10371,7 +10404,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="R157" s="1">
         <v>-1</v>
@@ -10385,7 +10418,7 @@
         <v>1025304</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -10403,7 +10436,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="M158" s="1">
         <v>2025304</v>
@@ -10412,7 +10445,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="R158" s="1">
         <v>-1</v>
@@ -10426,7 +10459,7 @@
         <v>1025305</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -10444,7 +10477,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M159" s="1">
         <v>2025305</v>
@@ -10453,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="R159" s="1">
         <v>-1</v>
@@ -10467,7 +10500,7 @@
         <v>1025306</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -10485,7 +10518,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M160" s="1">
         <v>2025306</v>
@@ -10494,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="R160" s="1">
         <v>-1</v>
@@ -10508,7 +10541,7 @@
         <v>1025401</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -10526,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="M161" s="1">
         <v>2025401</v>
@@ -10535,7 +10568,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="R161" s="1">
         <v>-1</v>
@@ -10549,7 +10582,7 @@
         <v>1025402</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -10567,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="M162" s="1">
         <v>2025402</v>
@@ -10576,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="R162" s="1">
         <v>-1</v>
@@ -10590,7 +10623,7 @@
         <v>1025403</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -10608,7 +10641,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="M163" s="1">
         <v>2025403</v>
@@ -10617,7 +10650,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="R163" s="1">
         <v>-1</v>
@@ -10631,7 +10664,7 @@
         <v>1025404</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
@@ -10649,7 +10682,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M164" s="1">
         <v>2025404</v>
@@ -10658,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="R164" s="1">
         <v>-1</v>
@@ -10672,7 +10705,7 @@
         <v>1025405</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
@@ -10690,7 +10723,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="M165" s="1">
         <v>2025405</v>
@@ -10699,7 +10732,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="R165" s="1">
         <v>-1</v>
@@ -10713,7 +10746,7 @@
         <v>1025406</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E166" s="1">
         <v>2</v>
@@ -10731,7 +10764,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="M166" s="1">
         <v>2025406</v>
@@ -10740,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="R166" s="1">
         <v>-1</v>
@@ -10754,7 +10787,7 @@
         <v>1025501</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E167" s="1">
         <v>2</v>
@@ -10772,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="M167" s="1">
         <v>2025501</v>
@@ -10781,7 +10814,7 @@
         <v>0</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="R167" s="1">
         <v>-1</v>
@@ -10795,7 +10828,7 @@
         <v>1025502</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E168" s="1">
         <v>2</v>
@@ -10813,7 +10846,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M168" s="1">
         <v>2025502</v>
@@ -10822,7 +10855,7 @@
         <v>0</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="R168" s="1">
         <v>-1</v>
@@ -10836,7 +10869,7 @@
         <v>1025503</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E169" s="1">
         <v>2</v>
@@ -10854,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M169" s="1">
         <v>2025503</v>
@@ -10863,7 +10896,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="R169" s="1">
         <v>-1</v>
@@ -10877,7 +10910,7 @@
         <v>1025504</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E170" s="1">
         <v>2</v>
@@ -10895,7 +10928,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M170" s="1">
         <v>2025504</v>
@@ -10904,7 +10937,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="R170" s="1">
         <v>-1</v>
@@ -10918,7 +10951,7 @@
         <v>1025505</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E171" s="1">
         <v>2</v>
@@ -10936,7 +10969,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M171" s="1">
         <v>2025505</v>
@@ -10945,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="R171" s="1">
         <v>-1</v>
@@ -10959,7 +10992,7 @@
         <v>1025506</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E172" s="1">
         <v>2</v>
@@ -10977,7 +11010,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="M172" s="1">
         <v>2025506</v>
@@ -10986,7 +11019,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="R172" s="1">
         <v>-1</v>
@@ -11019,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="M173" s="1">
         <v>2125101</v>
@@ -11062,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="L174" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M174" s="1">
         <v>2125102</v>
@@ -11105,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="L175" s="14" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="M175" s="1">
         <v>2125103</v>
@@ -11148,7 +11181,7 @@
         <v>1</v>
       </c>
       <c r="L176" s="14" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="M176" s="1">
         <v>2125104</v>
@@ -11191,7 +11224,7 @@
         <v>1</v>
       </c>
       <c r="L177" s="14" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="M177" s="1">
         <v>2125105</v>
@@ -11234,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="L178" s="14" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M178" s="1">
         <v>2125106</v>
@@ -11277,7 +11310,7 @@
         <v>1</v>
       </c>
       <c r="L179" s="14" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M179" s="1">
         <v>2125201</v>
@@ -11320,7 +11353,7 @@
         <v>1</v>
       </c>
       <c r="L180" s="14" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M180" s="1">
         <v>2125202</v>
@@ -11363,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="L181" s="14" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="M181" s="1">
         <v>2125203</v>
@@ -11406,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="L182" s="14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="M182" s="1">
         <v>2125204</v>
@@ -11449,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="L183" s="14" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="M183" s="1">
         <v>2125205</v>
@@ -11492,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="L184" s="14" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="M184" s="1">
         <v>2125206</v>
@@ -11535,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="L185" s="14" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="M185" s="1">
         <v>2125301</v>
@@ -11578,7 +11611,7 @@
         <v>1</v>
       </c>
       <c r="L186" s="14" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="M186" s="1">
         <v>2125302</v>
@@ -11621,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="L187" s="14" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="M187" s="1">
         <v>2125303</v>
@@ -11664,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="L188" s="14" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="M188" s="1">
         <v>2125304</v>
@@ -11707,7 +11740,7 @@
         <v>1</v>
       </c>
       <c r="L189" s="14" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="M189" s="1">
         <v>2125305</v>
@@ -11750,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="L190" s="14" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M190" s="1">
         <v>2125306</v>
@@ -11793,7 +11826,7 @@
         <v>1</v>
       </c>
       <c r="L191" s="14" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M191" s="1">
         <v>2125401</v>
@@ -11836,7 +11869,7 @@
         <v>1</v>
       </c>
       <c r="L192" s="14" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="M192" s="1">
         <v>2125402</v>
@@ -11879,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="L193" s="14" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M193" s="1">
         <v>2125403</v>
@@ -11922,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="L194" s="14" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="M194" s="1">
         <v>2125404</v>
@@ -11965,7 +11998,7 @@
         <v>1</v>
       </c>
       <c r="L195" s="14" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="M195" s="1">
         <v>2125405</v>
@@ -12008,7 +12041,7 @@
         <v>1</v>
       </c>
       <c r="L196" s="14" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="M196" s="1">
         <v>2125406</v>
@@ -12051,7 +12084,7 @@
         <v>1</v>
       </c>
       <c r="L197" s="14" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M197" s="1">
         <v>2125501</v>
@@ -12094,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="L198" s="14" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="M198" s="1">
         <v>2125502</v>
@@ -12137,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="L199" s="14" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="M199" s="1">
         <v>2125503</v>
@@ -12180,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="L200" s="14" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M200" s="1">
         <v>2125504</v>
@@ -12223,7 +12256,7 @@
         <v>1</v>
       </c>
       <c r="L201" s="14" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="M201" s="1">
         <v>2125505</v>
@@ -12266,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="L202" s="14" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="M202" s="1">
         <v>2125506</v>
@@ -12290,7 +12323,7 @@
         <v>1026001</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E203" s="1">
         <v>2</v>
@@ -12308,7 +12341,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M203" s="1">
         <v>2026001</v>
@@ -12317,7 +12350,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="R203" s="1">
         <v>-1</v>
@@ -12331,7 +12364,7 @@
         <v>1026002</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E204" s="1">
         <v>2</v>
@@ -12349,7 +12382,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M204" s="1">
         <v>2026002</v>
@@ -12358,7 +12391,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="R204" s="1">
         <v>-1</v>
@@ -12372,7 +12405,7 @@
         <v>1026101</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E205" s="1">
         <v>2</v>
@@ -12390,7 +12423,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M205" s="1">
         <v>2026101</v>
@@ -12399,7 +12432,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="R205" s="1">
         <v>-1</v>
@@ -12413,7 +12446,7 @@
         <v>1026102</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -12431,7 +12464,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M206" s="1">
         <v>2026102</v>
@@ -12440,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="R206" s="1">
         <v>-1</v>
@@ -12454,7 +12487,7 @@
         <v>1026201</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -12472,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M207" s="1">
         <v>2026201</v>
@@ -12481,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="R207" s="1">
         <v>-1</v>
@@ -12495,7 +12528,7 @@
         <v>1026202</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -12513,7 +12546,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M208" s="1">
         <v>2026202</v>
@@ -12522,7 +12555,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="R208" s="1">
         <v>-1</v>
@@ -12536,7 +12569,7 @@
         <v>1026301</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -12554,7 +12587,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M209" s="1">
         <v>2026301</v>
@@ -12563,7 +12596,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="R209" s="1">
         <v>-1</v>
@@ -12577,7 +12610,7 @@
         <v>1026302</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -12595,7 +12628,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M210" s="1">
         <v>2026302</v>
@@ -12604,7 +12637,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="R210" s="1">
         <v>-1</v>
@@ -12618,7 +12651,7 @@
         <v>1026401</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -12636,7 +12669,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M211" s="1">
         <v>2026401</v>
@@ -12645,7 +12678,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="R211" s="1">
         <v>-1</v>
@@ -12659,7 +12692,7 @@
         <v>1026402</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -12677,7 +12710,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M212" s="1">
         <v>2026402</v>
@@ -12686,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="R212" s="1">
         <v>-1</v>
@@ -12700,7 +12733,7 @@
         <v>1027001</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -12718,7 +12751,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M213" s="1">
         <v>2027001</v>
@@ -12727,7 +12760,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="R213" s="1">
         <v>-1</v>
@@ -12741,7 +12774,7 @@
         <v>1027002</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -12759,7 +12792,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M214" s="1">
         <v>2027002</v>
@@ -12768,7 +12801,7 @@
         <v>0</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="R214" s="1">
         <v>-1</v>
@@ -12782,7 +12815,7 @@
         <v>1027101</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -12800,7 +12833,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M215" s="1">
         <v>2027101</v>
@@ -12809,7 +12842,7 @@
         <v>0</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="R215" s="1">
         <v>-1</v>
@@ -12823,7 +12856,7 @@
         <v>1027102</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -12841,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M216" s="1">
         <v>2027102</v>
@@ -12850,7 +12883,7 @@
         <v>0</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="R216" s="1">
         <v>-1</v>
@@ -12864,7 +12897,7 @@
         <v>1027201</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -12882,7 +12915,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M217" s="1">
         <v>2027201</v>
@@ -12891,7 +12924,7 @@
         <v>0</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="R217" s="1">
         <v>-1</v>
@@ -12905,7 +12938,7 @@
         <v>1027202</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -12923,7 +12956,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M218" s="1">
         <v>2027202</v>
@@ -12932,7 +12965,7 @@
         <v>0</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="R218" s="1">
         <v>-1</v>
@@ -12946,7 +12979,7 @@
         <v>1027301</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -12964,7 +12997,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M219" s="1">
         <v>2027301</v>
@@ -12973,7 +13006,7 @@
         <v>0</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="R219" s="1">
         <v>-1</v>
@@ -12987,7 +13020,7 @@
         <v>1027302</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -13005,7 +13038,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M220" s="1">
         <v>2027302</v>
@@ -13014,7 +13047,7 @@
         <v>0</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="R220" s="1">
         <v>-1</v>
@@ -13028,7 +13061,7 @@
         <v>1027401</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -13046,7 +13079,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M221" s="1">
         <v>2027401</v>
@@ -13055,7 +13088,7 @@
         <v>0</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="R221" s="1">
         <v>-1</v>
@@ -13069,7 +13102,7 @@
         <v>1027402</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -13087,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="M222" s="1">
         <v>2027402</v>
@@ -13096,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="R222" s="1">
         <v>-1</v>
@@ -13110,7 +13143,7 @@
         <v>1028001</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -13128,7 +13161,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M223" s="1">
         <v>2028001</v>
@@ -13137,7 +13170,7 @@
         <v>0</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="R223" s="1">
         <v>-1</v>
@@ -13151,7 +13184,7 @@
         <v>1028002</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -13169,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M224" s="1">
         <v>2028002</v>
@@ -13178,7 +13211,7 @@
         <v>0</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="R224" s="1">
         <v>-1</v>
@@ -13192,7 +13225,7 @@
         <v>1028101</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -13210,7 +13243,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M225" s="1">
         <v>2028101</v>
@@ -13219,7 +13252,7 @@
         <v>0</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="R225" s="1">
         <v>-1</v>
@@ -13233,7 +13266,7 @@
         <v>1028102</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E226" s="1">
         <v>2</v>
@@ -13251,7 +13284,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M226" s="1">
         <v>2028102</v>
@@ -13260,7 +13293,7 @@
         <v>0</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="R226" s="1">
         <v>-1</v>
@@ -13274,7 +13307,7 @@
         <v>1028201</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
@@ -13292,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M227" s="1">
         <v>2028201</v>
@@ -13301,7 +13334,7 @@
         <v>0</v>
       </c>
       <c r="O227" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="R227" s="1">
         <v>-1</v>
@@ -13315,7 +13348,7 @@
         <v>1028202</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
@@ -13333,7 +13366,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M228" s="1">
         <v>2028202</v>
@@ -13342,7 +13375,7 @@
         <v>0</v>
       </c>
       <c r="O228" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="R228" s="1">
         <v>-1</v>
@@ -13356,7 +13389,7 @@
         <v>1028301</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
@@ -13374,7 +13407,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M229" s="1">
         <v>2028301</v>
@@ -13383,7 +13416,7 @@
         <v>0</v>
       </c>
       <c r="O229" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="R229" s="1">
         <v>-1</v>
@@ -13397,7 +13430,7 @@
         <v>1028302</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
@@ -13415,7 +13448,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M230" s="1">
         <v>2028302</v>
@@ -13424,7 +13457,7 @@
         <v>0</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="R230" s="1">
         <v>-1</v>
@@ -13438,7 +13471,7 @@
         <v>1028401</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
@@ -13456,7 +13489,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M231" s="1">
         <v>2028401</v>
@@ -13465,7 +13498,7 @@
         <v>0</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="R231" s="1">
         <v>-1</v>
@@ -13479,7 +13512,7 @@
         <v>1028402</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
@@ -13497,7 +13530,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="M232" s="1">
         <v>2028402</v>
@@ -13506,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="R232" s="1">
         <v>-1</v>
@@ -13539,7 +13572,7 @@
         <v>1</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M233" s="1">
         <v>2126001</v>
@@ -13582,7 +13615,7 @@
         <v>1</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="M234" s="1">
         <v>2126002</v>
@@ -13625,7 +13658,7 @@
         <v>1</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M235" s="1">
         <v>2126101</v>
@@ -13668,7 +13701,7 @@
         <v>1</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M236" s="1">
         <v>2126102</v>
@@ -13711,7 +13744,7 @@
         <v>1</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M237" s="1">
         <v>2126201</v>
@@ -13754,7 +13787,7 @@
         <v>1</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M238" s="1">
         <v>2126202</v>
@@ -13797,7 +13830,7 @@
         <v>1</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M239" s="1">
         <v>2126301</v>
@@ -13840,7 +13873,7 @@
         <v>1</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M240" s="1">
         <v>2126302</v>
@@ -13883,7 +13916,7 @@
         <v>1</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M241" s="1">
         <v>2126401</v>
@@ -13926,7 +13959,7 @@
         <v>1</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M242" s="1">
         <v>2126402</v>
@@ -13969,7 +14002,7 @@
         <v>1</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M243" s="1">
         <v>2127001</v>
@@ -14012,7 +14045,7 @@
         <v>1</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M244" s="1">
         <v>2127002</v>
@@ -14055,7 +14088,7 @@
         <v>1</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M245" s="1">
         <v>2127101</v>
@@ -14098,7 +14131,7 @@
         <v>1</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M246" s="1">
         <v>2127102</v>
@@ -14141,7 +14174,7 @@
         <v>1</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M247" s="1">
         <v>2127201</v>
@@ -14184,7 +14217,7 @@
         <v>1</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M248" s="1">
         <v>2127202</v>
@@ -14227,7 +14260,7 @@
         <v>1</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M249" s="1">
         <v>2127301</v>
@@ -14270,7 +14303,7 @@
         <v>1</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="M250" s="1">
         <v>2127302</v>
@@ -14313,7 +14346,7 @@
         <v>1</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M251" s="1">
         <v>2127401</v>
@@ -14356,7 +14389,7 @@
         <v>1</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="M252" s="1">
         <v>2127402</v>
@@ -14399,7 +14432,7 @@
         <v>1</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M253" s="1">
         <v>2128001</v>
@@ -14442,7 +14475,7 @@
         <v>1</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M254" s="1">
         <v>2128002</v>
@@ -14485,7 +14518,7 @@
         <v>1</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M255" s="1">
         <v>2128101</v>
@@ -14528,7 +14561,7 @@
         <v>1</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M256" s="1">
         <v>2128102</v>
@@ -14571,7 +14604,7 @@
         <v>1</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M257" s="1">
         <v>2128201</v>
@@ -14614,7 +14647,7 @@
         <v>1</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M258" s="1">
         <v>2128202</v>
@@ -14657,7 +14690,7 @@
         <v>1</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M259" s="1">
         <v>2128301</v>
@@ -14700,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M260" s="1">
         <v>2128302</v>
@@ -14743,7 +14776,7 @@
         <v>1</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M261" s="1">
         <v>2128401</v>
@@ -14786,7 +14819,7 @@
         <v>1</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="M262" s="1">
         <v>2128402</v>
@@ -14810,7 +14843,7 @@
         <v>1130001</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -14828,7 +14861,7 @@
         <v>1</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="M263" s="1">
         <v>2130001</v>
@@ -14837,7 +14870,7 @@
         <v>0</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="R263" s="1">
         <v>999999</v>
@@ -14851,7 +14884,7 @@
         <v>1130002</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E264" s="1">
         <v>1</v>
@@ -14869,7 +14902,7 @@
         <v>1</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M264" s="1">
         <v>2130002</v>
@@ -14878,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="R264" s="1">
         <v>999999</v>
@@ -14892,7 +14925,7 @@
         <v>1130003</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E265" s="1">
         <v>1</v>
@@ -14910,7 +14943,7 @@
         <v>1</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M265" s="1">
         <v>2130003</v>
@@ -14919,7 +14952,7 @@
         <v>0</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="R265" s="1">
         <v>999999</v>
@@ -14933,7 +14966,7 @@
         <v>1130004</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E266" s="1">
         <v>1</v>
@@ -14951,7 +14984,7 @@
         <v>1</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="M266" s="1">
         <v>2130004</v>
@@ -14960,7 +14993,7 @@
         <v>0</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="R266" s="1">
         <v>999999</v>
@@ -14974,7 +15007,7 @@
         <v>1130005</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E267" s="1">
         <v>1</v>
@@ -14992,7 +15025,7 @@
         <v>1</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="M267" s="1">
         <v>2130005</v>
@@ -15001,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="R267" s="1">
         <v>999999</v>
@@ -15015,7 +15048,7 @@
         <v>1130006</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E268" s="1">
         <v>1</v>
@@ -15033,7 +15066,7 @@
         <v>1</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M268" s="1">
         <v>2130006</v>
@@ -15042,7 +15075,7 @@
         <v>0</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="R268" s="1">
         <v>999999</v>
@@ -15056,7 +15089,7 @@
         <v>1131001</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -15072,6 +15105,9 @@
       </c>
       <c r="K269" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L269" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="M269" s="1">
         <v>2131001</v>
@@ -15080,7 +15116,7 @@
         <v>0</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="270" spans="1:18">
@@ -15091,7 +15127,7 @@
         <v>1131002</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -15107,6 +15143,9 @@
       </c>
       <c r="K270" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L270" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="M270" s="1">
         <v>2131002</v>
@@ -15115,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="271" spans="1:18">
@@ -15126,7 +15165,7 @@
         <v>1131003</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -15142,6 +15181,9 @@
       </c>
       <c r="K271" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L271" s="1" t="s">
+        <v>479</v>
       </c>
       <c r="M271" s="1">
         <v>2131003</v>
@@ -15150,7 +15192,7 @@
         <v>0</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="272" spans="1:18">
@@ -15161,7 +15203,7 @@
         <v>1131004</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -15177,6 +15219,9 @@
       </c>
       <c r="K272" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L272" s="1" t="s">
+        <v>482</v>
       </c>
       <c r="M272" s="1">
         <v>2131004</v>
@@ -15185,7 +15230,7 @@
         <v>0</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="273" spans="1:15">
@@ -15196,7 +15241,7 @@
         <v>1131005</v>
       </c>
       <c r="D273" s="15" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -15212,6 +15257,9 @@
       </c>
       <c r="K273" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L273" s="1" t="s">
+        <v>485</v>
       </c>
       <c r="M273" s="1">
         <v>2131005</v>
@@ -15220,7 +15268,7 @@
         <v>0</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="274" spans="1:15">
@@ -15231,7 +15279,7 @@
         <v>1131006</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -15247,6 +15295,9 @@
       </c>
       <c r="K274" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L274" s="1" t="s">
+        <v>488</v>
       </c>
       <c r="M274" s="1">
         <v>2131006</v>
@@ -15255,7 +15306,7 @@
         <v>0</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="275" spans="1:15">
@@ -15266,7 +15317,7 @@
         <v>1131101</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -15282,6 +15333,9 @@
       </c>
       <c r="K275" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L275" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="M275" s="1">
         <v>2131101</v>
@@ -15290,7 +15344,7 @@
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="276" spans="1:15">
@@ -15301,7 +15355,7 @@
         <v>1131102</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -15317,6 +15371,9 @@
       </c>
       <c r="K276" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L276" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="M276" s="1">
         <v>2131102</v>
@@ -15325,7 +15382,7 @@
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="277" spans="1:15">
@@ -15336,7 +15393,7 @@
         <v>1131103</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -15352,6 +15409,9 @@
       </c>
       <c r="K277" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L277" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="M277" s="1">
         <v>2131103</v>
@@ -15360,7 +15420,7 @@
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="278" spans="1:15">
@@ -15371,7 +15431,7 @@
         <v>1131104</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -15387,6 +15447,9 @@
       </c>
       <c r="K278" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L278" s="1" t="s">
+        <v>497</v>
       </c>
       <c r="M278" s="1">
         <v>2131104</v>
@@ -15395,7 +15458,7 @@
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="279" spans="1:15">
@@ -15406,7 +15469,7 @@
         <v>1131105</v>
       </c>
       <c r="D279" s="15" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -15422,6 +15485,9 @@
       </c>
       <c r="K279" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L279" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="M279" s="1">
         <v>2131105</v>
@@ -15430,7 +15496,7 @@
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="280" spans="1:15">
@@ -15441,7 +15507,7 @@
         <v>1131106</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -15457,6 +15523,9 @@
       </c>
       <c r="K280" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="L280" s="1" t="s">
+        <v>501</v>
       </c>
       <c r="M280" s="1">
         <v>2131106</v>
@@ -15465,7 +15534,7 @@
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="281" spans="1:15">
@@ -15476,7 +15545,7 @@
         <v>1131201</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15493,6 +15562,9 @@
       <c r="K281" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L281" s="1" t="s">
+        <v>503</v>
+      </c>
       <c r="M281" s="1">
         <v>2131201</v>
       </c>
@@ -15500,7 +15572,7 @@
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
     </row>
     <row r="282" spans="1:15">
@@ -15511,7 +15583,7 @@
         <v>1131202</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15528,6 +15600,9 @@
       <c r="K282" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L282" s="1" t="s">
+        <v>505</v>
+      </c>
       <c r="M282" s="1">
         <v>2131202</v>
       </c>
@@ -15535,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
     </row>
     <row r="283" spans="1:15">
@@ -15546,7 +15621,7 @@
         <v>1131203</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15563,6 +15638,9 @@
       <c r="K283" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L283" s="1" t="s">
+        <v>507</v>
+      </c>
       <c r="M283" s="1">
         <v>2131203</v>
       </c>
@@ -15570,7 +15648,7 @@
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
     </row>
     <row r="284" spans="1:15">
@@ -15581,7 +15659,7 @@
         <v>1131204</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15598,6 +15676,9 @@
       <c r="K284" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L284" s="1" t="s">
+        <v>509</v>
+      </c>
       <c r="M284" s="1">
         <v>2131204</v>
       </c>
@@ -15605,7 +15686,7 @@
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
     </row>
     <row r="285" spans="1:15">
@@ -15616,7 +15697,7 @@
         <v>1131205</v>
       </c>
       <c r="D285" s="15" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15633,6 +15714,9 @@
       <c r="K285" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L285" s="1" t="s">
+        <v>511</v>
+      </c>
       <c r="M285" s="1">
         <v>2131205</v>
       </c>
@@ -15640,7 +15724,7 @@
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
     </row>
     <row r="286" spans="1:15">
@@ -15651,7 +15735,7 @@
         <v>1131206</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15668,6 +15752,9 @@
       <c r="K286" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L286" s="1" t="s">
+        <v>513</v>
+      </c>
       <c r="M286" s="1">
         <v>2131206</v>
       </c>
@@ -15675,7 +15762,7 @@
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
     </row>
     <row r="287" spans="1:15">
@@ -15686,7 +15773,7 @@
         <v>1131301</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -15703,6 +15790,9 @@
       <c r="K287" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L287" s="1" t="s">
+        <v>515</v>
+      </c>
       <c r="M287" s="1">
         <v>2131301</v>
       </c>
@@ -15710,7 +15800,7 @@
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
     </row>
     <row r="288" spans="1:15">
@@ -15721,7 +15811,7 @@
         <v>1131302</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -15738,6 +15828,9 @@
       <c r="K288" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L288" s="1" t="s">
+        <v>518</v>
+      </c>
       <c r="M288" s="1">
         <v>2131302</v>
       </c>
@@ -15745,7 +15838,7 @@
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>507</v>
+        <v>477</v>
       </c>
     </row>
     <row r="289" spans="1:15">
@@ -15756,7 +15849,7 @@
         <v>1131303</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -15773,6 +15866,9 @@
       <c r="K289" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L289" s="1" t="s">
+        <v>520</v>
+      </c>
       <c r="M289" s="1">
         <v>2131303</v>
       </c>
@@ -15780,7 +15876,7 @@
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
     </row>
     <row r="290" spans="1:15">
@@ -15791,7 +15887,7 @@
         <v>1131304</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -15808,6 +15904,9 @@
       <c r="K290" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L290" s="1" t="s">
+        <v>522</v>
+      </c>
       <c r="M290" s="1">
         <v>2131304</v>
       </c>
@@ -15815,7 +15914,7 @@
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
     </row>
     <row r="291" spans="1:15">
@@ -15826,7 +15925,7 @@
         <v>1131305</v>
       </c>
       <c r="D291" s="15" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -15843,6 +15942,9 @@
       <c r="K291" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L291" s="1" t="s">
+        <v>524</v>
+      </c>
       <c r="M291" s="1">
         <v>2131305</v>
       </c>
@@ -15850,7 +15952,7 @@
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>513</v>
+        <v>486</v>
       </c>
     </row>
     <row r="292" spans="1:15">
@@ -15861,7 +15963,7 @@
         <v>1131306</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -15878,6 +15980,9 @@
       <c r="K292" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L292" s="1" t="s">
+        <v>526</v>
+      </c>
       <c r="M292" s="1">
         <v>2131306</v>
       </c>
@@ -15885,7 +15990,7 @@
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
     </row>
     <row r="293" spans="1:15">
@@ -15896,7 +16001,7 @@
         <v>1131401</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -15913,6 +16018,9 @@
       <c r="K293" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L293" s="1" t="s">
+        <v>528</v>
+      </c>
       <c r="M293" s="1">
         <v>2131401</v>
       </c>
@@ -15920,7 +16028,7 @@
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>517</v>
+        <v>474</v>
       </c>
     </row>
     <row r="294" spans="1:15">
@@ -15931,7 +16039,7 @@
         <v>1131402</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -15948,6 +16056,9 @@
       <c r="K294" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L294" s="1" t="s">
+        <v>530</v>
+      </c>
       <c r="M294" s="1">
         <v>2131402</v>
       </c>
@@ -15955,7 +16066,7 @@
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>519</v>
+        <v>477</v>
       </c>
     </row>
     <row r="295" spans="1:15">
@@ -15966,7 +16077,7 @@
         <v>1131403</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -15983,6 +16094,9 @@
       <c r="K295" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L295" s="1" t="s">
+        <v>532</v>
+      </c>
       <c r="M295" s="1">
         <v>2131403</v>
       </c>
@@ -15990,7 +16104,7 @@
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
     </row>
     <row r="296" spans="1:15">
@@ -16001,7 +16115,7 @@
         <v>1131404</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -16018,6 +16132,9 @@
       <c r="K296" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L296" s="1" t="s">
+        <v>534</v>
+      </c>
       <c r="M296" s="1">
         <v>2131404</v>
       </c>
@@ -16025,7 +16142,7 @@
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>523</v>
+        <v>483</v>
       </c>
     </row>
     <row r="297" spans="1:15">
@@ -16036,7 +16153,7 @@
         <v>1131405</v>
       </c>
       <c r="D297" s="15" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -16053,6 +16170,9 @@
       <c r="K297" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L297" s="1" t="s">
+        <v>536</v>
+      </c>
       <c r="M297" s="1">
         <v>2131405</v>
       </c>
@@ -16060,7 +16180,7 @@
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>525</v>
+        <v>486</v>
       </c>
     </row>
     <row r="298" spans="1:15">
@@ -16071,7 +16191,7 @@
         <v>1131406</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -16088,6 +16208,9 @@
       <c r="K298" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L298" s="1" t="s">
+        <v>538</v>
+      </c>
       <c r="M298" s="1">
         <v>2131406</v>
       </c>
@@ -16095,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>527</v>
+        <v>489</v>
       </c>
     </row>
     <row r="299" spans="1:15">
@@ -16106,7 +16229,7 @@
         <v>1140001</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -16124,7 +16247,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="M299" s="1">
         <v>2140001</v>
@@ -16133,7 +16256,7 @@
         <v>0</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
     </row>
     <row r="300" spans="1:15">
@@ -16144,7 +16267,7 @@
         <v>1140002</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -16162,7 +16285,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="M300" s="1">
         <v>2140002</v>
@@ -16171,7 +16294,7 @@
         <v>0</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
     </row>
     <row r="301" spans="1:15">
@@ -16182,7 +16305,7 @@
         <v>1140003</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -16200,7 +16323,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="M301" s="1">
         <v>2140003</v>
@@ -16209,7 +16332,7 @@
         <v>0</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
     </row>
     <row r="302" spans="1:15">
@@ -16220,7 +16343,7 @@
         <v>1140004</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -16238,7 +16361,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="M302" s="1">
         <v>2140004</v>
@@ -16247,7 +16370,7 @@
         <v>0</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="303" spans="1:15">
@@ -16258,7 +16381,7 @@
         <v>1140005</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -16276,7 +16399,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="M303" s="1">
         <v>2140005</v>
@@ -16285,7 +16408,7 @@
         <v>0</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
     </row>
     <row r="304" spans="1:15">
@@ -16296,7 +16419,7 @@
         <v>1140006</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -16314,7 +16437,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="M304" s="1">
         <v>2140006</v>
@@ -16323,7 +16446,7 @@
         <v>0</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
     </row>
     <row r="305" spans="1:18">
@@ -16334,7 +16457,7 @@
         <v>1150001</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -16352,7 +16475,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="M305" s="1">
         <v>2150001</v>
@@ -16376,7 +16499,7 @@
         <v>1150002</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -16394,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="M306" s="1">
         <v>2150002</v>
@@ -16418,7 +16541,7 @@
         <v>1150003</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -16436,7 +16559,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="M307" s="1">
         <v>2150003</v>
@@ -16460,7 +16583,7 @@
         <v>1150004</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16478,7 +16601,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="M308" s="1">
         <v>2150004</v>
@@ -16502,7 +16625,7 @@
         <v>1150005</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16520,7 +16643,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="M309" s="1">
         <v>2150005</v>
@@ -16544,7 +16667,7 @@
         <v>1150006</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16562,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="M310" s="1">
         <v>2150006</v>
@@ -16586,7 +16709,7 @@
         <v>1150007</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -16604,7 +16727,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="M311" s="1">
         <v>2150007</v>
@@ -16628,7 +16751,7 @@
         <v>1150008</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -16646,7 +16769,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="M312" s="1">
         <v>2150008</v>
@@ -16670,7 +16793,7 @@
         <v>1150009</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -16688,7 +16811,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="M313" s="1">
         <v>2150009</v>
@@ -16712,7 +16835,7 @@
         <v>1150010</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -16730,7 +16853,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="M314" s="1">
         <v>2150010</v>
@@ -16754,7 +16877,7 @@
         <v>1150011</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -16772,7 +16895,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="M315" s="1">
         <v>2150011</v>
@@ -16796,7 +16919,7 @@
         <v>1150012</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -16814,7 +16937,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="M316" s="1">
         <v>2150012</v>
@@ -16838,7 +16961,7 @@
         <v>1150013</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -16856,7 +16979,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="M317" s="1">
         <v>2150013</v>
@@ -16880,7 +17003,7 @@
         <v>1150014</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -16898,7 +17021,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="M318" s="1">
         <v>2150014</v>
@@ -16922,7 +17045,7 @@
         <v>1150015</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -16940,7 +17063,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="M319" s="1">
         <v>2150015</v>
@@ -16964,7 +17087,7 @@
         <v>1150016</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -16982,7 +17105,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="M320" s="1">
         <v>2150016</v>
@@ -17006,7 +17129,7 @@
         <v>1150017</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -17024,7 +17147,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="M321" s="1">
         <v>2150017</v>
@@ -17048,7 +17171,7 @@
         <v>1150018</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -17066,7 +17189,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="M322" s="1">
         <v>2150018</v>
@@ -17090,7 +17213,7 @@
         <v>1150019</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -17108,7 +17231,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="M323" s="1">
         <v>2150019</v>
@@ -17132,7 +17255,7 @@
         <v>1150020</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -17150,7 +17273,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="M324" s="1">
         <v>2150020</v>
@@ -17174,7 +17297,7 @@
         <v>1150021</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -17192,7 +17315,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="M325" s="1">
         <v>2150021</v>
@@ -17216,7 +17339,7 @@
         <v>1150022</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -17234,7 +17357,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="M326" s="1">
         <v>2150022</v>
@@ -17258,7 +17381,7 @@
         <v>1150023</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -17276,7 +17399,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="M327" s="1">
         <v>2150023</v>
@@ -17300,7 +17423,7 @@
         <v>1150024</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -17318,7 +17441,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="M328" s="1">
         <v>2150024</v>
@@ -17342,7 +17465,7 @@
         <v>1150025</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -17360,7 +17483,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="M329" s="1">
         <v>2150025</v>
@@ -17384,7 +17507,7 @@
         <v>1150026</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -17402,7 +17525,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="M330" s="1">
         <v>2150026</v>
@@ -17426,7 +17549,7 @@
         <v>1150027</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17444,7 +17567,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="M331" s="1">
         <v>2150027</v>
@@ -17468,7 +17591,7 @@
         <v>1150028</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17486,7 +17609,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="M332" s="1">
         <v>2150028</v>
@@ -17510,7 +17633,7 @@
         <v>1150029</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17528,7 +17651,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="M333" s="1">
         <v>2150029</v>
@@ -17552,7 +17675,7 @@
         <v>1150030</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -17570,7 +17693,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="M334" s="1">
         <v>2150030</v>
@@ -17594,7 +17717,7 @@
         <v>1150031</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -17612,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="M335" s="1">
         <v>2150031</v>
@@ -17636,7 +17759,7 @@
         <v>1150032</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -17654,7 +17777,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="M336" s="1">
         <v>2150032</v>
@@ -17678,7 +17801,7 @@
         <v>1150033</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -17696,7 +17819,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="M337" s="1">
         <v>2150033</v>
@@ -17720,7 +17843,7 @@
         <v>1150034</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -17738,7 +17861,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="M338" s="1">
         <v>2150034</v>
@@ -17762,7 +17885,7 @@
         <v>1150035</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -17780,7 +17903,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="M339" s="1">
         <v>2150035</v>
@@ -17804,7 +17927,7 @@
         <v>1150036</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -17822,7 +17945,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="M340" s="1">
         <v>2150036</v>
@@ -17846,7 +17969,7 @@
         <v>1150037</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -17864,7 +17987,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="M341" s="1">
         <v>2150037</v>
@@ -17888,7 +18011,7 @@
         <v>1150038</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -17906,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="M342" s="1">
         <v>2150038</v>
@@ -17930,7 +18053,7 @@
         <v>1150039</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -17948,7 +18071,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="M343" s="1">
         <v>2150039</v>
@@ -17972,7 +18095,7 @@
         <v>1150040</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -17990,7 +18113,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="M344" s="1">
         <v>2150040</v>
@@ -18014,7 +18137,7 @@
         <v>1150041</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -18032,7 +18155,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="M345" s="1">
         <v>2150041</v>
@@ -18056,7 +18179,7 @@
         <v>1150042</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -18074,7 +18197,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="M346" s="1">
         <v>2150042</v>
@@ -18098,7 +18221,7 @@
         <v>1150043</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -18116,7 +18239,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="M347" s="1">
         <v>2150043</v>
@@ -18140,7 +18263,7 @@
         <v>1150044</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -18158,7 +18281,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="M348" s="1">
         <v>2150044</v>
@@ -18182,7 +18305,7 @@
         <v>1150045</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -18200,7 +18323,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="M349" s="1">
         <v>2150045</v>
@@ -18224,7 +18347,7 @@
         <v>1150046</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -18242,7 +18365,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="M350" s="1">
         <v>2150046</v>
@@ -18266,7 +18389,7 @@
         <v>1150047</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -18284,7 +18407,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="M351" s="1">
         <v>2150047</v>
@@ -18308,7 +18431,7 @@
         <v>1150048</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -18326,7 +18449,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="M352" s="1">
         <v>2150048</v>
@@ -18350,7 +18473,7 @@
         <v>1150049</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -18368,7 +18491,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="M353" s="1">
         <v>2150049</v>
@@ -18392,7 +18515,7 @@
         <v>1150050</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -18410,7 +18533,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="M354" s="1">
         <v>2150050</v>
@@ -18434,7 +18557,7 @@
         <v>1150051</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18452,7 +18575,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="M355" s="1">
         <v>2150051</v>
@@ -18476,7 +18599,7 @@
         <v>1150052</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18494,7 +18617,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="M356" s="1">
         <v>2150052</v>
@@ -18518,7 +18641,7 @@
         <v>1150053</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18536,7 +18659,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="M357" s="1">
         <v>2150053</v>
@@ -18560,7 +18683,7 @@
         <v>1150054</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -18578,7 +18701,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="M358" s="1">
         <v>2150054</v>
@@ -18602,7 +18725,7 @@
         <v>1150055</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="E359" s="1">
         <v>2</v>
@@ -18620,7 +18743,7 @@
         <v>0</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="M359" s="1">
         <v>2150055</v>
@@ -18644,7 +18767,7 @@
         <v>1150056</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="E360" s="1">
         <v>2</v>
@@ -18662,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="M360" s="1">
         <v>2150056</v>
@@ -18686,7 +18809,7 @@
         <v>1150057</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="E361" s="1">
         <v>2</v>
@@ -18704,7 +18827,7 @@
         <v>0</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="M361" s="1">
         <v>2150057</v>
@@ -18728,7 +18851,7 @@
         <v>1150058</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="E362" s="1">
         <v>2</v>
@@ -18746,7 +18869,7 @@
         <v>0</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="M362" s="1">
         <v>2150058</v>
@@ -18770,7 +18893,7 @@
         <v>1150059</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="E363" s="1">
         <v>2</v>
@@ -18788,7 +18911,7 @@
         <v>0</v>
       </c>
       <c r="L363" s="1" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="M363" s="1">
         <v>2150059</v>
@@ -18812,7 +18935,7 @@
         <v>1150060</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="E364" s="1">
         <v>2</v>
@@ -18830,7 +18953,7 @@
         <v>0</v>
       </c>
       <c r="L364" s="1" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="M364" s="1">
         <v>2150060</v>
@@ -18854,7 +18977,7 @@
         <v>1150061</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="E365" s="1">
         <v>2</v>
@@ -18872,7 +18995,7 @@
         <v>0</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="M365" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="684">
   <si>
     <t>道具ID</t>
   </si>
@@ -1768,6 +1768,9 @@
     <t>可以指定开出任意白色宝石的箱子</t>
   </si>
   <si>
+    <t>1131001_1;1131002_1;1131003_1;1131004_1;1131005_1;1131006_1</t>
+  </si>
+  <si>
     <t>绿色宝石箱</t>
   </si>
   <si>
@@ -1777,6 +1780,9 @@
     <t>可以指定开出任意绿色宝石的箱子</t>
   </si>
   <si>
+    <t>1131101_1;1131102_1;1131103_1;1131104_1;1131105_1;1131106_1</t>
+  </si>
+  <si>
     <t>蓝色宝石箱</t>
   </si>
   <si>
@@ -1786,6 +1792,9 @@
     <t>可以指定开出任意蓝色宝石的箱子</t>
   </si>
   <si>
+    <t>1131201_1;1131202_1;1131203_1;1131204_1;1131205_1;1131206_1</t>
+  </si>
+  <si>
     <t>紫色宝石箱</t>
   </si>
   <si>
@@ -1795,6 +1804,9 @@
     <t>可以指定开出任意紫色宝石的箱子</t>
   </si>
   <si>
+    <t>1131301_1;1131302_1;1131303_1;1131304_1;1131305_1;1131306_1</t>
+  </si>
+  <si>
     <t>橙色宝石箱</t>
   </si>
   <si>
@@ -1802,6 +1814,9 @@
   </si>
   <si>
     <t>可以指定开出任意橙色宝石的箱子</t>
+  </si>
+  <si>
+    <t>1131401_1;1131402_1;1131403_1;1131404_1;1131405_1;1131406_1</t>
   </si>
   <si>
     <t>基础命中.白</t>
@@ -7214,6 +7229,9 @@
       <c r="O79" s="1" t="s">
         <v>218</v>
       </c>
+      <c r="R79" s="1">
+        <v>-1</v>
+      </c>
     </row>
     <row r="80" spans="1:20">
       <c r="A80" s="1">
@@ -7252,6 +7270,9 @@
       <c r="O80" s="1" t="s">
         <v>220</v>
       </c>
+      <c r="R80" s="1">
+        <v>-1</v>
+      </c>
     </row>
     <row r="81" spans="1:18">
       <c r="A81" s="1">
@@ -7290,6 +7311,9 @@
       <c r="O81" s="1" t="s">
         <v>222</v>
       </c>
+      <c r="R81" s="1">
+        <v>-1</v>
+      </c>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="1">
@@ -7328,6 +7352,9 @@
       <c r="O82" s="1" t="s">
         <v>224</v>
       </c>
+      <c r="R82" s="1">
+        <v>-1</v>
+      </c>
     </row>
     <row r="83" spans="1:18">
       <c r="A83" s="1">
@@ -7366,6 +7393,9 @@
       <c r="O83" s="1" t="s">
         <v>226</v>
       </c>
+      <c r="R83" s="1">
+        <v>-1</v>
+      </c>
     </row>
     <row r="84" ht="17.25" spans="1:18">
       <c r="A84" s="1">
@@ -8148,6 +8178,9 @@
         <f>"使用该道具后可以指定生成游客"&amp;O143</f>
         <v>使用该道具后可以指定生成游客街头潮人</v>
       </c>
+      <c r="R101" s="1">
+        <v>999999</v>
+      </c>
       <c r="S101" s="1" t="s">
         <v>262</v>
       </c>
@@ -8188,6 +8221,9 @@
         <f t="shared" ref="O102:O130" si="1">"使用该道具后可以指定生成游客"&amp;O144</f>
         <v>使用该道具后可以指定生成游客复古绅士</v>
       </c>
+      <c r="R102" s="1">
+        <v>999999</v>
+      </c>
       <c r="S102" s="1" t="s">
         <v>263</v>
       </c>
@@ -8228,6 +8264,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客酷盖少年</v>
       </c>
+      <c r="R103" s="1">
+        <v>999999</v>
+      </c>
       <c r="S103" s="1" t="s">
         <v>264</v>
       </c>
@@ -8268,6 +8307,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客潮流先锋</v>
       </c>
+      <c r="R104" s="1">
+        <v>999999</v>
+      </c>
       <c r="S104" s="1" t="s">
         <v>265</v>
       </c>
@@ -8308,6 +8350,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客时尚教主</v>
       </c>
+      <c r="R105" s="1">
+        <v>999999</v>
+      </c>
       <c r="S105" s="1" t="s">
         <v>266</v>
       </c>
@@ -8348,6 +8393,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客街拍达人</v>
       </c>
+      <c r="R106" s="1">
+        <v>999999</v>
+      </c>
       <c r="S106" s="1" t="s">
         <v>267</v>
       </c>
@@ -8388,6 +8436,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客运动健将</v>
       </c>
+      <c r="R107" s="1">
+        <v>999999</v>
+      </c>
       <c r="S107" s="1" t="s">
         <v>268</v>
       </c>
@@ -8428,6 +8479,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客跑酷少年</v>
       </c>
+      <c r="R108" s="1">
+        <v>999999</v>
+      </c>
       <c r="S108" s="1" t="s">
         <v>269</v>
       </c>
@@ -8468,6 +8522,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客滑板高手</v>
       </c>
+      <c r="R109" s="1">
+        <v>999999</v>
+      </c>
       <c r="S109" s="1" t="s">
         <v>270</v>
       </c>
@@ -8508,6 +8565,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客甜心辣妹</v>
       </c>
+      <c r="R110" s="1">
+        <v>999999</v>
+      </c>
       <c r="S110" s="1" t="s">
         <v>271</v>
       </c>
@@ -8548,6 +8608,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客活力少女</v>
       </c>
+      <c r="R111" s="1">
+        <v>999999</v>
+      </c>
       <c r="S111" s="1" t="s">
         <v>272</v>
       </c>
@@ -8588,6 +8651,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客优雅女神</v>
       </c>
+      <c r="R112" s="1">
+        <v>999999</v>
+      </c>
       <c r="S112" s="1" t="s">
         <v>273</v>
       </c>
@@ -8628,6 +8694,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客健身狂魔</v>
       </c>
+      <c r="R113" s="1">
+        <v>999999</v>
+      </c>
       <c r="S113" s="1" t="s">
         <v>274</v>
       </c>
@@ -8668,6 +8737,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客单车骑士</v>
       </c>
+      <c r="R114" s="1">
+        <v>999999</v>
+      </c>
       <c r="S114" s="1" t="s">
         <v>275</v>
       </c>
@@ -8708,6 +8780,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客登山行者</v>
       </c>
+      <c r="R115" s="1">
+        <v>999999</v>
+      </c>
       <c r="S115" s="1" t="s">
         <v>276</v>
       </c>
@@ -8748,6 +8823,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客文艺青年</v>
       </c>
+      <c r="R116" s="1">
+        <v>999999</v>
+      </c>
       <c r="S116" s="1" t="s">
         <v>277</v>
       </c>
@@ -8788,6 +8866,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客书香少女</v>
       </c>
+      <c r="R117" s="1">
+        <v>999999</v>
+      </c>
       <c r="S117" s="1" t="s">
         <v>278</v>
       </c>
@@ -8828,6 +8909,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客民谣歌手</v>
       </c>
+      <c r="R118" s="1">
+        <v>999999</v>
+      </c>
       <c r="S118" s="1" t="s">
         <v>279</v>
       </c>
@@ -8868,6 +8952,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客马拉松客</v>
       </c>
+      <c r="R119" s="1">
+        <v>999999</v>
+      </c>
       <c r="S119" s="1" t="s">
         <v>280</v>
       </c>
@@ -8908,6 +8995,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客极限玩家</v>
       </c>
+      <c r="R120" s="1">
+        <v>999999</v>
+      </c>
       <c r="S120" s="1" t="s">
         <v>281</v>
       </c>
@@ -8948,6 +9038,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客科技极客</v>
       </c>
+      <c r="R121" s="1">
+        <v>999999</v>
+      </c>
       <c r="S121" s="1" t="s">
         <v>282</v>
       </c>
@@ -8988,6 +9081,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客独立画家</v>
       </c>
+      <c r="R122" s="1">
+        <v>999999</v>
+      </c>
       <c r="S122" s="1" t="s">
         <v>283</v>
       </c>
@@ -9028,6 +9124,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客浪漫诗人</v>
       </c>
+      <c r="R123" s="1">
+        <v>999999</v>
+      </c>
       <c r="S123" s="1" t="s">
         <v>284</v>
       </c>
@@ -9068,6 +9167,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客古典乐迷</v>
       </c>
+      <c r="R124" s="1">
+        <v>999999</v>
+      </c>
       <c r="S124" s="1" t="s">
         <v>285</v>
       </c>
@@ -9108,6 +9210,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客创业新贵</v>
       </c>
+      <c r="R125" s="1">
+        <v>999999</v>
+      </c>
       <c r="S125" s="1" t="s">
         <v>286</v>
       </c>
@@ -9148,6 +9253,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客摸金校尉</v>
       </c>
+      <c r="R126" s="1">
+        <v>999999</v>
+      </c>
       <c r="S126" s="1" t="s">
         <v>287</v>
       </c>
@@ -9188,6 +9296,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客氪金大佬</v>
       </c>
+      <c r="R127" s="1">
+        <v>999999</v>
+      </c>
       <c r="S127" s="1" t="s">
         <v>288</v>
       </c>
@@ -9228,6 +9339,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客穿搭博主</v>
       </c>
+      <c r="R128" s="1">
+        <v>999999</v>
+      </c>
       <c r="S128" s="1" t="s">
         <v>289</v>
       </c>
@@ -9268,6 +9382,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客美妆新秀</v>
       </c>
+      <c r="R129" s="1">
+        <v>999999</v>
+      </c>
       <c r="S129" s="1" t="s">
         <v>290</v>
       </c>
@@ -9308,6 +9425,9 @@
         <f t="shared" si="1"/>
         <v>使用该道具后可以指定生成游客高定女王</v>
       </c>
+      <c r="R130" s="1">
+        <v>999999</v>
+      </c>
       <c r="S130" s="1" t="s">
         <v>291</v>
       </c>
@@ -9346,6 +9466,9 @@
       <c r="O131" s="1" t="s">
         <v>293</v>
       </c>
+      <c r="R131" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="132" spans="1:19">
       <c r="A132" s="1">
@@ -9381,6 +9504,9 @@
       <c r="O132" s="1" t="s">
         <v>295</v>
       </c>
+      <c r="R132" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="133" spans="1:19">
       <c r="A133" s="1">
@@ -9416,6 +9542,9 @@
       <c r="O133" s="1" t="s">
         <v>297</v>
       </c>
+      <c r="R133" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="134" spans="1:19">
       <c r="A134" s="1">
@@ -9451,6 +9580,9 @@
       <c r="O134" s="1" t="s">
         <v>299</v>
       </c>
+      <c r="R134" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="135" spans="1:19">
       <c r="A135" s="1">
@@ -9486,6 +9618,9 @@
       <c r="O135" s="1" t="s">
         <v>301</v>
       </c>
+      <c r="R135" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="136" ht="17.25" spans="1:19">
       <c r="A136" s="1">
@@ -9530,6 +9665,9 @@
       <c r="O136" s="1" t="s">
         <v>304</v>
       </c>
+      <c r="R136" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="137" ht="17.25" spans="1:19">
       <c r="A137" s="1">
@@ -9574,6 +9712,9 @@
       <c r="O137" s="1" t="s">
         <v>307</v>
       </c>
+      <c r="R137" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="138" spans="1:19">
       <c r="A138" s="1">
@@ -9618,6 +9759,9 @@
       <c r="O138" s="1" t="s">
         <v>310</v>
       </c>
+      <c r="R138" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="139" spans="1:19">
       <c r="A139" s="1">
@@ -9662,6 +9806,9 @@
       <c r="O139" s="1" t="s">
         <v>313</v>
       </c>
+      <c r="R139" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="140" spans="1:19">
       <c r="A140" s="1">
@@ -9706,6 +9853,9 @@
       <c r="O140" s="1" t="s">
         <v>316</v>
       </c>
+      <c r="R140" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="141" spans="1:19">
       <c r="A141" s="1">
@@ -9750,6 +9900,9 @@
       <c r="O141" s="1" t="s">
         <v>319</v>
       </c>
+      <c r="R141" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="142" spans="1:19">
       <c r="A142" s="1">
@@ -9794,6 +9947,9 @@
       <c r="O142" s="1" t="s">
         <v>322</v>
       </c>
+      <c r="R142" s="1">
+        <v>999999</v>
+      </c>
     </row>
     <row r="143" spans="1:19">
       <c r="A143" s="1">
@@ -14577,7 +14733,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="257" spans="1:18">
+    <row r="257" spans="1:20">
       <c r="A257" s="1">
         <v>1128201</v>
       </c>
@@ -14620,7 +14776,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="258" spans="1:18">
+    <row r="258" spans="1:20">
       <c r="A258" s="1">
         <v>1128202</v>
       </c>
@@ -14663,7 +14819,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="259" spans="1:18">
+    <row r="259" spans="1:20">
       <c r="A259" s="1">
         <v>1128301</v>
       </c>
@@ -14706,7 +14862,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="260" spans="1:18">
+    <row r="260" spans="1:20">
       <c r="A260" s="1">
         <v>1128302</v>
       </c>
@@ -14749,7 +14905,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="261" spans="1:18">
+    <row r="261" spans="1:20">
       <c r="A261" s="1">
         <v>1128401</v>
       </c>
@@ -14792,7 +14948,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="262" spans="1:18">
+    <row r="262" spans="1:20">
       <c r="A262" s="1">
         <v>1128402</v>
       </c>
@@ -14835,7 +14991,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="263" spans="1:18">
+    <row r="263" spans="1:20">
       <c r="A263" s="1">
         <v>1130001</v>
       </c>
@@ -14876,7 +15032,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="264" spans="1:18">
+    <row r="264" spans="1:20">
       <c r="A264" s="1">
         <v>1130002</v>
       </c>
@@ -14916,8 +15072,11 @@
       <c r="R264" s="1">
         <v>999999</v>
       </c>
-    </row>
-    <row r="265" spans="1:18">
+      <c r="T264" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="265" spans="1:20">
       <c r="A265" s="1">
         <v>1130003</v>
       </c>
@@ -14925,7 +15084,7 @@
         <v>1130003</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E265" s="1">
         <v>1</v>
@@ -14943,7 +15102,7 @@
         <v>1</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M265" s="1">
         <v>2130003</v>
@@ -14952,13 +15111,16 @@
         <v>0</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R265" s="1">
         <v>999999</v>
       </c>
-    </row>
-    <row r="266" spans="1:18">
+      <c r="T265" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="266" spans="1:20">
       <c r="A266" s="1">
         <v>1130004</v>
       </c>
@@ -14966,7 +15128,7 @@
         <v>1130004</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E266" s="1">
         <v>1</v>
@@ -14984,7 +15146,7 @@
         <v>1</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M266" s="1">
         <v>2130004</v>
@@ -14993,13 +15155,16 @@
         <v>0</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="R266" s="1">
         <v>999999</v>
       </c>
-    </row>
-    <row r="267" spans="1:18">
+      <c r="T266" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="267" spans="1:20">
       <c r="A267" s="1">
         <v>1130005</v>
       </c>
@@ -15007,7 +15172,7 @@
         <v>1130005</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E267" s="1">
         <v>1</v>
@@ -15025,7 +15190,7 @@
         <v>1</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M267" s="1">
         <v>2130005</v>
@@ -15034,13 +15199,16 @@
         <v>0</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="R267" s="1">
         <v>999999</v>
       </c>
-    </row>
-    <row r="268" spans="1:18">
+      <c r="T267" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="268" spans="1:20">
       <c r="A268" s="1">
         <v>1130006</v>
       </c>
@@ -15048,7 +15216,7 @@
         <v>1130006</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E268" s="1">
         <v>1</v>
@@ -15066,7 +15234,7 @@
         <v>1</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="M268" s="1">
         <v>2130006</v>
@@ -15075,13 +15243,16 @@
         <v>0</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="R268" s="1">
         <v>999999</v>
       </c>
-    </row>
-    <row r="269" spans="1:18">
+      <c r="T268" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="269" spans="1:20">
       <c r="A269" s="1">
         <v>1131001</v>
       </c>
@@ -15089,7 +15260,7 @@
         <v>1131001</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -15107,7 +15278,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="M269" s="1">
         <v>2131001</v>
@@ -15116,10 +15287,13 @@
         <v>0</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="270" spans="1:18">
+        <v>479</v>
+      </c>
+      <c r="R269" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="270" spans="1:20">
       <c r="A270" s="1">
         <v>1131002</v>
       </c>
@@ -15127,7 +15301,7 @@
         <v>1131002</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -15145,7 +15319,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="M270" s="1">
         <v>2131002</v>
@@ -15154,10 +15328,13 @@
         <v>0</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="271" spans="1:18">
+        <v>482</v>
+      </c>
+      <c r="R270" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="271" spans="1:20">
       <c r="A271" s="1">
         <v>1131003</v>
       </c>
@@ -15165,7 +15342,7 @@
         <v>1131003</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -15183,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="M271" s="1">
         <v>2131003</v>
@@ -15192,10 +15369,13 @@
         <v>0</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="272" spans="1:18">
+        <v>485</v>
+      </c>
+      <c r="R271" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="272" spans="1:20">
       <c r="A272" s="1">
         <v>1131004</v>
       </c>
@@ -15203,7 +15383,7 @@
         <v>1131004</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -15221,7 +15401,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="M272" s="1">
         <v>2131004</v>
@@ -15230,10 +15410,13 @@
         <v>0</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="273" spans="1:15">
+        <v>488</v>
+      </c>
+      <c r="R272" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18">
       <c r="A273" s="1">
         <v>1131005</v>
       </c>
@@ -15241,7 +15424,7 @@
         <v>1131005</v>
       </c>
       <c r="D273" s="15" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -15259,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="M273" s="1">
         <v>2131005</v>
@@ -15268,10 +15451,13 @@
         <v>0</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="274" spans="1:15">
+        <v>491</v>
+      </c>
+      <c r="R273" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18">
       <c r="A274" s="1">
         <v>1131006</v>
       </c>
@@ -15279,7 +15465,7 @@
         <v>1131006</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -15297,7 +15483,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="M274" s="1">
         <v>2131006</v>
@@ -15306,10 +15492,13 @@
         <v>0</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="275" spans="1:15">
+        <v>494</v>
+      </c>
+      <c r="R274" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18">
       <c r="A275" s="1">
         <v>1131101</v>
       </c>
@@ -15317,7 +15506,7 @@
         <v>1131101</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -15335,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="M275" s="1">
         <v>2131101</v>
@@ -15344,10 +15533,13 @@
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="276" spans="1:15">
+        <v>479</v>
+      </c>
+      <c r="R275" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18">
       <c r="A276" s="1">
         <v>1131102</v>
       </c>
@@ -15355,7 +15547,7 @@
         <v>1131102</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -15373,7 +15565,7 @@
         <v>0</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="M276" s="1">
         <v>2131102</v>
@@ -15382,10 +15574,13 @@
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="277" spans="1:15">
+        <v>482</v>
+      </c>
+      <c r="R276" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18">
       <c r="A277" s="1">
         <v>1131103</v>
       </c>
@@ -15393,7 +15588,7 @@
         <v>1131103</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -15411,7 +15606,7 @@
         <v>0</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="M277" s="1">
         <v>2131103</v>
@@ -15420,10 +15615,13 @@
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="278" spans="1:15">
+        <v>485</v>
+      </c>
+      <c r="R277" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18">
       <c r="A278" s="1">
         <v>1131104</v>
       </c>
@@ -15431,7 +15629,7 @@
         <v>1131104</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -15449,7 +15647,7 @@
         <v>0</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="M278" s="1">
         <v>2131104</v>
@@ -15458,10 +15656,13 @@
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="279" spans="1:15">
+        <v>488</v>
+      </c>
+      <c r="R278" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18">
       <c r="A279" s="1">
         <v>1131105</v>
       </c>
@@ -15469,7 +15670,7 @@
         <v>1131105</v>
       </c>
       <c r="D279" s="15" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -15487,7 +15688,7 @@
         <v>0</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="M279" s="1">
         <v>2131105</v>
@@ -15496,10 +15697,13 @@
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="280" spans="1:15">
+        <v>491</v>
+      </c>
+      <c r="R279" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18">
       <c r="A280" s="1">
         <v>1131106</v>
       </c>
@@ -15507,7 +15711,7 @@
         <v>1131106</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -15525,7 +15729,7 @@
         <v>0</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="M280" s="1">
         <v>2131106</v>
@@ -15534,10 +15738,13 @@
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="281" spans="1:15">
+        <v>494</v>
+      </c>
+      <c r="R280" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="281" spans="1:18">
       <c r="A281" s="1">
         <v>1131201</v>
       </c>
@@ -15545,7 +15752,7 @@
         <v>1131201</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15563,7 +15770,7 @@
         <v>0</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="M281" s="1">
         <v>2131201</v>
@@ -15572,10 +15779,13 @@
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="282" spans="1:15">
+        <v>479</v>
+      </c>
+      <c r="R281" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="282" spans="1:18">
       <c r="A282" s="1">
         <v>1131202</v>
       </c>
@@ -15583,7 +15793,7 @@
         <v>1131202</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15601,7 +15811,7 @@
         <v>0</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="M282" s="1">
         <v>2131202</v>
@@ -15610,10 +15820,13 @@
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="283" spans="1:15">
+        <v>482</v>
+      </c>
+      <c r="R282" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18">
       <c r="A283" s="1">
         <v>1131203</v>
       </c>
@@ -15621,7 +15834,7 @@
         <v>1131203</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15639,7 +15852,7 @@
         <v>0</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M283" s="1">
         <v>2131203</v>
@@ -15648,10 +15861,13 @@
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="284" spans="1:15">
+        <v>485</v>
+      </c>
+      <c r="R283" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18">
       <c r="A284" s="1">
         <v>1131204</v>
       </c>
@@ -15659,7 +15875,7 @@
         <v>1131204</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15677,7 +15893,7 @@
         <v>0</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="M284" s="1">
         <v>2131204</v>
@@ -15686,10 +15902,13 @@
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="285" spans="1:15">
+        <v>488</v>
+      </c>
+      <c r="R284" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18">
       <c r="A285" s="1">
         <v>1131205</v>
       </c>
@@ -15697,7 +15916,7 @@
         <v>1131205</v>
       </c>
       <c r="D285" s="15" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15715,7 +15934,7 @@
         <v>0</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="M285" s="1">
         <v>2131205</v>
@@ -15724,10 +15943,13 @@
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="286" spans="1:15">
+        <v>491</v>
+      </c>
+      <c r="R285" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18">
       <c r="A286" s="1">
         <v>1131206</v>
       </c>
@@ -15735,7 +15957,7 @@
         <v>1131206</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15753,7 +15975,7 @@
         <v>0</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="M286" s="1">
         <v>2131206</v>
@@ -15762,10 +15984,13 @@
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="287" spans="1:15">
+        <v>494</v>
+      </c>
+      <c r="R286" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18">
       <c r="A287" s="1">
         <v>1131301</v>
       </c>
@@ -15773,7 +15998,7 @@
         <v>1131301</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -15791,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="M287" s="1">
         <v>2131301</v>
@@ -15800,10 +16025,13 @@
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="288" spans="1:15">
+        <v>521</v>
+      </c>
+      <c r="R287" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18">
       <c r="A288" s="1">
         <v>1131302</v>
       </c>
@@ -15811,7 +16039,7 @@
         <v>1131302</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -15829,7 +16057,7 @@
         <v>0</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="M288" s="1">
         <v>2131302</v>
@@ -15838,10 +16066,13 @@
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="289" spans="1:15">
+        <v>482</v>
+      </c>
+      <c r="R288" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18">
       <c r="A289" s="1">
         <v>1131303</v>
       </c>
@@ -15849,7 +16080,7 @@
         <v>1131303</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -15867,7 +16098,7 @@
         <v>0</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="M289" s="1">
         <v>2131303</v>
@@ -15876,10 +16107,13 @@
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="290" spans="1:15">
+        <v>485</v>
+      </c>
+      <c r="R289" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18">
       <c r="A290" s="1">
         <v>1131304</v>
       </c>
@@ -15887,7 +16121,7 @@
         <v>1131304</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -15905,7 +16139,7 @@
         <v>0</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="M290" s="1">
         <v>2131304</v>
@@ -15914,10 +16148,13 @@
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="291" spans="1:15">
+        <v>488</v>
+      </c>
+      <c r="R290" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18">
       <c r="A291" s="1">
         <v>1131305</v>
       </c>
@@ -15925,7 +16162,7 @@
         <v>1131305</v>
       </c>
       <c r="D291" s="15" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -15943,7 +16180,7 @@
         <v>0</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="M291" s="1">
         <v>2131305</v>
@@ -15952,10 +16189,13 @@
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="292" spans="1:15">
+        <v>491</v>
+      </c>
+      <c r="R291" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18">
       <c r="A292" s="1">
         <v>1131306</v>
       </c>
@@ -15963,7 +16203,7 @@
         <v>1131306</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -15981,7 +16221,7 @@
         <v>0</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="M292" s="1">
         <v>2131306</v>
@@ -15990,10 +16230,13 @@
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="293" spans="1:15">
+        <v>494</v>
+      </c>
+      <c r="R292" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18">
       <c r="A293" s="1">
         <v>1131401</v>
       </c>
@@ -16001,7 +16244,7 @@
         <v>1131401</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -16019,7 +16262,7 @@
         <v>0</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="M293" s="1">
         <v>2131401</v>
@@ -16028,10 +16271,13 @@
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="294" spans="1:15">
+        <v>479</v>
+      </c>
+      <c r="R293" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18">
       <c r="A294" s="1">
         <v>1131402</v>
       </c>
@@ -16039,7 +16285,7 @@
         <v>1131402</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -16057,7 +16303,7 @@
         <v>0</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M294" s="1">
         <v>2131402</v>
@@ -16066,10 +16312,13 @@
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="295" spans="1:15">
+        <v>482</v>
+      </c>
+      <c r="R294" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18">
       <c r="A295" s="1">
         <v>1131403</v>
       </c>
@@ -16077,7 +16326,7 @@
         <v>1131403</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -16095,7 +16344,7 @@
         <v>0</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="M295" s="1">
         <v>2131403</v>
@@ -16104,10 +16353,13 @@
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="296" spans="1:15">
+        <v>485</v>
+      </c>
+      <c r="R295" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18">
       <c r="A296" s="1">
         <v>1131404</v>
       </c>
@@ -16115,7 +16367,7 @@
         <v>1131404</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -16133,7 +16385,7 @@
         <v>0</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="M296" s="1">
         <v>2131404</v>
@@ -16142,10 +16394,13 @@
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="297" spans="1:15">
+        <v>488</v>
+      </c>
+      <c r="R296" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18">
       <c r="A297" s="1">
         <v>1131405</v>
       </c>
@@ -16153,7 +16408,7 @@
         <v>1131405</v>
       </c>
       <c r="D297" s="15" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -16171,7 +16426,7 @@
         <v>0</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="M297" s="1">
         <v>2131405</v>
@@ -16180,10 +16435,13 @@
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="298" spans="1:15">
+        <v>491</v>
+      </c>
+      <c r="R297" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18">
       <c r="A298" s="1">
         <v>1131406</v>
       </c>
@@ -16191,7 +16449,7 @@
         <v>1131406</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -16209,7 +16467,7 @@
         <v>0</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="M298" s="1">
         <v>2131406</v>
@@ -16218,10 +16476,13 @@
         <v>0</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="299" spans="1:15">
+        <v>494</v>
+      </c>
+      <c r="R298" s="1">
+        <v>999999</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18">
       <c r="A299" s="1">
         <v>1140001</v>
       </c>
@@ -16229,7 +16490,7 @@
         <v>1140001</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -16247,7 +16508,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="M299" s="1">
         <v>2140001</v>
@@ -16256,10 +16517,13 @@
         <v>0</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="300" spans="1:15">
+        <v>546</v>
+      </c>
+      <c r="R299" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:18">
       <c r="A300" s="1">
         <v>1140002</v>
       </c>
@@ -16267,7 +16531,7 @@
         <v>1140002</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -16285,7 +16549,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="M300" s="1">
         <v>2140002</v>
@@ -16294,10 +16558,13 @@
         <v>0</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="301" spans="1:15">
+        <v>549</v>
+      </c>
+      <c r="R300" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:18">
       <c r="A301" s="1">
         <v>1140003</v>
       </c>
@@ -16305,7 +16572,7 @@
         <v>1140003</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -16323,7 +16590,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="M301" s="1">
         <v>2140003</v>
@@ -16332,10 +16599,13 @@
         <v>0</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="302" spans="1:15">
+        <v>552</v>
+      </c>
+      <c r="R301" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:18">
       <c r="A302" s="1">
         <v>1140004</v>
       </c>
@@ -16343,7 +16613,7 @@
         <v>1140004</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -16361,7 +16631,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="M302" s="1">
         <v>2140004</v>
@@ -16370,10 +16640,13 @@
         <v>0</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="303" spans="1:15">
+        <v>555</v>
+      </c>
+      <c r="R302" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:18">
       <c r="A303" s="1">
         <v>1140005</v>
       </c>
@@ -16381,7 +16654,7 @@
         <v>1140005</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -16399,7 +16672,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="M303" s="1">
         <v>2140005</v>
@@ -16408,10 +16681,13 @@
         <v>0</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="304" spans="1:15">
+        <v>558</v>
+      </c>
+      <c r="R303" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:18">
       <c r="A304" s="1">
         <v>1140006</v>
       </c>
@@ -16419,7 +16695,7 @@
         <v>1140006</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -16437,7 +16713,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M304" s="1">
         <v>2140006</v>
@@ -16446,7 +16722,10 @@
         <v>0</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>556</v>
+        <v>561</v>
+      </c>
+      <c r="R304" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:18">
@@ -16457,7 +16736,7 @@
         <v>1150001</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -16475,7 +16754,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="M305" s="1">
         <v>2150001</v>
@@ -16499,7 +16778,7 @@
         <v>1150002</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -16517,7 +16796,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="M306" s="1">
         <v>2150002</v>
@@ -16541,7 +16820,7 @@
         <v>1150003</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -16559,7 +16838,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="M307" s="1">
         <v>2150003</v>
@@ -16583,7 +16862,7 @@
         <v>1150004</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16601,7 +16880,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="M308" s="1">
         <v>2150004</v>
@@ -16625,7 +16904,7 @@
         <v>1150005</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16643,7 +16922,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="M309" s="1">
         <v>2150005</v>
@@ -16667,7 +16946,7 @@
         <v>1150006</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16685,7 +16964,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="M310" s="1">
         <v>2150006</v>
@@ -16709,7 +16988,7 @@
         <v>1150007</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -16727,7 +17006,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="M311" s="1">
         <v>2150007</v>
@@ -16751,7 +17030,7 @@
         <v>1150008</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -16769,7 +17048,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="M312" s="1">
         <v>2150008</v>
@@ -16793,7 +17072,7 @@
         <v>1150009</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -16811,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="M313" s="1">
         <v>2150009</v>
@@ -16835,7 +17114,7 @@
         <v>1150010</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -16853,7 +17132,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="M314" s="1">
         <v>2150010</v>
@@ -16877,7 +17156,7 @@
         <v>1150011</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -16895,7 +17174,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="M315" s="1">
         <v>2150011</v>
@@ -16919,7 +17198,7 @@
         <v>1150012</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -16937,7 +17216,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="M316" s="1">
         <v>2150012</v>
@@ -16961,7 +17240,7 @@
         <v>1150013</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -16979,7 +17258,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="M317" s="1">
         <v>2150013</v>
@@ -17003,7 +17282,7 @@
         <v>1150014</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -17021,7 +17300,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="M318" s="1">
         <v>2150014</v>
@@ -17045,7 +17324,7 @@
         <v>1150015</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -17063,7 +17342,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="M319" s="1">
         <v>2150015</v>
@@ -17087,7 +17366,7 @@
         <v>1150016</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -17105,7 +17384,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="M320" s="1">
         <v>2150016</v>
@@ -17129,7 +17408,7 @@
         <v>1150017</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -17147,7 +17426,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="M321" s="1">
         <v>2150017</v>
@@ -17171,7 +17450,7 @@
         <v>1150018</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -17189,7 +17468,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="M322" s="1">
         <v>2150018</v>
@@ -17213,7 +17492,7 @@
         <v>1150019</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -17231,7 +17510,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="M323" s="1">
         <v>2150019</v>
@@ -17255,7 +17534,7 @@
         <v>1150020</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -17273,7 +17552,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="M324" s="1">
         <v>2150020</v>
@@ -17297,7 +17576,7 @@
         <v>1150021</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -17315,7 +17594,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="M325" s="1">
         <v>2150021</v>
@@ -17339,7 +17618,7 @@
         <v>1150022</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -17357,7 +17636,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="M326" s="1">
         <v>2150022</v>
@@ -17381,7 +17660,7 @@
         <v>1150023</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -17399,7 +17678,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="M327" s="1">
         <v>2150023</v>
@@ -17423,7 +17702,7 @@
         <v>1150024</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -17441,7 +17720,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="M328" s="1">
         <v>2150024</v>
@@ -17465,7 +17744,7 @@
         <v>1150025</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -17483,7 +17762,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="M329" s="1">
         <v>2150025</v>
@@ -17507,7 +17786,7 @@
         <v>1150026</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -17525,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="M330" s="1">
         <v>2150026</v>
@@ -17549,7 +17828,7 @@
         <v>1150027</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17567,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="M331" s="1">
         <v>2150027</v>
@@ -17591,7 +17870,7 @@
         <v>1150028</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17609,7 +17888,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="M332" s="1">
         <v>2150028</v>
@@ -17633,7 +17912,7 @@
         <v>1150029</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17651,7 +17930,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="M333" s="1">
         <v>2150029</v>
@@ -17675,7 +17954,7 @@
         <v>1150030</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -17693,7 +17972,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="M334" s="1">
         <v>2150030</v>
@@ -17717,7 +17996,7 @@
         <v>1150031</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -17735,7 +18014,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="M335" s="1">
         <v>2150031</v>
@@ -17759,7 +18038,7 @@
         <v>1150032</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -17777,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="M336" s="1">
         <v>2150032</v>
@@ -17801,7 +18080,7 @@
         <v>1150033</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -17819,7 +18098,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="M337" s="1">
         <v>2150033</v>
@@ -17843,7 +18122,7 @@
         <v>1150034</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -17861,7 +18140,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="M338" s="1">
         <v>2150034</v>
@@ -17885,7 +18164,7 @@
         <v>1150035</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -17903,7 +18182,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="M339" s="1">
         <v>2150035</v>
@@ -17927,7 +18206,7 @@
         <v>1150036</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -17945,7 +18224,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="M340" s="1">
         <v>2150036</v>
@@ -17969,7 +18248,7 @@
         <v>1150037</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -17987,7 +18266,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="M341" s="1">
         <v>2150037</v>
@@ -18011,7 +18290,7 @@
         <v>1150038</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -18029,7 +18308,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="M342" s="1">
         <v>2150038</v>
@@ -18053,7 +18332,7 @@
         <v>1150039</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -18071,7 +18350,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="M343" s="1">
         <v>2150039</v>
@@ -18095,7 +18374,7 @@
         <v>1150040</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -18113,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="M344" s="1">
         <v>2150040</v>
@@ -18137,7 +18416,7 @@
         <v>1150041</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -18155,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="M345" s="1">
         <v>2150041</v>
@@ -18179,7 +18458,7 @@
         <v>1150042</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -18197,7 +18476,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="M346" s="1">
         <v>2150042</v>
@@ -18221,7 +18500,7 @@
         <v>1150043</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -18239,7 +18518,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="M347" s="1">
         <v>2150043</v>
@@ -18263,7 +18542,7 @@
         <v>1150044</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -18281,7 +18560,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="M348" s="1">
         <v>2150044</v>
@@ -18305,7 +18584,7 @@
         <v>1150045</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -18323,7 +18602,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="M349" s="1">
         <v>2150045</v>
@@ -18347,7 +18626,7 @@
         <v>1150046</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -18365,7 +18644,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="M350" s="1">
         <v>2150046</v>
@@ -18389,7 +18668,7 @@
         <v>1150047</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -18407,7 +18686,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="M351" s="1">
         <v>2150047</v>
@@ -18431,7 +18710,7 @@
         <v>1150048</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -18449,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="M352" s="1">
         <v>2150048</v>
@@ -18473,7 +18752,7 @@
         <v>1150049</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -18491,7 +18770,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="M353" s="1">
         <v>2150049</v>
@@ -18515,7 +18794,7 @@
         <v>1150050</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -18533,7 +18812,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="M354" s="1">
         <v>2150050</v>
@@ -18557,7 +18836,7 @@
         <v>1150051</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18575,7 +18854,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="M355" s="1">
         <v>2150051</v>
@@ -18599,7 +18878,7 @@
         <v>1150052</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18617,7 +18896,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="M356" s="1">
         <v>2150052</v>
@@ -18641,7 +18920,7 @@
         <v>1150053</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18659,7 +18938,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="M357" s="1">
         <v>2150053</v>
@@ -18683,7 +18962,7 @@
         <v>1150054</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -18701,7 +18980,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="M358" s="1">
         <v>2150054</v>
@@ -18725,7 +19004,7 @@
         <v>1150055</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="E359" s="1">
         <v>2</v>
@@ -18743,7 +19022,7 @@
         <v>0</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="M359" s="1">
         <v>2150055</v>
@@ -18767,7 +19046,7 @@
         <v>1150056</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="E360" s="1">
         <v>2</v>
@@ -18785,7 +19064,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="M360" s="1">
         <v>2150056</v>
@@ -18809,7 +19088,7 @@
         <v>1150057</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="E361" s="1">
         <v>2</v>
@@ -18827,7 +19106,7 @@
         <v>0</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="M361" s="1">
         <v>2150057</v>
@@ -18851,7 +19130,7 @@
         <v>1150058</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E362" s="1">
         <v>2</v>
@@ -18869,7 +19148,7 @@
         <v>0</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="M362" s="1">
         <v>2150058</v>
@@ -18893,7 +19172,7 @@
         <v>1150059</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="E363" s="1">
         <v>2</v>
@@ -18911,7 +19190,7 @@
         <v>0</v>
       </c>
       <c r="L363" s="1" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="M363" s="1">
         <v>2150059</v>
@@ -18935,7 +19214,7 @@
         <v>1150060</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="E364" s="1">
         <v>2</v>
@@ -18953,7 +19232,7 @@
         <v>0</v>
       </c>
       <c r="L364" s="1" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="M364" s="1">
         <v>2150060</v>
@@ -18977,7 +19256,7 @@
         <v>1150061</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="E365" s="1">
         <v>2</v>
@@ -18995,7 +19274,7 @@
         <v>0</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="M365" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="687">
   <si>
     <t>道具ID</t>
   </si>
@@ -997,12 +997,18 @@
     <t>游客抽卡道具</t>
   </si>
   <si>
+    <t>daoju_ykck.png</t>
+  </si>
+  <si>
     <t>用于游客卡池抽奖的道具</t>
   </si>
   <si>
     <t>雇员抽卡道具</t>
   </si>
   <si>
+    <t>daoju_gyck.png</t>
+  </si>
+  <si>
     <t>用于雇员卡池抽卡的道具</t>
   </si>
   <si>
@@ -1825,7 +1831,7 @@
     <t>sj_bs_tb_sj_b.png</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+%s</t>
+    <t>普通模式Spin基础中奖概率+%s%%</t>
   </si>
   <si>
     <t>免费命中.白</t>
@@ -1834,7 +1840,7 @@
     <t>sj_bs_tb_sj_b_1.png</t>
   </si>
   <si>
-    <t>处于免费旋转模式时，该模式内50倍中奖概率+%s</t>
+    <t>处于免费旋转模式时，该模式内50倍中奖概率+%s%%</t>
   </si>
   <si>
     <t>基础收益.白</t>
@@ -1843,7 +1849,7 @@
     <t>sj_bs_tb_f_b.png</t>
   </si>
   <si>
-    <t>5-10倍区间的中奖概率+%s</t>
+    <t>5-10倍区间的中奖概率+%s%%</t>
   </si>
   <si>
     <t>大奖冲刺.白</t>
@@ -1852,7 +1858,7 @@
     <t>sj_bs_tb_f_b_1.png</t>
   </si>
   <si>
-    <t>20-50倍区间的触发概率+%s</t>
+    <t>20-50倍区间的触发概率+%s%%</t>
   </si>
   <si>
     <t>下注提升.白</t>
@@ -1870,7 +1876,7 @@
     <t>sj_bs_tb_sj_b_1_1.png</t>
   </si>
   <si>
-    <t>进入免费旋转模式的概率+%s</t>
+    <t>进入免费旋转模式的概率+%s%%</t>
   </si>
   <si>
     <t>基础命中.绿</t>
@@ -1903,6 +1909,9 @@
     <t>sj_bs_tb_sj_lv-1.png</t>
   </si>
   <si>
+    <t>下注的金额提升到%s%%</t>
+  </si>
+  <si>
     <t>免费模式.绿</t>
   </si>
   <si>
@@ -1951,7 +1960,7 @@
     <t>sj_bs_tb_sj_zi.png</t>
   </si>
   <si>
-    <t>普通模式Spin基础中奖概率+%ss</t>
+    <t>普通模式Spin基础中奖概率+%s%%s</t>
   </si>
   <si>
     <t>免费命中.紫</t>
@@ -6966,7 +6975,7 @@
         <v>1</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="M73" s="1">
         <v>2024013</v>
@@ -6975,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R73" s="1">
         <v>999999</v>
@@ -6989,7 +6998,7 @@
         <v>1024014</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -7007,7 +7016,7 @@
         <v>1</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>65</v>
+        <v>206</v>
       </c>
       <c r="M74" s="1">
         <v>2024014</v>
@@ -7016,7 +7025,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="R74" s="1">
         <v>999999</v>
@@ -7030,7 +7039,7 @@
         <v>1024015</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7057,13 +7066,13 @@
         <v>0</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="R75" s="1">
         <v>999999</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:20">
@@ -7074,7 +7083,7 @@
         <v>1024016</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7101,13 +7110,13 @@
         <v>0</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="R76" s="1">
         <v>999999</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:20">
@@ -7118,7 +7127,7 @@
         <v>1024017</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -7145,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R77" s="1">
         <v>999999</v>
@@ -7159,7 +7168,7 @@
         <v>1024018</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -7177,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M78" s="1">
         <v>2024018</v>
@@ -7186,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="R78" s="1">
         <v>-1</v>
@@ -7200,25 +7209,25 @@
         <v>1024019</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E79" s="1">
+        <v>2</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I79" s="1">
+        <v>1</v>
+      </c>
+      <c r="J79" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="E79" s="1">
-        <v>2</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I79" s="1">
-        <v>1</v>
-      </c>
-      <c r="J79" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="M79" s="1">
         <v>2024019</v>
@@ -7227,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R79" s="1">
         <v>-1</v>
@@ -7241,7 +7250,7 @@
         <v>1024020</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -7259,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M80" s="1">
         <v>2024020</v>
@@ -7268,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R80" s="1">
         <v>-1</v>
@@ -7282,7 +7291,7 @@
         <v>1024021</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -7300,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M81" s="1">
         <v>2024021</v>
@@ -7309,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="R81" s="1">
         <v>-1</v>
@@ -7323,7 +7332,7 @@
         <v>1024022</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -7341,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M82" s="1">
         <v>2024022</v>
@@ -7350,7 +7359,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R82" s="1">
         <v>-1</v>
@@ -7364,7 +7373,7 @@
         <v>1024023</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -7382,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M83" s="1">
         <v>2024023</v>
@@ -7391,7 +7400,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="R83" s="1">
         <v>-1</v>
@@ -7405,7 +7414,7 @@
         <v>1024024</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -7429,7 +7438,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M84" s="1">
         <v>2024024</v>
@@ -7438,7 +7447,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R84" s="1">
         <v>999999</v>
@@ -7452,7 +7461,7 @@
         <v>1024024</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -7476,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M85" s="1">
         <v>2024025</v>
@@ -7485,7 +7494,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="R85" s="1">
         <v>999999</v>
@@ -7499,7 +7508,7 @@
         <v>1024024</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
@@ -7523,7 +7532,7 @@
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M86" s="1">
         <v>2024026</v>
@@ -7532,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="R86" s="1">
         <v>999999</v>
@@ -7546,7 +7555,7 @@
         <v>1024024</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -7570,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M87" s="1">
         <v>2024027</v>
@@ -7579,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="R87" s="1">
         <v>999999</v>
@@ -7593,7 +7602,7 @@
         <v>1024024</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -7617,7 +7626,7 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M88" s="1">
         <v>2024028</v>
@@ -7626,7 +7635,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="R88" s="1">
         <v>999999</v>
@@ -7640,7 +7649,7 @@
         <v>1024024</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -7664,7 +7673,7 @@
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M89" s="1">
         <v>2024029</v>
@@ -7673,7 +7682,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="R89" s="1">
         <v>999999</v>
@@ -7687,7 +7696,7 @@
         <v>1024024</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -7711,7 +7720,7 @@
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M90" s="1">
         <v>2024030</v>
@@ -7720,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R90" s="1">
         <v>999999</v>
@@ -7734,7 +7743,7 @@
         <v>1024024</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
@@ -7758,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M91" s="1">
         <v>2024031</v>
@@ -7767,7 +7776,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="R91" s="1">
         <v>999999</v>
@@ -7781,7 +7790,7 @@
         <v>1024024</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -7805,7 +7814,7 @@
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M92" s="1">
         <v>2024032</v>
@@ -7814,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="R92" s="1">
         <v>999999</v>
@@ -7828,7 +7837,7 @@
         <v>1024024</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
@@ -7852,7 +7861,7 @@
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M93" s="1">
         <v>2024033</v>
@@ -7861,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="R93" s="1">
         <v>999999</v>
@@ -7875,7 +7884,7 @@
         <v>1024025</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -7899,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="R94" s="1">
         <v>999999</v>
@@ -7913,7 +7922,7 @@
         <v>1024026</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -7937,7 +7946,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="R95" s="1">
         <v>999999</v>
@@ -7951,7 +7960,7 @@
         <v>1024027</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -7975,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="R96" s="1">
         <v>999999</v>
@@ -7989,7 +7998,7 @@
         <v>1024028</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -8013,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="R97" s="1">
         <v>999999</v>
@@ -8027,7 +8036,7 @@
         <v>1024029</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -8051,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="R98" s="1">
         <v>999999</v>
@@ -8065,7 +8074,7 @@
         <v>1024030</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -8089,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="R99" s="1">
         <v>999999</v>
@@ -8103,7 +8112,7 @@
         <v>1024024</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -8127,7 +8136,7 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M100" s="1">
         <v>2024040</v>
@@ -8136,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="R100" s="1">
         <v>999999</v>
@@ -8182,7 +8191,7 @@
         <v>999999</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -8225,7 +8234,7 @@
         <v>999999</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -8268,7 +8277,7 @@
         <v>999999</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -8311,7 +8320,7 @@
         <v>999999</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -8354,7 +8363,7 @@
         <v>999999</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -8397,7 +8406,7 @@
         <v>999999</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -8440,7 +8449,7 @@
         <v>999999</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -8483,7 +8492,7 @@
         <v>999999</v>
       </c>
       <c r="S108" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -8526,7 +8535,7 @@
         <v>999999</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -8569,7 +8578,7 @@
         <v>999999</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -8612,7 +8621,7 @@
         <v>999999</v>
       </c>
       <c r="S111" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -8655,7 +8664,7 @@
         <v>999999</v>
       </c>
       <c r="S112" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -8698,7 +8707,7 @@
         <v>999999</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -8741,7 +8750,7 @@
         <v>999999</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -8784,7 +8793,7 @@
         <v>999999</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -8827,7 +8836,7 @@
         <v>999999</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -8870,7 +8879,7 @@
         <v>999999</v>
       </c>
       <c r="S117" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -8913,7 +8922,7 @@
         <v>999999</v>
       </c>
       <c r="S118" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -8956,7 +8965,7 @@
         <v>999999</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -8999,7 +9008,7 @@
         <v>999999</v>
       </c>
       <c r="S120" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -9042,7 +9051,7 @@
         <v>999999</v>
       </c>
       <c r="S121" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -9085,7 +9094,7 @@
         <v>999999</v>
       </c>
       <c r="S122" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -9128,7 +9137,7 @@
         <v>999999</v>
       </c>
       <c r="S123" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -9171,7 +9180,7 @@
         <v>999999</v>
       </c>
       <c r="S124" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -9214,7 +9223,7 @@
         <v>999999</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -9257,7 +9266,7 @@
         <v>999999</v>
       </c>
       <c r="S126" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -9300,7 +9309,7 @@
         <v>999999</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -9343,7 +9352,7 @@
         <v>999999</v>
       </c>
       <c r="S128" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -9386,7 +9395,7 @@
         <v>999999</v>
       </c>
       <c r="S129" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -9429,7 +9438,7 @@
         <v>999999</v>
       </c>
       <c r="S130" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -9440,7 +9449,7 @@
         <v>1024061</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
@@ -9464,7 +9473,7 @@
         <v>0</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="R131" s="1">
         <v>999999</v>
@@ -9478,7 +9487,7 @@
         <v>1024062</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -9502,7 +9511,7 @@
         <v>0</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="R132" s="1">
         <v>999999</v>
@@ -9516,7 +9525,7 @@
         <v>1024063</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -9540,7 +9549,7 @@
         <v>0</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="R133" s="1">
         <v>999999</v>
@@ -9554,7 +9563,7 @@
         <v>1024064</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -9578,7 +9587,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R134" s="1">
         <v>999999</v>
@@ -9592,7 +9601,7 @@
         <v>1024065</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -9616,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R135" s="1">
         <v>999999</v>
@@ -9630,7 +9639,7 @@
         <v>1024024</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -9642,7 +9651,7 @@
         <v>1</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I136" s="1">
         <v>1</v>
@@ -9654,7 +9663,7 @@
         <v>1</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M136" s="1">
         <v>2024076</v>
@@ -9663,7 +9672,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="R136" s="1">
         <v>999999</v>
@@ -9677,7 +9686,7 @@
         <v>1024024</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -9689,7 +9698,7 @@
         <v>1</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I137" s="1">
         <v>1</v>
@@ -9701,7 +9710,7 @@
         <v>1</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M137" s="1">
         <v>2024077</v>
@@ -9710,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="R137" s="1">
         <v>999999</v>
@@ -9724,7 +9733,7 @@
         <v>1024024</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -9736,7 +9745,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I138" s="1">
         <v>1</v>
@@ -9748,7 +9757,7 @@
         <v>1</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M138" s="1">
         <v>2024078</v>
@@ -9757,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="R138" s="1">
         <v>999999</v>
@@ -9771,7 +9780,7 @@
         <v>1024024</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -9783,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I139" s="1">
         <v>1</v>
@@ -9795,7 +9804,7 @@
         <v>1</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M139" s="1">
         <v>2024079</v>
@@ -9804,7 +9813,7 @@
         <v>0</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="R139" s="1">
         <v>999999</v>
@@ -9818,7 +9827,7 @@
         <v>1024024</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -9830,7 +9839,7 @@
         <v>1</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I140" s="1">
         <v>1</v>
@@ -9842,7 +9851,7 @@
         <v>1</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M140" s="1">
         <v>2024080</v>
@@ -9851,7 +9860,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="R140" s="1">
         <v>999999</v>
@@ -9865,7 +9874,7 @@
         <v>1024024</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -9877,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I141" s="1">
         <v>1</v>
@@ -9889,7 +9898,7 @@
         <v>1</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M141" s="1">
         <v>2024081</v>
@@ -9898,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="R141" s="1">
         <v>999999</v>
@@ -9912,7 +9921,7 @@
         <v>1024024</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -9924,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I142" s="1">
         <v>1</v>
@@ -9936,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M142" s="1">
         <v>2024082</v>
@@ -9945,7 +9954,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="R142" s="1">
         <v>999999</v>
@@ -9959,7 +9968,7 @@
         <v>1025101</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -9977,7 +9986,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M143" s="1">
         <v>2025101</v>
@@ -9986,7 +9995,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="R143" s="1">
         <v>-1</v>
@@ -10000,7 +10009,7 @@
         <v>1025102</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -10018,7 +10027,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M144" s="1">
         <v>2025102</v>
@@ -10027,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="R144" s="1">
         <v>-1</v>
@@ -10041,7 +10050,7 @@
         <v>1025103</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -10059,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M145" s="1">
         <v>2025103</v>
@@ -10068,7 +10077,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="R145" s="1">
         <v>-1</v>
@@ -10082,7 +10091,7 @@
         <v>1025104</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -10100,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M146" s="1">
         <v>2025104</v>
@@ -10109,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="R146" s="1">
         <v>-1</v>
@@ -10123,7 +10132,7 @@
         <v>1025105</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -10141,7 +10150,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M147" s="1">
         <v>2025105</v>
@@ -10150,7 +10159,7 @@
         <v>0</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R147" s="1">
         <v>-1</v>
@@ -10164,7 +10173,7 @@
         <v>1025106</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -10182,7 +10191,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M148" s="1">
         <v>2025106</v>
@@ -10191,7 +10200,7 @@
         <v>0</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="R148" s="1">
         <v>-1</v>
@@ -10205,7 +10214,7 @@
         <v>1025201</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -10223,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M149" s="1">
         <v>2025201</v>
@@ -10232,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="R149" s="1">
         <v>-1</v>
@@ -10246,7 +10255,7 @@
         <v>1025202</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -10264,7 +10273,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M150" s="1">
         <v>2025202</v>
@@ -10273,7 +10282,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="R150" s="1">
         <v>-1</v>
@@ -10287,7 +10296,7 @@
         <v>1025203</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -10305,7 +10314,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M151" s="1">
         <v>2025203</v>
@@ -10314,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="R151" s="1">
         <v>-1</v>
@@ -10328,7 +10337,7 @@
         <v>1025204</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -10346,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M152" s="1">
         <v>2025204</v>
@@ -10355,7 +10364,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="R152" s="1">
         <v>-1</v>
@@ -10369,7 +10378,7 @@
         <v>1025205</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -10387,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M153" s="1">
         <v>2025205</v>
@@ -10396,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="R153" s="1">
         <v>-1</v>
@@ -10410,7 +10419,7 @@
         <v>1025206</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -10428,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M154" s="1">
         <v>2025206</v>
@@ -10437,7 +10446,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="R154" s="1">
         <v>-1</v>
@@ -10451,7 +10460,7 @@
         <v>1025301</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -10469,7 +10478,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M155" s="1">
         <v>2025301</v>
@@ -10478,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="R155" s="1">
         <v>-1</v>
@@ -10492,7 +10501,7 @@
         <v>1025302</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -10510,7 +10519,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M156" s="1">
         <v>2025302</v>
@@ -10519,7 +10528,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="R156" s="1">
         <v>-1</v>
@@ -10533,7 +10542,7 @@
         <v>1025303</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -10551,7 +10560,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M157" s="1">
         <v>2025303</v>
@@ -10560,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="R157" s="1">
         <v>-1</v>
@@ -10574,7 +10583,7 @@
         <v>1025304</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -10592,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M158" s="1">
         <v>2025304</v>
@@ -10601,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="R158" s="1">
         <v>-1</v>
@@ -10615,7 +10624,7 @@
         <v>1025305</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -10633,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="M159" s="1">
         <v>2025305</v>
@@ -10642,7 +10651,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="R159" s="1">
         <v>-1</v>
@@ -10656,7 +10665,7 @@
         <v>1025306</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -10674,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M160" s="1">
         <v>2025306</v>
@@ -10683,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="R160" s="1">
         <v>-1</v>
@@ -10697,7 +10706,7 @@
         <v>1025401</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -10715,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M161" s="1">
         <v>2025401</v>
@@ -10724,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="R161" s="1">
         <v>-1</v>
@@ -10738,7 +10747,7 @@
         <v>1025402</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -10756,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M162" s="1">
         <v>2025402</v>
@@ -10765,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="R162" s="1">
         <v>-1</v>
@@ -10779,7 +10788,7 @@
         <v>1025403</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -10797,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M163" s="1">
         <v>2025403</v>
@@ -10806,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="R163" s="1">
         <v>-1</v>
@@ -10820,7 +10829,7 @@
         <v>1025404</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
@@ -10838,7 +10847,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M164" s="1">
         <v>2025404</v>
@@ -10847,7 +10856,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="R164" s="1">
         <v>-1</v>
@@ -10861,7 +10870,7 @@
         <v>1025405</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
@@ -10879,7 +10888,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M165" s="1">
         <v>2025405</v>
@@ -10888,7 +10897,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="R165" s="1">
         <v>-1</v>
@@ -10902,7 +10911,7 @@
         <v>1025406</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E166" s="1">
         <v>2</v>
@@ -10920,7 +10929,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M166" s="1">
         <v>2025406</v>
@@ -10929,7 +10938,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="R166" s="1">
         <v>-1</v>
@@ -10943,7 +10952,7 @@
         <v>1025501</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E167" s="1">
         <v>2</v>
@@ -10961,7 +10970,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M167" s="1">
         <v>2025501</v>
@@ -10970,7 +10979,7 @@
         <v>0</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="R167" s="1">
         <v>-1</v>
@@ -10984,7 +10993,7 @@
         <v>1025502</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E168" s="1">
         <v>2</v>
@@ -11002,7 +11011,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M168" s="1">
         <v>2025502</v>
@@ -11011,7 +11020,7 @@
         <v>0</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="R168" s="1">
         <v>-1</v>
@@ -11025,7 +11034,7 @@
         <v>1025503</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E169" s="1">
         <v>2</v>
@@ -11043,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M169" s="1">
         <v>2025503</v>
@@ -11052,7 +11061,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="R169" s="1">
         <v>-1</v>
@@ -11066,7 +11075,7 @@
         <v>1025504</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E170" s="1">
         <v>2</v>
@@ -11084,7 +11093,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M170" s="1">
         <v>2025504</v>
@@ -11093,7 +11102,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="R170" s="1">
         <v>-1</v>
@@ -11107,7 +11116,7 @@
         <v>1025505</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E171" s="1">
         <v>2</v>
@@ -11125,7 +11134,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M171" s="1">
         <v>2025505</v>
@@ -11134,7 +11143,7 @@
         <v>0</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="R171" s="1">
         <v>-1</v>
@@ -11148,7 +11157,7 @@
         <v>1025506</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E172" s="1">
         <v>2</v>
@@ -11166,7 +11175,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M172" s="1">
         <v>2025506</v>
@@ -11175,7 +11184,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="R172" s="1">
         <v>-1</v>
@@ -11208,7 +11217,7 @@
         <v>1</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M173" s="1">
         <v>2125101</v>
@@ -11251,7 +11260,7 @@
         <v>1</v>
       </c>
       <c r="L174" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M174" s="1">
         <v>2125102</v>
@@ -11294,7 +11303,7 @@
         <v>1</v>
       </c>
       <c r="L175" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M175" s="1">
         <v>2125103</v>
@@ -11337,7 +11346,7 @@
         <v>1</v>
       </c>
       <c r="L176" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M176" s="1">
         <v>2125104</v>
@@ -11380,7 +11389,7 @@
         <v>1</v>
       </c>
       <c r="L177" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M177" s="1">
         <v>2125105</v>
@@ -11423,7 +11432,7 @@
         <v>1</v>
       </c>
       <c r="L178" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M178" s="1">
         <v>2125106</v>
@@ -11466,7 +11475,7 @@
         <v>1</v>
       </c>
       <c r="L179" s="14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M179" s="1">
         <v>2125201</v>
@@ -11509,7 +11518,7 @@
         <v>1</v>
       </c>
       <c r="L180" s="14" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M180" s="1">
         <v>2125202</v>
@@ -11552,7 +11561,7 @@
         <v>1</v>
       </c>
       <c r="L181" s="14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M181" s="1">
         <v>2125203</v>
@@ -11595,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="L182" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M182" s="1">
         <v>2125204</v>
@@ -11638,7 +11647,7 @@
         <v>1</v>
       </c>
       <c r="L183" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M183" s="1">
         <v>2125205</v>
@@ -11681,7 +11690,7 @@
         <v>1</v>
       </c>
       <c r="L184" s="14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M184" s="1">
         <v>2125206</v>
@@ -11724,7 +11733,7 @@
         <v>1</v>
       </c>
       <c r="L185" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M185" s="1">
         <v>2125301</v>
@@ -11767,7 +11776,7 @@
         <v>1</v>
       </c>
       <c r="L186" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M186" s="1">
         <v>2125302</v>
@@ -11810,7 +11819,7 @@
         <v>1</v>
       </c>
       <c r="L187" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M187" s="1">
         <v>2125303</v>
@@ -11853,7 +11862,7 @@
         <v>1</v>
       </c>
       <c r="L188" s="14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M188" s="1">
         <v>2125304</v>
@@ -11896,7 +11905,7 @@
         <v>1</v>
       </c>
       <c r="L189" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M189" s="1">
         <v>2125305</v>
@@ -11939,7 +11948,7 @@
         <v>1</v>
       </c>
       <c r="L190" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M190" s="1">
         <v>2125306</v>
@@ -11982,7 +11991,7 @@
         <v>1</v>
       </c>
       <c r="L191" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M191" s="1">
         <v>2125401</v>
@@ -12025,7 +12034,7 @@
         <v>1</v>
       </c>
       <c r="L192" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M192" s="1">
         <v>2125402</v>
@@ -12068,7 +12077,7 @@
         <v>1</v>
       </c>
       <c r="L193" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M193" s="1">
         <v>2125403</v>
@@ -12111,7 +12120,7 @@
         <v>1</v>
       </c>
       <c r="L194" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M194" s="1">
         <v>2125404</v>
@@ -12154,7 +12163,7 @@
         <v>1</v>
       </c>
       <c r="L195" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M195" s="1">
         <v>2125405</v>
@@ -12197,7 +12206,7 @@
         <v>1</v>
       </c>
       <c r="L196" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M196" s="1">
         <v>2125406</v>
@@ -12240,7 +12249,7 @@
         <v>1</v>
       </c>
       <c r="L197" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M197" s="1">
         <v>2125501</v>
@@ -12283,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="L198" s="14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M198" s="1">
         <v>2125502</v>
@@ -12326,7 +12335,7 @@
         <v>1</v>
       </c>
       <c r="L199" s="14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M199" s="1">
         <v>2125503</v>
@@ -12369,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="L200" s="14" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="M200" s="1">
         <v>2125504</v>
@@ -12412,7 +12421,7 @@
         <v>1</v>
       </c>
       <c r="L201" s="14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M201" s="1">
         <v>2125505</v>
@@ -12455,7 +12464,7 @@
         <v>1</v>
       </c>
       <c r="L202" s="14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M202" s="1">
         <v>2125506</v>
@@ -12479,7 +12488,7 @@
         <v>1026001</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E203" s="1">
         <v>2</v>
@@ -12497,7 +12506,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M203" s="1">
         <v>2026001</v>
@@ -12506,7 +12515,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="R203" s="1">
         <v>-1</v>
@@ -12520,7 +12529,7 @@
         <v>1026002</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E204" s="1">
         <v>2</v>
@@ -12538,7 +12547,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M204" s="1">
         <v>2026002</v>
@@ -12547,7 +12556,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="R204" s="1">
         <v>-1</v>
@@ -12561,7 +12570,7 @@
         <v>1026101</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E205" s="1">
         <v>2</v>
@@ -12579,7 +12588,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M205" s="1">
         <v>2026101</v>
@@ -12588,7 +12597,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="R205" s="1">
         <v>-1</v>
@@ -12602,7 +12611,7 @@
         <v>1026102</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -12620,7 +12629,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M206" s="1">
         <v>2026102</v>
@@ -12629,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="R206" s="1">
         <v>-1</v>
@@ -12643,7 +12652,7 @@
         <v>1026201</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -12661,7 +12670,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M207" s="1">
         <v>2026201</v>
@@ -12670,7 +12679,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="R207" s="1">
         <v>-1</v>
@@ -12684,7 +12693,7 @@
         <v>1026202</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -12702,7 +12711,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M208" s="1">
         <v>2026202</v>
@@ -12711,7 +12720,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="R208" s="1">
         <v>-1</v>
@@ -12725,7 +12734,7 @@
         <v>1026301</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -12743,7 +12752,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M209" s="1">
         <v>2026301</v>
@@ -12752,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="R209" s="1">
         <v>-1</v>
@@ -12766,7 +12775,7 @@
         <v>1026302</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -12784,7 +12793,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M210" s="1">
         <v>2026302</v>
@@ -12793,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="R210" s="1">
         <v>-1</v>
@@ -12807,7 +12816,7 @@
         <v>1026401</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -12825,7 +12834,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M211" s="1">
         <v>2026401</v>
@@ -12834,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="R211" s="1">
         <v>-1</v>
@@ -12848,7 +12857,7 @@
         <v>1026402</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -12866,7 +12875,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M212" s="1">
         <v>2026402</v>
@@ -12875,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="R212" s="1">
         <v>-1</v>
@@ -12889,7 +12898,7 @@
         <v>1027001</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -12907,7 +12916,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M213" s="1">
         <v>2027001</v>
@@ -12916,7 +12925,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="R213" s="1">
         <v>-1</v>
@@ -12930,7 +12939,7 @@
         <v>1027002</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -12948,7 +12957,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M214" s="1">
         <v>2027002</v>
@@ -12957,7 +12966,7 @@
         <v>0</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="R214" s="1">
         <v>-1</v>
@@ -12971,7 +12980,7 @@
         <v>1027101</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -12989,7 +12998,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M215" s="1">
         <v>2027101</v>
@@ -12998,7 +13007,7 @@
         <v>0</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="R215" s="1">
         <v>-1</v>
@@ -13012,7 +13021,7 @@
         <v>1027102</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -13030,7 +13039,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M216" s="1">
         <v>2027102</v>
@@ -13039,7 +13048,7 @@
         <v>0</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="R216" s="1">
         <v>-1</v>
@@ -13053,7 +13062,7 @@
         <v>1027201</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -13071,7 +13080,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M217" s="1">
         <v>2027201</v>
@@ -13080,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="R217" s="1">
         <v>-1</v>
@@ -13094,7 +13103,7 @@
         <v>1027202</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -13112,7 +13121,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M218" s="1">
         <v>2027202</v>
@@ -13121,7 +13130,7 @@
         <v>0</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="R218" s="1">
         <v>-1</v>
@@ -13135,7 +13144,7 @@
         <v>1027301</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -13153,7 +13162,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M219" s="1">
         <v>2027301</v>
@@ -13162,7 +13171,7 @@
         <v>0</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="R219" s="1">
         <v>-1</v>
@@ -13176,7 +13185,7 @@
         <v>1027302</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -13194,7 +13203,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M220" s="1">
         <v>2027302</v>
@@ -13203,7 +13212,7 @@
         <v>0</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="R220" s="1">
         <v>-1</v>
@@ -13217,7 +13226,7 @@
         <v>1027401</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -13235,7 +13244,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M221" s="1">
         <v>2027401</v>
@@ -13244,7 +13253,7 @@
         <v>0</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="R221" s="1">
         <v>-1</v>
@@ -13258,7 +13267,7 @@
         <v>1027402</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -13276,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M222" s="1">
         <v>2027402</v>
@@ -13285,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="R222" s="1">
         <v>-1</v>
@@ -13299,7 +13308,7 @@
         <v>1028001</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -13317,7 +13326,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M223" s="1">
         <v>2028001</v>
@@ -13326,7 +13335,7 @@
         <v>0</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="R223" s="1">
         <v>-1</v>
@@ -13340,7 +13349,7 @@
         <v>1028002</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -13358,7 +13367,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M224" s="1">
         <v>2028002</v>
@@ -13367,7 +13376,7 @@
         <v>0</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R224" s="1">
         <v>-1</v>
@@ -13381,7 +13390,7 @@
         <v>1028101</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -13399,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M225" s="1">
         <v>2028101</v>
@@ -13408,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="R225" s="1">
         <v>-1</v>
@@ -13422,7 +13431,7 @@
         <v>1028102</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E226" s="1">
         <v>2</v>
@@ -13440,7 +13449,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M226" s="1">
         <v>2028102</v>
@@ -13449,7 +13458,7 @@
         <v>0</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="R226" s="1">
         <v>-1</v>
@@ -13463,7 +13472,7 @@
         <v>1028201</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
@@ -13481,7 +13490,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M227" s="1">
         <v>2028201</v>
@@ -13490,7 +13499,7 @@
         <v>0</v>
       </c>
       <c r="O227" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="R227" s="1">
         <v>-1</v>
@@ -13504,7 +13513,7 @@
         <v>1028202</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
@@ -13522,7 +13531,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M228" s="1">
         <v>2028202</v>
@@ -13531,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="O228" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="R228" s="1">
         <v>-1</v>
@@ -13545,7 +13554,7 @@
         <v>1028301</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
@@ -13563,7 +13572,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M229" s="1">
         <v>2028301</v>
@@ -13572,7 +13581,7 @@
         <v>0</v>
       </c>
       <c r="O229" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="R229" s="1">
         <v>-1</v>
@@ -13586,7 +13595,7 @@
         <v>1028302</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
@@ -13604,7 +13613,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M230" s="1">
         <v>2028302</v>
@@ -13613,7 +13622,7 @@
         <v>0</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="R230" s="1">
         <v>-1</v>
@@ -13627,7 +13636,7 @@
         <v>1028401</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
@@ -13645,7 +13654,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M231" s="1">
         <v>2028401</v>
@@ -13654,7 +13663,7 @@
         <v>0</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="R231" s="1">
         <v>-1</v>
@@ -13668,7 +13677,7 @@
         <v>1028402</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
@@ -13686,7 +13695,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M232" s="1">
         <v>2028402</v>
@@ -13695,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="R232" s="1">
         <v>-1</v>
@@ -13728,7 +13737,7 @@
         <v>1</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M233" s="1">
         <v>2126001</v>
@@ -13771,7 +13780,7 @@
         <v>1</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M234" s="1">
         <v>2126002</v>
@@ -13814,7 +13823,7 @@
         <v>1</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M235" s="1">
         <v>2126101</v>
@@ -13857,7 +13866,7 @@
         <v>1</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M236" s="1">
         <v>2126102</v>
@@ -13900,7 +13909,7 @@
         <v>1</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M237" s="1">
         <v>2126201</v>
@@ -13943,7 +13952,7 @@
         <v>1</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M238" s="1">
         <v>2126202</v>
@@ -13986,7 +13995,7 @@
         <v>1</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M239" s="1">
         <v>2126301</v>
@@ -14029,7 +14038,7 @@
         <v>1</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M240" s="1">
         <v>2126302</v>
@@ -14072,7 +14081,7 @@
         <v>1</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M241" s="1">
         <v>2126401</v>
@@ -14115,7 +14124,7 @@
         <v>1</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M242" s="1">
         <v>2126402</v>
@@ -14158,7 +14167,7 @@
         <v>1</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M243" s="1">
         <v>2127001</v>
@@ -14201,7 +14210,7 @@
         <v>1</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M244" s="1">
         <v>2127002</v>
@@ -14244,7 +14253,7 @@
         <v>1</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M245" s="1">
         <v>2127101</v>
@@ -14287,7 +14296,7 @@
         <v>1</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M246" s="1">
         <v>2127102</v>
@@ -14330,7 +14339,7 @@
         <v>1</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M247" s="1">
         <v>2127201</v>
@@ -14373,7 +14382,7 @@
         <v>1</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M248" s="1">
         <v>2127202</v>
@@ -14416,7 +14425,7 @@
         <v>1</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M249" s="1">
         <v>2127301</v>
@@ -14459,7 +14468,7 @@
         <v>1</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M250" s="1">
         <v>2127302</v>
@@ -14502,7 +14511,7 @@
         <v>1</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M251" s="1">
         <v>2127401</v>
@@ -14545,7 +14554,7 @@
         <v>1</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M252" s="1">
         <v>2127402</v>
@@ -14588,7 +14597,7 @@
         <v>1</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M253" s="1">
         <v>2128001</v>
@@ -14631,7 +14640,7 @@
         <v>1</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M254" s="1">
         <v>2128002</v>
@@ -14674,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M255" s="1">
         <v>2128101</v>
@@ -14717,7 +14726,7 @@
         <v>1</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M256" s="1">
         <v>2128102</v>
@@ -14760,7 +14769,7 @@
         <v>1</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M257" s="1">
         <v>2128201</v>
@@ -14803,7 +14812,7 @@
         <v>1</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M258" s="1">
         <v>2128202</v>
@@ -14846,7 +14855,7 @@
         <v>1</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M259" s="1">
         <v>2128301</v>
@@ -14889,7 +14898,7 @@
         <v>1</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M260" s="1">
         <v>2128302</v>
@@ -14932,7 +14941,7 @@
         <v>1</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M261" s="1">
         <v>2128401</v>
@@ -14975,7 +14984,7 @@
         <v>1</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M262" s="1">
         <v>2128402</v>
@@ -14999,7 +15008,7 @@
         <v>1130001</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -15017,7 +15026,7 @@
         <v>1</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M263" s="1">
         <v>2130001</v>
@@ -15026,7 +15035,7 @@
         <v>0</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="R263" s="1">
         <v>999999</v>
@@ -15040,7 +15049,7 @@
         <v>1130002</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E264" s="1">
         <v>1</v>
@@ -15058,7 +15067,7 @@
         <v>1</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M264" s="1">
         <v>2130002</v>
@@ -15067,13 +15076,13 @@
         <v>0</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="R264" s="1">
         <v>999999</v>
       </c>
       <c r="T264" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="265" spans="1:20">
@@ -15084,7 +15093,7 @@
         <v>1130003</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E265" s="1">
         <v>1</v>
@@ -15102,7 +15111,7 @@
         <v>1</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M265" s="1">
         <v>2130003</v>
@@ -15111,13 +15120,13 @@
         <v>0</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R265" s="1">
         <v>999999</v>
       </c>
       <c r="T265" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="266" spans="1:20">
@@ -15128,7 +15137,7 @@
         <v>1130004</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E266" s="1">
         <v>1</v>
@@ -15146,7 +15155,7 @@
         <v>1</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M266" s="1">
         <v>2130004</v>
@@ -15155,13 +15164,13 @@
         <v>0</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="R266" s="1">
         <v>999999</v>
       </c>
       <c r="T266" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="267" spans="1:20">
@@ -15172,7 +15181,7 @@
         <v>1130005</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E267" s="1">
         <v>1</v>
@@ -15190,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M267" s="1">
         <v>2130005</v>
@@ -15199,13 +15208,13 @@
         <v>0</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="R267" s="1">
         <v>999999</v>
       </c>
       <c r="T267" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="268" spans="1:20">
@@ -15216,7 +15225,7 @@
         <v>1130006</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E268" s="1">
         <v>1</v>
@@ -15234,7 +15243,7 @@
         <v>1</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M268" s="1">
         <v>2130006</v>
@@ -15243,13 +15252,13 @@
         <v>0</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="R268" s="1">
         <v>999999</v>
       </c>
       <c r="T268" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="269" spans="1:20">
@@ -15260,7 +15269,7 @@
         <v>1131001</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -15278,7 +15287,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M269" s="1">
         <v>2131001</v>
@@ -15287,7 +15296,7 @@
         <v>0</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="R269" s="1">
         <v>999999</v>
@@ -15301,7 +15310,7 @@
         <v>1131002</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -15319,7 +15328,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M270" s="1">
         <v>2131002</v>
@@ -15328,7 +15337,7 @@
         <v>0</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="R270" s="1">
         <v>999999</v>
@@ -15342,7 +15351,7 @@
         <v>1131003</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -15360,7 +15369,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M271" s="1">
         <v>2131003</v>
@@ -15369,7 +15378,7 @@
         <v>0</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="R271" s="1">
         <v>999999</v>
@@ -15383,7 +15392,7 @@
         <v>1131004</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -15401,7 +15410,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M272" s="1">
         <v>2131004</v>
@@ -15410,7 +15419,7 @@
         <v>0</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="R272" s="1">
         <v>999999</v>
@@ -15424,7 +15433,7 @@
         <v>1131005</v>
       </c>
       <c r="D273" s="15" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -15442,7 +15451,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M273" s="1">
         <v>2131005</v>
@@ -15451,7 +15460,7 @@
         <v>0</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="R273" s="1">
         <v>999999</v>
@@ -15465,7 +15474,7 @@
         <v>1131006</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -15483,7 +15492,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M274" s="1">
         <v>2131006</v>
@@ -15492,7 +15501,7 @@
         <v>0</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="R274" s="1">
         <v>999999</v>
@@ -15506,7 +15515,7 @@
         <v>1131101</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -15524,16 +15533,16 @@
         <v>0</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M275" s="1">
-        <v>2131101</v>
+        <v>2131001</v>
       </c>
       <c r="N275" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="R275" s="1">
         <v>999999</v>
@@ -15547,7 +15556,7 @@
         <v>1131102</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -15565,16 +15574,16 @@
         <v>0</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M276" s="1">
-        <v>2131102</v>
+        <v>2131002</v>
       </c>
       <c r="N276" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="R276" s="1">
         <v>999999</v>
@@ -15588,7 +15597,7 @@
         <v>1131103</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -15606,16 +15615,16 @@
         <v>0</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M277" s="1">
-        <v>2131103</v>
+        <v>2131003</v>
       </c>
       <c r="N277" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="R277" s="1">
         <v>999999</v>
@@ -15629,7 +15638,7 @@
         <v>1131104</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -15647,16 +15656,16 @@
         <v>0</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M278" s="1">
-        <v>2131104</v>
+        <v>2131004</v>
       </c>
       <c r="N278" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="R278" s="1">
         <v>999999</v>
@@ -15670,7 +15679,7 @@
         <v>1131105</v>
       </c>
       <c r="D279" s="15" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -15688,16 +15697,16 @@
         <v>0</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M279" s="1">
-        <v>2131105</v>
+        <v>2131005</v>
       </c>
       <c r="N279" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="R279" s="1">
         <v>999999</v>
@@ -15711,7 +15720,7 @@
         <v>1131106</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -15729,16 +15738,16 @@
         <v>0</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="M280" s="1">
-        <v>2131106</v>
+        <v>2131006</v>
       </c>
       <c r="N280" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="R280" s="1">
         <v>999999</v>
@@ -15752,7 +15761,7 @@
         <v>1131201</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15770,16 +15779,16 @@
         <v>0</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M281" s="1">
-        <v>2131201</v>
+        <v>2131001</v>
       </c>
       <c r="N281" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="R281" s="1">
         <v>999999</v>
@@ -15793,7 +15802,7 @@
         <v>1131202</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15811,16 +15820,16 @@
         <v>0</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="M282" s="1">
-        <v>2131202</v>
+        <v>2131002</v>
       </c>
       <c r="N282" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="R282" s="1">
         <v>999999</v>
@@ -15834,7 +15843,7 @@
         <v>1131203</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15852,16 +15861,16 @@
         <v>0</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M283" s="1">
-        <v>2131203</v>
+        <v>2131003</v>
       </c>
       <c r="N283" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="R283" s="1">
         <v>999999</v>
@@ -15875,7 +15884,7 @@
         <v>1131204</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15893,16 +15902,16 @@
         <v>0</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="M284" s="1">
-        <v>2131204</v>
+        <v>2131004</v>
       </c>
       <c r="N284" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="R284" s="1">
         <v>999999</v>
@@ -15916,7 +15925,7 @@
         <v>1131205</v>
       </c>
       <c r="D285" s="15" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15934,16 +15943,16 @@
         <v>0</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M285" s="1">
-        <v>2131205</v>
+        <v>2131005</v>
       </c>
       <c r="N285" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="R285" s="1">
         <v>999999</v>
@@ -15957,7 +15966,7 @@
         <v>1131206</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15975,16 +15984,16 @@
         <v>0</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M286" s="1">
-        <v>2131206</v>
+        <v>2131006</v>
       </c>
       <c r="N286" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="R286" s="1">
         <v>999999</v>
@@ -15998,7 +16007,7 @@
         <v>1131301</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -16016,16 +16025,16 @@
         <v>0</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="M287" s="1">
-        <v>2131301</v>
+        <v>2131001</v>
       </c>
       <c r="N287" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="R287" s="1">
         <v>999999</v>
@@ -16039,7 +16048,7 @@
         <v>1131302</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -16057,16 +16066,16 @@
         <v>0</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M288" s="1">
-        <v>2131302</v>
+        <v>2131002</v>
       </c>
       <c r="N288" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="R288" s="1">
         <v>999999</v>
@@ -16080,7 +16089,7 @@
         <v>1131303</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -16098,16 +16107,16 @@
         <v>0</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M289" s="1">
-        <v>2131303</v>
+        <v>2131003</v>
       </c>
       <c r="N289" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="R289" s="1">
         <v>999999</v>
@@ -16121,7 +16130,7 @@
         <v>1131304</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -16139,16 +16148,16 @@
         <v>0</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M290" s="1">
-        <v>2131304</v>
+        <v>2131004</v>
       </c>
       <c r="N290" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="R290" s="1">
         <v>999999</v>
@@ -16162,7 +16171,7 @@
         <v>1131305</v>
       </c>
       <c r="D291" s="15" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -16180,16 +16189,16 @@
         <v>0</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M291" s="1">
-        <v>2131305</v>
+        <v>2131005</v>
       </c>
       <c r="N291" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="R291" s="1">
         <v>999999</v>
@@ -16203,7 +16212,7 @@
         <v>1131306</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -16221,16 +16230,16 @@
         <v>0</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="M292" s="1">
-        <v>2131306</v>
+        <v>2131006</v>
       </c>
       <c r="N292" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="R292" s="1">
         <v>999999</v>
@@ -16244,7 +16253,7 @@
         <v>1131401</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -16262,16 +16271,16 @@
         <v>0</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M293" s="1">
-        <v>2131401</v>
+        <v>2131001</v>
       </c>
       <c r="N293" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="R293" s="1">
         <v>999999</v>
@@ -16285,7 +16294,7 @@
         <v>1131402</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -16303,16 +16312,16 @@
         <v>0</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="M294" s="1">
-        <v>2131402</v>
+        <v>2131002</v>
       </c>
       <c r="N294" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="R294" s="1">
         <v>999999</v>
@@ -16326,7 +16335,7 @@
         <v>1131403</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -16344,16 +16353,16 @@
         <v>0</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="M295" s="1">
-        <v>2131403</v>
+        <v>2131003</v>
       </c>
       <c r="N295" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="R295" s="1">
         <v>999999</v>
@@ -16367,7 +16376,7 @@
         <v>1131404</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -16385,16 +16394,16 @@
         <v>0</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="M296" s="1">
-        <v>2131404</v>
+        <v>2131004</v>
       </c>
       <c r="N296" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="R296" s="1">
         <v>999999</v>
@@ -16408,7 +16417,7 @@
         <v>1131405</v>
       </c>
       <c r="D297" s="15" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -16426,16 +16435,16 @@
         <v>0</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M297" s="1">
-        <v>2131405</v>
+        <v>2131005</v>
       </c>
       <c r="N297" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="R297" s="1">
         <v>999999</v>
@@ -16449,7 +16458,7 @@
         <v>1131406</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -16467,16 +16476,16 @@
         <v>0</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="M298" s="1">
-        <v>2131406</v>
+        <v>2131006</v>
       </c>
       <c r="N298" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="R298" s="1">
         <v>999999</v>
@@ -16490,7 +16499,7 @@
         <v>1140001</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -16508,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="M299" s="1">
         <v>2140001</v>
@@ -16517,7 +16526,7 @@
         <v>0</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="R299" s="1">
         <v>1</v>
@@ -16531,7 +16540,7 @@
         <v>1140002</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -16549,7 +16558,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M300" s="1">
         <v>2140002</v>
@@ -16558,7 +16567,7 @@
         <v>0</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="R300" s="1">
         <v>1</v>
@@ -16572,7 +16581,7 @@
         <v>1140003</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -16590,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M301" s="1">
         <v>2140003</v>
@@ -16599,7 +16608,7 @@
         <v>0</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="R301" s="1">
         <v>1</v>
@@ -16613,7 +16622,7 @@
         <v>1140004</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -16631,7 +16640,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="M302" s="1">
         <v>2140004</v>
@@ -16640,7 +16649,7 @@
         <v>0</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R302" s="1">
         <v>1</v>
@@ -16654,7 +16663,7 @@
         <v>1140005</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -16672,7 +16681,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M303" s="1">
         <v>2140005</v>
@@ -16681,7 +16690,7 @@
         <v>0</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="R303" s="1">
         <v>1</v>
@@ -16695,7 +16704,7 @@
         <v>1140006</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -16713,7 +16722,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M304" s="1">
         <v>2140006</v>
@@ -16722,7 +16731,7 @@
         <v>0</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="R304" s="1">
         <v>1</v>
@@ -16736,7 +16745,7 @@
         <v>1150001</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -16754,7 +16763,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M305" s="1">
         <v>2150001</v>
@@ -16778,7 +16787,7 @@
         <v>1150002</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -16796,7 +16805,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M306" s="1">
         <v>2150002</v>
@@ -16820,7 +16829,7 @@
         <v>1150003</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -16838,7 +16847,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="M307" s="1">
         <v>2150003</v>
@@ -16862,7 +16871,7 @@
         <v>1150004</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16880,7 +16889,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M308" s="1">
         <v>2150004</v>
@@ -16904,7 +16913,7 @@
         <v>1150005</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16922,7 +16931,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="M309" s="1">
         <v>2150005</v>
@@ -16946,7 +16955,7 @@
         <v>1150006</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16964,7 +16973,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="M310" s="1">
         <v>2150006</v>
@@ -16988,7 +16997,7 @@
         <v>1150007</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -17006,7 +17015,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="M311" s="1">
         <v>2150007</v>
@@ -17030,7 +17039,7 @@
         <v>1150008</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -17048,7 +17057,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M312" s="1">
         <v>2150008</v>
@@ -17072,7 +17081,7 @@
         <v>1150009</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -17090,7 +17099,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="M313" s="1">
         <v>2150009</v>
@@ -17114,7 +17123,7 @@
         <v>1150010</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -17132,7 +17141,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M314" s="1">
         <v>2150010</v>
@@ -17156,7 +17165,7 @@
         <v>1150011</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -17174,7 +17183,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="M315" s="1">
         <v>2150011</v>
@@ -17198,7 +17207,7 @@
         <v>1150012</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -17216,7 +17225,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="M316" s="1">
         <v>2150012</v>
@@ -17240,7 +17249,7 @@
         <v>1150013</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -17258,7 +17267,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="M317" s="1">
         <v>2150013</v>
@@ -17282,7 +17291,7 @@
         <v>1150014</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -17300,7 +17309,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M318" s="1">
         <v>2150014</v>
@@ -17324,7 +17333,7 @@
         <v>1150015</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -17342,7 +17351,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M319" s="1">
         <v>2150015</v>
@@ -17366,7 +17375,7 @@
         <v>1150016</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -17384,7 +17393,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="M320" s="1">
         <v>2150016</v>
@@ -17408,7 +17417,7 @@
         <v>1150017</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -17426,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M321" s="1">
         <v>2150017</v>
@@ -17450,7 +17459,7 @@
         <v>1150018</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -17468,7 +17477,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="M322" s="1">
         <v>2150018</v>
@@ -17492,7 +17501,7 @@
         <v>1150019</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -17510,7 +17519,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M323" s="1">
         <v>2150019</v>
@@ -17534,7 +17543,7 @@
         <v>1150020</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -17552,7 +17561,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="M324" s="1">
         <v>2150020</v>
@@ -17576,7 +17585,7 @@
         <v>1150021</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -17594,7 +17603,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="M325" s="1">
         <v>2150021</v>
@@ -17618,7 +17627,7 @@
         <v>1150022</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -17636,7 +17645,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="M326" s="1">
         <v>2150022</v>
@@ -17660,7 +17669,7 @@
         <v>1150023</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -17678,7 +17687,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M327" s="1">
         <v>2150023</v>
@@ -17702,7 +17711,7 @@
         <v>1150024</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -17720,7 +17729,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="M328" s="1">
         <v>2150024</v>
@@ -17744,7 +17753,7 @@
         <v>1150025</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -17762,7 +17771,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="M329" s="1">
         <v>2150025</v>
@@ -17786,7 +17795,7 @@
         <v>1150026</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -17804,7 +17813,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="M330" s="1">
         <v>2150026</v>
@@ -17828,7 +17837,7 @@
         <v>1150027</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17846,7 +17855,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="M331" s="1">
         <v>2150027</v>
@@ -17870,7 +17879,7 @@
         <v>1150028</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17888,7 +17897,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M332" s="1">
         <v>2150028</v>
@@ -17912,7 +17921,7 @@
         <v>1150029</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17930,7 +17939,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="M333" s="1">
         <v>2150029</v>
@@ -17954,7 +17963,7 @@
         <v>1150030</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -17972,7 +17981,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M334" s="1">
         <v>2150030</v>
@@ -17996,7 +18005,7 @@
         <v>1150031</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -18014,7 +18023,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="M335" s="1">
         <v>2150031</v>
@@ -18038,7 +18047,7 @@
         <v>1150032</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -18056,7 +18065,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="M336" s="1">
         <v>2150032</v>
@@ -18080,7 +18089,7 @@
         <v>1150033</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -18098,7 +18107,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="M337" s="1">
         <v>2150033</v>
@@ -18122,7 +18131,7 @@
         <v>1150034</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -18140,7 +18149,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="M338" s="1">
         <v>2150034</v>
@@ -18164,7 +18173,7 @@
         <v>1150035</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -18182,7 +18191,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M339" s="1">
         <v>2150035</v>
@@ -18206,7 +18215,7 @@
         <v>1150036</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -18224,7 +18233,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M340" s="1">
         <v>2150036</v>
@@ -18248,7 +18257,7 @@
         <v>1150037</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -18266,7 +18275,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="M341" s="1">
         <v>2150037</v>
@@ -18290,7 +18299,7 @@
         <v>1150038</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -18308,7 +18317,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="M342" s="1">
         <v>2150038</v>
@@ -18332,7 +18341,7 @@
         <v>1150039</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -18350,7 +18359,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="M343" s="1">
         <v>2150039</v>
@@ -18374,7 +18383,7 @@
         <v>1150040</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -18392,7 +18401,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="M344" s="1">
         <v>2150040</v>
@@ -18416,7 +18425,7 @@
         <v>1150041</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -18434,7 +18443,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="M345" s="1">
         <v>2150041</v>
@@ -18458,7 +18467,7 @@
         <v>1150042</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -18476,7 +18485,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="M346" s="1">
         <v>2150042</v>
@@ -18500,7 +18509,7 @@
         <v>1150043</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -18518,7 +18527,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="M347" s="1">
         <v>2150043</v>
@@ -18542,7 +18551,7 @@
         <v>1150044</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -18560,7 +18569,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="M348" s="1">
         <v>2150044</v>
@@ -18584,7 +18593,7 @@
         <v>1150045</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -18602,7 +18611,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="M349" s="1">
         <v>2150045</v>
@@ -18626,7 +18635,7 @@
         <v>1150046</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -18644,7 +18653,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="M350" s="1">
         <v>2150046</v>
@@ -18668,7 +18677,7 @@
         <v>1150047</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -18686,7 +18695,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="M351" s="1">
         <v>2150047</v>
@@ -18710,7 +18719,7 @@
         <v>1150048</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -18728,7 +18737,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="M352" s="1">
         <v>2150048</v>
@@ -18752,7 +18761,7 @@
         <v>1150049</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -18770,7 +18779,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="M353" s="1">
         <v>2150049</v>
@@ -18794,7 +18803,7 @@
         <v>1150050</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -18812,7 +18821,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="M354" s="1">
         <v>2150050</v>
@@ -18836,7 +18845,7 @@
         <v>1150051</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18854,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="M355" s="1">
         <v>2150051</v>
@@ -18878,7 +18887,7 @@
         <v>1150052</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18896,7 +18905,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="M356" s="1">
         <v>2150052</v>
@@ -18920,7 +18929,7 @@
         <v>1150053</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18938,7 +18947,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="M357" s="1">
         <v>2150053</v>
@@ -18962,7 +18971,7 @@
         <v>1150054</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -18980,7 +18989,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="M358" s="1">
         <v>2150054</v>
@@ -19004,7 +19013,7 @@
         <v>1150055</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E359" s="1">
         <v>2</v>
@@ -19022,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="M359" s="1">
         <v>2150055</v>
@@ -19046,7 +19055,7 @@
         <v>1150056</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E360" s="1">
         <v>2</v>
@@ -19064,7 +19073,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="M360" s="1">
         <v>2150056</v>
@@ -19088,7 +19097,7 @@
         <v>1150057</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E361" s="1">
         <v>2</v>
@@ -19106,7 +19115,7 @@
         <v>0</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="M361" s="1">
         <v>2150057</v>
@@ -19130,7 +19139,7 @@
         <v>1150058</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E362" s="1">
         <v>2</v>
@@ -19148,7 +19157,7 @@
         <v>0</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="M362" s="1">
         <v>2150058</v>
@@ -19172,7 +19181,7 @@
         <v>1150059</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E363" s="1">
         <v>2</v>
@@ -19190,7 +19199,7 @@
         <v>0</v>
       </c>
       <c r="L363" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="M363" s="1">
         <v>2150059</v>
@@ -19214,7 +19223,7 @@
         <v>1150060</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E364" s="1">
         <v>2</v>
@@ -19232,7 +19241,7 @@
         <v>0</v>
       </c>
       <c r="L364" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="M364" s="1">
         <v>2150060</v>
@@ -19256,7 +19265,7 @@
         <v>1150061</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="E365" s="1">
         <v>2</v>
@@ -19274,7 +19283,7 @@
         <v>0</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="M365" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="693">
   <si>
     <t>道具ID</t>
   </si>
@@ -1141,34 +1141,52 @@
     <t>镐</t>
   </si>
   <si>
+    <t>wk_yx_xx_2.png</t>
+  </si>
+  <si>
     <t>挖矿小游戏的基础挖掘道具</t>
   </si>
   <si>
     <t>炸弹</t>
   </si>
   <si>
+    <t>wk_yx_xx_1.png</t>
+  </si>
+  <si>
     <t>挖矿小游戏的特殊挖掘道具，可挖掘一横排；</t>
   </si>
   <si>
     <t>挖机</t>
   </si>
   <si>
+    <t>wk_yx_xx_3.png</t>
+  </si>
+  <si>
     <t>挖矿小游戏的特殊挖掘道具，可挖掘3*3范围的格子</t>
   </si>
   <si>
     <t>铜矿</t>
   </si>
   <si>
+    <t>wk_yx_tk.png</t>
+  </si>
+  <si>
     <t>挖矿小游戏中的低价值矿石，可在兑换商店中兑换道具</t>
   </si>
   <si>
     <t>银矿</t>
   </si>
   <si>
+    <t>wk_yx_yk.png</t>
+  </si>
+  <si>
     <t>挖矿小游戏中的中价值矿石，可在兑换商店中兑换道具</t>
   </si>
   <si>
     <t>金矿</t>
+  </si>
+  <si>
+    <t>wk_yx_jk.png</t>
   </si>
   <si>
     <t>挖矿小游戏中的高价值矿石，可在兑换商店中兑换道具</t>
@@ -7901,6 +7919,9 @@
       <c r="K94" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L94" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="M94" s="1">
         <v>2024034</v>
       </c>
@@ -7908,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R94" s="1">
         <v>999999</v>
@@ -7922,7 +7943,7 @@
         <v>1024026</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -7938,6 +7959,9 @@
       </c>
       <c r="K95" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="M95" s="1">
         <v>2024035</v>
@@ -7946,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="R95" s="1">
         <v>999999</v>
@@ -7960,7 +7984,7 @@
         <v>1024027</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -7976,6 +8000,9 @@
       </c>
       <c r="K96" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="M96" s="1">
         <v>2024036</v>
@@ -7984,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="R96" s="1">
         <v>999999</v>
@@ -7998,7 +8025,7 @@
         <v>1024028</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -8014,6 +8041,9 @@
       </c>
       <c r="K97" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L97" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="M97" s="1">
         <v>2024037</v>
@@ -8022,7 +8052,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="R97" s="1">
         <v>999999</v>
@@ -8036,7 +8066,7 @@
         <v>1024029</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -8052,6 +8082,9 @@
       </c>
       <c r="K98" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="M98" s="1">
         <v>2024038</v>
@@ -8060,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="R98" s="1">
         <v>999999</v>
@@ -8074,7 +8107,7 @@
         <v>1024030</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -8090,6 +8123,9 @@
       </c>
       <c r="K99" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="M99" s="1">
         <v>2024039</v>
@@ -8098,7 +8134,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="R99" s="1">
         <v>999999</v>
@@ -8136,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="M100" s="1">
         <v>2024040</v>
@@ -8145,7 +8181,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="R100" s="1">
         <v>999999</v>
@@ -8191,7 +8227,7 @@
         <v>999999</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -8234,7 +8270,7 @@
         <v>999999</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -8277,7 +8313,7 @@
         <v>999999</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -8320,7 +8356,7 @@
         <v>999999</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -8363,7 +8399,7 @@
         <v>999999</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -8406,7 +8442,7 @@
         <v>999999</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -8449,7 +8485,7 @@
         <v>999999</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -8492,7 +8528,7 @@
         <v>999999</v>
       </c>
       <c r="S108" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -8535,7 +8571,7 @@
         <v>999999</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -8578,7 +8614,7 @@
         <v>999999</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -8621,7 +8657,7 @@
         <v>999999</v>
       </c>
       <c r="S111" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -8664,7 +8700,7 @@
         <v>999999</v>
       </c>
       <c r="S112" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -8707,7 +8743,7 @@
         <v>999999</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -8750,7 +8786,7 @@
         <v>999999</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -8793,7 +8829,7 @@
         <v>999999</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -8836,7 +8872,7 @@
         <v>999999</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -8879,7 +8915,7 @@
         <v>999999</v>
       </c>
       <c r="S117" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -8922,7 +8958,7 @@
         <v>999999</v>
       </c>
       <c r="S118" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -8965,7 +9001,7 @@
         <v>999999</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -9008,7 +9044,7 @@
         <v>999999</v>
       </c>
       <c r="S120" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -9051,7 +9087,7 @@
         <v>999999</v>
       </c>
       <c r="S121" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -9094,7 +9130,7 @@
         <v>999999</v>
       </c>
       <c r="S122" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -9137,7 +9173,7 @@
         <v>999999</v>
       </c>
       <c r="S123" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -9180,7 +9216,7 @@
         <v>999999</v>
       </c>
       <c r="S124" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -9223,7 +9259,7 @@
         <v>999999</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -9266,7 +9302,7 @@
         <v>999999</v>
       </c>
       <c r="S126" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -9309,7 +9345,7 @@
         <v>999999</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -9352,7 +9388,7 @@
         <v>999999</v>
       </c>
       <c r="S128" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -9395,7 +9431,7 @@
         <v>999999</v>
       </c>
       <c r="S129" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -9438,7 +9474,7 @@
         <v>999999</v>
       </c>
       <c r="S130" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -9449,7 +9485,7 @@
         <v>1024061</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
@@ -9473,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="R131" s="1">
         <v>999999</v>
@@ -9487,7 +9523,7 @@
         <v>1024062</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -9511,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="R132" s="1">
         <v>999999</v>
@@ -9525,7 +9561,7 @@
         <v>1024063</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -9549,7 +9585,7 @@
         <v>0</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="R133" s="1">
         <v>999999</v>
@@ -9563,7 +9599,7 @@
         <v>1024064</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -9587,7 +9623,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="R134" s="1">
         <v>999999</v>
@@ -9601,7 +9637,7 @@
         <v>1024065</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -9625,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="R135" s="1">
         <v>999999</v>
@@ -9651,7 +9687,7 @@
         <v>1</v>
       </c>
       <c r="H136" s="12" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I136" s="1">
         <v>1</v>
@@ -9663,7 +9699,7 @@
         <v>1</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="M136" s="1">
         <v>2024076</v>
@@ -9672,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="R136" s="1">
         <v>999999</v>
@@ -9698,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="I137" s="1">
         <v>1</v>
@@ -9710,7 +9746,7 @@
         <v>1</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="M137" s="1">
         <v>2024077</v>
@@ -9719,7 +9755,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="R137" s="1">
         <v>999999</v>
@@ -9745,7 +9781,7 @@
         <v>1</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="I138" s="1">
         <v>1</v>
@@ -9757,7 +9793,7 @@
         <v>1</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="M138" s="1">
         <v>2024078</v>
@@ -9766,7 +9802,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="R138" s="1">
         <v>999999</v>
@@ -9792,7 +9828,7 @@
         <v>1</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I139" s="1">
         <v>1</v>
@@ -9804,7 +9840,7 @@
         <v>1</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M139" s="1">
         <v>2024079</v>
@@ -9813,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="R139" s="1">
         <v>999999</v>
@@ -9839,7 +9875,7 @@
         <v>1</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="I140" s="1">
         <v>1</v>
@@ -9851,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="M140" s="1">
         <v>2024080</v>
@@ -9860,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="R140" s="1">
         <v>999999</v>
@@ -9886,7 +9922,7 @@
         <v>1</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I141" s="1">
         <v>1</v>
@@ -9898,7 +9934,7 @@
         <v>1</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M141" s="1">
         <v>2024081</v>
@@ -9907,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="R141" s="1">
         <v>999999</v>
@@ -9933,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I142" s="1">
         <v>1</v>
@@ -9945,7 +9981,7 @@
         <v>1</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="M142" s="1">
         <v>2024082</v>
@@ -9954,7 +9990,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="R142" s="1">
         <v>999999</v>
@@ -9968,7 +10004,7 @@
         <v>1025101</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -9986,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="M143" s="1">
         <v>2025101</v>
@@ -9995,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="R143" s="1">
         <v>-1</v>
@@ -10009,7 +10045,7 @@
         <v>1025102</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -10027,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="M144" s="1">
         <v>2025102</v>
@@ -10036,7 +10072,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="R144" s="1">
         <v>-1</v>
@@ -10050,7 +10086,7 @@
         <v>1025103</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -10068,7 +10104,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="M145" s="1">
         <v>2025103</v>
@@ -10077,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="R145" s="1">
         <v>-1</v>
@@ -10091,7 +10127,7 @@
         <v>1025104</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -10109,7 +10145,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="M146" s="1">
         <v>2025104</v>
@@ -10118,7 +10154,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="R146" s="1">
         <v>-1</v>
@@ -10132,7 +10168,7 @@
         <v>1025105</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -10150,7 +10186,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="M147" s="1">
         <v>2025105</v>
@@ -10159,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="R147" s="1">
         <v>-1</v>
@@ -10173,7 +10209,7 @@
         <v>1025106</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -10191,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="M148" s="1">
         <v>2025106</v>
@@ -10200,7 +10236,7 @@
         <v>0</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="R148" s="1">
         <v>-1</v>
@@ -10214,7 +10250,7 @@
         <v>1025201</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -10232,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="M149" s="1">
         <v>2025201</v>
@@ -10241,7 +10277,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="R149" s="1">
         <v>-1</v>
@@ -10255,7 +10291,7 @@
         <v>1025202</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -10273,7 +10309,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="M150" s="1">
         <v>2025202</v>
@@ -10282,7 +10318,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="R150" s="1">
         <v>-1</v>
@@ -10296,7 +10332,7 @@
         <v>1025203</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -10314,7 +10350,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="M151" s="1">
         <v>2025203</v>
@@ -10323,7 +10359,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="R151" s="1">
         <v>-1</v>
@@ -10337,7 +10373,7 @@
         <v>1025204</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -10355,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="M152" s="1">
         <v>2025204</v>
@@ -10364,7 +10400,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="R152" s="1">
         <v>-1</v>
@@ -10378,7 +10414,7 @@
         <v>1025205</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -10396,7 +10432,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="M153" s="1">
         <v>2025205</v>
@@ -10405,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="R153" s="1">
         <v>-1</v>
@@ -10419,7 +10455,7 @@
         <v>1025206</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -10437,7 +10473,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="M154" s="1">
         <v>2025206</v>
@@ -10446,7 +10482,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="R154" s="1">
         <v>-1</v>
@@ -10460,7 +10496,7 @@
         <v>1025301</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -10478,7 +10514,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="M155" s="1">
         <v>2025301</v>
@@ -10487,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="R155" s="1">
         <v>-1</v>
@@ -10501,7 +10537,7 @@
         <v>1025302</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -10519,7 +10555,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="M156" s="1">
         <v>2025302</v>
@@ -10528,7 +10564,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="R156" s="1">
         <v>-1</v>
@@ -10542,7 +10578,7 @@
         <v>1025303</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -10560,7 +10596,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="M157" s="1">
         <v>2025303</v>
@@ -10569,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="R157" s="1">
         <v>-1</v>
@@ -10583,7 +10619,7 @@
         <v>1025304</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -10601,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="M158" s="1">
         <v>2025304</v>
@@ -10610,7 +10646,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="R158" s="1">
         <v>-1</v>
@@ -10624,7 +10660,7 @@
         <v>1025305</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -10642,7 +10678,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="M159" s="1">
         <v>2025305</v>
@@ -10651,7 +10687,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="R159" s="1">
         <v>-1</v>
@@ -10665,7 +10701,7 @@
         <v>1025306</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -10683,7 +10719,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="M160" s="1">
         <v>2025306</v>
@@ -10692,7 +10728,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="R160" s="1">
         <v>-1</v>
@@ -10706,7 +10742,7 @@
         <v>1025401</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -10724,7 +10760,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="M161" s="1">
         <v>2025401</v>
@@ -10733,7 +10769,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="R161" s="1">
         <v>-1</v>
@@ -10747,7 +10783,7 @@
         <v>1025402</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -10765,7 +10801,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="M162" s="1">
         <v>2025402</v>
@@ -10774,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="R162" s="1">
         <v>-1</v>
@@ -10788,7 +10824,7 @@
         <v>1025403</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -10806,7 +10842,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="M163" s="1">
         <v>2025403</v>
@@ -10815,7 +10851,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="R163" s="1">
         <v>-1</v>
@@ -10829,7 +10865,7 @@
         <v>1025404</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
@@ -10847,7 +10883,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="M164" s="1">
         <v>2025404</v>
@@ -10856,7 +10892,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="R164" s="1">
         <v>-1</v>
@@ -10870,7 +10906,7 @@
         <v>1025405</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
@@ -10888,7 +10924,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="M165" s="1">
         <v>2025405</v>
@@ -10897,7 +10933,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="R165" s="1">
         <v>-1</v>
@@ -10911,7 +10947,7 @@
         <v>1025406</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E166" s="1">
         <v>2</v>
@@ -10929,7 +10965,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="M166" s="1">
         <v>2025406</v>
@@ -10938,7 +10974,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="R166" s="1">
         <v>-1</v>
@@ -10952,7 +10988,7 @@
         <v>1025501</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E167" s="1">
         <v>2</v>
@@ -10970,7 +11006,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="M167" s="1">
         <v>2025501</v>
@@ -10979,7 +11015,7 @@
         <v>0</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="R167" s="1">
         <v>-1</v>
@@ -10993,7 +11029,7 @@
         <v>1025502</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E168" s="1">
         <v>2</v>
@@ -11011,7 +11047,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="M168" s="1">
         <v>2025502</v>
@@ -11020,7 +11056,7 @@
         <v>0</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="R168" s="1">
         <v>-1</v>
@@ -11034,7 +11070,7 @@
         <v>1025503</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E169" s="1">
         <v>2</v>
@@ -11052,7 +11088,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="M169" s="1">
         <v>2025503</v>
@@ -11061,7 +11097,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="R169" s="1">
         <v>-1</v>
@@ -11075,7 +11111,7 @@
         <v>1025504</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E170" s="1">
         <v>2</v>
@@ -11093,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="M170" s="1">
         <v>2025504</v>
@@ -11102,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="R170" s="1">
         <v>-1</v>
@@ -11116,7 +11152,7 @@
         <v>1025505</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E171" s="1">
         <v>2</v>
@@ -11134,7 +11170,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="M171" s="1">
         <v>2025505</v>
@@ -11143,7 +11179,7 @@
         <v>0</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="R171" s="1">
         <v>-1</v>
@@ -11157,7 +11193,7 @@
         <v>1025506</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="E172" s="1">
         <v>2</v>
@@ -11175,7 +11211,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="M172" s="1">
         <v>2025506</v>
@@ -11184,7 +11220,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="R172" s="1">
         <v>-1</v>
@@ -11217,7 +11253,7 @@
         <v>1</v>
       </c>
       <c r="L173" s="14" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="M173" s="1">
         <v>2125101</v>
@@ -11260,7 +11296,7 @@
         <v>1</v>
       </c>
       <c r="L174" s="14" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M174" s="1">
         <v>2125102</v>
@@ -11303,7 +11339,7 @@
         <v>1</v>
       </c>
       <c r="L175" s="14" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="M175" s="1">
         <v>2125103</v>
@@ -11346,7 +11382,7 @@
         <v>1</v>
       </c>
       <c r="L176" s="14" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M176" s="1">
         <v>2125104</v>
@@ -11389,7 +11425,7 @@
         <v>1</v>
       </c>
       <c r="L177" s="14" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="M177" s="1">
         <v>2125105</v>
@@ -11432,7 +11468,7 @@
         <v>1</v>
       </c>
       <c r="L178" s="14" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="M178" s="1">
         <v>2125106</v>
@@ -11475,7 +11511,7 @@
         <v>1</v>
       </c>
       <c r="L179" s="14" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="M179" s="1">
         <v>2125201</v>
@@ -11518,7 +11554,7 @@
         <v>1</v>
       </c>
       <c r="L180" s="14" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="M180" s="1">
         <v>2125202</v>
@@ -11561,7 +11597,7 @@
         <v>1</v>
       </c>
       <c r="L181" s="14" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="M181" s="1">
         <v>2125203</v>
@@ -11604,7 +11640,7 @@
         <v>1</v>
       </c>
       <c r="L182" s="14" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="M182" s="1">
         <v>2125204</v>
@@ -11647,7 +11683,7 @@
         <v>1</v>
       </c>
       <c r="L183" s="14" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="M183" s="1">
         <v>2125205</v>
@@ -11690,7 +11726,7 @@
         <v>1</v>
       </c>
       <c r="L184" s="14" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="M184" s="1">
         <v>2125206</v>
@@ -11733,7 +11769,7 @@
         <v>1</v>
       </c>
       <c r="L185" s="14" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="M185" s="1">
         <v>2125301</v>
@@ -11776,7 +11812,7 @@
         <v>1</v>
       </c>
       <c r="L186" s="14" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="M186" s="1">
         <v>2125302</v>
@@ -11819,7 +11855,7 @@
         <v>1</v>
       </c>
       <c r="L187" s="14" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="M187" s="1">
         <v>2125303</v>
@@ -11862,7 +11898,7 @@
         <v>1</v>
       </c>
       <c r="L188" s="14" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="M188" s="1">
         <v>2125304</v>
@@ -11905,7 +11941,7 @@
         <v>1</v>
       </c>
       <c r="L189" s="14" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="M189" s="1">
         <v>2125305</v>
@@ -11948,7 +11984,7 @@
         <v>1</v>
       </c>
       <c r="L190" s="14" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="M190" s="1">
         <v>2125306</v>
@@ -11991,7 +12027,7 @@
         <v>1</v>
       </c>
       <c r="L191" s="14" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="M191" s="1">
         <v>2125401</v>
@@ -12034,7 +12070,7 @@
         <v>1</v>
       </c>
       <c r="L192" s="14" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="M192" s="1">
         <v>2125402</v>
@@ -12077,7 +12113,7 @@
         <v>1</v>
       </c>
       <c r="L193" s="14" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="M193" s="1">
         <v>2125403</v>
@@ -12120,7 +12156,7 @@
         <v>1</v>
       </c>
       <c r="L194" s="14" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="M194" s="1">
         <v>2125404</v>
@@ -12163,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="L195" s="14" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="M195" s="1">
         <v>2125405</v>
@@ -12206,7 +12242,7 @@
         <v>1</v>
       </c>
       <c r="L196" s="14" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="M196" s="1">
         <v>2125406</v>
@@ -12249,7 +12285,7 @@
         <v>1</v>
       </c>
       <c r="L197" s="14" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="M197" s="1">
         <v>2125501</v>
@@ -12292,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="L198" s="14" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="M198" s="1">
         <v>2125502</v>
@@ -12335,7 +12371,7 @@
         <v>1</v>
       </c>
       <c r="L199" s="14" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M199" s="1">
         <v>2125503</v>
@@ -12378,7 +12414,7 @@
         <v>1</v>
       </c>
       <c r="L200" s="14" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="M200" s="1">
         <v>2125504</v>
@@ -12421,7 +12457,7 @@
         <v>1</v>
       </c>
       <c r="L201" s="14" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="M201" s="1">
         <v>2125505</v>
@@ -12464,7 +12500,7 @@
         <v>1</v>
       </c>
       <c r="L202" s="14" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="M202" s="1">
         <v>2125506</v>
@@ -12488,7 +12524,7 @@
         <v>1026001</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E203" s="1">
         <v>2</v>
@@ -12506,7 +12542,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="M203" s="1">
         <v>2026001</v>
@@ -12515,7 +12551,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="R203" s="1">
         <v>-1</v>
@@ -12529,7 +12565,7 @@
         <v>1026002</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E204" s="1">
         <v>2</v>
@@ -12547,7 +12583,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="M204" s="1">
         <v>2026002</v>
@@ -12556,7 +12592,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="R204" s="1">
         <v>-1</v>
@@ -12570,7 +12606,7 @@
         <v>1026101</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E205" s="1">
         <v>2</v>
@@ -12597,7 +12633,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="R205" s="1">
         <v>-1</v>
@@ -12611,7 +12647,7 @@
         <v>1026102</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -12638,7 +12674,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="R206" s="1">
         <v>-1</v>
@@ -12652,7 +12688,7 @@
         <v>1026201</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -12679,7 +12715,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="R207" s="1">
         <v>-1</v>
@@ -12693,7 +12729,7 @@
         <v>1026202</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -12720,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="R208" s="1">
         <v>-1</v>
@@ -12734,7 +12770,7 @@
         <v>1026301</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -12761,7 +12797,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="R209" s="1">
         <v>-1</v>
@@ -12775,7 +12811,7 @@
         <v>1026302</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -12802,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="R210" s="1">
         <v>-1</v>
@@ -12816,7 +12852,7 @@
         <v>1026401</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -12843,7 +12879,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="R211" s="1">
         <v>-1</v>
@@ -12857,7 +12893,7 @@
         <v>1026402</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -12884,7 +12920,7 @@
         <v>0</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="R212" s="1">
         <v>-1</v>
@@ -12898,7 +12934,7 @@
         <v>1027001</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -12916,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="M213" s="1">
         <v>2027001</v>
@@ -12925,7 +12961,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="R213" s="1">
         <v>-1</v>
@@ -12939,7 +12975,7 @@
         <v>1027002</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -12966,7 +13002,7 @@
         <v>0</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="R214" s="1">
         <v>-1</v>
@@ -12980,7 +13016,7 @@
         <v>1027101</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -13007,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="R215" s="1">
         <v>-1</v>
@@ -13021,7 +13057,7 @@
         <v>1027102</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -13048,7 +13084,7 @@
         <v>0</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="R216" s="1">
         <v>-1</v>
@@ -13062,7 +13098,7 @@
         <v>1027201</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -13089,7 +13125,7 @@
         <v>0</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="R217" s="1">
         <v>-1</v>
@@ -13103,7 +13139,7 @@
         <v>1027202</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -13130,7 +13166,7 @@
         <v>0</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="R218" s="1">
         <v>-1</v>
@@ -13144,7 +13180,7 @@
         <v>1027301</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -13171,7 +13207,7 @@
         <v>0</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="R219" s="1">
         <v>-1</v>
@@ -13185,7 +13221,7 @@
         <v>1027302</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -13203,7 +13239,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="M220" s="1">
         <v>2027302</v>
@@ -13212,7 +13248,7 @@
         <v>0</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="R220" s="1">
         <v>-1</v>
@@ -13226,7 +13262,7 @@
         <v>1027401</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -13253,7 +13289,7 @@
         <v>0</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="R221" s="1">
         <v>-1</v>
@@ -13267,7 +13303,7 @@
         <v>1027402</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -13285,7 +13321,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="M222" s="1">
         <v>2027402</v>
@@ -13294,7 +13330,7 @@
         <v>0</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="R222" s="1">
         <v>-1</v>
@@ -13308,7 +13344,7 @@
         <v>1028001</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -13335,7 +13371,7 @@
         <v>0</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="R223" s="1">
         <v>-1</v>
@@ -13349,7 +13385,7 @@
         <v>1028002</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -13376,7 +13412,7 @@
         <v>0</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="R224" s="1">
         <v>-1</v>
@@ -13390,7 +13426,7 @@
         <v>1028101</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -13417,7 +13453,7 @@
         <v>0</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="R225" s="1">
         <v>-1</v>
@@ -13431,7 +13467,7 @@
         <v>1028102</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="E226" s="1">
         <v>2</v>
@@ -13458,7 +13494,7 @@
         <v>0</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="R226" s="1">
         <v>-1</v>
@@ -13472,7 +13508,7 @@
         <v>1028201</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
@@ -13499,7 +13535,7 @@
         <v>0</v>
       </c>
       <c r="O227" s="1" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="R227" s="1">
         <v>-1</v>
@@ -13513,7 +13549,7 @@
         <v>1028202</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
@@ -13540,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="O228" s="1" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="R228" s="1">
         <v>-1</v>
@@ -13554,7 +13590,7 @@
         <v>1028301</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
@@ -13581,7 +13617,7 @@
         <v>0</v>
       </c>
       <c r="O229" s="1" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="R229" s="1">
         <v>-1</v>
@@ -13595,7 +13631,7 @@
         <v>1028302</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
@@ -13622,7 +13658,7 @@
         <v>0</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="R230" s="1">
         <v>-1</v>
@@ -13636,7 +13672,7 @@
         <v>1028401</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
@@ -13663,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="R231" s="1">
         <v>-1</v>
@@ -13677,7 +13713,7 @@
         <v>1028402</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
@@ -13704,7 +13740,7 @@
         <v>0</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="R232" s="1">
         <v>-1</v>
@@ -13737,7 +13773,7 @@
         <v>1</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="M233" s="1">
         <v>2126001</v>
@@ -13780,7 +13816,7 @@
         <v>1</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="M234" s="1">
         <v>2126002</v>
@@ -13823,7 +13859,7 @@
         <v>1</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M235" s="1">
         <v>2126101</v>
@@ -13866,7 +13902,7 @@
         <v>1</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M236" s="1">
         <v>2126102</v>
@@ -13909,7 +13945,7 @@
         <v>1</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M237" s="1">
         <v>2126201</v>
@@ -13952,7 +13988,7 @@
         <v>1</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M238" s="1">
         <v>2126202</v>
@@ -13995,7 +14031,7 @@
         <v>1</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M239" s="1">
         <v>2126301</v>
@@ -14038,7 +14074,7 @@
         <v>1</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M240" s="1">
         <v>2126302</v>
@@ -14081,7 +14117,7 @@
         <v>1</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M241" s="1">
         <v>2126401</v>
@@ -14124,7 +14160,7 @@
         <v>1</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M242" s="1">
         <v>2126402</v>
@@ -14167,7 +14203,7 @@
         <v>1</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="M243" s="1">
         <v>2127001</v>
@@ -14210,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M244" s="1">
         <v>2127002</v>
@@ -14253,7 +14289,7 @@
         <v>1</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M245" s="1">
         <v>2127101</v>
@@ -14296,7 +14332,7 @@
         <v>1</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M246" s="1">
         <v>2127102</v>
@@ -14339,7 +14375,7 @@
         <v>1</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M247" s="1">
         <v>2127201</v>
@@ -14382,7 +14418,7 @@
         <v>1</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M248" s="1">
         <v>2127202</v>
@@ -14425,7 +14461,7 @@
         <v>1</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M249" s="1">
         <v>2127301</v>
@@ -14468,7 +14504,7 @@
         <v>1</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="M250" s="1">
         <v>2127302</v>
@@ -14511,7 +14547,7 @@
         <v>1</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M251" s="1">
         <v>2127401</v>
@@ -14554,7 +14590,7 @@
         <v>1</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="M252" s="1">
         <v>2127402</v>
@@ -14597,7 +14633,7 @@
         <v>1</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M253" s="1">
         <v>2128001</v>
@@ -14640,7 +14676,7 @@
         <v>1</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M254" s="1">
         <v>2128002</v>
@@ -14683,7 +14719,7 @@
         <v>1</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M255" s="1">
         <v>2128101</v>
@@ -14726,7 +14762,7 @@
         <v>1</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M256" s="1">
         <v>2128102</v>
@@ -14769,7 +14805,7 @@
         <v>1</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M257" s="1">
         <v>2128201</v>
@@ -14812,7 +14848,7 @@
         <v>1</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M258" s="1">
         <v>2128202</v>
@@ -14855,7 +14891,7 @@
         <v>1</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M259" s="1">
         <v>2128301</v>
@@ -14898,7 +14934,7 @@
         <v>1</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M260" s="1">
         <v>2128302</v>
@@ -14941,7 +14977,7 @@
         <v>1</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M261" s="1">
         <v>2128401</v>
@@ -14984,7 +15020,7 @@
         <v>1</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M262" s="1">
         <v>2128402</v>
@@ -15008,7 +15044,7 @@
         <v>1130001</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -15026,7 +15062,7 @@
         <v>1</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="M263" s="1">
         <v>2130001</v>
@@ -15035,7 +15071,7 @@
         <v>0</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="R263" s="1">
         <v>999999</v>
@@ -15049,7 +15085,7 @@
         <v>1130002</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="E264" s="1">
         <v>1</v>
@@ -15067,7 +15103,7 @@
         <v>1</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="M264" s="1">
         <v>2130002</v>
@@ -15076,13 +15112,13 @@
         <v>0</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="R264" s="1">
         <v>999999</v>
       </c>
       <c r="T264" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="265" spans="1:20">
@@ -15093,7 +15129,7 @@
         <v>1130003</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="E265" s="1">
         <v>1</v>
@@ -15111,7 +15147,7 @@
         <v>1</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="M265" s="1">
         <v>2130003</v>
@@ -15120,13 +15156,13 @@
         <v>0</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="R265" s="1">
         <v>999999</v>
       </c>
       <c r="T265" s="1" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="266" spans="1:20">
@@ -15137,7 +15173,7 @@
         <v>1130004</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E266" s="1">
         <v>1</v>
@@ -15155,7 +15191,7 @@
         <v>1</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="M266" s="1">
         <v>2130004</v>
@@ -15164,13 +15200,13 @@
         <v>0</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="R266" s="1">
         <v>999999</v>
       </c>
       <c r="T266" s="1" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="267" spans="1:20">
@@ -15181,7 +15217,7 @@
         <v>1130005</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E267" s="1">
         <v>1</v>
@@ -15199,7 +15235,7 @@
         <v>1</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="M267" s="1">
         <v>2130005</v>
@@ -15208,13 +15244,13 @@
         <v>0</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="R267" s="1">
         <v>999999</v>
       </c>
       <c r="T267" s="1" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="268" spans="1:20">
@@ -15225,7 +15261,7 @@
         <v>1130006</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E268" s="1">
         <v>1</v>
@@ -15243,7 +15279,7 @@
         <v>1</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="M268" s="1">
         <v>2130006</v>
@@ -15252,13 +15288,13 @@
         <v>0</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="R268" s="1">
         <v>999999</v>
       </c>
       <c r="T268" s="1" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="269" spans="1:20">
@@ -15269,7 +15305,7 @@
         <v>1131001</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -15287,7 +15323,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="M269" s="1">
         <v>2131001</v>
@@ -15296,7 +15332,7 @@
         <v>0</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="R269" s="1">
         <v>999999</v>
@@ -15310,7 +15346,7 @@
         <v>1131002</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -15328,7 +15364,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="M270" s="1">
         <v>2131002</v>
@@ -15337,7 +15373,7 @@
         <v>0</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="R270" s="1">
         <v>999999</v>
@@ -15351,7 +15387,7 @@
         <v>1131003</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -15369,7 +15405,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="M271" s="1">
         <v>2131003</v>
@@ -15378,7 +15414,7 @@
         <v>0</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="R271" s="1">
         <v>999999</v>
@@ -15392,7 +15428,7 @@
         <v>1131004</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -15410,7 +15446,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="M272" s="1">
         <v>2131004</v>
@@ -15419,7 +15455,7 @@
         <v>0</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="R272" s="1">
         <v>999999</v>
@@ -15433,7 +15469,7 @@
         <v>1131005</v>
       </c>
       <c r="D273" s="15" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -15451,7 +15487,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="M273" s="1">
         <v>2131005</v>
@@ -15460,7 +15496,7 @@
         <v>0</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="R273" s="1">
         <v>999999</v>
@@ -15474,7 +15510,7 @@
         <v>1131006</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -15492,7 +15528,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="M274" s="1">
         <v>2131006</v>
@@ -15501,7 +15537,7 @@
         <v>0</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="R274" s="1">
         <v>999999</v>
@@ -15515,7 +15551,7 @@
         <v>1131101</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -15533,7 +15569,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="M275" s="1">
         <v>2131001</v>
@@ -15542,7 +15578,7 @@
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="R275" s="1">
         <v>999999</v>
@@ -15556,7 +15592,7 @@
         <v>1131102</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -15574,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="M276" s="1">
         <v>2131002</v>
@@ -15583,7 +15619,7 @@
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="R276" s="1">
         <v>999999</v>
@@ -15597,7 +15633,7 @@
         <v>1131103</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -15615,7 +15651,7 @@
         <v>0</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="M277" s="1">
         <v>2131003</v>
@@ -15624,7 +15660,7 @@
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="R277" s="1">
         <v>999999</v>
@@ -15638,7 +15674,7 @@
         <v>1131104</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -15656,7 +15692,7 @@
         <v>0</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="M278" s="1">
         <v>2131004</v>
@@ -15665,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="R278" s="1">
         <v>999999</v>
@@ -15679,7 +15715,7 @@
         <v>1131105</v>
       </c>
       <c r="D279" s="15" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -15697,7 +15733,7 @@
         <v>0</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="M279" s="1">
         <v>2131005</v>
@@ -15706,7 +15742,7 @@
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="R279" s="1">
         <v>999999</v>
@@ -15720,7 +15756,7 @@
         <v>1131106</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -15738,7 +15774,7 @@
         <v>0</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="M280" s="1">
         <v>2131006</v>
@@ -15747,7 +15783,7 @@
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="R280" s="1">
         <v>999999</v>
@@ -15761,7 +15797,7 @@
         <v>1131201</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15779,7 +15815,7 @@
         <v>0</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="M281" s="1">
         <v>2131001</v>
@@ -15788,7 +15824,7 @@
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="R281" s="1">
         <v>999999</v>
@@ -15802,7 +15838,7 @@
         <v>1131202</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15820,7 +15856,7 @@
         <v>0</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="M282" s="1">
         <v>2131002</v>
@@ -15829,7 +15865,7 @@
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="R282" s="1">
         <v>999999</v>
@@ -15843,7 +15879,7 @@
         <v>1131203</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15861,7 +15897,7 @@
         <v>0</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="M283" s="1">
         <v>2131003</v>
@@ -15870,7 +15906,7 @@
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="R283" s="1">
         <v>999999</v>
@@ -15884,7 +15920,7 @@
         <v>1131204</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15902,7 +15938,7 @@
         <v>0</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="M284" s="1">
         <v>2131004</v>
@@ -15911,7 +15947,7 @@
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="R284" s="1">
         <v>999999</v>
@@ -15925,7 +15961,7 @@
         <v>1131205</v>
       </c>
       <c r="D285" s="15" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15943,7 +15979,7 @@
         <v>0</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="M285" s="1">
         <v>2131005</v>
@@ -15952,7 +15988,7 @@
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="R285" s="1">
         <v>999999</v>
@@ -15966,7 +16002,7 @@
         <v>1131206</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -15984,7 +16020,7 @@
         <v>0</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="M286" s="1">
         <v>2131006</v>
@@ -15993,7 +16029,7 @@
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="R286" s="1">
         <v>999999</v>
@@ -16007,7 +16043,7 @@
         <v>1131301</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -16025,7 +16061,7 @@
         <v>0</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="M287" s="1">
         <v>2131001</v>
@@ -16034,7 +16070,7 @@
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="R287" s="1">
         <v>999999</v>
@@ -16048,7 +16084,7 @@
         <v>1131302</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -16066,7 +16102,7 @@
         <v>0</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="M288" s="1">
         <v>2131002</v>
@@ -16075,7 +16111,7 @@
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="R288" s="1">
         <v>999999</v>
@@ -16089,7 +16125,7 @@
         <v>1131303</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -16107,7 +16143,7 @@
         <v>0</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="M289" s="1">
         <v>2131003</v>
@@ -16116,7 +16152,7 @@
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="R289" s="1">
         <v>999999</v>
@@ -16130,7 +16166,7 @@
         <v>1131304</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -16148,7 +16184,7 @@
         <v>0</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="M290" s="1">
         <v>2131004</v>
@@ -16157,7 +16193,7 @@
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="R290" s="1">
         <v>999999</v>
@@ -16171,7 +16207,7 @@
         <v>1131305</v>
       </c>
       <c r="D291" s="15" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -16189,7 +16225,7 @@
         <v>0</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="M291" s="1">
         <v>2131005</v>
@@ -16198,7 +16234,7 @@
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="R291" s="1">
         <v>999999</v>
@@ -16212,7 +16248,7 @@
         <v>1131306</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -16230,7 +16266,7 @@
         <v>0</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="M292" s="1">
         <v>2131006</v>
@@ -16239,7 +16275,7 @@
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="R292" s="1">
         <v>999999</v>
@@ -16253,7 +16289,7 @@
         <v>1131401</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -16271,7 +16307,7 @@
         <v>0</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="M293" s="1">
         <v>2131001</v>
@@ -16280,7 +16316,7 @@
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="R293" s="1">
         <v>999999</v>
@@ -16294,7 +16330,7 @@
         <v>1131402</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -16312,7 +16348,7 @@
         <v>0</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="M294" s="1">
         <v>2131002</v>
@@ -16321,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="R294" s="1">
         <v>999999</v>
@@ -16335,7 +16371,7 @@
         <v>1131403</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -16353,7 +16389,7 @@
         <v>0</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="M295" s="1">
         <v>2131003</v>
@@ -16362,7 +16398,7 @@
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="R295" s="1">
         <v>999999</v>
@@ -16376,7 +16412,7 @@
         <v>1131404</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -16394,7 +16430,7 @@
         <v>0</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="M296" s="1">
         <v>2131004</v>
@@ -16403,7 +16439,7 @@
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="R296" s="1">
         <v>999999</v>
@@ -16417,7 +16453,7 @@
         <v>1131405</v>
       </c>
       <c r="D297" s="15" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -16435,7 +16471,7 @@
         <v>0</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="M297" s="1">
         <v>2131005</v>
@@ -16444,7 +16480,7 @@
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="R297" s="1">
         <v>999999</v>
@@ -16458,7 +16494,7 @@
         <v>1131406</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -16476,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="M298" s="1">
         <v>2131006</v>
@@ -16485,7 +16521,7 @@
         <v>0</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="R298" s="1">
         <v>999999</v>
@@ -16499,7 +16535,7 @@
         <v>1140001</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -16517,7 +16553,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="M299" s="1">
         <v>2140001</v>
@@ -16526,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="R299" s="1">
         <v>1</v>
@@ -16540,7 +16576,7 @@
         <v>1140002</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -16558,7 +16594,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="M300" s="1">
         <v>2140002</v>
@@ -16567,7 +16603,7 @@
         <v>0</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="R300" s="1">
         <v>1</v>
@@ -16581,7 +16617,7 @@
         <v>1140003</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -16599,7 +16635,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="M301" s="1">
         <v>2140003</v>
@@ -16608,7 +16644,7 @@
         <v>0</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="R301" s="1">
         <v>1</v>
@@ -16622,7 +16658,7 @@
         <v>1140004</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -16640,7 +16676,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="M302" s="1">
         <v>2140004</v>
@@ -16649,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="R302" s="1">
         <v>1</v>
@@ -16663,7 +16699,7 @@
         <v>1140005</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -16681,7 +16717,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="M303" s="1">
         <v>2140005</v>
@@ -16690,7 +16726,7 @@
         <v>0</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="R303" s="1">
         <v>1</v>
@@ -16704,7 +16740,7 @@
         <v>1140006</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -16722,7 +16758,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="M304" s="1">
         <v>2140006</v>
@@ -16731,7 +16767,7 @@
         <v>0</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="R304" s="1">
         <v>1</v>
@@ -16745,7 +16781,7 @@
         <v>1150001</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -16763,7 +16799,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="M305" s="1">
         <v>2150001</v>
@@ -16787,7 +16823,7 @@
         <v>1150002</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -16805,7 +16841,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="M306" s="1">
         <v>2150002</v>
@@ -16829,7 +16865,7 @@
         <v>1150003</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -16847,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="M307" s="1">
         <v>2150003</v>
@@ -16871,7 +16907,7 @@
         <v>1150004</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16889,7 +16925,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M308" s="1">
         <v>2150004</v>
@@ -16913,7 +16949,7 @@
         <v>1150005</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16931,7 +16967,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="M309" s="1">
         <v>2150005</v>
@@ -16955,7 +16991,7 @@
         <v>1150006</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -16973,7 +17009,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="M310" s="1">
         <v>2150006</v>
@@ -16997,7 +17033,7 @@
         <v>1150007</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -17015,7 +17051,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="M311" s="1">
         <v>2150007</v>
@@ -17039,7 +17075,7 @@
         <v>1150008</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -17057,7 +17093,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="M312" s="1">
         <v>2150008</v>
@@ -17081,7 +17117,7 @@
         <v>1150009</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -17099,7 +17135,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="M313" s="1">
         <v>2150009</v>
@@ -17123,7 +17159,7 @@
         <v>1150010</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -17141,7 +17177,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="M314" s="1">
         <v>2150010</v>
@@ -17165,7 +17201,7 @@
         <v>1150011</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -17183,7 +17219,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="M315" s="1">
         <v>2150011</v>
@@ -17207,7 +17243,7 @@
         <v>1150012</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -17225,7 +17261,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="M316" s="1">
         <v>2150012</v>
@@ -17249,7 +17285,7 @@
         <v>1150013</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -17267,7 +17303,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="M317" s="1">
         <v>2150013</v>
@@ -17291,7 +17327,7 @@
         <v>1150014</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -17309,7 +17345,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="M318" s="1">
         <v>2150014</v>
@@ -17333,7 +17369,7 @@
         <v>1150015</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -17351,7 +17387,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="M319" s="1">
         <v>2150015</v>
@@ -17375,7 +17411,7 @@
         <v>1150016</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -17393,7 +17429,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="M320" s="1">
         <v>2150016</v>
@@ -17417,7 +17453,7 @@
         <v>1150017</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -17435,7 +17471,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="M321" s="1">
         <v>2150017</v>
@@ -17459,7 +17495,7 @@
         <v>1150018</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -17477,7 +17513,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="M322" s="1">
         <v>2150018</v>
@@ -17501,7 +17537,7 @@
         <v>1150019</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -17519,7 +17555,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="M323" s="1">
         <v>2150019</v>
@@ -17543,7 +17579,7 @@
         <v>1150020</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -17561,7 +17597,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="M324" s="1">
         <v>2150020</v>
@@ -17585,7 +17621,7 @@
         <v>1150021</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -17603,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="M325" s="1">
         <v>2150021</v>
@@ -17627,7 +17663,7 @@
         <v>1150022</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -17645,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="M326" s="1">
         <v>2150022</v>
@@ -17669,7 +17705,7 @@
         <v>1150023</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -17687,7 +17723,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="M327" s="1">
         <v>2150023</v>
@@ -17711,7 +17747,7 @@
         <v>1150024</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -17729,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="M328" s="1">
         <v>2150024</v>
@@ -17753,7 +17789,7 @@
         <v>1150025</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -17771,7 +17807,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="M329" s="1">
         <v>2150025</v>
@@ -17795,7 +17831,7 @@
         <v>1150026</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -17813,7 +17849,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="M330" s="1">
         <v>2150026</v>
@@ -17837,7 +17873,7 @@
         <v>1150027</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17855,7 +17891,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="M331" s="1">
         <v>2150027</v>
@@ -17879,7 +17915,7 @@
         <v>1150028</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17897,7 +17933,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="M332" s="1">
         <v>2150028</v>
@@ -17921,7 +17957,7 @@
         <v>1150029</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17939,7 +17975,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="M333" s="1">
         <v>2150029</v>
@@ -17963,7 +17999,7 @@
         <v>1150030</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -17981,7 +18017,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="M334" s="1">
         <v>2150030</v>
@@ -18005,7 +18041,7 @@
         <v>1150031</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -18023,7 +18059,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="M335" s="1">
         <v>2150031</v>
@@ -18047,7 +18083,7 @@
         <v>1150032</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -18065,7 +18101,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="M336" s="1">
         <v>2150032</v>
@@ -18089,7 +18125,7 @@
         <v>1150033</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -18107,7 +18143,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="M337" s="1">
         <v>2150033</v>
@@ -18131,7 +18167,7 @@
         <v>1150034</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -18149,7 +18185,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="M338" s="1">
         <v>2150034</v>
@@ -18173,7 +18209,7 @@
         <v>1150035</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -18191,7 +18227,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="M339" s="1">
         <v>2150035</v>
@@ -18215,7 +18251,7 @@
         <v>1150036</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -18233,7 +18269,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="M340" s="1">
         <v>2150036</v>
@@ -18257,7 +18293,7 @@
         <v>1150037</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -18275,7 +18311,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="M341" s="1">
         <v>2150037</v>
@@ -18299,7 +18335,7 @@
         <v>1150038</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -18317,7 +18353,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="M342" s="1">
         <v>2150038</v>
@@ -18341,7 +18377,7 @@
         <v>1150039</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -18359,7 +18395,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="M343" s="1">
         <v>2150039</v>
@@ -18383,7 +18419,7 @@
         <v>1150040</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -18401,7 +18437,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="M344" s="1">
         <v>2150040</v>
@@ -18425,7 +18461,7 @@
         <v>1150041</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -18443,7 +18479,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="M345" s="1">
         <v>2150041</v>
@@ -18467,7 +18503,7 @@
         <v>1150042</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -18485,7 +18521,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="M346" s="1">
         <v>2150042</v>
@@ -18509,7 +18545,7 @@
         <v>1150043</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -18527,7 +18563,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="M347" s="1">
         <v>2150043</v>
@@ -18551,7 +18587,7 @@
         <v>1150044</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -18569,7 +18605,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="M348" s="1">
         <v>2150044</v>
@@ -18593,7 +18629,7 @@
         <v>1150045</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -18611,7 +18647,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="M349" s="1">
         <v>2150045</v>
@@ -18635,7 +18671,7 @@
         <v>1150046</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -18653,7 +18689,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="M350" s="1">
         <v>2150046</v>
@@ -18677,7 +18713,7 @@
         <v>1150047</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -18695,7 +18731,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="M351" s="1">
         <v>2150047</v>
@@ -18719,7 +18755,7 @@
         <v>1150048</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -18737,7 +18773,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="M352" s="1">
         <v>2150048</v>
@@ -18761,7 +18797,7 @@
         <v>1150049</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -18779,7 +18815,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="M353" s="1">
         <v>2150049</v>
@@ -18803,7 +18839,7 @@
         <v>1150050</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -18821,7 +18857,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="M354" s="1">
         <v>2150050</v>
@@ -18845,7 +18881,7 @@
         <v>1150051</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18863,7 +18899,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="M355" s="1">
         <v>2150051</v>
@@ -18887,7 +18923,7 @@
         <v>1150052</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18905,7 +18941,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="M356" s="1">
         <v>2150052</v>
@@ -18929,7 +18965,7 @@
         <v>1150053</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18947,7 +18983,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="M357" s="1">
         <v>2150053</v>
@@ -18971,7 +19007,7 @@
         <v>1150054</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -18989,7 +19025,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="M358" s="1">
         <v>2150054</v>
@@ -19013,7 +19049,7 @@
         <v>1150055</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E359" s="1">
         <v>2</v>
@@ -19031,7 +19067,7 @@
         <v>0</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="M359" s="1">
         <v>2150055</v>
@@ -19055,7 +19091,7 @@
         <v>1150056</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E360" s="1">
         <v>2</v>
@@ -19073,7 +19109,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="M360" s="1">
         <v>2150056</v>
@@ -19097,7 +19133,7 @@
         <v>1150057</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="E361" s="1">
         <v>2</v>
@@ -19115,7 +19151,7 @@
         <v>0</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="M361" s="1">
         <v>2150057</v>
@@ -19139,7 +19175,7 @@
         <v>1150058</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="E362" s="1">
         <v>2</v>
@@ -19157,7 +19193,7 @@
         <v>0</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="M362" s="1">
         <v>2150058</v>
@@ -19181,7 +19217,7 @@
         <v>1150059</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E363" s="1">
         <v>2</v>
@@ -19199,7 +19235,7 @@
         <v>0</v>
       </c>
       <c r="L363" s="1" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="M363" s="1">
         <v>2150059</v>
@@ -19223,7 +19259,7 @@
         <v>1150060</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="E364" s="1">
         <v>2</v>
@@ -19241,7 +19277,7 @@
         <v>0</v>
       </c>
       <c r="L364" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="M364" s="1">
         <v>2150060</v>
@@ -19265,7 +19301,7 @@
         <v>1150061</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="E365" s="1">
         <v>2</v>
@@ -19283,7 +19319,7 @@
         <v>0</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="M365" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="696">
   <si>
     <t>道具ID</t>
   </si>
@@ -958,24 +958,36 @@
     <t>加速建筑升级的CD时间</t>
   </si>
   <si>
-    <t>雇员升级材料1</t>
+    <t>胜运砾石</t>
   </si>
   <si>
     <t>daoju_cailiao_1.png</t>
   </si>
   <si>
-    <t>雇员升级材料2</t>
+    <t>雇员游戏经理升级所需要的经验材料
+获取途径：游客在场景中进行交互概率掉落</t>
+  </si>
+  <si>
+    <t>鸿运原石</t>
   </si>
   <si>
     <t>daoju_cailiao_2.png</t>
   </si>
   <si>
-    <t>雇员升级材料3</t>
+    <t>雇员服务经理升级所需要的经验材料
+获取途径：游客在场景中进行交互概率掉落</t>
+  </si>
+  <si>
+    <t>幸运宝石</t>
   </si>
   <si>
     <t>daoju_cailiao_3.png</t>
   </si>
   <si>
+    <t>雇员管理经理升级所需要的经验材料
+获取途径：游客在场景中进行交互概率掉落</t>
+  </si>
+  <si>
     <t>声誉值</t>
   </si>
   <si>
@@ -1000,7 +1012,8 @@
     <t>daoju_ykck.png</t>
   </si>
   <si>
-    <t>用于游客卡池抽奖的道具</t>
+    <t>用于游客卡池抽奖的道具
+获取途径：可以通过完成多人任务奖励获得</t>
   </si>
   <si>
     <t>雇员抽卡道具</t>
@@ -1009,13 +1022,15 @@
     <t>daoju_gyck.png</t>
   </si>
   <si>
-    <t>用于雇员卡池抽卡的道具</t>
+    <t>用于雇员卡池抽卡的道具
+获取途径：可以通过完成多人任务奖励获得</t>
   </si>
   <si>
     <t>游客人员邀请函</t>
   </si>
   <si>
-    <t>用于指定生成游客人员的道具</t>
+    <t>用于指定生成游客人员的道具
+获取途径：商城购买</t>
   </si>
   <si>
     <t>1025101_1;1025102_1;1025103_1;1025104_1;1025105_1;1025106_1;1025201_1;1025202_1;1025203_1;1025204_1;1025205_1;1025206_1;1025301_1;1025302_1;1025303_1;1025304_1;1025305_1;1025306_1;1025401_1;1025402_1;1025403_1;1025404_1;1025405_1;1025406_1;1025501_1;1025502_1;1025503_1;1025504_1;1025505_1;1025506_1</t>
@@ -1024,7 +1039,8 @@
     <t>游客品质邀请函</t>
   </si>
   <si>
-    <t>用于指定生成某类品质游客的道具</t>
+    <t>用于指定生成某类品质游客的道具
+获取途径：商城购买</t>
   </si>
   <si>
     <t>1024019_1;1024020_1;1024021_1;1024022_1;1024023_1</t>
@@ -1033,7 +1049,8 @@
     <t>联盟任务补充券</t>
   </si>
   <si>
-    <t>用于补充联盟任务的道具</t>
+    <t>用于补充联盟任务的道具
+获取途径：钻石购买</t>
   </si>
   <si>
     <t>试玩体力</t>
@@ -1780,7 +1797,8 @@
     <t>daoju_tzj.png</t>
   </si>
   <si>
-    <t>用于主动匹配所消耗的道具</t>
+    <t>用于主动匹配所消耗的道具
+获取途径：商城购买</t>
   </si>
   <si>
     <t>白色宝石箱</t>
@@ -1789,7 +1807,8 @@
     <t>daoju_baox_b.png</t>
   </si>
   <si>
-    <t>可以指定开出任意白色宝石的箱子</t>
+    <t>可以指定开出任意白色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131001_1;1131002_1;1131003_1;1131004_1;1131005_1;1131006_1</t>
@@ -1801,7 +1820,8 @@
     <t>daoju_baox_lv.png</t>
   </si>
   <si>
-    <t>可以指定开出任意绿色宝石的箱子</t>
+    <t>可以指定开出任意绿色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131101_1;1131102_1;1131103_1;1131104_1;1131105_1;1131106_1</t>
@@ -1813,7 +1833,8 @@
     <t>daoju_baox_lan.png</t>
   </si>
   <si>
-    <t>可以指定开出任意蓝色宝石的箱子</t>
+    <t>可以指定开出任意蓝色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131201_1;1131202_1;1131203_1;1131204_1;1131205_1;1131206_1</t>
@@ -1825,7 +1846,8 @@
     <t>daoju_baox_zi.png</t>
   </si>
   <si>
-    <t>可以指定开出任意紫色宝石的箱子</t>
+    <t>可以指定开出任意紫色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131301_1;1131302_1;1131303_1;1131304_1;1131305_1;1131306_1</t>
@@ -1837,7 +1859,8 @@
     <t>daoju_baox_ju.png</t>
   </si>
   <si>
-    <t>可以指定开出任意橙色宝石的箱子</t>
+    <t>可以指定开出任意橙色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131401_1;1131402_1;1131403_1;1131404_1;1131405_1;1131406_1</t>
@@ -3140,7 +3163,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3176,6 +3199,9 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6762,7 +6788,7 @@
         <v>999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" ht="21" customHeight="1" spans="1:20">
       <c r="A68" s="1">
         <v>1024008</v>
       </c>
@@ -6796,14 +6822,14 @@
       <c r="N68" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O68" s="1" t="s">
-        <v>190</v>
+      <c r="O68" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="R68" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" ht="22" customHeight="1" spans="1:20">
       <c r="A69" s="1">
         <v>1024009</v>
       </c>
@@ -6811,7 +6837,7 @@
         <v>1024009</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
@@ -6829,7 +6855,7 @@
         <v>1</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M69" s="1">
         <v>2024009</v>
@@ -6837,14 +6863,14 @@
       <c r="N69" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O69" s="1" t="s">
-        <v>192</v>
+      <c r="O69" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="R69" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="70" spans="1:20">
+    <row r="70" ht="19" customHeight="1" spans="1:20">
       <c r="A70" s="1">
         <v>1024010</v>
       </c>
@@ -6852,7 +6878,7 @@
         <v>1024010</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
@@ -6870,7 +6896,7 @@
         <v>1</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M70" s="1">
         <v>2024010</v>
@@ -6878,8 +6904,8 @@
       <c r="N70" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O70" s="1" t="s">
-        <v>194</v>
+      <c r="O70" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="R70" s="1">
         <v>999999</v>
@@ -6893,7 +6919,7 @@
         <v>1024011</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
@@ -6911,7 +6937,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M71" s="1">
         <v>2024011</v>
@@ -6920,7 +6946,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="R71" s="1">
         <v>-1</v>
@@ -6934,7 +6960,7 @@
         <v>1024012</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
@@ -6952,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M72" s="1">
         <v>2024012</v>
@@ -6961,13 +6987,13 @@
         <v>0</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="R72" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="73" spans="1:20">
+    <row r="73" ht="19" customHeight="1" spans="1:20">
       <c r="A73" s="1">
         <v>1024013</v>
       </c>
@@ -6975,7 +7001,7 @@
         <v>1024013</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -6993,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="M73" s="1">
         <v>2024013</v>
@@ -7001,14 +7027,14 @@
       <c r="N73" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O73" s="1" t="s">
-        <v>204</v>
+      <c r="O73" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="R73" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="74" spans="1:20">
+    <row r="74" ht="16" customHeight="1" spans="1:20">
       <c r="A74" s="1">
         <v>1024014</v>
       </c>
@@ -7016,7 +7042,7 @@
         <v>1024014</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -7034,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M74" s="1">
         <v>2024014</v>
@@ -7042,14 +7068,14 @@
       <c r="N74" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O74" s="1" t="s">
-        <v>207</v>
+      <c r="O74" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="R74" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="75" spans="1:20">
+    <row r="75" ht="23" customHeight="1" spans="1:20">
       <c r="A75" s="1">
         <v>1024015</v>
       </c>
@@ -7057,7 +7083,7 @@
         <v>1024015</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E75" s="1">
         <v>1</v>
@@ -7083,17 +7109,17 @@
       <c r="N75" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O75" s="1" t="s">
-        <v>209</v>
+      <c r="O75" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="R75" s="1">
         <v>999999</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1" spans="1:20">
       <c r="A76" s="1">
         <v>1024016</v>
       </c>
@@ -7101,7 +7127,7 @@
         <v>1024016</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -7127,17 +7153,17 @@
       <c r="N76" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O76" s="1" t="s">
-        <v>212</v>
+      <c r="O76" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="R76" s="1">
         <v>999999</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1" spans="1:20">
       <c r="A77" s="1">
         <v>1024017</v>
       </c>
@@ -7145,7 +7171,7 @@
         <v>1024017</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -7171,8 +7197,8 @@
       <c r="N77" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O77" s="1" t="s">
-        <v>215</v>
+      <c r="O77" s="12" t="s">
+        <v>218</v>
       </c>
       <c r="R77" s="1">
         <v>999999</v>
@@ -7186,7 +7212,7 @@
         <v>1024018</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -7204,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M78" s="1">
         <v>2024018</v>
@@ -7213,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R78" s="1">
         <v>-1</v>
@@ -7227,7 +7253,7 @@
         <v>1024019</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
@@ -7245,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M79" s="1">
         <v>2024019</v>
@@ -7254,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R79" s="1">
         <v>-1</v>
@@ -7268,7 +7294,7 @@
         <v>1024020</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -7286,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M80" s="1">
         <v>2024020</v>
@@ -7295,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="R80" s="1">
         <v>-1</v>
@@ -7309,7 +7335,7 @@
         <v>1024021</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -7327,7 +7353,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M81" s="1">
         <v>2024021</v>
@@ -7336,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R81" s="1">
         <v>-1</v>
@@ -7350,7 +7376,7 @@
         <v>1024022</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -7368,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M82" s="1">
         <v>2024022</v>
@@ -7377,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="R82" s="1">
         <v>-1</v>
@@ -7391,7 +7417,7 @@
         <v>1024023</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -7409,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M83" s="1">
         <v>2024023</v>
@@ -7418,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="R83" s="1">
         <v>-1</v>
@@ -7432,7 +7458,7 @@
         <v>1024024</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -7443,7 +7469,7 @@
       <c r="G84" s="1">
         <v>1</v>
       </c>
-      <c r="H84" s="12">
+      <c r="H84" s="13">
         <v>100300</v>
       </c>
       <c r="I84" s="1">
@@ -7456,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M84" s="1">
         <v>2024024</v>
@@ -7465,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R84" s="1">
         <v>999999</v>
@@ -7479,7 +7505,7 @@
         <v>1024024</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -7490,7 +7516,7 @@
       <c r="G85" s="1">
         <v>1</v>
       </c>
-      <c r="H85" s="12">
+      <c r="H85" s="13">
         <v>103400</v>
       </c>
       <c r="I85" s="1">
@@ -7503,7 +7529,7 @@
         <v>1</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M85" s="1">
         <v>2024025</v>
@@ -7512,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="R85" s="1">
         <v>999999</v>
@@ -7526,7 +7552,7 @@
         <v>1024024</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
@@ -7537,7 +7563,7 @@
       <c r="G86" s="1">
         <v>1</v>
       </c>
-      <c r="H86" s="13">
+      <c r="H86" s="14">
         <v>103401</v>
       </c>
       <c r="I86" s="1">
@@ -7550,7 +7576,7 @@
         <v>1</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="M86" s="1">
         <v>2024026</v>
@@ -7559,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="R86" s="1">
         <v>999999</v>
@@ -7573,7 +7599,7 @@
         <v>1024024</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -7584,7 +7610,7 @@
       <c r="G87" s="1">
         <v>1</v>
       </c>
-      <c r="H87" s="13">
+      <c r="H87" s="14">
         <v>101400</v>
       </c>
       <c r="I87" s="1">
@@ -7597,7 +7623,7 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M87" s="1">
         <v>2024027</v>
@@ -7606,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="R87" s="1">
         <v>999999</v>
@@ -7620,7 +7646,7 @@
         <v>1024024</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -7631,7 +7657,7 @@
       <c r="G88" s="1">
         <v>1</v>
       </c>
-      <c r="H88" s="13">
+      <c r="H88" s="14">
         <v>103500</v>
       </c>
       <c r="I88" s="1">
@@ -7644,7 +7670,7 @@
         <v>1</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M88" s="1">
         <v>2024028</v>
@@ -7653,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="R88" s="1">
         <v>999999</v>
@@ -7667,7 +7693,7 @@
         <v>1024024</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -7678,7 +7704,7 @@
       <c r="G89" s="1">
         <v>1</v>
       </c>
-      <c r="H89" s="13">
+      <c r="H89" s="14">
         <v>103501</v>
       </c>
       <c r="I89" s="1">
@@ -7691,7 +7717,7 @@
         <v>1</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M89" s="1">
         <v>2024029</v>
@@ -7700,7 +7726,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="R89" s="1">
         <v>999999</v>
@@ -7714,7 +7740,7 @@
         <v>1024024</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -7725,7 +7751,7 @@
       <c r="G90" s="1">
         <v>1</v>
       </c>
-      <c r="H90" s="13">
+      <c r="H90" s="14">
         <v>100700</v>
       </c>
       <c r="I90" s="1">
@@ -7738,7 +7764,7 @@
         <v>1</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M90" s="1">
         <v>2024030</v>
@@ -7747,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="R90" s="1">
         <v>999999</v>
@@ -7761,7 +7787,7 @@
         <v>1024024</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E91" s="1">
         <v>2</v>
@@ -7772,7 +7798,7 @@
       <c r="G91" s="1">
         <v>1</v>
       </c>
-      <c r="H91" s="13">
+      <c r="H91" s="14">
         <v>103700</v>
       </c>
       <c r="I91" s="1">
@@ -7785,7 +7811,7 @@
         <v>1</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M91" s="1">
         <v>2024031</v>
@@ -7794,7 +7820,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="R91" s="1">
         <v>999999</v>
@@ -7808,7 +7834,7 @@
         <v>1024024</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -7819,7 +7845,7 @@
       <c r="G92" s="1">
         <v>1</v>
       </c>
-      <c r="H92" s="13">
+      <c r="H92" s="14">
         <v>103600</v>
       </c>
       <c r="I92" s="1">
@@ -7832,7 +7858,7 @@
         <v>1</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M92" s="1">
         <v>2024032</v>
@@ -7841,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R92" s="1">
         <v>999999</v>
@@ -7855,7 +7881,7 @@
         <v>1024024</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E93" s="1">
         <v>2</v>
@@ -7866,7 +7892,7 @@
       <c r="G93" s="1">
         <v>1</v>
       </c>
-      <c r="H93" s="13">
+      <c r="H93" s="14">
         <v>101700</v>
       </c>
       <c r="I93" s="1">
@@ -7879,7 +7905,7 @@
         <v>1</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M93" s="1">
         <v>2024033</v>
@@ -7888,7 +7914,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="R93" s="1">
         <v>999999</v>
@@ -7902,7 +7928,7 @@
         <v>1024025</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -7920,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M94" s="1">
         <v>2024034</v>
@@ -7929,7 +7955,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="R94" s="1">
         <v>999999</v>
@@ -7943,7 +7969,7 @@
         <v>1024026</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E95" s="1">
         <v>2</v>
@@ -7961,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M95" s="1">
         <v>2024035</v>
@@ -7970,7 +7996,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="R95" s="1">
         <v>999999</v>
@@ -7984,7 +8010,7 @@
         <v>1024027</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -8002,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="M96" s="1">
         <v>2024036</v>
@@ -8011,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R96" s="1">
         <v>999999</v>
@@ -8025,7 +8051,7 @@
         <v>1024028</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E97" s="1">
         <v>2</v>
@@ -8043,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M97" s="1">
         <v>2024037</v>
@@ -8052,7 +8078,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="R97" s="1">
         <v>999999</v>
@@ -8066,7 +8092,7 @@
         <v>1024029</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -8084,7 +8110,7 @@
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M98" s="1">
         <v>2024038</v>
@@ -8093,7 +8119,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="R98" s="1">
         <v>999999</v>
@@ -8107,7 +8133,7 @@
         <v>1024030</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -8125,7 +8151,7 @@
         <v>1</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="M99" s="1">
         <v>2024039</v>
@@ -8134,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="R99" s="1">
         <v>999999</v>
@@ -8148,7 +8174,7 @@
         <v>1024024</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -8159,7 +8185,7 @@
       <c r="G100" s="1">
         <v>1</v>
       </c>
-      <c r="H100" s="13">
+      <c r="H100" s="14">
         <v>101200</v>
       </c>
       <c r="I100" s="1">
@@ -8172,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M100" s="1">
         <v>2024040</v>
@@ -8181,7 +8207,7 @@
         <v>0</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="R100" s="1">
         <v>999999</v>
@@ -8227,7 +8253,7 @@
         <v>999999</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -8270,7 +8296,7 @@
         <v>999999</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -8313,7 +8339,7 @@
         <v>999999</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -8356,7 +8382,7 @@
         <v>999999</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -8399,7 +8425,7 @@
         <v>999999</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -8442,7 +8468,7 @@
         <v>999999</v>
       </c>
       <c r="S106" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -8485,7 +8511,7 @@
         <v>999999</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -8528,7 +8554,7 @@
         <v>999999</v>
       </c>
       <c r="S108" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -8571,7 +8597,7 @@
         <v>999999</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -8614,7 +8640,7 @@
         <v>999999</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -8657,7 +8683,7 @@
         <v>999999</v>
       </c>
       <c r="S111" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -8700,7 +8726,7 @@
         <v>999999</v>
       </c>
       <c r="S112" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -8743,7 +8769,7 @@
         <v>999999</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -8786,7 +8812,7 @@
         <v>999999</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -8829,7 +8855,7 @@
         <v>999999</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -8872,7 +8898,7 @@
         <v>999999</v>
       </c>
       <c r="S116" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -8915,7 +8941,7 @@
         <v>999999</v>
       </c>
       <c r="S117" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -8958,7 +8984,7 @@
         <v>999999</v>
       </c>
       <c r="S118" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -9001,7 +9027,7 @@
         <v>999999</v>
       </c>
       <c r="S119" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -9044,7 +9070,7 @@
         <v>999999</v>
       </c>
       <c r="S120" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -9087,7 +9113,7 @@
         <v>999999</v>
       </c>
       <c r="S121" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -9130,7 +9156,7 @@
         <v>999999</v>
       </c>
       <c r="S122" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -9173,7 +9199,7 @@
         <v>999999</v>
       </c>
       <c r="S123" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -9216,7 +9242,7 @@
         <v>999999</v>
       </c>
       <c r="S124" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -9259,7 +9285,7 @@
         <v>999999</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -9302,7 +9328,7 @@
         <v>999999</v>
       </c>
       <c r="S126" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -9345,7 +9371,7 @@
         <v>999999</v>
       </c>
       <c r="S127" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -9388,7 +9414,7 @@
         <v>999999</v>
       </c>
       <c r="S128" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -9431,7 +9457,7 @@
         <v>999999</v>
       </c>
       <c r="S129" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -9474,7 +9500,7 @@
         <v>999999</v>
       </c>
       <c r="S130" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -9485,7 +9511,7 @@
         <v>1024061</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E131" s="1">
         <v>1</v>
@@ -9509,7 +9535,7 @@
         <v>0</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="R131" s="1">
         <v>999999</v>
@@ -9523,7 +9549,7 @@
         <v>1024062</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -9547,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="R132" s="1">
         <v>999999</v>
@@ -9561,7 +9587,7 @@
         <v>1024063</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -9585,7 +9611,7 @@
         <v>0</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="R133" s="1">
         <v>999999</v>
@@ -9599,7 +9625,7 @@
         <v>1024064</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -9623,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="R134" s="1">
         <v>999999</v>
@@ -9637,7 +9663,7 @@
         <v>1024065</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -9661,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="O135" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="R135" s="1">
         <v>999999</v>
@@ -9675,7 +9701,7 @@
         <v>1024024</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -9686,8 +9712,8 @@
       <c r="G136" s="1">
         <v>1</v>
       </c>
-      <c r="H136" s="12" t="s">
-        <v>310</v>
+      <c r="H136" s="13" t="s">
+        <v>313</v>
       </c>
       <c r="I136" s="1">
         <v>1</v>
@@ -9699,7 +9725,7 @@
         <v>1</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M136" s="1">
         <v>2024076</v>
@@ -9708,7 +9734,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="R136" s="1">
         <v>999999</v>
@@ -9722,7 +9748,7 @@
         <v>1024024</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -9733,8 +9759,8 @@
       <c r="G137" s="1">
         <v>1</v>
       </c>
-      <c r="H137" s="12" t="s">
-        <v>313</v>
+      <c r="H137" s="13" t="s">
+        <v>316</v>
       </c>
       <c r="I137" s="1">
         <v>1</v>
@@ -9746,7 +9772,7 @@
         <v>1</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M137" s="1">
         <v>2024077</v>
@@ -9755,7 +9781,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="R137" s="1">
         <v>999999</v>
@@ -9769,7 +9795,7 @@
         <v>1024024</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -9780,8 +9806,8 @@
       <c r="G138" s="1">
         <v>1</v>
       </c>
-      <c r="H138" s="13" t="s">
-        <v>316</v>
+      <c r="H138" s="14" t="s">
+        <v>319</v>
       </c>
       <c r="I138" s="1">
         <v>1</v>
@@ -9793,7 +9819,7 @@
         <v>1</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="M138" s="1">
         <v>2024078</v>
@@ -9802,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="R138" s="1">
         <v>999999</v>
@@ -9816,7 +9842,7 @@
         <v>1024024</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -9827,8 +9853,8 @@
       <c r="G139" s="1">
         <v>1</v>
       </c>
-      <c r="H139" s="13" t="s">
-        <v>319</v>
+      <c r="H139" s="14" t="s">
+        <v>322</v>
       </c>
       <c r="I139" s="1">
         <v>1</v>
@@ -9840,7 +9866,7 @@
         <v>1</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M139" s="1">
         <v>2024079</v>
@@ -9849,7 +9875,7 @@
         <v>0</v>
       </c>
       <c r="O139" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="R139" s="1">
         <v>999999</v>
@@ -9863,7 +9889,7 @@
         <v>1024024</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -9874,8 +9900,8 @@
       <c r="G140" s="1">
         <v>1</v>
       </c>
-      <c r="H140" s="13" t="s">
-        <v>322</v>
+      <c r="H140" s="14" t="s">
+        <v>325</v>
       </c>
       <c r="I140" s="1">
         <v>1</v>
@@ -9887,7 +9913,7 @@
         <v>1</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M140" s="1">
         <v>2024080</v>
@@ -9896,7 +9922,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="R140" s="1">
         <v>999999</v>
@@ -9910,7 +9936,7 @@
         <v>1024024</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -9921,8 +9947,8 @@
       <c r="G141" s="1">
         <v>1</v>
       </c>
-      <c r="H141" s="13" t="s">
-        <v>325</v>
+      <c r="H141" s="14" t="s">
+        <v>328</v>
       </c>
       <c r="I141" s="1">
         <v>1</v>
@@ -9934,7 +9960,7 @@
         <v>1</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M141" s="1">
         <v>2024081</v>
@@ -9943,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="O141" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="R141" s="1">
         <v>999999</v>
@@ -9957,7 +9983,7 @@
         <v>1024024</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -9968,8 +9994,8 @@
       <c r="G142" s="1">
         <v>1</v>
       </c>
-      <c r="H142" s="13" t="s">
-        <v>328</v>
+      <c r="H142" s="14" t="s">
+        <v>331</v>
       </c>
       <c r="I142" s="1">
         <v>1</v>
@@ -9981,7 +10007,7 @@
         <v>1</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M142" s="1">
         <v>2024082</v>
@@ -9990,7 +10016,7 @@
         <v>0</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="R142" s="1">
         <v>999999</v>
@@ -10004,7 +10030,7 @@
         <v>1025101</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -10022,7 +10048,7 @@
         <v>0</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M143" s="1">
         <v>2025101</v>
@@ -10031,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="R143" s="1">
         <v>-1</v>
@@ -10045,7 +10071,7 @@
         <v>1025102</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -10063,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="M144" s="1">
         <v>2025102</v>
@@ -10072,7 +10098,7 @@
         <v>0</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="R144" s="1">
         <v>-1</v>
@@ -10086,7 +10112,7 @@
         <v>1025103</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -10104,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M145" s="1">
         <v>2025103</v>
@@ -10113,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="R145" s="1">
         <v>-1</v>
@@ -10127,7 +10153,7 @@
         <v>1025104</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E146" s="1">
         <v>2</v>
@@ -10145,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M146" s="1">
         <v>2025104</v>
@@ -10154,7 +10180,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="R146" s="1">
         <v>-1</v>
@@ -10168,7 +10194,7 @@
         <v>1025105</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -10186,7 +10212,7 @@
         <v>0</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M147" s="1">
         <v>2025105</v>
@@ -10195,7 +10221,7 @@
         <v>0</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="R147" s="1">
         <v>-1</v>
@@ -10209,7 +10235,7 @@
         <v>1025106</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -10227,7 +10253,7 @@
         <v>0</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="M148" s="1">
         <v>2025106</v>
@@ -10236,7 +10262,7 @@
         <v>0</v>
       </c>
       <c r="O148" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="R148" s="1">
         <v>-1</v>
@@ -10250,7 +10276,7 @@
         <v>1025201</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -10268,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M149" s="1">
         <v>2025201</v>
@@ -10277,7 +10303,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="R149" s="1">
         <v>-1</v>
@@ -10291,7 +10317,7 @@
         <v>1025202</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -10309,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M150" s="1">
         <v>2025202</v>
@@ -10318,7 +10344,7 @@
         <v>0</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="R150" s="1">
         <v>-1</v>
@@ -10332,7 +10358,7 @@
         <v>1025203</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -10350,7 +10376,7 @@
         <v>0</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M151" s="1">
         <v>2025203</v>
@@ -10359,7 +10385,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="R151" s="1">
         <v>-1</v>
@@ -10373,7 +10399,7 @@
         <v>1025204</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -10391,7 +10417,7 @@
         <v>0</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="M152" s="1">
         <v>2025204</v>
@@ -10400,7 +10426,7 @@
         <v>0</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="R152" s="1">
         <v>-1</v>
@@ -10414,7 +10440,7 @@
         <v>1025205</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -10432,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M153" s="1">
         <v>2025205</v>
@@ -10441,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="R153" s="1">
         <v>-1</v>
@@ -10455,7 +10481,7 @@
         <v>1025206</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -10473,7 +10499,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="M154" s="1">
         <v>2025206</v>
@@ -10482,7 +10508,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="R154" s="1">
         <v>-1</v>
@@ -10496,7 +10522,7 @@
         <v>1025301</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -10514,7 +10540,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M155" s="1">
         <v>2025301</v>
@@ -10523,7 +10549,7 @@
         <v>0</v>
       </c>
       <c r="O155" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="R155" s="1">
         <v>-1</v>
@@ -10537,7 +10563,7 @@
         <v>1025302</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -10555,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M156" s="1">
         <v>2025302</v>
@@ -10564,7 +10590,7 @@
         <v>0</v>
       </c>
       <c r="O156" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="R156" s="1">
         <v>-1</v>
@@ -10578,7 +10604,7 @@
         <v>1025303</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -10596,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M157" s="1">
         <v>2025303</v>
@@ -10605,7 +10631,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="R157" s="1">
         <v>-1</v>
@@ -10619,7 +10645,7 @@
         <v>1025304</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -10637,7 +10663,7 @@
         <v>0</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M158" s="1">
         <v>2025304</v>
@@ -10646,7 +10672,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="R158" s="1">
         <v>-1</v>
@@ -10660,7 +10686,7 @@
         <v>1025305</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E159" s="1">
         <v>2</v>
@@ -10678,7 +10704,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M159" s="1">
         <v>2025305</v>
@@ -10687,7 +10713,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="R159" s="1">
         <v>-1</v>
@@ -10701,7 +10727,7 @@
         <v>1025306</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E160" s="1">
         <v>2</v>
@@ -10719,7 +10745,7 @@
         <v>0</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M160" s="1">
         <v>2025306</v>
@@ -10728,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="R160" s="1">
         <v>-1</v>
@@ -10742,7 +10768,7 @@
         <v>1025401</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E161" s="1">
         <v>2</v>
@@ -10760,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M161" s="1">
         <v>2025401</v>
@@ -10769,7 +10795,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="R161" s="1">
         <v>-1</v>
@@ -10783,7 +10809,7 @@
         <v>1025402</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E162" s="1">
         <v>2</v>
@@ -10801,7 +10827,7 @@
         <v>0</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M162" s="1">
         <v>2025402</v>
@@ -10810,7 +10836,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="R162" s="1">
         <v>-1</v>
@@ -10824,7 +10850,7 @@
         <v>1025403</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E163" s="1">
         <v>2</v>
@@ -10842,7 +10868,7 @@
         <v>0</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M163" s="1">
         <v>2025403</v>
@@ -10851,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="O163" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="R163" s="1">
         <v>-1</v>
@@ -10865,7 +10891,7 @@
         <v>1025404</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E164" s="1">
         <v>2</v>
@@ -10883,7 +10909,7 @@
         <v>0</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M164" s="1">
         <v>2025404</v>
@@ -10892,7 +10918,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="R164" s="1">
         <v>-1</v>
@@ -10906,7 +10932,7 @@
         <v>1025405</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E165" s="1">
         <v>2</v>
@@ -10924,7 +10950,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M165" s="1">
         <v>2025405</v>
@@ -10933,7 +10959,7 @@
         <v>0</v>
       </c>
       <c r="O165" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="R165" s="1">
         <v>-1</v>
@@ -10947,7 +10973,7 @@
         <v>1025406</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E166" s="1">
         <v>2</v>
@@ -10965,7 +10991,7 @@
         <v>0</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M166" s="1">
         <v>2025406</v>
@@ -10974,7 +11000,7 @@
         <v>0</v>
       </c>
       <c r="O166" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="R166" s="1">
         <v>-1</v>
@@ -10988,7 +11014,7 @@
         <v>1025501</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E167" s="1">
         <v>2</v>
@@ -11006,7 +11032,7 @@
         <v>0</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M167" s="1">
         <v>2025501</v>
@@ -11015,7 +11041,7 @@
         <v>0</v>
       </c>
       <c r="O167" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="R167" s="1">
         <v>-1</v>
@@ -11029,7 +11055,7 @@
         <v>1025502</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E168" s="1">
         <v>2</v>
@@ -11047,7 +11073,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M168" s="1">
         <v>2025502</v>
@@ -11056,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="O168" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="R168" s="1">
         <v>-1</v>
@@ -11070,7 +11096,7 @@
         <v>1025503</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E169" s="1">
         <v>2</v>
@@ -11088,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M169" s="1">
         <v>2025503</v>
@@ -11097,7 +11123,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="R169" s="1">
         <v>-1</v>
@@ -11111,7 +11137,7 @@
         <v>1025504</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E170" s="1">
         <v>2</v>
@@ -11129,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M170" s="1">
         <v>2025504</v>
@@ -11138,7 +11164,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="R170" s="1">
         <v>-1</v>
@@ -11152,7 +11178,7 @@
         <v>1025505</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E171" s="1">
         <v>2</v>
@@ -11170,7 +11196,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M171" s="1">
         <v>2025505</v>
@@ -11179,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="O171" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="R171" s="1">
         <v>-1</v>
@@ -11193,7 +11219,7 @@
         <v>1025506</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E172" s="1">
         <v>2</v>
@@ -11211,7 +11237,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M172" s="1">
         <v>2025506</v>
@@ -11220,7 +11246,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="R172" s="1">
         <v>-1</v>
@@ -11252,8 +11278,8 @@
       <c r="K173" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L173" s="14" t="s">
-        <v>391</v>
+      <c r="L173" s="15" t="s">
+        <v>394</v>
       </c>
       <c r="M173" s="1">
         <v>2125101</v>
@@ -11295,8 +11321,8 @@
       <c r="K174" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L174" s="14" t="s">
-        <v>392</v>
+      <c r="L174" s="15" t="s">
+        <v>395</v>
       </c>
       <c r="M174" s="1">
         <v>2125102</v>
@@ -11338,8 +11364,8 @@
       <c r="K175" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L175" s="14" t="s">
-        <v>393</v>
+      <c r="L175" s="15" t="s">
+        <v>396</v>
       </c>
       <c r="M175" s="1">
         <v>2125103</v>
@@ -11381,8 +11407,8 @@
       <c r="K176" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L176" s="14" t="s">
-        <v>394</v>
+      <c r="L176" s="15" t="s">
+        <v>397</v>
       </c>
       <c r="M176" s="1">
         <v>2125104</v>
@@ -11424,8 +11450,8 @@
       <c r="K177" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L177" s="14" t="s">
-        <v>395</v>
+      <c r="L177" s="15" t="s">
+        <v>398</v>
       </c>
       <c r="M177" s="1">
         <v>2125105</v>
@@ -11467,8 +11493,8 @@
       <c r="K178" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L178" s="14" t="s">
-        <v>396</v>
+      <c r="L178" s="15" t="s">
+        <v>399</v>
       </c>
       <c r="M178" s="1">
         <v>2125106</v>
@@ -11510,8 +11536,8 @@
       <c r="K179" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L179" s="14" t="s">
-        <v>397</v>
+      <c r="L179" s="15" t="s">
+        <v>400</v>
       </c>
       <c r="M179" s="1">
         <v>2125201</v>
@@ -11553,8 +11579,8 @@
       <c r="K180" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L180" s="14" t="s">
-        <v>398</v>
+      <c r="L180" s="15" t="s">
+        <v>401</v>
       </c>
       <c r="M180" s="1">
         <v>2125202</v>
@@ -11596,8 +11622,8 @@
       <c r="K181" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L181" s="14" t="s">
-        <v>399</v>
+      <c r="L181" s="15" t="s">
+        <v>402</v>
       </c>
       <c r="M181" s="1">
         <v>2125203</v>
@@ -11639,8 +11665,8 @@
       <c r="K182" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L182" s="14" t="s">
-        <v>400</v>
+      <c r="L182" s="15" t="s">
+        <v>403</v>
       </c>
       <c r="M182" s="1">
         <v>2125204</v>
@@ -11682,8 +11708,8 @@
       <c r="K183" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L183" s="14" t="s">
-        <v>401</v>
+      <c r="L183" s="15" t="s">
+        <v>404</v>
       </c>
       <c r="M183" s="1">
         <v>2125205</v>
@@ -11725,8 +11751,8 @@
       <c r="K184" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L184" s="14" t="s">
-        <v>402</v>
+      <c r="L184" s="15" t="s">
+        <v>405</v>
       </c>
       <c r="M184" s="1">
         <v>2125206</v>
@@ -11768,8 +11794,8 @@
       <c r="K185" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L185" s="14" t="s">
-        <v>403</v>
+      <c r="L185" s="15" t="s">
+        <v>406</v>
       </c>
       <c r="M185" s="1">
         <v>2125301</v>
@@ -11811,8 +11837,8 @@
       <c r="K186" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L186" s="14" t="s">
-        <v>404</v>
+      <c r="L186" s="15" t="s">
+        <v>407</v>
       </c>
       <c r="M186" s="1">
         <v>2125302</v>
@@ -11854,8 +11880,8 @@
       <c r="K187" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L187" s="14" t="s">
-        <v>405</v>
+      <c r="L187" s="15" t="s">
+        <v>408</v>
       </c>
       <c r="M187" s="1">
         <v>2125303</v>
@@ -11897,8 +11923,8 @@
       <c r="K188" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L188" s="14" t="s">
-        <v>406</v>
+      <c r="L188" s="15" t="s">
+        <v>409</v>
       </c>
       <c r="M188" s="1">
         <v>2125304</v>
@@ -11940,8 +11966,8 @@
       <c r="K189" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L189" s="14" t="s">
-        <v>407</v>
+      <c r="L189" s="15" t="s">
+        <v>410</v>
       </c>
       <c r="M189" s="1">
         <v>2125305</v>
@@ -11983,8 +12009,8 @@
       <c r="K190" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L190" s="14" t="s">
-        <v>408</v>
+      <c r="L190" s="15" t="s">
+        <v>411</v>
       </c>
       <c r="M190" s="1">
         <v>2125306</v>
@@ -12026,8 +12052,8 @@
       <c r="K191" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L191" s="14" t="s">
-        <v>409</v>
+      <c r="L191" s="15" t="s">
+        <v>412</v>
       </c>
       <c r="M191" s="1">
         <v>2125401</v>
@@ -12069,8 +12095,8 @@
       <c r="K192" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L192" s="14" t="s">
-        <v>410</v>
+      <c r="L192" s="15" t="s">
+        <v>413</v>
       </c>
       <c r="M192" s="1">
         <v>2125402</v>
@@ -12112,8 +12138,8 @@
       <c r="K193" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L193" s="14" t="s">
-        <v>411</v>
+      <c r="L193" s="15" t="s">
+        <v>414</v>
       </c>
       <c r="M193" s="1">
         <v>2125403</v>
@@ -12155,8 +12181,8 @@
       <c r="K194" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L194" s="14" t="s">
-        <v>412</v>
+      <c r="L194" s="15" t="s">
+        <v>415</v>
       </c>
       <c r="M194" s="1">
         <v>2125404</v>
@@ -12198,8 +12224,8 @@
       <c r="K195" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L195" s="14" t="s">
-        <v>413</v>
+      <c r="L195" s="15" t="s">
+        <v>416</v>
       </c>
       <c r="M195" s="1">
         <v>2125405</v>
@@ -12241,8 +12267,8 @@
       <c r="K196" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L196" s="14" t="s">
-        <v>414</v>
+      <c r="L196" s="15" t="s">
+        <v>417</v>
       </c>
       <c r="M196" s="1">
         <v>2125406</v>
@@ -12284,8 +12310,8 @@
       <c r="K197" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L197" s="14" t="s">
-        <v>415</v>
+      <c r="L197" s="15" t="s">
+        <v>418</v>
       </c>
       <c r="M197" s="1">
         <v>2125501</v>
@@ -12327,8 +12353,8 @@
       <c r="K198" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L198" s="14" t="s">
-        <v>416</v>
+      <c r="L198" s="15" t="s">
+        <v>419</v>
       </c>
       <c r="M198" s="1">
         <v>2125502</v>
@@ -12370,8 +12396,8 @@
       <c r="K199" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L199" s="14" t="s">
-        <v>417</v>
+      <c r="L199" s="15" t="s">
+        <v>420</v>
       </c>
       <c r="M199" s="1">
         <v>2125503</v>
@@ -12413,8 +12439,8 @@
       <c r="K200" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L200" s="14" t="s">
-        <v>418</v>
+      <c r="L200" s="15" t="s">
+        <v>421</v>
       </c>
       <c r="M200" s="1">
         <v>2125504</v>
@@ -12456,8 +12482,8 @@
       <c r="K201" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L201" s="14" t="s">
-        <v>419</v>
+      <c r="L201" s="15" t="s">
+        <v>422</v>
       </c>
       <c r="M201" s="1">
         <v>2125505</v>
@@ -12499,8 +12525,8 @@
       <c r="K202" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L202" s="14" t="s">
-        <v>420</v>
+      <c r="L202" s="15" t="s">
+        <v>423</v>
       </c>
       <c r="M202" s="1">
         <v>2125506</v>
@@ -12524,7 +12550,7 @@
         <v>1026001</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E203" s="1">
         <v>2</v>
@@ -12542,7 +12568,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M203" s="1">
         <v>2026001</v>
@@ -12551,7 +12577,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="R203" s="1">
         <v>-1</v>
@@ -12565,7 +12591,7 @@
         <v>1026002</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E204" s="1">
         <v>2</v>
@@ -12583,7 +12609,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M204" s="1">
         <v>2026002</v>
@@ -12592,7 +12618,7 @@
         <v>0</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R204" s="1">
         <v>-1</v>
@@ -12606,7 +12632,7 @@
         <v>1026101</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E205" s="1">
         <v>2</v>
@@ -12624,7 +12650,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M205" s="1">
         <v>2026101</v>
@@ -12633,7 +12659,7 @@
         <v>0</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="R205" s="1">
         <v>-1</v>
@@ -12647,7 +12673,7 @@
         <v>1026102</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E206" s="1">
         <v>2</v>
@@ -12665,7 +12691,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M206" s="1">
         <v>2026102</v>
@@ -12674,7 +12700,7 @@
         <v>0</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="R206" s="1">
         <v>-1</v>
@@ -12688,7 +12714,7 @@
         <v>1026201</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E207" s="1">
         <v>2</v>
@@ -12706,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M207" s="1">
         <v>2026201</v>
@@ -12715,7 +12741,7 @@
         <v>0</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="R207" s="1">
         <v>-1</v>
@@ -12729,7 +12755,7 @@
         <v>1026202</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E208" s="1">
         <v>2</v>
@@ -12747,7 +12773,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M208" s="1">
         <v>2026202</v>
@@ -12756,7 +12782,7 @@
         <v>0</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="R208" s="1">
         <v>-1</v>
@@ -12770,7 +12796,7 @@
         <v>1026301</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E209" s="1">
         <v>2</v>
@@ -12788,7 +12814,7 @@
         <v>0</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M209" s="1">
         <v>2026301</v>
@@ -12797,7 +12823,7 @@
         <v>0</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="R209" s="1">
         <v>-1</v>
@@ -12811,7 +12837,7 @@
         <v>1026302</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E210" s="1">
         <v>2</v>
@@ -12829,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M210" s="1">
         <v>2026302</v>
@@ -12838,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="R210" s="1">
         <v>-1</v>
@@ -12852,7 +12878,7 @@
         <v>1026401</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E211" s="1">
         <v>2</v>
@@ -12870,7 +12896,7 @@
         <v>0</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M211" s="1">
         <v>2026401</v>
@@ -12879,7 +12905,7 @@
         <v>0</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="R211" s="1">
         <v>-1</v>
@@ -12893,7 +12919,7 @@
         <v>1026402</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E212" s="1">
         <v>2</v>
@@ -12911,7 +12937,7 @@
         <v>0</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M212" s="1">
         <v>2026402</v>
@@ -12920,7 +12946,7 @@
         <v>0</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R212" s="1">
         <v>-1</v>
@@ -12934,7 +12960,7 @@
         <v>1027001</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E213" s="1">
         <v>2</v>
@@ -12952,7 +12978,7 @@
         <v>0</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="M213" s="1">
         <v>2027001</v>
@@ -12961,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="R213" s="1">
         <v>-1</v>
@@ -12975,7 +13001,7 @@
         <v>1027002</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E214" s="1">
         <v>2</v>
@@ -12993,7 +13019,7 @@
         <v>0</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M214" s="1">
         <v>2027002</v>
@@ -13002,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="R214" s="1">
         <v>-1</v>
@@ -13016,7 +13042,7 @@
         <v>1027101</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E215" s="1">
         <v>2</v>
@@ -13034,7 +13060,7 @@
         <v>0</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M215" s="1">
         <v>2027101</v>
@@ -13043,7 +13069,7 @@
         <v>0</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="R215" s="1">
         <v>-1</v>
@@ -13057,7 +13083,7 @@
         <v>1027102</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E216" s="1">
         <v>2</v>
@@ -13075,7 +13101,7 @@
         <v>0</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M216" s="1">
         <v>2027102</v>
@@ -13084,7 +13110,7 @@
         <v>0</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="R216" s="1">
         <v>-1</v>
@@ -13098,7 +13124,7 @@
         <v>1027201</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E217" s="1">
         <v>2</v>
@@ -13116,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M217" s="1">
         <v>2027201</v>
@@ -13125,7 +13151,7 @@
         <v>0</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="R217" s="1">
         <v>-1</v>
@@ -13139,7 +13165,7 @@
         <v>1027202</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E218" s="1">
         <v>2</v>
@@ -13157,7 +13183,7 @@
         <v>0</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M218" s="1">
         <v>2027202</v>
@@ -13166,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="R218" s="1">
         <v>-1</v>
@@ -13180,7 +13206,7 @@
         <v>1027301</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E219" s="1">
         <v>2</v>
@@ -13198,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M219" s="1">
         <v>2027301</v>
@@ -13207,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="R219" s="1">
         <v>-1</v>
@@ -13221,7 +13247,7 @@
         <v>1027302</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E220" s="1">
         <v>2</v>
@@ -13239,7 +13265,7 @@
         <v>0</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M220" s="1">
         <v>2027302</v>
@@ -13248,7 +13274,7 @@
         <v>0</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="R220" s="1">
         <v>-1</v>
@@ -13262,7 +13288,7 @@
         <v>1027401</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E221" s="1">
         <v>2</v>
@@ -13280,7 +13306,7 @@
         <v>0</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M221" s="1">
         <v>2027401</v>
@@ -13289,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="R221" s="1">
         <v>-1</v>
@@ -13303,7 +13329,7 @@
         <v>1027402</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E222" s="1">
         <v>2</v>
@@ -13321,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M222" s="1">
         <v>2027402</v>
@@ -13330,7 +13356,7 @@
         <v>0</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="R222" s="1">
         <v>-1</v>
@@ -13344,7 +13370,7 @@
         <v>1028001</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E223" s="1">
         <v>2</v>
@@ -13362,7 +13388,7 @@
         <v>0</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M223" s="1">
         <v>2028001</v>
@@ -13371,7 +13397,7 @@
         <v>0</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="R223" s="1">
         <v>-1</v>
@@ -13385,7 +13411,7 @@
         <v>1028002</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E224" s="1">
         <v>2</v>
@@ -13403,7 +13429,7 @@
         <v>0</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M224" s="1">
         <v>2028002</v>
@@ -13412,7 +13438,7 @@
         <v>0</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="R224" s="1">
         <v>-1</v>
@@ -13426,7 +13452,7 @@
         <v>1028101</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E225" s="1">
         <v>2</v>
@@ -13444,7 +13470,7 @@
         <v>0</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M225" s="1">
         <v>2028101</v>
@@ -13453,7 +13479,7 @@
         <v>0</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="R225" s="1">
         <v>-1</v>
@@ -13467,7 +13493,7 @@
         <v>1028102</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E226" s="1">
         <v>2</v>
@@ -13485,7 +13511,7 @@
         <v>0</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M226" s="1">
         <v>2028102</v>
@@ -13494,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="R226" s="1">
         <v>-1</v>
@@ -13508,7 +13534,7 @@
         <v>1028201</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E227" s="1">
         <v>2</v>
@@ -13526,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M227" s="1">
         <v>2028201</v>
@@ -13535,7 +13561,7 @@
         <v>0</v>
       </c>
       <c r="O227" s="1" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="R227" s="1">
         <v>-1</v>
@@ -13549,7 +13575,7 @@
         <v>1028202</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E228" s="1">
         <v>2</v>
@@ -13567,7 +13593,7 @@
         <v>0</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M228" s="1">
         <v>2028202</v>
@@ -13576,7 +13602,7 @@
         <v>0</v>
       </c>
       <c r="O228" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="R228" s="1">
         <v>-1</v>
@@ -13590,7 +13616,7 @@
         <v>1028301</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E229" s="1">
         <v>2</v>
@@ -13608,7 +13634,7 @@
         <v>0</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M229" s="1">
         <v>2028301</v>
@@ -13617,7 +13643,7 @@
         <v>0</v>
       </c>
       <c r="O229" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="R229" s="1">
         <v>-1</v>
@@ -13631,7 +13657,7 @@
         <v>1028302</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E230" s="1">
         <v>2</v>
@@ -13649,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M230" s="1">
         <v>2028302</v>
@@ -13658,7 +13684,7 @@
         <v>0</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="R230" s="1">
         <v>-1</v>
@@ -13672,7 +13698,7 @@
         <v>1028401</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E231" s="1">
         <v>2</v>
@@ -13690,7 +13716,7 @@
         <v>0</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M231" s="1">
         <v>2028401</v>
@@ -13699,7 +13725,7 @@
         <v>0</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="R231" s="1">
         <v>-1</v>
@@ -13713,7 +13739,7 @@
         <v>1028402</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E232" s="1">
         <v>2</v>
@@ -13731,7 +13757,7 @@
         <v>0</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M232" s="1">
         <v>2028402</v>
@@ -13740,7 +13766,7 @@
         <v>0</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="R232" s="1">
         <v>-1</v>
@@ -13773,7 +13799,7 @@
         <v>1</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M233" s="1">
         <v>2126001</v>
@@ -13816,7 +13842,7 @@
         <v>1</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M234" s="1">
         <v>2126002</v>
@@ -13859,7 +13885,7 @@
         <v>1</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M235" s="1">
         <v>2126101</v>
@@ -13902,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M236" s="1">
         <v>2126102</v>
@@ -13945,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M237" s="1">
         <v>2126201</v>
@@ -13988,7 +14014,7 @@
         <v>1</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M238" s="1">
         <v>2126202</v>
@@ -14031,7 +14057,7 @@
         <v>1</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M239" s="1">
         <v>2126301</v>
@@ -14074,7 +14100,7 @@
         <v>1</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M240" s="1">
         <v>2126302</v>
@@ -14117,7 +14143,7 @@
         <v>1</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M241" s="1">
         <v>2126401</v>
@@ -14160,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M242" s="1">
         <v>2126402</v>
@@ -14203,7 +14229,7 @@
         <v>1</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M243" s="1">
         <v>2127001</v>
@@ -14246,7 +14272,7 @@
         <v>1</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M244" s="1">
         <v>2127002</v>
@@ -14289,7 +14315,7 @@
         <v>1</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M245" s="1">
         <v>2127101</v>
@@ -14332,7 +14358,7 @@
         <v>1</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M246" s="1">
         <v>2127102</v>
@@ -14375,7 +14401,7 @@
         <v>1</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M247" s="1">
         <v>2127201</v>
@@ -14418,7 +14444,7 @@
         <v>1</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M248" s="1">
         <v>2127202</v>
@@ -14461,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M249" s="1">
         <v>2127301</v>
@@ -14504,7 +14530,7 @@
         <v>1</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M250" s="1">
         <v>2127302</v>
@@ -14547,7 +14573,7 @@
         <v>1</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M251" s="1">
         <v>2127401</v>
@@ -14590,7 +14616,7 @@
         <v>1</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M252" s="1">
         <v>2127402</v>
@@ -14633,7 +14659,7 @@
         <v>1</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M253" s="1">
         <v>2128001</v>
@@ -14676,7 +14702,7 @@
         <v>1</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M254" s="1">
         <v>2128002</v>
@@ -14719,7 +14745,7 @@
         <v>1</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M255" s="1">
         <v>2128101</v>
@@ -14762,7 +14788,7 @@
         <v>1</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M256" s="1">
         <v>2128102</v>
@@ -14805,7 +14831,7 @@
         <v>1</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M257" s="1">
         <v>2128201</v>
@@ -14848,7 +14874,7 @@
         <v>1</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M258" s="1">
         <v>2128202</v>
@@ -14891,7 +14917,7 @@
         <v>1</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M259" s="1">
         <v>2128301</v>
@@ -14934,7 +14960,7 @@
         <v>1</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M260" s="1">
         <v>2128302</v>
@@ -14977,7 +15003,7 @@
         <v>1</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M261" s="1">
         <v>2128401</v>
@@ -15020,7 +15046,7 @@
         <v>1</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M262" s="1">
         <v>2128402</v>
@@ -15036,7 +15062,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="263" spans="1:20">
+    <row r="263" ht="18" customHeight="1" spans="1:20">
       <c r="A263" s="1">
         <v>1130001</v>
       </c>
@@ -15044,7 +15070,7 @@
         <v>1130001</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E263" s="1">
         <v>2</v>
@@ -15062,7 +15088,7 @@
         <v>1</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M263" s="1">
         <v>2130001</v>
@@ -15070,14 +15096,14 @@
       <c r="N263" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O263" s="1" t="s">
-        <v>464</v>
+      <c r="O263" s="12" t="s">
+        <v>467</v>
       </c>
       <c r="R263" s="1">
         <v>999999</v>
       </c>
     </row>
-    <row r="264" spans="1:20">
+    <row r="264" ht="23" customHeight="1" spans="1:20">
       <c r="A264" s="1">
         <v>1130002</v>
       </c>
@@ -15085,7 +15111,7 @@
         <v>1130002</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E264" s="1">
         <v>1</v>
@@ -15103,7 +15129,7 @@
         <v>1</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M264" s="1">
         <v>2130002</v>
@@ -15111,17 +15137,17 @@
       <c r="N264" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O264" s="1" t="s">
-        <v>467</v>
+      <c r="O264" s="12" t="s">
+        <v>470</v>
       </c>
       <c r="R264" s="1">
         <v>999999</v>
       </c>
       <c r="T264" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="265" spans="1:20">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="265" ht="19" customHeight="1" spans="1:20">
       <c r="A265" s="1">
         <v>1130003</v>
       </c>
@@ -15129,7 +15155,7 @@
         <v>1130003</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E265" s="1">
         <v>1</v>
@@ -15147,7 +15173,7 @@
         <v>1</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M265" s="1">
         <v>2130003</v>
@@ -15155,17 +15181,17 @@
       <c r="N265" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O265" s="1" t="s">
-        <v>471</v>
+      <c r="O265" s="12" t="s">
+        <v>474</v>
       </c>
       <c r="R265" s="1">
         <v>999999</v>
       </c>
       <c r="T265" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="266" spans="1:20">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="266" ht="21" customHeight="1" spans="1:20">
       <c r="A266" s="1">
         <v>1130004</v>
       </c>
@@ -15173,7 +15199,7 @@
         <v>1130004</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E266" s="1">
         <v>1</v>
@@ -15191,7 +15217,7 @@
         <v>1</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M266" s="1">
         <v>2130004</v>
@@ -15199,17 +15225,17 @@
       <c r="N266" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O266" s="1" t="s">
-        <v>475</v>
+      <c r="O266" s="12" t="s">
+        <v>478</v>
       </c>
       <c r="R266" s="1">
         <v>999999</v>
       </c>
       <c r="T266" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="267" spans="1:20">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="267" ht="20" customHeight="1" spans="1:20">
       <c r="A267" s="1">
         <v>1130005</v>
       </c>
@@ -15217,7 +15243,7 @@
         <v>1130005</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E267" s="1">
         <v>1</v>
@@ -15235,7 +15261,7 @@
         <v>1</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M267" s="1">
         <v>2130005</v>
@@ -15243,17 +15269,17 @@
       <c r="N267" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O267" s="1" t="s">
-        <v>479</v>
+      <c r="O267" s="12" t="s">
+        <v>482</v>
       </c>
       <c r="R267" s="1">
         <v>999999</v>
       </c>
       <c r="T267" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="268" spans="1:20">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="268" ht="18" customHeight="1" spans="1:20">
       <c r="A268" s="1">
         <v>1130006</v>
       </c>
@@ -15261,7 +15287,7 @@
         <v>1130006</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E268" s="1">
         <v>1</v>
@@ -15279,7 +15305,7 @@
         <v>1</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="M268" s="1">
         <v>2130006</v>
@@ -15287,14 +15313,14 @@
       <c r="N268" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="O268" s="1" t="s">
-        <v>483</v>
+      <c r="O268" s="12" t="s">
+        <v>486</v>
       </c>
       <c r="R268" s="1">
         <v>999999</v>
       </c>
       <c r="T268" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="269" spans="1:20">
@@ -15305,7 +15331,7 @@
         <v>1131001</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E269" s="1">
         <v>2</v>
@@ -15323,7 +15349,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M269" s="1">
         <v>2131001</v>
@@ -15332,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="R269" s="1">
         <v>999999</v>
@@ -15346,7 +15372,7 @@
         <v>1131002</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E270" s="1">
         <v>2</v>
@@ -15364,7 +15390,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M270" s="1">
         <v>2131002</v>
@@ -15373,7 +15399,7 @@
         <v>0</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="R270" s="1">
         <v>999999</v>
@@ -15387,7 +15413,7 @@
         <v>1131003</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E271" s="1">
         <v>2</v>
@@ -15405,7 +15431,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M271" s="1">
         <v>2131003</v>
@@ -15414,7 +15440,7 @@
         <v>0</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R271" s="1">
         <v>999999</v>
@@ -15428,7 +15454,7 @@
         <v>1131004</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E272" s="1">
         <v>2</v>
@@ -15446,7 +15472,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="M272" s="1">
         <v>2131004</v>
@@ -15455,7 +15481,7 @@
         <v>0</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="R272" s="1">
         <v>999999</v>
@@ -15468,8 +15494,8 @@
       <c r="C273" s="1">
         <v>1131005</v>
       </c>
-      <c r="D273" s="15" t="s">
-        <v>497</v>
+      <c r="D273" s="16" t="s">
+        <v>500</v>
       </c>
       <c r="E273" s="1">
         <v>2</v>
@@ -15487,7 +15513,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M273" s="1">
         <v>2131005</v>
@@ -15496,7 +15522,7 @@
         <v>0</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="R273" s="1">
         <v>999999</v>
@@ -15510,7 +15536,7 @@
         <v>1131006</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E274" s="1">
         <v>2</v>
@@ -15528,7 +15554,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M274" s="1">
         <v>2131006</v>
@@ -15537,7 +15563,7 @@
         <v>0</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="R274" s="1">
         <v>999999</v>
@@ -15551,7 +15577,7 @@
         <v>1131101</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E275" s="1">
         <v>2</v>
@@ -15569,7 +15595,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M275" s="1">
         <v>2131001</v>
@@ -15578,7 +15604,7 @@
         <v>0</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="R275" s="1">
         <v>999999</v>
@@ -15592,7 +15618,7 @@
         <v>1131102</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E276" s="1">
         <v>2</v>
@@ -15610,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="M276" s="1">
         <v>2131002</v>
@@ -15619,7 +15645,7 @@
         <v>0</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="R276" s="1">
         <v>999999</v>
@@ -15633,7 +15659,7 @@
         <v>1131103</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E277" s="1">
         <v>2</v>
@@ -15651,7 +15677,7 @@
         <v>0</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M277" s="1">
         <v>2131003</v>
@@ -15660,7 +15686,7 @@
         <v>0</v>
       </c>
       <c r="O277" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R277" s="1">
         <v>999999</v>
@@ -15674,7 +15700,7 @@
         <v>1131104</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E278" s="1">
         <v>2</v>
@@ -15692,7 +15718,7 @@
         <v>0</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="M278" s="1">
         <v>2131004</v>
@@ -15701,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="R278" s="1">
         <v>999999</v>
@@ -15714,8 +15740,8 @@
       <c r="C279" s="1">
         <v>1131105</v>
       </c>
-      <c r="D279" s="15" t="s">
-        <v>511</v>
+      <c r="D279" s="16" t="s">
+        <v>514</v>
       </c>
       <c r="E279" s="1">
         <v>2</v>
@@ -15733,7 +15759,7 @@
         <v>0</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M279" s="1">
         <v>2131005</v>
@@ -15742,7 +15768,7 @@
         <v>0</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="R279" s="1">
         <v>999999</v>
@@ -15756,7 +15782,7 @@
         <v>1131106</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E280" s="1">
         <v>2</v>
@@ -15774,7 +15800,7 @@
         <v>0</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M280" s="1">
         <v>2131006</v>
@@ -15783,7 +15809,7 @@
         <v>0</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="R280" s="1">
         <v>999999</v>
@@ -15797,7 +15823,7 @@
         <v>1131201</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E281" s="1">
         <v>2</v>
@@ -15815,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M281" s="1">
         <v>2131001</v>
@@ -15824,7 +15850,7 @@
         <v>0</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="R281" s="1">
         <v>999999</v>
@@ -15838,7 +15864,7 @@
         <v>1131202</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E282" s="1">
         <v>2</v>
@@ -15856,7 +15882,7 @@
         <v>0</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="M282" s="1">
         <v>2131002</v>
@@ -15865,7 +15891,7 @@
         <v>0</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="R282" s="1">
         <v>999999</v>
@@ -15879,7 +15905,7 @@
         <v>1131203</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E283" s="1">
         <v>2</v>
@@ -15897,7 +15923,7 @@
         <v>0</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M283" s="1">
         <v>2131003</v>
@@ -15906,7 +15932,7 @@
         <v>0</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R283" s="1">
         <v>999999</v>
@@ -15920,7 +15946,7 @@
         <v>1131204</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E284" s="1">
         <v>2</v>
@@ -15938,7 +15964,7 @@
         <v>0</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="M284" s="1">
         <v>2131004</v>
@@ -15947,7 +15973,7 @@
         <v>0</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="R284" s="1">
         <v>999999</v>
@@ -15960,8 +15986,8 @@
       <c r="C285" s="1">
         <v>1131205</v>
       </c>
-      <c r="D285" s="15" t="s">
-        <v>524</v>
+      <c r="D285" s="16" t="s">
+        <v>527</v>
       </c>
       <c r="E285" s="1">
         <v>2</v>
@@ -15979,7 +16005,7 @@
         <v>0</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="M285" s="1">
         <v>2131005</v>
@@ -15988,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="R285" s="1">
         <v>999999</v>
@@ -16002,7 +16028,7 @@
         <v>1131206</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E286" s="1">
         <v>2</v>
@@ -16020,7 +16046,7 @@
         <v>0</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M286" s="1">
         <v>2131006</v>
@@ -16029,7 +16055,7 @@
         <v>0</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="R286" s="1">
         <v>999999</v>
@@ -16043,7 +16069,7 @@
         <v>1131301</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E287" s="1">
         <v>2</v>
@@ -16061,7 +16087,7 @@
         <v>0</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M287" s="1">
         <v>2131001</v>
@@ -16070,7 +16096,7 @@
         <v>0</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="R287" s="1">
         <v>999999</v>
@@ -16084,7 +16110,7 @@
         <v>1131302</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E288" s="1">
         <v>2</v>
@@ -16102,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M288" s="1">
         <v>2131002</v>
@@ -16111,7 +16137,7 @@
         <v>0</v>
       </c>
       <c r="O288" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="R288" s="1">
         <v>999999</v>
@@ -16125,7 +16151,7 @@
         <v>1131303</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E289" s="1">
         <v>2</v>
@@ -16143,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="M289" s="1">
         <v>2131003</v>
@@ -16152,7 +16178,7 @@
         <v>0</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R289" s="1">
         <v>999999</v>
@@ -16166,7 +16192,7 @@
         <v>1131304</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E290" s="1">
         <v>2</v>
@@ -16184,7 +16210,7 @@
         <v>0</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="M290" s="1">
         <v>2131004</v>
@@ -16193,7 +16219,7 @@
         <v>0</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="R290" s="1">
         <v>999999</v>
@@ -16206,8 +16232,8 @@
       <c r="C291" s="1">
         <v>1131305</v>
       </c>
-      <c r="D291" s="15" t="s">
-        <v>537</v>
+      <c r="D291" s="16" t="s">
+        <v>540</v>
       </c>
       <c r="E291" s="1">
         <v>2</v>
@@ -16225,7 +16251,7 @@
         <v>0</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="M291" s="1">
         <v>2131005</v>
@@ -16234,7 +16260,7 @@
         <v>0</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="R291" s="1">
         <v>999999</v>
@@ -16248,7 +16274,7 @@
         <v>1131306</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E292" s="1">
         <v>2</v>
@@ -16266,7 +16292,7 @@
         <v>0</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M292" s="1">
         <v>2131006</v>
@@ -16275,7 +16301,7 @@
         <v>0</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="R292" s="1">
         <v>999999</v>
@@ -16289,7 +16315,7 @@
         <v>1131401</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E293" s="1">
         <v>2</v>
@@ -16307,7 +16333,7 @@
         <v>0</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M293" s="1">
         <v>2131001</v>
@@ -16316,7 +16342,7 @@
         <v>0</v>
       </c>
       <c r="O293" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="R293" s="1">
         <v>999999</v>
@@ -16330,7 +16356,7 @@
         <v>1131402</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E294" s="1">
         <v>2</v>
@@ -16348,7 +16374,7 @@
         <v>0</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M294" s="1">
         <v>2131002</v>
@@ -16357,7 +16383,7 @@
         <v>0</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="R294" s="1">
         <v>999999</v>
@@ -16371,7 +16397,7 @@
         <v>1131403</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E295" s="1">
         <v>2</v>
@@ -16389,7 +16415,7 @@
         <v>0</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="M295" s="1">
         <v>2131003</v>
@@ -16398,7 +16424,7 @@
         <v>0</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="R295" s="1">
         <v>999999</v>
@@ -16412,7 +16438,7 @@
         <v>1131404</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E296" s="1">
         <v>2</v>
@@ -16430,7 +16456,7 @@
         <v>0</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M296" s="1">
         <v>2131004</v>
@@ -16439,7 +16465,7 @@
         <v>0</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="R296" s="1">
         <v>999999</v>
@@ -16452,8 +16478,8 @@
       <c r="C297" s="1">
         <v>1131405</v>
       </c>
-      <c r="D297" s="15" t="s">
-        <v>549</v>
+      <c r="D297" s="16" t="s">
+        <v>552</v>
       </c>
       <c r="E297" s="1">
         <v>2</v>
@@ -16471,7 +16497,7 @@
         <v>0</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="M297" s="1">
         <v>2131005</v>
@@ -16480,7 +16506,7 @@
         <v>0</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="R297" s="1">
         <v>999999</v>
@@ -16494,7 +16520,7 @@
         <v>1131406</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E298" s="1">
         <v>2</v>
@@ -16512,7 +16538,7 @@
         <v>0</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="M298" s="1">
         <v>2131006</v>
@@ -16521,7 +16547,7 @@
         <v>0</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="R298" s="1">
         <v>999999</v>
@@ -16535,7 +16561,7 @@
         <v>1140001</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E299" s="1">
         <v>2</v>
@@ -16553,7 +16579,7 @@
         <v>0</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="M299" s="1">
         <v>2140001</v>
@@ -16562,7 +16588,7 @@
         <v>0</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="R299" s="1">
         <v>1</v>
@@ -16576,7 +16602,7 @@
         <v>1140002</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E300" s="1">
         <v>2</v>
@@ -16594,7 +16620,7 @@
         <v>0</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M300" s="1">
         <v>2140002</v>
@@ -16603,7 +16629,7 @@
         <v>0</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="R300" s="1">
         <v>1</v>
@@ -16617,7 +16643,7 @@
         <v>1140003</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E301" s="1">
         <v>2</v>
@@ -16635,7 +16661,7 @@
         <v>0</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M301" s="1">
         <v>2140003</v>
@@ -16644,7 +16670,7 @@
         <v>0</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="R301" s="1">
         <v>1</v>
@@ -16658,7 +16684,7 @@
         <v>1140004</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E302" s="1">
         <v>2</v>
@@ -16676,7 +16702,7 @@
         <v>0</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M302" s="1">
         <v>2140004</v>
@@ -16685,7 +16711,7 @@
         <v>0</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="R302" s="1">
         <v>1</v>
@@ -16699,7 +16725,7 @@
         <v>1140005</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E303" s="1">
         <v>2</v>
@@ -16717,7 +16743,7 @@
         <v>0</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M303" s="1">
         <v>2140005</v>
@@ -16726,7 +16752,7 @@
         <v>0</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="R303" s="1">
         <v>1</v>
@@ -16740,7 +16766,7 @@
         <v>1140006</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E304" s="1">
         <v>2</v>
@@ -16758,7 +16784,7 @@
         <v>0</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M304" s="1">
         <v>2140006</v>
@@ -16767,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="R304" s="1">
         <v>1</v>
@@ -16781,7 +16807,7 @@
         <v>1150001</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E305" s="1">
         <v>2</v>
@@ -16799,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M305" s="1">
         <v>2150001</v>
@@ -16823,7 +16849,7 @@
         <v>1150002</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E306" s="1">
         <v>2</v>
@@ -16841,7 +16867,7 @@
         <v>0</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M306" s="1">
         <v>2150002</v>
@@ -16865,7 +16891,7 @@
         <v>1150003</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E307" s="1">
         <v>2</v>
@@ -16883,7 +16909,7 @@
         <v>0</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="M307" s="1">
         <v>2150003</v>
@@ -16907,7 +16933,7 @@
         <v>1150004</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E308" s="1">
         <v>2</v>
@@ -16925,7 +16951,7 @@
         <v>0</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="M308" s="1">
         <v>2150004</v>
@@ -16949,7 +16975,7 @@
         <v>1150005</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E309" s="1">
         <v>2</v>
@@ -16967,7 +16993,7 @@
         <v>0</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="M309" s="1">
         <v>2150005</v>
@@ -16991,7 +17017,7 @@
         <v>1150006</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E310" s="1">
         <v>2</v>
@@ -17009,7 +17035,7 @@
         <v>0</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M310" s="1">
         <v>2150006</v>
@@ -17033,7 +17059,7 @@
         <v>1150007</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E311" s="1">
         <v>2</v>
@@ -17051,7 +17077,7 @@
         <v>0</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M311" s="1">
         <v>2150007</v>
@@ -17075,7 +17101,7 @@
         <v>1150008</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E312" s="1">
         <v>2</v>
@@ -17093,7 +17119,7 @@
         <v>0</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="M312" s="1">
         <v>2150008</v>
@@ -17117,7 +17143,7 @@
         <v>1150009</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E313" s="1">
         <v>2</v>
@@ -17135,7 +17161,7 @@
         <v>0</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="M313" s="1">
         <v>2150009</v>
@@ -17159,7 +17185,7 @@
         <v>1150010</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E314" s="1">
         <v>2</v>
@@ -17177,7 +17203,7 @@
         <v>0</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M314" s="1">
         <v>2150010</v>
@@ -17201,7 +17227,7 @@
         <v>1150011</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E315" s="1">
         <v>2</v>
@@ -17219,7 +17245,7 @@
         <v>0</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M315" s="1">
         <v>2150011</v>
@@ -17243,7 +17269,7 @@
         <v>1150012</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E316" s="1">
         <v>2</v>
@@ -17261,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="M316" s="1">
         <v>2150012</v>
@@ -17285,7 +17311,7 @@
         <v>1150013</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E317" s="1">
         <v>2</v>
@@ -17303,7 +17329,7 @@
         <v>0</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M317" s="1">
         <v>2150013</v>
@@ -17327,7 +17353,7 @@
         <v>1150014</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E318" s="1">
         <v>2</v>
@@ -17345,7 +17371,7 @@
         <v>0</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="M318" s="1">
         <v>2150014</v>
@@ -17369,7 +17395,7 @@
         <v>1150015</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E319" s="1">
         <v>2</v>
@@ -17387,7 +17413,7 @@
         <v>0</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="M319" s="1">
         <v>2150015</v>
@@ -17411,7 +17437,7 @@
         <v>1150016</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E320" s="1">
         <v>2</v>
@@ -17429,7 +17455,7 @@
         <v>0</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="M320" s="1">
         <v>2150016</v>
@@ -17453,7 +17479,7 @@
         <v>1150017</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E321" s="1">
         <v>2</v>
@@ -17471,7 +17497,7 @@
         <v>0</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M321" s="1">
         <v>2150017</v>
@@ -17495,7 +17521,7 @@
         <v>1150018</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E322" s="1">
         <v>2</v>
@@ -17513,7 +17539,7 @@
         <v>0</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="M322" s="1">
         <v>2150018</v>
@@ -17537,7 +17563,7 @@
         <v>1150019</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E323" s="1">
         <v>2</v>
@@ -17555,7 +17581,7 @@
         <v>0</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M323" s="1">
         <v>2150019</v>
@@ -17579,7 +17605,7 @@
         <v>1150020</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E324" s="1">
         <v>2</v>
@@ -17597,7 +17623,7 @@
         <v>0</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="M324" s="1">
         <v>2150020</v>
@@ -17621,7 +17647,7 @@
         <v>1150021</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E325" s="1">
         <v>2</v>
@@ -17639,7 +17665,7 @@
         <v>0</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M325" s="1">
         <v>2150021</v>
@@ -17663,7 +17689,7 @@
         <v>1150022</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E326" s="1">
         <v>2</v>
@@ -17681,7 +17707,7 @@
         <v>0</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="M326" s="1">
         <v>2150022</v>
@@ -17705,7 +17731,7 @@
         <v>1150023</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E327" s="1">
         <v>2</v>
@@ -17723,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="M327" s="1">
         <v>2150023</v>
@@ -17747,7 +17773,7 @@
         <v>1150024</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="E328" s="1">
         <v>2</v>
@@ -17765,7 +17791,7 @@
         <v>0</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="M328" s="1">
         <v>2150024</v>
@@ -17789,7 +17815,7 @@
         <v>1150025</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E329" s="1">
         <v>2</v>
@@ -17807,7 +17833,7 @@
         <v>0</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="M329" s="1">
         <v>2150025</v>
@@ -17831,7 +17857,7 @@
         <v>1150026</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="E330" s="1">
         <v>2</v>
@@ -17849,7 +17875,7 @@
         <v>0</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="M330" s="1">
         <v>2150026</v>
@@ -17873,7 +17899,7 @@
         <v>1150027</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E331" s="1">
         <v>2</v>
@@ -17891,7 +17917,7 @@
         <v>0</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="M331" s="1">
         <v>2150027</v>
@@ -17915,7 +17941,7 @@
         <v>1150028</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E332" s="1">
         <v>2</v>
@@ -17933,7 +17959,7 @@
         <v>0</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="M332" s="1">
         <v>2150028</v>
@@ -17957,7 +17983,7 @@
         <v>1150029</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="E333" s="1">
         <v>2</v>
@@ -17975,7 +18001,7 @@
         <v>0</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M333" s="1">
         <v>2150029</v>
@@ -17999,7 +18025,7 @@
         <v>1150030</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="E334" s="1">
         <v>2</v>
@@ -18017,7 +18043,7 @@
         <v>0</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="M334" s="1">
         <v>2150030</v>
@@ -18041,7 +18067,7 @@
         <v>1150031</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E335" s="1">
         <v>2</v>
@@ -18059,7 +18085,7 @@
         <v>0</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="M335" s="1">
         <v>2150031</v>
@@ -18083,7 +18109,7 @@
         <v>1150032</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="E336" s="1">
         <v>2</v>
@@ -18101,7 +18127,7 @@
         <v>0</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="M336" s="1">
         <v>2150032</v>
@@ -18125,7 +18151,7 @@
         <v>1150033</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="E337" s="1">
         <v>2</v>
@@ -18143,7 +18169,7 @@
         <v>0</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M337" s="1">
         <v>2150033</v>
@@ -18167,7 +18193,7 @@
         <v>1150034</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="E338" s="1">
         <v>2</v>
@@ -18185,7 +18211,7 @@
         <v>0</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="M338" s="1">
         <v>2150034</v>
@@ -18209,7 +18235,7 @@
         <v>1150035</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="E339" s="1">
         <v>2</v>
@@ -18227,7 +18253,7 @@
         <v>0</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="M339" s="1">
         <v>2150035</v>
@@ -18251,7 +18277,7 @@
         <v>1150036</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E340" s="1">
         <v>2</v>
@@ -18269,7 +18295,7 @@
         <v>0</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M340" s="1">
         <v>2150036</v>
@@ -18293,7 +18319,7 @@
         <v>1150037</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="E341" s="1">
         <v>2</v>
@@ -18311,7 +18337,7 @@
         <v>0</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="M341" s="1">
         <v>2150037</v>
@@ -18335,7 +18361,7 @@
         <v>1150038</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="E342" s="1">
         <v>2</v>
@@ -18353,7 +18379,7 @@
         <v>0</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="M342" s="1">
         <v>2150038</v>
@@ -18377,7 +18403,7 @@
         <v>1150039</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="E343" s="1">
         <v>2</v>
@@ -18395,7 +18421,7 @@
         <v>0</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="M343" s="1">
         <v>2150039</v>
@@ -18419,7 +18445,7 @@
         <v>1150040</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="E344" s="1">
         <v>2</v>
@@ -18437,7 +18463,7 @@
         <v>0</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="M344" s="1">
         <v>2150040</v>
@@ -18461,7 +18487,7 @@
         <v>1150041</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="E345" s="1">
         <v>2</v>
@@ -18479,7 +18505,7 @@
         <v>0</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="M345" s="1">
         <v>2150041</v>
@@ -18503,7 +18529,7 @@
         <v>1150042</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E346" s="1">
         <v>2</v>
@@ -18521,7 +18547,7 @@
         <v>0</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="M346" s="1">
         <v>2150042</v>
@@ -18545,7 +18571,7 @@
         <v>1150043</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="E347" s="1">
         <v>2</v>
@@ -18563,7 +18589,7 @@
         <v>0</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="M347" s="1">
         <v>2150043</v>
@@ -18587,7 +18613,7 @@
         <v>1150044</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="E348" s="1">
         <v>2</v>
@@ -18605,7 +18631,7 @@
         <v>0</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="M348" s="1">
         <v>2150044</v>
@@ -18629,7 +18655,7 @@
         <v>1150045</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E349" s="1">
         <v>2</v>
@@ -18647,7 +18673,7 @@
         <v>0</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="M349" s="1">
         <v>2150045</v>
@@ -18671,7 +18697,7 @@
         <v>1150046</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E350" s="1">
         <v>2</v>
@@ -18689,7 +18715,7 @@
         <v>0</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="M350" s="1">
         <v>2150046</v>
@@ -18713,7 +18739,7 @@
         <v>1150047</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="E351" s="1">
         <v>2</v>
@@ -18731,7 +18757,7 @@
         <v>0</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="M351" s="1">
         <v>2150047</v>
@@ -18755,7 +18781,7 @@
         <v>1150048</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E352" s="1">
         <v>2</v>
@@ -18773,7 +18799,7 @@
         <v>0</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="M352" s="1">
         <v>2150048</v>
@@ -18797,7 +18823,7 @@
         <v>1150049</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E353" s="1">
         <v>2</v>
@@ -18815,7 +18841,7 @@
         <v>0</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="M353" s="1">
         <v>2150049</v>
@@ -18839,7 +18865,7 @@
         <v>1150050</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E354" s="1">
         <v>2</v>
@@ -18857,7 +18883,7 @@
         <v>0</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="M354" s="1">
         <v>2150050</v>
@@ -18881,7 +18907,7 @@
         <v>1150051</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E355" s="1">
         <v>2</v>
@@ -18899,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="M355" s="1">
         <v>2150051</v>
@@ -18923,7 +18949,7 @@
         <v>1150052</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="E356" s="1">
         <v>2</v>
@@ -18941,7 +18967,7 @@
         <v>0</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="M356" s="1">
         <v>2150052</v>
@@ -18965,7 +18991,7 @@
         <v>1150053</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="E357" s="1">
         <v>2</v>
@@ -18983,7 +19009,7 @@
         <v>0</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="M357" s="1">
         <v>2150053</v>
@@ -19007,7 +19033,7 @@
         <v>1150054</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E358" s="1">
         <v>2</v>
@@ -19025,7 +19051,7 @@
         <v>0</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="M358" s="1">
         <v>2150054</v>
@@ -19049,7 +19075,7 @@
         <v>1150055</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="E359" s="1">
         <v>2</v>
@@ -19067,7 +19093,7 @@
         <v>0</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="M359" s="1">
         <v>2150055</v>
@@ -19091,7 +19117,7 @@
         <v>1150056</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E360" s="1">
         <v>2</v>
@@ -19109,7 +19135,7 @@
         <v>0</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="M360" s="1">
         <v>2150056</v>
@@ -19133,7 +19159,7 @@
         <v>1150057</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E361" s="1">
         <v>2</v>
@@ -19151,7 +19177,7 @@
         <v>0</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="M361" s="1">
         <v>2150057</v>
@@ -19175,7 +19201,7 @@
         <v>1150058</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E362" s="1">
         <v>2</v>
@@ -19193,7 +19219,7 @@
         <v>0</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="M362" s="1">
         <v>2150058</v>
@@ -19217,7 +19243,7 @@
         <v>1150059</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E363" s="1">
         <v>2</v>
@@ -19235,7 +19261,7 @@
         <v>0</v>
       </c>
       <c r="L363" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="M363" s="1">
         <v>2150059</v>
@@ -19259,7 +19285,7 @@
         <v>1150060</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E364" s="1">
         <v>2</v>
@@ -19277,7 +19303,7 @@
         <v>0</v>
       </c>
       <c r="L364" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="M364" s="1">
         <v>2150060</v>
@@ -19301,7 +19327,7 @@
         <v>1150061</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="E365" s="1">
         <v>2</v>
@@ -19319,7 +19345,7 @@
         <v>0</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="M365" s="1">
         <v>2150061</v>

--- a/ploy/resources/sample/Item.xlsx
+++ b/ploy/resources/sample/Item.xlsx
@@ -386,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="726">
   <si>
     <t>道具ID</t>
   </si>
@@ -958,24 +958,36 @@
     <t>加速建筑升级的CD时间</t>
   </si>
   <si>
-    <t>雇员升级材料1</t>
+    <t>胜运砾石</t>
   </si>
   <si>
     <t>daoju_cailiao_1.png</t>
   </si>
   <si>
-    <t>雇员升级材料2</t>
+    <t>雇员游戏经理升级所需要的经验材料
+获取途径：游客在场景中进行交互概率掉落</t>
+  </si>
+  <si>
+    <t>鸿运原石</t>
   </si>
   <si>
     <t>daoju_cailiao_2.png</t>
   </si>
   <si>
-    <t>雇员升级材料3</t>
+    <t>雇员服务经理升级所需要的经验材料
+获取途径：游客在场景中进行交互概率掉落</t>
+  </si>
+  <si>
+    <t>幸运宝石</t>
   </si>
   <si>
     <t>daoju_cailiao_3.png</t>
   </si>
   <si>
+    <t>雇员管理经理升级所需要的经验材料
+获取途径：游客在场景中进行交互概率掉落</t>
+  </si>
+  <si>
     <t>声誉值</t>
   </si>
   <si>
@@ -994,37 +1006,41 @@
     <t>联盟商店兑换商品的道具</t>
   </si>
   <si>
-    <t>游客抽卡道具</t>
+    <t>游客邀请函</t>
   </si>
   <si>
     <t>daoju_ykck.png</t>
   </si>
   <si>
-    <t>用于游客卡池抽奖的道具</t>
-  </si>
-  <si>
-    <t>雇员抽卡道具</t>
+    <t>用于游客卡池抽奖的道具
+获取途径：可以通过完成多人任务奖励获得</t>
+  </si>
+  <si>
+    <t>雇员邀请函</t>
   </si>
   <si>
     <t>daoju_gyck.png</t>
   </si>
   <si>
-    <t>用于雇员卡池抽卡的道具</t>
-  </si>
-  <si>
-    <t>游客人员邀请函</t>
-  </si>
-  <si>
-    <t>用于指定生成游客人员的道具</t>
+    <t>用于雇员卡池抽卡的道具
+获取途径：可以通过完成多人任务奖励获得</t>
+  </si>
+  <si>
+    <t>名流招商卡</t>
+  </si>
+  <si>
+    <t>用于指定生成游客人员的道具
+获取途径：商城购买</t>
   </si>
   <si>
     <t>1025101_1;1025102_1;1025103_1;1025104_1;1025105_1;1025106_1;1025201_1;1025202_1;1025203_1;1025204_1;1025205_1;1025206_1;1025301_1;1025302_1;1025303_1;1025304_1;1025305_1;1025306_1;1025401_1;1025402_1;1025403_1;1025404_1;1025405_1;1025406_1;1025501_1;1025502_1;1025503_1;1025504_1;1025505_1;1025506_1</t>
   </si>
   <si>
-    <t>游客品质邀请函</t>
-  </si>
-  <si>
-    <t>用于指定生成某类品质游客的道具</t>
+    <t>富豪招商卡</t>
+  </si>
+  <si>
+    <t>用于指定生成某类品质游客的道具
+获取途径：商城购买</t>
   </si>
   <si>
     <t>1024019_1;1024020_1;1024021_1;1024022_1;1024023_1</t>
@@ -1033,7 +1049,8 @@
     <t>联盟任务补充券</t>
   </si>
   <si>
-    <t>用于补充联盟任务的道具</t>
+    <t>用于补充联盟任务的道具
+获取途径：钻石购买</t>
   </si>
   <si>
     <t>试玩体力</t>
@@ -1288,31 +1305,31 @@
     <t>1025506_1</t>
   </si>
   <si>
-    <t>白色品质游客邀请函</t>
+    <t>游客招商卡.白</t>
   </si>
   <si>
     <t>使用该道具后可以指定生成白色品质游客中的任意一个</t>
   </si>
   <si>
-    <t>绿色品质游客邀请函</t>
+    <t>游客招商卡.绿</t>
   </si>
   <si>
     <t>使用该道具后可以指定生成绿色品质游客中的任意一个</t>
   </si>
   <si>
-    <t>蓝色品质游客邀请函</t>
+    <t>游客招商卡.蓝</t>
   </si>
   <si>
     <t>使用该道具后可以指定生成蓝色品质游客中的任意一个</t>
   </si>
   <si>
-    <t>紫色品质游客邀请函</t>
+    <t>游客招商卡.紫</t>
   </si>
   <si>
     <t>使用该道具后可以指定生成紫色品质游客中的任意一个</t>
   </si>
   <si>
-    <t>橙色品质游客邀请函</t>
+    <t>游客招商卡.橙</t>
   </si>
   <si>
     <t>使用该道具后可以指定生成橙色品质游客中的任意一个</t>
@@ -1387,180 +1404,270 @@
     <t>yk_jtcr.png</t>
   </si>
   <si>
+    <t>无拘无束，随性洒脱，热爱自由与冒险，独立而充满活力的生活态度。</t>
+  </si>
+  <si>
     <t>复古绅士</t>
   </si>
   <si>
     <t>yk_fgss.png</t>
   </si>
   <si>
+    <t>温和内敛，对复古文化有着深厚情感，绅士风度和怀旧气息兼具。</t>
+  </si>
+  <si>
     <t>酷盖少年</t>
   </si>
   <si>
     <t>yk_kgsn.png</t>
   </si>
   <si>
+    <t>叛逆不羁，果断有个性，外表冷酷内心火热，对主流规则有自己的态度。</t>
+  </si>
+  <si>
     <t>潮流先锋</t>
   </si>
   <si>
     <t>yk_clxf.png</t>
   </si>
   <si>
+    <t>大胆前卫、个性鲜明，对时尚有着敏锐嗅觉，敢于尝试各种混搭风格。</t>
+  </si>
+  <si>
     <t>时尚教主</t>
   </si>
   <si>
     <t>yk_ssjz.png</t>
   </si>
   <si>
+    <t>阳光积极，充满正能量，将运动与时尚完美融合，做事充满行动力。</t>
+  </si>
+  <si>
     <t>街拍达人</t>
   </si>
   <si>
     <t>yk_jpdr.png</t>
   </si>
   <si>
+    <t>性格开朗，善于交流，对美有着独特视角，善于用镜头记录生活。</t>
+  </si>
+  <si>
     <t>运动健将</t>
   </si>
   <si>
     <t>yk_ydjj.png</t>
   </si>
   <si>
+    <t>自律进取，意志坚定，性格直爽讲义气，对健身有着近乎执着的追求。</t>
+  </si>
+  <si>
     <t>跑酷少年</t>
   </si>
   <si>
     <t>yk_pksn.png</t>
   </si>
   <si>
+    <t>性格坚韧不服输，骨子里流淌着冒险血液，追求极限与自由。</t>
+  </si>
+  <si>
     <t>滑板高手</t>
   </si>
   <si>
     <t>yk_hbgs.png</t>
   </si>
   <si>
+    <t>开朗随和，随性洒脱，热爱滑板文化，善于用运动表达态度。</t>
+  </si>
+  <si>
     <t>甜心辣妹</t>
   </si>
   <si>
     <t>yk_txlm.png</t>
   </si>
   <si>
+    <t>活泼开朗爱撒娇，对舞蹈和表演有天赋，善于用笑容感染他人。</t>
+  </si>
+  <si>
     <t>活力少女</t>
   </si>
   <si>
     <t>yk_hlsn.png</t>
   </si>
   <si>
+    <t>温柔有耐心，热爱运动和自然，善于帮助和鼓励身边的人。</t>
+  </si>
+  <si>
     <t>优雅女神</t>
   </si>
   <si>
     <t>yk_yyns.png</t>
   </si>
   <si>
+    <t>高贵内敛，沉稳大方，气质高雅，举手投足间散发独特魅力。</t>
+  </si>
+  <si>
     <t>健身狂魔</t>
   </si>
   <si>
     <t>yk_jskm.png</t>
   </si>
   <si>
+    <t>豪爽直率，意志如钢铁般坚定，对健美有着近乎疯狂的执着。</t>
+  </si>
+  <si>
     <t>单车骑士</t>
   </si>
   <si>
     <t>yk_dcqs.png</t>
   </si>
   <si>
+    <t>性格沉稳专注，对骑行有着纯粹热爱，追求速度与耐力极限。</t>
+  </si>
+  <si>
     <t>登山行者</t>
   </si>
   <si>
     <t>yk_dsxz.png</t>
   </si>
   <si>
+    <t>坚韧乐观，骨子里流淌着探险血液，勇于挑战自然极限。</t>
+  </si>
+  <si>
     <t>文艺青年</t>
   </si>
   <si>
     <t>yk_wyqn.png</t>
   </si>
   <si>
+    <t>性格安静沉思，对艺术有着敏锐感知力，内心世界丰富细腻。</t>
+  </si>
+  <si>
     <t>书香少女</t>
   </si>
   <si>
     <t>yk_sxsn.png</t>
   </si>
   <si>
+    <t>知性浪漫，温柔细腻，对文学有着深厚热爱，内心世界如诗集般美好。</t>
+  </si>
+  <si>
     <t>民谣歌手</t>
   </si>
   <si>
     <t>yk_mygs.png</t>
   </si>
   <si>
+    <t>温暖感性，对音乐有着纯粹热爱，用歌声讲述人生故事。</t>
+  </si>
+  <si>
     <t>马拉松客</t>
   </si>
   <si>
     <t>yk_mlsk.png</t>
   </si>
   <si>
+    <t>坚韧不拔，对马拉松有着执着追求，意志力超群。</t>
+  </si>
+  <si>
     <t>极限玩家</t>
   </si>
   <si>
     <t>yk_jxwj.png</t>
   </si>
   <si>
+    <t>大胆冒险，无所畏惧，追求极致刺激和冒险体验。</t>
+  </si>
+  <si>
     <t>科技极客</t>
   </si>
   <si>
     <t>yk_kjjk.png</t>
   </si>
   <si>
+    <t>性格内向但才华横溢，对科技有着狂热追求，思维敏捷逻辑清晰。</t>
+  </si>
+  <si>
     <t>独立画家</t>
   </si>
   <si>
     <t>yk_dlhj.png</t>
   </si>
   <si>
+    <t>性格敏感浪漫，善于用色彩表达情感，对艺术有着纯粹热爱。</t>
+  </si>
+  <si>
     <t>浪漫诗人</t>
   </si>
   <si>
     <t>yk_lmsr.png</t>
   </si>
   <si>
+    <t>性格温柔浪漫，善于用文字记录感动，内心世界如诗歌般优美。</t>
+  </si>
+  <si>
     <t>古典乐迷</t>
   </si>
   <si>
     <t>yk_gdlm.png</t>
   </si>
   <si>
+    <t>性格内敛深沉，品味高雅讲究，对古典音乐有着深厚造诣。</t>
+  </si>
+  <si>
     <t>创业新贵</t>
   </si>
   <si>
     <t>yk_cyxg.png</t>
   </si>
   <si>
+    <t>自信强势，眼光敏锐决策果断，对商业成功有着强烈渴望。</t>
+  </si>
+  <si>
     <t>摸金校尉</t>
   </si>
   <si>
     <t>yk_mjxw.png</t>
   </si>
   <si>
+    <t>行事低调内敛，性格沉稳睿智，对古董研究有着深厚学识。</t>
+  </si>
+  <si>
     <t>氪金大佬</t>
   </si>
   <si>
     <t>yk_kjdl.png</t>
   </si>
   <si>
+    <t>性格直率豪爽，天生王者气场，出手阔绰毫不吝啬。</t>
+  </si>
+  <si>
     <t>穿搭博主</t>
   </si>
   <si>
     <t>yk_cdbz.png</t>
   </si>
   <si>
+    <t>自信开朗，善于表达，对时尚有着极致追求，镜头感极强。</t>
+  </si>
+  <si>
     <t>美妆新秀</t>
   </si>
   <si>
     <t>yk_mzxx.png</t>
   </si>
   <si>
+    <t>热情大方，对美妆有着专业热情，善于发现每个人的美。</t>
+  </si>
+  <si>
     <t>高定女王</t>
   </si>
   <si>
     <t>yk_gdnw.png</t>
   </si>
   <si>
+    <t>高贵从容，举手投足间散发着贵族般的优雅与威严，对品质有极致追求。</t>
+  </si>
+  <si>
     <t>daoju_yk_jtcr.png</t>
   </si>
   <si>
@@ -1780,7 +1887,8 @@
     <t>daoju_tzj.png</t>
   </si>
   <si>
-    <t>用于主动匹配所消耗的道具</t>
+    <t>用于主动匹配所消耗的道具
+获取途径：商城购买</t>
   </si>
   <si>
     <t>白色宝石箱</t>
@@ -1789,7 +1897,8 @@
     <t>daoju_baox_b.png</t>
   </si>
   <si>
-    <t>可以指定开出任意白色宝石的箱子</t>
+    <t>可以指定开出任意白色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131001_1;1131002_1;1131003_1;1131004_1;1131005_1;1131006_1</t>
@@ -1801,7 +1910,8 @@
     <t>daoju_baox_lv.png</t>
   </si>
   <si>
-    <t>可以指定开出任意绿色宝石的箱子</t>
+    <t>可以指定开出任意绿色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131101_1;1131102_1;1131103_1;1131104_1;1131105_1;1131106_1</t>
@@ -1813,7 +1923,8 @@
     <t>daoju_baox_lan.png</t>
   </si>
   <si>
-    <t>可以指定开出任意蓝色宝石的箱子</t>
+    <t>可以指定开出任意蓝色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131201_1;1131202_1;1131203_1;1131204_1;1131205_1;1131206_1</t>
@@ -1825,7 +1936,8 @@
     <t>daoju_baox_zi.png</t>
   </si>
   <si>
-    <t>可以指定开出任意紫色宝石的箱子</t>
+    <t>可以指定开出任意紫色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131301_1;1131302_1;1131303_1;1131304_1;1131305_1;1131306_1</t>
@@ -1837,7 +1949,8 @@
     <t>daoju_baox_ju.png</t>
   </si>
   <si>
-    <t>可以指定开出任意橙色宝石的箱子</t>
+    <t>可以指定开出任意橙色宝石的箱子
+获取途径：赛季商店进行兑换</t>
   </si>
   <si>
     <t>1131401_1;1131402_1;1131403_1;1131404_1;1131405_1;1131406_1</t>
@@ -2477,7 +2590,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2510,6 +2623,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -3010,16 +3129,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3028,119 +3144,122 @@
     <xf numFmtId="0" fon